--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -14340,10 +14340,10 @@
         <v>300</v>
       </c>
       <c r="N326" t="n">
-        <v>169.22033898305</v>
+        <v>156</v>
       </c>
       <c r="O326" t="n">
-        <v>50766.101694915</v>
+        <v>46800</v>
       </c>
       <c r="P326" t="n">
         <v>195</v>
@@ -15473,10 +15473,10 @@
         <v>172</v>
       </c>
       <c r="N352" t="n">
-        <v>4242.3899305556</v>
+        <v>4193.85</v>
       </c>
       <c r="O352" t="n">
-        <v>729691.0680555631</v>
+        <v>721342.2000000001</v>
       </c>
       <c r="P352" t="n">
         <v>7500</v>
@@ -15653,10 +15653,10 @@
         <v>99</v>
       </c>
       <c r="N356" t="n">
-        <v>6470.8036363636</v>
+        <v>6441.03</v>
       </c>
       <c r="O356" t="n">
-        <v>640609.5599999964</v>
+        <v>637661.97</v>
       </c>
       <c r="P356" t="n">
         <v>10500</v>
@@ -23501,10 +23501,10 @@
         <v>116</v>
       </c>
       <c r="N538" t="n">
-        <v>1406.381965812</v>
+        <v>1359.89</v>
       </c>
       <c r="O538" t="n">
-        <v>163140.308034192</v>
+        <v>157747.24</v>
       </c>
       <c r="P538" t="n">
         <v>2600</v>
@@ -23542,10 +23542,10 @@
         <v>73</v>
       </c>
       <c r="N539" t="n">
-        <v>2109.2758108108</v>
+        <v>2081.1521621622</v>
       </c>
       <c r="O539" t="n">
-        <v>153977.1341891884</v>
+        <v>151924.1078378406</v>
       </c>
       <c r="P539" t="n">
         <v>3000</v>
@@ -28126,10 +28126,10 @@
         <v>37</v>
       </c>
       <c r="N645" t="n">
-        <v>4254.3242335766</v>
+        <v>4163.1601459854</v>
       </c>
       <c r="O645" t="n">
-        <v>157409.9966423342</v>
+        <v>154036.9254014598</v>
       </c>
       <c r="P645" t="n">
         <v>6700</v>
@@ -28310,10 +28310,10 @@
         <v>38</v>
       </c>
       <c r="N649" t="n">
-        <v>5234.4433367983</v>
+        <v>5218.1704573805</v>
       </c>
       <c r="O649" t="n">
-        <v>198908.8467983354</v>
+        <v>198290.477380459</v>
       </c>
       <c r="P649" t="n">
         <v>8500</v>
@@ -28678,10 +28678,10 @@
         <v>36</v>
       </c>
       <c r="N657" t="n">
-        <v>1821.7243939394</v>
+        <v>1812.57</v>
       </c>
       <c r="O657" t="n">
-        <v>65582.0781818184</v>
+        <v>65252.52</v>
       </c>
       <c r="P657" t="n">
         <v>2900</v>
@@ -28908,10 +28908,10 @@
         <v>48</v>
       </c>
       <c r="N662" t="n">
-        <v>15692.208588957</v>
+        <v>15502</v>
       </c>
       <c r="O662" t="n">
-        <v>753226.012269936</v>
+        <v>744096</v>
       </c>
       <c r="P662" t="n">
         <v>25900</v>
@@ -39221,10 +39221,10 @@
         <v>467</v>
       </c>
       <c r="N886" t="n">
-        <v>2861.1357880311</v>
+        <v>2857.22</v>
       </c>
       <c r="O886" t="n">
-        <v>1336150.413010524</v>
+        <v>1334321.74</v>
       </c>
       <c r="P886" t="n">
         <v>4900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1440,10 +1440,10 @@
         <v>13</v>
       </c>
       <c r="N25" t="n">
-        <v>27225.941422594</v>
+        <v>27000</v>
       </c>
       <c r="O25" t="n">
-        <v>353937.238493722</v>
+        <v>351000</v>
       </c>
       <c r="P25" t="n">
         <v>30000</v>
@@ -1677,10 +1677,10 @@
         <v>55</v>
       </c>
       <c r="N31" t="n">
-        <v>5784.4419026549</v>
+        <v>5758.9597787611</v>
       </c>
       <c r="O31" t="n">
-        <v>318144.3046460195</v>
+        <v>316742.7878318605</v>
       </c>
       <c r="P31" t="n">
         <v>16900</v>
@@ -2809,10 +2809,10 @@
         <v>48</v>
       </c>
       <c r="N59" t="n">
-        <v>4644.5877192982</v>
+        <v>4604.2</v>
       </c>
       <c r="O59" t="n">
-        <v>222940.2105263136</v>
+        <v>221001.6</v>
       </c>
       <c r="P59" t="n">
         <v>7500</v>
@@ -3335,10 +3335,10 @@
         <v>205</v>
       </c>
       <c r="N72" t="n">
-        <v>2421.5176470588</v>
+        <v>2413.0011764706</v>
       </c>
       <c r="O72" t="n">
-        <v>496411.117647054</v>
+        <v>494665.241176473</v>
       </c>
       <c r="P72" t="n">
         <v>4700</v>
@@ -3374,10 +3374,10 @@
         <v>74</v>
       </c>
       <c r="N73" t="n">
-        <v>2487.0572046589</v>
+        <v>2474.7042429285</v>
       </c>
       <c r="O73" t="n">
-        <v>184042.2331447586</v>
+        <v>183128.113976709</v>
       </c>
       <c r="P73" t="n">
         <v>4500</v>
@@ -3803,10 +3803,10 @@
         <v>17</v>
       </c>
       <c r="N84" t="n">
-        <v>21510.733070539</v>
+        <v>21333.69</v>
       </c>
       <c r="O84" t="n">
-        <v>365682.462199163</v>
+        <v>362672.73</v>
       </c>
       <c r="P84" t="n">
         <v>30000</v>
@@ -4995,10 +4995,10 @@
         <v>20</v>
       </c>
       <c r="N111" t="n">
-        <v>20547.289545455</v>
+        <v>18835.016818182</v>
       </c>
       <c r="O111" t="n">
-        <v>410945.7909091</v>
+        <v>376700.33636364</v>
       </c>
       <c r="P111" t="n">
         <v>40500</v>
@@ -5160,10 +5160,10 @@
         <v>13</v>
       </c>
       <c r="N115" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="O115" t="n">
-        <v>205851.308710944</v>
+        <v>204255.561757819</v>
       </c>
       <c r="P115" t="n">
         <v>28500</v>
@@ -5207,10 +5207,10 @@
         <v>11</v>
       </c>
       <c r="N116" t="n">
-        <v>9642.5297333333</v>
+        <v>9392.0745333333</v>
       </c>
       <c r="O116" t="n">
-        <v>106067.8270666663</v>
+        <v>103312.8198666663</v>
       </c>
       <c r="P116" t="n">
         <v>18500</v>
@@ -8195,10 +8195,10 @@
         <v>34</v>
       </c>
       <c r="N185" t="n">
-        <v>27232.75862069</v>
+        <v>27000</v>
       </c>
       <c r="O185" t="n">
-        <v>925913.79310346</v>
+        <v>918000</v>
       </c>
       <c r="P185" t="n">
         <v>20000</v>
@@ -8312,10 +8312,10 @@
         <v>36</v>
       </c>
       <c r="N188" t="n">
-        <v>8104.9092</v>
+        <v>8046.39</v>
       </c>
       <c r="O188" t="n">
-        <v>291776.7312</v>
+        <v>289670.04</v>
       </c>
       <c r="P188" t="n">
         <v>20900</v>
@@ -8721,10 +8721,10 @@
         <v>13</v>
       </c>
       <c r="N197" t="n">
-        <v>7477.1013333333</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O197" t="n">
-        <v>97202.3173333329</v>
+        <v>96134.1607777772</v>
       </c>
       <c r="P197" t="n">
         <v>17900</v>
@@ -9236,10 +9236,10 @@
         <v>34</v>
       </c>
       <c r="N209" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="O209" t="n">
-        <v>87614.68994708841</v>
+        <v>87153.56</v>
       </c>
       <c r="P209" t="n">
         <v>4700</v>
@@ -9324,10 +9324,10 @@
         <v>18</v>
       </c>
       <c r="N211" t="n">
-        <v>11705.0765</v>
+        <v>11513.19</v>
       </c>
       <c r="O211" t="n">
-        <v>210691.377</v>
+        <v>207237.42</v>
       </c>
       <c r="P211" t="n">
         <v>17900</v>
@@ -11631,10 +11631,10 @@
         <v>2</v>
       </c>
       <c r="N265" t="n">
-        <v>13624.59908046</v>
+        <v>13593.35</v>
       </c>
       <c r="O265" t="n">
-        <v>27249.19816092</v>
+        <v>27186.7</v>
       </c>
       <c r="P265" t="n">
         <v>25500</v>
@@ -14125,10 +14125,10 @@
         <v>1601</v>
       </c>
       <c r="N321" t="n">
-        <v>2289.4664730119</v>
+        <v>2267.0481788216</v>
       </c>
       <c r="O321" t="n">
-        <v>3665435.823292051</v>
+        <v>3629544.134293381</v>
       </c>
       <c r="P321" t="n">
         <v>3900</v>
@@ -14906,10 +14906,10 @@
         <v>129</v>
       </c>
       <c r="N339" t="n">
-        <v>4898.3218562874</v>
+        <v>4891</v>
       </c>
       <c r="O339" t="n">
-        <v>631883.5194610746</v>
+        <v>630939</v>
       </c>
       <c r="P339" t="n">
         <v>8200</v>
@@ -17017,10 +17017,10 @@
         <v>110</v>
       </c>
       <c r="N387" t="n">
-        <v>2225.439688716</v>
+        <v>2204</v>
       </c>
       <c r="O387" t="n">
-        <v>244798.36575876</v>
+        <v>242440</v>
       </c>
       <c r="P387" t="n">
         <v>1500</v>
@@ -21249,10 +21249,10 @@
         <v>66</v>
       </c>
       <c r="N484" t="n">
-        <v>2667.5690712743</v>
+        <v>2661.82</v>
       </c>
       <c r="O484" t="n">
-        <v>176059.5587041038</v>
+        <v>175680.12</v>
       </c>
       <c r="P484" t="n">
         <v>3200</v>
@@ -21331,10 +21331,10 @@
         <v>159</v>
       </c>
       <c r="N486" t="n">
-        <v>4508.1255605381</v>
+        <v>4488</v>
       </c>
       <c r="O486" t="n">
-        <v>716791.9641255579</v>
+        <v>713592</v>
       </c>
       <c r="P486" t="n">
         <v>6200</v>
@@ -21372,10 +21372,10 @@
         <v>107</v>
       </c>
       <c r="N487" t="n">
-        <v>2613.7446197991</v>
+        <v>2610</v>
       </c>
       <c r="O487" t="n">
-        <v>279670.6743185037</v>
+        <v>279270</v>
       </c>
       <c r="P487" t="n">
         <v>3200</v>
@@ -21495,10 +21495,10 @@
         <v>76</v>
       </c>
       <c r="N490" t="n">
-        <v>2306.01</v>
+        <v>2286.55</v>
       </c>
       <c r="O490" t="n">
-        <v>175256.76</v>
+        <v>173777.8</v>
       </c>
       <c r="P490" t="n">
         <v>3200</v>
@@ -24541,10 +24541,10 @@
         <v>61</v>
       </c>
       <c r="N562" t="n">
-        <v>13805.304244604</v>
+        <v>13513.64294964</v>
       </c>
       <c r="O562" t="n">
-        <v>842123.558920844</v>
+        <v>824332.2199280399</v>
       </c>
       <c r="P562" t="n">
         <v>21900</v>
@@ -26097,10 +26097,10 @@
         <v>122</v>
       </c>
       <c r="N598" t="n">
-        <v>5453.6557676349</v>
+        <v>5431.12</v>
       </c>
       <c r="O598" t="n">
-        <v>665346.0036514578</v>
+        <v>662596.64</v>
       </c>
       <c r="P598" t="n">
         <v>8900</v>
@@ -26317,10 +26317,10 @@
         <v>40</v>
       </c>
       <c r="N603" t="n">
-        <v>27226.972222222</v>
+        <v>26854</v>
       </c>
       <c r="O603" t="n">
-        <v>1089078.88888888</v>
+        <v>1074160</v>
       </c>
       <c r="P603" t="n">
         <v>43900</v>
@@ -27001,10 +27001,10 @@
         <v>55</v>
       </c>
       <c r="N619" t="n">
-        <v>13971.496466667</v>
+        <v>13878.97</v>
       </c>
       <c r="O619" t="n">
-        <v>768432.305666685</v>
+        <v>763343.35</v>
       </c>
       <c r="P619" t="n">
         <v>21900</v>
@@ -27550,10 +27550,10 @@
         <v>36</v>
       </c>
       <c r="N632" t="n">
-        <v>4692.9807692308</v>
+        <v>4437</v>
       </c>
       <c r="O632" t="n">
-        <v>168947.3076923088</v>
+        <v>159732</v>
       </c>
       <c r="P632" t="n">
         <v>4900</v>
@@ -27906,10 +27906,10 @@
         <v>75</v>
       </c>
       <c r="N640" t="n">
-        <v>3117.5970357143</v>
+        <v>3113.8900238095</v>
       </c>
       <c r="O640" t="n">
-        <v>233819.7776785725</v>
+        <v>233541.7517857125</v>
       </c>
       <c r="P640" t="n">
         <v>5000</v>
@@ -28136,10 +28136,10 @@
         <v>78</v>
       </c>
       <c r="N645" t="n">
-        <v>9099.032608695699</v>
+        <v>8878.450000000001</v>
       </c>
       <c r="O645" t="n">
-        <v>709724.5434782646</v>
+        <v>692519.1000000001</v>
       </c>
       <c r="P645" t="n">
         <v>14100</v>
@@ -28182,10 +28182,10 @@
         <v>35</v>
       </c>
       <c r="N646" t="n">
-        <v>2498.7228351648</v>
+        <v>2495.98</v>
       </c>
       <c r="O646" t="n">
-        <v>87455.299230768</v>
+        <v>87359.3</v>
       </c>
       <c r="P646" t="n">
         <v>4100</v>
@@ -28504,10 +28504,10 @@
         <v>65</v>
       </c>
       <c r="N653" t="n">
-        <v>3969.9272029703</v>
+        <v>3965.02</v>
       </c>
       <c r="O653" t="n">
-        <v>258045.2681930695</v>
+        <v>257726.3</v>
       </c>
       <c r="P653" t="n">
         <v>6500</v>
@@ -28550,10 +28550,10 @@
         <v>90</v>
       </c>
       <c r="N654" t="n">
-        <v>5844.4237327189</v>
+        <v>5791.05</v>
       </c>
       <c r="O654" t="n">
-        <v>525998.135944701</v>
+        <v>521194.5</v>
       </c>
       <c r="P654" t="n">
         <v>9300</v>
@@ -28642,10 +28642,10 @@
         <v>2</v>
       </c>
       <c r="N656" t="n">
-        <v>1817.3525065963</v>
+        <v>1812.57</v>
       </c>
       <c r="O656" t="n">
-        <v>3634.7050131926</v>
+        <v>3625.14</v>
       </c>
       <c r="P656" t="n">
         <v>2900</v>
@@ -29614,10 +29614,10 @@
         <v>14</v>
       </c>
       <c r="N677" t="n">
-        <v>22795.894912427</v>
+        <v>22739</v>
       </c>
       <c r="O677" t="n">
-        <v>319142.528773978</v>
+        <v>318346</v>
       </c>
       <c r="P677" t="n">
         <v>36900</v>
@@ -29706,10 +29706,10 @@
         <v>61</v>
       </c>
       <c r="N679" t="n">
-        <v>16092.045229682</v>
+        <v>16058</v>
       </c>
       <c r="O679" t="n">
-        <v>981614.759010602</v>
+        <v>979538</v>
       </c>
       <c r="P679" t="n">
         <v>25900</v>
@@ -32516,10 +32516,10 @@
         <v>64</v>
       </c>
       <c r="N740" t="n">
-        <v>21748.414253898</v>
+        <v>21676</v>
       </c>
       <c r="O740" t="n">
-        <v>1391898.512249472</v>
+        <v>1387264</v>
       </c>
       <c r="P740" t="n">
         <v>34900</v>
@@ -34673,10 +34673,10 @@
         <v>301</v>
       </c>
       <c r="N787" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="O787" t="n">
-        <v>1175096.15785442</v>
+        <v>1173298</v>
       </c>
       <c r="P787" t="n">
         <v>6900</v>
@@ -34719,10 +34719,10 @@
         <v>104</v>
       </c>
       <c r="N788" t="n">
-        <v>13585.460030166</v>
+        <v>13565</v>
       </c>
       <c r="O788" t="n">
-        <v>1412887.843137264</v>
+        <v>1410760</v>
       </c>
       <c r="P788" t="n">
         <v>22500</v>
@@ -36422,10 +36422,10 @@
         <v>17</v>
       </c>
       <c r="N825" t="n">
-        <v>21937.5</v>
+        <v>21762</v>
       </c>
       <c r="O825" t="n">
-        <v>372937.5</v>
+        <v>369954</v>
       </c>
       <c r="P825" t="n">
         <v>35900</v>
@@ -51283,10 +51283,10 @@
         <v>3</v>
       </c>
       <c r="N1154" t="n">
-        <v>449.18534246575</v>
+        <v>415.07</v>
       </c>
       <c r="O1154" t="n">
-        <v>1347.55602739725</v>
+        <v>1245.21</v>
       </c>
       <c r="P1154" t="n">
         <v>2900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -691,10 +691,10 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>96741.40695121999</v>
+        <v>96741.407037037</v>
       </c>
       <c r="O7" t="n">
-        <v>96741.40695121999</v>
+        <v>96741.407037037</v>
       </c>
       <c r="P7" t="n">
         <v>188900</v>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1104,19 +1104,19 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N17" t="n">
         <v>27000</v>
       </c>
       <c r="O17" t="n">
-        <v>783000</v>
+        <v>675000</v>
       </c>
       <c r="P17" t="n">
         <v>20000</v>
       </c>
       <c r="Q17" t="n">
-        <v>580000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="18">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>27</v>
+        <v>241</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1398,19 +1398,19 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>27</v>
+        <v>241</v>
       </c>
       <c r="N24" t="n">
-        <v>1811.3037703513</v>
+        <v>1815.9962867012</v>
       </c>
       <c r="O24" t="n">
-        <v>48905.2017994851</v>
+        <v>437655.1050949892</v>
       </c>
       <c r="P24" t="n">
         <v>2600</v>
       </c>
       <c r="Q24" t="n">
-        <v>70200</v>
+        <v>626600</v>
       </c>
     </row>
     <row r="25">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1476,19 +1476,19 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N26" t="n">
-        <v>1990.0436380597</v>
+        <v>2001.2446341463</v>
       </c>
       <c r="O26" t="n">
-        <v>153233.3601305969</v>
+        <v>148092.1029268262</v>
       </c>
       <c r="P26" t="n">
         <v>4400</v>
       </c>
       <c r="Q26" t="n">
-        <v>338800</v>
+        <v>325600</v>
       </c>
     </row>
     <row r="27">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3009,19 +3009,19 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>6272.8541142857</v>
+        <v>6300.2067296512</v>
       </c>
       <c r="O64" t="n">
-        <v>276005.5810285708</v>
+        <v>258308.4759156992</v>
       </c>
       <c r="P64" t="n">
         <v>7900</v>
       </c>
       <c r="Q64" t="n">
-        <v>347600</v>
+        <v>323900</v>
       </c>
     </row>
     <row r="65">
@@ -3129,10 +3129,10 @@
         <v>48</v>
       </c>
       <c r="N67" t="n">
-        <v>3926.8371340839</v>
+        <v>3926.8371326165</v>
       </c>
       <c r="O67" t="n">
-        <v>188488.1824360272</v>
+        <v>188488.182365592</v>
       </c>
       <c r="P67" t="n">
         <v>4800</v>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4266,10 +4266,10 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N95" t="n">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="O95" t="n">
         <v>16000</v>
@@ -4278,7 +4278,7 @@
         <v>4800</v>
       </c>
       <c r="Q95" t="n">
-        <v>19200</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="96">
@@ -5079,10 +5079,10 @@
         <v>17</v>
       </c>
       <c r="N113" t="n">
-        <v>16486.41027027</v>
+        <v>16486.410204082</v>
       </c>
       <c r="O113" t="n">
-        <v>280268.97459459</v>
+        <v>280268.973469394</v>
       </c>
       <c r="P113" t="n">
         <v>30500</v>
@@ -5160,10 +5160,10 @@
         <v>13</v>
       </c>
       <c r="N115" t="n">
-        <v>15711.966289063</v>
+        <v>15711.966215139</v>
       </c>
       <c r="O115" t="n">
-        <v>204255.561757819</v>
+        <v>204255.560796807</v>
       </c>
       <c r="P115" t="n">
         <v>28500</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5415,19 +5415,19 @@
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N121" t="n">
         <v>6321.94</v>
       </c>
       <c r="O121" t="n">
-        <v>278165.36</v>
+        <v>246555.66</v>
       </c>
       <c r="P121" t="n">
         <v>14100</v>
       </c>
       <c r="Q121" t="n">
-        <v>620400</v>
+        <v>549900</v>
       </c>
     </row>
     <row r="122">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5493,19 +5493,19 @@
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N123" t="n">
         <v>20195.32</v>
       </c>
       <c r="O123" t="n">
-        <v>343320.44</v>
+        <v>282734.48</v>
       </c>
       <c r="P123" t="n">
         <v>45900</v>
       </c>
       <c r="Q123" t="n">
-        <v>780300</v>
+        <v>642600</v>
       </c>
     </row>
     <row r="124">
@@ -5632,11 +5632,14 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>52698</v>
+        <v>52637</v>
+      </c>
+      <c r="B127" t="n">
+        <v>6941607352212</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>52698 ASPERSOR DEAGUA DINOSAURIOS BESTWAY</t>
+          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5646,11 +5649,11 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5659,37 +5662,42 @@
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N127" t="n">
-        <v>17112</v>
+        <v>22267.552</v>
       </c>
       <c r="O127" t="n">
-        <v>102672</v>
+        <v>111337.76</v>
       </c>
       <c r="P127" t="n">
-        <v>27500</v>
+        <v>46300</v>
       </c>
       <c r="Q127" t="n">
-        <v>165000</v>
+        <v>231500</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>53069</v>
+        <v>52698</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>53069 JUEGO DE PISCINA GRANDE</t>
+          <t>52698 ASPERSOR DEAGUA DINOSAURIOS BESTWAY</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5698,28 +5706,28 @@
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N128" t="n">
-        <v>137679.73</v>
+        <v>17112</v>
       </c>
       <c r="O128" t="n">
-        <v>688398.65</v>
+        <v>102672</v>
       </c>
       <c r="P128" t="n">
-        <v>209900</v>
+        <v>27500</v>
       </c>
       <c r="Q128" t="n">
-        <v>1049500</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>53117</v>
+        <v>53069</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>53117 JUEGO DE PISCINA GRANDE</t>
+          <t>53069 JUEGO DE PISCINA GRANDE</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5728,7 +5736,7 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5737,36 +5745,28 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N129" t="n">
-        <v>152774</v>
+        <v>137679.73</v>
       </c>
       <c r="O129" t="n">
-        <v>305548</v>
+        <v>550718.92</v>
       </c>
       <c r="P129" t="n">
-        <v>244900</v>
+        <v>209900</v>
       </c>
       <c r="Q129" t="n">
-        <v>489800</v>
+        <v>839600</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>53157</v>
-      </c>
-      <c r="B130" t="n">
-        <v>6941607352137</v>
+        <v>53117</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>53117 JUEGO DE PISCINA GRANDE</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5784,28 +5784,31 @@
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>36574.852142857</v>
+        <v>152774</v>
       </c>
       <c r="O130" t="n">
-        <v>585197.634285712</v>
+        <v>305548</v>
       </c>
       <c r="P130" t="n">
-        <v>65900</v>
+        <v>244900</v>
       </c>
       <c r="Q130" t="n">
-        <v>1054400</v>
+        <v>489800</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>53167</v>
+        <v>53157</v>
+      </c>
+      <c r="B131" t="n">
+        <v>6941607352137</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>53167 PARQUE ACUATICO BESTWAY</t>
+          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5815,11 +5818,11 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5828,19 +5831,19 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N131" t="n">
-        <v>140235.34</v>
+        <v>36574.852142857</v>
       </c>
       <c r="O131" t="n">
-        <v>140235.34</v>
+        <v>585197.634285712</v>
       </c>
       <c r="P131" t="n">
-        <v>223900</v>
+        <v>65900</v>
       </c>
       <c r="Q131" t="n">
-        <v>223900</v>
+        <v>1054400</v>
       </c>
     </row>
     <row r="132">
@@ -6174,7 +6177,7 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -6183,19 +6186,19 @@
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N139" t="n">
-        <v>62349.660526316</v>
+        <v>62349.659444444</v>
       </c>
       <c r="O139" t="n">
-        <v>311748.30263158</v>
+        <v>249398.637777776</v>
       </c>
       <c r="P139" t="n">
         <v>109900</v>
       </c>
       <c r="Q139" t="n">
-        <v>549500</v>
+        <v>439600</v>
       </c>
     </row>
     <row r="140">
@@ -6221,7 +6224,7 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -6230,19 +6233,19 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N140" t="n">
-        <v>77455.73765217399</v>
+        <v>77455.73771929801</v>
       </c>
       <c r="O140" t="n">
-        <v>697101.6388695659</v>
+        <v>619645.901754384</v>
       </c>
       <c r="P140" t="n">
         <v>122900</v>
       </c>
       <c r="Q140" t="n">
-        <v>1106100</v>
+        <v>983200</v>
       </c>
     </row>
     <row r="141">
@@ -6280,10 +6283,10 @@
         <v>2</v>
       </c>
       <c r="N141" t="n">
-        <v>141416.8844586</v>
+        <v>141416.88447284</v>
       </c>
       <c r="O141" t="n">
-        <v>282833.7689172</v>
+        <v>282833.76894568</v>
       </c>
       <c r="P141" t="n">
         <v>251900</v>
@@ -6310,7 +6313,7 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -6319,19 +6322,19 @@
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N142" t="n">
-        <v>174389.78666667</v>
+        <v>174389.78756757</v>
       </c>
       <c r="O142" t="n">
-        <v>523169.36000001</v>
+        <v>174389.78756757</v>
       </c>
       <c r="P142" t="n">
         <v>368200</v>
       </c>
       <c r="Q142" t="n">
-        <v>1104600</v>
+        <v>368200</v>
       </c>
     </row>
     <row r="143">
@@ -6416,10 +6419,10 @@
         <v>2</v>
       </c>
       <c r="N144" t="n">
-        <v>344599.17885246</v>
+        <v>344599.17881356</v>
       </c>
       <c r="O144" t="n">
-        <v>689198.35770492</v>
+        <v>689198.35762712</v>
       </c>
       <c r="P144" t="n">
         <v>532900</v>
@@ -8261,7 +8264,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -8270,19 +8273,19 @@
         <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="N187" t="n">
-        <v>3865.67</v>
+        <v>3872.3234767642</v>
       </c>
       <c r="O187" t="n">
-        <v>730611.63</v>
+        <v>720252.1666781412</v>
       </c>
       <c r="P187" t="n">
         <v>5500</v>
       </c>
       <c r="Q187" t="n">
-        <v>1039500</v>
+        <v>1023000</v>
       </c>
     </row>
     <row r="188">
@@ -8484,7 +8487,7 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -8493,19 +8496,19 @@
         <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="N192" t="n">
-        <v>2572.67</v>
+        <v>2589.9594489247</v>
       </c>
       <c r="O192" t="n">
-        <v>105479.47</v>
+        <v>93238.5401612892</v>
       </c>
       <c r="P192" t="n">
         <v>4700</v>
       </c>
       <c r="Q192" t="n">
-        <v>192700</v>
+        <v>169200</v>
       </c>
     </row>
     <row r="193">
@@ -8668,7 +8671,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -8677,19 +8680,19 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="N196" t="n">
-        <v>2570.16</v>
+        <v>2597.4440764331</v>
       </c>
       <c r="O196" t="n">
-        <v>71964.48</v>
+        <v>59741.2137579613</v>
       </c>
       <c r="P196" t="n">
         <v>4700</v>
       </c>
       <c r="Q196" t="n">
-        <v>131600</v>
+        <v>108100</v>
       </c>
     </row>
     <row r="197">
@@ -8748,7 +8751,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -8757,19 +8760,19 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N198" t="n">
-        <v>3114.49</v>
+        <v>3126.0967950311</v>
       </c>
       <c r="O198" t="n">
-        <v>227357.77</v>
+        <v>218826.775652177</v>
       </c>
       <c r="P198" t="n">
         <v>5500</v>
       </c>
       <c r="Q198" t="n">
-        <v>401500</v>
+        <v>385000</v>
       </c>
     </row>
     <row r="199">
@@ -8904,7 +8907,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -8913,19 +8916,19 @@
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N202" t="n">
-        <v>4378</v>
+        <v>4411.4198473282</v>
       </c>
       <c r="O202" t="n">
-        <v>192632</v>
+        <v>180868.2137404562</v>
       </c>
       <c r="P202" t="n">
         <v>3900</v>
       </c>
       <c r="Q202" t="n">
-        <v>171600</v>
+        <v>159900</v>
       </c>
     </row>
     <row r="203">
@@ -9224,7 +9227,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -9233,19 +9236,19 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N209" t="n">
-        <v>2563.34</v>
+        <v>2597.7011260054</v>
       </c>
       <c r="O209" t="n">
-        <v>87153.56</v>
+        <v>75333.33265415661</v>
       </c>
       <c r="P209" t="n">
         <v>4700</v>
       </c>
       <c r="Q209" t="n">
-        <v>159800</v>
+        <v>136300</v>
       </c>
     </row>
     <row r="210">
@@ -9876,7 +9879,7 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -9885,19 +9888,19 @@
         <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="N224" t="n">
-        <v>2833</v>
+        <v>2837.5718128026</v>
       </c>
       <c r="O224" t="n">
-        <v>628926</v>
+        <v>612915.5115653616</v>
       </c>
       <c r="P224" t="n">
         <v>3500</v>
       </c>
       <c r="Q224" t="n">
-        <v>777000</v>
+        <v>756000</v>
       </c>
     </row>
     <row r="225">
@@ -9958,7 +9961,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>1305</v>
+        <v>1552</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -9967,19 +9970,19 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>1305</v>
+        <v>1552</v>
       </c>
       <c r="N226" t="n">
         <v>1726.32</v>
       </c>
       <c r="O226" t="n">
-        <v>2252847.6</v>
+        <v>2679248.64</v>
       </c>
       <c r="P226" t="n">
         <v>1500</v>
       </c>
       <c r="Q226" t="n">
-        <v>1957500</v>
+        <v>2328000</v>
       </c>
     </row>
     <row r="227">
@@ -10057,10 +10060,10 @@
         <v>125</v>
       </c>
       <c r="N228" t="n">
-        <v>4937.3101589595</v>
+        <v>4937.3101595359</v>
       </c>
       <c r="O228" t="n">
-        <v>617163.7698699374</v>
+        <v>617163.7699419876</v>
       </c>
       <c r="P228" t="n">
         <v>7500</v>
@@ -10168,7 +10171,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10177,19 +10180,19 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="N231" t="n">
-        <v>3456.13</v>
+        <v>3489.6196317829</v>
       </c>
       <c r="O231" t="n">
-        <v>573717.5800000001</v>
+        <v>540891.0429263494</v>
       </c>
       <c r="P231" t="n">
         <v>5700</v>
       </c>
       <c r="Q231" t="n">
-        <v>946200</v>
+        <v>883500</v>
       </c>
     </row>
     <row r="232">
@@ -10550,7 +10553,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>883</v>
+        <v>831</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -10559,19 +10562,19 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>883</v>
+        <v>831</v>
       </c>
       <c r="N240" t="n">
-        <v>1098.0525080824</v>
+        <v>1098.0527732407</v>
       </c>
       <c r="O240" t="n">
-        <v>969580.3646367592</v>
+        <v>912481.8545630217</v>
       </c>
       <c r="P240" t="n">
         <v>1500</v>
       </c>
       <c r="Q240" t="n">
-        <v>1324500</v>
+        <v>1246500</v>
       </c>
     </row>
     <row r="241">
@@ -12224,7 +12227,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12233,19 +12236,19 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N279" t="n">
         <v>3247</v>
       </c>
       <c r="O279" t="n">
-        <v>139621</v>
+        <v>103904</v>
       </c>
       <c r="P279" t="n">
         <v>5200</v>
       </c>
       <c r="Q279" t="n">
-        <v>223600</v>
+        <v>166400</v>
       </c>
     </row>
     <row r="280">
@@ -12270,7 +12273,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12279,19 +12282,19 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="N280" t="n">
-        <v>2344</v>
+        <v>2588.3559055118</v>
       </c>
       <c r="O280" t="n">
-        <v>651632</v>
+        <v>688502.6708661388</v>
       </c>
       <c r="P280" t="n">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="Q280" t="n">
-        <v>1167600</v>
+        <v>1197000</v>
       </c>
     </row>
     <row r="281">
@@ -12572,7 +12575,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -12581,19 +12584,19 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N287" t="n">
-        <v>6713.08</v>
+        <v>6816.3581538462</v>
       </c>
       <c r="O287" t="n">
-        <v>208105.48</v>
+        <v>177225.3120000012</v>
       </c>
       <c r="P287" t="n">
         <v>9900</v>
       </c>
       <c r="Q287" t="n">
-        <v>306900</v>
+        <v>257400</v>
       </c>
     </row>
     <row r="288">
@@ -12846,7 +12849,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -12855,19 +12858,19 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N293" t="n">
-        <v>3230.067792</v>
+        <v>3230.0677597403</v>
       </c>
       <c r="O293" t="n">
-        <v>487740.236592</v>
+        <v>478050.0284415644</v>
       </c>
       <c r="P293" t="n">
         <v>6200</v>
       </c>
       <c r="Q293" t="n">
-        <v>936200</v>
+        <v>917600</v>
       </c>
     </row>
     <row r="294">
@@ -13025,7 +13028,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -13034,19 +13037,19 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N297" t="n">
         <v>1337.34</v>
       </c>
       <c r="O297" t="n">
-        <v>468069</v>
+        <v>466731.66</v>
       </c>
       <c r="P297" t="n">
         <v>2500</v>
       </c>
       <c r="Q297" t="n">
-        <v>875000</v>
+        <v>872500</v>
       </c>
     </row>
     <row r="298">
@@ -13158,7 +13161,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13167,19 +13170,19 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="N300" t="n">
         <v>1026.13</v>
       </c>
       <c r="O300" t="n">
-        <v>729578.4300000001</v>
+        <v>711108.0900000001</v>
       </c>
       <c r="P300" t="n">
         <v>1900</v>
       </c>
       <c r="Q300" t="n">
-        <v>1350900</v>
+        <v>1316700</v>
       </c>
     </row>
     <row r="301">
@@ -13296,7 +13299,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -13305,19 +13308,19 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="N303" t="n">
-        <v>7507.39</v>
+        <v>7538.62740638</v>
       </c>
       <c r="O303" t="n">
-        <v>1268748.91</v>
+        <v>1228796.26723994</v>
       </c>
       <c r="P303" t="n">
         <v>13500</v>
       </c>
       <c r="Q303" t="n">
-        <v>2281500</v>
+        <v>2200500</v>
       </c>
     </row>
     <row r="304">
@@ -13345,7 +13348,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -13354,19 +13357,19 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="N304" t="n">
-        <v>8796</v>
+        <v>8907.908396946599</v>
       </c>
       <c r="O304" t="n">
-        <v>1011540</v>
+        <v>908606.6564885532</v>
       </c>
       <c r="P304" t="n">
         <v>14900</v>
       </c>
       <c r="Q304" t="n">
-        <v>1713500</v>
+        <v>1519800</v>
       </c>
     </row>
     <row r="305">
@@ -13527,7 +13530,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -13536,19 +13539,19 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="N308" t="n">
-        <v>3795.7100070299</v>
+        <v>3801.7317574476</v>
       </c>
       <c r="O308" t="n">
-        <v>1180465.812186299</v>
+        <v>1148122.990749175</v>
       </c>
       <c r="P308" t="n">
         <v>6200</v>
       </c>
       <c r="Q308" t="n">
-        <v>1928200</v>
+        <v>1872400</v>
       </c>
     </row>
     <row r="309">
@@ -13573,7 +13576,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -13582,19 +13585,19 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="N309" t="n">
-        <v>3684</v>
+        <v>3695.2967632027</v>
       </c>
       <c r="O309" t="n">
-        <v>1016784</v>
+        <v>986644.2357751209</v>
       </c>
       <c r="P309" t="n">
         <v>6200</v>
       </c>
       <c r="Q309" t="n">
-        <v>1711200</v>
+        <v>1655400</v>
       </c>
     </row>
     <row r="310">
@@ -13793,7 +13796,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -13802,19 +13805,19 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="N314" t="n">
-        <v>4890.9300454545</v>
+        <v>4890.930045977</v>
       </c>
       <c r="O314" t="n">
-        <v>405947.1937727235</v>
+        <v>308128.592896551</v>
       </c>
       <c r="P314" t="n">
         <v>8200</v>
       </c>
       <c r="Q314" t="n">
-        <v>680600</v>
+        <v>516600</v>
       </c>
     </row>
     <row r="315">
@@ -13851,10 +13854,10 @@
         <v>76</v>
       </c>
       <c r="N315" t="n">
-        <v>5484.9473809524</v>
+        <v>5484.947804878</v>
       </c>
       <c r="O315" t="n">
-        <v>416856.0009523824</v>
+        <v>416856.033170728</v>
       </c>
       <c r="P315" t="n">
         <v>8500</v>
@@ -13888,7 +13891,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>1045</v>
+        <v>1001</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -13897,19 +13900,19 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>1045</v>
+        <v>1001</v>
       </c>
       <c r="N316" t="n">
-        <v>1203.38</v>
+        <v>1213.150338295</v>
       </c>
       <c r="O316" t="n">
-        <v>1257532.1</v>
+        <v>1214363.488633295</v>
       </c>
       <c r="P316" t="n">
         <v>1900</v>
       </c>
       <c r="Q316" t="n">
-        <v>1985500</v>
+        <v>1901900</v>
       </c>
     </row>
     <row r="317">
@@ -13934,7 +13937,7 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>821</v>
+        <v>710</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -13943,19 +13946,19 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>821</v>
+        <v>710</v>
       </c>
       <c r="N317" t="n">
         <v>3472</v>
       </c>
       <c r="O317" t="n">
-        <v>2850512</v>
+        <v>2465120</v>
       </c>
       <c r="P317" t="n">
         <v>4800</v>
       </c>
       <c r="Q317" t="n">
-        <v>3940800</v>
+        <v>3408000</v>
       </c>
     </row>
     <row r="318">
@@ -13980,7 +13983,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -13989,19 +13992,19 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N318" t="n">
         <v>5888</v>
       </c>
       <c r="O318" t="n">
-        <v>341504</v>
+        <v>329728</v>
       </c>
       <c r="P318" t="n">
         <v>9500</v>
       </c>
       <c r="Q318" t="n">
-        <v>551000</v>
+        <v>532000</v>
       </c>
     </row>
     <row r="319">
@@ -14113,7 +14116,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>1601</v>
+        <v>1580</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14122,19 +14125,19 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>1601</v>
+        <v>1580</v>
       </c>
       <c r="N321" t="n">
-        <v>2267.0481788216</v>
+        <v>2286.8353823774</v>
       </c>
       <c r="O321" t="n">
-        <v>3629544.134293381</v>
+        <v>3613199.904156292</v>
       </c>
       <c r="P321" t="n">
         <v>3900</v>
       </c>
       <c r="Q321" t="n">
-        <v>6243900</v>
+        <v>6162000</v>
       </c>
     </row>
     <row r="322">
@@ -14241,7 +14244,7 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -14250,19 +14253,19 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N324" t="n">
         <v>7041</v>
       </c>
       <c r="O324" t="n">
-        <v>415419</v>
+        <v>359091</v>
       </c>
       <c r="P324" t="n">
         <v>11500</v>
       </c>
       <c r="Q324" t="n">
-        <v>678500</v>
+        <v>586500</v>
       </c>
     </row>
     <row r="325">
@@ -14287,7 +14290,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -14296,19 +14299,19 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N325" t="n">
         <v>5667.94</v>
       </c>
       <c r="O325" t="n">
-        <v>379751.98</v>
+        <v>340076.4</v>
       </c>
       <c r="P325" t="n">
         <v>9500</v>
       </c>
       <c r="Q325" t="n">
-        <v>636500</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="326">
@@ -14379,7 +14382,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -14388,19 +14391,19 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N327" t="n">
-        <v>8662</v>
+        <v>8687.96003996</v>
       </c>
       <c r="O327" t="n">
-        <v>424438</v>
+        <v>390958.2017982</v>
       </c>
       <c r="P327" t="n">
         <v>14200</v>
       </c>
       <c r="Q327" t="n">
-        <v>695800</v>
+        <v>639000</v>
       </c>
     </row>
     <row r="328">
@@ -14679,7 +14682,7 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -14688,19 +14691,19 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N334" t="n">
-        <v>3594.2542583732</v>
+        <v>3594.2542480527</v>
       </c>
       <c r="O334" t="n">
-        <v>298323.1034449756</v>
+        <v>294728.8483403214</v>
       </c>
       <c r="P334" t="n">
         <v>6500</v>
       </c>
       <c r="Q334" t="n">
-        <v>539500</v>
+        <v>533000</v>
       </c>
     </row>
     <row r="335">
@@ -14773,10 +14776,10 @@
         <v>5</v>
       </c>
       <c r="N336" t="n">
-        <v>10803.271052632</v>
+        <v>10803.27125</v>
       </c>
       <c r="O336" t="n">
-        <v>54016.35526316</v>
+        <v>54016.35625</v>
       </c>
       <c r="P336" t="n">
         <v>5000</v>
@@ -14807,7 +14810,7 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -14816,19 +14819,19 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N337" t="n">
         <v>2953.73</v>
       </c>
       <c r="O337" t="n">
-        <v>605514.65</v>
+        <v>599607.1900000001</v>
       </c>
       <c r="P337" t="n">
         <v>4900</v>
       </c>
       <c r="Q337" t="n">
-        <v>1004500</v>
+        <v>994700</v>
       </c>
     </row>
     <row r="338">
@@ -14848,7 +14851,7 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -14857,19 +14860,19 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N338" t="n">
-        <v>3240.8500291121</v>
+        <v>3240.8500291545</v>
       </c>
       <c r="O338" t="n">
-        <v>816694.2073362492</v>
+        <v>813453.3573177796</v>
       </c>
       <c r="P338" t="n">
         <v>5200</v>
       </c>
       <c r="Q338" t="n">
-        <v>1310400</v>
+        <v>1305200</v>
       </c>
     </row>
     <row r="339">
@@ -14894,7 +14897,7 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
@@ -14903,19 +14906,19 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="N339" t="n">
         <v>4891</v>
       </c>
       <c r="O339" t="n">
-        <v>630939</v>
+        <v>601593</v>
       </c>
       <c r="P339" t="n">
         <v>8200</v>
       </c>
       <c r="Q339" t="n">
-        <v>1057800</v>
+        <v>1008600</v>
       </c>
     </row>
     <row r="340">
@@ -14940,7 +14943,7 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
@@ -14949,19 +14952,19 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N340" t="n">
-        <v>8154</v>
+        <v>8209.849315068501</v>
       </c>
       <c r="O340" t="n">
-        <v>334314</v>
+        <v>287344.7260273976</v>
       </c>
       <c r="P340" t="n">
         <v>13500</v>
       </c>
       <c r="Q340" t="n">
-        <v>553500</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="341">
@@ -14984,7 +14987,7 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>1655</v>
+        <v>1646</v>
       </c>
       <c r="K341" t="n">
         <v>0</v>
@@ -14993,19 +14996,19 @@
         <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>1655</v>
+        <v>1646</v>
       </c>
       <c r="N341" t="n">
-        <v>616.01871952955</v>
+        <v>616.28176305926</v>
       </c>
       <c r="O341" t="n">
-        <v>1019510.980821405</v>
+        <v>1014399.781995542</v>
       </c>
       <c r="P341" t="n">
         <v>800</v>
       </c>
       <c r="Q341" t="n">
-        <v>1324000</v>
+        <v>1316800</v>
       </c>
     </row>
     <row r="342">
@@ -15028,7 +15031,7 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>335</v>
+        <v>115</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -15037,19 +15040,19 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>335</v>
+        <v>115</v>
       </c>
       <c r="N342" t="n">
         <v>2090.85</v>
       </c>
       <c r="O342" t="n">
-        <v>700434.75</v>
+        <v>240447.75</v>
       </c>
       <c r="P342" t="n">
         <v>2900</v>
       </c>
       <c r="Q342" t="n">
-        <v>971500</v>
+        <v>333500</v>
       </c>
     </row>
     <row r="343">
@@ -15113,7 +15116,7 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
@@ -15122,19 +15125,19 @@
         <v>0</v>
       </c>
       <c r="M344" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N344" t="n">
-        <v>5191.4800265252</v>
+        <v>5191.4800265604</v>
       </c>
       <c r="O344" t="n">
-        <v>1770294.689045093</v>
+        <v>1765103.209030536</v>
       </c>
       <c r="P344" t="n">
         <v>9100</v>
       </c>
       <c r="Q344" t="n">
-        <v>3103100</v>
+        <v>3094000</v>
       </c>
     </row>
     <row r="345">
@@ -15250,7 +15253,7 @@
         </is>
       </c>
       <c r="J347" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="K347" t="n">
         <v>0</v>
@@ -15259,19 +15262,19 @@
         <v>0</v>
       </c>
       <c r="M347" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N347" t="n">
         <v>1381.75</v>
       </c>
       <c r="O347" t="n">
-        <v>341292.25</v>
+        <v>333001.75</v>
       </c>
       <c r="P347" t="n">
         <v>2500</v>
       </c>
       <c r="Q347" t="n">
-        <v>617500</v>
+        <v>602500</v>
       </c>
     </row>
     <row r="348">
@@ -15381,7 +15384,7 @@
         </is>
       </c>
       <c r="J350" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K350" t="n">
         <v>0</v>
@@ -15390,19 +15393,19 @@
         <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="N350" t="n">
         <v>3309</v>
       </c>
       <c r="O350" t="n">
-        <v>360681</v>
+        <v>340827</v>
       </c>
       <c r="P350" t="n">
         <v>5900</v>
       </c>
       <c r="Q350" t="n">
-        <v>643100</v>
+        <v>607700</v>
       </c>
     </row>
     <row r="351">
@@ -15425,7 +15428,7 @@
         </is>
       </c>
       <c r="J351" t="n">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
@@ -15434,19 +15437,19 @@
         <v>0</v>
       </c>
       <c r="M351" t="n">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="N351" t="n">
         <v>1441.01</v>
       </c>
       <c r="O351" t="n">
-        <v>626839.35</v>
+        <v>623957.33</v>
       </c>
       <c r="P351" t="n">
         <v>2100</v>
       </c>
       <c r="Q351" t="n">
-        <v>913500</v>
+        <v>909300</v>
       </c>
     </row>
     <row r="352">
@@ -15466,7 +15469,7 @@
         </is>
       </c>
       <c r="J352" t="n">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
@@ -15475,19 +15478,19 @@
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="N352" t="n">
         <v>4193.85</v>
       </c>
       <c r="O352" t="n">
-        <v>721342.2000000001</v>
+        <v>515843.55</v>
       </c>
       <c r="P352" t="n">
         <v>7500</v>
       </c>
       <c r="Q352" t="n">
-        <v>1290000</v>
+        <v>922500</v>
       </c>
     </row>
     <row r="353">
@@ -15527,10 +15530,10 @@
         <v>429</v>
       </c>
       <c r="N353" t="n">
-        <v>3041.6600123153</v>
+        <v>3041.6600123457</v>
       </c>
       <c r="O353" t="n">
-        <v>1304872.145283264</v>
+        <v>1304872.145296305</v>
       </c>
       <c r="P353" t="n">
         <v>5500</v>
@@ -15614,16 +15617,16 @@
         <v>115</v>
       </c>
       <c r="N355" t="n">
-        <v>4086.2</v>
+        <v>4372.2107862617</v>
       </c>
       <c r="O355" t="n">
-        <v>469913</v>
+        <v>502804.2404200956</v>
       </c>
       <c r="P355" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q355" t="n">
-        <v>793500</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="356">
@@ -15646,7 +15649,7 @@
         </is>
       </c>
       <c r="J356" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="K356" t="n">
         <v>0</v>
@@ -15655,19 +15658,19 @@
         <v>0</v>
       </c>
       <c r="M356" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="N356" t="n">
-        <v>6441.03</v>
+        <v>6493.1840890688</v>
       </c>
       <c r="O356" t="n">
-        <v>528164.46</v>
+        <v>441536.5180566784</v>
       </c>
       <c r="P356" t="n">
         <v>10500</v>
       </c>
       <c r="Q356" t="n">
-        <v>861000</v>
+        <v>714000</v>
       </c>
     </row>
     <row r="357">
@@ -15692,7 +15695,7 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -15701,19 +15704,19 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N357" t="n">
-        <v>1592.567808681</v>
+        <v>1592.5677691978</v>
       </c>
       <c r="O357" t="n">
-        <v>50962.169877792</v>
+        <v>31851.355383956</v>
       </c>
       <c r="P357" t="n">
         <v>3900</v>
       </c>
       <c r="Q357" t="n">
-        <v>124800</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="358">
@@ -15820,7 +15823,7 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
@@ -15829,19 +15832,19 @@
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="N360" t="n">
-        <v>3655.96</v>
+        <v>3660.708</v>
       </c>
       <c r="O360" t="n">
-        <v>471618.84</v>
+        <v>450267.084</v>
       </c>
       <c r="P360" t="n">
         <v>5500</v>
       </c>
       <c r="Q360" t="n">
-        <v>709500</v>
+        <v>676500</v>
       </c>
     </row>
     <row r="361">
@@ -16169,7 +16172,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -16178,19 +16181,19 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="N368" t="n">
         <v>5633.97</v>
       </c>
       <c r="O368" t="n">
-        <v>281698.5</v>
+        <v>185921.01</v>
       </c>
       <c r="P368" t="n">
         <v>9600</v>
       </c>
       <c r="Q368" t="n">
-        <v>480000</v>
+        <v>316800</v>
       </c>
     </row>
     <row r="369">
@@ -16215,7 +16218,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -16224,19 +16227,19 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="N369" t="n">
         <v>6242.93</v>
       </c>
       <c r="O369" t="n">
-        <v>755394.53</v>
+        <v>680479.37</v>
       </c>
       <c r="P369" t="n">
         <v>10400</v>
       </c>
       <c r="Q369" t="n">
-        <v>1258400</v>
+        <v>1133600</v>
       </c>
     </row>
     <row r="370">
@@ -16396,7 +16399,7 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
@@ -16405,19 +16408,19 @@
         <v>0</v>
       </c>
       <c r="M373" t="n">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="N373" t="n">
         <v>1312.43</v>
       </c>
       <c r="O373" t="n">
-        <v>904264.27</v>
+        <v>896389.6900000001</v>
       </c>
       <c r="P373" t="n">
         <v>2300</v>
       </c>
       <c r="Q373" t="n">
-        <v>1584700</v>
+        <v>1570900</v>
       </c>
     </row>
     <row r="374">
@@ -16481,7 +16484,7 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
@@ -16490,19 +16493,19 @@
         <v>0</v>
       </c>
       <c r="M375" t="n">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="N375" t="n">
-        <v>1532.6290334949</v>
+        <v>1535.9702761427</v>
       </c>
       <c r="O375" t="n">
-        <v>554811.7101251539</v>
+        <v>509942.1316793764</v>
       </c>
       <c r="P375" t="n">
         <v>1200</v>
       </c>
       <c r="Q375" t="n">
-        <v>434400</v>
+        <v>398400</v>
       </c>
     </row>
     <row r="376">
@@ -16698,7 +16701,7 @@
         </is>
       </c>
       <c r="J380" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K380" t="n">
         <v>0</v>
@@ -16707,19 +16710,19 @@
         <v>0</v>
       </c>
       <c r="M380" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N380" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O380" t="n">
-        <v>433058.26</v>
+        <v>423643.95</v>
       </c>
       <c r="P380" t="n">
         <v>16900</v>
       </c>
       <c r="Q380" t="n">
-        <v>777400</v>
+        <v>760500</v>
       </c>
     </row>
     <row r="381">
@@ -16742,7 +16745,7 @@
         </is>
       </c>
       <c r="J381" t="n">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="K381" t="n">
         <v>0</v>
@@ -16751,19 +16754,19 @@
         <v>0</v>
       </c>
       <c r="M381" t="n">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="N381" t="n">
         <v>1387.55</v>
       </c>
       <c r="O381" t="n">
-        <v>488417.6</v>
+        <v>471767</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
       </c>
       <c r="Q381" t="n">
-        <v>809600</v>
+        <v>782000</v>
       </c>
     </row>
     <row r="382">
@@ -16783,7 +16786,7 @@
         </is>
       </c>
       <c r="J382" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K382" t="n">
         <v>0</v>
@@ -16792,19 +16795,19 @@
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="N382" t="n">
-        <v>1461.54</v>
+        <v>1466.9464364982</v>
       </c>
       <c r="O382" t="n">
-        <v>137384.76</v>
+        <v>133492.1257213362</v>
       </c>
       <c r="P382" t="n">
         <v>1900</v>
       </c>
       <c r="Q382" t="n">
-        <v>178600</v>
+        <v>172900</v>
       </c>
     </row>
     <row r="383">
@@ -16912,7 +16915,7 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
@@ -16921,19 +16924,19 @@
         <v>0</v>
       </c>
       <c r="M385" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N385" t="n">
         <v>13304.13</v>
       </c>
       <c r="O385" t="n">
-        <v>532165.2</v>
+        <v>518861.0699999999</v>
       </c>
       <c r="P385" t="n">
         <v>20900</v>
       </c>
       <c r="Q385" t="n">
-        <v>836000</v>
+        <v>815100</v>
       </c>
     </row>
     <row r="386">
@@ -17005,7 +17008,7 @@
         </is>
       </c>
       <c r="J387" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K387" t="n">
         <v>0</v>
@@ -17014,19 +17017,19 @@
         <v>0</v>
       </c>
       <c r="M387" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="N387" t="n">
-        <v>2204</v>
+        <v>2216.939334638</v>
       </c>
       <c r="O387" t="n">
-        <v>242440</v>
+        <v>237212.508806266</v>
       </c>
       <c r="P387" t="n">
         <v>1500</v>
       </c>
       <c r="Q387" t="n">
-        <v>165000</v>
+        <v>160500</v>
       </c>
     </row>
     <row r="388">
@@ -17191,7 +17194,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -17200,19 +17203,19 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N391" t="n">
         <v>3761.6</v>
       </c>
       <c r="O391" t="n">
-        <v>116609.6</v>
+        <v>101563.2</v>
       </c>
       <c r="P391" t="n">
         <v>6900</v>
       </c>
       <c r="Q391" t="n">
-        <v>213900</v>
+        <v>186300</v>
       </c>
     </row>
     <row r="392">
@@ -17276,7 +17279,7 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K393" t="n">
         <v>0</v>
@@ -17285,19 +17288,19 @@
         <v>0</v>
       </c>
       <c r="M393" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N393" t="n">
         <v>45945</v>
       </c>
       <c r="O393" t="n">
-        <v>367560</v>
+        <v>781065</v>
       </c>
       <c r="P393" t="n">
         <v>73900</v>
       </c>
       <c r="Q393" t="n">
-        <v>591200</v>
+        <v>1256300</v>
       </c>
     </row>
     <row r="394">
@@ -17497,7 +17500,7 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K398" t="n">
         <v>0</v>
@@ -17506,19 +17509,19 @@
         <v>0</v>
       </c>
       <c r="M398" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N398" t="n">
-        <v>9678.9</v>
+        <v>9795.0468</v>
       </c>
       <c r="O398" t="n">
-        <v>377477.1</v>
+        <v>352621.6848</v>
       </c>
       <c r="P398" t="n">
         <v>15500</v>
       </c>
       <c r="Q398" t="n">
-        <v>604500</v>
+        <v>558000</v>
       </c>
     </row>
     <row r="399">
@@ -17667,7 +17670,7 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
@@ -17676,19 +17679,19 @@
         <v>0</v>
       </c>
       <c r="M402" t="n">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="N402" t="n">
         <v>3751</v>
       </c>
       <c r="O402" t="n">
-        <v>3495932</v>
+        <v>3480928</v>
       </c>
       <c r="P402" t="n">
         <v>6400</v>
       </c>
       <c r="Q402" t="n">
-        <v>5964800</v>
+        <v>5939200</v>
       </c>
     </row>
     <row r="403">
@@ -17808,7 +17811,7 @@
         </is>
       </c>
       <c r="J405" t="n">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="K405" t="n">
         <v>0</v>
@@ -17817,19 +17820,19 @@
         <v>0</v>
       </c>
       <c r="M405" t="n">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="N405" t="n">
-        <v>1630.9229356747</v>
+        <v>1630.9229788882</v>
       </c>
       <c r="O405" t="n">
-        <v>1479247.102656953</v>
+        <v>1461306.989083827</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
       </c>
       <c r="Q405" t="n">
-        <v>2267500</v>
+        <v>2240000</v>
       </c>
     </row>
     <row r="406">
@@ -17895,7 +17898,7 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
@@ -17904,19 +17907,19 @@
         <v>0</v>
       </c>
       <c r="M407" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="N407" t="n">
-        <v>1467.328030303</v>
+        <v>1467.3275193798</v>
       </c>
       <c r="O407" t="n">
-        <v>347756.743181811</v>
+        <v>338952.6569767338</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
       </c>
       <c r="Q407" t="n">
-        <v>592500</v>
+        <v>577500</v>
       </c>
     </row>
     <row r="408">
@@ -17941,7 +17944,7 @@
         </is>
       </c>
       <c r="J408" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="K408" t="n">
         <v>0</v>
@@ -17950,19 +17953,19 @@
         <v>0</v>
       </c>
       <c r="M408" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="N408" t="n">
-        <v>1690.6038424947</v>
+        <v>1690.6043069815</v>
       </c>
       <c r="O408" t="n">
-        <v>255281.1802166997</v>
+        <v>238375.2072843915</v>
       </c>
       <c r="P408" t="n">
         <v>2900</v>
       </c>
       <c r="Q408" t="n">
-        <v>437900</v>
+        <v>408900</v>
       </c>
     </row>
     <row r="409">
@@ -17987,7 +17990,7 @@
         </is>
       </c>
       <c r="J409" t="n">
-        <v>2315</v>
+        <v>2269</v>
       </c>
       <c r="K409" t="n">
         <v>0</v>
@@ -17996,19 +17999,19 @@
         <v>0</v>
       </c>
       <c r="M409" t="n">
-        <v>2315</v>
+        <v>2269</v>
       </c>
       <c r="N409" t="n">
-        <v>1550.192872291</v>
+        <v>1550.1929105882</v>
       </c>
       <c r="O409" t="n">
-        <v>3588696.499353665</v>
+        <v>3517387.714124626</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
       </c>
       <c r="Q409" t="n">
-        <v>5787500</v>
+        <v>5672500</v>
       </c>
     </row>
     <row r="410">
@@ -18045,10 +18048,10 @@
         <v>3</v>
       </c>
       <c r="N410" t="n">
-        <v>1579.3914114833</v>
+        <v>1579.3913493976</v>
       </c>
       <c r="O410" t="n">
-        <v>4738.1742344499</v>
+        <v>4738.1740481928</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
@@ -18091,10 +18094,10 @@
         <v>1100</v>
       </c>
       <c r="N411" t="n">
-        <v>2403.5098964308</v>
+        <v>2403.5099727039</v>
       </c>
       <c r="O411" t="n">
-        <v>2643860.88607388</v>
+        <v>2643860.96997429</v>
       </c>
       <c r="P411" t="n">
         <v>3500</v>
@@ -18137,10 +18140,10 @@
         <v>90</v>
       </c>
       <c r="N412" t="n">
-        <v>2521.5486317136</v>
+        <v>2521.5483026316</v>
       </c>
       <c r="O412" t="n">
-        <v>226939.376854224</v>
+        <v>226939.347236844</v>
       </c>
       <c r="P412" t="n">
         <v>3900</v>
@@ -18854,7 +18857,7 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K429" t="n">
         <v>0</v>
@@ -18863,19 +18866,19 @@
         <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N429" t="n">
-        <v>1301.3994046938</v>
+        <v>1303.6380504587</v>
       </c>
       <c r="O429" t="n">
-        <v>59864.37261591481</v>
+        <v>56056.4361697241</v>
       </c>
       <c r="P429" t="n">
         <v>2000</v>
       </c>
       <c r="Q429" t="n">
-        <v>92000</v>
+        <v>86000</v>
       </c>
     </row>
     <row r="430">
@@ -19218,7 +19221,7 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
@@ -19227,19 +19230,19 @@
         <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="N437" t="n">
-        <v>5067.21</v>
+        <v>5081.9760320544</v>
       </c>
       <c r="O437" t="n">
-        <v>1702582.56</v>
+        <v>1677052.090577952</v>
       </c>
       <c r="P437" t="n">
         <v>4200</v>
       </c>
       <c r="Q437" t="n">
-        <v>1411200</v>
+        <v>1386000</v>
       </c>
     </row>
     <row r="438">
@@ -19262,7 +19265,7 @@
         </is>
       </c>
       <c r="J438" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K438" t="n">
         <v>0</v>
@@ -19271,19 +19274,19 @@
         <v>0</v>
       </c>
       <c r="M438" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N438" t="n">
-        <v>2651.8557491857</v>
+        <v>2678.0253782895</v>
       </c>
       <c r="O438" t="n">
-        <v>76903.8167263853</v>
+        <v>61594.58370065851</v>
       </c>
       <c r="P438" t="n">
         <v>3800</v>
       </c>
       <c r="Q438" t="n">
-        <v>110200</v>
+        <v>87400</v>
       </c>
     </row>
     <row r="439">
@@ -19308,7 +19311,7 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
@@ -19317,19 +19320,19 @@
         <v>0</v>
       </c>
       <c r="M439" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="N439" t="n">
-        <v>1965</v>
+        <v>2030.7740585774</v>
       </c>
       <c r="O439" t="n">
-        <v>176850</v>
+        <v>134031.0878661084</v>
       </c>
       <c r="P439" t="n">
         <v>3700</v>
       </c>
       <c r="Q439" t="n">
-        <v>333000</v>
+        <v>244200</v>
       </c>
     </row>
     <row r="440">
@@ -19441,7 +19444,7 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="K442" t="n">
         <v>0</v>
@@ -19450,19 +19453,19 @@
         <v>0</v>
       </c>
       <c r="M442" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="N442" t="n">
-        <v>3253</v>
+        <v>3319.8424657534</v>
       </c>
       <c r="O442" t="n">
-        <v>471685</v>
+        <v>401700.9383561614</v>
       </c>
       <c r="P442" t="n">
         <v>3900</v>
       </c>
       <c r="Q442" t="n">
-        <v>565500</v>
+        <v>471900</v>
       </c>
     </row>
     <row r="443">
@@ -19702,7 +19705,7 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="K448" t="n">
         <v>0</v>
@@ -19711,19 +19714,19 @@
         <v>0</v>
       </c>
       <c r="M448" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="N448" t="n">
-        <v>204.05076502732</v>
+        <v>210.96774011299</v>
       </c>
       <c r="O448" t="n">
-        <v>33464.32546448048</v>
+        <v>33332.90293785242</v>
       </c>
       <c r="P448" t="n">
         <v>500</v>
       </c>
       <c r="Q448" t="n">
-        <v>82000</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="449">
@@ -20095,7 +20098,7 @@
         </is>
       </c>
       <c r="J457" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="K457" t="n">
         <v>0</v>
@@ -20104,19 +20107,19 @@
         <v>0</v>
       </c>
       <c r="M457" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="N457" t="n">
-        <v>933.18544959128</v>
+        <v>948.69545706371</v>
       </c>
       <c r="O457" t="n">
-        <v>274356.5221798363</v>
+        <v>273224.2916343485</v>
       </c>
       <c r="P457" t="n">
         <v>1200</v>
       </c>
       <c r="Q457" t="n">
-        <v>352800</v>
+        <v>345600</v>
       </c>
     </row>
     <row r="458">
@@ -20865,7 +20868,7 @@
         </is>
       </c>
       <c r="J475" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K475" t="n">
         <v>0</v>
@@ -20874,19 +20877,19 @@
         <v>0</v>
       </c>
       <c r="M475" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N475" t="n">
         <v>9338</v>
       </c>
       <c r="O475" t="n">
-        <v>289478</v>
+        <v>233450</v>
       </c>
       <c r="P475" t="n">
         <v>15500</v>
       </c>
       <c r="Q475" t="n">
-        <v>480500</v>
+        <v>387500</v>
       </c>
     </row>
     <row r="476">
@@ -21237,7 +21240,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -21246,19 +21249,19 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N484" t="n">
-        <v>2661.82</v>
+        <v>2696.7673085339</v>
       </c>
       <c r="O484" t="n">
-        <v>175680.12</v>
+        <v>161806.038512034</v>
       </c>
       <c r="P484" t="n">
         <v>3200</v>
       </c>
       <c r="Q484" t="n">
-        <v>211200</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="485">
@@ -21319,7 +21322,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -21328,19 +21331,19 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="N486" t="n">
-        <v>4488</v>
+        <v>4550.9158878505</v>
       </c>
       <c r="O486" t="n">
-        <v>713592</v>
+        <v>682637.3831775751</v>
       </c>
       <c r="P486" t="n">
         <v>6200</v>
       </c>
       <c r="Q486" t="n">
-        <v>985800</v>
+        <v>930000</v>
       </c>
     </row>
     <row r="487">
@@ -21360,7 +21363,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -21369,19 +21372,19 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="N487" t="n">
-        <v>2610</v>
+        <v>2621.3808139535</v>
       </c>
       <c r="O487" t="n">
-        <v>279270</v>
+        <v>256895.319767443</v>
       </c>
       <c r="P487" t="n">
         <v>3200</v>
       </c>
       <c r="Q487" t="n">
-        <v>342400</v>
+        <v>313600</v>
       </c>
     </row>
     <row r="488">
@@ -21524,7 +21527,7 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K491" t="n">
         <v>0</v>
@@ -21533,19 +21536,19 @@
         <v>0</v>
       </c>
       <c r="M491" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="N491" t="n">
-        <v>1969</v>
+        <v>1979.2819843342</v>
       </c>
       <c r="O491" t="n">
-        <v>328823</v>
+        <v>318664.3994778062</v>
       </c>
       <c r="P491" t="n">
         <v>1500</v>
       </c>
       <c r="Q491" t="n">
-        <v>250500</v>
+        <v>241500</v>
       </c>
     </row>
     <row r="492">
@@ -21565,7 +21568,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -21574,19 +21577,19 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="N492" t="n">
-        <v>1958.73</v>
+        <v>2040.34375</v>
       </c>
       <c r="O492" t="n">
-        <v>54844.44</v>
+        <v>34685.84375</v>
       </c>
       <c r="P492" t="n">
         <v>3400</v>
       </c>
       <c r="Q492" t="n">
-        <v>95200</v>
+        <v>57800</v>
       </c>
     </row>
     <row r="493">
@@ -21606,7 +21609,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
@@ -21615,19 +21618,19 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="N493" t="n">
-        <v>8794.48</v>
+        <v>8818.9498942682</v>
       </c>
       <c r="O493" t="n">
-        <v>1503856.08</v>
+        <v>1446307.782659985</v>
       </c>
       <c r="P493" t="n">
         <v>14500</v>
       </c>
       <c r="Q493" t="n">
-        <v>2479500</v>
+        <v>2378000</v>
       </c>
     </row>
     <row r="494">
@@ -21693,7 +21696,7 @@
         </is>
       </c>
       <c r="J495" t="n">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="K495" t="n">
         <v>0</v>
@@ -21702,19 +21705,19 @@
         <v>0</v>
       </c>
       <c r="M495" t="n">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="N495" t="n">
         <v>2567</v>
       </c>
       <c r="O495" t="n">
-        <v>266968</v>
+        <v>174556</v>
       </c>
       <c r="P495" t="n">
         <v>4500</v>
       </c>
       <c r="Q495" t="n">
-        <v>468000</v>
+        <v>306000</v>
       </c>
     </row>
     <row r="496">
@@ -21816,7 +21819,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -21825,19 +21828,19 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="N498" t="n">
         <v>6652</v>
       </c>
       <c r="O498" t="n">
-        <v>545464</v>
+        <v>505552</v>
       </c>
       <c r="P498" t="n">
         <v>5900</v>
       </c>
       <c r="Q498" t="n">
-        <v>483800</v>
+        <v>448400</v>
       </c>
     </row>
     <row r="499">
@@ -21857,7 +21860,7 @@
         </is>
       </c>
       <c r="J499" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K499" t="n">
         <v>0</v>
@@ -21866,19 +21869,19 @@
         <v>0</v>
       </c>
       <c r="M499" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N499" t="n">
-        <v>14975</v>
+        <v>15626.086956522</v>
       </c>
       <c r="O499" t="n">
-        <v>344425</v>
+        <v>343773.913043484</v>
       </c>
       <c r="P499" t="n">
         <v>19900</v>
       </c>
       <c r="Q499" t="n">
-        <v>457700</v>
+        <v>437800</v>
       </c>
     </row>
     <row r="500">
@@ -21939,7 +21942,7 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
@@ -21948,19 +21951,19 @@
         <v>0</v>
       </c>
       <c r="M501" t="n">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="N501" t="n">
-        <v>2517.22</v>
+        <v>2558.6841592313</v>
       </c>
       <c r="O501" t="n">
-        <v>659511.6399999999</v>
+        <v>608966.8298970493</v>
       </c>
       <c r="P501" t="n">
         <v>4200</v>
       </c>
       <c r="Q501" t="n">
-        <v>1100400</v>
+        <v>999600</v>
       </c>
     </row>
     <row r="502">
@@ -22062,7 +22065,7 @@
         </is>
       </c>
       <c r="J504" t="n">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
@@ -22071,19 +22074,19 @@
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="N504" t="n">
-        <v>2029.8735344015</v>
+        <v>2035.7801454898</v>
       </c>
       <c r="O504" t="n">
-        <v>1023056.261338356</v>
+        <v>977174.469835104</v>
       </c>
       <c r="P504" t="n">
         <v>3600</v>
       </c>
       <c r="Q504" t="n">
-        <v>1814400</v>
+        <v>1728000</v>
       </c>
     </row>
     <row r="505">
@@ -22308,7 +22311,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -22317,19 +22320,19 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N510" t="n">
-        <v>22485.695945946</v>
+        <v>22561.918644068</v>
       </c>
       <c r="O510" t="n">
-        <v>1506541.628378382</v>
+        <v>1443962.793220352</v>
       </c>
       <c r="P510" t="n">
         <v>36500</v>
       </c>
       <c r="Q510" t="n">
-        <v>2445500</v>
+        <v>2336000</v>
       </c>
     </row>
     <row r="511">
@@ -22513,7 +22516,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -22522,19 +22525,19 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="N515" t="n">
-        <v>7103</v>
+        <v>7136.7702060222</v>
       </c>
       <c r="O515" t="n">
-        <v>937596</v>
+        <v>906369.8161648194</v>
       </c>
       <c r="P515" t="n">
         <v>10700</v>
       </c>
       <c r="Q515" t="n">
-        <v>1412400</v>
+        <v>1358900</v>
       </c>
     </row>
     <row r="516">
@@ -22685,7 +22688,7 @@
         </is>
       </c>
       <c r="J519" t="n">
-        <v>1424</v>
+        <v>1412</v>
       </c>
       <c r="K519" t="n">
         <v>0</v>
@@ -22694,19 +22697,19 @@
         <v>0</v>
       </c>
       <c r="M519" t="n">
-        <v>1424</v>
+        <v>1412</v>
       </c>
       <c r="N519" t="n">
-        <v>880.32919651056</v>
+        <v>880.32923254206</v>
       </c>
       <c r="O519" t="n">
-        <v>1253588.775831037</v>
+        <v>1243024.876349389</v>
       </c>
       <c r="P519" t="n">
         <v>1200</v>
       </c>
       <c r="Q519" t="n">
-        <v>1708800</v>
+        <v>1694400</v>
       </c>
     </row>
     <row r="520">
@@ -23146,7 +23149,7 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -23155,19 +23158,19 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N530" t="n">
-        <v>14371.45</v>
+        <v>15639.519117647</v>
       </c>
       <c r="O530" t="n">
-        <v>114971.6</v>
+        <v>78197.595588235</v>
       </c>
       <c r="P530" t="n">
         <v>23300</v>
       </c>
       <c r="Q530" t="n">
-        <v>186400</v>
+        <v>116500</v>
       </c>
     </row>
     <row r="531">
@@ -23683,10 +23686,10 @@
         <v>280</v>
       </c>
       <c r="N542" t="n">
-        <v>4285.1952156057</v>
+        <v>4285.1952263374</v>
       </c>
       <c r="O542" t="n">
-        <v>1199854.660369596</v>
+        <v>1199854.663374472</v>
       </c>
       <c r="P542" t="n">
         <v>6900</v>
@@ -24483,7 +24486,7 @@
         </is>
       </c>
       <c r="J561" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -24492,19 +24495,19 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N561" t="n">
-        <v>11562.038545455</v>
+        <v>11652.839895288</v>
       </c>
       <c r="O561" t="n">
-        <v>670598.2356363899</v>
+        <v>640906.19424084</v>
       </c>
       <c r="P561" t="n">
         <v>18500</v>
       </c>
       <c r="Q561" t="n">
-        <v>1073000</v>
+        <v>1017500</v>
       </c>
     </row>
     <row r="562">
@@ -24575,7 +24578,7 @@
         </is>
       </c>
       <c r="J563" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K563" t="n">
         <v>0</v>
@@ -24584,19 +24587,19 @@
         <v>0</v>
       </c>
       <c r="M563" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N563" t="n">
-        <v>12005.159834711</v>
+        <v>12155.852217573</v>
       </c>
       <c r="O563" t="n">
-        <v>828356.0285950589</v>
+        <v>802286.2463598179</v>
       </c>
       <c r="P563" t="n">
         <v>19500</v>
       </c>
       <c r="Q563" t="n">
-        <v>1345500</v>
+        <v>1287000</v>
       </c>
     </row>
     <row r="564">
@@ -24621,7 +24624,7 @@
         </is>
       </c>
       <c r="J564" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K564" t="n">
         <v>0</v>
@@ -24630,19 +24633,19 @@
         <v>0</v>
       </c>
       <c r="M564" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N564" t="n">
         <v>60174</v>
       </c>
       <c r="O564" t="n">
-        <v>180522</v>
+        <v>361044</v>
       </c>
       <c r="P564" t="n">
         <v>96900</v>
       </c>
       <c r="Q564" t="n">
-        <v>290700</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="565">
@@ -25159,7 +25162,7 @@
         </is>
       </c>
       <c r="J577" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K577" t="n">
         <v>0</v>
@@ -25168,19 +25171,19 @@
         <v>0</v>
       </c>
       <c r="M577" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N577" t="n">
         <v>39596.9</v>
       </c>
       <c r="O577" t="n">
-        <v>593953.5</v>
+        <v>475162.8</v>
       </c>
       <c r="P577" t="n">
         <v>64900</v>
       </c>
       <c r="Q577" t="n">
-        <v>973500</v>
+        <v>778800</v>
       </c>
     </row>
     <row r="578">
@@ -25645,7 +25648,7 @@
         </is>
       </c>
       <c r="J588" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K588" t="n">
         <v>0</v>
@@ -25654,19 +25657,19 @@
         <v>0</v>
       </c>
       <c r="M588" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N588" t="n">
-        <v>22730.48</v>
+        <v>22817.681329923</v>
       </c>
       <c r="O588" t="n">
-        <v>772836.3199999999</v>
+        <v>707348.1212276131</v>
       </c>
       <c r="P588" t="n">
         <v>36900</v>
       </c>
       <c r="Q588" t="n">
-        <v>1254600</v>
+        <v>1143900</v>
       </c>
     </row>
     <row r="589">
@@ -26172,7 +26175,7 @@
         </is>
       </c>
       <c r="J600" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="K600" t="n">
         <v>0</v>
@@ -26181,19 +26184,19 @@
         <v>0</v>
       </c>
       <c r="M600" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N600" t="n">
-        <v>1560.9983239983</v>
+        <v>1560.9985110132</v>
       </c>
       <c r="O600" t="n">
-        <v>280979.698319694</v>
+        <v>271613.7409162968</v>
       </c>
       <c r="P600" t="n">
         <v>2900</v>
       </c>
       <c r="Q600" t="n">
-        <v>522000</v>
+        <v>504600</v>
       </c>
     </row>
     <row r="601">
@@ -27587,7 +27590,7 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
@@ -27596,19 +27599,19 @@
         <v>0</v>
       </c>
       <c r="M633" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N633" t="n">
-        <v>3590.77</v>
+        <v>3779.7578947368</v>
       </c>
       <c r="O633" t="n">
-        <v>179538.5</v>
+        <v>105833.2210526304</v>
       </c>
       <c r="P633" t="n">
         <v>3900</v>
       </c>
       <c r="Q633" t="n">
-        <v>195000</v>
+        <v>109200</v>
       </c>
     </row>
     <row r="634">
@@ -27848,7 +27851,7 @@
         </is>
       </c>
       <c r="J639" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
@@ -27857,19 +27860,19 @@
         <v>0</v>
       </c>
       <c r="M639" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N639" t="n">
         <v>2634.61</v>
       </c>
       <c r="O639" t="n">
-        <v>121192.06</v>
+        <v>115922.84</v>
       </c>
       <c r="P639" t="n">
         <v>4200</v>
       </c>
       <c r="Q639" t="n">
-        <v>193200</v>
+        <v>184800</v>
       </c>
     </row>
     <row r="640">
@@ -27894,7 +27897,7 @@
         </is>
       </c>
       <c r="J640" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K640" t="n">
         <v>0</v>
@@ -27903,19 +27906,19 @@
         <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N640" t="n">
-        <v>3113.8900238095</v>
+        <v>3113.8900239521</v>
       </c>
       <c r="O640" t="n">
-        <v>233541.7517857125</v>
+        <v>221086.1917005991</v>
       </c>
       <c r="P640" t="n">
         <v>5000</v>
       </c>
       <c r="Q640" t="n">
-        <v>375000</v>
+        <v>355000</v>
       </c>
     </row>
     <row r="641">
@@ -27986,7 +27989,7 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="K642" t="n">
         <v>0</v>
@@ -27995,19 +27998,19 @@
         <v>0</v>
       </c>
       <c r="M642" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="N642" t="n">
         <v>4690.64</v>
       </c>
       <c r="O642" t="n">
-        <v>276747.76</v>
+        <v>229841.36</v>
       </c>
       <c r="P642" t="n">
         <v>7500</v>
       </c>
       <c r="Q642" t="n">
-        <v>442500</v>
+        <v>367500</v>
       </c>
     </row>
     <row r="643">
@@ -28032,7 +28035,7 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -28041,19 +28044,19 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N643" t="n">
         <v>5410.72</v>
       </c>
       <c r="O643" t="n">
-        <v>454500.48</v>
+        <v>432857.6</v>
       </c>
       <c r="P643" t="n">
         <v>8700</v>
       </c>
       <c r="Q643" t="n">
-        <v>730800</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="644">
@@ -28078,7 +28081,7 @@
         </is>
       </c>
       <c r="J644" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K644" t="n">
         <v>0</v>
@@ -28087,19 +28090,19 @@
         <v>0</v>
       </c>
       <c r="M644" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N644" t="n">
-        <v>4163.16016</v>
+        <v>4265.5329508197</v>
       </c>
       <c r="O644" t="n">
-        <v>116568.48448</v>
+        <v>106638.3237704925</v>
       </c>
       <c r="P644" t="n">
         <v>6700</v>
       </c>
       <c r="Q644" t="n">
-        <v>187600</v>
+        <v>167500</v>
       </c>
     </row>
     <row r="645">
@@ -28124,7 +28127,7 @@
         </is>
       </c>
       <c r="J645" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K645" t="n">
         <v>0</v>
@@ -28133,19 +28136,19 @@
         <v>0</v>
       </c>
       <c r="M645" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N645" t="n">
         <v>8878.450000000001</v>
       </c>
       <c r="O645" t="n">
-        <v>692519.1000000001</v>
+        <v>674762.2000000001</v>
       </c>
       <c r="P645" t="n">
         <v>14100</v>
       </c>
       <c r="Q645" t="n">
-        <v>1099800</v>
+        <v>1071600</v>
       </c>
     </row>
     <row r="646">
@@ -28262,7 +28265,7 @@
         </is>
       </c>
       <c r="J648" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K648" t="n">
         <v>0</v>
@@ -28271,19 +28274,19 @@
         <v>0</v>
       </c>
       <c r="M648" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N648" t="n">
-        <v>5218.1704646251</v>
+        <v>5218.1704756757</v>
       </c>
       <c r="O648" t="n">
-        <v>161763.2844033781</v>
+        <v>140890.6028432439</v>
       </c>
       <c r="P648" t="n">
         <v>8500</v>
       </c>
       <c r="Q648" t="n">
-        <v>263500</v>
+        <v>229500</v>
       </c>
     </row>
     <row r="649">
@@ -28308,7 +28311,7 @@
         </is>
       </c>
       <c r="J649" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="K649" t="n">
         <v>0</v>
@@ -28317,19 +28320,19 @@
         <v>0</v>
       </c>
       <c r="M649" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="N649" t="n">
-        <v>1595.0095153061</v>
+        <v>1595.0095090439</v>
       </c>
       <c r="O649" t="n">
-        <v>232871.3892346906</v>
+        <v>223301.331266146</v>
       </c>
       <c r="P649" t="n">
         <v>2600</v>
       </c>
       <c r="Q649" t="n">
-        <v>379600</v>
+        <v>364000</v>
       </c>
     </row>
     <row r="650">
@@ -28354,7 +28357,7 @@
         </is>
       </c>
       <c r="J650" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K650" t="n">
         <v>0</v>
@@ -28363,19 +28366,19 @@
         <v>0</v>
       </c>
       <c r="M650" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N650" t="n">
-        <v>3610.650023015</v>
+        <v>3610.6500232019</v>
       </c>
       <c r="O650" t="n">
-        <v>140815.350897585</v>
+        <v>126372.7508120665</v>
       </c>
       <c r="P650" t="n">
         <v>5800</v>
       </c>
       <c r="Q650" t="n">
-        <v>226200</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="651">
@@ -28400,7 +28403,7 @@
         </is>
       </c>
       <c r="J651" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K651" t="n">
         <v>0</v>
@@ -28409,19 +28412,19 @@
         <v>0</v>
       </c>
       <c r="M651" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="N651" t="n">
-        <v>5194</v>
+        <v>5220.5451448041</v>
       </c>
       <c r="O651" t="n">
-        <v>446684</v>
+        <v>428084.7018739362</v>
       </c>
       <c r="P651" t="n">
         <v>9000</v>
       </c>
       <c r="Q651" t="n">
-        <v>774000</v>
+        <v>738000</v>
       </c>
     </row>
     <row r="652">
@@ -28446,7 +28449,7 @@
         </is>
       </c>
       <c r="J652" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="K652" t="n">
         <v>0</v>
@@ -28455,19 +28458,19 @@
         <v>0</v>
       </c>
       <c r="M652" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="N652" t="n">
         <v>4227.77</v>
       </c>
       <c r="O652" t="n">
-        <v>283260.59</v>
+        <v>257893.97</v>
       </c>
       <c r="P652" t="n">
         <v>6900</v>
       </c>
       <c r="Q652" t="n">
-        <v>462300</v>
+        <v>420900</v>
       </c>
     </row>
     <row r="653">
@@ -28492,7 +28495,7 @@
         </is>
       </c>
       <c r="J653" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="K653" t="n">
         <v>0</v>
@@ -28501,19 +28504,19 @@
         <v>0</v>
       </c>
       <c r="M653" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="N653" t="n">
         <v>3965.02</v>
       </c>
       <c r="O653" t="n">
-        <v>257726.3</v>
+        <v>218076.1</v>
       </c>
       <c r="P653" t="n">
         <v>6500</v>
       </c>
       <c r="Q653" t="n">
-        <v>422500</v>
+        <v>357500</v>
       </c>
     </row>
     <row r="654">
@@ -28538,7 +28541,7 @@
         </is>
       </c>
       <c r="J654" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K654" t="n">
         <v>0</v>
@@ -28547,19 +28550,19 @@
         <v>0</v>
       </c>
       <c r="M654" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N654" t="n">
         <v>5791.05</v>
       </c>
       <c r="O654" t="n">
-        <v>521194.5</v>
+        <v>498030.3</v>
       </c>
       <c r="P654" t="n">
         <v>9300</v>
       </c>
       <c r="Q654" t="n">
-        <v>837000</v>
+        <v>799800</v>
       </c>
     </row>
     <row r="655">
@@ -28630,7 +28633,7 @@
         </is>
       </c>
       <c r="J656" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K656" t="n">
         <v>0</v>
@@ -28639,19 +28642,19 @@
         <v>0</v>
       </c>
       <c r="M656" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N656" t="n">
         <v>1812.57</v>
       </c>
       <c r="O656" t="n">
-        <v>3625.14</v>
+        <v>1812.57</v>
       </c>
       <c r="P656" t="n">
         <v>2900</v>
       </c>
       <c r="Q656" t="n">
-        <v>5800</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="657">
@@ -28780,10 +28783,10 @@
         <v>432</v>
       </c>
       <c r="N659" t="n">
-        <v>1664.3615095729</v>
+        <v>1664.3613046757</v>
       </c>
       <c r="O659" t="n">
-        <v>719004.1721354928</v>
+        <v>719004.0836199024</v>
       </c>
       <c r="P659" t="n">
         <v>2900</v>
@@ -29384,10 +29387,10 @@
         <v>4</v>
       </c>
       <c r="N672" t="n">
-        <v>23521.624927536</v>
+        <v>23521.624852941</v>
       </c>
       <c r="O672" t="n">
-        <v>94086.49971014399</v>
+        <v>94086.499411764</v>
       </c>
       <c r="P672" t="n">
         <v>39000</v>
@@ -29464,7 +29467,7 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
@@ -29473,19 +29476,19 @@
         <v>0</v>
       </c>
       <c r="M674" t="n">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="N674" t="n">
-        <v>1778.4725043029</v>
+        <v>1778.4725093418</v>
       </c>
       <c r="O674" t="n">
-        <v>2825992.809337308</v>
+        <v>2811765.037269386</v>
       </c>
       <c r="P674" t="n">
         <v>4900</v>
       </c>
       <c r="Q674" t="n">
-        <v>7786100</v>
+        <v>7746900</v>
       </c>
     </row>
     <row r="675">
@@ -29510,7 +29513,7 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
@@ -29519,19 +29522,19 @@
         <v>0</v>
       </c>
       <c r="M675" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="N675" t="n">
         <v>1548</v>
       </c>
       <c r="O675" t="n">
-        <v>495360</v>
+        <v>482976</v>
       </c>
       <c r="P675" t="n">
         <v>3900</v>
       </c>
       <c r="Q675" t="n">
-        <v>1248000</v>
+        <v>1216800</v>
       </c>
     </row>
     <row r="676">
@@ -29602,7 +29605,7 @@
         </is>
       </c>
       <c r="J677" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K677" t="n">
         <v>0</v>
@@ -29611,19 +29614,19 @@
         <v>0</v>
       </c>
       <c r="M677" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N677" t="n">
         <v>22739</v>
       </c>
       <c r="O677" t="n">
-        <v>318346</v>
+        <v>272868</v>
       </c>
       <c r="P677" t="n">
         <v>36900</v>
       </c>
       <c r="Q677" t="n">
-        <v>516600</v>
+        <v>442800</v>
       </c>
     </row>
     <row r="678">
@@ -30019,7 +30022,7 @@
         </is>
       </c>
       <c r="J686" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="K686" t="n">
         <v>0</v>
@@ -30028,19 +30031,19 @@
         <v>0</v>
       </c>
       <c r="M686" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="N686" t="n">
-        <v>11450</v>
+        <v>11682.094594595</v>
       </c>
       <c r="O686" t="n">
-        <v>767150</v>
+        <v>712607.7702702951</v>
       </c>
       <c r="P686" t="n">
         <v>18300</v>
       </c>
       <c r="Q686" t="n">
-        <v>1226100</v>
+        <v>1116300</v>
       </c>
     </row>
     <row r="687">
@@ -30111,7 +30114,7 @@
         </is>
       </c>
       <c r="J688" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K688" t="n">
         <v>0</v>
@@ -30120,19 +30123,19 @@
         <v>0</v>
       </c>
       <c r="M688" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N688" t="n">
-        <v>6300</v>
+        <v>6365.625</v>
       </c>
       <c r="O688" t="n">
-        <v>831600</v>
+        <v>802068.75</v>
       </c>
       <c r="P688" t="n">
         <v>10200</v>
       </c>
       <c r="Q688" t="n">
-        <v>1346400</v>
+        <v>1285200</v>
       </c>
     </row>
     <row r="689">
@@ -30295,7 +30298,7 @@
         </is>
       </c>
       <c r="J692" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K692" t="n">
         <v>0</v>
@@ -30304,19 +30307,19 @@
         <v>0</v>
       </c>
       <c r="M692" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N692" t="n">
-        <v>7230</v>
+        <v>7371.3029315961</v>
       </c>
       <c r="O692" t="n">
-        <v>448260</v>
+        <v>412792.9641693816</v>
       </c>
       <c r="P692" t="n">
         <v>11600</v>
       </c>
       <c r="Q692" t="n">
-        <v>719200</v>
+        <v>649600</v>
       </c>
     </row>
     <row r="693">
@@ -30341,7 +30344,7 @@
         </is>
       </c>
       <c r="J693" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K693" t="n">
         <v>0</v>
@@ -30350,19 +30353,19 @@
         <v>0</v>
       </c>
       <c r="M693" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="N693" t="n">
-        <v>5200</v>
+        <v>5291.8727915194</v>
       </c>
       <c r="O693" t="n">
-        <v>379600</v>
+        <v>359847.3498233192</v>
       </c>
       <c r="P693" t="n">
         <v>8500</v>
       </c>
       <c r="Q693" t="n">
-        <v>620500</v>
+        <v>578000</v>
       </c>
     </row>
     <row r="694">
@@ -30387,7 +30390,7 @@
         </is>
       </c>
       <c r="J694" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K694" t="n">
         <v>0</v>
@@ -30396,19 +30399,19 @@
         <v>0</v>
       </c>
       <c r="M694" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N694" t="n">
-        <v>1400</v>
+        <v>1420.3389830508</v>
       </c>
       <c r="O694" t="n">
-        <v>88200</v>
+        <v>80959.3220338956</v>
       </c>
       <c r="P694" t="n">
         <v>2300</v>
       </c>
       <c r="Q694" t="n">
-        <v>144900</v>
+        <v>131100</v>
       </c>
     </row>
     <row r="695">
@@ -30433,7 +30436,7 @@
         </is>
       </c>
       <c r="J695" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K695" t="n">
         <v>0</v>
@@ -30442,19 +30445,19 @@
         <v>0</v>
       </c>
       <c r="M695" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N695" t="n">
-        <v>6000</v>
+        <v>6085.1063829787</v>
       </c>
       <c r="O695" t="n">
-        <v>498000</v>
+        <v>468553.1914893599</v>
       </c>
       <c r="P695" t="n">
         <v>10000</v>
       </c>
       <c r="Q695" t="n">
-        <v>830000</v>
+        <v>770000</v>
       </c>
     </row>
     <row r="696">
@@ -30479,7 +30482,7 @@
         </is>
       </c>
       <c r="J696" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="K696" t="n">
         <v>0</v>
@@ -30488,19 +30491,19 @@
         <v>0</v>
       </c>
       <c r="M696" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="N696" t="n">
-        <v>1230</v>
+        <v>1243.273381295</v>
       </c>
       <c r="O696" t="n">
-        <v>179580</v>
+        <v>174058.2733813</v>
       </c>
       <c r="P696" t="n">
         <v>2000</v>
       </c>
       <c r="Q696" t="n">
-        <v>292000</v>
+        <v>280000</v>
       </c>
     </row>
     <row r="697">
@@ -30520,7 +30523,7 @@
         </is>
       </c>
       <c r="J697" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K697" t="n">
         <v>0</v>
@@ -30529,19 +30532,19 @@
         <v>0</v>
       </c>
       <c r="M697" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N697" t="n">
         <v>1817</v>
       </c>
       <c r="O697" t="n">
-        <v>305256</v>
+        <v>301622</v>
       </c>
       <c r="P697" t="n">
         <v>3100</v>
       </c>
       <c r="Q697" t="n">
-        <v>520800</v>
+        <v>514600</v>
       </c>
     </row>
     <row r="698">
@@ -30617,7 +30620,7 @@
         </is>
       </c>
       <c r="J699" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K699" t="n">
         <v>0</v>
@@ -30626,19 +30629,19 @@
         <v>0</v>
       </c>
       <c r="M699" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="N699" t="n">
-        <v>1390</v>
+        <v>1441.9626168224</v>
       </c>
       <c r="O699" t="n">
-        <v>40310</v>
+        <v>24513.3644859808</v>
       </c>
       <c r="P699" t="n">
         <v>2300</v>
       </c>
       <c r="Q699" t="n">
-        <v>66700</v>
+        <v>39100</v>
       </c>
     </row>
     <row r="700">
@@ -30663,7 +30666,7 @@
         </is>
       </c>
       <c r="J700" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K700" t="n">
         <v>0</v>
@@ -30672,19 +30675,19 @@
         <v>0</v>
       </c>
       <c r="M700" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N700" t="n">
-        <v>1870</v>
+        <v>1944.3046357616</v>
       </c>
       <c r="O700" t="n">
-        <v>91630</v>
+        <v>71939.2715231792</v>
       </c>
       <c r="P700" t="n">
         <v>3000</v>
       </c>
       <c r="Q700" t="n">
-        <v>147000</v>
+        <v>111000</v>
       </c>
     </row>
     <row r="701">
@@ -30709,7 +30712,7 @@
         </is>
       </c>
       <c r="J701" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="K701" t="n">
         <v>0</v>
@@ -30718,19 +30721,19 @@
         <v>0</v>
       </c>
       <c r="M701" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="N701" t="n">
-        <v>2019.86</v>
+        <v>2110.9815037594</v>
       </c>
       <c r="O701" t="n">
-        <v>155529.22</v>
+        <v>137213.797744361</v>
       </c>
       <c r="P701" t="n">
         <v>3300</v>
       </c>
       <c r="Q701" t="n">
-        <v>254100</v>
+        <v>214500</v>
       </c>
     </row>
     <row r="702">
@@ -30755,7 +30758,7 @@
         </is>
       </c>
       <c r="J702" t="n">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="K702" t="n">
         <v>0</v>
@@ -30764,19 +30767,19 @@
         <v>0</v>
       </c>
       <c r="M702" t="n">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="N702" t="n">
-        <v>520</v>
+        <v>539.28902627512</v>
       </c>
       <c r="O702" t="n">
-        <v>77480</v>
+        <v>67411.12828439</v>
       </c>
       <c r="P702" t="n">
         <v>850</v>
       </c>
       <c r="Q702" t="n">
-        <v>126650</v>
+        <v>106250</v>
       </c>
     </row>
     <row r="703">
@@ -30801,7 +30804,7 @@
         </is>
       </c>
       <c r="J703" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K703" t="n">
         <v>0</v>
@@ -30810,19 +30813,19 @@
         <v>0</v>
       </c>
       <c r="M703" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="N703" t="n">
-        <v>2260</v>
+        <v>2318.1974248927</v>
       </c>
       <c r="O703" t="n">
-        <v>223740</v>
+        <v>215592.3605150211</v>
       </c>
       <c r="P703" t="n">
         <v>3800</v>
       </c>
       <c r="Q703" t="n">
-        <v>376200</v>
+        <v>353400</v>
       </c>
     </row>
     <row r="704">
@@ -30893,7 +30896,7 @@
         </is>
       </c>
       <c r="J705" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K705" t="n">
         <v>0</v>
@@ -30902,19 +30905,19 @@
         <v>0</v>
       </c>
       <c r="M705" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N705" t="n">
-        <v>1840</v>
+        <v>1872.4705882353</v>
       </c>
       <c r="O705" t="n">
-        <v>69920</v>
+        <v>59919.0588235296</v>
       </c>
       <c r="P705" t="n">
         <v>3000</v>
       </c>
       <c r="Q705" t="n">
-        <v>114000</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="706">
@@ -30985,7 +30988,7 @@
         </is>
       </c>
       <c r="J707" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K707" t="n">
         <v>0</v>
@@ -30994,19 +30997,19 @@
         <v>0</v>
       </c>
       <c r="M707" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="N707" t="n">
-        <v>2840</v>
+        <v>2878.4650112867</v>
       </c>
       <c r="O707" t="n">
-        <v>232880</v>
+        <v>218763.3408577892</v>
       </c>
       <c r="P707" t="n">
         <v>4600</v>
       </c>
       <c r="Q707" t="n">
-        <v>377200</v>
+        <v>349600</v>
       </c>
     </row>
     <row r="708">
@@ -31126,7 +31129,7 @@
         </is>
       </c>
       <c r="J710" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K710" t="n">
         <v>0</v>
@@ -31135,19 +31138,19 @@
         <v>0</v>
       </c>
       <c r="M710" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N710" t="n">
         <v>44055</v>
       </c>
       <c r="O710" t="n">
-        <v>660825</v>
+        <v>1057320</v>
       </c>
       <c r="P710" t="n">
         <v>70900</v>
       </c>
       <c r="Q710" t="n">
-        <v>1063500</v>
+        <v>1701600</v>
       </c>
     </row>
     <row r="711">
@@ -31218,7 +31221,7 @@
         </is>
       </c>
       <c r="J712" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K712" t="n">
         <v>0</v>
@@ -31227,19 +31230,19 @@
         <v>0</v>
       </c>
       <c r="M712" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N712" t="n">
         <v>32295</v>
       </c>
       <c r="O712" t="n">
-        <v>807375</v>
+        <v>775080</v>
       </c>
       <c r="P712" t="n">
         <v>51900</v>
       </c>
       <c r="Q712" t="n">
-        <v>1297500</v>
+        <v>1245600</v>
       </c>
     </row>
     <row r="713">
@@ -31356,7 +31359,7 @@
         </is>
       </c>
       <c r="J715" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K715" t="n">
         <v>0</v>
@@ -31365,19 +31368,19 @@
         <v>0</v>
       </c>
       <c r="M715" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="N715" t="n">
-        <v>13687</v>
+        <v>13863.987068966</v>
       </c>
       <c r="O715" t="n">
-        <v>1560318</v>
+        <v>1497310.603448328</v>
       </c>
       <c r="P715" t="n">
         <v>21900</v>
       </c>
       <c r="Q715" t="n">
-        <v>2496600</v>
+        <v>2365200</v>
       </c>
     </row>
     <row r="716">
@@ -32092,7 +32095,7 @@
         </is>
       </c>
       <c r="J731" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K731" t="n">
         <v>0</v>
@@ -32101,19 +32104,19 @@
         <v>0</v>
       </c>
       <c r="M731" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N731" t="n">
-        <v>5858</v>
+        <v>6112.6956521739</v>
       </c>
       <c r="O731" t="n">
-        <v>70296</v>
+        <v>36676.1739130434</v>
       </c>
       <c r="P731" t="n">
         <v>9500</v>
       </c>
       <c r="Q731" t="n">
-        <v>114000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="732">
@@ -32412,7 +32415,7 @@
         </is>
       </c>
       <c r="J738" t="n">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K738" t="n">
         <v>0</v>
@@ -32421,19 +32424,19 @@
         <v>0</v>
       </c>
       <c r="M738" t="n">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="N738" t="n">
-        <v>2328.1187566293</v>
+        <v>2328.1187536917</v>
       </c>
       <c r="O738" t="n">
-        <v>1638995.604667027</v>
+        <v>1634339.365091573</v>
       </c>
       <c r="P738" t="n">
         <v>4500</v>
       </c>
       <c r="Q738" t="n">
-        <v>3168000</v>
+        <v>3159000</v>
       </c>
     </row>
     <row r="739">
@@ -32826,7 +32829,7 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
@@ -32835,19 +32838,19 @@
         <v>0</v>
       </c>
       <c r="M747" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="N747" t="n">
         <v>3519</v>
       </c>
       <c r="O747" t="n">
-        <v>932535</v>
+        <v>911421</v>
       </c>
       <c r="P747" t="n">
         <v>5900</v>
       </c>
       <c r="Q747" t="n">
-        <v>1563500</v>
+        <v>1528100</v>
       </c>
     </row>
     <row r="748">
@@ -32918,7 +32921,7 @@
         </is>
       </c>
       <c r="J749" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K749" t="n">
         <v>0</v>
@@ -32927,19 +32930,19 @@
         <v>0</v>
       </c>
       <c r="M749" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N749" t="n">
-        <v>9003</v>
+        <v>9045.4669811321</v>
       </c>
       <c r="O749" t="n">
-        <v>711237</v>
+        <v>687455.4905660396</v>
       </c>
       <c r="P749" t="n">
         <v>14900</v>
       </c>
       <c r="Q749" t="n">
-        <v>1177100</v>
+        <v>1132400</v>
       </c>
     </row>
     <row r="750">
@@ -33787,7 +33790,7 @@
         </is>
       </c>
       <c r="J768" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K768" t="n">
         <v>0</v>
@@ -33796,19 +33799,19 @@
         <v>0</v>
       </c>
       <c r="M768" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N768" t="n">
         <v>5342</v>
       </c>
       <c r="O768" t="n">
-        <v>21368</v>
+        <v>10684</v>
       </c>
       <c r="P768" t="n">
         <v>8900</v>
       </c>
       <c r="Q768" t="n">
-        <v>35600</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="769">
@@ -33833,7 +33836,7 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K769" t="n">
         <v>0</v>
@@ -33842,19 +33845,19 @@
         <v>0</v>
       </c>
       <c r="M769" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N769" t="n">
-        <v>4202</v>
+        <v>4223.6597938144</v>
       </c>
       <c r="O769" t="n">
-        <v>294140</v>
+        <v>287208.8659793792</v>
       </c>
       <c r="P769" t="n">
         <v>7900</v>
       </c>
       <c r="Q769" t="n">
-        <v>553000</v>
+        <v>537200</v>
       </c>
     </row>
     <row r="770">
@@ -33925,7 +33928,7 @@
         </is>
       </c>
       <c r="J771" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K771" t="n">
         <v>0</v>
@@ -33934,19 +33937,19 @@
         <v>0</v>
       </c>
       <c r="M771" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N771" t="n">
         <v>16469</v>
       </c>
       <c r="O771" t="n">
-        <v>1086954</v>
+        <v>1070485</v>
       </c>
       <c r="P771" t="n">
         <v>26900</v>
       </c>
       <c r="Q771" t="n">
-        <v>1775400</v>
+        <v>1748500</v>
       </c>
     </row>
     <row r="772">
@@ -34017,7 +34020,7 @@
         </is>
       </c>
       <c r="J773" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K773" t="n">
         <v>0</v>
@@ -34026,19 +34029,19 @@
         <v>0</v>
       </c>
       <c r="M773" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N773" t="n">
         <v>12556</v>
       </c>
       <c r="O773" t="n">
-        <v>1406272</v>
+        <v>1368604</v>
       </c>
       <c r="P773" t="n">
         <v>21900</v>
       </c>
       <c r="Q773" t="n">
-        <v>2452800</v>
+        <v>2387100</v>
       </c>
     </row>
     <row r="774">
@@ -34063,7 +34066,7 @@
         </is>
       </c>
       <c r="J774" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K774" t="n">
         <v>0</v>
@@ -34072,19 +34075,19 @@
         <v>0</v>
       </c>
       <c r="M774" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N774" t="n">
-        <v>9839</v>
+        <v>10095.669565217</v>
       </c>
       <c r="O774" t="n">
-        <v>846154</v>
+        <v>837940.573913011</v>
       </c>
       <c r="P774" t="n">
         <v>16900</v>
       </c>
       <c r="Q774" t="n">
-        <v>1453400</v>
+        <v>1402700</v>
       </c>
     </row>
     <row r="775">
@@ -34167,10 +34170,10 @@
         <v>280</v>
       </c>
       <c r="N776" t="n">
-        <v>5869.1727755511</v>
+        <v>5869.1727610442</v>
       </c>
       <c r="O776" t="n">
-        <v>1643368.377154308</v>
+        <v>1643368.373092376</v>
       </c>
       <c r="P776" t="n">
         <v>9500</v>
@@ -34615,7 +34618,7 @@
         </is>
       </c>
       <c r="J786" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K786" t="n">
         <v>0</v>
@@ -34624,19 +34627,19 @@
         <v>0</v>
       </c>
       <c r="M786" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="N786" t="n">
         <v>7562</v>
       </c>
       <c r="O786" t="n">
-        <v>597398</v>
+        <v>552026</v>
       </c>
       <c r="P786" t="n">
         <v>12900</v>
       </c>
       <c r="Q786" t="n">
-        <v>1019100</v>
+        <v>941700</v>
       </c>
     </row>
     <row r="787">
@@ -34661,7 +34664,7 @@
         </is>
       </c>
       <c r="J787" t="n">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="K787" t="n">
         <v>0</v>
@@ -34670,19 +34673,19 @@
         <v>0</v>
       </c>
       <c r="M787" t="n">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="N787" t="n">
         <v>3898</v>
       </c>
       <c r="O787" t="n">
-        <v>1173298</v>
+        <v>1149910</v>
       </c>
       <c r="P787" t="n">
         <v>6900</v>
       </c>
       <c r="Q787" t="n">
-        <v>2076900</v>
+        <v>2035500</v>
       </c>
     </row>
     <row r="788">
@@ -34845,7 +34848,7 @@
         </is>
       </c>
       <c r="J791" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K791" t="n">
         <v>0</v>
@@ -34854,19 +34857,19 @@
         <v>0</v>
       </c>
       <c r="M791" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N791" t="n">
         <v>5438</v>
       </c>
       <c r="O791" t="n">
-        <v>266462</v>
+        <v>261024</v>
       </c>
       <c r="P791" t="n">
         <v>8900</v>
       </c>
       <c r="Q791" t="n">
-        <v>436100</v>
+        <v>427200</v>
       </c>
     </row>
     <row r="792">
@@ -35766,7 +35769,7 @@
         </is>
       </c>
       <c r="J811" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K811" t="n">
         <v>0</v>
@@ -35775,19 +35778,19 @@
         <v>0</v>
       </c>
       <c r="M811" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N811" t="n">
         <v>20014</v>
       </c>
       <c r="O811" t="n">
-        <v>520364</v>
+        <v>500350</v>
       </c>
       <c r="P811" t="n">
         <v>33900</v>
       </c>
       <c r="Q811" t="n">
-        <v>881400</v>
+        <v>847500</v>
       </c>
     </row>
     <row r="812">
@@ -35916,10 +35919,10 @@
         <v>102</v>
       </c>
       <c r="N814" t="n">
-        <v>4268.7030223881</v>
+        <v>4268.7033206107</v>
       </c>
       <c r="O814" t="n">
-        <v>435407.7082835862</v>
+        <v>435407.7387022914</v>
       </c>
       <c r="P814" t="n">
         <v>6900</v>
@@ -35950,7 +35953,7 @@
         </is>
       </c>
       <c r="J815" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="K815" t="n">
         <v>0</v>
@@ -35959,19 +35962,19 @@
         <v>0</v>
       </c>
       <c r="M815" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N815" t="n">
         <v>5215</v>
       </c>
       <c r="O815" t="n">
-        <v>526715</v>
+        <v>505855</v>
       </c>
       <c r="P815" t="n">
         <v>8900</v>
       </c>
       <c r="Q815" t="n">
-        <v>898900</v>
+        <v>863300</v>
       </c>
     </row>
     <row r="816">
@@ -36180,7 +36183,7 @@
         </is>
       </c>
       <c r="J820" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K820" t="n">
         <v>0</v>
@@ -36189,19 +36192,19 @@
         <v>0</v>
       </c>
       <c r="M820" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N820" t="n">
         <v>5588</v>
       </c>
       <c r="O820" t="n">
-        <v>407924</v>
+        <v>396748</v>
       </c>
       <c r="P820" t="n">
         <v>9500</v>
       </c>
       <c r="Q820" t="n">
-        <v>693500</v>
+        <v>674500</v>
       </c>
     </row>
     <row r="821">
@@ -36640,7 +36643,7 @@
         </is>
       </c>
       <c r="J830" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K830" t="n">
         <v>0</v>
@@ -36649,19 +36652,19 @@
         <v>0</v>
       </c>
       <c r="M830" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N830" t="n">
         <v>4118</v>
       </c>
       <c r="O830" t="n">
-        <v>61770</v>
+        <v>49416</v>
       </c>
       <c r="P830" t="n">
         <v>6900</v>
       </c>
       <c r="Q830" t="n">
-        <v>103500</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="831">
@@ -36873,7 +36876,7 @@
         </is>
       </c>
       <c r="J835" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K835" t="n">
         <v>0</v>
@@ -36882,19 +36885,19 @@
         <v>0</v>
       </c>
       <c r="M835" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N835" t="n">
         <v>64612</v>
       </c>
       <c r="O835" t="n">
-        <v>2002972</v>
+        <v>1744524</v>
       </c>
       <c r="P835" t="n">
         <v>103900</v>
       </c>
       <c r="Q835" t="n">
-        <v>3220900</v>
+        <v>2805300</v>
       </c>
     </row>
     <row r="836">
@@ -36919,7 +36922,7 @@
         </is>
       </c>
       <c r="J836" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K836" t="n">
         <v>0</v>
@@ -36928,19 +36931,19 @@
         <v>0</v>
       </c>
       <c r="M836" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N836" t="n">
         <v>38252</v>
       </c>
       <c r="O836" t="n">
-        <v>38252</v>
+        <v>420772</v>
       </c>
       <c r="P836" t="n">
         <v>61900</v>
       </c>
       <c r="Q836" t="n">
-        <v>61900</v>
+        <v>680900</v>
       </c>
     </row>
     <row r="837">
@@ -36965,7 +36968,7 @@
         </is>
       </c>
       <c r="J837" t="n">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="K837" t="n">
         <v>0</v>
@@ -36974,19 +36977,19 @@
         <v>0</v>
       </c>
       <c r="M837" t="n">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="N837" t="n">
-        <v>1516.0388180509</v>
+        <v>1516.0388166875</v>
       </c>
       <c r="O837" t="n">
-        <v>930847.8342832527</v>
+        <v>915687.44527925</v>
       </c>
       <c r="P837" t="n">
         <v>2300</v>
       </c>
       <c r="Q837" t="n">
-        <v>1412200</v>
+        <v>1389200</v>
       </c>
     </row>
     <row r="838">
@@ -37011,7 +37014,7 @@
         </is>
       </c>
       <c r="J838" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="K838" t="n">
         <v>0</v>
@@ -37020,19 +37023,19 @@
         <v>0</v>
       </c>
       <c r="M838" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="N838" t="n">
-        <v>4248.6122696629</v>
+        <v>4248.6136842105</v>
       </c>
       <c r="O838" t="n">
-        <v>845473.8416629171</v>
+        <v>735010.1673684164</v>
       </c>
       <c r="P838" t="n">
         <v>5900</v>
       </c>
       <c r="Q838" t="n">
-        <v>1174100</v>
+        <v>1020700</v>
       </c>
     </row>
     <row r="839">
@@ -37101,7 +37104,7 @@
         </is>
       </c>
       <c r="J840" t="n">
-        <v>426</v>
+        <v>378</v>
       </c>
       <c r="K840" t="n">
         <v>0</v>
@@ -37110,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="M840" t="n">
-        <v>426</v>
+        <v>378</v>
       </c>
       <c r="N840" t="n">
-        <v>2458.5135821813</v>
+        <v>2458.5134637046</v>
       </c>
       <c r="O840" t="n">
-        <v>1047326.786009234</v>
+        <v>929318.0892803387</v>
       </c>
       <c r="P840" t="n">
         <v>3500</v>
       </c>
       <c r="Q840" t="n">
-        <v>1491000</v>
+        <v>1323000</v>
       </c>
     </row>
     <row r="841">
@@ -37147,7 +37150,7 @@
         </is>
       </c>
       <c r="J841" t="n">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="K841" t="n">
         <v>0</v>
@@ -37156,19 +37159,19 @@
         <v>0</v>
       </c>
       <c r="M841" t="n">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="N841" t="n">
-        <v>1907.3945816073</v>
+        <v>1946.0906677937</v>
       </c>
       <c r="O841" t="n">
-        <v>417719.4133719987</v>
+        <v>379487.6802197715</v>
       </c>
       <c r="P841" t="n">
         <v>2500</v>
       </c>
       <c r="Q841" t="n">
-        <v>547500</v>
+        <v>487500</v>
       </c>
     </row>
     <row r="842">
@@ -37193,7 +37196,7 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
@@ -37202,19 +37205,19 @@
         <v>0</v>
       </c>
       <c r="M842" t="n">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="N842" t="n">
-        <v>1771.0914183976</v>
+        <v>1796.7129837251</v>
       </c>
       <c r="O842" t="n">
-        <v>377242.4721186888</v>
+        <v>339578.7539240439</v>
       </c>
       <c r="P842" t="n">
         <v>2500</v>
       </c>
       <c r="Q842" t="n">
-        <v>532500</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="843">
@@ -37239,7 +37242,7 @@
         </is>
       </c>
       <c r="J843" t="n">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="K843" t="n">
         <v>0</v>
@@ -37248,19 +37251,19 @@
         <v>0</v>
       </c>
       <c r="M843" t="n">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="N843" t="n">
-        <v>2079.384280218</v>
+        <v>2095.5452849741</v>
       </c>
       <c r="O843" t="n">
-        <v>929484.7732574461</v>
+        <v>886415.6555440443</v>
       </c>
       <c r="P843" t="n">
         <v>2900</v>
       </c>
       <c r="Q843" t="n">
-        <v>1296300</v>
+        <v>1226700</v>
       </c>
     </row>
     <row r="844">
@@ -37285,7 +37288,7 @@
         </is>
       </c>
       <c r="J844" t="n">
-        <v>496</v>
+        <v>448</v>
       </c>
       <c r="K844" t="n">
         <v>0</v>
@@ -37294,19 +37297,19 @@
         <v>0</v>
       </c>
       <c r="M844" t="n">
-        <v>496</v>
+        <v>448</v>
       </c>
       <c r="N844" t="n">
-        <v>1803.0149016773</v>
+        <v>1828.4692441176</v>
       </c>
       <c r="O844" t="n">
-        <v>894295.3912319408</v>
+        <v>819154.2213646849</v>
       </c>
       <c r="P844" t="n">
         <v>2500</v>
       </c>
       <c r="Q844" t="n">
-        <v>1240000</v>
+        <v>1120000</v>
       </c>
     </row>
     <row r="845">
@@ -37343,10 +37346,10 @@
         <v>74</v>
       </c>
       <c r="N845" t="n">
-        <v>3306.5954716981</v>
+        <v>3306.5954602774</v>
       </c>
       <c r="O845" t="n">
-        <v>244688.0649056594</v>
+        <v>244688.0640605276</v>
       </c>
       <c r="P845" t="n">
         <v>4900</v>
@@ -37377,7 +37380,7 @@
         </is>
       </c>
       <c r="J846" t="n">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="K846" t="n">
         <v>0</v>
@@ -37386,19 +37389,19 @@
         <v>0</v>
       </c>
       <c r="M846" t="n">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="N846" t="n">
-        <v>2122.1641716329</v>
+        <v>2137.4820360902</v>
       </c>
       <c r="O846" t="n">
-        <v>1012272.309868893</v>
+        <v>955454.4701323194</v>
       </c>
       <c r="P846" t="n">
         <v>2900</v>
       </c>
       <c r="Q846" t="n">
-        <v>1383300</v>
+        <v>1296300</v>
       </c>
     </row>
     <row r="847">
@@ -37435,10 +37438,10 @@
         <v>66</v>
       </c>
       <c r="N847" t="n">
-        <v>2108.7895881384</v>
+        <v>2108.7897270195</v>
       </c>
       <c r="O847" t="n">
-        <v>139180.1128171344</v>
+        <v>139180.121983287</v>
       </c>
       <c r="P847" t="n">
         <v>2900</v>
@@ -37481,10 +37484,10 @@
         <v>739</v>
       </c>
       <c r="N848" t="n">
-        <v>2056.0839842611</v>
+        <v>2056.0839525344</v>
       </c>
       <c r="O848" t="n">
-        <v>1519446.064368953</v>
+        <v>1519446.040922922</v>
       </c>
       <c r="P848" t="n">
         <v>2900</v>
@@ -37515,7 +37518,7 @@
         </is>
       </c>
       <c r="J849" t="n">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="K849" t="n">
         <v>0</v>
@@ -37524,19 +37527,19 @@
         <v>0</v>
       </c>
       <c r="M849" t="n">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="N849" t="n">
-        <v>3224.5678063672</v>
+        <v>3276.0008772707</v>
       </c>
       <c r="O849" t="n">
-        <v>960921.2062974256</v>
+        <v>858312.2298449235</v>
       </c>
       <c r="P849" t="n">
         <v>4500</v>
       </c>
       <c r="Q849" t="n">
-        <v>1341000</v>
+        <v>1179000</v>
       </c>
     </row>
     <row r="850">
@@ -37561,7 +37564,7 @@
         </is>
       </c>
       <c r="J850" t="n">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="K850" t="n">
         <v>0</v>
@@ -37570,19 +37573,19 @@
         <v>0</v>
       </c>
       <c r="M850" t="n">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="N850" t="n">
-        <v>1655.9314682295</v>
+        <v>1655.9314259144</v>
       </c>
       <c r="O850" t="n">
-        <v>788223.378877242</v>
+        <v>778287.770179768</v>
       </c>
       <c r="P850" t="n">
         <v>2500</v>
       </c>
       <c r="Q850" t="n">
-        <v>1190000</v>
+        <v>1175000</v>
       </c>
     </row>
     <row r="851">
@@ -37932,7 +37935,7 @@
         </is>
       </c>
       <c r="J858" t="n">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="K858" t="n">
         <v>0</v>
@@ -37941,19 +37944,19 @@
         <v>0</v>
       </c>
       <c r="M858" t="n">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="N858" t="n">
-        <v>1592.2744517433</v>
+        <v>1592.2745718734</v>
       </c>
       <c r="O858" t="n">
-        <v>313678.0669934301</v>
+        <v>257948.4806434908</v>
       </c>
       <c r="P858" t="n">
         <v>2500</v>
       </c>
       <c r="Q858" t="n">
-        <v>492500</v>
+        <v>405000</v>
       </c>
     </row>
     <row r="859">
@@ -37976,7 +37979,7 @@
         </is>
       </c>
       <c r="J859" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K859" t="n">
         <v>0</v>
@@ -37985,19 +37988,19 @@
         <v>0</v>
       </c>
       <c r="M859" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N859" t="n">
-        <v>5347.73</v>
+        <v>5414.576625</v>
       </c>
       <c r="O859" t="n">
-        <v>48129.56999999999</v>
+        <v>32487.45975</v>
       </c>
       <c r="P859" t="n">
         <v>9500</v>
       </c>
       <c r="Q859" t="n">
-        <v>85500</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="860">
@@ -38080,10 +38083,10 @@
         <v>88</v>
       </c>
       <c r="N861" t="n">
-        <v>1906.1874003466</v>
+        <v>1906.1870703125</v>
       </c>
       <c r="O861" t="n">
-        <v>167744.4912305008</v>
+        <v>167744.4621875</v>
       </c>
       <c r="P861" t="n">
         <v>2900</v>
@@ -38172,10 +38175,10 @@
         <v>13</v>
       </c>
       <c r="N863" t="n">
-        <v>1668.6136503497</v>
+        <v>1668.6141040462</v>
       </c>
       <c r="O863" t="n">
-        <v>21691.9774545461</v>
+        <v>21691.9833526006</v>
       </c>
       <c r="P863" t="n">
         <v>2500</v>
@@ -38218,10 +38221,10 @@
         <v>87</v>
       </c>
       <c r="N864" t="n">
-        <v>2546.9854340836</v>
+        <v>2546.9853442623</v>
       </c>
       <c r="O864" t="n">
-        <v>221587.7327652732</v>
+        <v>221587.7249508201</v>
       </c>
       <c r="P864" t="n">
         <v>3900</v>
@@ -38252,7 +38255,7 @@
         </is>
       </c>
       <c r="J865" t="n">
-        <v>424</v>
+        <v>292</v>
       </c>
       <c r="K865" t="n">
         <v>0</v>
@@ -38261,19 +38264,19 @@
         <v>0</v>
       </c>
       <c r="M865" t="n">
-        <v>424</v>
+        <v>292</v>
       </c>
       <c r="N865" t="n">
-        <v>1259.2742585952</v>
+        <v>1259.274396777</v>
       </c>
       <c r="O865" t="n">
-        <v>533932.2856443648</v>
+        <v>367708.123858884</v>
       </c>
       <c r="P865" t="n">
         <v>1900</v>
       </c>
       <c r="Q865" t="n">
-        <v>805600</v>
+        <v>554800</v>
       </c>
     </row>
     <row r="866">
@@ -38298,7 +38301,7 @@
         </is>
       </c>
       <c r="J866" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="K866" t="n">
         <v>0</v>
@@ -38307,19 +38310,19 @@
         <v>0</v>
       </c>
       <c r="M866" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="N866" t="n">
-        <v>2980</v>
+        <v>3051.52</v>
       </c>
       <c r="O866" t="n">
-        <v>181780</v>
+        <v>167833.6</v>
       </c>
       <c r="P866" t="n">
         <v>4800</v>
       </c>
       <c r="Q866" t="n">
-        <v>292800</v>
+        <v>264000</v>
       </c>
     </row>
     <row r="867">
@@ -38400,10 +38403,10 @@
         <v>121</v>
       </c>
       <c r="N868" t="n">
-        <v>692.15203442189</v>
+        <v>692.1520380194499</v>
       </c>
       <c r="O868" t="n">
-        <v>83750.39616504869</v>
+        <v>83750.39660035344</v>
       </c>
       <c r="P868" t="n">
         <v>1200</v>
@@ -39363,7 +39366,7 @@
         </is>
       </c>
       <c r="J889" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K889" t="n">
         <v>0</v>
@@ -39372,19 +39375,19 @@
         <v>0</v>
       </c>
       <c r="M889" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N889" t="n">
-        <v>2682.71</v>
+        <v>2769.7168108108</v>
       </c>
       <c r="O889" t="n">
-        <v>131452.79</v>
+        <v>110788.672432432</v>
       </c>
       <c r="P889" t="n">
         <v>10900</v>
       </c>
       <c r="Q889" t="n">
-        <v>534100</v>
+        <v>436000</v>
       </c>
     </row>
     <row r="890">
@@ -39769,7 +39772,7 @@
         </is>
       </c>
       <c r="J898" t="n">
-        <v>3803</v>
+        <v>3763</v>
       </c>
       <c r="K898" t="n">
         <v>0</v>
@@ -39778,19 +39781,19 @@
         <v>0</v>
       </c>
       <c r="M898" t="n">
-        <v>3803</v>
+        <v>3763</v>
       </c>
       <c r="N898" t="n">
-        <v>574.67193864057</v>
+        <v>577.72789151821</v>
       </c>
       <c r="O898" t="n">
-        <v>2185477.382650088</v>
+        <v>2173990.055783024</v>
       </c>
       <c r="P898" t="n">
         <v>800</v>
       </c>
       <c r="Q898" t="n">
-        <v>3042400</v>
+        <v>3010400</v>
       </c>
     </row>
     <row r="899">
@@ -39861,7 +39864,7 @@
         </is>
       </c>
       <c r="J900" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K900" t="n">
         <v>0</v>
@@ -39870,19 +39873,19 @@
         <v>0</v>
       </c>
       <c r="M900" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N900" t="n">
         <v>6898.4</v>
       </c>
       <c r="O900" t="n">
-        <v>310428</v>
+        <v>269037.6</v>
       </c>
       <c r="P900" t="n">
         <v>12900</v>
       </c>
       <c r="Q900" t="n">
-        <v>580500</v>
+        <v>503100</v>
       </c>
     </row>
     <row r="901">
@@ -40041,7 +40044,7 @@
         </is>
       </c>
       <c r="J904" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="K904" t="n">
         <v>0</v>
@@ -40050,19 +40053,19 @@
         <v>0</v>
       </c>
       <c r="M904" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="N904" t="n">
         <v>1828.64</v>
       </c>
       <c r="O904" t="n">
-        <v>1115470.4</v>
+        <v>1100841.28</v>
       </c>
       <c r="P904" t="n">
         <v>2000</v>
       </c>
       <c r="Q904" t="n">
-        <v>1220000</v>
+        <v>1204000</v>
       </c>
     </row>
     <row r="905">
@@ -40090,7 +40093,7 @@
         </is>
       </c>
       <c r="J905" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K905" t="n">
         <v>0</v>
@@ -40099,19 +40102,19 @@
         <v>0</v>
       </c>
       <c r="M905" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="N905" t="n">
-        <v>2270.320952381</v>
+        <v>2483.1635416667</v>
       </c>
       <c r="O905" t="n">
-        <v>84001.87523809701</v>
+        <v>69528.57916666759</v>
       </c>
       <c r="P905" t="n">
         <v>3900</v>
       </c>
       <c r="Q905" t="n">
-        <v>144300</v>
+        <v>109200</v>
       </c>
     </row>
     <row r="906">
@@ -40539,7 +40542,7 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
@@ -40548,19 +40551,19 @@
         <v>0</v>
       </c>
       <c r="M915" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N915" t="n">
-        <v>2590.4173043478</v>
+        <v>2733.0090825688</v>
       </c>
       <c r="O915" t="n">
-        <v>77712.519130434</v>
+        <v>65592.21798165119</v>
       </c>
       <c r="P915" t="n">
         <v>2800</v>
       </c>
       <c r="Q915" t="n">
-        <v>84000</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="916">
@@ -40629,7 +40632,7 @@
         </is>
       </c>
       <c r="J917" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="K917" t="n">
         <v>0</v>
@@ -40638,19 +40641,19 @@
         <v>0</v>
       </c>
       <c r="M917" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="N917" t="n">
-        <v>1684.79</v>
+        <v>1815.5064655172</v>
       </c>
       <c r="O917" t="n">
-        <v>198805.22</v>
+        <v>181550.64655172</v>
       </c>
       <c r="P917" t="n">
         <v>2900</v>
       </c>
       <c r="Q917" t="n">
-        <v>342200</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="918">
@@ -40673,7 +40676,7 @@
         </is>
       </c>
       <c r="J918" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K918" t="n">
         <v>0</v>
@@ -40682,19 +40685,19 @@
         <v>0</v>
       </c>
       <c r="M918" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N918" t="n">
-        <v>6213.51</v>
+        <v>6349.5722627737</v>
       </c>
       <c r="O918" t="n">
-        <v>391451.13</v>
+        <v>380974.335766422</v>
       </c>
       <c r="P918" t="n">
         <v>10300</v>
       </c>
       <c r="Q918" t="n">
-        <v>648900</v>
+        <v>618000</v>
       </c>
     </row>
     <row r="919">
@@ -40729,10 +40732,10 @@
         <v>1</v>
       </c>
       <c r="N919" t="n">
-        <v>1283.65434375</v>
+        <v>1283.6542902208</v>
       </c>
       <c r="O919" t="n">
-        <v>1283.65434375</v>
+        <v>1283.6542902208</v>
       </c>
       <c r="P919" t="n">
         <v>1900</v>
@@ -41113,7 +41116,7 @@
         </is>
       </c>
       <c r="J928" t="n">
-        <v>1708</v>
+        <v>1418</v>
       </c>
       <c r="K928" t="n">
         <v>0</v>
@@ -41122,19 +41125,19 @@
         <v>0</v>
       </c>
       <c r="M928" t="n">
-        <v>1708</v>
+        <v>1418</v>
       </c>
       <c r="N928" t="n">
         <v>177.65</v>
       </c>
       <c r="O928" t="n">
-        <v>303426.2</v>
+        <v>251907.7</v>
       </c>
       <c r="P928" t="n">
         <v>300</v>
       </c>
       <c r="Q928" t="n">
-        <v>512400</v>
+        <v>425400</v>
       </c>
     </row>
     <row r="929">
@@ -41423,7 +41426,7 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>3833</v>
+        <v>3817</v>
       </c>
       <c r="K935" t="n">
         <v>0</v>
@@ -41432,19 +41435,19 @@
         <v>0</v>
       </c>
       <c r="M935" t="n">
-        <v>3833</v>
+        <v>3817</v>
       </c>
       <c r="N935" t="n">
-        <v>517.28742027978</v>
+        <v>517.28747614462</v>
       </c>
       <c r="O935" t="n">
-        <v>1982762.681932397</v>
+        <v>1974486.296444014</v>
       </c>
       <c r="P935" t="n">
         <v>900</v>
       </c>
       <c r="Q935" t="n">
-        <v>3449700</v>
+        <v>3435300</v>
       </c>
     </row>
     <row r="936">
@@ -41600,7 +41603,7 @@
         </is>
       </c>
       <c r="J939" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K939" t="n">
         <v>0</v>
@@ -41609,19 +41612,19 @@
         <v>0</v>
       </c>
       <c r="M939" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="N939" t="n">
         <v>2703.52</v>
       </c>
       <c r="O939" t="n">
-        <v>124361.92</v>
+        <v>89216.16</v>
       </c>
       <c r="P939" t="n">
         <v>5800</v>
       </c>
       <c r="Q939" t="n">
-        <v>266800</v>
+        <v>191400</v>
       </c>
     </row>
     <row r="940">
@@ -41649,7 +41652,7 @@
         </is>
       </c>
       <c r="J940" t="n">
-        <v>893</v>
+        <v>854</v>
       </c>
       <c r="K940" t="n">
         <v>0</v>
@@ -41658,19 +41661,19 @@
         <v>0</v>
       </c>
       <c r="M940" t="n">
-        <v>893</v>
+        <v>854</v>
       </c>
       <c r="N940" t="n">
-        <v>3110.8434146796</v>
+        <v>3110.8433414956</v>
       </c>
       <c r="O940" t="n">
-        <v>2777983.169308883</v>
+        <v>2656660.213637242</v>
       </c>
       <c r="P940" t="n">
         <v>4500</v>
       </c>
       <c r="Q940" t="n">
-        <v>4018500</v>
+        <v>3843000</v>
       </c>
     </row>
     <row r="941">
@@ -41783,7 +41786,7 @@
         </is>
       </c>
       <c r="J943" t="n">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="K943" t="n">
         <v>0</v>
@@ -41792,19 +41795,19 @@
         <v>0</v>
       </c>
       <c r="M943" t="n">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="N943" t="n">
-        <v>2030.02</v>
+        <v>2047.4600343643</v>
       </c>
       <c r="O943" t="n">
-        <v>1088090.72</v>
+        <v>1056489.377731979</v>
       </c>
       <c r="P943" t="n">
         <v>3600</v>
       </c>
       <c r="Q943" t="n">
-        <v>1929600</v>
+        <v>1857600</v>
       </c>
     </row>
     <row r="944">
@@ -41871,7 +41874,7 @@
         </is>
       </c>
       <c r="J945" t="n">
-        <v>1901</v>
+        <v>1829</v>
       </c>
       <c r="K945" t="n">
         <v>0</v>
@@ -41880,19 +41883,19 @@
         <v>0</v>
       </c>
       <c r="M945" t="n">
-        <v>1901</v>
+        <v>1829</v>
       </c>
       <c r="N945" t="n">
-        <v>703.79546441605</v>
+        <v>704.1779547101401</v>
       </c>
       <c r="O945" t="n">
-        <v>1337915.177854911</v>
+        <v>1287941.479164846</v>
       </c>
       <c r="P945" t="n">
         <v>900</v>
       </c>
       <c r="Q945" t="n">
-        <v>1710900</v>
+        <v>1646100</v>
       </c>
     </row>
     <row r="946">
@@ -41915,7 +41918,7 @@
         </is>
       </c>
       <c r="J946" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K946" t="n">
         <v>0</v>
@@ -41924,19 +41927,19 @@
         <v>0</v>
       </c>
       <c r="M946" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="N946" t="n">
-        <v>6076.92</v>
+        <v>6556.6768421053</v>
       </c>
       <c r="O946" t="n">
-        <v>498307.44</v>
+        <v>498307.4400000028</v>
       </c>
       <c r="P946" t="n">
         <v>7900</v>
       </c>
       <c r="Q946" t="n">
-        <v>647800</v>
+        <v>600400</v>
       </c>
     </row>
     <row r="947">
@@ -41964,7 +41967,7 @@
         </is>
       </c>
       <c r="J947" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K947" t="n">
         <v>0</v>
@@ -41973,19 +41976,19 @@
         <v>0</v>
       </c>
       <c r="M947" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N947" t="n">
-        <v>3182.2510791367</v>
+        <v>3216.9665454545</v>
       </c>
       <c r="O947" t="n">
-        <v>143201.2985611515</v>
+        <v>125461.6952727255</v>
       </c>
       <c r="P947" t="n">
         <v>6900</v>
       </c>
       <c r="Q947" t="n">
-        <v>310500</v>
+        <v>269100</v>
       </c>
     </row>
     <row r="948">
@@ -42156,10 +42159,10 @@
         <v>3</v>
       </c>
       <c r="N951" t="n">
-        <v>2501.3856097561</v>
+        <v>2501.3854811715</v>
       </c>
       <c r="O951" t="n">
-        <v>7504.1568292683</v>
+        <v>7504.1564435145</v>
       </c>
       <c r="P951" t="n">
         <v>4100</v>
@@ -42278,7 +42281,7 @@
         </is>
       </c>
       <c r="J954" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="K954" t="n">
         <v>0</v>
@@ -42287,19 +42290,19 @@
         <v>0</v>
       </c>
       <c r="M954" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="N954" t="n">
-        <v>3384.9036995828</v>
+        <v>3442.356096181</v>
       </c>
       <c r="O954" t="n">
-        <v>622822.2807232352</v>
+        <v>592085.248543132</v>
       </c>
       <c r="P954" t="n">
         <v>4500</v>
       </c>
       <c r="Q954" t="n">
-        <v>828000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="955">
@@ -42455,7 +42458,7 @@
         </is>
       </c>
       <c r="J958" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="K958" t="n">
         <v>0</v>
@@ -42464,19 +42467,19 @@
         <v>0</v>
       </c>
       <c r="M958" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="N958" t="n">
         <v>1937</v>
       </c>
       <c r="O958" t="n">
-        <v>321542</v>
+        <v>311857</v>
       </c>
       <c r="P958" t="n">
         <v>3300</v>
       </c>
       <c r="Q958" t="n">
-        <v>547800</v>
+        <v>531300</v>
       </c>
     </row>
     <row r="959">
@@ -42499,7 +42502,7 @@
         </is>
       </c>
       <c r="J959" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K959" t="n">
         <v>0</v>
@@ -42508,19 +42511,19 @@
         <v>0</v>
       </c>
       <c r="M959" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N959" t="n">
         <v>2525.02</v>
       </c>
       <c r="O959" t="n">
-        <v>234826.86</v>
+        <v>214626.7</v>
       </c>
       <c r="P959" t="n">
         <v>3000</v>
       </c>
       <c r="Q959" t="n">
-        <v>279000</v>
+        <v>255000</v>
       </c>
     </row>
     <row r="960">
@@ -42668,7 +42671,7 @@
         </is>
       </c>
       <c r="J963" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K963" t="n">
         <v>0</v>
@@ -42677,19 +42680,19 @@
         <v>0</v>
       </c>
       <c r="M963" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N963" t="n">
-        <v>2077.4944744318</v>
+        <v>2077.4944871795</v>
       </c>
       <c r="O963" t="n">
-        <v>567155.9915198814</v>
+        <v>563001.0060256445</v>
       </c>
       <c r="P963" t="n">
         <v>2900</v>
       </c>
       <c r="Q963" t="n">
-        <v>791700</v>
+        <v>785900</v>
       </c>
     </row>
     <row r="964">
@@ -42712,7 +42715,7 @@
         </is>
       </c>
       <c r="J964" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K964" t="n">
         <v>0</v>
@@ -42721,19 +42724,19 @@
         <v>0</v>
       </c>
       <c r="M964" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N964" t="n">
-        <v>3629.7161601643</v>
+        <v>3674.9932848233</v>
       </c>
       <c r="O964" t="n">
-        <v>105261.7686447647</v>
+        <v>84524.8455509359</v>
       </c>
       <c r="P964" t="n">
         <v>4900</v>
       </c>
       <c r="Q964" t="n">
-        <v>142100</v>
+        <v>112700</v>
       </c>
     </row>
     <row r="965">
@@ -42940,10 +42943,10 @@
         <v>74</v>
       </c>
       <c r="N969" t="n">
-        <v>1595.5193419662</v>
+        <v>1595.51921946</v>
       </c>
       <c r="O969" t="n">
-        <v>118068.4313054988</v>
+        <v>118068.42224004</v>
       </c>
       <c r="P969" t="n">
         <v>2500</v>
@@ -43465,10 +43468,10 @@
         <v>4</v>
       </c>
       <c r="N980" t="n">
-        <v>2098.4047658402</v>
+        <v>2098.4047922438</v>
       </c>
       <c r="O980" t="n">
-        <v>8393.6190633608</v>
+        <v>8393.619168975199</v>
       </c>
       <c r="P980" t="n">
         <v>9500</v>
@@ -43546,7 +43549,7 @@
         </is>
       </c>
       <c r="J982" t="n">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="K982" t="n">
         <v>0</v>
@@ -43555,19 +43558,19 @@
         <v>0</v>
       </c>
       <c r="M982" t="n">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="N982" t="n">
         <v>1669.6</v>
       </c>
       <c r="O982" t="n">
-        <v>719597.6</v>
+        <v>707910.3999999999</v>
       </c>
       <c r="P982" t="n">
         <v>2900</v>
       </c>
       <c r="Q982" t="n">
-        <v>1249900</v>
+        <v>1229600</v>
       </c>
     </row>
     <row r="983">
@@ -43688,7 +43691,7 @@
         </is>
       </c>
       <c r="J985" t="n">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="K985" t="n">
         <v>0</v>
@@ -43697,19 +43700,19 @@
         <v>0</v>
       </c>
       <c r="M985" t="n">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="N985" t="n">
-        <v>3063.621874063</v>
+        <v>3063.6218825301</v>
       </c>
       <c r="O985" t="n">
-        <v>3985772.058155963</v>
+        <v>3976581.203524069</v>
       </c>
       <c r="P985" t="n">
         <v>3500</v>
       </c>
       <c r="Q985" t="n">
-        <v>4553500</v>
+        <v>4543000</v>
       </c>
     </row>
     <row r="986">
@@ -44127,10 +44130,10 @@
         <v>16</v>
       </c>
       <c r="N994" t="n">
-        <v>3414.566095679</v>
+        <v>3414.5660866203</v>
       </c>
       <c r="O994" t="n">
-        <v>54633.057530864</v>
+        <v>54633.0573859248</v>
       </c>
       <c r="P994" t="n">
         <v>3500</v>
@@ -44246,7 +44249,7 @@
         </is>
       </c>
       <c r="J997" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K997" t="n">
         <v>0</v>
@@ -44255,19 +44258,19 @@
         <v>0</v>
       </c>
       <c r="M997" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N997" t="n">
-        <v>2505.7604968944</v>
+        <v>2602.7576774194</v>
       </c>
       <c r="O997" t="n">
-        <v>112759.222360248</v>
+        <v>101507.5494193566</v>
       </c>
       <c r="P997" t="n">
         <v>3000</v>
       </c>
       <c r="Q997" t="n">
-        <v>135000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="998">
@@ -44574,7 +44577,7 @@
         </is>
       </c>
       <c r="J1004" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="K1004" t="n">
         <v>0</v>
@@ -44583,19 +44586,19 @@
         <v>0</v>
       </c>
       <c r="M1004" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="N1004" t="n">
-        <v>1759.84</v>
+        <v>1900.0042477876</v>
       </c>
       <c r="O1004" t="n">
-        <v>214700.48</v>
+        <v>214700.4799999988</v>
       </c>
       <c r="P1004" t="n">
         <v>3300</v>
       </c>
       <c r="Q1004" t="n">
-        <v>402600</v>
+        <v>372900</v>
       </c>
     </row>
     <row r="1005">
@@ -45050,10 +45053,10 @@
         <v>2</v>
       </c>
       <c r="N1014" t="n">
-        <v>2000.6538150289</v>
+        <v>2000.656035503</v>
       </c>
       <c r="O1014" t="n">
-        <v>4001.3076300578</v>
+        <v>4001.312071006</v>
       </c>
       <c r="P1014" t="n">
         <v>2000</v>
@@ -45133,7 +45136,7 @@
         </is>
       </c>
       <c r="J1016" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K1016" t="n">
         <v>0</v>
@@ -45142,19 +45145,19 @@
         <v>0</v>
       </c>
       <c r="M1016" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N1016" t="n">
         <v>1024.29</v>
       </c>
       <c r="O1016" t="n">
-        <v>6145.74</v>
+        <v>3072.87</v>
       </c>
       <c r="P1016" t="n">
         <v>2900</v>
       </c>
       <c r="Q1016" t="n">
-        <v>17400</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="1017">
@@ -45182,7 +45185,7 @@
         </is>
       </c>
       <c r="J1017" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K1017" t="n">
         <v>0</v>
@@ -45191,19 +45194,19 @@
         <v>0</v>
       </c>
       <c r="M1017" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N1017" t="n">
-        <v>711.48</v>
+        <v>713.93197013211</v>
       </c>
       <c r="O1017" t="n">
-        <v>9960.720000000001</v>
+        <v>3569.65985066055</v>
       </c>
       <c r="P1017" t="n">
         <v>2500</v>
       </c>
       <c r="Q1017" t="n">
-        <v>35000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="1018">
@@ -45429,10 +45432,10 @@
         <v>215</v>
       </c>
       <c r="N1022" t="n">
-        <v>7046.9398307595</v>
+        <v>7046.9398305803</v>
       </c>
       <c r="O1022" t="n">
-        <v>1515092.063613293</v>
+        <v>1515092.063574764</v>
       </c>
       <c r="P1022" t="n">
         <v>9900</v>
@@ -45748,10 +45751,10 @@
         <v>11</v>
       </c>
       <c r="N1029" t="n">
-        <v>2397.6836666667</v>
+        <v>2397.7455</v>
       </c>
       <c r="O1029" t="n">
-        <v>26374.5203333337</v>
+        <v>26375.2005</v>
       </c>
       <c r="P1029" t="n">
         <v>2000</v>
@@ -46076,7 +46079,7 @@
         </is>
       </c>
       <c r="J1036" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K1036" t="n">
         <v>0</v>
@@ -46085,19 +46088,19 @@
         <v>0</v>
       </c>
       <c r="M1036" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N1036" t="n">
-        <v>2010.71</v>
+        <v>2251.9952</v>
       </c>
       <c r="O1036" t="n">
-        <v>48257.04</v>
+        <v>40535.9136</v>
       </c>
       <c r="P1036" t="n">
         <v>7200</v>
       </c>
       <c r="Q1036" t="n">
-        <v>172800</v>
+        <v>129600</v>
       </c>
     </row>
     <row r="1037">
@@ -46354,7 +46357,7 @@
         </is>
       </c>
       <c r="J1042" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K1042" t="n">
         <v>0</v>
@@ -46363,19 +46366,19 @@
         <v>0</v>
       </c>
       <c r="M1042" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="N1042" t="n">
-        <v>2752.52</v>
+        <v>2851.4129341317</v>
       </c>
       <c r="O1042" t="n">
-        <v>57802.92</v>
+        <v>42771.19401197549</v>
       </c>
       <c r="P1042" t="n">
         <v>4500</v>
       </c>
       <c r="Q1042" t="n">
-        <v>94500</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="1043">
@@ -46565,7 +46568,7 @@
         </is>
       </c>
       <c r="J1047" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K1047" t="n">
         <v>0</v>
@@ -46574,19 +46577,19 @@
         <v>0</v>
       </c>
       <c r="M1047" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="N1047" t="n">
         <v>2459</v>
       </c>
       <c r="O1047" t="n">
-        <v>233605</v>
+        <v>206556</v>
       </c>
       <c r="P1047" t="n">
         <v>3900</v>
       </c>
       <c r="Q1047" t="n">
-        <v>370500</v>
+        <v>327600</v>
       </c>
     </row>
     <row r="1048">
@@ -46609,7 +46612,7 @@
         </is>
       </c>
       <c r="J1048" t="n">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="K1048" t="n">
         <v>0</v>
@@ -46618,19 +46621,19 @@
         <v>0</v>
       </c>
       <c r="M1048" t="n">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="N1048" t="n">
-        <v>704.89680318544</v>
+        <v>714.37850499616</v>
       </c>
       <c r="O1048" t="n">
-        <v>296056.6573378848</v>
+        <v>275035.7244235216</v>
       </c>
       <c r="P1048" t="n">
         <v>900</v>
       </c>
       <c r="Q1048" t="n">
-        <v>378000</v>
+        <v>346500</v>
       </c>
     </row>
     <row r="1049">
@@ -46873,10 +46876,10 @@
         <v>259</v>
       </c>
       <c r="N1054" t="n">
-        <v>6172.7748154093</v>
+        <v>6172.7748309179</v>
       </c>
       <c r="O1054" t="n">
-        <v>1598748.677191009</v>
+        <v>1598748.681207736</v>
       </c>
       <c r="P1054" t="n">
         <v>8000</v>
@@ -47162,7 +47165,7 @@
         </is>
       </c>
       <c r="J1061" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="K1061" t="n">
         <v>0</v>
@@ -47171,19 +47174,19 @@
         <v>0</v>
       </c>
       <c r="M1061" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N1061" t="n">
-        <v>824.64110643805</v>
+        <v>827.85503734979</v>
       </c>
       <c r="O1061" t="n">
-        <v>43705.97864121665</v>
+        <v>33942.05653134139</v>
       </c>
       <c r="P1061" t="n">
         <v>1000</v>
       </c>
       <c r="Q1061" t="n">
-        <v>53000</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="1062">
@@ -47417,7 +47420,7 @@
         </is>
       </c>
       <c r="J1067" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K1067" t="n">
         <v>0</v>
@@ -47426,19 +47429,19 @@
         <v>0</v>
       </c>
       <c r="M1067" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N1067" t="n">
-        <v>2489.1752825298</v>
+        <v>2496.9418200728</v>
       </c>
       <c r="O1067" t="n">
-        <v>129437.1146915496</v>
+        <v>114859.3237233488</v>
       </c>
       <c r="P1067" t="n">
         <v>3000</v>
       </c>
       <c r="Q1067" t="n">
-        <v>156000</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="1068">
@@ -47502,7 +47505,7 @@
         </is>
       </c>
       <c r="J1069" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K1069" t="n">
         <v>0</v>
@@ -47511,19 +47514,19 @@
         <v>0</v>
       </c>
       <c r="M1069" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N1069" t="n">
-        <v>2952.08775</v>
+        <v>2967.9876840215</v>
       </c>
       <c r="O1069" t="n">
-        <v>121035.59775</v>
+        <v>112783.531992817</v>
       </c>
       <c r="P1069" t="n">
         <v>3800</v>
       </c>
       <c r="Q1069" t="n">
-        <v>155800</v>
+        <v>144400</v>
       </c>
     </row>
     <row r="1070">
@@ -47546,7 +47549,7 @@
         </is>
       </c>
       <c r="J1070" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K1070" t="n">
         <v>0</v>
@@ -47555,19 +47558,19 @@
         <v>0</v>
       </c>
       <c r="M1070" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N1070" t="n">
-        <v>3167.0258364312</v>
+        <v>3178.8430970149</v>
       </c>
       <c r="O1070" t="n">
-        <v>256529.0927509272</v>
+        <v>247949.7615671622</v>
       </c>
       <c r="P1070" t="n">
         <v>4000</v>
       </c>
       <c r="Q1070" t="n">
-        <v>324000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="1071">
@@ -47807,7 +47810,7 @@
         </is>
       </c>
       <c r="J1076" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1076" t="n">
         <v>0</v>
@@ -47816,19 +47819,19 @@
         <v>0</v>
       </c>
       <c r="M1076" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N1076" t="n">
-        <v>2988.7998657718</v>
+        <v>2998.8631649832</v>
       </c>
       <c r="O1076" t="n">
-        <v>11955.1994630872</v>
+        <v>2998.8631649832</v>
       </c>
       <c r="P1076" t="n">
         <v>3800</v>
       </c>
       <c r="Q1076" t="n">
-        <v>15200</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="1077">
@@ -47980,7 +47983,7 @@
         </is>
       </c>
       <c r="J1080" t="n">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="K1080" t="n">
         <v>0</v>
@@ -47989,19 +47992,19 @@
         <v>0</v>
       </c>
       <c r="M1080" t="n">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="N1080" t="n">
-        <v>3181.9</v>
+        <v>3192.6751439214</v>
       </c>
       <c r="O1080" t="n">
-        <v>1059572.7</v>
+        <v>989729.294615634</v>
       </c>
       <c r="P1080" t="n">
         <v>5100</v>
       </c>
       <c r="Q1080" t="n">
-        <v>1698300</v>
+        <v>1581000</v>
       </c>
     </row>
     <row r="1081">
@@ -48106,7 +48109,7 @@
         </is>
       </c>
       <c r="J1083" t="n">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="K1083" t="n">
         <v>0</v>
@@ -48115,19 +48118,19 @@
         <v>0</v>
       </c>
       <c r="M1083" t="n">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="N1083" t="n">
-        <v>1794.2879877441</v>
+        <v>1803.5408695029</v>
       </c>
       <c r="O1083" t="n">
-        <v>410891.9491933989</v>
+        <v>348083.3878140597</v>
       </c>
       <c r="P1083" t="n">
         <v>1600</v>
       </c>
       <c r="Q1083" t="n">
-        <v>366400</v>
+        <v>308800</v>
       </c>
     </row>
     <row r="1084">
@@ -48282,7 +48285,7 @@
         </is>
       </c>
       <c r="J1087" t="n">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="K1087" t="n">
         <v>0</v>
@@ -48291,19 +48294,19 @@
         <v>0</v>
       </c>
       <c r="M1087" t="n">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="N1087" t="n">
-        <v>2830.224701087</v>
+        <v>3081.4280769231</v>
       </c>
       <c r="O1087" t="n">
-        <v>345287.413532614</v>
+        <v>283491.3830769252</v>
       </c>
       <c r="P1087" t="n">
         <v>2400</v>
       </c>
       <c r="Q1087" t="n">
-        <v>292800</v>
+        <v>220800</v>
       </c>
     </row>
     <row r="1088">
@@ -48458,7 +48461,7 @@
         </is>
       </c>
       <c r="J1091" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="K1091" t="n">
         <v>0</v>
@@ -48467,19 +48470,19 @@
         <v>0</v>
       </c>
       <c r="M1091" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="N1091" t="n">
-        <v>2523.3377665827</v>
+        <v>2540.4017582418</v>
       </c>
       <c r="O1091" t="n">
-        <v>164016.9548278755</v>
+        <v>104156.4720879138</v>
       </c>
       <c r="P1091" t="n">
         <v>2800</v>
       </c>
       <c r="Q1091" t="n">
-        <v>182000</v>
+        <v>114800</v>
       </c>
     </row>
     <row r="1092">
@@ -49134,7 +49137,7 @@
         </is>
       </c>
       <c r="J1107" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="K1107" t="n">
         <v>0</v>
@@ -49143,19 +49146,19 @@
         <v>0</v>
       </c>
       <c r="M1107" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="N1107" t="n">
         <v>5077</v>
       </c>
       <c r="O1107" t="n">
-        <v>837705</v>
+        <v>797089</v>
       </c>
       <c r="P1107" t="n">
         <v>8500</v>
       </c>
       <c r="Q1107" t="n">
-        <v>1402500</v>
+        <v>1334500</v>
       </c>
     </row>
     <row r="1108">
@@ -49267,7 +49270,7 @@
         </is>
       </c>
       <c r="J1110" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="K1110" t="n">
         <v>0</v>
@@ -49276,19 +49279,19 @@
         <v>0</v>
       </c>
       <c r="M1110" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="N1110" t="n">
-        <v>705.52801652893</v>
+        <v>707.12182981928</v>
       </c>
       <c r="O1110" t="n">
-        <v>206014.1808264476</v>
+        <v>204358.2088177719</v>
       </c>
       <c r="P1110" t="n">
         <v>1500</v>
       </c>
       <c r="Q1110" t="n">
-        <v>438000</v>
+        <v>433500</v>
       </c>
     </row>
     <row r="1111">
@@ -49308,7 +49311,7 @@
         </is>
       </c>
       <c r="J1111" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K1111" t="n">
         <v>0</v>
@@ -49317,19 +49320,19 @@
         <v>0</v>
       </c>
       <c r="M1111" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N1111" t="n">
-        <v>4985.404494382</v>
+        <v>4985.4045627376</v>
       </c>
       <c r="O1111" t="n">
-        <v>229328.606741572</v>
+        <v>209386.9916349792</v>
       </c>
       <c r="P1111" t="n">
         <v>7900</v>
       </c>
       <c r="Q1111" t="n">
-        <v>363400</v>
+        <v>331800</v>
       </c>
     </row>
     <row r="1112">
@@ -49371,10 +49374,10 @@
         <v>69</v>
       </c>
       <c r="N1112" t="n">
-        <v>1757.320513834</v>
+        <v>1757.320515873</v>
       </c>
       <c r="O1112" t="n">
-        <v>121255.115454546</v>
+        <v>121255.115595237</v>
       </c>
       <c r="P1112" t="n">
         <v>2000</v>
@@ -50080,7 +50083,7 @@
         </is>
       </c>
       <c r="J1128" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K1128" t="n">
         <v>0</v>
@@ -50089,19 +50092,19 @@
         <v>0</v>
       </c>
       <c r="M1128" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="N1128" t="n">
-        <v>1160.1549333333</v>
+        <v>1338.6403076923</v>
       </c>
       <c r="O1128" t="n">
-        <v>45246.0423999987</v>
+        <v>38820.5689230767</v>
       </c>
       <c r="P1128" t="n">
         <v>1600</v>
       </c>
       <c r="Q1128" t="n">
-        <v>62400</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="1129">
@@ -51455,7 +51458,7 @@
         </is>
       </c>
       <c r="J1158" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K1158" t="n">
         <v>0</v>
@@ -51464,19 +51467,19 @@
         <v>0</v>
       </c>
       <c r="M1158" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="N1158" t="n">
-        <v>576.58</v>
+        <v>614.59626373626</v>
       </c>
       <c r="O1158" t="n">
-        <v>19603.72</v>
+        <v>17208.69538461528</v>
       </c>
       <c r="P1158" t="n">
         <v>5900</v>
       </c>
       <c r="Q1158" t="n">
-        <v>200600</v>
+        <v>165200</v>
       </c>
     </row>
     <row r="1159">
@@ -51690,7 +51693,7 @@
         </is>
       </c>
       <c r="J1163" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="K1163" t="n">
         <v>0</v>
@@ -51699,19 +51702,19 @@
         <v>0</v>
       </c>
       <c r="M1163" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="N1163" t="n">
-        <v>227.41590317919</v>
+        <v>229.9076771366</v>
       </c>
       <c r="O1163" t="n">
-        <v>29791.48331647389</v>
+        <v>26669.2905478456</v>
       </c>
       <c r="P1163" t="n">
         <v>1200</v>
       </c>
       <c r="Q1163" t="n">
-        <v>157200</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="1164">
@@ -52135,7 +52138,7 @@
         </is>
       </c>
       <c r="J1173" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K1173" t="n">
         <v>0</v>
@@ -52144,19 +52147,19 @@
         <v>0</v>
       </c>
       <c r="M1173" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N1173" t="n">
-        <v>2200</v>
+        <v>2464</v>
       </c>
       <c r="O1173" t="n">
-        <v>48400</v>
+        <v>46816</v>
       </c>
       <c r="P1173" t="n">
         <v>2700</v>
       </c>
       <c r="Q1173" t="n">
-        <v>59400</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="1174">
@@ -52181,7 +52184,7 @@
         </is>
       </c>
       <c r="J1174" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K1174" t="n">
         <v>0</v>
@@ -52190,10 +52193,10 @@
         <v>0</v>
       </c>
       <c r="M1174" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N1174" t="n">
-        <v>2200</v>
+        <v>2750</v>
       </c>
       <c r="O1174" t="n">
         <v>33000</v>
@@ -52202,7 +52205,7 @@
         <v>2700</v>
       </c>
       <c r="Q1174" t="n">
-        <v>40500</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="1175">
@@ -52636,7 +52639,7 @@
         </is>
       </c>
       <c r="J1184" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K1184" t="n">
         <v>0</v>
@@ -52645,19 +52648,19 @@
         <v>0</v>
       </c>
       <c r="M1184" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N1184" t="n">
         <v>4550</v>
       </c>
       <c r="O1184" t="n">
-        <v>1528800</v>
+        <v>1510600</v>
       </c>
       <c r="P1184" t="n">
         <v>6500</v>
       </c>
       <c r="Q1184" t="n">
-        <v>2184000</v>
+        <v>2158000</v>
       </c>
     </row>
     <row r="1185">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1401,10 +1401,10 @@
         <v>241</v>
       </c>
       <c r="N24" t="n">
-        <v>1815.9962867012</v>
+        <v>1811.3037996546</v>
       </c>
       <c r="O24" t="n">
-        <v>437655.1050949892</v>
+        <v>436524.2157167586</v>
       </c>
       <c r="P24" t="n">
         <v>2600</v>
@@ -1479,10 +1479,10 @@
         <v>74</v>
       </c>
       <c r="N26" t="n">
-        <v>2001.2446341463</v>
+        <v>1990.0436022514</v>
       </c>
       <c r="O26" t="n">
-        <v>148092.1029268262</v>
+        <v>147263.2265666036</v>
       </c>
       <c r="P26" t="n">
         <v>4400</v>
@@ -3012,10 +3012,10 @@
         <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>6300.2067296512</v>
+        <v>6272.8541860465</v>
       </c>
       <c r="O64" t="n">
-        <v>258308.4759156992</v>
+        <v>257187.0216279065</v>
       </c>
       <c r="P64" t="n">
         <v>7900</v>
@@ -4269,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="N95" t="n">
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="O95" t="n">
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="P95" t="n">
         <v>4800</v>
@@ -8276,10 +8276,10 @@
         <v>186</v>
       </c>
       <c r="N187" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O187" t="n">
-        <v>720252.1666781412</v>
+        <v>719014.62</v>
       </c>
       <c r="P187" t="n">
         <v>5500</v>
@@ -8499,10 +8499,10 @@
         <v>36</v>
       </c>
       <c r="N192" t="n">
-        <v>2589.9594489247</v>
+        <v>2572.67</v>
       </c>
       <c r="O192" t="n">
-        <v>93238.5401612892</v>
+        <v>92616.12</v>
       </c>
       <c r="P192" t="n">
         <v>4700</v>
@@ -8683,10 +8683,10 @@
         <v>23</v>
       </c>
       <c r="N196" t="n">
-        <v>2597.4440764331</v>
+        <v>2570.16</v>
       </c>
       <c r="O196" t="n">
-        <v>59741.2137579613</v>
+        <v>59113.67999999999</v>
       </c>
       <c r="P196" t="n">
         <v>4700</v>
@@ -8763,10 +8763,10 @@
         <v>70</v>
       </c>
       <c r="N198" t="n">
-        <v>3126.0967950311</v>
+        <v>3114.49</v>
       </c>
       <c r="O198" t="n">
-        <v>218826.775652177</v>
+        <v>218014.3</v>
       </c>
       <c r="P198" t="n">
         <v>5500</v>
@@ -8919,10 +8919,10 @@
         <v>41</v>
       </c>
       <c r="N202" t="n">
-        <v>4411.4198473282</v>
+        <v>4378</v>
       </c>
       <c r="O202" t="n">
-        <v>180868.2137404562</v>
+        <v>179498</v>
       </c>
       <c r="P202" t="n">
         <v>3900</v>
@@ -9239,10 +9239,10 @@
         <v>29</v>
       </c>
       <c r="N209" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="O209" t="n">
-        <v>75333.33265415661</v>
+        <v>74336.86</v>
       </c>
       <c r="P209" t="n">
         <v>4700</v>
@@ -9891,10 +9891,10 @@
         <v>216</v>
       </c>
       <c r="N224" t="n">
-        <v>2837.5718128026</v>
+        <v>2833</v>
       </c>
       <c r="O224" t="n">
-        <v>612915.5115653616</v>
+        <v>611928</v>
       </c>
       <c r="P224" t="n">
         <v>3500</v>
@@ -10183,10 +10183,10 @@
         <v>155</v>
       </c>
       <c r="N231" t="n">
-        <v>3489.6196317829</v>
+        <v>3456.13</v>
       </c>
       <c r="O231" t="n">
-        <v>540891.0429263494</v>
+        <v>535700.15</v>
       </c>
       <c r="P231" t="n">
         <v>5700</v>
@@ -12285,10 +12285,10 @@
         <v>266</v>
       </c>
       <c r="N280" t="n">
-        <v>2588.3559055118</v>
+        <v>2582.2560787402</v>
       </c>
       <c r="O280" t="n">
-        <v>688502.6708661388</v>
+        <v>686880.1169448931</v>
       </c>
       <c r="P280" t="n">
         <v>4500</v>
@@ -12587,10 +12587,10 @@
         <v>26</v>
       </c>
       <c r="N287" t="n">
-        <v>6816.3581538462</v>
+        <v>6713.08</v>
       </c>
       <c r="O287" t="n">
-        <v>177225.3120000012</v>
+        <v>174540.08</v>
       </c>
       <c r="P287" t="n">
         <v>9900</v>
@@ -13311,10 +13311,10 @@
         <v>163</v>
       </c>
       <c r="N303" t="n">
-        <v>7538.62740638</v>
+        <v>7507.39</v>
       </c>
       <c r="O303" t="n">
-        <v>1228796.26723994</v>
+        <v>1223704.57</v>
       </c>
       <c r="P303" t="n">
         <v>13500</v>
@@ -13360,10 +13360,10 @@
         <v>102</v>
       </c>
       <c r="N304" t="n">
-        <v>8907.908396946599</v>
+        <v>8796</v>
       </c>
       <c r="O304" t="n">
-        <v>908606.6564885532</v>
+        <v>897192</v>
       </c>
       <c r="P304" t="n">
         <v>14900</v>
@@ -13542,10 +13542,10 @@
         <v>302</v>
       </c>
       <c r="N308" t="n">
-        <v>3801.7317574476</v>
+        <v>3795.7100070509</v>
       </c>
       <c r="O308" t="n">
-        <v>1148122.990749175</v>
+        <v>1146304.422129372</v>
       </c>
       <c r="P308" t="n">
         <v>6200</v>
@@ -13588,10 +13588,10 @@
         <v>267</v>
       </c>
       <c r="N309" t="n">
-        <v>3695.2967632027</v>
+        <v>3684</v>
       </c>
       <c r="O309" t="n">
-        <v>986644.2357751209</v>
+        <v>983628</v>
       </c>
       <c r="P309" t="n">
         <v>6200</v>
@@ -13903,10 +13903,10 @@
         <v>1001</v>
       </c>
       <c r="N316" t="n">
-        <v>1213.150338295</v>
+        <v>1203.38</v>
       </c>
       <c r="O316" t="n">
-        <v>1214363.488633295</v>
+        <v>1204583.38</v>
       </c>
       <c r="P316" t="n">
         <v>1900</v>
@@ -14128,10 +14128,10 @@
         <v>1580</v>
       </c>
       <c r="N321" t="n">
-        <v>2286.8353823774</v>
+        <v>2267.048162926</v>
       </c>
       <c r="O321" t="n">
-        <v>3613199.904156292</v>
+        <v>3581936.09742308</v>
       </c>
       <c r="P321" t="n">
         <v>3900</v>
@@ -14394,10 +14394,10 @@
         <v>45</v>
       </c>
       <c r="N327" t="n">
-        <v>8687.96003996</v>
+        <v>8662</v>
       </c>
       <c r="O327" t="n">
-        <v>390958.2017982</v>
+        <v>389790</v>
       </c>
       <c r="P327" t="n">
         <v>14200</v>
@@ -14955,10 +14955,10 @@
         <v>35</v>
       </c>
       <c r="N340" t="n">
-        <v>8209.849315068501</v>
+        <v>8154</v>
       </c>
       <c r="O340" t="n">
-        <v>287344.7260273976</v>
+        <v>285390</v>
       </c>
       <c r="P340" t="n">
         <v>13500</v>
@@ -14999,10 +14999,10 @@
         <v>1646</v>
       </c>
       <c r="N341" t="n">
-        <v>616.28176305926</v>
+        <v>616.01871898278</v>
       </c>
       <c r="O341" t="n">
-        <v>1014399.781995542</v>
+        <v>1013966.811445656</v>
       </c>
       <c r="P341" t="n">
         <v>800</v>
@@ -15661,10 +15661,10 @@
         <v>68</v>
       </c>
       <c r="N356" t="n">
-        <v>6493.1840890688</v>
+        <v>6441.03</v>
       </c>
       <c r="O356" t="n">
-        <v>441536.5180566784</v>
+        <v>437990.04</v>
       </c>
       <c r="P356" t="n">
         <v>10500</v>
@@ -15835,10 +15835,10 @@
         <v>123</v>
       </c>
       <c r="N360" t="n">
-        <v>3660.708</v>
+        <v>3655.96</v>
       </c>
       <c r="O360" t="n">
-        <v>450267.084</v>
+        <v>449683.08</v>
       </c>
       <c r="P360" t="n">
         <v>5500</v>
@@ -16496,10 +16496,10 @@
         <v>332</v>
       </c>
       <c r="N375" t="n">
-        <v>1535.9702761427</v>
+        <v>1532.6290291403</v>
       </c>
       <c r="O375" t="n">
-        <v>509942.1316793764</v>
+        <v>508832.8376745796</v>
       </c>
       <c r="P375" t="n">
         <v>1200</v>
@@ -16798,10 +16798,10 @@
         <v>91</v>
       </c>
       <c r="N382" t="n">
-        <v>1466.9464364982</v>
+        <v>1461.54</v>
       </c>
       <c r="O382" t="n">
-        <v>133492.1257213362</v>
+        <v>133000.14</v>
       </c>
       <c r="P382" t="n">
         <v>1900</v>
@@ -17020,10 +17020,10 @@
         <v>107</v>
       </c>
       <c r="N387" t="n">
-        <v>2216.939334638</v>
+        <v>2204</v>
       </c>
       <c r="O387" t="n">
-        <v>237212.508806266</v>
+        <v>235828</v>
       </c>
       <c r="P387" t="n">
         <v>1500</v>
@@ -17512,10 +17512,10 @@
         <v>36</v>
       </c>
       <c r="N398" t="n">
-        <v>9795.0468</v>
+        <v>9678.9</v>
       </c>
       <c r="O398" t="n">
-        <v>352621.6848</v>
+        <v>348440.4</v>
       </c>
       <c r="P398" t="n">
         <v>15500</v>
@@ -18869,10 +18869,10 @@
         <v>43</v>
       </c>
       <c r="N429" t="n">
-        <v>1303.6380504587</v>
+        <v>1301.3994036697</v>
       </c>
       <c r="O429" t="n">
-        <v>56056.4361697241</v>
+        <v>55960.1743577971</v>
       </c>
       <c r="P429" t="n">
         <v>2000</v>
@@ -19233,10 +19233,10 @@
         <v>330</v>
       </c>
       <c r="N437" t="n">
-        <v>5081.9760320544</v>
+        <v>5067.21</v>
       </c>
       <c r="O437" t="n">
-        <v>1677052.090577952</v>
+        <v>1672179.3</v>
       </c>
       <c r="P437" t="n">
         <v>4200</v>
@@ -19277,10 +19277,10 @@
         <v>23</v>
       </c>
       <c r="N438" t="n">
-        <v>2678.0253782895</v>
+        <v>2651.8557072368</v>
       </c>
       <c r="O438" t="n">
-        <v>61594.58370065851</v>
+        <v>60992.68126644639</v>
       </c>
       <c r="P438" t="n">
         <v>3800</v>
@@ -19323,10 +19323,10 @@
         <v>66</v>
       </c>
       <c r="N439" t="n">
-        <v>2030.7740585774</v>
+        <v>1965</v>
       </c>
       <c r="O439" t="n">
-        <v>134031.0878661084</v>
+        <v>129690</v>
       </c>
       <c r="P439" t="n">
         <v>3700</v>
@@ -19456,10 +19456,10 @@
         <v>121</v>
       </c>
       <c r="N442" t="n">
-        <v>3319.8424657534</v>
+        <v>3253</v>
       </c>
       <c r="O442" t="n">
-        <v>401700.9383561614</v>
+        <v>393613</v>
       </c>
       <c r="P442" t="n">
         <v>3900</v>
@@ -19717,10 +19717,10 @@
         <v>158</v>
       </c>
       <c r="N448" t="n">
-        <v>210.96774011299</v>
+        <v>204.05079096045</v>
       </c>
       <c r="O448" t="n">
-        <v>33332.90293785242</v>
+        <v>32240.0249717511</v>
       </c>
       <c r="P448" t="n">
         <v>500</v>
@@ -20110,10 +20110,10 @@
         <v>288</v>
       </c>
       <c r="N457" t="n">
-        <v>948.69545706371</v>
+        <v>933.18537396122</v>
       </c>
       <c r="O457" t="n">
-        <v>273224.2916343485</v>
+        <v>268757.3877008313</v>
       </c>
       <c r="P457" t="n">
         <v>1200</v>
@@ -21252,10 +21252,10 @@
         <v>60</v>
       </c>
       <c r="N484" t="n">
-        <v>2696.7673085339</v>
+        <v>2661.82</v>
       </c>
       <c r="O484" t="n">
-        <v>161806.038512034</v>
+        <v>159709.2</v>
       </c>
       <c r="P484" t="n">
         <v>3200</v>
@@ -21334,10 +21334,10 @@
         <v>150</v>
       </c>
       <c r="N486" t="n">
-        <v>4550.9158878505</v>
+        <v>4488</v>
       </c>
       <c r="O486" t="n">
-        <v>682637.3831775751</v>
+        <v>673200</v>
       </c>
       <c r="P486" t="n">
         <v>6200</v>
@@ -21375,10 +21375,10 @@
         <v>98</v>
       </c>
       <c r="N487" t="n">
-        <v>2621.3808139535</v>
+        <v>2610</v>
       </c>
       <c r="O487" t="n">
-        <v>256895.319767443</v>
+        <v>255780</v>
       </c>
       <c r="P487" t="n">
         <v>3200</v>
@@ -21539,10 +21539,10 @@
         <v>161</v>
       </c>
       <c r="N491" t="n">
-        <v>1979.2819843342</v>
+        <v>1969</v>
       </c>
       <c r="O491" t="n">
-        <v>318664.3994778062</v>
+        <v>317009</v>
       </c>
       <c r="P491" t="n">
         <v>1500</v>
@@ -21580,10 +21580,10 @@
         <v>17</v>
       </c>
       <c r="N492" t="n">
-        <v>2040.34375</v>
+        <v>1958.73</v>
       </c>
       <c r="O492" t="n">
-        <v>34685.84375</v>
+        <v>33298.41</v>
       </c>
       <c r="P492" t="n">
         <v>3400</v>
@@ -21621,10 +21621,10 @@
         <v>164</v>
       </c>
       <c r="N493" t="n">
-        <v>8818.9498942682</v>
+        <v>8794.48</v>
       </c>
       <c r="O493" t="n">
-        <v>1446307.782659985</v>
+        <v>1442294.72</v>
       </c>
       <c r="P493" t="n">
         <v>14500</v>
@@ -21872,10 +21872,10 @@
         <v>22</v>
       </c>
       <c r="N499" t="n">
-        <v>15626.086956522</v>
+        <v>14975</v>
       </c>
       <c r="O499" t="n">
-        <v>343773.913043484</v>
+        <v>329450</v>
       </c>
       <c r="P499" t="n">
         <v>19900</v>
@@ -21954,10 +21954,10 @@
         <v>238</v>
       </c>
       <c r="N501" t="n">
-        <v>2558.6841592313</v>
+        <v>2517.22</v>
       </c>
       <c r="O501" t="n">
-        <v>608966.8298970493</v>
+        <v>599098.36</v>
       </c>
       <c r="P501" t="n">
         <v>4200</v>
@@ -22077,10 +22077,10 @@
         <v>480</v>
       </c>
       <c r="N504" t="n">
-        <v>2035.7801454898</v>
+        <v>2029.8736372454</v>
       </c>
       <c r="O504" t="n">
-        <v>977174.469835104</v>
+        <v>974339.345877792</v>
       </c>
       <c r="P504" t="n">
         <v>3600</v>
@@ -22323,10 +22323,10 @@
         <v>64</v>
       </c>
       <c r="N510" t="n">
-        <v>22561.918644068</v>
+        <v>22485.695932203</v>
       </c>
       <c r="O510" t="n">
-        <v>1443962.793220352</v>
+        <v>1439084.539660992</v>
       </c>
       <c r="P510" t="n">
         <v>36500</v>
@@ -22528,10 +22528,10 @@
         <v>127</v>
       </c>
       <c r="N515" t="n">
-        <v>7136.7702060222</v>
+        <v>7103</v>
       </c>
       <c r="O515" t="n">
-        <v>906369.8161648194</v>
+        <v>902081</v>
       </c>
       <c r="P515" t="n">
         <v>10700</v>
@@ -23161,10 +23161,10 @@
         <v>5</v>
       </c>
       <c r="N530" t="n">
-        <v>15639.519117647</v>
+        <v>14371.45</v>
       </c>
       <c r="O530" t="n">
-        <v>78197.595588235</v>
+        <v>71857.25</v>
       </c>
       <c r="P530" t="n">
         <v>23300</v>
@@ -24498,10 +24498,10 @@
         <v>55</v>
       </c>
       <c r="N561" t="n">
-        <v>11652.839895288</v>
+        <v>11562.038534031</v>
       </c>
       <c r="O561" t="n">
-        <v>640906.19424084</v>
+        <v>635912.119371705</v>
       </c>
       <c r="P561" t="n">
         <v>18500</v>
@@ -24590,10 +24590,10 @@
         <v>66</v>
       </c>
       <c r="N563" t="n">
-        <v>12155.852217573</v>
+        <v>12005.159832636</v>
       </c>
       <c r="O563" t="n">
-        <v>802286.2463598179</v>
+        <v>792340.548953976</v>
       </c>
       <c r="P563" t="n">
         <v>19500</v>
@@ -25660,10 +25660,10 @@
         <v>31</v>
       </c>
       <c r="N588" t="n">
-        <v>22817.681329923</v>
+        <v>22730.48</v>
       </c>
       <c r="O588" t="n">
-        <v>707348.1212276131</v>
+        <v>704644.88</v>
       </c>
       <c r="P588" t="n">
         <v>36900</v>
@@ -27602,10 +27602,10 @@
         <v>28</v>
       </c>
       <c r="N633" t="n">
-        <v>3779.7578947368</v>
+        <v>3590.77</v>
       </c>
       <c r="O633" t="n">
-        <v>105833.2210526304</v>
+        <v>100541.56</v>
       </c>
       <c r="P633" t="n">
         <v>3900</v>
@@ -28093,10 +28093,10 @@
         <v>25</v>
       </c>
       <c r="N644" t="n">
-        <v>4265.5329508197</v>
+        <v>4163.1601639344</v>
       </c>
       <c r="O644" t="n">
-        <v>106638.3237704925</v>
+        <v>104079.00409836</v>
       </c>
       <c r="P644" t="n">
         <v>6700</v>
@@ -28415,10 +28415,10 @@
         <v>82</v>
       </c>
       <c r="N651" t="n">
-        <v>5220.5451448041</v>
+        <v>5194</v>
       </c>
       <c r="O651" t="n">
-        <v>428084.7018739362</v>
+        <v>425908</v>
       </c>
       <c r="P651" t="n">
         <v>9000</v>
@@ -30034,10 +30034,10 @@
         <v>61</v>
       </c>
       <c r="N686" t="n">
-        <v>11682.094594595</v>
+        <v>11450</v>
       </c>
       <c r="O686" t="n">
-        <v>712607.7702702951</v>
+        <v>698450</v>
       </c>
       <c r="P686" t="n">
         <v>18300</v>
@@ -30126,10 +30126,10 @@
         <v>126</v>
       </c>
       <c r="N688" t="n">
-        <v>6365.625</v>
+        <v>6300</v>
       </c>
       <c r="O688" t="n">
-        <v>802068.75</v>
+        <v>793800</v>
       </c>
       <c r="P688" t="n">
         <v>10200</v>
@@ -30310,10 +30310,10 @@
         <v>56</v>
       </c>
       <c r="N692" t="n">
-        <v>7371.3029315961</v>
+        <v>7230</v>
       </c>
       <c r="O692" t="n">
-        <v>412792.9641693816</v>
+        <v>404880</v>
       </c>
       <c r="P692" t="n">
         <v>11600</v>
@@ -30356,10 +30356,10 @@
         <v>68</v>
       </c>
       <c r="N693" t="n">
-        <v>5291.8727915194</v>
+        <v>5200</v>
       </c>
       <c r="O693" t="n">
-        <v>359847.3498233192</v>
+        <v>353600</v>
       </c>
       <c r="P693" t="n">
         <v>8500</v>
@@ -30402,10 +30402,10 @@
         <v>57</v>
       </c>
       <c r="N694" t="n">
-        <v>1420.3389830508</v>
+        <v>1400</v>
       </c>
       <c r="O694" t="n">
-        <v>80959.3220338956</v>
+        <v>79800</v>
       </c>
       <c r="P694" t="n">
         <v>2300</v>
@@ -30448,10 +30448,10 @@
         <v>77</v>
       </c>
       <c r="N695" t="n">
-        <v>6085.1063829787</v>
+        <v>6000</v>
       </c>
       <c r="O695" t="n">
-        <v>468553.1914893599</v>
+        <v>462000</v>
       </c>
       <c r="P695" t="n">
         <v>10000</v>
@@ -30494,10 +30494,10 @@
         <v>140</v>
       </c>
       <c r="N696" t="n">
-        <v>1243.273381295</v>
+        <v>1230</v>
       </c>
       <c r="O696" t="n">
-        <v>174058.2733813</v>
+        <v>172200</v>
       </c>
       <c r="P696" t="n">
         <v>2000</v>
@@ -30632,10 +30632,10 @@
         <v>17</v>
       </c>
       <c r="N699" t="n">
-        <v>1441.9626168224</v>
+        <v>1390</v>
       </c>
       <c r="O699" t="n">
-        <v>24513.3644859808</v>
+        <v>23630</v>
       </c>
       <c r="P699" t="n">
         <v>2300</v>
@@ -30678,10 +30678,10 @@
         <v>37</v>
       </c>
       <c r="N700" t="n">
-        <v>1944.3046357616</v>
+        <v>1870</v>
       </c>
       <c r="O700" t="n">
-        <v>71939.2715231792</v>
+        <v>69190</v>
       </c>
       <c r="P700" t="n">
         <v>3000</v>
@@ -30724,10 +30724,10 @@
         <v>65</v>
       </c>
       <c r="N701" t="n">
-        <v>2110.9815037594</v>
+        <v>2019.86</v>
       </c>
       <c r="O701" t="n">
-        <v>137213.797744361</v>
+        <v>131290.9</v>
       </c>
       <c r="P701" t="n">
         <v>3300</v>
@@ -30770,10 +30770,10 @@
         <v>125</v>
       </c>
       <c r="N702" t="n">
-        <v>539.28902627512</v>
+        <v>520</v>
       </c>
       <c r="O702" t="n">
-        <v>67411.12828439</v>
+        <v>65000</v>
       </c>
       <c r="P702" t="n">
         <v>850</v>
@@ -30816,10 +30816,10 @@
         <v>93</v>
       </c>
       <c r="N703" t="n">
-        <v>2318.1974248927</v>
+        <v>2260</v>
       </c>
       <c r="O703" t="n">
-        <v>215592.3605150211</v>
+        <v>210180</v>
       </c>
       <c r="P703" t="n">
         <v>3800</v>
@@ -30908,10 +30908,10 @@
         <v>32</v>
       </c>
       <c r="N705" t="n">
-        <v>1872.4705882353</v>
+        <v>1840</v>
       </c>
       <c r="O705" t="n">
-        <v>59919.0588235296</v>
+        <v>58880</v>
       </c>
       <c r="P705" t="n">
         <v>3000</v>
@@ -31000,10 +31000,10 @@
         <v>76</v>
       </c>
       <c r="N707" t="n">
-        <v>2878.4650112867</v>
+        <v>2840</v>
       </c>
       <c r="O707" t="n">
-        <v>218763.3408577892</v>
+        <v>215840</v>
       </c>
       <c r="P707" t="n">
         <v>4600</v>
@@ -31371,10 +31371,10 @@
         <v>108</v>
       </c>
       <c r="N715" t="n">
-        <v>13863.987068966</v>
+        <v>13687</v>
       </c>
       <c r="O715" t="n">
-        <v>1497310.603448328</v>
+        <v>1478196</v>
       </c>
       <c r="P715" t="n">
         <v>21900</v>
@@ -32107,10 +32107,10 @@
         <v>6</v>
       </c>
       <c r="N731" t="n">
-        <v>6112.6956521739</v>
+        <v>5858</v>
       </c>
       <c r="O731" t="n">
-        <v>36676.1739130434</v>
+        <v>35148</v>
       </c>
       <c r="P731" t="n">
         <v>9500</v>
@@ -32933,10 +32933,10 @@
         <v>76</v>
       </c>
       <c r="N749" t="n">
-        <v>9045.4669811321</v>
+        <v>9003</v>
       </c>
       <c r="O749" t="n">
-        <v>687455.4905660396</v>
+        <v>684228</v>
       </c>
       <c r="P749" t="n">
         <v>14900</v>
@@ -33848,10 +33848,10 @@
         <v>68</v>
       </c>
       <c r="N769" t="n">
-        <v>4223.6597938144</v>
+        <v>4202</v>
       </c>
       <c r="O769" t="n">
-        <v>287208.8659793792</v>
+        <v>285736</v>
       </c>
       <c r="P769" t="n">
         <v>7900</v>
@@ -34078,10 +34078,10 @@
         <v>83</v>
       </c>
       <c r="N774" t="n">
-        <v>10095.669565217</v>
+        <v>9839</v>
       </c>
       <c r="O774" t="n">
-        <v>837940.573913011</v>
+        <v>816637</v>
       </c>
       <c r="P774" t="n">
         <v>16900</v>
@@ -37162,10 +37162,10 @@
         <v>195</v>
       </c>
       <c r="N841" t="n">
-        <v>1946.0906677937</v>
+        <v>1907.3944716822</v>
       </c>
       <c r="O841" t="n">
-        <v>379487.6802197715</v>
+        <v>371941.921978029</v>
       </c>
       <c r="P841" t="n">
         <v>2500</v>
@@ -37208,10 +37208,10 @@
         <v>189</v>
       </c>
       <c r="N842" t="n">
-        <v>1796.7129837251</v>
+        <v>1771.091283906</v>
       </c>
       <c r="O842" t="n">
-        <v>339578.7539240439</v>
+        <v>334736.252658234</v>
       </c>
       <c r="P842" t="n">
         <v>2500</v>
@@ -37254,10 +37254,10 @@
         <v>423</v>
       </c>
       <c r="N843" t="n">
-        <v>2095.5452849741</v>
+        <v>2079.3842227979</v>
       </c>
       <c r="O843" t="n">
-        <v>886415.6555440443</v>
+        <v>879579.5262435116</v>
       </c>
       <c r="P843" t="n">
         <v>2900</v>
@@ -37300,10 +37300,10 @@
         <v>448</v>
       </c>
       <c r="N844" t="n">
-        <v>1828.4692441176</v>
+        <v>1803.0149852941</v>
       </c>
       <c r="O844" t="n">
-        <v>819154.2213646849</v>
+        <v>807750.7134117568</v>
       </c>
       <c r="P844" t="n">
         <v>2500</v>
@@ -37392,10 +37392,10 @@
         <v>447</v>
       </c>
       <c r="N846" t="n">
-        <v>2137.4820360902</v>
+        <v>2122.1641172932</v>
       </c>
       <c r="O846" t="n">
-        <v>955454.4701323194</v>
+        <v>948607.3604300604</v>
       </c>
       <c r="P846" t="n">
         <v>2900</v>
@@ -37530,10 +37530,10 @@
         <v>262</v>
       </c>
       <c r="N849" t="n">
-        <v>3276.0008772707</v>
+        <v>3224.5679308817</v>
       </c>
       <c r="O849" t="n">
-        <v>858312.2298449235</v>
+        <v>844836.7978910053</v>
       </c>
       <c r="P849" t="n">
         <v>4500</v>
@@ -37991,10 +37991,10 @@
         <v>6</v>
       </c>
       <c r="N859" t="n">
-        <v>5414.576625</v>
+        <v>5347.73</v>
       </c>
       <c r="O859" t="n">
-        <v>32487.45975</v>
+        <v>32086.38</v>
       </c>
       <c r="P859" t="n">
         <v>9500</v>
@@ -38313,10 +38313,10 @@
         <v>55</v>
       </c>
       <c r="N866" t="n">
-        <v>3051.52</v>
+        <v>2980</v>
       </c>
       <c r="O866" t="n">
-        <v>167833.6</v>
+        <v>163900</v>
       </c>
       <c r="P866" t="n">
         <v>4800</v>
@@ -39378,10 +39378,10 @@
         <v>40</v>
       </c>
       <c r="N889" t="n">
-        <v>2769.7168108108</v>
+        <v>2682.71</v>
       </c>
       <c r="O889" t="n">
-        <v>110788.672432432</v>
+        <v>107308.4</v>
       </c>
       <c r="P889" t="n">
         <v>10900</v>
@@ -39784,10 +39784,10 @@
         <v>3763</v>
       </c>
       <c r="N898" t="n">
-        <v>577.72789151821</v>
+        <v>574.67194894975</v>
       </c>
       <c r="O898" t="n">
-        <v>2173990.055783024</v>
+        <v>2162490.543897909</v>
       </c>
       <c r="P898" t="n">
         <v>800</v>
@@ -40105,10 +40105,10 @@
         <v>28</v>
       </c>
       <c r="N905" t="n">
-        <v>2483.1635416667</v>
+        <v>2270.3210416667</v>
       </c>
       <c r="O905" t="n">
-        <v>69528.57916666759</v>
+        <v>63568.9891666676</v>
       </c>
       <c r="P905" t="n">
         <v>3900</v>
@@ -40554,10 +40554,10 @@
         <v>24</v>
       </c>
       <c r="N915" t="n">
-        <v>2733.0090825688</v>
+        <v>2590.4171559633</v>
       </c>
       <c r="O915" t="n">
-        <v>65592.21798165119</v>
+        <v>62170.0117431192</v>
       </c>
       <c r="P915" t="n">
         <v>2800</v>
@@ -40644,10 +40644,10 @@
         <v>100</v>
       </c>
       <c r="N917" t="n">
-        <v>1815.5064655172</v>
+        <v>1684.79</v>
       </c>
       <c r="O917" t="n">
-        <v>181550.64655172</v>
+        <v>168479</v>
       </c>
       <c r="P917" t="n">
         <v>2900</v>
@@ -40688,10 +40688,10 @@
         <v>60</v>
       </c>
       <c r="N918" t="n">
-        <v>6349.5722627737</v>
+        <v>6213.51</v>
       </c>
       <c r="O918" t="n">
-        <v>380974.335766422</v>
+        <v>372810.6</v>
       </c>
       <c r="P918" t="n">
         <v>10300</v>
@@ -41798,10 +41798,10 @@
         <v>516</v>
       </c>
       <c r="N943" t="n">
-        <v>2047.4600343643</v>
+        <v>2030.02</v>
       </c>
       <c r="O943" t="n">
-        <v>1056489.377731979</v>
+        <v>1047490.32</v>
       </c>
       <c r="P943" t="n">
         <v>3600</v>
@@ -41886,10 +41886,10 @@
         <v>1829</v>
       </c>
       <c r="N945" t="n">
-        <v>704.1779547101401</v>
+        <v>703.79545471015</v>
       </c>
       <c r="O945" t="n">
-        <v>1287941.479164846</v>
+        <v>1287241.886664864</v>
       </c>
       <c r="P945" t="n">
         <v>900</v>
@@ -41930,10 +41930,10 @@
         <v>76</v>
       </c>
       <c r="N946" t="n">
-        <v>6556.6768421053</v>
+        <v>6076.92</v>
       </c>
       <c r="O946" t="n">
-        <v>498307.4400000028</v>
+        <v>461845.92</v>
       </c>
       <c r="P946" t="n">
         <v>7900</v>
@@ -41979,10 +41979,10 @@
         <v>39</v>
       </c>
       <c r="N947" t="n">
-        <v>3216.9665454545</v>
+        <v>3182.2510909091</v>
       </c>
       <c r="O947" t="n">
-        <v>125461.6952727255</v>
+        <v>124107.7925454549</v>
       </c>
       <c r="P947" t="n">
         <v>6900</v>
@@ -42293,10 +42293,10 @@
         <v>172</v>
       </c>
       <c r="N954" t="n">
-        <v>3442.356096181</v>
+        <v>3384.9037623762</v>
       </c>
       <c r="O954" t="n">
-        <v>592085.248543132</v>
+        <v>582203.4471287064</v>
       </c>
       <c r="P954" t="n">
         <v>4500</v>
@@ -42727,10 +42727,10 @@
         <v>23</v>
       </c>
       <c r="N964" t="n">
-        <v>3674.9932848233</v>
+        <v>3629.7161122661</v>
       </c>
       <c r="O964" t="n">
-        <v>84524.8455509359</v>
+        <v>83483.4705821203</v>
       </c>
       <c r="P964" t="n">
         <v>4900</v>
@@ -44261,10 +44261,10 @@
         <v>39</v>
       </c>
       <c r="N997" t="n">
-        <v>2602.7576774194</v>
+        <v>2505.760516129</v>
       </c>
       <c r="O997" t="n">
-        <v>101507.5494193566</v>
+        <v>97724.66012903099</v>
       </c>
       <c r="P997" t="n">
         <v>3000</v>
@@ -44589,10 +44589,10 @@
         <v>113</v>
       </c>
       <c r="N1004" t="n">
-        <v>1900.0042477876</v>
+        <v>1759.84</v>
       </c>
       <c r="O1004" t="n">
-        <v>214700.4799999988</v>
+        <v>198861.92</v>
       </c>
       <c r="P1004" t="n">
         <v>3300</v>
@@ -45197,10 +45197,10 @@
         <v>5</v>
       </c>
       <c r="N1017" t="n">
-        <v>713.93197013211</v>
+        <v>711.48</v>
       </c>
       <c r="O1017" t="n">
-        <v>3569.65985066055</v>
+        <v>3557.4</v>
       </c>
       <c r="P1017" t="n">
         <v>2500</v>
@@ -46091,10 +46091,10 @@
         <v>18</v>
       </c>
       <c r="N1036" t="n">
-        <v>2251.9952</v>
+        <v>2010.71</v>
       </c>
       <c r="O1036" t="n">
-        <v>40535.9136</v>
+        <v>36192.78</v>
       </c>
       <c r="P1036" t="n">
         <v>7200</v>
@@ -46369,10 +46369,10 @@
         <v>15</v>
       </c>
       <c r="N1042" t="n">
-        <v>2851.4129341317</v>
+        <v>2752.52</v>
       </c>
       <c r="O1042" t="n">
-        <v>42771.19401197549</v>
+        <v>41287.8</v>
       </c>
       <c r="P1042" t="n">
         <v>4500</v>
@@ -46624,10 +46624,10 @@
         <v>385</v>
       </c>
       <c r="N1048" t="n">
-        <v>714.37850499616</v>
+        <v>704.8968946963899</v>
       </c>
       <c r="O1048" t="n">
-        <v>275035.7244235216</v>
+        <v>271385.3044581101</v>
       </c>
       <c r="P1048" t="n">
         <v>900</v>
@@ -47177,10 +47177,10 @@
         <v>41</v>
       </c>
       <c r="N1061" t="n">
-        <v>827.85503734979</v>
+        <v>824.64111075024</v>
       </c>
       <c r="O1061" t="n">
-        <v>33942.05653134139</v>
+        <v>33810.28554075984</v>
       </c>
       <c r="P1061" t="n">
         <v>1000</v>
@@ -47432,10 +47432,10 @@
         <v>46</v>
       </c>
       <c r="N1067" t="n">
-        <v>2496.9418200728</v>
+        <v>2489.1752678107</v>
       </c>
       <c r="O1067" t="n">
-        <v>114859.3237233488</v>
+        <v>114502.0623192922</v>
       </c>
       <c r="P1067" t="n">
         <v>3000</v>
@@ -47517,10 +47517,10 @@
         <v>38</v>
       </c>
       <c r="N1069" t="n">
-        <v>2967.9876840215</v>
+        <v>2952.0877378815</v>
       </c>
       <c r="O1069" t="n">
-        <v>112783.531992817</v>
+        <v>112179.334039497</v>
       </c>
       <c r="P1069" t="n">
         <v>3800</v>
@@ -47561,10 +47561,10 @@
         <v>78</v>
       </c>
       <c r="N1070" t="n">
-        <v>3178.8430970149</v>
+        <v>3167.0258208955</v>
       </c>
       <c r="O1070" t="n">
-        <v>247949.7615671622</v>
+        <v>247028.014029849</v>
       </c>
       <c r="P1070" t="n">
         <v>4000</v>
@@ -47822,10 +47822,10 @@
         <v>1</v>
       </c>
       <c r="N1076" t="n">
-        <v>2998.8631649832</v>
+        <v>2988.7998653199</v>
       </c>
       <c r="O1076" t="n">
-        <v>2998.8631649832</v>
+        <v>2988.7998653199</v>
       </c>
       <c r="P1076" t="n">
         <v>3800</v>
@@ -47995,10 +47995,10 @@
         <v>310</v>
       </c>
       <c r="N1080" t="n">
-        <v>3192.6751439214</v>
+        <v>3181.9</v>
       </c>
       <c r="O1080" t="n">
-        <v>989729.294615634</v>
+        <v>986389</v>
       </c>
       <c r="P1080" t="n">
         <v>5100</v>
@@ -48121,10 +48121,10 @@
         <v>193</v>
       </c>
       <c r="N1083" t="n">
-        <v>1803.5408695029</v>
+        <v>1794.2879773671</v>
       </c>
       <c r="O1083" t="n">
-        <v>348083.3878140597</v>
+        <v>346297.5796318503</v>
       </c>
       <c r="P1083" t="n">
         <v>1600</v>
@@ -48297,10 +48297,10 @@
         <v>92</v>
       </c>
       <c r="N1087" t="n">
-        <v>3081.4280769231</v>
+        <v>2830.2251183432</v>
       </c>
       <c r="O1087" t="n">
-        <v>283491.3830769252</v>
+        <v>260380.7108875744</v>
       </c>
       <c r="P1087" t="n">
         <v>2400</v>
@@ -48473,10 +48473,10 @@
         <v>41</v>
       </c>
       <c r="N1091" t="n">
-        <v>2540.4017582418</v>
+        <v>2523.3377514793</v>
       </c>
       <c r="O1091" t="n">
-        <v>104156.4720879138</v>
+        <v>103456.8478106513</v>
       </c>
       <c r="P1091" t="n">
         <v>2800</v>
@@ -49282,10 +49282,10 @@
         <v>289</v>
       </c>
       <c r="N1110" t="n">
-        <v>707.12182981928</v>
+        <v>705.52801204819</v>
       </c>
       <c r="O1110" t="n">
-        <v>204358.2088177719</v>
+        <v>203897.5954819269</v>
       </c>
       <c r="P1110" t="n">
         <v>1500</v>
@@ -50095,10 +50095,10 @@
         <v>29</v>
       </c>
       <c r="N1128" t="n">
-        <v>1338.6403076923</v>
+        <v>1160.1556923077</v>
       </c>
       <c r="O1128" t="n">
-        <v>38820.5689230767</v>
+        <v>33644.5150769233</v>
       </c>
       <c r="P1128" t="n">
         <v>1600</v>
@@ -51470,10 +51470,10 @@
         <v>28</v>
       </c>
       <c r="N1158" t="n">
-        <v>614.59626373626</v>
+        <v>576.58</v>
       </c>
       <c r="O1158" t="n">
-        <v>17208.69538461528</v>
+        <v>16144.24</v>
       </c>
       <c r="P1158" t="n">
         <v>5900</v>
@@ -51705,10 +51705,10 @@
         <v>116</v>
       </c>
       <c r="N1163" t="n">
-        <v>229.9076771366</v>
+        <v>227.41596785975</v>
       </c>
       <c r="O1163" t="n">
-        <v>26669.2905478456</v>
+        <v>26380.252271731</v>
       </c>
       <c r="P1163" t="n">
         <v>1200</v>
@@ -52150,10 +52150,10 @@
         <v>19</v>
       </c>
       <c r="N1173" t="n">
-        <v>2464</v>
+        <v>2200</v>
       </c>
       <c r="O1173" t="n">
-        <v>46816</v>
+        <v>41800</v>
       </c>
       <c r="P1173" t="n">
         <v>2700</v>
@@ -52196,10 +52196,10 @@
         <v>12</v>
       </c>
       <c r="N1174" t="n">
-        <v>2750</v>
+        <v>2200</v>
       </c>
       <c r="O1174" t="n">
-        <v>33000</v>
+        <v>26400</v>
       </c>
       <c r="P1174" t="n">
         <v>2700</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -691,10 +691,10 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>96741.407037037</v>
+        <v>96741.407125</v>
       </c>
       <c r="O7" t="n">
-        <v>96741.407037037</v>
+        <v>96741.407125</v>
       </c>
       <c r="P7" t="n">
         <v>188900</v>
@@ -779,22 +779,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>74676.654222222</v>
+        <v>74676.65386363601</v>
       </c>
       <c r="O9" t="n">
-        <v>522736.579555554</v>
+        <v>448059.923181816</v>
       </c>
       <c r="P9" t="n">
         <v>144900</v>
       </c>
       <c r="Q9" t="n">
-        <v>1014300</v>
+        <v>869400</v>
       </c>
     </row>
     <row r="10">
@@ -1401,10 +1401,10 @@
         <v>241</v>
       </c>
       <c r="N24" t="n">
-        <v>1811.3037996546</v>
+        <v>1811.3039621792</v>
       </c>
       <c r="O24" t="n">
-        <v>436524.2157167586</v>
+        <v>436524.2548851872</v>
       </c>
       <c r="P24" t="n">
         <v>2600</v>
@@ -1473,22 +1473,22 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N26" t="n">
-        <v>1990.0436022514</v>
+        <v>1990.0435660377</v>
       </c>
       <c r="O26" t="n">
-        <v>147263.2265666036</v>
+        <v>141293.0931886767</v>
       </c>
       <c r="P26" t="n">
         <v>4400</v>
       </c>
       <c r="Q26" t="n">
-        <v>325600</v>
+        <v>312400</v>
       </c>
     </row>
     <row r="27">
@@ -1560,10 +1560,10 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>7588.3739393939</v>
+        <v>7588.3731034483</v>
       </c>
       <c r="O28" t="n">
-        <v>7588.3739393939</v>
+        <v>7588.3731034483</v>
       </c>
       <c r="P28" t="n">
         <v>14900</v>
@@ -2109,10 +2109,10 @@
         <v>13</v>
       </c>
       <c r="N42" t="n">
-        <v>20826.676136364</v>
+        <v>20826.676585366</v>
       </c>
       <c r="O42" t="n">
-        <v>270746.789772732</v>
+        <v>270746.795609758</v>
       </c>
       <c r="P42" t="n">
         <v>39100</v>
@@ -2764,22 +2764,22 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
         <v>35831.14</v>
       </c>
       <c r="O58" t="n">
-        <v>107493.42</v>
+        <v>71662.28</v>
       </c>
       <c r="P58" t="n">
         <v>62900</v>
       </c>
       <c r="Q58" t="n">
-        <v>188700</v>
+        <v>125800</v>
       </c>
     </row>
     <row r="59">
@@ -2967,22 +2967,22 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N63" t="n">
         <v>3585</v>
       </c>
       <c r="O63" t="n">
-        <v>75285</v>
+        <v>68115</v>
       </c>
       <c r="P63" t="n">
         <v>4500</v>
       </c>
       <c r="Q63" t="n">
-        <v>94500</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="64">
@@ -3012,10 +3012,10 @@
         <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>6272.8541860465</v>
+        <v>6272.8542228739</v>
       </c>
       <c r="O64" t="n">
-        <v>257187.0216279065</v>
+        <v>257187.0231378299</v>
       </c>
       <c r="P64" t="n">
         <v>7900</v>
@@ -3123,22 +3123,22 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N67" t="n">
-        <v>3926.8371326165</v>
+        <v>3926.8371296771</v>
       </c>
       <c r="O67" t="n">
-        <v>188488.182365592</v>
+        <v>180634.5079651466</v>
       </c>
       <c r="P67" t="n">
         <v>4800</v>
       </c>
       <c r="Q67" t="n">
-        <v>230400</v>
+        <v>220800</v>
       </c>
     </row>
     <row r="68">
@@ -3335,10 +3335,10 @@
         <v>205</v>
       </c>
       <c r="N72" t="n">
-        <v>2413.0011764706</v>
+        <v>2413.0010330579</v>
       </c>
       <c r="O72" t="n">
-        <v>494665.241176473</v>
+        <v>494665.2117768695</v>
       </c>
       <c r="P72" t="n">
         <v>4700</v>
@@ -3446,22 +3446,22 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N75" t="n">
-        <v>12793.680086207</v>
+        <v>12793.68008658</v>
       </c>
       <c r="O75" t="n">
-        <v>1292161.688706907</v>
+        <v>1279368.008658</v>
       </c>
       <c r="P75" t="n">
         <v>24000</v>
       </c>
       <c r="Q75" t="n">
-        <v>2424000</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="76">
@@ -3530,10 +3530,10 @@
         <v>168</v>
       </c>
       <c r="N77" t="n">
-        <v>3716.330188383</v>
+        <v>3716.3301889764</v>
       </c>
       <c r="O77" t="n">
-        <v>624343.471648344</v>
+        <v>624343.4717480353</v>
       </c>
       <c r="P77" t="n">
         <v>9500</v>
@@ -3563,22 +3563,22 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N78" t="n">
         <v>10345.01</v>
       </c>
       <c r="O78" t="n">
-        <v>113795.11</v>
+        <v>103450.1</v>
       </c>
       <c r="P78" t="n">
         <v>17900</v>
       </c>
       <c r="Q78" t="n">
-        <v>196900</v>
+        <v>179000</v>
       </c>
     </row>
     <row r="79">
@@ -4183,22 +4183,22 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N93" t="n">
         <v>1800</v>
       </c>
       <c r="O93" t="n">
-        <v>133200</v>
+        <v>131400</v>
       </c>
       <c r="P93" t="n">
         <v>2200</v>
       </c>
       <c r="Q93" t="n">
-        <v>162800</v>
+        <v>160600</v>
       </c>
     </row>
     <row r="94">
@@ -4817,10 +4817,10 @@
         <v>14</v>
       </c>
       <c r="N107" t="n">
-        <v>30708.904814815</v>
+        <v>30708.894545455</v>
       </c>
       <c r="O107" t="n">
-        <v>429924.66740741</v>
+        <v>429924.52363637</v>
       </c>
       <c r="P107" t="n">
         <v>53500</v>
@@ -4948,10 +4948,10 @@
         <v>23</v>
       </c>
       <c r="N110" t="n">
-        <v>10994.352244898</v>
+        <v>10994.353043478</v>
       </c>
       <c r="O110" t="n">
-        <v>252870.101632654</v>
+        <v>252870.119999994</v>
       </c>
       <c r="P110" t="n">
         <v>16900</v>
@@ -4989,22 +4989,22 @@
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N111" t="n">
-        <v>18835.016818182</v>
+        <v>18835.017619048</v>
       </c>
       <c r="O111" t="n">
-        <v>376700.33636364</v>
+        <v>357865.334761912</v>
       </c>
       <c r="P111" t="n">
         <v>40500</v>
       </c>
       <c r="Q111" t="n">
-        <v>810000</v>
+        <v>769500</v>
       </c>
     </row>
     <row r="112">
@@ -5160,10 +5160,10 @@
         <v>13</v>
       </c>
       <c r="N115" t="n">
-        <v>15711.966215139</v>
+        <v>15711.9662</v>
       </c>
       <c r="O115" t="n">
-        <v>204255.560796807</v>
+        <v>204255.5606</v>
       </c>
       <c r="P115" t="n">
         <v>28500</v>
@@ -5254,10 +5254,10 @@
         <v>2</v>
       </c>
       <c r="N117" t="n">
-        <v>30238.812278481</v>
+        <v>30238.812307692</v>
       </c>
       <c r="O117" t="n">
-        <v>60477.624556962</v>
+        <v>60477.624615384</v>
       </c>
       <c r="P117" t="n">
         <v>51100</v>
@@ -5665,10 +5665,10 @@
         <v>5</v>
       </c>
       <c r="N127" t="n">
-        <v>22267.552</v>
+        <v>22267.552083333</v>
       </c>
       <c r="O127" t="n">
-        <v>111337.76</v>
+        <v>111337.760416665</v>
       </c>
       <c r="P127" t="n">
         <v>46300</v>
@@ -6089,22 +6089,22 @@
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N137" t="n">
-        <v>36306.276</v>
+        <v>36306.278421053</v>
       </c>
       <c r="O137" t="n">
-        <v>254143.932</v>
+        <v>217837.670526318</v>
       </c>
       <c r="P137" t="n">
         <v>64900</v>
       </c>
       <c r="Q137" t="n">
-        <v>454300</v>
+        <v>389400</v>
       </c>
     </row>
     <row r="138">
@@ -6142,10 +6142,10 @@
         <v>8</v>
       </c>
       <c r="N138" t="n">
-        <v>56906.800422535</v>
+        <v>56906.800571429</v>
       </c>
       <c r="O138" t="n">
-        <v>455254.40338028</v>
+        <v>455254.404571432</v>
       </c>
       <c r="P138" t="n">
         <v>95900</v>
@@ -6236,10 +6236,10 @@
         <v>8</v>
       </c>
       <c r="N140" t="n">
-        <v>77455.73771929801</v>
+        <v>77455.737927928</v>
       </c>
       <c r="O140" t="n">
-        <v>619645.901754384</v>
+        <v>619645.903423424</v>
       </c>
       <c r="P140" t="n">
         <v>122900</v>
@@ -6283,10 +6283,10 @@
         <v>2</v>
       </c>
       <c r="N141" t="n">
-        <v>141416.88447284</v>
+        <v>141416.88453074</v>
       </c>
       <c r="O141" t="n">
-        <v>282833.76894568</v>
+        <v>282833.76906148</v>
       </c>
       <c r="P141" t="n">
         <v>251900</v>
@@ -6419,10 +6419,10 @@
         <v>2</v>
       </c>
       <c r="N144" t="n">
-        <v>344599.17881356</v>
+        <v>344599.1787931</v>
       </c>
       <c r="O144" t="n">
-        <v>689198.35762712</v>
+        <v>689198.3575862</v>
       </c>
       <c r="P144" t="n">
         <v>532900</v>
@@ -7018,22 +7018,22 @@
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N158" t="n">
         <v>21018</v>
       </c>
       <c r="O158" t="n">
-        <v>147126</v>
+        <v>126108</v>
       </c>
       <c r="P158" t="n">
         <v>31900</v>
       </c>
       <c r="Q158" t="n">
-        <v>223300</v>
+        <v>191400</v>
       </c>
     </row>
     <row r="159">
@@ -7254,22 +7254,22 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N164" t="n">
-        <v>61666.873842239</v>
+        <v>61666.873852041</v>
       </c>
       <c r="O164" t="n">
-        <v>370001.243053434</v>
+        <v>308334.369260205</v>
       </c>
       <c r="P164" t="n">
         <v>98900</v>
       </c>
       <c r="Q164" t="n">
-        <v>593400</v>
+        <v>494500</v>
       </c>
     </row>
     <row r="165">
@@ -8677,22 +8677,22 @@
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M196" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N196" t="n">
         <v>2570.16</v>
       </c>
       <c r="O196" t="n">
-        <v>59113.67999999999</v>
+        <v>53973.36</v>
       </c>
       <c r="P196" t="n">
         <v>4700</v>
       </c>
       <c r="Q196" t="n">
-        <v>108100</v>
+        <v>98700</v>
       </c>
     </row>
     <row r="197">
@@ -9584,10 +9584,10 @@
         <v>2</v>
       </c>
       <c r="N217" t="n">
-        <v>732.63410958904</v>
+        <v>732.63413793103</v>
       </c>
       <c r="O217" t="n">
-        <v>1465.26821917808</v>
+        <v>1465.26827586206</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
@@ -9967,22 +9967,22 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M226" t="n">
-        <v>1552</v>
+        <v>1526</v>
       </c>
       <c r="N226" t="n">
         <v>1726.32</v>
       </c>
       <c r="O226" t="n">
-        <v>2679248.64</v>
+        <v>2634364.32</v>
       </c>
       <c r="P226" t="n">
         <v>1500</v>
       </c>
       <c r="Q226" t="n">
-        <v>2328000</v>
+        <v>2289000</v>
       </c>
     </row>
     <row r="227">
@@ -10060,10 +10060,10 @@
         <v>125</v>
       </c>
       <c r="N228" t="n">
-        <v>4937.3101595359</v>
+        <v>4937.3101601164</v>
       </c>
       <c r="O228" t="n">
-        <v>617163.7699419876</v>
+        <v>617163.77001455</v>
       </c>
       <c r="P228" t="n">
         <v>7500</v>
@@ -10269,22 +10269,22 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M233" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N233" t="n">
         <v>39171.85</v>
       </c>
       <c r="O233" t="n">
-        <v>509234.05</v>
+        <v>430890.35</v>
       </c>
       <c r="P233" t="n">
         <v>68900</v>
       </c>
       <c r="Q233" t="n">
-        <v>895700</v>
+        <v>757900</v>
       </c>
     </row>
     <row r="234">
@@ -10559,22 +10559,22 @@
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M240" t="n">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="N240" t="n">
-        <v>1098.0527732407</v>
+        <v>1098.0529624405</v>
       </c>
       <c r="O240" t="n">
-        <v>912481.8545630217</v>
+        <v>904795.641050972</v>
       </c>
       <c r="P240" t="n">
         <v>1500</v>
       </c>
       <c r="Q240" t="n">
-        <v>1246500</v>
+        <v>1236000</v>
       </c>
     </row>
     <row r="241">
@@ -10775,10 +10775,10 @@
         <v>43</v>
       </c>
       <c r="N245" t="n">
-        <v>31233.611787072</v>
+        <v>31233.611793893</v>
       </c>
       <c r="O245" t="n">
-        <v>1343045.306844096</v>
+        <v>1343045.307137399</v>
       </c>
       <c r="P245" t="n">
         <v>45500</v>
@@ -11669,22 +11669,22 @@
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M266" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N266" t="n">
         <v>17207.41</v>
       </c>
       <c r="O266" t="n">
-        <v>1152896.47</v>
+        <v>1118481.65</v>
       </c>
       <c r="P266" t="n">
         <v>20000</v>
       </c>
       <c r="Q266" t="n">
-        <v>1340000</v>
+        <v>1300000</v>
       </c>
     </row>
     <row r="267">
@@ -12279,22 +12279,22 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M280" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N280" t="n">
-        <v>2582.2560787402</v>
+        <v>2582.2560663507</v>
       </c>
       <c r="O280" t="n">
-        <v>686880.1169448931</v>
+        <v>668804.3211848313</v>
       </c>
       <c r="P280" t="n">
         <v>4500</v>
       </c>
       <c r="Q280" t="n">
-        <v>1197000</v>
+        <v>1165500</v>
       </c>
     </row>
     <row r="281">
@@ -12371,22 +12371,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M282" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N282" t="n">
         <v>5182.57</v>
       </c>
       <c r="O282" t="n">
-        <v>362779.9</v>
+        <v>352414.76</v>
       </c>
       <c r="P282" t="n">
         <v>6500</v>
       </c>
       <c r="Q282" t="n">
-        <v>455000</v>
+        <v>442000</v>
       </c>
     </row>
     <row r="283">
@@ -12806,22 +12806,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M292" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N292" t="n">
         <v>8214</v>
       </c>
       <c r="O292" t="n">
-        <v>854256</v>
+        <v>837828</v>
       </c>
       <c r="P292" t="n">
         <v>7900</v>
       </c>
       <c r="Q292" t="n">
-        <v>821600</v>
+        <v>805800</v>
       </c>
     </row>
     <row r="293">
@@ -13034,22 +13034,22 @@
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M297" t="n">
-        <v>349</v>
+        <v>309</v>
       </c>
       <c r="N297" t="n">
         <v>1337.34</v>
       </c>
       <c r="O297" t="n">
-        <v>466731.66</v>
+        <v>413238.06</v>
       </c>
       <c r="P297" t="n">
         <v>2500</v>
       </c>
       <c r="Q297" t="n">
-        <v>872500</v>
+        <v>772500</v>
       </c>
     </row>
     <row r="298">
@@ -13354,22 +13354,22 @@
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M304" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N304" t="n">
         <v>8796</v>
       </c>
       <c r="O304" t="n">
-        <v>897192</v>
+        <v>888396</v>
       </c>
       <c r="P304" t="n">
         <v>14900</v>
       </c>
       <c r="Q304" t="n">
-        <v>1519800</v>
+        <v>1504900</v>
       </c>
     </row>
     <row r="305">
@@ -13669,22 +13669,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M311" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N311" t="n">
         <v>4357.55</v>
       </c>
       <c r="O311" t="n">
-        <v>1228829.1</v>
+        <v>1220114</v>
       </c>
       <c r="P311" t="n">
         <v>7500</v>
       </c>
       <c r="Q311" t="n">
-        <v>2115000</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="312">
@@ -13808,10 +13808,10 @@
         <v>63</v>
       </c>
       <c r="N314" t="n">
-        <v>4890.930045977</v>
+        <v>4890.9300460299</v>
       </c>
       <c r="O314" t="n">
-        <v>308128.592896551</v>
+        <v>308128.5928998837</v>
       </c>
       <c r="P314" t="n">
         <v>8200</v>
@@ -13848,22 +13848,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M315" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N315" t="n">
-        <v>5484.947804878</v>
+        <v>5484.94825</v>
       </c>
       <c r="O315" t="n">
-        <v>416856.033170728</v>
+        <v>400401.22225</v>
       </c>
       <c r="P315" t="n">
         <v>8500</v>
       </c>
       <c r="Q315" t="n">
-        <v>646000</v>
+        <v>620500</v>
       </c>
     </row>
     <row r="316">
@@ -13943,22 +13943,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M317" t="n">
-        <v>710</v>
+        <v>677</v>
       </c>
       <c r="N317" t="n">
         <v>3472</v>
       </c>
       <c r="O317" t="n">
-        <v>2465120</v>
+        <v>2350544</v>
       </c>
       <c r="P317" t="n">
         <v>4800</v>
       </c>
       <c r="Q317" t="n">
-        <v>3408000</v>
+        <v>3249600</v>
       </c>
     </row>
     <row r="318">
@@ -14128,10 +14128,10 @@
         <v>1580</v>
       </c>
       <c r="N321" t="n">
-        <v>2267.048162926</v>
+        <v>2267.0481598668</v>
       </c>
       <c r="O321" t="n">
-        <v>3581936.09742308</v>
+        <v>3581936.092589544</v>
       </c>
       <c r="P321" t="n">
         <v>3900</v>
@@ -14296,22 +14296,22 @@
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M325" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N325" t="n">
         <v>5667.94</v>
       </c>
       <c r="O325" t="n">
-        <v>340076.4</v>
+        <v>328740.52</v>
       </c>
       <c r="P325" t="n">
         <v>9500</v>
       </c>
       <c r="Q325" t="n">
-        <v>570000</v>
+        <v>551000</v>
       </c>
     </row>
     <row r="326">
@@ -14388,22 +14388,22 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M327" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N327" t="n">
         <v>8662</v>
       </c>
       <c r="O327" t="n">
-        <v>389790</v>
+        <v>381128</v>
       </c>
       <c r="P327" t="n">
         <v>14200</v>
       </c>
       <c r="Q327" t="n">
-        <v>639000</v>
+        <v>624800</v>
       </c>
     </row>
     <row r="328">
@@ -14475,22 +14475,22 @@
         <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M329" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N329" t="n">
         <v>10716.34</v>
       </c>
       <c r="O329" t="n">
-        <v>310773.86</v>
+        <v>278624.84</v>
       </c>
       <c r="P329" t="n">
         <v>39000</v>
       </c>
       <c r="Q329" t="n">
-        <v>1131000</v>
+        <v>1014000</v>
       </c>
     </row>
     <row r="330">
@@ -14688,22 +14688,22 @@
         <v>0</v>
       </c>
       <c r="L334" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M334" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N334" t="n">
-        <v>3594.2542480527</v>
+        <v>3594.2542307692</v>
       </c>
       <c r="O334" t="n">
-        <v>294728.8483403214</v>
+        <v>280351.8299999976</v>
       </c>
       <c r="P334" t="n">
         <v>6500</v>
       </c>
       <c r="Q334" t="n">
-        <v>533000</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="335">
@@ -14857,22 +14857,22 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M338" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N338" t="n">
-        <v>3240.8500291545</v>
+        <v>3240.8500293255</v>
       </c>
       <c r="O338" t="n">
-        <v>813453.3573177796</v>
+        <v>803730.807272724</v>
       </c>
       <c r="P338" t="n">
         <v>5200</v>
       </c>
       <c r="Q338" t="n">
-        <v>1305200</v>
+        <v>1289600</v>
       </c>
     </row>
     <row r="339">
@@ -15034,25 +15034,25 @@
         <v>115</v>
       </c>
       <c r="K342" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M342" t="n">
-        <v>115</v>
+        <v>420</v>
       </c>
       <c r="N342" t="n">
         <v>2090.85</v>
       </c>
       <c r="O342" t="n">
-        <v>240447.75</v>
+        <v>878157</v>
       </c>
       <c r="P342" t="n">
         <v>2900</v>
       </c>
       <c r="Q342" t="n">
-        <v>333500</v>
+        <v>1218000</v>
       </c>
     </row>
     <row r="343">
@@ -15128,10 +15128,10 @@
         <v>340</v>
       </c>
       <c r="N344" t="n">
-        <v>5191.4800265604</v>
+        <v>5191.4800268456</v>
       </c>
       <c r="O344" t="n">
-        <v>1765103.209030536</v>
+        <v>1765103.209127504</v>
       </c>
       <c r="P344" t="n">
         <v>9100</v>
@@ -15259,22 +15259,22 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M347" t="n">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N347" t="n">
         <v>1381.75</v>
       </c>
       <c r="O347" t="n">
-        <v>333001.75</v>
+        <v>324711.25</v>
       </c>
       <c r="P347" t="n">
         <v>2500</v>
       </c>
       <c r="Q347" t="n">
-        <v>602500</v>
+        <v>587500</v>
       </c>
     </row>
     <row r="348">
@@ -15344,22 +15344,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M349" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N349" t="n">
         <v>15851.61</v>
       </c>
       <c r="O349" t="n">
-        <v>237774.15</v>
+        <v>221922.54</v>
       </c>
       <c r="P349" t="n">
         <v>23900</v>
       </c>
       <c r="Q349" t="n">
-        <v>358500</v>
+        <v>334600</v>
       </c>
     </row>
     <row r="350">
@@ -15434,22 +15434,22 @@
         <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M351" t="n">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N351" t="n">
         <v>1441.01</v>
       </c>
       <c r="O351" t="n">
-        <v>623957.33</v>
+        <v>621075.3099999999</v>
       </c>
       <c r="P351" t="n">
         <v>2100</v>
       </c>
       <c r="Q351" t="n">
-        <v>909300</v>
+        <v>905100</v>
       </c>
     </row>
     <row r="352">
@@ -15475,22 +15475,22 @@
         <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M352" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N352" t="n">
         <v>4193.85</v>
       </c>
       <c r="O352" t="n">
-        <v>515843.55</v>
+        <v>507455.85</v>
       </c>
       <c r="P352" t="n">
         <v>7500</v>
       </c>
       <c r="Q352" t="n">
-        <v>922500</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="353">
@@ -15530,10 +15530,10 @@
         <v>429</v>
       </c>
       <c r="N353" t="n">
-        <v>3041.6600123457</v>
+        <v>3041.6600124378</v>
       </c>
       <c r="O353" t="n">
-        <v>1304872.145296305</v>
+        <v>1304872.145335816</v>
       </c>
       <c r="P353" t="n">
         <v>5500</v>
@@ -15617,10 +15617,10 @@
         <v>115</v>
       </c>
       <c r="N355" t="n">
-        <v>4372.2107862617</v>
+        <v>4372.2107863175</v>
       </c>
       <c r="O355" t="n">
-        <v>502804.2404200956</v>
+        <v>502804.2404265125</v>
       </c>
       <c r="P355" t="n">
         <v>7500</v>
@@ -15655,22 +15655,22 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M356" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="N356" t="n">
         <v>6441.03</v>
       </c>
       <c r="O356" t="n">
-        <v>437990.04</v>
+        <v>315610.47</v>
       </c>
       <c r="P356" t="n">
         <v>10500</v>
       </c>
       <c r="Q356" t="n">
-        <v>714000</v>
+        <v>514500</v>
       </c>
     </row>
     <row r="357">
@@ -15707,10 +15707,10 @@
         <v>20</v>
       </c>
       <c r="N357" t="n">
-        <v>1592.5677691978</v>
+        <v>1592.5677332171</v>
       </c>
       <c r="O357" t="n">
-        <v>31851.355383956</v>
+        <v>31851.354664342</v>
       </c>
       <c r="P357" t="n">
         <v>3900</v>
@@ -15829,22 +15829,22 @@
         <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M360" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N360" t="n">
         <v>3655.96</v>
       </c>
       <c r="O360" t="n">
-        <v>449683.08</v>
+        <v>442371.16</v>
       </c>
       <c r="P360" t="n">
         <v>5500</v>
       </c>
       <c r="Q360" t="n">
-        <v>676500</v>
+        <v>665500</v>
       </c>
     </row>
     <row r="361">
@@ -16178,22 +16178,22 @@
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M368" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N368" t="n">
         <v>5633.97</v>
       </c>
       <c r="O368" t="n">
-        <v>185921.01</v>
+        <v>169019.1</v>
       </c>
       <c r="P368" t="n">
         <v>9600</v>
       </c>
       <c r="Q368" t="n">
-        <v>316800</v>
+        <v>288000</v>
       </c>
     </row>
     <row r="369">
@@ -16224,22 +16224,22 @@
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M369" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="N369" t="n">
         <v>6242.93</v>
       </c>
       <c r="O369" t="n">
-        <v>680479.37</v>
+        <v>630535.9300000001</v>
       </c>
       <c r="P369" t="n">
         <v>10400</v>
       </c>
       <c r="Q369" t="n">
-        <v>1133600</v>
+        <v>1050400</v>
       </c>
     </row>
     <row r="370">
@@ -16273,22 +16273,22 @@
         <v>0</v>
       </c>
       <c r="L370" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M370" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="N370" t="n">
         <v>4648.6</v>
       </c>
       <c r="O370" t="n">
-        <v>1654901.6</v>
+        <v>1631658.6</v>
       </c>
       <c r="P370" t="n">
         <v>8900</v>
       </c>
       <c r="Q370" t="n">
-        <v>3168400</v>
+        <v>3123900</v>
       </c>
     </row>
     <row r="371">
@@ -16496,10 +16496,10 @@
         <v>332</v>
       </c>
       <c r="N375" t="n">
-        <v>1532.6290291403</v>
+        <v>1532.629028858</v>
       </c>
       <c r="O375" t="n">
-        <v>508832.8376745796</v>
+        <v>508832.8375808561</v>
       </c>
       <c r="P375" t="n">
         <v>1200</v>
@@ -16707,22 +16707,22 @@
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M380" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N380" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O380" t="n">
-        <v>423643.95</v>
+        <v>414229.64</v>
       </c>
       <c r="P380" t="n">
         <v>16900</v>
       </c>
       <c r="Q380" t="n">
-        <v>760500</v>
+        <v>743600</v>
       </c>
     </row>
     <row r="381">
@@ -16751,22 +16751,22 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M381" t="n">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="N381" t="n">
         <v>1387.55</v>
       </c>
       <c r="O381" t="n">
-        <v>471767</v>
+        <v>428752.95</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
       </c>
       <c r="Q381" t="n">
-        <v>782000</v>
+        <v>710700</v>
       </c>
     </row>
     <row r="382">
@@ -16877,22 +16877,22 @@
         <v>0</v>
       </c>
       <c r="L384" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M384" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N384" t="n">
-        <v>2021.7211191336</v>
+        <v>2021.7211218335</v>
       </c>
       <c r="O384" t="n">
-        <v>371996.6859205824</v>
+        <v>363909.80193003</v>
       </c>
       <c r="P384" t="n">
         <v>2400</v>
       </c>
       <c r="Q384" t="n">
-        <v>441600</v>
+        <v>432000</v>
       </c>
     </row>
     <row r="385">
@@ -16921,22 +16921,22 @@
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M385" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N385" t="n">
         <v>13304.13</v>
       </c>
       <c r="O385" t="n">
-        <v>518861.0699999999</v>
+        <v>492252.81</v>
       </c>
       <c r="P385" t="n">
         <v>20900</v>
       </c>
       <c r="Q385" t="n">
-        <v>815100</v>
+        <v>773300</v>
       </c>
     </row>
     <row r="386">
@@ -17014,22 +17014,22 @@
         <v>0</v>
       </c>
       <c r="L387" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M387" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N387" t="n">
         <v>2204</v>
       </c>
       <c r="O387" t="n">
-        <v>235828</v>
+        <v>231420</v>
       </c>
       <c r="P387" t="n">
         <v>1500</v>
       </c>
       <c r="Q387" t="n">
-        <v>160500</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="388">
@@ -17200,22 +17200,22 @@
         <v>0</v>
       </c>
       <c r="L391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M391" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N391" t="n">
         <v>3761.6</v>
       </c>
       <c r="O391" t="n">
-        <v>101563.2</v>
+        <v>94040</v>
       </c>
       <c r="P391" t="n">
         <v>6900</v>
       </c>
       <c r="Q391" t="n">
-        <v>186300</v>
+        <v>172500</v>
       </c>
     </row>
     <row r="392">
@@ -17336,22 +17336,22 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M394" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N394" t="n">
         <v>11921.4</v>
       </c>
       <c r="O394" t="n">
-        <v>1847817</v>
+        <v>1800131.4</v>
       </c>
       <c r="P394" t="n">
         <v>19900</v>
       </c>
       <c r="Q394" t="n">
-        <v>3084500</v>
+        <v>3004900</v>
       </c>
     </row>
     <row r="395">
@@ -17676,22 +17676,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M402" t="n">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="N402" t="n">
         <v>3751</v>
       </c>
       <c r="O402" t="n">
-        <v>3480928</v>
+        <v>3454671</v>
       </c>
       <c r="P402" t="n">
         <v>6400</v>
       </c>
       <c r="Q402" t="n">
-        <v>5939200</v>
+        <v>5894400</v>
       </c>
     </row>
     <row r="403">
@@ -17725,22 +17725,22 @@
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N403" t="n">
         <v>9903</v>
       </c>
       <c r="O403" t="n">
-        <v>683307</v>
+        <v>673404</v>
       </c>
       <c r="P403" t="n">
         <v>15900</v>
       </c>
       <c r="Q403" t="n">
-        <v>1097100</v>
+        <v>1081200</v>
       </c>
     </row>
     <row r="404">
@@ -17817,22 +17817,22 @@
         <v>0</v>
       </c>
       <c r="L405" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M405" t="n">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="N405" t="n">
-        <v>1630.9229788882</v>
+        <v>1630.9230192383</v>
       </c>
       <c r="O405" t="n">
-        <v>1461306.989083827</v>
+        <v>1451521.487122087</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
       </c>
       <c r="Q405" t="n">
-        <v>2240000</v>
+        <v>2225000</v>
       </c>
     </row>
     <row r="406">
@@ -17950,22 +17950,22 @@
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M408" t="n">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="N408" t="n">
-        <v>1690.6043069815</v>
+        <v>1690.603799682</v>
       </c>
       <c r="O408" t="n">
-        <v>238375.2072843915</v>
+        <v>174132.191367246</v>
       </c>
       <c r="P408" t="n">
         <v>2900</v>
       </c>
       <c r="Q408" t="n">
-        <v>408900</v>
+        <v>298700</v>
       </c>
     </row>
     <row r="409">
@@ -17996,22 +17996,22 @@
         <v>0</v>
       </c>
       <c r="L409" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M409" t="n">
-        <v>2269</v>
+        <v>2253</v>
       </c>
       <c r="N409" t="n">
-        <v>1550.1929105882</v>
+        <v>1550.19293615</v>
       </c>
       <c r="O409" t="n">
-        <v>3517387.714124626</v>
+        <v>3492584.68514595</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
       </c>
       <c r="Q409" t="n">
-        <v>5672500</v>
+        <v>5632500</v>
       </c>
     </row>
     <row r="410">
@@ -18048,10 +18048,10 @@
         <v>3</v>
       </c>
       <c r="N410" t="n">
-        <v>1579.3913493976</v>
+        <v>1579.3910696517</v>
       </c>
       <c r="O410" t="n">
-        <v>4738.1740481928</v>
+        <v>4738.173208955101</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
@@ -18094,10 +18094,10 @@
         <v>1100</v>
       </c>
       <c r="N411" t="n">
-        <v>2403.5099727039</v>
+        <v>2403.5100306848</v>
       </c>
       <c r="O411" t="n">
-        <v>2643860.96997429</v>
+        <v>2643861.03375328</v>
       </c>
       <c r="P411" t="n">
         <v>3500</v>
@@ -18134,22 +18134,22 @@
         <v>0</v>
       </c>
       <c r="L412" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M412" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N412" t="n">
-        <v>2521.5483026316</v>
+        <v>2521.5479047619</v>
       </c>
       <c r="O412" t="n">
-        <v>226939.347236844</v>
+        <v>221896.2156190472</v>
       </c>
       <c r="P412" t="n">
         <v>3900</v>
       </c>
       <c r="Q412" t="n">
-        <v>351000</v>
+        <v>343200</v>
       </c>
     </row>
     <row r="413">
@@ -21825,22 +21825,22 @@
         <v>0</v>
       </c>
       <c r="L498" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M498" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N498" t="n">
         <v>6652</v>
       </c>
       <c r="O498" t="n">
-        <v>505552</v>
+        <v>485596</v>
       </c>
       <c r="P498" t="n">
         <v>5900</v>
       </c>
       <c r="Q498" t="n">
-        <v>448400</v>
+        <v>430700</v>
       </c>
     </row>
     <row r="499">
@@ -22323,10 +22323,10 @@
         <v>64</v>
       </c>
       <c r="N510" t="n">
-        <v>22485.695932203</v>
+        <v>22485.695927602</v>
       </c>
       <c r="O510" t="n">
-        <v>1439084.539660992</v>
+        <v>1439084.539366528</v>
       </c>
       <c r="P510" t="n">
         <v>36500</v>
@@ -22659,10 +22659,10 @@
         <v>169</v>
       </c>
       <c r="N518" t="n">
-        <v>2680.739700489</v>
+        <v>2680.7396999388</v>
       </c>
       <c r="O518" t="n">
-        <v>453045.009382641</v>
+        <v>453045.0092896572</v>
       </c>
       <c r="P518" t="n">
         <v>4900</v>
@@ -22694,22 +22694,22 @@
         <v>0</v>
       </c>
       <c r="L519" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M519" t="n">
-        <v>1412</v>
+        <v>1382</v>
       </c>
       <c r="N519" t="n">
-        <v>880.32923254206</v>
+        <v>880.32929682061</v>
       </c>
       <c r="O519" t="n">
-        <v>1243024.876349389</v>
+        <v>1216615.088206083</v>
       </c>
       <c r="P519" t="n">
         <v>1200</v>
       </c>
       <c r="Q519" t="n">
-        <v>1694400</v>
+        <v>1658400</v>
       </c>
     </row>
     <row r="520">
@@ -22869,10 +22869,10 @@
         <v>9</v>
       </c>
       <c r="N523" t="n">
-        <v>11431.604880952</v>
+        <v>11431.604819277</v>
       </c>
       <c r="O523" t="n">
-        <v>102884.443928568</v>
+        <v>102884.443373493</v>
       </c>
       <c r="P523" t="n">
         <v>48900</v>
@@ -23068,22 +23068,22 @@
         <v>0</v>
       </c>
       <c r="L528" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M528" t="n">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="N528" t="n">
-        <v>1732.9153957286</v>
+        <v>1732.9153666245</v>
       </c>
       <c r="O528" t="n">
-        <v>341384.3329585342</v>
+        <v>306726.0198925365</v>
       </c>
       <c r="P528" t="n">
         <v>1900</v>
       </c>
       <c r="Q528" t="n">
-        <v>374300</v>
+        <v>336300</v>
       </c>
     </row>
     <row r="529">
@@ -23247,22 +23247,22 @@
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M532" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N532" t="n">
         <v>56503</v>
       </c>
       <c r="O532" t="n">
-        <v>1412575</v>
+        <v>1299569</v>
       </c>
       <c r="P532" t="n">
         <v>90500</v>
       </c>
       <c r="Q532" t="n">
-        <v>2262500</v>
+        <v>2081500</v>
       </c>
     </row>
     <row r="533">
@@ -23294,10 +23294,10 @@
         <v>19</v>
       </c>
       <c r="N533" t="n">
-        <v>3731.0243234323</v>
+        <v>3731.0243377483</v>
       </c>
       <c r="O533" t="n">
-        <v>70889.46214521371</v>
+        <v>70889.4624172177</v>
       </c>
       <c r="P533" t="n">
         <v>5200</v>
@@ -23686,10 +23686,10 @@
         <v>280</v>
       </c>
       <c r="N542" t="n">
-        <v>4285.1952263374</v>
+        <v>4285.1952479339</v>
       </c>
       <c r="O542" t="n">
-        <v>1199854.663374472</v>
+        <v>1199854.669421492</v>
       </c>
       <c r="P542" t="n">
         <v>6900</v>
@@ -23770,22 +23770,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M544" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N544" t="n">
         <v>9776.99</v>
       </c>
       <c r="O544" t="n">
-        <v>2170491.78</v>
+        <v>2150937.8</v>
       </c>
       <c r="P544" t="n">
         <v>15900</v>
       </c>
       <c r="Q544" t="n">
-        <v>3529800</v>
+        <v>3498000</v>
       </c>
     </row>
     <row r="545">
@@ -24359,22 +24359,22 @@
         <v>0</v>
       </c>
       <c r="L558" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M558" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N558" t="n">
-        <v>30244.600034662</v>
+        <v>30244.600034682</v>
       </c>
       <c r="O558" t="n">
-        <v>514158.200589254</v>
+        <v>483913.600554912</v>
       </c>
       <c r="P558" t="n">
         <v>48900</v>
       </c>
       <c r="Q558" t="n">
-        <v>831300</v>
+        <v>782400</v>
       </c>
     </row>
     <row r="559">
@@ -24538,22 +24538,22 @@
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M562" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N562" t="n">
-        <v>13513.64294964</v>
+        <v>13513.642971014</v>
       </c>
       <c r="O562" t="n">
-        <v>824332.2199280399</v>
+        <v>810818.57826084</v>
       </c>
       <c r="P562" t="n">
         <v>21900</v>
       </c>
       <c r="Q562" t="n">
-        <v>1335900</v>
+        <v>1314000</v>
       </c>
     </row>
     <row r="563">
@@ -25654,22 +25654,22 @@
         <v>0</v>
       </c>
       <c r="L588" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M588" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N588" t="n">
         <v>22730.48</v>
       </c>
       <c r="O588" t="n">
-        <v>704644.88</v>
+        <v>613722.96</v>
       </c>
       <c r="P588" t="n">
         <v>36900</v>
       </c>
       <c r="Q588" t="n">
-        <v>1143900</v>
+        <v>996300</v>
       </c>
     </row>
     <row r="589">
@@ -25838,22 +25838,22 @@
         <v>0</v>
       </c>
       <c r="L592" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M592" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N592" t="n">
-        <v>27123.765259259</v>
+        <v>27123.765250464</v>
       </c>
       <c r="O592" t="n">
-        <v>1139198.140888878</v>
+        <v>1112074.375269024</v>
       </c>
       <c r="P592" t="n">
         <v>44500</v>
       </c>
       <c r="Q592" t="n">
-        <v>1869000</v>
+        <v>1824500</v>
       </c>
     </row>
     <row r="593">
@@ -26181,22 +26181,22 @@
         <v>0</v>
       </c>
       <c r="L600" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M600" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="N600" t="n">
-        <v>1560.9985110132</v>
+        <v>1560.9988178914</v>
       </c>
       <c r="O600" t="n">
-        <v>271613.7409162968</v>
+        <v>232588.8238658186</v>
       </c>
       <c r="P600" t="n">
         <v>2900</v>
       </c>
       <c r="Q600" t="n">
-        <v>504600</v>
+        <v>432100</v>
       </c>
     </row>
     <row r="601">
@@ -26314,22 +26314,22 @@
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M603" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N603" t="n">
         <v>26854</v>
       </c>
       <c r="O603" t="n">
-        <v>1074160</v>
+        <v>1047306</v>
       </c>
       <c r="P603" t="n">
         <v>43900</v>
       </c>
       <c r="Q603" t="n">
-        <v>1756000</v>
+        <v>1712100</v>
       </c>
     </row>
     <row r="604">
@@ -26497,10 +26497,10 @@
         <v>141</v>
       </c>
       <c r="N607" t="n">
-        <v>7969.9501643017</v>
+        <v>7969.950164794</v>
       </c>
       <c r="O607" t="n">
-        <v>1123762.97316654</v>
+        <v>1123762.973235954</v>
       </c>
       <c r="P607" t="n">
         <v>12900</v>
@@ -26742,22 +26742,22 @@
         <v>0</v>
       </c>
       <c r="L613" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M613" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N613" t="n">
         <v>21508</v>
       </c>
       <c r="O613" t="n">
-        <v>193572</v>
+        <v>172064</v>
       </c>
       <c r="P613" t="n">
         <v>36900</v>
       </c>
       <c r="Q613" t="n">
-        <v>332100</v>
+        <v>295200</v>
       </c>
     </row>
     <row r="614">
@@ -27909,10 +27909,10 @@
         <v>71</v>
       </c>
       <c r="N640" t="n">
-        <v>3113.8900239521</v>
+        <v>3113.8900249066</v>
       </c>
       <c r="O640" t="n">
-        <v>221086.1917005991</v>
+        <v>221086.1917683686</v>
       </c>
       <c r="P640" t="n">
         <v>5000</v>
@@ -27995,22 +27995,22 @@
         <v>0</v>
       </c>
       <c r="L642" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M642" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="N642" t="n">
         <v>4690.64</v>
       </c>
       <c r="O642" t="n">
-        <v>229841.36</v>
+        <v>168863.04</v>
       </c>
       <c r="P642" t="n">
         <v>7500</v>
       </c>
       <c r="Q642" t="n">
-        <v>367500</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="643">
@@ -28041,22 +28041,22 @@
         <v>0</v>
       </c>
       <c r="L643" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M643" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="N643" t="n">
         <v>5410.72</v>
       </c>
       <c r="O643" t="n">
-        <v>432857.6</v>
+        <v>384161.12</v>
       </c>
       <c r="P643" t="n">
         <v>8700</v>
       </c>
       <c r="Q643" t="n">
-        <v>696000</v>
+        <v>617700</v>
       </c>
     </row>
     <row r="644">
@@ -28087,22 +28087,22 @@
         <v>0</v>
       </c>
       <c r="L644" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M644" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N644" t="n">
-        <v>4163.1601639344</v>
+        <v>4163.1601724138</v>
       </c>
       <c r="O644" t="n">
-        <v>104079.00409836</v>
+        <v>79100.0432758622</v>
       </c>
       <c r="P644" t="n">
         <v>6700</v>
       </c>
       <c r="Q644" t="n">
-        <v>167500</v>
+        <v>127300</v>
       </c>
     </row>
     <row r="645">
@@ -28271,22 +28271,22 @@
         <v>0</v>
       </c>
       <c r="L648" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M648" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N648" t="n">
-        <v>5218.1704756757</v>
+        <v>5218.1704867257</v>
       </c>
       <c r="O648" t="n">
-        <v>140890.6028432439</v>
+        <v>125236.0916814168</v>
       </c>
       <c r="P648" t="n">
         <v>8500</v>
       </c>
       <c r="Q648" t="n">
-        <v>229500</v>
+        <v>204000</v>
       </c>
     </row>
     <row r="649">
@@ -28323,10 +28323,10 @@
         <v>140</v>
       </c>
       <c r="N649" t="n">
-        <v>1595.0095090439</v>
+        <v>1595.0094973545</v>
       </c>
       <c r="O649" t="n">
-        <v>223301.331266146</v>
+        <v>223301.32962963</v>
       </c>
       <c r="P649" t="n">
         <v>2600</v>
@@ -28360,25 +28360,25 @@
         <v>35</v>
       </c>
       <c r="K650" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L650" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M650" t="n">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="N650" t="n">
-        <v>3610.6500232019</v>
+        <v>3610.6500236967</v>
       </c>
       <c r="O650" t="n">
-        <v>126372.7508120665</v>
+        <v>299683.9519668261</v>
       </c>
       <c r="P650" t="n">
         <v>5800</v>
       </c>
       <c r="Q650" t="n">
-        <v>203000</v>
+        <v>481400</v>
       </c>
     </row>
     <row r="651">
@@ -28685,22 +28685,22 @@
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M657" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N657" t="n">
         <v>6058.52</v>
       </c>
       <c r="O657" t="n">
-        <v>224165.24</v>
+        <v>193872.64</v>
       </c>
       <c r="P657" t="n">
         <v>9700</v>
       </c>
       <c r="Q657" t="n">
-        <v>358900</v>
+        <v>310400</v>
       </c>
     </row>
     <row r="658">
@@ -28777,22 +28777,22 @@
         <v>0</v>
       </c>
       <c r="L659" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M659" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N659" t="n">
-        <v>1664.3613046757</v>
+        <v>1664.3609992194</v>
       </c>
       <c r="O659" t="n">
-        <v>719004.0836199024</v>
+        <v>717339.5906635614</v>
       </c>
       <c r="P659" t="n">
         <v>2900</v>
       </c>
       <c r="Q659" t="n">
-        <v>1252800</v>
+        <v>1249900</v>
       </c>
     </row>
     <row r="660">
@@ -28869,22 +28869,22 @@
         <v>0</v>
       </c>
       <c r="L661" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M661" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N661" t="n">
         <v>15502</v>
       </c>
       <c r="O661" t="n">
-        <v>713092</v>
+        <v>697590</v>
       </c>
       <c r="P661" t="n">
         <v>25900</v>
       </c>
       <c r="Q661" t="n">
-        <v>1191400</v>
+        <v>1165500</v>
       </c>
     </row>
     <row r="662">
@@ -29335,22 +29335,22 @@
         <v>0</v>
       </c>
       <c r="L671" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M671" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N671" t="n">
         <v>3646</v>
       </c>
       <c r="O671" t="n">
-        <v>539608</v>
+        <v>525024</v>
       </c>
       <c r="P671" t="n">
         <v>6900</v>
       </c>
       <c r="Q671" t="n">
-        <v>1021200</v>
+        <v>993600</v>
       </c>
     </row>
     <row r="672">
@@ -29473,22 +29473,22 @@
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M674" t="n">
-        <v>1581</v>
+        <v>1573</v>
       </c>
       <c r="N674" t="n">
-        <v>1778.4725093418</v>
+        <v>1778.4725198441</v>
       </c>
       <c r="O674" t="n">
-        <v>2811765.037269386</v>
+        <v>2797537.273714769</v>
       </c>
       <c r="P674" t="n">
         <v>4900</v>
       </c>
       <c r="Q674" t="n">
-        <v>7746900</v>
+        <v>7707700</v>
       </c>
     </row>
     <row r="675">
@@ -30529,22 +30529,22 @@
         <v>0</v>
       </c>
       <c r="L697" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M697" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N697" t="n">
         <v>1817</v>
       </c>
       <c r="O697" t="n">
-        <v>301622</v>
+        <v>297988</v>
       </c>
       <c r="P697" t="n">
         <v>3100</v>
       </c>
       <c r="Q697" t="n">
-        <v>514600</v>
+        <v>508400</v>
       </c>
     </row>
     <row r="698">
@@ -31411,22 +31411,22 @@
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M716" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N716" t="n">
         <v>55898</v>
       </c>
       <c r="O716" t="n">
-        <v>1229756</v>
+        <v>1173858</v>
       </c>
       <c r="P716" t="n">
         <v>89900</v>
       </c>
       <c r="Q716" t="n">
-        <v>1977800</v>
+        <v>1887900</v>
       </c>
     </row>
     <row r="717">
@@ -31641,22 +31641,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M721" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N721" t="n">
         <v>3424</v>
       </c>
       <c r="O721" t="n">
-        <v>657408</v>
+        <v>653984</v>
       </c>
       <c r="P721" t="n">
         <v>5900</v>
       </c>
       <c r="Q721" t="n">
-        <v>1132800</v>
+        <v>1126900</v>
       </c>
     </row>
     <row r="722">
@@ -31733,22 +31733,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M723" t="n">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="N723" t="n">
         <v>8858.16</v>
       </c>
       <c r="O723" t="n">
-        <v>2577724.56</v>
+        <v>2542291.92</v>
       </c>
       <c r="P723" t="n">
         <v>15500</v>
       </c>
       <c r="Q723" t="n">
-        <v>4510500</v>
+        <v>4448500</v>
       </c>
     </row>
     <row r="724">
@@ -32427,10 +32427,10 @@
         <v>702</v>
       </c>
       <c r="N738" t="n">
-        <v>2328.1187536917</v>
+        <v>2328.1187525865</v>
       </c>
       <c r="O738" t="n">
-        <v>1634339.365091573</v>
+        <v>1634339.364315723</v>
       </c>
       <c r="P738" t="n">
         <v>4500</v>
@@ -33301,10 +33301,10 @@
         <v>18</v>
       </c>
       <c r="N757" t="n">
-        <v>4907.821904048</v>
+        <v>4907.8219155354</v>
       </c>
       <c r="O757" t="n">
-        <v>88340.794272864</v>
+        <v>88340.7944796372</v>
       </c>
       <c r="P757" t="n">
         <v>8200</v>
@@ -33571,22 +33571,22 @@
         <v>0</v>
       </c>
       <c r="L763" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M763" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N763" t="n">
-        <v>3903.7358605664</v>
+        <v>3903.7358951965</v>
       </c>
       <c r="O763" t="n">
-        <v>476255.7749891008</v>
+        <v>468448.30742358</v>
       </c>
       <c r="P763" t="n">
         <v>7500</v>
       </c>
       <c r="Q763" t="n">
-        <v>915000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="764">
@@ -33704,22 +33704,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M766" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N766" t="n">
         <v>12113</v>
       </c>
       <c r="O766" t="n">
-        <v>763119</v>
+        <v>726780</v>
       </c>
       <c r="P766" t="n">
         <v>19900</v>
       </c>
       <c r="Q766" t="n">
-        <v>1253700</v>
+        <v>1194000</v>
       </c>
     </row>
     <row r="767">
@@ -33934,22 +33934,22 @@
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M771" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N771" t="n">
         <v>16469</v>
       </c>
       <c r="O771" t="n">
-        <v>1070485</v>
+        <v>1054016</v>
       </c>
       <c r="P771" t="n">
         <v>26900</v>
       </c>
       <c r="Q771" t="n">
-        <v>1748500</v>
+        <v>1721600</v>
       </c>
     </row>
     <row r="772">
@@ -34164,22 +34164,22 @@
         <v>0</v>
       </c>
       <c r="L776" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M776" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N776" t="n">
-        <v>5869.1727610442</v>
+        <v>5869.1727464789</v>
       </c>
       <c r="O776" t="n">
-        <v>1643368.373092376</v>
+        <v>1631630.023521134</v>
       </c>
       <c r="P776" t="n">
         <v>9500</v>
       </c>
       <c r="Q776" t="n">
-        <v>2660000</v>
+        <v>2641000</v>
       </c>
     </row>
     <row r="777">
@@ -34210,22 +34210,22 @@
         <v>0</v>
       </c>
       <c r="L777" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M777" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N777" t="n">
         <v>6849.2</v>
       </c>
       <c r="O777" t="n">
-        <v>849300.7999999999</v>
+        <v>842451.6</v>
       </c>
       <c r="P777" t="n">
         <v>11500</v>
       </c>
       <c r="Q777" t="n">
-        <v>1426000</v>
+        <v>1414500</v>
       </c>
     </row>
     <row r="778">
@@ -34302,22 +34302,22 @@
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M779" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N779" t="n">
         <v>5772</v>
       </c>
       <c r="O779" t="n">
-        <v>940836</v>
+        <v>935064</v>
       </c>
       <c r="P779" t="n">
         <v>9900</v>
       </c>
       <c r="Q779" t="n">
-        <v>1613700</v>
+        <v>1603800</v>
       </c>
     </row>
     <row r="780">
@@ -34348,22 +34348,22 @@
         <v>0</v>
       </c>
       <c r="L780" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M780" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N780" t="n">
         <v>6268</v>
       </c>
       <c r="O780" t="n">
-        <v>770964</v>
+        <v>758428</v>
       </c>
       <c r="P780" t="n">
         <v>10900</v>
       </c>
       <c r="Q780" t="n">
-        <v>1340700</v>
+        <v>1318900</v>
       </c>
     </row>
     <row r="781">
@@ -34440,22 +34440,22 @@
         <v>0</v>
       </c>
       <c r="L782" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M782" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N782" t="n">
         <v>6645</v>
       </c>
       <c r="O782" t="n">
-        <v>1667895</v>
+        <v>1661250</v>
       </c>
       <c r="P782" t="n">
         <v>10900</v>
       </c>
       <c r="Q782" t="n">
-        <v>2735900</v>
+        <v>2725000</v>
       </c>
     </row>
     <row r="783">
@@ -34624,22 +34624,22 @@
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M786" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N786" t="n">
         <v>7562</v>
       </c>
       <c r="O786" t="n">
-        <v>552026</v>
+        <v>544464</v>
       </c>
       <c r="P786" t="n">
         <v>12900</v>
       </c>
       <c r="Q786" t="n">
-        <v>941700</v>
+        <v>928800</v>
       </c>
     </row>
     <row r="787">
@@ -34995,22 +34995,22 @@
         <v>0</v>
       </c>
       <c r="L794" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M794" t="n">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="N794" t="n">
         <v>753</v>
       </c>
       <c r="O794" t="n">
-        <v>588093</v>
+        <v>583575</v>
       </c>
       <c r="P794" t="n">
         <v>1600</v>
       </c>
       <c r="Q794" t="n">
-        <v>1249600</v>
+        <v>1240000</v>
       </c>
     </row>
     <row r="795">
@@ -35683,22 +35683,22 @@
         <v>0</v>
       </c>
       <c r="L809" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M809" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="N809" t="n">
         <v>10755</v>
       </c>
       <c r="O809" t="n">
-        <v>602280</v>
+        <v>494730</v>
       </c>
       <c r="P809" t="n">
         <v>17900</v>
       </c>
       <c r="Q809" t="n">
-        <v>1002400</v>
+        <v>823400</v>
       </c>
     </row>
     <row r="810">
@@ -35913,22 +35913,22 @@
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M814" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="N814" t="n">
-        <v>4268.7033206107</v>
+        <v>4268.7035271318</v>
       </c>
       <c r="O814" t="n">
-        <v>435407.7387022914</v>
+        <v>418332.9456589164</v>
       </c>
       <c r="P814" t="n">
         <v>6900</v>
       </c>
       <c r="Q814" t="n">
-        <v>703800</v>
+        <v>676200</v>
       </c>
     </row>
     <row r="815">
@@ -36143,22 +36143,22 @@
         <v>0</v>
       </c>
       <c r="L819" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M819" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N819" t="n">
         <v>40073</v>
       </c>
       <c r="O819" t="n">
-        <v>2204015</v>
+        <v>2163942</v>
       </c>
       <c r="P819" t="n">
         <v>64900</v>
       </c>
       <c r="Q819" t="n">
-        <v>3569500</v>
+        <v>3504600</v>
       </c>
     </row>
     <row r="820">
@@ -36327,22 +36327,22 @@
         <v>0</v>
       </c>
       <c r="L823" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M823" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N823" t="n">
         <v>2573</v>
       </c>
       <c r="O823" t="n">
-        <v>414253</v>
+        <v>411680</v>
       </c>
       <c r="P823" t="n">
         <v>4500</v>
       </c>
       <c r="Q823" t="n">
-        <v>724500</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="824">
@@ -36695,22 +36695,22 @@
         <v>0</v>
       </c>
       <c r="L831" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M831" t="n">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N831" t="n">
         <v>5476</v>
       </c>
       <c r="O831" t="n">
-        <v>2535388</v>
+        <v>2524436</v>
       </c>
       <c r="P831" t="n">
         <v>8900</v>
       </c>
       <c r="Q831" t="n">
-        <v>4120700</v>
+        <v>4102900</v>
       </c>
     </row>
     <row r="832">
@@ -36882,22 +36882,22 @@
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M835" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N835" t="n">
         <v>64612</v>
       </c>
       <c r="O835" t="n">
-        <v>1744524</v>
+        <v>1679912</v>
       </c>
       <c r="P835" t="n">
         <v>103900</v>
       </c>
       <c r="Q835" t="n">
-        <v>2805300</v>
+        <v>2701400</v>
       </c>
     </row>
     <row r="836">
@@ -36928,22 +36928,22 @@
         <v>0</v>
       </c>
       <c r="L836" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M836" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N836" t="n">
         <v>38252</v>
       </c>
       <c r="O836" t="n">
-        <v>420772</v>
+        <v>306016</v>
       </c>
       <c r="P836" t="n">
         <v>61900</v>
       </c>
       <c r="Q836" t="n">
-        <v>680900</v>
+        <v>495200</v>
       </c>
     </row>
     <row r="837">
@@ -36980,10 +36980,10 @@
         <v>604</v>
       </c>
       <c r="N837" t="n">
-        <v>1516.0388166875</v>
+        <v>1516.0388137227</v>
       </c>
       <c r="O837" t="n">
-        <v>915687.44527925</v>
+        <v>915687.4434885108</v>
       </c>
       <c r="P837" t="n">
         <v>2300</v>
@@ -37020,22 +37020,22 @@
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M838" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N838" t="n">
-        <v>4248.6136842105</v>
+        <v>4248.6172239748</v>
       </c>
       <c r="O838" t="n">
-        <v>735010.1673684164</v>
+        <v>726513.5452996908</v>
       </c>
       <c r="P838" t="n">
         <v>5900</v>
       </c>
       <c r="Q838" t="n">
-        <v>1020700</v>
+        <v>1008900</v>
       </c>
     </row>
     <row r="839">
@@ -37116,10 +37116,10 @@
         <v>378</v>
       </c>
       <c r="N840" t="n">
-        <v>2458.5134637046</v>
+        <v>2458.5134514107</v>
       </c>
       <c r="O840" t="n">
-        <v>929318.0892803387</v>
+        <v>929318.0846332446</v>
       </c>
       <c r="P840" t="n">
         <v>3500</v>
@@ -37300,10 +37300,10 @@
         <v>448</v>
       </c>
       <c r="N844" t="n">
-        <v>1803.0149852941</v>
+        <v>1803.0149867608</v>
       </c>
       <c r="O844" t="n">
-        <v>807750.7134117568</v>
+        <v>807750.7140688384</v>
       </c>
       <c r="P844" t="n">
         <v>2500</v>
@@ -37438,10 +37438,10 @@
         <v>66</v>
       </c>
       <c r="N847" t="n">
-        <v>2108.7897270195</v>
+        <v>2108.7897651007</v>
       </c>
       <c r="O847" t="n">
-        <v>139180.121983287</v>
+        <v>139180.1244966462</v>
       </c>
       <c r="P847" t="n">
         <v>2900</v>
@@ -37484,10 +37484,10 @@
         <v>739</v>
       </c>
       <c r="N848" t="n">
-        <v>2056.0839525344</v>
+        <v>2056.0838952972</v>
       </c>
       <c r="O848" t="n">
-        <v>1519446.040922922</v>
+        <v>1519445.998624631</v>
       </c>
       <c r="P848" t="n">
         <v>2900</v>
@@ -37524,22 +37524,22 @@
         <v>0</v>
       </c>
       <c r="L849" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M849" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="N849" t="n">
-        <v>3224.5679308817</v>
+        <v>3224.5679626335</v>
       </c>
       <c r="O849" t="n">
-        <v>844836.7978910053</v>
+        <v>828713.9663968094</v>
       </c>
       <c r="P849" t="n">
         <v>4500</v>
       </c>
       <c r="Q849" t="n">
-        <v>1179000</v>
+        <v>1156500</v>
       </c>
     </row>
     <row r="850">
@@ -37576,10 +37576,10 @@
         <v>470</v>
       </c>
       <c r="N850" t="n">
-        <v>1655.9314259144</v>
+        <v>1655.93135625</v>
       </c>
       <c r="O850" t="n">
-        <v>778287.770179768</v>
+        <v>778287.7374374999</v>
       </c>
       <c r="P850" t="n">
         <v>2500</v>
@@ -37619,22 +37619,22 @@
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M851" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N851" t="n">
         <v>5121</v>
       </c>
       <c r="O851" t="n">
-        <v>51210</v>
+        <v>46089</v>
       </c>
       <c r="P851" t="n">
         <v>9900</v>
       </c>
       <c r="Q851" t="n">
-        <v>99000</v>
+        <v>89100</v>
       </c>
     </row>
     <row r="852">
@@ -37941,22 +37941,22 @@
         <v>0</v>
       </c>
       <c r="L858" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M858" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="N858" t="n">
-        <v>1592.2745718734</v>
+        <v>1592.2746762208</v>
       </c>
       <c r="O858" t="n">
-        <v>257948.4806434908</v>
+        <v>248394.8494904448</v>
       </c>
       <c r="P858" t="n">
         <v>2500</v>
       </c>
       <c r="Q858" t="n">
-        <v>405000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="859">
@@ -38037,10 +38037,10 @@
         <v>80</v>
       </c>
       <c r="N860" t="n">
-        <v>2311.9273755656</v>
+        <v>2311.9269828927</v>
       </c>
       <c r="O860" t="n">
-        <v>184954.190045248</v>
+        <v>184954.158631416</v>
       </c>
       <c r="P860" t="n">
         <v>3500</v>
@@ -38083,10 +38083,10 @@
         <v>88</v>
       </c>
       <c r="N861" t="n">
-        <v>1906.1870703125</v>
+        <v>1906.1869325153</v>
       </c>
       <c r="O861" t="n">
-        <v>167744.4621875</v>
+        <v>167744.4500613464</v>
       </c>
       <c r="P861" t="n">
         <v>2900</v>
@@ -38129,10 +38129,10 @@
         <v>101</v>
       </c>
       <c r="N862" t="n">
-        <v>2060.1608716323</v>
+        <v>2060.160798722</v>
       </c>
       <c r="O862" t="n">
-        <v>208076.2480348623</v>
+        <v>208076.240670922</v>
       </c>
       <c r="P862" t="n">
         <v>2900</v>
@@ -38169,22 +38169,22 @@
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M863" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="N863" t="n">
-        <v>1668.6141040462</v>
+        <v>1668.6155910543</v>
       </c>
       <c r="O863" t="n">
-        <v>21691.9833526006</v>
+        <v>8343.077955271499</v>
       </c>
       <c r="P863" t="n">
         <v>2500</v>
       </c>
       <c r="Q863" t="n">
-        <v>32500</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="864">
@@ -38215,22 +38215,22 @@
         <v>0</v>
       </c>
       <c r="L864" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M864" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="N864" t="n">
-        <v>2546.9853442623</v>
+        <v>2546.9852428811</v>
       </c>
       <c r="O864" t="n">
-        <v>221587.7249508201</v>
+        <v>191023.8932160825</v>
       </c>
       <c r="P864" t="n">
         <v>3900</v>
       </c>
       <c r="Q864" t="n">
-        <v>339300</v>
+        <v>292500</v>
       </c>
     </row>
     <row r="865">
@@ -38261,22 +38261,22 @@
         <v>0</v>
       </c>
       <c r="L865" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M865" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="N865" t="n">
-        <v>1259.274396777</v>
+        <v>1259.2744102228</v>
       </c>
       <c r="O865" t="n">
-        <v>367708.123858884</v>
+        <v>357633.9325032752</v>
       </c>
       <c r="P865" t="n">
         <v>1900</v>
       </c>
       <c r="Q865" t="n">
-        <v>554800</v>
+        <v>539600</v>
       </c>
     </row>
     <row r="866">
@@ -38353,22 +38353,22 @@
         <v>0</v>
       </c>
       <c r="L867" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M867" t="n">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="N867" t="n">
         <v>1801</v>
       </c>
       <c r="O867" t="n">
-        <v>763624</v>
+        <v>736609</v>
       </c>
       <c r="P867" t="n">
         <v>2900</v>
       </c>
       <c r="Q867" t="n">
-        <v>1229600</v>
+        <v>1186100</v>
       </c>
     </row>
     <row r="868">
@@ -38403,10 +38403,10 @@
         <v>121</v>
       </c>
       <c r="N868" t="n">
-        <v>692.1520380194499</v>
+        <v>692.15204525288</v>
       </c>
       <c r="O868" t="n">
-        <v>83750.39660035344</v>
+        <v>83750.39747559848</v>
       </c>
       <c r="P868" t="n">
         <v>1200</v>
@@ -39185,22 +39185,22 @@
         <v>0</v>
       </c>
       <c r="L885" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M885" t="n">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="N885" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O885" t="n">
-        <v>2790958.56</v>
+        <v>2737286.28</v>
       </c>
       <c r="P885" t="n">
         <v>14900</v>
       </c>
       <c r="Q885" t="n">
-        <v>4648800</v>
+        <v>4559400</v>
       </c>
     </row>
     <row r="886">
@@ -39277,22 +39277,22 @@
         <v>0</v>
       </c>
       <c r="L887" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M887" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="N887" t="n">
-        <v>3026.5146116505</v>
+        <v>3026.514679803</v>
       </c>
       <c r="O887" t="n">
-        <v>6053.029223301</v>
+        <v>-3026.514679803</v>
       </c>
       <c r="P887" t="n">
         <v>7000</v>
       </c>
       <c r="Q887" t="n">
-        <v>14000</v>
+        <v>-7000</v>
       </c>
     </row>
     <row r="888">
@@ -39824,22 +39824,22 @@
         <v>0</v>
       </c>
       <c r="L899" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M899" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N899" t="n">
         <v>1865.66</v>
       </c>
       <c r="O899" t="n">
-        <v>100745.64</v>
+        <v>97014.32000000001</v>
       </c>
       <c r="P899" t="n">
         <v>2000</v>
       </c>
       <c r="Q899" t="n">
-        <v>108000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="900">
@@ -40099,22 +40099,22 @@
         <v>0</v>
       </c>
       <c r="L905" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M905" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N905" t="n">
-        <v>2270.3210416667</v>
+        <v>2270.3210752688</v>
       </c>
       <c r="O905" t="n">
-        <v>63568.9891666676</v>
+        <v>56758.02688172</v>
       </c>
       <c r="P905" t="n">
         <v>3900</v>
       </c>
       <c r="Q905" t="n">
-        <v>109200</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="906">
@@ -40149,10 +40149,10 @@
         <v>561</v>
       </c>
       <c r="N906" t="n">
-        <v>481.48791484103</v>
+        <v>481.48791460674</v>
       </c>
       <c r="O906" t="n">
-        <v>270114.7202258178</v>
+        <v>270114.7200943811</v>
       </c>
       <c r="P906" t="n">
         <v>650</v>
@@ -40466,22 +40466,22 @@
         <v>0</v>
       </c>
       <c r="L913" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M913" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="N913" t="n">
-        <v>2286.1661853593</v>
+        <v>2286.1661647535</v>
       </c>
       <c r="O913" t="n">
-        <v>329207.9306917392</v>
+        <v>310918.598406476</v>
       </c>
       <c r="P913" t="n">
         <v>3000</v>
       </c>
       <c r="Q913" t="n">
-        <v>432000</v>
+        <v>408000</v>
       </c>
     </row>
     <row r="914">
@@ -40594,22 +40594,22 @@
         <v>0</v>
       </c>
       <c r="L916" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M916" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N916" t="n">
         <v>5050</v>
       </c>
       <c r="O916" t="n">
-        <v>595900</v>
+        <v>585800</v>
       </c>
       <c r="P916" t="n">
         <v>2000</v>
       </c>
       <c r="Q916" t="n">
-        <v>236000</v>
+        <v>232000</v>
       </c>
     </row>
     <row r="917">
@@ -40732,10 +40732,10 @@
         <v>1</v>
       </c>
       <c r="N919" t="n">
-        <v>1283.6542902208</v>
+        <v>1283.6540655738</v>
       </c>
       <c r="O919" t="n">
-        <v>1283.6542902208</v>
+        <v>1283.6540655738</v>
       </c>
       <c r="P919" t="n">
         <v>1900</v>
@@ -41122,22 +41122,22 @@
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M928" t="n">
-        <v>1418</v>
+        <v>1238</v>
       </c>
       <c r="N928" t="n">
         <v>177.65</v>
       </c>
       <c r="O928" t="n">
-        <v>251907.7</v>
+        <v>219930.7</v>
       </c>
       <c r="P928" t="n">
         <v>300</v>
       </c>
       <c r="Q928" t="n">
-        <v>425400</v>
+        <v>371400</v>
       </c>
     </row>
     <row r="929">
@@ -41432,22 +41432,22 @@
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M935" t="n">
-        <v>3817</v>
+        <v>3745</v>
       </c>
       <c r="N935" t="n">
-        <v>517.28747614462</v>
+        <v>517.28760395334</v>
       </c>
       <c r="O935" t="n">
-        <v>1974486.296444014</v>
+        <v>1937242.076805258</v>
       </c>
       <c r="P935" t="n">
         <v>900</v>
       </c>
       <c r="Q935" t="n">
-        <v>3435300</v>
+        <v>3370500</v>
       </c>
     </row>
     <row r="936">
@@ -41658,22 +41658,22 @@
         <v>0</v>
       </c>
       <c r="L940" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M940" t="n">
-        <v>854</v>
+        <v>828</v>
       </c>
       <c r="N940" t="n">
-        <v>3110.8433414956</v>
+        <v>3110.843282022</v>
       </c>
       <c r="O940" t="n">
-        <v>2656660.213637242</v>
+        <v>2575778.237514216</v>
       </c>
       <c r="P940" t="n">
         <v>4500</v>
       </c>
       <c r="Q940" t="n">
-        <v>3843000</v>
+        <v>3726000</v>
       </c>
     </row>
     <row r="941">
@@ -41880,22 +41880,22 @@
         <v>0</v>
       </c>
       <c r="L945" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M945" t="n">
-        <v>1829</v>
+        <v>1685</v>
       </c>
       <c r="N945" t="n">
-        <v>703.79545471015</v>
+        <v>703.79543678174</v>
       </c>
       <c r="O945" t="n">
-        <v>1287241.886664864</v>
+        <v>1185895.310977232</v>
       </c>
       <c r="P945" t="n">
         <v>900</v>
       </c>
       <c r="Q945" t="n">
-        <v>1646100</v>
+        <v>1516500</v>
       </c>
     </row>
     <row r="946">
@@ -42063,22 +42063,22 @@
         <v>0</v>
       </c>
       <c r="L949" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M949" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N949" t="n">
-        <v>3920.10552</v>
+        <v>3920.1054098361</v>
       </c>
       <c r="O949" t="n">
-        <v>286167.70296</v>
+        <v>274407.378688527</v>
       </c>
       <c r="P949" t="n">
         <v>5500</v>
       </c>
       <c r="Q949" t="n">
-        <v>401500</v>
+        <v>385000</v>
       </c>
     </row>
     <row r="950">
@@ -42159,10 +42159,10 @@
         <v>3</v>
       </c>
       <c r="N951" t="n">
-        <v>2501.3854811715</v>
+        <v>2501.3854621849</v>
       </c>
       <c r="O951" t="n">
-        <v>7504.1564435145</v>
+        <v>7504.1563865547</v>
       </c>
       <c r="P951" t="n">
         <v>4100</v>
@@ -42464,22 +42464,22 @@
         <v>0</v>
       </c>
       <c r="L958" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M958" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N958" t="n">
         <v>1937</v>
       </c>
       <c r="O958" t="n">
-        <v>311857</v>
+        <v>306046</v>
       </c>
       <c r="P958" t="n">
         <v>3300</v>
       </c>
       <c r="Q958" t="n">
-        <v>531300</v>
+        <v>521400</v>
       </c>
     </row>
     <row r="959">
@@ -42508,22 +42508,22 @@
         <v>0</v>
       </c>
       <c r="L959" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M959" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="N959" t="n">
         <v>2525.02</v>
       </c>
       <c r="O959" t="n">
-        <v>214626.7</v>
+        <v>199476.58</v>
       </c>
       <c r="P959" t="n">
         <v>3000</v>
       </c>
       <c r="Q959" t="n">
-        <v>255000</v>
+        <v>237000</v>
       </c>
     </row>
     <row r="960">
@@ -42727,10 +42727,10 @@
         <v>23</v>
       </c>
       <c r="N964" t="n">
-        <v>3629.7161122661</v>
+        <v>3629.7161041667</v>
       </c>
       <c r="O964" t="n">
-        <v>83483.4705821203</v>
+        <v>83483.4703958341</v>
       </c>
       <c r="P964" t="n">
         <v>4900</v>
@@ -42943,10 +42943,10 @@
         <v>74</v>
       </c>
       <c r="N969" t="n">
-        <v>1595.51921946</v>
+        <v>1595.5191410878</v>
       </c>
       <c r="O969" t="n">
-        <v>118068.42224004</v>
+        <v>118068.4164404972</v>
       </c>
       <c r="P969" t="n">
         <v>2500</v>
@@ -44130,10 +44130,10 @@
         <v>16</v>
       </c>
       <c r="N994" t="n">
-        <v>3414.5660866203</v>
+        <v>3414.5660805577</v>
       </c>
       <c r="O994" t="n">
-        <v>54633.0573859248</v>
+        <v>54633.0572889232</v>
       </c>
       <c r="P994" t="n">
         <v>3500</v>
@@ -44354,10 +44354,10 @@
         <v>1</v>
       </c>
       <c r="N999" t="n">
-        <v>1783.7988878843</v>
+        <v>1783.7988868778</v>
       </c>
       <c r="O999" t="n">
-        <v>1783.7988878843</v>
+        <v>1783.7988868778</v>
       </c>
       <c r="P999" t="n">
         <v>1500</v>
@@ -45053,10 +45053,10 @@
         <v>2</v>
       </c>
       <c r="N1014" t="n">
-        <v>2000.656035503</v>
+        <v>2000.6571856287</v>
       </c>
       <c r="O1014" t="n">
-        <v>4001.312071006</v>
+        <v>4001.3143712574</v>
       </c>
       <c r="P1014" t="n">
         <v>2000</v>
@@ -45432,10 +45432,10 @@
         <v>215</v>
       </c>
       <c r="N1022" t="n">
-        <v>7046.9398305803</v>
+        <v>7046.9398302567</v>
       </c>
       <c r="O1022" t="n">
-        <v>1515092.063574764</v>
+        <v>1515092.06350519</v>
       </c>
       <c r="P1022" t="n">
         <v>9900</v>
@@ -45472,22 +45472,22 @@
         <v>0</v>
       </c>
       <c r="L1023" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1023" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N1023" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1023" t="n">
-        <v>1898400.66</v>
+        <v>1825385.25</v>
       </c>
       <c r="P1023" t="n">
         <v>27900</v>
       </c>
       <c r="Q1023" t="n">
-        <v>2176200</v>
+        <v>2092500</v>
       </c>
     </row>
     <row r="1024">
@@ -45791,22 +45791,22 @@
         <v>0</v>
       </c>
       <c r="L1030" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1030" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N1030" t="n">
         <v>1338.14</v>
       </c>
       <c r="O1030" t="n">
-        <v>137828.42</v>
+        <v>136490.28</v>
       </c>
       <c r="P1030" t="n">
         <v>2500</v>
       </c>
       <c r="Q1030" t="n">
-        <v>257500</v>
+        <v>255000</v>
       </c>
     </row>
     <row r="1031">
@@ -46085,22 +46085,22 @@
         <v>0</v>
       </c>
       <c r="L1036" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1036" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N1036" t="n">
         <v>2010.71</v>
       </c>
       <c r="O1036" t="n">
-        <v>36192.78</v>
+        <v>32171.36</v>
       </c>
       <c r="P1036" t="n">
         <v>7200</v>
       </c>
       <c r="Q1036" t="n">
-        <v>129600</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="1037">
@@ -46574,22 +46574,22 @@
         <v>0</v>
       </c>
       <c r="L1047" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1047" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N1047" t="n">
         <v>2459</v>
       </c>
       <c r="O1047" t="n">
-        <v>206556</v>
+        <v>186884</v>
       </c>
       <c r="P1047" t="n">
         <v>3900</v>
       </c>
       <c r="Q1047" t="n">
-        <v>327600</v>
+        <v>296400</v>
       </c>
     </row>
     <row r="1048">
@@ -46914,22 +46914,22 @@
         <v>0</v>
       </c>
       <c r="L1055" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1055" t="n">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N1055" t="n">
         <v>6761.25</v>
       </c>
       <c r="O1055" t="n">
-        <v>3549656.25</v>
+        <v>3536133.75</v>
       </c>
       <c r="P1055" t="n">
         <v>5200</v>
       </c>
       <c r="Q1055" t="n">
-        <v>2730000</v>
+        <v>2719600</v>
       </c>
     </row>
     <row r="1056">
@@ -47989,22 +47989,22 @@
         <v>0</v>
       </c>
       <c r="L1080" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M1080" t="n">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="N1080" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1080" t="n">
-        <v>986389</v>
+        <v>929114.8</v>
       </c>
       <c r="P1080" t="n">
         <v>5100</v>
       </c>
       <c r="Q1080" t="n">
-        <v>1581000</v>
+        <v>1489200</v>
       </c>
     </row>
     <row r="1081">
@@ -48036,10 +48036,10 @@
         <v>3</v>
       </c>
       <c r="N1081" t="n">
-        <v>1213.6821153846</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O1081" t="n">
-        <v>3641.0463461538</v>
+        <v>3641.0463583815</v>
       </c>
       <c r="P1081" t="n">
         <v>1500</v>
@@ -48473,10 +48473,10 @@
         <v>41</v>
       </c>
       <c r="N1091" t="n">
-        <v>2523.3377514793</v>
+        <v>2523.3377476715</v>
       </c>
       <c r="O1091" t="n">
-        <v>103456.8478106513</v>
+        <v>103456.8476545315</v>
       </c>
       <c r="P1091" t="n">
         <v>2800</v>
@@ -49143,22 +49143,22 @@
         <v>0</v>
       </c>
       <c r="L1107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1107" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N1107" t="n">
         <v>5077</v>
       </c>
       <c r="O1107" t="n">
-        <v>797089</v>
+        <v>781858</v>
       </c>
       <c r="P1107" t="n">
         <v>8500</v>
       </c>
       <c r="Q1107" t="n">
-        <v>1334500</v>
+        <v>1309000</v>
       </c>
     </row>
     <row r="1108">
@@ -49317,22 +49317,22 @@
         <v>0</v>
       </c>
       <c r="L1111" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1111" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N1111" t="n">
-        <v>4985.4045627376</v>
+        <v>4985.4046332046</v>
       </c>
       <c r="O1111" t="n">
-        <v>209386.9916349792</v>
+        <v>189445.3760617748</v>
       </c>
       <c r="P1111" t="n">
         <v>7900</v>
       </c>
       <c r="Q1111" t="n">
-        <v>331800</v>
+        <v>300200</v>
       </c>
     </row>
     <row r="1112">
@@ -49374,10 +49374,10 @@
         <v>69</v>
       </c>
       <c r="N1112" t="n">
-        <v>1757.320515873</v>
+        <v>1757.3205179283</v>
       </c>
       <c r="O1112" t="n">
-        <v>121255.115595237</v>
+        <v>121255.1157370527</v>
       </c>
       <c r="P1112" t="n">
         <v>2000</v>
@@ -50043,22 +50043,22 @@
         <v>0</v>
       </c>
       <c r="L1127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N1127" t="n">
         <v>9450</v>
       </c>
       <c r="O1127" t="n">
-        <v>37800</v>
+        <v>28350</v>
       </c>
       <c r="P1127" t="n">
         <v>11900</v>
       </c>
       <c r="Q1127" t="n">
-        <v>47600</v>
+        <v>35700</v>
       </c>
     </row>
     <row r="1128">
@@ -50411,22 +50411,22 @@
         <v>0</v>
       </c>
       <c r="L1135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1135" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N1135" t="n">
         <v>17500</v>
       </c>
       <c r="O1135" t="n">
-        <v>227500</v>
+        <v>210000</v>
       </c>
       <c r="P1135" t="n">
         <v>21000</v>
       </c>
       <c r="Q1135" t="n">
-        <v>273000</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="1136">
@@ -50641,22 +50641,22 @@
         <v>0</v>
       </c>
       <c r="L1140" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1140" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N1140" t="n">
         <v>1000</v>
       </c>
       <c r="O1140" t="n">
-        <v>35000</v>
+        <v>29000</v>
       </c>
       <c r="P1140" t="n">
         <v>1200</v>
       </c>
       <c r="Q1140" t="n">
-        <v>42000</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="1141">
@@ -50733,22 +50733,22 @@
         <v>0</v>
       </c>
       <c r="L1142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N1142" t="n">
         <v>9300</v>
       </c>
       <c r="O1142" t="n">
-        <v>74400</v>
+        <v>65100</v>
       </c>
       <c r="P1142" t="n">
         <v>11200</v>
       </c>
       <c r="Q1142" t="n">
-        <v>89600</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="1143">
@@ -51193,22 +51193,22 @@
         <v>0</v>
       </c>
       <c r="L1152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1152" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N1152" t="n">
         <v>2400</v>
       </c>
       <c r="O1152" t="n">
-        <v>57600</v>
+        <v>55200</v>
       </c>
       <c r="P1152" t="n">
         <v>2900</v>
       </c>
       <c r="Q1152" t="n">
-        <v>69600</v>
+        <v>66700</v>
       </c>
     </row>
     <row r="1153">
@@ -52374,22 +52374,22 @@
         <v>0</v>
       </c>
       <c r="L1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1178" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N1178" t="n">
         <v>2200</v>
       </c>
       <c r="O1178" t="n">
-        <v>156200</v>
+        <v>154000</v>
       </c>
       <c r="P1178" t="n">
         <v>2700</v>
       </c>
       <c r="Q1178" t="n">
-        <v>191700</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="1179">
@@ -52645,22 +52645,22 @@
         <v>0</v>
       </c>
       <c r="L1184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1184" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N1184" t="n">
         <v>4550</v>
       </c>
       <c r="O1184" t="n">
-        <v>1510600</v>
+        <v>1496950</v>
       </c>
       <c r="P1184" t="n">
         <v>6500</v>
       </c>
       <c r="Q1184" t="n">
-        <v>2158000</v>
+        <v>2138500</v>
       </c>
     </row>
     <row r="1185">
@@ -52911,22 +52911,22 @@
         <v>0</v>
       </c>
       <c r="L1190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1190" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N1190" t="n">
         <v>8746.92</v>
       </c>
       <c r="O1190" t="n">
-        <v>104963.04</v>
+        <v>96216.12</v>
       </c>
       <c r="P1190" t="n">
         <v>11000</v>
       </c>
       <c r="Q1190" t="n">
-        <v>132000</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="1191">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
         </is>
       </c>
     </row>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>6</v>
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>71</v>
@@ -2758,13 +2758,13 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>2</v>
@@ -2961,13 +2961,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>19</v>
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>46</v>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>100</v>
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>10</v>
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>73</v>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
         <v>19</v>
@@ -6083,13 +6083,13 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
         <v>6</v>
@@ -7012,13 +7012,13 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
         <v>6</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
         <v>5</v>
@@ -8671,13 +8671,13 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
         <v>21</v>
@@ -9961,13 +9961,13 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>1552</v>
+        <v>1526</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
         <v>1526</v>
@@ -10263,13 +10263,13 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
         <v>11</v>
@@ -10553,13 +10553,13 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
         <v>824</v>
@@ -11663,13 +11663,13 @@
         </is>
       </c>
       <c r="J266" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
         <v>65</v>
@@ -12273,13 +12273,13 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
         <v>259</v>
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
         <v>68</v>
@@ -12800,13 +12800,13 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
         <v>102</v>
@@ -13028,13 +13028,13 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>349</v>
+        <v>309</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
         <v>309</v>
@@ -13348,13 +13348,13 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M304" t="n">
         <v>101</v>
@@ -13663,13 +13663,13 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M311" t="n">
         <v>280</v>
@@ -13842,13 +13842,13 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
         <v>73</v>
@@ -13937,13 +13937,13 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>710</v>
+        <v>677</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M317" t="n">
         <v>677</v>
@@ -14290,13 +14290,13 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M325" t="n">
         <v>58</v>
@@ -14382,13 +14382,13 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M327" t="n">
         <v>44</v>
@@ -14469,13 +14469,13 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M329" t="n">
         <v>26</v>
@@ -14682,13 +14682,13 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
       </c>
       <c r="L334" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M334" t="n">
         <v>78</v>
@@ -14851,13 +14851,13 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
         <v>248</v>
@@ -15031,13 +15031,13 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>115</v>
+        <v>420</v>
       </c>
       <c r="K342" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M342" t="n">
         <v>420</v>
@@ -15253,13 +15253,13 @@
         </is>
       </c>
       <c r="J347" t="n">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="K347" t="n">
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M347" t="n">
         <v>235</v>
@@ -15338,13 +15338,13 @@
         </is>
       </c>
       <c r="J349" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K349" t="n">
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M349" t="n">
         <v>14</v>
@@ -15428,13 +15428,13 @@
         </is>
       </c>
       <c r="J351" t="n">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M351" t="n">
         <v>431</v>
@@ -15469,13 +15469,13 @@
         </is>
       </c>
       <c r="J352" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M352" t="n">
         <v>121</v>
@@ -15649,13 +15649,13 @@
         </is>
       </c>
       <c r="J356" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="K356" t="n">
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M356" t="n">
         <v>49</v>
@@ -15823,13 +15823,13 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M360" t="n">
         <v>121</v>
@@ -16172,13 +16172,13 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M368" t="n">
         <v>30</v>
@@ -16218,13 +16218,13 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M369" t="n">
         <v>101</v>
@@ -16267,13 +16267,13 @@
         </is>
       </c>
       <c r="J370" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K370" t="n">
         <v>0</v>
       </c>
       <c r="L370" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M370" t="n">
         <v>351</v>
@@ -16701,13 +16701,13 @@
         </is>
       </c>
       <c r="J380" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K380" t="n">
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M380" t="n">
         <v>44</v>
@@ -16745,13 +16745,13 @@
         </is>
       </c>
       <c r="J381" t="n">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="K381" t="n">
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M381" t="n">
         <v>309</v>
@@ -16871,13 +16871,13 @@
         </is>
       </c>
       <c r="J384" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K384" t="n">
         <v>0</v>
       </c>
       <c r="L384" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M384" t="n">
         <v>180</v>
@@ -16915,13 +16915,13 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M385" t="n">
         <v>37</v>
@@ -17008,13 +17008,13 @@
         </is>
       </c>
       <c r="J387" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K387" t="n">
         <v>0</v>
       </c>
       <c r="L387" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M387" t="n">
         <v>105</v>
@@ -17194,13 +17194,13 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
       </c>
       <c r="L391" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M391" t="n">
         <v>25</v>
@@ -17330,13 +17330,13 @@
         </is>
       </c>
       <c r="J394" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K394" t="n">
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M394" t="n">
         <v>151</v>
@@ -17670,13 +17670,13 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M402" t="n">
         <v>921</v>
@@ -17719,13 +17719,13 @@
         </is>
       </c>
       <c r="J403" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K403" t="n">
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M403" t="n">
         <v>68</v>
@@ -17811,13 +17811,13 @@
         </is>
       </c>
       <c r="J405" t="n">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="K405" t="n">
         <v>0</v>
       </c>
       <c r="L405" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M405" t="n">
         <v>890</v>
@@ -17944,13 +17944,13 @@
         </is>
       </c>
       <c r="J408" t="n">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="K408" t="n">
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M408" t="n">
         <v>103</v>
@@ -17990,13 +17990,13 @@
         </is>
       </c>
       <c r="J409" t="n">
-        <v>2269</v>
+        <v>2253</v>
       </c>
       <c r="K409" t="n">
         <v>0</v>
       </c>
       <c r="L409" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M409" t="n">
         <v>2253</v>
@@ -18128,13 +18128,13 @@
         </is>
       </c>
       <c r="J412" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K412" t="n">
         <v>0</v>
       </c>
       <c r="L412" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M412" t="n">
         <v>88</v>
@@ -21819,13 +21819,13 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
       </c>
       <c r="L498" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M498" t="n">
         <v>73</v>
@@ -22688,13 +22688,13 @@
         </is>
       </c>
       <c r="J519" t="n">
-        <v>1412</v>
+        <v>1382</v>
       </c>
       <c r="K519" t="n">
         <v>0</v>
       </c>
       <c r="L519" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M519" t="n">
         <v>1382</v>
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="J528" t="n">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
       </c>
       <c r="L528" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M528" t="n">
         <v>177</v>
@@ -23241,13 +23241,13 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M532" t="n">
         <v>23</v>
@@ -23764,13 +23764,13 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M544" t="n">
         <v>220</v>
@@ -24353,13 +24353,13 @@
         </is>
       </c>
       <c r="J558" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
       </c>
       <c r="L558" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M558" t="n">
         <v>16</v>
@@ -24532,13 +24532,13 @@
         </is>
       </c>
       <c r="J562" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K562" t="n">
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M562" t="n">
         <v>60</v>
@@ -25648,13 +25648,13 @@
         </is>
       </c>
       <c r="J588" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K588" t="n">
         <v>0</v>
       </c>
       <c r="L588" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M588" t="n">
         <v>27</v>
@@ -25832,13 +25832,13 @@
         </is>
       </c>
       <c r="J592" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K592" t="n">
         <v>0</v>
       </c>
       <c r="L592" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M592" t="n">
         <v>41</v>
@@ -26175,13 +26175,13 @@
         </is>
       </c>
       <c r="J600" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="K600" t="n">
         <v>0</v>
       </c>
       <c r="L600" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M600" t="n">
         <v>149</v>
@@ -26308,13 +26308,13 @@
         </is>
       </c>
       <c r="J603" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K603" t="n">
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M603" t="n">
         <v>39</v>
@@ -26736,13 +26736,13 @@
         </is>
       </c>
       <c r="J613" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K613" t="n">
         <v>0</v>
       </c>
       <c r="L613" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M613" t="n">
         <v>8</v>
@@ -27989,13 +27989,13 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="K642" t="n">
         <v>0</v>
       </c>
       <c r="L642" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M642" t="n">
         <v>36</v>
@@ -28035,13 +28035,13 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
       </c>
       <c r="L643" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M643" t="n">
         <v>71</v>
@@ -28081,13 +28081,13 @@
         </is>
       </c>
       <c r="J644" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K644" t="n">
         <v>0</v>
       </c>
       <c r="L644" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M644" t="n">
         <v>19</v>
@@ -28265,13 +28265,13 @@
         </is>
       </c>
       <c r="J648" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K648" t="n">
         <v>0</v>
       </c>
       <c r="L648" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M648" t="n">
         <v>24</v>
@@ -28357,13 +28357,13 @@
         </is>
       </c>
       <c r="J650" t="n">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="K650" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L650" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M650" t="n">
         <v>83</v>
@@ -28679,13 +28679,13 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M657" t="n">
         <v>32</v>
@@ -28771,13 +28771,13 @@
         </is>
       </c>
       <c r="J659" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K659" t="n">
         <v>0</v>
       </c>
       <c r="L659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M659" t="n">
         <v>431</v>
@@ -28863,13 +28863,13 @@
         </is>
       </c>
       <c r="J661" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K661" t="n">
         <v>0</v>
       </c>
       <c r="L661" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M661" t="n">
         <v>45</v>
@@ -29329,13 +29329,13 @@
         </is>
       </c>
       <c r="J671" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="K671" t="n">
         <v>0</v>
       </c>
       <c r="L671" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M671" t="n">
         <v>144</v>
@@ -29467,13 +29467,13 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>1581</v>
+        <v>1573</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M674" t="n">
         <v>1573</v>
@@ -30523,13 +30523,13 @@
         </is>
       </c>
       <c r="J697" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K697" t="n">
         <v>0</v>
       </c>
       <c r="L697" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M697" t="n">
         <v>164</v>
@@ -31405,13 +31405,13 @@
         </is>
       </c>
       <c r="J716" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K716" t="n">
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M716" t="n">
         <v>21</v>
@@ -31635,13 +31635,13 @@
         </is>
       </c>
       <c r="J721" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K721" t="n">
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M721" t="n">
         <v>191</v>
@@ -31727,13 +31727,13 @@
         </is>
       </c>
       <c r="J723" t="n">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K723" t="n">
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M723" t="n">
         <v>287</v>
@@ -33565,13 +33565,13 @@
         </is>
       </c>
       <c r="J763" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K763" t="n">
         <v>0</v>
       </c>
       <c r="L763" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M763" t="n">
         <v>120</v>
@@ -33698,13 +33698,13 @@
         </is>
       </c>
       <c r="J766" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K766" t="n">
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M766" t="n">
         <v>60</v>
@@ -33928,13 +33928,13 @@
         </is>
       </c>
       <c r="J771" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K771" t="n">
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M771" t="n">
         <v>64</v>
@@ -34158,13 +34158,13 @@
         </is>
       </c>
       <c r="J776" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K776" t="n">
         <v>0</v>
       </c>
       <c r="L776" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M776" t="n">
         <v>278</v>
@@ -34204,13 +34204,13 @@
         </is>
       </c>
       <c r="J777" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K777" t="n">
         <v>0</v>
       </c>
       <c r="L777" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M777" t="n">
         <v>123</v>
@@ -34296,13 +34296,13 @@
         </is>
       </c>
       <c r="J779" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K779" t="n">
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M779" t="n">
         <v>162</v>
@@ -34342,13 +34342,13 @@
         </is>
       </c>
       <c r="J780" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K780" t="n">
         <v>0</v>
       </c>
       <c r="L780" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M780" t="n">
         <v>121</v>
@@ -34434,13 +34434,13 @@
         </is>
       </c>
       <c r="J782" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K782" t="n">
         <v>0</v>
       </c>
       <c r="L782" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M782" t="n">
         <v>250</v>
@@ -34618,13 +34618,13 @@
         </is>
       </c>
       <c r="J786" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K786" t="n">
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M786" t="n">
         <v>72</v>
@@ -34989,13 +34989,13 @@
         </is>
       </c>
       <c r="J794" t="n">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="K794" t="n">
         <v>0</v>
       </c>
       <c r="L794" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M794" t="n">
         <v>775</v>
@@ -35677,13 +35677,13 @@
         </is>
       </c>
       <c r="J809" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="K809" t="n">
         <v>0</v>
       </c>
       <c r="L809" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M809" t="n">
         <v>46</v>
@@ -35907,13 +35907,13 @@
         </is>
       </c>
       <c r="J814" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K814" t="n">
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M814" t="n">
         <v>98</v>
@@ -36137,13 +36137,13 @@
         </is>
       </c>
       <c r="J819" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K819" t="n">
         <v>0</v>
       </c>
       <c r="L819" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M819" t="n">
         <v>54</v>
@@ -36321,13 +36321,13 @@
         </is>
       </c>
       <c r="J823" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K823" t="n">
         <v>0</v>
       </c>
       <c r="L823" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M823" t="n">
         <v>160</v>
@@ -36689,13 +36689,13 @@
         </is>
       </c>
       <c r="J831" t="n">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K831" t="n">
         <v>0</v>
       </c>
       <c r="L831" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M831" t="n">
         <v>461</v>
@@ -36876,13 +36876,13 @@
         </is>
       </c>
       <c r="J835" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K835" t="n">
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M835" t="n">
         <v>26</v>
@@ -36922,13 +36922,13 @@
         </is>
       </c>
       <c r="J836" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K836" t="n">
         <v>0</v>
       </c>
       <c r="L836" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M836" t="n">
         <v>8</v>
@@ -37014,13 +37014,13 @@
         </is>
       </c>
       <c r="J838" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K838" t="n">
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M838" t="n">
         <v>171</v>
@@ -37518,13 +37518,13 @@
         </is>
       </c>
       <c r="J849" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="K849" t="n">
         <v>0</v>
       </c>
       <c r="L849" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M849" t="n">
         <v>257</v>
@@ -37613,13 +37613,13 @@
         </is>
       </c>
       <c r="J851" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K851" t="n">
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M851" t="n">
         <v>9</v>
@@ -37935,13 +37935,13 @@
         </is>
       </c>
       <c r="J858" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="K858" t="n">
         <v>0</v>
       </c>
       <c r="L858" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M858" t="n">
         <v>156</v>
@@ -38163,13 +38163,13 @@
         </is>
       </c>
       <c r="J863" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K863" t="n">
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M863" t="n">
         <v>5</v>
@@ -38209,13 +38209,13 @@
         </is>
       </c>
       <c r="J864" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K864" t="n">
         <v>0</v>
       </c>
       <c r="L864" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M864" t="n">
         <v>75</v>
@@ -38255,13 +38255,13 @@
         </is>
       </c>
       <c r="J865" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="K865" t="n">
         <v>0</v>
       </c>
       <c r="L865" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M865" t="n">
         <v>284</v>
@@ -38347,13 +38347,13 @@
         </is>
       </c>
       <c r="J867" t="n">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="K867" t="n">
         <v>0</v>
       </c>
       <c r="L867" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M867" t="n">
         <v>409</v>
@@ -39179,13 +39179,13 @@
         </is>
       </c>
       <c r="J885" t="n">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="K885" t="n">
         <v>0</v>
       </c>
       <c r="L885" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M885" t="n">
         <v>306</v>
@@ -39271,13 +39271,13 @@
         </is>
       </c>
       <c r="J887" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K887" t="n">
         <v>0</v>
       </c>
       <c r="L887" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M887" t="n">
         <v>-1</v>
@@ -39818,13 +39818,13 @@
         </is>
       </c>
       <c r="J899" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K899" t="n">
         <v>0</v>
       </c>
       <c r="L899" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M899" t="n">
         <v>52</v>
@@ -40093,13 +40093,13 @@
         </is>
       </c>
       <c r="J905" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K905" t="n">
         <v>0</v>
       </c>
       <c r="L905" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M905" t="n">
         <v>25</v>
@@ -40460,13 +40460,13 @@
         </is>
       </c>
       <c r="J913" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="K913" t="n">
         <v>0</v>
       </c>
       <c r="L913" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M913" t="n">
         <v>136</v>
@@ -40588,13 +40588,13 @@
         </is>
       </c>
       <c r="J916" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K916" t="n">
         <v>0</v>
       </c>
       <c r="L916" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M916" t="n">
         <v>116</v>
@@ -41116,13 +41116,13 @@
         </is>
       </c>
       <c r="J928" t="n">
-        <v>1418</v>
+        <v>1238</v>
       </c>
       <c r="K928" t="n">
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M928" t="n">
         <v>1238</v>
@@ -41426,13 +41426,13 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>3817</v>
+        <v>3745</v>
       </c>
       <c r="K935" t="n">
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M935" t="n">
         <v>3745</v>
@@ -41652,13 +41652,13 @@
         </is>
       </c>
       <c r="J940" t="n">
-        <v>854</v>
+        <v>828</v>
       </c>
       <c r="K940" t="n">
         <v>0</v>
       </c>
       <c r="L940" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M940" t="n">
         <v>828</v>
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="J945" t="n">
-        <v>1829</v>
+        <v>1685</v>
       </c>
       <c r="K945" t="n">
         <v>0</v>
       </c>
       <c r="L945" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M945" t="n">
         <v>1685</v>
@@ -42057,13 +42057,13 @@
         </is>
       </c>
       <c r="J949" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K949" t="n">
         <v>0</v>
       </c>
       <c r="L949" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M949" t="n">
         <v>70</v>
@@ -42458,13 +42458,13 @@
         </is>
       </c>
       <c r="J958" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K958" t="n">
         <v>0</v>
       </c>
       <c r="L958" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M958" t="n">
         <v>158</v>
@@ -42502,13 +42502,13 @@
         </is>
       </c>
       <c r="J959" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K959" t="n">
         <v>0</v>
       </c>
       <c r="L959" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M959" t="n">
         <v>79</v>
@@ -45466,13 +45466,13 @@
         </is>
       </c>
       <c r="J1023" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K1023" t="n">
         <v>0</v>
       </c>
       <c r="L1023" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1023" t="n">
         <v>75</v>
@@ -45785,13 +45785,13 @@
         </is>
       </c>
       <c r="J1030" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K1030" t="n">
         <v>0</v>
       </c>
       <c r="L1030" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1030" t="n">
         <v>102</v>
@@ -46079,13 +46079,13 @@
         </is>
       </c>
       <c r="J1036" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K1036" t="n">
         <v>0</v>
       </c>
       <c r="L1036" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1036" t="n">
         <v>16</v>
@@ -46568,13 +46568,13 @@
         </is>
       </c>
       <c r="J1047" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="K1047" t="n">
         <v>0</v>
       </c>
       <c r="L1047" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M1047" t="n">
         <v>76</v>
@@ -46908,13 +46908,13 @@
         </is>
       </c>
       <c r="J1055" t="n">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="K1055" t="n">
         <v>0</v>
       </c>
       <c r="L1055" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1055" t="n">
         <v>523</v>
@@ -47983,13 +47983,13 @@
         </is>
       </c>
       <c r="J1080" t="n">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="K1080" t="n">
         <v>0</v>
       </c>
       <c r="L1080" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M1080" t="n">
         <v>292</v>
@@ -49137,13 +49137,13 @@
         </is>
       </c>
       <c r="J1107" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K1107" t="n">
         <v>0</v>
       </c>
       <c r="L1107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1107" t="n">
         <v>154</v>
@@ -49311,13 +49311,13 @@
         </is>
       </c>
       <c r="J1111" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K1111" t="n">
         <v>0</v>
       </c>
       <c r="L1111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1111" t="n">
         <v>38</v>
@@ -50037,13 +50037,13 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
       </c>
       <c r="L1127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1127" t="n">
         <v>3</v>
@@ -50405,13 +50405,13 @@
         </is>
       </c>
       <c r="J1135" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K1135" t="n">
         <v>0</v>
       </c>
       <c r="L1135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1135" t="n">
         <v>12</v>
@@ -50635,13 +50635,13 @@
         </is>
       </c>
       <c r="J1140" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K1140" t="n">
         <v>0</v>
       </c>
       <c r="L1140" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1140" t="n">
         <v>29</v>
@@ -50727,13 +50727,13 @@
         </is>
       </c>
       <c r="J1142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K1142" t="n">
         <v>0</v>
       </c>
       <c r="L1142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1142" t="n">
         <v>7</v>
@@ -51187,13 +51187,13 @@
         </is>
       </c>
       <c r="J1152" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K1152" t="n">
         <v>0</v>
       </c>
       <c r="L1152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1152" t="n">
         <v>23</v>
@@ -52368,13 +52368,13 @@
         </is>
       </c>
       <c r="J1178" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K1178" t="n">
         <v>0</v>
       </c>
       <c r="L1178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1178" t="n">
         <v>70</v>
@@ -52639,13 +52639,13 @@
         </is>
       </c>
       <c r="J1184" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="K1184" t="n">
         <v>0</v>
       </c>
       <c r="L1184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1184" t="n">
         <v>329</v>
@@ -52905,13 +52905,13 @@
         </is>
       </c>
       <c r="J1190" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K1190" t="n">
         <v>0</v>
       </c>
       <c r="L1190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1190" t="n">
         <v>11</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -691,10 +691,10 @@
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>96741.407307692</v>
+        <v>96741.407402597</v>
       </c>
       <c r="O7" t="n">
-        <v>290224.221923076</v>
+        <v>290224.222207791</v>
       </c>
       <c r="P7" t="n">
         <v>188900</v>
@@ -1348,22 +1348,22 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M23" t="n">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="N23" t="n">
-        <v>1811.3041548631</v>
+        <v>1811.3043052838</v>
       </c>
       <c r="O23" t="n">
-        <v>414788.6514636499</v>
+        <v>382185.2084148818</v>
       </c>
       <c r="P23" t="n">
         <v>2600</v>
       </c>
       <c r="Q23" t="n">
-        <v>595400</v>
+        <v>548600</v>
       </c>
     </row>
     <row r="24">
@@ -1465,22 +1465,22 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="N26" t="n">
-        <v>3376.7465109371</v>
+        <v>3376.7465014893</v>
       </c>
       <c r="O26" t="n">
-        <v>222865.2697218486</v>
+        <v>189097.8040834008</v>
       </c>
       <c r="P26" t="n">
         <v>4500</v>
       </c>
       <c r="Q26" t="n">
-        <v>297000</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="27">
@@ -2717,22 +2717,22 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
         <v>35831.14</v>
       </c>
       <c r="O57" t="n">
-        <v>71662.28</v>
+        <v>35831.14</v>
       </c>
       <c r="P57" t="n">
         <v>62900</v>
       </c>
       <c r="Q57" t="n">
-        <v>125800</v>
+        <v>62900</v>
       </c>
     </row>
     <row r="58">
@@ -2756,22 +2756,22 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M58" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="N58" t="n">
         <v>4604.2</v>
       </c>
       <c r="O58" t="n">
-        <v>221001.6</v>
+        <v>174959.6</v>
       </c>
       <c r="P58" t="n">
         <v>7500</v>
       </c>
       <c r="Q58" t="n">
-        <v>360000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="59">
@@ -2920,22 +2920,22 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M62" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="N62" t="n">
         <v>3585</v>
       </c>
       <c r="O62" t="n">
-        <v>326235</v>
+        <v>308310</v>
       </c>
       <c r="P62" t="n">
         <v>4500</v>
       </c>
       <c r="Q62" t="n">
-        <v>409500</v>
+        <v>387000</v>
       </c>
     </row>
     <row r="63">
@@ -2965,10 +2965,10 @@
         <v>41</v>
       </c>
       <c r="N63" t="n">
-        <v>6272.8542666667</v>
+        <v>6272.8544651163</v>
       </c>
       <c r="O63" t="n">
-        <v>257187.0249333347</v>
+        <v>257187.0330697683</v>
       </c>
       <c r="P63" t="n">
         <v>7900</v>
@@ -3288,10 +3288,10 @@
         <v>205</v>
       </c>
       <c r="N71" t="n">
-        <v>2413.0010330579</v>
+        <v>2413.001059322</v>
       </c>
       <c r="O71" t="n">
-        <v>494665.2117768695</v>
+        <v>494665.21716101</v>
       </c>
       <c r="P71" t="n">
         <v>4700</v>
@@ -3867,22 +3867,22 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N86" t="n">
-        <v>14857.623171806</v>
+        <v>14857.623185841</v>
       </c>
       <c r="O86" t="n">
-        <v>371440.57929515</v>
+        <v>356582.956460184</v>
       </c>
       <c r="P86" t="n">
         <v>34900</v>
       </c>
       <c r="Q86" t="n">
-        <v>872500</v>
+        <v>837600</v>
       </c>
     </row>
     <row r="87">
@@ -3953,22 +3953,22 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N88" t="n">
         <v>10439</v>
       </c>
       <c r="O88" t="n">
-        <v>156585</v>
+        <v>146146</v>
       </c>
       <c r="P88" t="n">
         <v>16900</v>
       </c>
       <c r="Q88" t="n">
-        <v>253500</v>
+        <v>236600</v>
       </c>
     </row>
     <row r="89">
@@ -4181,10 +4181,10 @@
         <v>60</v>
       </c>
       <c r="N93" t="n">
-        <v>3910.628245614</v>
+        <v>3910.6282352941</v>
       </c>
       <c r="O93" t="n">
-        <v>234637.69473684</v>
+        <v>234637.694117646</v>
       </c>
       <c r="P93" t="n">
         <v>9100</v>
@@ -4990,10 +4990,10 @@
         <v>5</v>
       </c>
       <c r="N111" t="n">
-        <v>5059.5844444444</v>
+        <v>5059.58125</v>
       </c>
       <c r="O111" t="n">
-        <v>25297.922222222</v>
+        <v>25297.90625</v>
       </c>
       <c r="P111" t="n">
         <v>10000</v>
@@ -5062,25 +5062,25 @@
         <v>8</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="N113" t="n">
         <v>36762.36</v>
       </c>
       <c r="O113" t="n">
-        <v>294098.88</v>
+        <v>735247.2</v>
       </c>
       <c r="P113" t="n">
         <v>57100</v>
       </c>
       <c r="Q113" t="n">
-        <v>456800</v>
+        <v>1142000</v>
       </c>
     </row>
     <row r="114">
@@ -5104,25 +5104,25 @@
         <v>7</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="N114" t="n">
-        <v>15711.966106557</v>
+        <v>15711.966058091</v>
       </c>
       <c r="O114" t="n">
-        <v>109983.762745899</v>
+        <v>471358.98174273</v>
       </c>
       <c r="P114" t="n">
         <v>28500</v>
       </c>
       <c r="Q114" t="n">
-        <v>199500</v>
+        <v>855000</v>
       </c>
     </row>
     <row r="115">
@@ -5160,10 +5160,10 @@
         <v>11</v>
       </c>
       <c r="N115" t="n">
-        <v>9392.0745945946</v>
+        <v>9392.0746575342</v>
       </c>
       <c r="O115" t="n">
-        <v>103312.8205405406</v>
+        <v>103312.8212328762</v>
       </c>
       <c r="P115" t="n">
         <v>18500</v>
@@ -5284,25 +5284,25 @@
         <v>41</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="N118" t="n">
         <v>7407.7300524934</v>
       </c>
       <c r="O118" t="n">
-        <v>303716.9321522294</v>
+        <v>659287.9746719126</v>
       </c>
       <c r="P118" t="n">
         <v>10900</v>
       </c>
       <c r="Q118" t="n">
-        <v>446900</v>
+        <v>970100</v>
       </c>
     </row>
     <row r="119">
@@ -5997,25 +5997,25 @@
         <v>5</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M135" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N135" t="n">
-        <v>36306.281111111</v>
+        <v>36306.306666667</v>
       </c>
       <c r="O135" t="n">
-        <v>181531.405555555</v>
+        <v>399369.373333337</v>
       </c>
       <c r="P135" t="n">
         <v>64900</v>
       </c>
       <c r="Q135" t="n">
-        <v>324500</v>
+        <v>713900</v>
       </c>
     </row>
     <row r="136">
@@ -6044,25 +6044,25 @@
         <v>8</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M136" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N136" t="n">
-        <v>56906.800571429</v>
+        <v>56906.801935484</v>
       </c>
       <c r="O136" t="n">
-        <v>455254.404571432</v>
+        <v>227627.207741936</v>
       </c>
       <c r="P136" t="n">
         <v>95900</v>
       </c>
       <c r="Q136" t="n">
-        <v>767200</v>
+        <v>383600</v>
       </c>
     </row>
     <row r="137">
@@ -6188,22 +6188,22 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>141416.88453074</v>
+        <v>141416.88454545</v>
       </c>
       <c r="O139" t="n">
-        <v>282833.76906148</v>
+        <v>141416.88454545</v>
       </c>
       <c r="P139" t="n">
         <v>251900</v>
       </c>
       <c r="Q139" t="n">
-        <v>503800</v>
+        <v>251900</v>
       </c>
     </row>
     <row r="140">
@@ -7204,19 +7204,19 @@
         <v>4</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M163" t="n">
         <v>4</v>
       </c>
       <c r="N163" t="n">
-        <v>61666.873861893</v>
+        <v>61666.873932292</v>
       </c>
       <c r="O163" t="n">
-        <v>246667.495447572</v>
+        <v>246667.495729168</v>
       </c>
       <c r="P163" t="n">
         <v>98900</v>
@@ -7632,10 +7632,10 @@
         <v>5</v>
       </c>
       <c r="N172" t="n">
-        <v>408.26623529412</v>
+        <v>408.26614457831</v>
       </c>
       <c r="O172" t="n">
-        <v>2041.3311764706</v>
+        <v>2041.33072289155</v>
       </c>
       <c r="P172" t="n">
         <v>1600</v>
@@ -7848,22 +7848,22 @@
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N177" t="n">
         <v>24646.47</v>
       </c>
       <c r="O177" t="n">
-        <v>246464.7</v>
+        <v>221818.23</v>
       </c>
       <c r="P177" t="n">
         <v>43900</v>
       </c>
       <c r="Q177" t="n">
-        <v>439000</v>
+        <v>395100</v>
       </c>
     </row>
     <row r="178">
@@ -8223,22 +8223,22 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N186" t="n">
         <v>3865.67</v>
       </c>
       <c r="O186" t="n">
-        <v>711283.28</v>
+        <v>707417.61</v>
       </c>
       <c r="P186" t="n">
         <v>5500</v>
       </c>
       <c r="Q186" t="n">
-        <v>1012000</v>
+        <v>1006500</v>
       </c>
     </row>
     <row r="187">
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M187" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N187" t="n">
         <v>8046.39</v>
       </c>
       <c r="O187" t="n">
-        <v>289670.04</v>
+        <v>273577.26</v>
       </c>
       <c r="P187" t="n">
         <v>20900</v>
       </c>
       <c r="Q187" t="n">
-        <v>752400</v>
+        <v>710600</v>
       </c>
     </row>
     <row r="188">
@@ -8354,22 +8354,22 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M189" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N189" t="n">
         <v>6187.41</v>
       </c>
       <c r="O189" t="n">
-        <v>346494.96</v>
+        <v>334120.14</v>
       </c>
       <c r="P189" t="n">
         <v>11500</v>
       </c>
       <c r="Q189" t="n">
-        <v>644000</v>
+        <v>621000</v>
       </c>
     </row>
     <row r="190">
@@ -8400,22 +8400,22 @@
         <v>0</v>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M190" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N190" t="n">
         <v>5686.27</v>
       </c>
       <c r="O190" t="n">
-        <v>125097.94</v>
+        <v>113725.4</v>
       </c>
       <c r="P190" t="n">
         <v>11500</v>
       </c>
       <c r="Q190" t="n">
-        <v>253000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="191">
@@ -9756,22 +9756,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M221" t="n">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="N221" t="n">
-        <v>1950.2152424105</v>
+        <v>1950.2151724138</v>
       </c>
       <c r="O221" t="n">
-        <v>945854.3925690925</v>
+        <v>922451.7765517274</v>
       </c>
       <c r="P221" t="n">
         <v>2900</v>
       </c>
       <c r="Q221" t="n">
-        <v>1406500</v>
+        <v>1371700</v>
       </c>
     </row>
     <row r="222">
@@ -9920,22 +9920,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="N225" t="n">
         <v>1726.32</v>
       </c>
       <c r="O225" t="n">
-        <v>3388766.16</v>
+        <v>3387039.84</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
       </c>
       <c r="Q225" t="n">
-        <v>2944500</v>
+        <v>2943000</v>
       </c>
     </row>
     <row r="226">
@@ -10007,22 +10007,22 @@
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M227" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="N227" t="n">
-        <v>4937.3101603499</v>
+        <v>4937.3101608187</v>
       </c>
       <c r="O227" t="n">
-        <v>617163.7700437375</v>
+        <v>602351.8396198814</v>
       </c>
       <c r="P227" t="n">
         <v>7500</v>
       </c>
       <c r="Q227" t="n">
-        <v>937500</v>
+        <v>915000</v>
       </c>
     </row>
     <row r="228">
@@ -10130,22 +10130,22 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M230" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N230" t="n">
         <v>3456.13</v>
       </c>
       <c r="O230" t="n">
-        <v>535700.15</v>
+        <v>532244.02</v>
       </c>
       <c r="P230" t="n">
         <v>5700</v>
       </c>
       <c r="Q230" t="n">
-        <v>883500</v>
+        <v>877800</v>
       </c>
     </row>
     <row r="231">
@@ -10512,22 +10512,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M239" t="n">
-        <v>781</v>
+        <v>659</v>
       </c>
       <c r="N239" t="n">
-        <v>1098.0535004591</v>
+        <v>1098.0541801698</v>
       </c>
       <c r="O239" t="n">
-        <v>857579.7838585571</v>
+        <v>723617.7047318983</v>
       </c>
       <c r="P239" t="n">
         <v>1500</v>
       </c>
       <c r="Q239" t="n">
-        <v>1171500</v>
+        <v>988500</v>
       </c>
     </row>
     <row r="240">
@@ -11917,22 +11917,22 @@
         <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M272" t="n">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="N272" t="n">
         <v>2804.33</v>
       </c>
       <c r="O272" t="n">
-        <v>1662967.69</v>
+        <v>1629315.73</v>
       </c>
       <c r="P272" t="n">
         <v>4900</v>
       </c>
       <c r="Q272" t="n">
-        <v>2905700</v>
+        <v>2846900</v>
       </c>
     </row>
     <row r="273">
@@ -12227,22 +12227,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M279" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="N279" t="n">
         <v>3247</v>
       </c>
       <c r="O279" t="n">
-        <v>373405</v>
+        <v>347429</v>
       </c>
       <c r="P279" t="n">
         <v>5200</v>
       </c>
       <c r="Q279" t="n">
-        <v>598000</v>
+        <v>556400</v>
       </c>
     </row>
     <row r="280">
@@ -12273,22 +12273,22 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M280" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N280" t="n">
-        <v>2582.2560562265</v>
+        <v>2582.2560231583</v>
       </c>
       <c r="O280" t="n">
-        <v>653310.7822253044</v>
+        <v>637817.2377201001</v>
       </c>
       <c r="P280" t="n">
         <v>4500</v>
       </c>
       <c r="Q280" t="n">
-        <v>1138500</v>
+        <v>1111500</v>
       </c>
     </row>
     <row r="281">
@@ -12362,25 +12362,25 @@
         <v>87</v>
       </c>
       <c r="K282" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M282" t="n">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="N282" t="n">
-        <v>5216.8959875629</v>
+        <v>5216.8959762435</v>
       </c>
       <c r="O282" t="n">
-        <v>453869.9509179723</v>
+        <v>819052.6682702295</v>
       </c>
       <c r="P282" t="n">
         <v>8500</v>
       </c>
       <c r="Q282" t="n">
-        <v>739500</v>
+        <v>1334500</v>
       </c>
     </row>
     <row r="283">
@@ -12621,22 +12621,22 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M288" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N288" t="n">
         <v>6713.08</v>
       </c>
       <c r="O288" t="n">
-        <v>100696.2</v>
+        <v>67130.8</v>
       </c>
       <c r="P288" t="n">
         <v>9900</v>
       </c>
       <c r="Q288" t="n">
-        <v>148500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="289">
@@ -12667,22 +12667,22 @@
         <v>0</v>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M289" t="n">
-        <v>964</v>
+        <v>951</v>
       </c>
       <c r="N289" t="n">
-        <v>3158.860813875</v>
+        <v>3158.8608143857</v>
       </c>
       <c r="O289" t="n">
-        <v>3045141.8245755</v>
+        <v>3004076.6344808</v>
       </c>
       <c r="P289" t="n">
         <v>5600</v>
       </c>
       <c r="Q289" t="n">
-        <v>5398400</v>
+        <v>5325600</v>
       </c>
     </row>
     <row r="290">
@@ -12713,22 +12713,22 @@
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M290" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="N290" t="n">
         <v>1903</v>
       </c>
       <c r="O290" t="n">
-        <v>334928</v>
+        <v>323510</v>
       </c>
       <c r="P290" t="n">
         <v>3200</v>
       </c>
       <c r="Q290" t="n">
-        <v>563200</v>
+        <v>544000</v>
       </c>
     </row>
     <row r="291">
@@ -12805,22 +12805,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M292" t="n">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="N292" t="n">
         <v>5081</v>
       </c>
       <c r="O292" t="n">
-        <v>548748</v>
+        <v>467452</v>
       </c>
       <c r="P292" t="n">
         <v>8200</v>
       </c>
       <c r="Q292" t="n">
-        <v>885600</v>
+        <v>754400</v>
       </c>
     </row>
     <row r="293">
@@ -13074,22 +13074,22 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M298" t="n">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="N298" t="n">
         <v>1337.34</v>
       </c>
       <c r="O298" t="n">
-        <v>399864.66</v>
+        <v>391840.62</v>
       </c>
       <c r="P298" t="n">
         <v>2500</v>
       </c>
       <c r="Q298" t="n">
-        <v>747500</v>
+        <v>732500</v>
       </c>
     </row>
     <row r="299">
@@ -13120,22 +13120,22 @@
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M299" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N299" t="n">
-        <v>2694.8234682861</v>
+        <v>2694.8234624043</v>
       </c>
       <c r="O299" t="n">
-        <v>299125.4049797571</v>
+        <v>293735.7574020687</v>
       </c>
       <c r="P299" t="n">
         <v>4900</v>
       </c>
       <c r="Q299" t="n">
-        <v>543900</v>
+        <v>534100</v>
       </c>
     </row>
     <row r="300">
@@ -13207,22 +13207,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M301" t="n">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="N301" t="n">
-        <v>1026.13</v>
+        <v>1037.4476102941</v>
       </c>
       <c r="O301" t="n">
-        <v>696742.27</v>
+        <v>700277.1369485175</v>
       </c>
       <c r="P301" t="n">
         <v>1900</v>
       </c>
       <c r="Q301" t="n">
-        <v>1290100</v>
+        <v>1282500</v>
       </c>
     </row>
     <row r="302">
@@ -13299,22 +13299,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M303" t="n">
-        <v>5505</v>
+        <v>5495</v>
       </c>
       <c r="N303" t="n">
         <v>156.25</v>
       </c>
       <c r="O303" t="n">
-        <v>860156.25</v>
+        <v>858593.75</v>
       </c>
       <c r="P303" t="n">
         <v>250</v>
       </c>
       <c r="Q303" t="n">
-        <v>1376250</v>
+        <v>1373750</v>
       </c>
     </row>
     <row r="304">
@@ -13394,22 +13394,22 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M305" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N305" t="n">
         <v>8796</v>
       </c>
       <c r="O305" t="n">
-        <v>826824</v>
+        <v>791640</v>
       </c>
       <c r="P305" t="n">
         <v>14900</v>
       </c>
       <c r="Q305" t="n">
-        <v>1400600</v>
+        <v>1341000</v>
       </c>
     </row>
     <row r="306">
@@ -13709,22 +13709,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M312" t="n">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="N312" t="n">
         <v>4357.55</v>
       </c>
       <c r="O312" t="n">
-        <v>1211398.9</v>
+        <v>1172180.95</v>
       </c>
       <c r="P312" t="n">
         <v>7500</v>
       </c>
       <c r="Q312" t="n">
-        <v>2085000</v>
+        <v>2017500</v>
       </c>
     </row>
     <row r="313">
@@ -13755,22 +13755,22 @@
         <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M313" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N313" t="n">
         <v>2379.63</v>
       </c>
       <c r="O313" t="n">
-        <v>147537.06</v>
+        <v>138018.54</v>
       </c>
       <c r="P313" t="n">
         <v>4500</v>
       </c>
       <c r="Q313" t="n">
-        <v>279000</v>
+        <v>261000</v>
       </c>
     </row>
     <row r="314">
@@ -13842,22 +13842,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M315" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="N315" t="n">
-        <v>4890.9300461095</v>
+        <v>4890.9300462963</v>
       </c>
       <c r="O315" t="n">
-        <v>298346.7328126795</v>
+        <v>264110.2225000002</v>
       </c>
       <c r="P315" t="n">
         <v>8200</v>
       </c>
       <c r="Q315" t="n">
-        <v>500200</v>
+        <v>442800</v>
       </c>
     </row>
     <row r="316">
@@ -13937,22 +13937,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M317" t="n">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="N317" t="n">
         <v>1203.38</v>
       </c>
       <c r="O317" t="n">
-        <v>1131177.2</v>
+        <v>1111923.12</v>
       </c>
       <c r="P317" t="n">
         <v>1900</v>
       </c>
       <c r="Q317" t="n">
-        <v>1786000</v>
+        <v>1755600</v>
       </c>
     </row>
     <row r="318">
@@ -13983,22 +13983,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M318" t="n">
-        <v>931</v>
+        <v>910</v>
       </c>
       <c r="N318" t="n">
         <v>3472</v>
       </c>
       <c r="O318" t="n">
-        <v>3232432</v>
+        <v>3159520</v>
       </c>
       <c r="P318" t="n">
         <v>4800</v>
       </c>
       <c r="Q318" t="n">
-        <v>4468800</v>
+        <v>4368000</v>
       </c>
     </row>
     <row r="319">
@@ -14029,22 +14029,22 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M319" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="N319" t="n">
         <v>5888</v>
       </c>
       <c r="O319" t="n">
-        <v>329728</v>
+        <v>288512</v>
       </c>
       <c r="P319" t="n">
         <v>9500</v>
       </c>
       <c r="Q319" t="n">
-        <v>532000</v>
+        <v>465500</v>
       </c>
     </row>
     <row r="320">
@@ -14075,22 +14075,22 @@
         <v>0</v>
       </c>
       <c r="L320" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M320" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N320" t="n">
         <v>41064.84</v>
       </c>
       <c r="O320" t="n">
-        <v>944491.3199999999</v>
+        <v>821296.7999999999</v>
       </c>
       <c r="P320" t="n">
         <v>68900</v>
       </c>
       <c r="Q320" t="n">
-        <v>1584700</v>
+        <v>1378000</v>
       </c>
     </row>
     <row r="321">
@@ -14290,22 +14290,22 @@
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M325" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N325" t="n">
         <v>7041</v>
       </c>
       <c r="O325" t="n">
-        <v>316845</v>
+        <v>274599</v>
       </c>
       <c r="P325" t="n">
         <v>11500</v>
       </c>
       <c r="Q325" t="n">
-        <v>517500</v>
+        <v>448500</v>
       </c>
     </row>
     <row r="326">
@@ -14428,22 +14428,22 @@
         <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M328" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N328" t="n">
         <v>8662</v>
       </c>
       <c r="O328" t="n">
-        <v>355142</v>
+        <v>346480</v>
       </c>
       <c r="P328" t="n">
         <v>14200</v>
       </c>
       <c r="Q328" t="n">
-        <v>582200</v>
+        <v>568000</v>
       </c>
     </row>
     <row r="329">
@@ -14556,22 +14556,22 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M331" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N331" t="n">
         <v>9047</v>
       </c>
       <c r="O331" t="n">
-        <v>823277</v>
+        <v>805183</v>
       </c>
       <c r="P331" t="n">
         <v>5900</v>
       </c>
       <c r="Q331" t="n">
-        <v>536900</v>
+        <v>525100</v>
       </c>
     </row>
     <row r="332">
@@ -14597,22 +14597,22 @@
         <v>0</v>
       </c>
       <c r="L332" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M332" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N332" t="n">
         <v>7180.21</v>
       </c>
       <c r="O332" t="n">
-        <v>172325.04</v>
+        <v>157964.62</v>
       </c>
       <c r="P332" t="n">
         <v>15900</v>
       </c>
       <c r="Q332" t="n">
-        <v>381600</v>
+        <v>349800</v>
       </c>
     </row>
     <row r="333">
@@ -14728,22 +14728,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M335" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N335" t="n">
-        <v>3594.254188862</v>
+        <v>3594.2541747573</v>
       </c>
       <c r="O335" t="n">
-        <v>244409.284842616</v>
+        <v>237220.7755339818</v>
       </c>
       <c r="P335" t="n">
         <v>6500</v>
       </c>
       <c r="Q335" t="n">
-        <v>442000</v>
+        <v>429000</v>
       </c>
     </row>
     <row r="336">
@@ -15032,25 +15032,25 @@
         <v>24</v>
       </c>
       <c r="K342" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M342" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="N342" t="n">
-        <v>14822.378867257</v>
+        <v>14822.378864577</v>
       </c>
       <c r="O342" t="n">
-        <v>355737.092814168</v>
+        <v>652184.670041388</v>
       </c>
       <c r="P342" t="n">
         <v>24900</v>
       </c>
       <c r="Q342" t="n">
-        <v>597600</v>
+        <v>1095600</v>
       </c>
     </row>
     <row r="343">
@@ -15117,28 +15117,28 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>274</v>
+        <v>366</v>
       </c>
       <c r="K344" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="M344" t="n">
-        <v>274</v>
+        <v>464</v>
       </c>
       <c r="N344" t="n">
         <v>2090.85</v>
       </c>
       <c r="O344" t="n">
-        <v>572892.9</v>
+        <v>970154.3999999999</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
       </c>
       <c r="Q344" t="n">
-        <v>794600</v>
+        <v>1345600</v>
       </c>
     </row>
     <row r="345">
@@ -15296,22 +15296,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M348" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N348" t="n">
         <v>2665.4</v>
       </c>
       <c r="O348" t="n">
-        <v>50642.6</v>
+        <v>45311.8</v>
       </c>
       <c r="P348" t="n">
         <v>20900</v>
       </c>
       <c r="Q348" t="n">
-        <v>397100</v>
+        <v>355300</v>
       </c>
     </row>
     <row r="349">
@@ -15339,28 +15339,28 @@
         </is>
       </c>
       <c r="J349" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="K349" t="n">
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M349" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="N349" t="n">
         <v>1381.75</v>
       </c>
       <c r="O349" t="n">
-        <v>303985</v>
+        <v>294312.75</v>
       </c>
       <c r="P349" t="n">
         <v>2500</v>
       </c>
       <c r="Q349" t="n">
-        <v>550000</v>
+        <v>532500</v>
       </c>
     </row>
     <row r="350">
@@ -15436,10 +15436,10 @@
         <v>8</v>
       </c>
       <c r="N351" t="n">
-        <v>15851.61</v>
+        <v>15957.996644295</v>
       </c>
       <c r="O351" t="n">
-        <v>126812.88</v>
+        <v>127663.97315436</v>
       </c>
       <c r="P351" t="n">
         <v>23900</v>
@@ -15476,22 +15476,22 @@
         <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M352" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N352" t="n">
         <v>3309</v>
       </c>
       <c r="O352" t="n">
-        <v>301119</v>
+        <v>281265</v>
       </c>
       <c r="P352" t="n">
         <v>5900</v>
       </c>
       <c r="Q352" t="n">
-        <v>536900</v>
+        <v>501500</v>
       </c>
     </row>
     <row r="353">
@@ -15616,10 +15616,10 @@
         <v>427</v>
       </c>
       <c r="N355" t="n">
-        <v>3041.6600125549</v>
+        <v>3041.6600125945</v>
       </c>
       <c r="O355" t="n">
-        <v>1298788.825360942</v>
+        <v>1298788.825377851</v>
       </c>
       <c r="P355" t="n">
         <v>5500</v>
@@ -15697,22 +15697,22 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M357" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="N357" t="n">
-        <v>4372.2107866525</v>
+        <v>4372.2107869318</v>
       </c>
       <c r="O357" t="n">
-        <v>494059.8188917325</v>
+        <v>480943.186562498</v>
       </c>
       <c r="P357" t="n">
         <v>7500</v>
       </c>
       <c r="Q357" t="n">
-        <v>847500</v>
+        <v>825000</v>
       </c>
     </row>
     <row r="358">
@@ -15741,22 +15741,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M358" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="N358" t="n">
         <v>6441.03</v>
       </c>
       <c r="O358" t="n">
-        <v>772923.6</v>
+        <v>740718.45</v>
       </c>
       <c r="P358" t="n">
         <v>10500</v>
       </c>
       <c r="Q358" t="n">
-        <v>1260000</v>
+        <v>1207500</v>
       </c>
     </row>
     <row r="359">
@@ -15793,10 +15793,10 @@
         <v>19</v>
       </c>
       <c r="N359" t="n">
-        <v>1592.5676712942</v>
+        <v>1592.5675881262</v>
       </c>
       <c r="O359" t="n">
-        <v>30258.7857545898</v>
+        <v>30258.7841743978</v>
       </c>
       <c r="P359" t="n">
         <v>3900</v>
@@ -15869,22 +15869,22 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M361" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="N361" t="n">
         <v>2224.56</v>
       </c>
       <c r="O361" t="n">
-        <v>233578.8</v>
+        <v>220231.44</v>
       </c>
       <c r="P361" t="n">
         <v>3900</v>
       </c>
       <c r="Q361" t="n">
-        <v>409500</v>
+        <v>386100</v>
       </c>
     </row>
     <row r="362">
@@ -15915,22 +15915,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M362" t="n">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="N362" t="n">
         <v>3655.96</v>
       </c>
       <c r="O362" t="n">
-        <v>413123.48</v>
+        <v>325380.44</v>
       </c>
       <c r="P362" t="n">
         <v>5500</v>
       </c>
       <c r="Q362" t="n">
-        <v>621500</v>
+        <v>489500</v>
       </c>
     </row>
     <row r="363">
@@ -16264,22 +16264,22 @@
         <v>0</v>
       </c>
       <c r="L370" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M370" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="N370" t="n">
         <v>5633.97</v>
       </c>
       <c r="O370" t="n">
-        <v>129581.31</v>
+        <v>61973.67000000001</v>
       </c>
       <c r="P370" t="n">
         <v>9600</v>
       </c>
       <c r="Q370" t="n">
-        <v>220800</v>
+        <v>105600</v>
       </c>
     </row>
     <row r="371">
@@ -16359,22 +16359,22 @@
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M372" t="n">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="N372" t="n">
         <v>4648.6</v>
       </c>
       <c r="O372" t="n">
-        <v>1552632.4</v>
+        <v>1510795</v>
       </c>
       <c r="P372" t="n">
         <v>8900</v>
       </c>
       <c r="Q372" t="n">
-        <v>2972600</v>
+        <v>2892500</v>
       </c>
     </row>
     <row r="373">
@@ -16617,22 +16617,22 @@
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M378" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="N378" t="n">
-        <v>17472.91</v>
+        <v>17476.031091396</v>
       </c>
       <c r="O378" t="n">
-        <v>2026857.56</v>
+        <v>1922363.42005356</v>
       </c>
       <c r="P378" t="n">
         <v>2900</v>
       </c>
       <c r="Q378" t="n">
-        <v>336400</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="379">
@@ -16705,22 +16705,22 @@
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M380" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="N380" t="n">
         <v>1530.63</v>
       </c>
       <c r="O380" t="n">
-        <v>301534.11</v>
+        <v>292350.33</v>
       </c>
       <c r="P380" t="n">
         <v>2900</v>
       </c>
       <c r="Q380" t="n">
-        <v>571300</v>
+        <v>553900</v>
       </c>
     </row>
     <row r="381">
@@ -16749,22 +16749,22 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M381" t="n">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="N381" t="n">
         <v>1647.46</v>
       </c>
       <c r="O381" t="n">
-        <v>1000008.22</v>
+        <v>981886.16</v>
       </c>
       <c r="P381" t="n">
         <v>2900</v>
       </c>
       <c r="Q381" t="n">
-        <v>1760300</v>
+        <v>1728400</v>
       </c>
     </row>
     <row r="382">
@@ -16793,22 +16793,22 @@
         <v>0</v>
       </c>
       <c r="L382" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M382" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N382" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O382" t="n">
-        <v>404815.33</v>
+        <v>357743.78</v>
       </c>
       <c r="P382" t="n">
         <v>16900</v>
       </c>
       <c r="Q382" t="n">
-        <v>726700</v>
+        <v>642200</v>
       </c>
     </row>
     <row r="383">
@@ -16831,28 +16831,28 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M383" t="n">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="N383" t="n">
         <v>1387.55</v>
       </c>
       <c r="O383" t="n">
-        <v>765927.6</v>
+        <v>740951.7</v>
       </c>
       <c r="P383" t="n">
         <v>2300</v>
       </c>
       <c r="Q383" t="n">
-        <v>1269600</v>
+        <v>1228200</v>
       </c>
     </row>
     <row r="384">
@@ -17100,22 +17100,22 @@
         <v>0</v>
       </c>
       <c r="L389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M389" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N389" t="n">
         <v>2204</v>
       </c>
       <c r="O389" t="n">
-        <v>222604</v>
+        <v>220400</v>
       </c>
       <c r="P389" t="n">
         <v>1500</v>
       </c>
       <c r="Q389" t="n">
-        <v>151500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="390">
@@ -17237,22 +17237,22 @@
         <v>0</v>
       </c>
       <c r="L392" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M392" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="N392" t="n">
         <v>5853</v>
       </c>
       <c r="O392" t="n">
-        <v>1071099</v>
+        <v>1053540</v>
       </c>
       <c r="P392" t="n">
         <v>9900</v>
       </c>
       <c r="Q392" t="n">
-        <v>1811700</v>
+        <v>1782000</v>
       </c>
     </row>
     <row r="393">
@@ -17422,22 +17422,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M396" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="N396" t="n">
         <v>11921.4</v>
       </c>
       <c r="O396" t="n">
-        <v>1680917.4</v>
+        <v>1609389</v>
       </c>
       <c r="P396" t="n">
         <v>19900</v>
       </c>
       <c r="Q396" t="n">
-        <v>2805900</v>
+        <v>2686500</v>
       </c>
     </row>
     <row r="397">
@@ -17721,22 +17721,22 @@
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N403" t="n">
-        <v>1151.3923550423</v>
+        <v>1151.3923553227</v>
       </c>
       <c r="O403" t="n">
-        <v>461708.3343719624</v>
+        <v>460556.94212908</v>
       </c>
       <c r="P403" t="n">
         <v>1500</v>
       </c>
       <c r="Q403" t="n">
-        <v>601500</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="404">
@@ -17756,28 +17756,28 @@
         </is>
       </c>
       <c r="J404" t="n">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="K404" t="n">
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M404" t="n">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="N404" t="n">
         <v>3751</v>
       </c>
       <c r="O404" t="n">
-        <v>3394655</v>
+        <v>3390904</v>
       </c>
       <c r="P404" t="n">
         <v>6400</v>
       </c>
       <c r="Q404" t="n">
-        <v>5792000</v>
+        <v>5785600</v>
       </c>
     </row>
     <row r="405">
@@ -17811,22 +17811,22 @@
         <v>0</v>
       </c>
       <c r="L405" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M405" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N405" t="n">
         <v>9903</v>
       </c>
       <c r="O405" t="n">
-        <v>673404</v>
+        <v>623889</v>
       </c>
       <c r="P405" t="n">
         <v>15900</v>
       </c>
       <c r="Q405" t="n">
-        <v>1081200</v>
+        <v>1001700</v>
       </c>
     </row>
     <row r="406">
@@ -17903,22 +17903,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M407" t="n">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="N407" t="n">
-        <v>1630.9230521929</v>
+        <v>1630.9231064431</v>
       </c>
       <c r="O407" t="n">
-        <v>1409117.517094666</v>
+        <v>1405855.717753952</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
       </c>
       <c r="Q407" t="n">
-        <v>2160000</v>
+        <v>2155000</v>
       </c>
     </row>
     <row r="408">
@@ -18036,22 +18036,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M410" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="N410" t="n">
-        <v>1690.6034846029</v>
+        <v>1690.6033768352</v>
       </c>
       <c r="O410" t="n">
-        <v>792893.0342787601</v>
+        <v>787821.1736052032</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
       </c>
       <c r="Q410" t="n">
-        <v>1360100</v>
+        <v>1351400</v>
       </c>
     </row>
     <row r="411">
@@ -18082,22 +18082,22 @@
         <v>0</v>
       </c>
       <c r="L411" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M411" t="n">
-        <v>2199</v>
+        <v>2166</v>
       </c>
       <c r="N411" t="n">
-        <v>1550.1930031561</v>
+        <v>1550.1930735465</v>
       </c>
       <c r="O411" t="n">
-        <v>3408874.413940264</v>
+        <v>3357718.197301719</v>
       </c>
       <c r="P411" t="n">
         <v>2500</v>
       </c>
       <c r="Q411" t="n">
-        <v>5497500</v>
+        <v>5415000</v>
       </c>
     </row>
     <row r="412">
@@ -18174,22 +18174,22 @@
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M413" t="n">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="N413" t="n">
-        <v>2403.5101337902</v>
+        <v>2403.5102087442</v>
       </c>
       <c r="O413" t="n">
-        <v>2590983.924225836</v>
+        <v>2562141.882521317</v>
       </c>
       <c r="P413" t="n">
         <v>3500</v>
       </c>
       <c r="Q413" t="n">
-        <v>3773000</v>
+        <v>3731000</v>
       </c>
     </row>
     <row r="414">
@@ -18220,22 +18220,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M414" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="N414" t="n">
-        <v>2521.5468491124</v>
+        <v>2521.5455211726</v>
       </c>
       <c r="O414" t="n">
-        <v>153814.3577958564</v>
+        <v>73124.8201140054</v>
       </c>
       <c r="P414" t="n">
         <v>3900</v>
       </c>
       <c r="Q414" t="n">
-        <v>237900</v>
+        <v>113100</v>
       </c>
     </row>
     <row r="415">
@@ -19313,22 +19313,22 @@
         <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M439" t="n">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N439" t="n">
         <v>5067.21</v>
       </c>
       <c r="O439" t="n">
-        <v>1656977.67</v>
+        <v>1626574.41</v>
       </c>
       <c r="P439" t="n">
         <v>4200</v>
       </c>
       <c r="Q439" t="n">
-        <v>1373400</v>
+        <v>1348200</v>
       </c>
     </row>
     <row r="440">
@@ -20324,22 +20324,22 @@
         <v>0</v>
       </c>
       <c r="L462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M462" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N462" t="n">
         <v>16336.74</v>
       </c>
       <c r="O462" t="n">
-        <v>81683.7</v>
+        <v>65346.96</v>
       </c>
       <c r="P462" t="n">
         <v>30900</v>
       </c>
       <c r="Q462" t="n">
-        <v>154500</v>
+        <v>123600</v>
       </c>
     </row>
     <row r="463">
@@ -20960,22 +20960,22 @@
         <v>0</v>
       </c>
       <c r="L477" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M477" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="N477" t="n">
         <v>9338</v>
       </c>
       <c r="O477" t="n">
-        <v>205436</v>
+        <v>56028</v>
       </c>
       <c r="P477" t="n">
         <v>15500</v>
       </c>
       <c r="Q477" t="n">
-        <v>341000</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="478">
@@ -21414,22 +21414,22 @@
         <v>0</v>
       </c>
       <c r="L488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M488" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N488" t="n">
         <v>4488</v>
       </c>
       <c r="O488" t="n">
-        <v>664224</v>
+        <v>659736</v>
       </c>
       <c r="P488" t="n">
         <v>6200</v>
       </c>
       <c r="Q488" t="n">
-        <v>917600</v>
+        <v>911400</v>
       </c>
     </row>
     <row r="489">
@@ -21537,22 +21537,22 @@
         <v>0</v>
       </c>
       <c r="L491" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M491" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N491" t="n">
         <v>2916</v>
       </c>
       <c r="O491" t="n">
-        <v>329508</v>
+        <v>326592</v>
       </c>
       <c r="P491" t="n">
         <v>3200</v>
       </c>
       <c r="Q491" t="n">
-        <v>361600</v>
+        <v>358400</v>
       </c>
     </row>
     <row r="492">
@@ -21578,22 +21578,22 @@
         <v>0</v>
       </c>
       <c r="L492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M492" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N492" t="n">
         <v>2286.55</v>
       </c>
       <c r="O492" t="n">
-        <v>162345.05</v>
+        <v>160058.5</v>
       </c>
       <c r="P492" t="n">
         <v>3200</v>
       </c>
       <c r="Q492" t="n">
-        <v>227200</v>
+        <v>224000</v>
       </c>
     </row>
     <row r="493">
@@ -21660,22 +21660,22 @@
         <v>0</v>
       </c>
       <c r="L494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M494" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N494" t="n">
         <v>1958.73</v>
       </c>
       <c r="O494" t="n">
-        <v>27422.22</v>
+        <v>25463.49</v>
       </c>
       <c r="P494" t="n">
         <v>3400</v>
       </c>
       <c r="Q494" t="n">
-        <v>47600</v>
+        <v>44200</v>
       </c>
     </row>
     <row r="495">
@@ -21788,22 +21788,22 @@
         <v>0</v>
       </c>
       <c r="L497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M497" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N497" t="n">
         <v>2567</v>
       </c>
       <c r="O497" t="n">
-        <v>944656</v>
+        <v>942089</v>
       </c>
       <c r="P497" t="n">
         <v>4500</v>
       </c>
       <c r="Q497" t="n">
-        <v>1656000</v>
+        <v>1651500</v>
       </c>
     </row>
     <row r="498">
@@ -22028,28 +22028,28 @@
         </is>
       </c>
       <c r="J503" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K503" t="n">
         <v>0</v>
       </c>
       <c r="L503" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M503" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N503" t="n">
         <v>2517.22</v>
       </c>
       <c r="O503" t="n">
-        <v>573926.1599999999</v>
+        <v>571408.9399999999</v>
       </c>
       <c r="P503" t="n">
         <v>4200</v>
       </c>
       <c r="Q503" t="n">
-        <v>957600</v>
+        <v>953400</v>
       </c>
     </row>
     <row r="504">
@@ -22157,22 +22157,22 @@
         <v>0</v>
       </c>
       <c r="L506" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M506" t="n">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="N506" t="n">
-        <v>2029.8736460865</v>
+        <v>2029.8736549708</v>
       </c>
       <c r="O506" t="n">
-        <v>974339.35012152</v>
+        <v>966219.8597661009</v>
       </c>
       <c r="P506" t="n">
         <v>3600</v>
       </c>
       <c r="Q506" t="n">
-        <v>1728000</v>
+        <v>1713600</v>
       </c>
     </row>
     <row r="507">
@@ -22444,22 +22444,22 @@
         <v>0</v>
       </c>
       <c r="L513" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M513" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N513" t="n">
         <v>2673</v>
       </c>
       <c r="O513" t="n">
-        <v>729729</v>
+        <v>727056</v>
       </c>
       <c r="P513" t="n">
         <v>2500</v>
       </c>
       <c r="Q513" t="n">
-        <v>682500</v>
+        <v>680000</v>
       </c>
     </row>
     <row r="514">
@@ -22485,22 +22485,22 @@
         <v>0</v>
       </c>
       <c r="L514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M514" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N514" t="n">
         <v>11353</v>
       </c>
       <c r="O514" t="n">
-        <v>22706</v>
+        <v>11353</v>
       </c>
       <c r="P514" t="n">
         <v>16900</v>
       </c>
       <c r="Q514" t="n">
-        <v>33800</v>
+        <v>16900</v>
       </c>
     </row>
     <row r="515">
@@ -22526,22 +22526,22 @@
         <v>0</v>
       </c>
       <c r="L515" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M515" t="n">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="N515" t="n">
         <v>1866.74</v>
       </c>
       <c r="O515" t="n">
-        <v>1243248.84</v>
+        <v>1237648.62</v>
       </c>
       <c r="P515" t="n">
         <v>2900</v>
       </c>
       <c r="Q515" t="n">
-        <v>1931400</v>
+        <v>1922700</v>
       </c>
     </row>
     <row r="516">
@@ -22780,22 +22780,22 @@
         <v>0</v>
       </c>
       <c r="L521" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M521" t="n">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="N521" t="n">
-        <v>880.32932278334</v>
+        <v>880.32933581916</v>
       </c>
       <c r="O521" t="n">
-        <v>1214854.465441009</v>
+        <v>1209572.507415526</v>
       </c>
       <c r="P521" t="n">
         <v>1200</v>
       </c>
       <c r="Q521" t="n">
-        <v>1656000</v>
+        <v>1648800</v>
       </c>
     </row>
     <row r="522">
@@ -23072,22 +23072,22 @@
         <v>0</v>
       </c>
       <c r="L528" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M528" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="N528" t="n">
         <v>2465</v>
       </c>
       <c r="O528" t="n">
-        <v>458490</v>
+        <v>451095</v>
       </c>
       <c r="P528" t="n">
         <v>3700</v>
       </c>
       <c r="Q528" t="n">
-        <v>688200</v>
+        <v>677100</v>
       </c>
     </row>
     <row r="529">
@@ -23113,22 +23113,22 @@
         <v>0</v>
       </c>
       <c r="L529" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M529" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N529" t="n">
         <v>26595</v>
       </c>
       <c r="O529" t="n">
-        <v>478710</v>
+        <v>398925</v>
       </c>
       <c r="P529" t="n">
         <v>39900</v>
       </c>
       <c r="Q529" t="n">
-        <v>718200</v>
+        <v>598500</v>
       </c>
     </row>
     <row r="530">
@@ -23772,10 +23772,10 @@
         <v>280</v>
       </c>
       <c r="N544" t="n">
-        <v>4285.1952479339</v>
+        <v>4285.1952751817</v>
       </c>
       <c r="O544" t="n">
-        <v>1199854.669421492</v>
+        <v>1199854.677050876</v>
       </c>
       <c r="P544" t="n">
         <v>6900</v>
@@ -24532,22 +24532,22 @@
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M562" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N562" t="n">
         <v>11980</v>
       </c>
       <c r="O562" t="n">
-        <v>359400</v>
+        <v>335440</v>
       </c>
       <c r="P562" t="n">
         <v>19500</v>
       </c>
       <c r="Q562" t="n">
-        <v>585000</v>
+        <v>546000</v>
       </c>
     </row>
     <row r="563">
@@ -25563,25 +25563,25 @@
         <v>39</v>
       </c>
       <c r="K586" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="L586" t="n">
         <v>0</v>
       </c>
       <c r="M586" t="n">
-        <v>39</v>
+        <v>279</v>
       </c>
       <c r="N586" t="n">
         <v>4793.53</v>
       </c>
       <c r="O586" t="n">
-        <v>186947.67</v>
+        <v>1337394.87</v>
       </c>
       <c r="P586" t="n">
         <v>7900</v>
       </c>
       <c r="Q586" t="n">
-        <v>308100</v>
+        <v>2204100</v>
       </c>
     </row>
     <row r="587">
@@ -25694,22 +25694,22 @@
         <v>0</v>
       </c>
       <c r="L589" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M589" t="n">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="N589" t="n">
         <v>2014</v>
       </c>
       <c r="O589" t="n">
-        <v>1212428</v>
+        <v>1196316</v>
       </c>
       <c r="P589" t="n">
         <v>2000</v>
       </c>
       <c r="Q589" t="n">
-        <v>1204000</v>
+        <v>1188000</v>
       </c>
     </row>
     <row r="590">
@@ -25930,10 +25930,10 @@
         <v>41</v>
       </c>
       <c r="N594" t="n">
-        <v>27123.765250464</v>
+        <v>27123.765241636</v>
       </c>
       <c r="O594" t="n">
-        <v>1112074.375269024</v>
+        <v>1112074.374907076</v>
       </c>
       <c r="P594" t="n">
         <v>44500</v>
@@ -25970,22 +25970,22 @@
         <v>0</v>
       </c>
       <c r="L595" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M595" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N595" t="n">
         <v>16974.69</v>
       </c>
       <c r="O595" t="n">
-        <v>1561671.48</v>
+        <v>1476798.03</v>
       </c>
       <c r="P595" t="n">
         <v>26900</v>
       </c>
       <c r="Q595" t="n">
-        <v>2474800</v>
+        <v>2340300</v>
       </c>
     </row>
     <row r="596">
@@ -26093,22 +26093,22 @@
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M598" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N598" t="n">
         <v>4100.45</v>
       </c>
       <c r="O598" t="n">
-        <v>45104.95</v>
+        <v>28703.15</v>
       </c>
       <c r="P598" t="n">
         <v>26900</v>
       </c>
       <c r="Q598" t="n">
-        <v>295900</v>
+        <v>188300</v>
       </c>
     </row>
     <row r="599">
@@ -26180,22 +26180,22 @@
         <v>0</v>
       </c>
       <c r="L600" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M600" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N600" t="n">
         <v>5431.12</v>
       </c>
       <c r="O600" t="n">
-        <v>662596.64</v>
+        <v>651734.4</v>
       </c>
       <c r="P600" t="n">
         <v>8900</v>
       </c>
       <c r="Q600" t="n">
-        <v>1085800</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="601">
@@ -26261,28 +26261,28 @@
         </is>
       </c>
       <c r="J602" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K602" t="n">
         <v>0</v>
       </c>
       <c r="L602" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M602" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="N602" t="n">
-        <v>1560.9989986027</v>
+        <v>1560.9991607397</v>
       </c>
       <c r="O602" t="n">
-        <v>195124.8748253375</v>
+        <v>179514.9034850655</v>
       </c>
       <c r="P602" t="n">
         <v>2900</v>
       </c>
       <c r="Q602" t="n">
-        <v>362500</v>
+        <v>333500</v>
       </c>
     </row>
     <row r="603">
@@ -26583,10 +26583,10 @@
         <v>141</v>
       </c>
       <c r="N609" t="n">
-        <v>7969.950164794</v>
+        <v>7969.9501649175</v>
       </c>
       <c r="O609" t="n">
-        <v>1123762.973235954</v>
+        <v>1123762.973253367</v>
       </c>
       <c r="P609" t="n">
         <v>12900</v>
@@ -27038,22 +27038,22 @@
         <v>0</v>
       </c>
       <c r="L620" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M620" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N620" t="n">
         <v>12981.59</v>
       </c>
       <c r="O620" t="n">
-        <v>376466.11</v>
+        <v>350502.93</v>
       </c>
       <c r="P620" t="n">
         <v>21900</v>
       </c>
       <c r="Q620" t="n">
-        <v>635100</v>
+        <v>591300</v>
       </c>
     </row>
     <row r="621">
@@ -28078,25 +28078,25 @@
         <v>18</v>
       </c>
       <c r="K644" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L644" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M644" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="N644" t="n">
         <v>4690.64</v>
       </c>
       <c r="O644" t="n">
-        <v>84431.52</v>
+        <v>154791.12</v>
       </c>
       <c r="P644" t="n">
         <v>7500</v>
       </c>
       <c r="Q644" t="n">
-        <v>135000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="645">
@@ -28363,10 +28363,10 @@
         <v>24</v>
       </c>
       <c r="N650" t="n">
-        <v>5218.1704988662</v>
+        <v>5218.1705022831</v>
       </c>
       <c r="O650" t="n">
-        <v>125236.0919727888</v>
+        <v>125236.0920547944</v>
       </c>
       <c r="P650" t="n">
         <v>8500</v>
@@ -28409,10 +28409,10 @@
         <v>140</v>
       </c>
       <c r="N651" t="n">
-        <v>1595.0094843962</v>
+        <v>1595.0094808743</v>
       </c>
       <c r="O651" t="n">
-        <v>223301.327815468</v>
+        <v>223301.327322402</v>
       </c>
       <c r="P651" t="n">
         <v>2600</v>
@@ -28495,22 +28495,22 @@
         <v>0</v>
       </c>
       <c r="L653" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M653" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="N653" t="n">
         <v>5194</v>
       </c>
       <c r="O653" t="n">
-        <v>425908</v>
+        <v>394744</v>
       </c>
       <c r="P653" t="n">
         <v>9000</v>
       </c>
       <c r="Q653" t="n">
-        <v>738000</v>
+        <v>684000</v>
       </c>
     </row>
     <row r="654">
@@ -28633,22 +28633,22 @@
         <v>0</v>
       </c>
       <c r="L656" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M656" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="N656" t="n">
         <v>5791.05</v>
       </c>
       <c r="O656" t="n">
-        <v>498030.3</v>
+        <v>393791.4</v>
       </c>
       <c r="P656" t="n">
         <v>9300</v>
       </c>
       <c r="Q656" t="n">
-        <v>799800</v>
+        <v>632400</v>
       </c>
     </row>
     <row r="657">
@@ -28863,22 +28863,22 @@
         <v>0</v>
       </c>
       <c r="L661" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M661" t="n">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="N661" t="n">
-        <v>1664.3605954323</v>
+        <v>1664.360187234</v>
       </c>
       <c r="O661" t="n">
-        <v>694038.3682952691</v>
+        <v>675730.236017004</v>
       </c>
       <c r="P661" t="n">
         <v>2900</v>
       </c>
       <c r="Q661" t="n">
-        <v>1209300</v>
+        <v>1177400</v>
       </c>
     </row>
     <row r="662">
@@ -29145,22 +29145,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M667" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N667" t="n">
         <v>27307</v>
       </c>
       <c r="O667" t="n">
-        <v>136535</v>
+        <v>109228</v>
       </c>
       <c r="P667" t="n">
         <v>44900</v>
       </c>
       <c r="Q667" t="n">
-        <v>224500</v>
+        <v>179600</v>
       </c>
     </row>
     <row r="668">
@@ -29191,22 +29191,22 @@
         <v>0</v>
       </c>
       <c r="L668" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M668" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N668" t="n">
         <v>15824</v>
       </c>
       <c r="O668" t="n">
-        <v>474720</v>
+        <v>458896</v>
       </c>
       <c r="P668" t="n">
         <v>26900</v>
       </c>
       <c r="Q668" t="n">
-        <v>807000</v>
+        <v>780100</v>
       </c>
     </row>
     <row r="669">
@@ -29513,22 +29513,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M675" t="n">
-        <v>1541</v>
+        <v>1517</v>
       </c>
       <c r="N675" t="n">
-        <v>1778.4725400058</v>
+        <v>1778.4725489051</v>
       </c>
       <c r="O675" t="n">
-        <v>2740626.184148938</v>
+        <v>2697942.856689037</v>
       </c>
       <c r="P675" t="n">
         <v>4900</v>
       </c>
       <c r="Q675" t="n">
-        <v>7550900</v>
+        <v>7433300</v>
       </c>
     </row>
     <row r="676">
@@ -29559,22 +29559,22 @@
         <v>0</v>
       </c>
       <c r="L676" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M676" t="n">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="N676" t="n">
         <v>1548</v>
       </c>
       <c r="O676" t="n">
-        <v>482976</v>
+        <v>470592</v>
       </c>
       <c r="P676" t="n">
         <v>3900</v>
       </c>
       <c r="Q676" t="n">
-        <v>1216800</v>
+        <v>1185600</v>
       </c>
     </row>
     <row r="677">
@@ -29651,22 +29651,22 @@
         <v>0</v>
       </c>
       <c r="L678" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M678" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N678" t="n">
         <v>22739</v>
       </c>
       <c r="O678" t="n">
-        <v>250129</v>
+        <v>159173</v>
       </c>
       <c r="P678" t="n">
         <v>36900</v>
       </c>
       <c r="Q678" t="n">
-        <v>405900</v>
+        <v>258300</v>
       </c>
     </row>
     <row r="679">
@@ -29697,22 +29697,22 @@
         <v>0</v>
       </c>
       <c r="L679" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M679" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N679" t="n">
         <v>18016</v>
       </c>
       <c r="O679" t="n">
-        <v>306272</v>
+        <v>270240</v>
       </c>
       <c r="P679" t="n">
         <v>29900</v>
       </c>
       <c r="Q679" t="n">
-        <v>508300</v>
+        <v>448500</v>
       </c>
     </row>
     <row r="680">
@@ -29930,22 +29930,22 @@
         <v>0</v>
       </c>
       <c r="L684" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M684" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N684" t="n">
         <v>5148</v>
       </c>
       <c r="O684" t="n">
-        <v>128700</v>
+        <v>108108</v>
       </c>
       <c r="P684" t="n">
         <v>8600</v>
       </c>
       <c r="Q684" t="n">
-        <v>215000</v>
+        <v>180600</v>
       </c>
     </row>
     <row r="685">
@@ -31451,22 +31451,22 @@
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M717" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N717" t="n">
         <v>55898</v>
       </c>
       <c r="O717" t="n">
-        <v>1173858</v>
+        <v>1117960</v>
       </c>
       <c r="P717" t="n">
         <v>89900</v>
       </c>
       <c r="Q717" t="n">
-        <v>1887900</v>
+        <v>1798000</v>
       </c>
     </row>
     <row r="718">
@@ -31497,22 +31497,22 @@
         <v>0</v>
       </c>
       <c r="L718" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M718" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N718" t="n">
         <v>7713</v>
       </c>
       <c r="O718" t="n">
-        <v>555336</v>
+        <v>539910</v>
       </c>
       <c r="P718" t="n">
         <v>12500</v>
       </c>
       <c r="Q718" t="n">
-        <v>900000</v>
+        <v>875000</v>
       </c>
     </row>
     <row r="719">
@@ -31543,22 +31543,22 @@
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M719" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N719" t="n">
         <v>12709</v>
       </c>
       <c r="O719" t="n">
-        <v>38127</v>
+        <v>12709</v>
       </c>
       <c r="P719" t="n">
         <v>20500</v>
       </c>
       <c r="Q719" t="n">
-        <v>61500</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="720">
@@ -31589,22 +31589,22 @@
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M720" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N720" t="n">
         <v>28116</v>
       </c>
       <c r="O720" t="n">
-        <v>590436</v>
+        <v>534204</v>
       </c>
       <c r="P720" t="n">
         <v>45900</v>
       </c>
       <c r="Q720" t="n">
-        <v>963900</v>
+        <v>872100</v>
       </c>
     </row>
     <row r="721">
@@ -31635,22 +31635,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M721" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N721" t="n">
         <v>24847</v>
       </c>
       <c r="O721" t="n">
-        <v>670869</v>
+        <v>646022</v>
       </c>
       <c r="P721" t="n">
         <v>39900</v>
       </c>
       <c r="Q721" t="n">
-        <v>1077300</v>
+        <v>1037400</v>
       </c>
     </row>
     <row r="722">
@@ -31681,22 +31681,22 @@
         <v>0</v>
       </c>
       <c r="L722" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M722" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N722" t="n">
         <v>3424</v>
       </c>
       <c r="O722" t="n">
-        <v>653984</v>
+        <v>650560</v>
       </c>
       <c r="P722" t="n">
         <v>5900</v>
       </c>
       <c r="Q722" t="n">
-        <v>1126900</v>
+        <v>1121000</v>
       </c>
     </row>
     <row r="723">
@@ -31773,22 +31773,22 @@
         <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M724" t="n">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="N724" t="n">
         <v>8858.16</v>
       </c>
       <c r="O724" t="n">
-        <v>2489142.96</v>
+        <v>2400561.36</v>
       </c>
       <c r="P724" t="n">
         <v>15500</v>
       </c>
       <c r="Q724" t="n">
-        <v>4355500</v>
+        <v>4200500</v>
       </c>
     </row>
     <row r="725">
@@ -31865,22 +31865,22 @@
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M726" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N726" t="n">
         <v>10411</v>
       </c>
       <c r="O726" t="n">
-        <v>291508</v>
+        <v>270686</v>
       </c>
       <c r="P726" t="n">
         <v>16900</v>
       </c>
       <c r="Q726" t="n">
-        <v>473200</v>
+        <v>439400</v>
       </c>
     </row>
     <row r="727">
@@ -32049,22 +32049,22 @@
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M730" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N730" t="n">
         <v>11376</v>
       </c>
       <c r="O730" t="n">
-        <v>602928</v>
+        <v>580176</v>
       </c>
       <c r="P730" t="n">
         <v>18500</v>
       </c>
       <c r="Q730" t="n">
-        <v>980500</v>
+        <v>943500</v>
       </c>
     </row>
     <row r="731">
@@ -32095,22 +32095,22 @@
         <v>0</v>
       </c>
       <c r="L731" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M731" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="N731" t="n">
         <v>5014</v>
       </c>
       <c r="O731" t="n">
-        <v>391092</v>
+        <v>361008</v>
       </c>
       <c r="P731" t="n">
         <v>8200</v>
       </c>
       <c r="Q731" t="n">
-        <v>639600</v>
+        <v>590400</v>
       </c>
     </row>
     <row r="732">
@@ -32233,22 +32233,22 @@
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M734" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N734" t="n">
         <v>33216</v>
       </c>
       <c r="O734" t="n">
-        <v>298944</v>
+        <v>265728</v>
       </c>
       <c r="P734" t="n">
         <v>53900</v>
       </c>
       <c r="Q734" t="n">
-        <v>485100</v>
+        <v>431200</v>
       </c>
     </row>
     <row r="735">
@@ -32461,22 +32461,22 @@
         <v>0</v>
       </c>
       <c r="L739" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M739" t="n">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="N739" t="n">
-        <v>2328.1187525865</v>
+        <v>2328.1187507401</v>
       </c>
       <c r="O739" t="n">
-        <v>1634339.364315723</v>
+        <v>1632011.24426881</v>
       </c>
       <c r="P739" t="n">
         <v>4500</v>
       </c>
       <c r="Q739" t="n">
-        <v>3159000</v>
+        <v>3154500</v>
       </c>
     </row>
     <row r="740">
@@ -32875,22 +32875,22 @@
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M748" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N748" t="n">
         <v>3519</v>
       </c>
       <c r="O748" t="n">
-        <v>907902</v>
+        <v>904383</v>
       </c>
       <c r="P748" t="n">
         <v>5900</v>
       </c>
       <c r="Q748" t="n">
-        <v>1522200</v>
+        <v>1516300</v>
       </c>
     </row>
     <row r="749">
@@ -33059,22 +33059,22 @@
         <v>0</v>
       </c>
       <c r="L752" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M752" t="n">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="N752" t="n">
         <v>4544</v>
       </c>
       <c r="O752" t="n">
-        <v>1499520</v>
+        <v>1476800</v>
       </c>
       <c r="P752" t="n">
         <v>7900</v>
       </c>
       <c r="Q752" t="n">
-        <v>2607000</v>
+        <v>2567500</v>
       </c>
     </row>
     <row r="753">
@@ -33197,22 +33197,22 @@
         <v>0</v>
       </c>
       <c r="L755" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M755" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N755" t="n">
         <v>3396.38</v>
       </c>
       <c r="O755" t="n">
-        <v>410961.98</v>
+        <v>404169.22</v>
       </c>
       <c r="P755" t="n">
         <v>6500</v>
       </c>
       <c r="Q755" t="n">
-        <v>786500</v>
+        <v>773500</v>
       </c>
     </row>
     <row r="756">
@@ -33335,22 +33335,22 @@
         <v>0</v>
       </c>
       <c r="L758" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M758" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N758" t="n">
         <v>6414</v>
       </c>
       <c r="O758" t="n">
-        <v>1225074</v>
+        <v>1212246</v>
       </c>
       <c r="P758" t="n">
         <v>10900</v>
       </c>
       <c r="Q758" t="n">
-        <v>2081900</v>
+        <v>2060100</v>
       </c>
     </row>
     <row r="759">
@@ -33381,22 +33381,22 @@
         <v>0</v>
       </c>
       <c r="L759" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M759" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N759" t="n">
         <v>13210</v>
       </c>
       <c r="O759" t="n">
-        <v>2258910</v>
+        <v>2232490</v>
       </c>
       <c r="P759" t="n">
         <v>23900</v>
       </c>
       <c r="Q759" t="n">
-        <v>4086900</v>
+        <v>4039100</v>
       </c>
     </row>
     <row r="760">
@@ -33470,25 +33470,25 @@
         <v>14</v>
       </c>
       <c r="K761" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L761" t="n">
         <v>0</v>
       </c>
       <c r="M761" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N761" t="n">
         <v>76839</v>
       </c>
       <c r="O761" t="n">
-        <v>1075746</v>
+        <v>1306263</v>
       </c>
       <c r="P761" t="n">
         <v>122900</v>
       </c>
       <c r="Q761" t="n">
-        <v>1720600</v>
+        <v>2089300</v>
       </c>
     </row>
     <row r="762">
@@ -33565,22 +33565,22 @@
         <v>0</v>
       </c>
       <c r="L763" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M763" t="n">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="N763" t="n">
-        <v>3903.7359649123</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O763" t="n">
-        <v>464544.5798245637</v>
+        <v>402084.8238461586</v>
       </c>
       <c r="P763" t="n">
         <v>7500</v>
       </c>
       <c r="Q763" t="n">
-        <v>892500</v>
+        <v>772500</v>
       </c>
     </row>
     <row r="764">
@@ -33698,22 +33698,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M766" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N766" t="n">
         <v>12113</v>
       </c>
       <c r="O766" t="n">
-        <v>617763</v>
+        <v>581424</v>
       </c>
       <c r="P766" t="n">
         <v>19900</v>
       </c>
       <c r="Q766" t="n">
-        <v>1014900</v>
+        <v>955200</v>
       </c>
     </row>
     <row r="767">
@@ -33842,10 +33842,10 @@
         <v>65</v>
       </c>
       <c r="N769" t="n">
-        <v>4202</v>
+        <v>4213.1164021164</v>
       </c>
       <c r="O769" t="n">
-        <v>273130</v>
+        <v>273852.566137566</v>
       </c>
       <c r="P769" t="n">
         <v>7900</v>
@@ -33974,22 +33974,22 @@
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M772" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N772" t="n">
         <v>11922</v>
       </c>
       <c r="O772" t="n">
-        <v>11922</v>
+        <v>0</v>
       </c>
       <c r="P772" t="n">
         <v>19900</v>
       </c>
       <c r="Q772" t="n">
-        <v>19900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="773">
@@ -34066,22 +34066,22 @@
         <v>0</v>
       </c>
       <c r="L774" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M774" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="N774" t="n">
         <v>9839</v>
       </c>
       <c r="O774" t="n">
-        <v>796959</v>
+        <v>747764</v>
       </c>
       <c r="P774" t="n">
         <v>16900</v>
       </c>
       <c r="Q774" t="n">
-        <v>1368900</v>
+        <v>1284400</v>
       </c>
     </row>
     <row r="775">
@@ -34112,22 +34112,22 @@
         <v>0</v>
       </c>
       <c r="L775" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M775" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="N775" t="n">
         <v>2629</v>
       </c>
       <c r="O775" t="n">
-        <v>283932</v>
+        <v>252384</v>
       </c>
       <c r="P775" t="n">
         <v>4500</v>
       </c>
       <c r="Q775" t="n">
-        <v>486000</v>
+        <v>432000</v>
       </c>
     </row>
     <row r="776">
@@ -34155,25 +34155,25 @@
         <v>278</v>
       </c>
       <c r="K776" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L776" t="n">
         <v>0</v>
       </c>
       <c r="M776" t="n">
-        <v>278</v>
+        <v>494</v>
       </c>
       <c r="N776" t="n">
         <v>5869.1727464789</v>
       </c>
       <c r="O776" t="n">
-        <v>1631630.023521134</v>
+        <v>2899371.336760577</v>
       </c>
       <c r="P776" t="n">
         <v>9500</v>
       </c>
       <c r="Q776" t="n">
-        <v>2641000</v>
+        <v>4693000</v>
       </c>
     </row>
     <row r="777">
@@ -34250,22 +34250,22 @@
         <v>0</v>
       </c>
       <c r="L778" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M778" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N778" t="n">
         <v>4984</v>
       </c>
       <c r="O778" t="n">
-        <v>194376</v>
+        <v>184408</v>
       </c>
       <c r="P778" t="n">
         <v>7900</v>
       </c>
       <c r="Q778" t="n">
-        <v>308100</v>
+        <v>292300</v>
       </c>
     </row>
     <row r="779">
@@ -34296,22 +34296,22 @@
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M779" t="n">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="N779" t="n">
         <v>5772</v>
       </c>
       <c r="O779" t="n">
-        <v>923520</v>
+        <v>842712</v>
       </c>
       <c r="P779" t="n">
         <v>9900</v>
       </c>
       <c r="Q779" t="n">
-        <v>1584000</v>
+        <v>1445400</v>
       </c>
     </row>
     <row r="780">
@@ -34342,22 +34342,22 @@
         <v>0</v>
       </c>
       <c r="L780" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M780" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="N780" t="n">
         <v>6268</v>
       </c>
       <c r="O780" t="n">
-        <v>733356</v>
+        <v>689480</v>
       </c>
       <c r="P780" t="n">
         <v>10900</v>
       </c>
       <c r="Q780" t="n">
-        <v>1275300</v>
+        <v>1199000</v>
       </c>
     </row>
     <row r="781">
@@ -34431,25 +34431,25 @@
         <v>248</v>
       </c>
       <c r="K782" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L782" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M782" t="n">
-        <v>248</v>
+        <v>391</v>
       </c>
       <c r="N782" t="n">
         <v>6645</v>
       </c>
       <c r="O782" t="n">
-        <v>1647960</v>
+        <v>2598195</v>
       </c>
       <c r="P782" t="n">
         <v>10900</v>
       </c>
       <c r="Q782" t="n">
-        <v>2703200</v>
+        <v>4261900</v>
       </c>
     </row>
     <row r="783">
@@ -34618,22 +34618,22 @@
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M786" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N786" t="n">
         <v>7562</v>
       </c>
       <c r="O786" t="n">
-        <v>521778</v>
+        <v>461282</v>
       </c>
       <c r="P786" t="n">
         <v>12900</v>
       </c>
       <c r="Q786" t="n">
-        <v>890100</v>
+        <v>786900</v>
       </c>
     </row>
     <row r="787">
@@ -34710,22 +34710,22 @@
         <v>0</v>
       </c>
       <c r="L788" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M788" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N788" t="n">
         <v>13565</v>
       </c>
       <c r="O788" t="n">
-        <v>1397195</v>
+        <v>1383630</v>
       </c>
       <c r="P788" t="n">
         <v>22500</v>
       </c>
       <c r="Q788" t="n">
-        <v>2317500</v>
+        <v>2295000</v>
       </c>
     </row>
     <row r="789">
@@ -34802,22 +34802,22 @@
         <v>0</v>
       </c>
       <c r="L790" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M790" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N790" t="n">
         <v>5682</v>
       </c>
       <c r="O790" t="n">
-        <v>1255722</v>
+        <v>1250040</v>
       </c>
       <c r="P790" t="n">
         <v>9900</v>
       </c>
       <c r="Q790" t="n">
-        <v>2187900</v>
+        <v>2178000</v>
       </c>
     </row>
     <row r="791">
@@ -34848,22 +34848,22 @@
         <v>0</v>
       </c>
       <c r="L791" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M791" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N791" t="n">
         <v>5438</v>
       </c>
       <c r="O791" t="n">
-        <v>228396</v>
+        <v>217520</v>
       </c>
       <c r="P791" t="n">
         <v>8900</v>
       </c>
       <c r="Q791" t="n">
-        <v>373800</v>
+        <v>356000</v>
       </c>
     </row>
     <row r="792">
@@ -35035,22 +35035,22 @@
         <v>0</v>
       </c>
       <c r="L795" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M795" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N795" t="n">
         <v>11302</v>
       </c>
       <c r="O795" t="n">
-        <v>1401448</v>
+        <v>1378844</v>
       </c>
       <c r="P795" t="n">
         <v>18900</v>
       </c>
       <c r="Q795" t="n">
-        <v>2343600</v>
+        <v>2305800</v>
       </c>
     </row>
     <row r="796">
@@ -35173,22 +35173,22 @@
         <v>0</v>
       </c>
       <c r="L798" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M798" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N798" t="n">
         <v>11348</v>
       </c>
       <c r="O798" t="n">
-        <v>510660</v>
+        <v>453920</v>
       </c>
       <c r="P798" t="n">
         <v>19900</v>
       </c>
       <c r="Q798" t="n">
-        <v>895500</v>
+        <v>796000</v>
       </c>
     </row>
     <row r="799">
@@ -35219,22 +35219,22 @@
         <v>0</v>
       </c>
       <c r="L799" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M799" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N799" t="n">
-        <v>17075.989524138</v>
+        <v>17075.98952381</v>
       </c>
       <c r="O799" t="n">
-        <v>2954146.187675874</v>
+        <v>2937070.19809532</v>
       </c>
       <c r="P799" t="n">
         <v>27500</v>
       </c>
       <c r="Q799" t="n">
-        <v>4757500</v>
+        <v>4730000</v>
       </c>
     </row>
     <row r="800">
@@ -35490,22 +35490,22 @@
         <v>0</v>
       </c>
       <c r="L805" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M805" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N805" t="n">
         <v>59834</v>
       </c>
       <c r="O805" t="n">
-        <v>8316926</v>
+        <v>8137424</v>
       </c>
       <c r="P805" t="n">
         <v>7900</v>
       </c>
       <c r="Q805" t="n">
-        <v>1098100</v>
+        <v>1074400</v>
       </c>
     </row>
     <row r="806">
@@ -35674,25 +35674,25 @@
         <v>56</v>
       </c>
       <c r="K809" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L809" t="n">
         <v>0</v>
       </c>
       <c r="M809" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="N809" t="n">
         <v>10755</v>
       </c>
       <c r="O809" t="n">
-        <v>602280</v>
+        <v>924930</v>
       </c>
       <c r="P809" t="n">
         <v>17900</v>
       </c>
       <c r="Q809" t="n">
-        <v>1002400</v>
+        <v>1539400</v>
       </c>
     </row>
     <row r="810">
@@ -35769,22 +35769,22 @@
         <v>0</v>
       </c>
       <c r="L811" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M811" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N811" t="n">
         <v>20014</v>
       </c>
       <c r="O811" t="n">
-        <v>480336</v>
+        <v>460322</v>
       </c>
       <c r="P811" t="n">
         <v>33900</v>
       </c>
       <c r="Q811" t="n">
-        <v>813600</v>
+        <v>779700</v>
       </c>
     </row>
     <row r="812">
@@ -35907,22 +35907,22 @@
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M814" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N814" t="n">
-        <v>4268.7037401575</v>
+        <v>4268.7041295547</v>
       </c>
       <c r="O814" t="n">
-        <v>409795.55905512</v>
+        <v>388452.0757894777</v>
       </c>
       <c r="P814" t="n">
         <v>6900</v>
       </c>
       <c r="Q814" t="n">
-        <v>662400</v>
+        <v>627900</v>
       </c>
     </row>
     <row r="815">
@@ -35953,22 +35953,22 @@
         <v>0</v>
       </c>
       <c r="L815" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M815" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="N815" t="n">
         <v>5215</v>
       </c>
       <c r="O815" t="n">
-        <v>500640</v>
+        <v>469350</v>
       </c>
       <c r="P815" t="n">
         <v>8900</v>
       </c>
       <c r="Q815" t="n">
-        <v>854400</v>
+        <v>801000</v>
       </c>
     </row>
     <row r="816">
@@ -36229,22 +36229,22 @@
         <v>0</v>
       </c>
       <c r="L821" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M821" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N821" t="n">
         <v>16282</v>
       </c>
       <c r="O821" t="n">
-        <v>390768</v>
+        <v>325640</v>
       </c>
       <c r="P821" t="n">
         <v>27900</v>
       </c>
       <c r="Q821" t="n">
-        <v>669600</v>
+        <v>558000</v>
       </c>
     </row>
     <row r="822">
@@ -36275,22 +36275,22 @@
         <v>0</v>
       </c>
       <c r="L822" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M822" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N822" t="n">
         <v>8700</v>
       </c>
       <c r="O822" t="n">
-        <v>722100</v>
+        <v>687300</v>
       </c>
       <c r="P822" t="n">
         <v>14900</v>
       </c>
       <c r="Q822" t="n">
-        <v>1236700</v>
+        <v>1177100</v>
       </c>
     </row>
     <row r="823">
@@ -36367,22 +36367,22 @@
         <v>0</v>
       </c>
       <c r="L824" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M824" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N824" t="n">
         <v>2573</v>
       </c>
       <c r="O824" t="n">
-        <v>398815</v>
+        <v>396242</v>
       </c>
       <c r="P824" t="n">
         <v>4500</v>
       </c>
       <c r="Q824" t="n">
-        <v>697500</v>
+        <v>693000</v>
       </c>
     </row>
     <row r="825">
@@ -36413,22 +36413,22 @@
         <v>0</v>
       </c>
       <c r="L825" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M825" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N825" t="n">
         <v>21762</v>
       </c>
       <c r="O825" t="n">
-        <v>369954</v>
+        <v>326430</v>
       </c>
       <c r="P825" t="n">
         <v>35900</v>
       </c>
       <c r="Q825" t="n">
-        <v>610300</v>
+        <v>538500</v>
       </c>
     </row>
     <row r="826">
@@ -36459,22 +36459,22 @@
         <v>0</v>
       </c>
       <c r="L826" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M826" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N826" t="n">
         <v>3821</v>
       </c>
       <c r="O826" t="n">
-        <v>844441</v>
+        <v>832978</v>
       </c>
       <c r="P826" t="n">
         <v>5900</v>
       </c>
       <c r="Q826" t="n">
-        <v>1303900</v>
+        <v>1286200</v>
       </c>
     </row>
     <row r="827">
@@ -36505,22 +36505,22 @@
         <v>0</v>
       </c>
       <c r="L827" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M827" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N827" t="n">
         <v>15472</v>
       </c>
       <c r="O827" t="n">
-        <v>448688</v>
+        <v>417744</v>
       </c>
       <c r="P827" t="n">
         <v>25900</v>
       </c>
       <c r="Q827" t="n">
-        <v>751100</v>
+        <v>699300</v>
       </c>
     </row>
     <row r="828">
@@ -36597,22 +36597,22 @@
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M829" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N829" t="n">
         <v>7253</v>
       </c>
       <c r="O829" t="n">
-        <v>478698</v>
+        <v>471445</v>
       </c>
       <c r="P829" t="n">
         <v>11900</v>
       </c>
       <c r="Q829" t="n">
-        <v>785400</v>
+        <v>773500</v>
       </c>
     </row>
     <row r="830">
@@ -37014,22 +37014,22 @@
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M838" t="n">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="N838" t="n">
-        <v>4248.6196402878</v>
+        <v>4248.6214117647</v>
       </c>
       <c r="O838" t="n">
-        <v>713768.0995683505</v>
+        <v>616050.1047058814</v>
       </c>
       <c r="P838" t="n">
         <v>5900</v>
       </c>
       <c r="Q838" t="n">
-        <v>991200</v>
+        <v>855500</v>
       </c>
     </row>
     <row r="839">
@@ -37104,22 +37104,22 @@
         <v>0</v>
       </c>
       <c r="L840" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M840" t="n">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="N840" t="n">
-        <v>2458.5134452463</v>
+        <v>2458.5134204724</v>
       </c>
       <c r="O840" t="n">
-        <v>921942.5419673624</v>
+        <v>892440.3716314812</v>
       </c>
       <c r="P840" t="n">
         <v>3500</v>
       </c>
       <c r="Q840" t="n">
-        <v>1312500</v>
+        <v>1270500</v>
       </c>
     </row>
     <row r="841">
@@ -37150,22 +37150,22 @@
         <v>0</v>
       </c>
       <c r="L841" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M841" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="N841" t="n">
-        <v>1907.3944387755</v>
+        <v>1907.3944245524</v>
       </c>
       <c r="O841" t="n">
-        <v>370034.521122447</v>
+        <v>364312.3350895084</v>
       </c>
       <c r="P841" t="n">
         <v>2500</v>
       </c>
       <c r="Q841" t="n">
-        <v>485000</v>
+        <v>477500</v>
       </c>
     </row>
     <row r="842">
@@ -37242,22 +37242,22 @@
         <v>0</v>
       </c>
       <c r="L843" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M843" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N843" t="n">
-        <v>2079.3842077922</v>
+        <v>2079.384205911</v>
       </c>
       <c r="O843" t="n">
-        <v>873341.3672727239</v>
+        <v>871261.9822767091</v>
       </c>
       <c r="P843" t="n">
         <v>2900</v>
       </c>
       <c r="Q843" t="n">
-        <v>1218000</v>
+        <v>1215100</v>
       </c>
     </row>
     <row r="844">
@@ -37288,22 +37288,22 @@
         <v>0</v>
       </c>
       <c r="L844" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M844" t="n">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="N844" t="n">
-        <v>1803.0149882284</v>
+        <v>1803.0150073855</v>
       </c>
       <c r="O844" t="n">
-        <v>807750.7147263231</v>
+        <v>795129.6182570055</v>
       </c>
       <c r="P844" t="n">
         <v>2500</v>
       </c>
       <c r="Q844" t="n">
-        <v>1120000</v>
+        <v>1102500</v>
       </c>
     </row>
     <row r="845">
@@ -37334,22 +37334,22 @@
         <v>0</v>
       </c>
       <c r="L845" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M845" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N845" t="n">
-        <v>3306.595443038</v>
+        <v>3306.5954372624</v>
       </c>
       <c r="O845" t="n">
-        <v>241381.467341774</v>
+        <v>238074.8714828928</v>
       </c>
       <c r="P845" t="n">
         <v>4900</v>
       </c>
       <c r="Q845" t="n">
-        <v>357700</v>
+        <v>352800</v>
       </c>
     </row>
     <row r="846">
@@ -37386,10 +37386,10 @@
         <v>441</v>
       </c>
       <c r="N846" t="n">
-        <v>2122.1641066586</v>
+        <v>2122.1640959855</v>
       </c>
       <c r="O846" t="n">
-        <v>935874.3710364426</v>
+        <v>935874.3663296055</v>
       </c>
       <c r="P846" t="n">
         <v>2900</v>
@@ -37426,22 +37426,22 @@
         <v>0</v>
       </c>
       <c r="L847" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M847" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N847" t="n">
-        <v>2108.7898867497</v>
+        <v>2108.7899091941</v>
       </c>
       <c r="O847" t="n">
-        <v>99113.1246772359</v>
+        <v>90677.96609534629</v>
       </c>
       <c r="P847" t="n">
         <v>2900</v>
       </c>
       <c r="Q847" t="n">
-        <v>136300</v>
+        <v>124700</v>
       </c>
     </row>
     <row r="848">
@@ -37472,22 +37472,22 @@
         <v>0</v>
       </c>
       <c r="L848" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M848" t="n">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="N848" t="n">
-        <v>2056.0838862559</v>
+        <v>2056.083871734</v>
       </c>
       <c r="O848" t="n">
-        <v>1883372.839810404</v>
+        <v>1866924.155534472</v>
       </c>
       <c r="P848" t="n">
         <v>2900</v>
       </c>
       <c r="Q848" t="n">
-        <v>2656400</v>
+        <v>2633200</v>
       </c>
     </row>
     <row r="849">
@@ -37518,22 +37518,22 @@
         <v>0</v>
       </c>
       <c r="L849" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M849" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="N849" t="n">
-        <v>3224.5679768271</v>
+        <v>3224.5680666967</v>
       </c>
       <c r="O849" t="n">
-        <v>828713.9700445648</v>
+        <v>802917.4486074783</v>
       </c>
       <c r="P849" t="n">
         <v>4500</v>
       </c>
       <c r="Q849" t="n">
-        <v>1156500</v>
+        <v>1120500</v>
       </c>
     </row>
     <row r="850">
@@ -37564,22 +37564,22 @@
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M850" t="n">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="N850" t="n">
-        <v>1655.9313291536</v>
+        <v>1655.9312964128</v>
       </c>
       <c r="O850" t="n">
-        <v>773319.9307147312</v>
+        <v>753448.739867824</v>
       </c>
       <c r="P850" t="n">
         <v>2500</v>
       </c>
       <c r="Q850" t="n">
-        <v>1167500</v>
+        <v>1137500</v>
       </c>
     </row>
     <row r="851">
@@ -37797,22 +37797,22 @@
         <v>0</v>
       </c>
       <c r="L855" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M855" t="n">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="N855" t="n">
         <v>1662</v>
       </c>
       <c r="O855" t="n">
-        <v>1113540</v>
+        <v>1103568</v>
       </c>
       <c r="P855" t="n">
         <v>2900</v>
       </c>
       <c r="Q855" t="n">
-        <v>1943000</v>
+        <v>1925600</v>
       </c>
     </row>
     <row r="856">
@@ -37889,22 +37889,22 @@
         <v>0</v>
       </c>
       <c r="L857" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M857" t="n">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="N857" t="n">
         <v>2454</v>
       </c>
       <c r="O857" t="n">
-        <v>3123942</v>
+        <v>3114126</v>
       </c>
       <c r="P857" t="n">
         <v>4200</v>
       </c>
       <c r="Q857" t="n">
-        <v>5346600</v>
+        <v>5329800</v>
       </c>
     </row>
     <row r="858">
@@ -37935,22 +37935,22 @@
         <v>0</v>
       </c>
       <c r="L858" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M858" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="N858" t="n">
-        <v>1592.2748727876</v>
+        <v>1592.2752659892</v>
       </c>
       <c r="O858" t="n">
-        <v>219733.9324446888</v>
+        <v>199034.40824865</v>
       </c>
       <c r="P858" t="n">
         <v>2500</v>
       </c>
       <c r="Q858" t="n">
-        <v>345000</v>
+        <v>312500</v>
       </c>
     </row>
     <row r="859">
@@ -37985,10 +37985,10 @@
         <v>5</v>
       </c>
       <c r="N859" t="n">
-        <v>5347.73</v>
+        <v>5370.4862978723</v>
       </c>
       <c r="O859" t="n">
-        <v>26738.65</v>
+        <v>26852.4314893615</v>
       </c>
       <c r="P859" t="n">
         <v>9500</v>
@@ -38025,22 +38025,22 @@
         <v>0</v>
       </c>
       <c r="L860" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M860" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="N860" t="n">
-        <v>2311.9264781906</v>
+        <v>2311.9257410562</v>
       </c>
       <c r="O860" t="n">
-        <v>159522.9269951514</v>
+        <v>145651.3216865406</v>
       </c>
       <c r="P860" t="n">
         <v>3500</v>
       </c>
       <c r="Q860" t="n">
-        <v>241500</v>
+        <v>220500</v>
       </c>
     </row>
     <row r="861">
@@ -38071,22 +38071,22 @@
         <v>0</v>
       </c>
       <c r="L861" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M861" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N861" t="n">
-        <v>1906.1867105263</v>
+        <v>1906.1864705882</v>
       </c>
       <c r="O861" t="n">
-        <v>123902.1361842095</v>
+        <v>116277.3747058802</v>
       </c>
       <c r="P861" t="n">
         <v>2900</v>
       </c>
       <c r="Q861" t="n">
-        <v>188500</v>
+        <v>176900</v>
       </c>
     </row>
     <row r="862">
@@ -38123,10 +38123,10 @@
         <v>101</v>
       </c>
       <c r="N862" t="n">
-        <v>2060.1607096774</v>
+        <v>2060.1606493506</v>
       </c>
       <c r="O862" t="n">
-        <v>208076.2316774174</v>
+        <v>208076.2255844106</v>
       </c>
       <c r="P862" t="n">
         <v>2900</v>
@@ -38163,22 +38163,22 @@
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M863" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N863" t="n">
-        <v>1668.6158441558</v>
+        <v>1668.6165143824</v>
       </c>
       <c r="O863" t="n">
-        <v>8343.079220779</v>
+        <v>0</v>
       </c>
       <c r="P863" t="n">
         <v>2500</v>
       </c>
       <c r="Q863" t="n">
-        <v>12500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="864">
@@ -38255,22 +38255,22 @@
         <v>0</v>
       </c>
       <c r="L865" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M865" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="N865" t="n">
-        <v>1259.2744160105</v>
+        <v>1259.2744247206</v>
       </c>
       <c r="O865" t="n">
-        <v>357633.934146982</v>
+        <v>353856.1133464886</v>
       </c>
       <c r="P865" t="n">
         <v>1900</v>
       </c>
       <c r="Q865" t="n">
-        <v>539600</v>
+        <v>533900</v>
       </c>
     </row>
     <row r="866">
@@ -38344,25 +38344,25 @@
         <v>385</v>
       </c>
       <c r="K867" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L867" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M867" t="n">
-        <v>385</v>
+        <v>601</v>
       </c>
       <c r="N867" t="n">
         <v>1801</v>
       </c>
       <c r="O867" t="n">
-        <v>693385</v>
+        <v>1082401</v>
       </c>
       <c r="P867" t="n">
         <v>2900</v>
       </c>
       <c r="Q867" t="n">
-        <v>1116500</v>
+        <v>1742900</v>
       </c>
     </row>
     <row r="868">
@@ -38391,22 +38391,22 @@
         <v>0</v>
       </c>
       <c r="L868" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M868" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="N868" t="n">
-        <v>692.15205253785</v>
+        <v>692.15206356312</v>
       </c>
       <c r="O868" t="n">
-        <v>83750.39835707984</v>
+        <v>75444.57492838008</v>
       </c>
       <c r="P868" t="n">
         <v>1200</v>
       </c>
       <c r="Q868" t="n">
-        <v>145200</v>
+        <v>130800</v>
       </c>
     </row>
     <row r="869">
@@ -38904,10 +38904,10 @@
         <v>14</v>
       </c>
       <c r="N879" t="n">
-        <v>1757.9454901961</v>
+        <v>1757.9455445545</v>
       </c>
       <c r="O879" t="n">
-        <v>24611.2368627454</v>
+        <v>24611.237623763</v>
       </c>
       <c r="P879" t="n">
         <v>1800</v>
@@ -39864,22 +39864,22 @@
         <v>0</v>
       </c>
       <c r="L900" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M900" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="N900" t="n">
         <v>2357.74</v>
       </c>
       <c r="O900" t="n">
-        <v>297075.24</v>
+        <v>273497.84</v>
       </c>
       <c r="P900" t="n">
         <v>3000</v>
       </c>
       <c r="Q900" t="n">
-        <v>378000</v>
+        <v>348000</v>
       </c>
     </row>
     <row r="901">
@@ -40233,22 +40233,22 @@
         <v>0</v>
       </c>
       <c r="L908" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M908" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N908" t="n">
         <v>1621.2</v>
       </c>
       <c r="O908" t="n">
-        <v>81060</v>
+        <v>68090.40000000001</v>
       </c>
       <c r="P908" t="n">
         <v>2500</v>
       </c>
       <c r="Q908" t="n">
-        <v>125000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="909">
@@ -40408,13 +40408,13 @@
         </is>
       </c>
       <c r="J912" t="n">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="K912" t="n">
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M912" t="n">
         <v>460</v>
@@ -41070,22 +41070,22 @@
         <v>0</v>
       </c>
       <c r="L927" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="M927" t="n">
-        <v>878</v>
+        <v>538</v>
       </c>
       <c r="N927" t="n">
         <v>177.65</v>
       </c>
       <c r="O927" t="n">
-        <v>155976.7</v>
+        <v>95575.7</v>
       </c>
       <c r="P927" t="n">
         <v>300</v>
       </c>
       <c r="Q927" t="n">
-        <v>263400</v>
+        <v>161400</v>
       </c>
     </row>
     <row r="928">
@@ -41380,22 +41380,22 @@
         <v>0</v>
       </c>
       <c r="L934" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M934" t="n">
-        <v>3649</v>
+        <v>3529</v>
       </c>
       <c r="N934" t="n">
-        <v>517.28774146762</v>
+        <v>517.2878865955601</v>
       </c>
       <c r="O934" t="n">
-        <v>1887582.968615345</v>
+        <v>1825508.951795731</v>
       </c>
       <c r="P934" t="n">
         <v>900</v>
       </c>
       <c r="Q934" t="n">
-        <v>3284100</v>
+        <v>3176100</v>
       </c>
     </row>
     <row r="935">
@@ -41606,22 +41606,22 @@
         <v>0</v>
       </c>
       <c r="L939" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M939" t="n">
-        <v>746</v>
+        <v>686</v>
       </c>
       <c r="N939" t="n">
-        <v>3110.8430699863</v>
+        <v>3110.8429819337</v>
       </c>
       <c r="O939" t="n">
-        <v>2320688.93020978</v>
+        <v>2134038.285606518</v>
       </c>
       <c r="P939" t="n">
         <v>4500</v>
       </c>
       <c r="Q939" t="n">
-        <v>3357000</v>
+        <v>3087000</v>
       </c>
     </row>
     <row r="940">
@@ -41822,28 +41822,28 @@
         </is>
       </c>
       <c r="J944" t="n">
-        <v>1481</v>
+        <v>1529</v>
       </c>
       <c r="K944" t="n">
         <v>0</v>
       </c>
       <c r="L944" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M944" t="n">
-        <v>1481</v>
+        <v>1259</v>
       </c>
       <c r="N944" t="n">
-        <v>703.79541200942</v>
+        <v>703.79538564105</v>
       </c>
       <c r="O944" t="n">
-        <v>1042321.005185951</v>
+        <v>886078.3905220819</v>
       </c>
       <c r="P944" t="n">
         <v>900</v>
       </c>
       <c r="Q944" t="n">
-        <v>1332900</v>
+        <v>1133100</v>
       </c>
     </row>
     <row r="945">
@@ -41967,22 +41967,22 @@
         <v>0</v>
       </c>
       <c r="L947" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M947" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N947" t="n">
         <v>1858.84</v>
       </c>
       <c r="O947" t="n">
-        <v>5576.52</v>
+        <v>0</v>
       </c>
       <c r="P947" t="n">
         <v>2900</v>
       </c>
       <c r="Q947" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="948">
@@ -42107,10 +42107,10 @@
         <v>3</v>
       </c>
       <c r="N950" t="n">
-        <v>2501.385443038</v>
+        <v>2501.3854237288</v>
       </c>
       <c r="O950" t="n">
-        <v>7504.156329114001</v>
+        <v>7504.156271186401</v>
       </c>
       <c r="P950" t="n">
         <v>4100</v>
@@ -42150,22 +42150,22 @@
         <v>0</v>
       </c>
       <c r="L951" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M951" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N951" t="n">
         <v>14260.14</v>
       </c>
       <c r="O951" t="n">
-        <v>442064.34</v>
+        <v>413544.06</v>
       </c>
       <c r="P951" t="n">
         <v>15900</v>
       </c>
       <c r="Q951" t="n">
-        <v>492900</v>
+        <v>461100</v>
       </c>
     </row>
     <row r="952">
@@ -42412,22 +42412,22 @@
         <v>0</v>
       </c>
       <c r="L957" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M957" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="N957" t="n">
         <v>1937</v>
       </c>
       <c r="O957" t="n">
-        <v>284739</v>
+        <v>269243</v>
       </c>
       <c r="P957" t="n">
         <v>3300</v>
       </c>
       <c r="Q957" t="n">
-        <v>485100</v>
+        <v>458700</v>
       </c>
     </row>
     <row r="958">
@@ -42450,28 +42450,28 @@
         </is>
       </c>
       <c r="J958" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K958" t="n">
         <v>0</v>
       </c>
       <c r="L958" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M958" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N958" t="n">
         <v>2525.02</v>
       </c>
       <c r="O958" t="n">
-        <v>143926.14</v>
+        <v>118675.94</v>
       </c>
       <c r="P958" t="n">
         <v>3000</v>
       </c>
       <c r="Q958" t="n">
-        <v>171000</v>
+        <v>141000</v>
       </c>
     </row>
     <row r="959">
@@ -42502,22 +42502,22 @@
         <v>0</v>
       </c>
       <c r="L959" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M959" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="N959" t="n">
-        <v>712.62863414634</v>
+        <v>712.6285492228</v>
       </c>
       <c r="O959" t="n">
-        <v>18528.34448780484</v>
+        <v>9976.7996891192</v>
       </c>
       <c r="P959" t="n">
         <v>700</v>
       </c>
       <c r="Q959" t="n">
-        <v>18200</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="960">
@@ -42619,13 +42619,13 @@
         </is>
       </c>
       <c r="J962" t="n">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="K962" t="n">
         <v>0</v>
       </c>
       <c r="L962" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M962" t="n">
         <v>261</v>
@@ -42891,10 +42891,10 @@
         <v>74</v>
       </c>
       <c r="N968" t="n">
-        <v>1595.5191323094</v>
+        <v>1595.5190941049</v>
       </c>
       <c r="O968" t="n">
-        <v>118068.4157908956</v>
+        <v>118068.4129637626</v>
       </c>
       <c r="P968" t="n">
         <v>2500</v>
@@ -42931,22 +42931,22 @@
         <v>0</v>
       </c>
       <c r="L969" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M969" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N969" t="n">
         <v>1567.02</v>
       </c>
       <c r="O969" t="n">
-        <v>376084.8</v>
+        <v>374517.78</v>
       </c>
       <c r="P969" t="n">
         <v>2900</v>
       </c>
       <c r="Q969" t="n">
-        <v>696000</v>
+        <v>693100</v>
       </c>
     </row>
     <row r="970">
@@ -43315,22 +43315,22 @@
         <v>0</v>
       </c>
       <c r="L977" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M977" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N977" t="n">
         <v>16041.19</v>
       </c>
       <c r="O977" t="n">
-        <v>80205.95</v>
+        <v>64164.76</v>
       </c>
       <c r="P977" t="n">
         <v>40000</v>
       </c>
       <c r="Q977" t="n">
-        <v>200000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="978">
@@ -43416,10 +43416,10 @@
         <v>3</v>
       </c>
       <c r="N979" t="n">
-        <v>2098.4048595506</v>
+        <v>2098.4049008499</v>
       </c>
       <c r="O979" t="n">
-        <v>6295.2145786518</v>
+        <v>6295.2147025497</v>
       </c>
       <c r="P979" t="n">
         <v>9500</v>
@@ -43838,22 +43838,22 @@
         <v>0</v>
       </c>
       <c r="L988" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M988" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N988" t="n">
         <v>2672.89</v>
       </c>
       <c r="O988" t="n">
-        <v>29401.79</v>
+        <v>24056.01</v>
       </c>
       <c r="P988" t="n">
         <v>10200</v>
       </c>
       <c r="Q988" t="n">
-        <v>112200</v>
+        <v>91800</v>
       </c>
     </row>
     <row r="989">
@@ -44127,10 +44127,10 @@
         <v>55</v>
       </c>
       <c r="N994" t="n">
-        <v>3067.0905341246</v>
+        <v>3067.0905389222</v>
       </c>
       <c r="O994" t="n">
-        <v>168689.979376853</v>
+        <v>168689.979640721</v>
       </c>
       <c r="P994" t="n">
         <v>7200</v>
@@ -44302,10 +44302,10 @@
         <v>1</v>
       </c>
       <c r="N998" t="n">
-        <v>1783.7988868778</v>
+        <v>1783.7988843537</v>
       </c>
       <c r="O998" t="n">
-        <v>1783.7988868778</v>
+        <v>1783.7988843537</v>
       </c>
       <c r="P998" t="n">
         <v>1500</v>
@@ -44438,22 +44438,22 @@
         <v>0</v>
       </c>
       <c r="L1001" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1001" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N1001" t="n">
-        <v>4159.0002877698</v>
+        <v>4159.0002919708</v>
       </c>
       <c r="O1001" t="n">
-        <v>278653.0192805766</v>
+        <v>262017.0183941604</v>
       </c>
       <c r="P1001" t="n">
         <v>8900</v>
       </c>
       <c r="Q1001" t="n">
-        <v>596300</v>
+        <v>560700</v>
       </c>
     </row>
     <row r="1002">
@@ -44525,13 +44525,13 @@
         </is>
       </c>
       <c r="J1003" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K1003" t="n">
         <v>0</v>
       </c>
       <c r="L1003" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1003" t="n">
         <v>107</v>
@@ -44630,10 +44630,10 @@
         <v>1</v>
       </c>
       <c r="N1005" t="n">
-        <v>10737.526727273</v>
+        <v>10737.526666667</v>
       </c>
       <c r="O1005" t="n">
-        <v>10737.526727273</v>
+        <v>10737.526666667</v>
       </c>
       <c r="P1005" t="n">
         <v>18900</v>
@@ -45139,22 +45139,22 @@
         <v>0</v>
       </c>
       <c r="L1016" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1016" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N1016" t="n">
         <v>711.48</v>
       </c>
       <c r="O1016" t="n">
-        <v>3557.4</v>
+        <v>711.48</v>
       </c>
       <c r="P1016" t="n">
         <v>2500</v>
       </c>
       <c r="Q1016" t="n">
-        <v>12500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1017">
@@ -45238,10 +45238,10 @@
         <v>1</v>
       </c>
       <c r="N1018" t="n">
-        <v>1934.77</v>
+        <v>1942.8822431866</v>
       </c>
       <c r="O1018" t="n">
-        <v>1934.77</v>
+        <v>1942.8822431866</v>
       </c>
       <c r="P1018" t="n">
         <v>8900</v>
@@ -45380,10 +45380,10 @@
         <v>215</v>
       </c>
       <c r="N1021" t="n">
-        <v>7046.9398302567</v>
+        <v>7046.9398299681</v>
       </c>
       <c r="O1021" t="n">
-        <v>1515092.06350519</v>
+        <v>1515092.063443142</v>
       </c>
       <c r="P1021" t="n">
         <v>9900</v>
@@ -45420,22 +45420,22 @@
         <v>0</v>
       </c>
       <c r="L1022" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1022" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="N1022" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1022" t="n">
-        <v>1825385.25</v>
+        <v>1582000.55</v>
       </c>
       <c r="P1022" t="n">
         <v>27900</v>
       </c>
       <c r="Q1022" t="n">
-        <v>2092500</v>
+        <v>1813500</v>
       </c>
     </row>
     <row r="1023">
@@ -45464,22 +45464,22 @@
         <v>0</v>
       </c>
       <c r="L1023" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1023" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N1023" t="n">
         <v>10197</v>
       </c>
       <c r="O1023" t="n">
-        <v>295713</v>
+        <v>285516</v>
       </c>
       <c r="P1023" t="n">
         <v>14300</v>
       </c>
       <c r="Q1023" t="n">
-        <v>414700</v>
+        <v>400400</v>
       </c>
     </row>
     <row r="1024">
@@ -45508,22 +45508,22 @@
         <v>0</v>
       </c>
       <c r="L1024" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1024" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N1024" t="n">
         <v>10301.17</v>
       </c>
       <c r="O1024" t="n">
-        <v>278131.59</v>
+        <v>267830.42</v>
       </c>
       <c r="P1024" t="n">
         <v>14300</v>
       </c>
       <c r="Q1024" t="n">
-        <v>386100</v>
+        <v>371800</v>
       </c>
     </row>
     <row r="1025">
@@ -45935,22 +45935,22 @@
         <v>0</v>
       </c>
       <c r="L1033" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1033" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N1033" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1033" t="n">
-        <v>343638</v>
+        <v>325310.64</v>
       </c>
       <c r="P1033" t="n">
         <v>7900</v>
       </c>
       <c r="Q1033" t="n">
-        <v>592500</v>
+        <v>560900</v>
       </c>
     </row>
     <row r="1034">
@@ -46186,10 +46186,10 @@
         <v>6</v>
       </c>
       <c r="N1038" t="n">
-        <v>315.02678272981</v>
+        <v>315.02679218968</v>
       </c>
       <c r="O1038" t="n">
-        <v>1890.16069637886</v>
+        <v>1890.16075313808</v>
       </c>
       <c r="P1038" t="n">
         <v>2200</v>
@@ -46229,10 +46229,10 @@
         <v>0</v>
       </c>
       <c r="L1039" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M1039" t="n">
-        <v>2413</v>
+        <v>2402</v>
       </c>
       <c r="N1039" t="n">
         <v>0</v>
@@ -46244,7 +46244,7 @@
         <v>6500</v>
       </c>
       <c r="Q1039" t="n">
-        <v>15684500</v>
+        <v>15613000</v>
       </c>
     </row>
     <row r="1040">
@@ -46991,10 +46991,10 @@
         <v>57</v>
       </c>
       <c r="N1057" t="n">
-        <v>5577.2680821918</v>
+        <v>5577.2680778032</v>
       </c>
       <c r="O1057" t="n">
-        <v>317904.2806849326</v>
+        <v>317904.2804347824</v>
       </c>
       <c r="P1057" t="n">
         <v>6500</v>
@@ -47893,22 +47893,22 @@
         <v>0</v>
       </c>
       <c r="L1078" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1078" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N1078" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1078" t="n">
-        <v>43533.09</v>
+        <v>36473.67</v>
       </c>
       <c r="P1078" t="n">
         <v>1900</v>
       </c>
       <c r="Q1078" t="n">
-        <v>70300</v>
+        <v>58900</v>
       </c>
     </row>
     <row r="1079">
@@ -47937,22 +47937,22 @@
         <v>0</v>
       </c>
       <c r="L1079" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1079" t="n">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="N1079" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1079" t="n">
-        <v>894113.9</v>
+        <v>868658.7000000001</v>
       </c>
       <c r="P1079" t="n">
         <v>5100</v>
       </c>
       <c r="Q1079" t="n">
-        <v>1433100</v>
+        <v>1392300</v>
       </c>
     </row>
     <row r="1080">
@@ -47984,10 +47984,10 @@
         <v>3</v>
       </c>
       <c r="N1080" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821442495</v>
       </c>
       <c r="O1080" t="n">
-        <v>3641.0463583815</v>
+        <v>3641.0464327485</v>
       </c>
       <c r="P1080" t="n">
         <v>1500</v>
@@ -48063,22 +48063,22 @@
         <v>0</v>
       </c>
       <c r="L1082" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1082" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N1082" t="n">
-        <v>1794.2879773671</v>
+        <v>1794.2879767875</v>
       </c>
       <c r="O1082" t="n">
-        <v>346297.5796318503</v>
+        <v>342709.0035664125</v>
       </c>
       <c r="P1082" t="n">
         <v>1600</v>
       </c>
       <c r="Q1082" t="n">
-        <v>308800</v>
+        <v>305600</v>
       </c>
     </row>
     <row r="1083">
@@ -49322,10 +49322,10 @@
         <v>58</v>
       </c>
       <c r="N1111" t="n">
-        <v>1757.3205295316</v>
+        <v>1757.3205360825</v>
       </c>
       <c r="O1111" t="n">
-        <v>101924.5907128328</v>
+        <v>101924.591092785</v>
       </c>
       <c r="P1111" t="n">
         <v>2000</v>
@@ -49715,22 +49715,22 @@
         <v>0</v>
       </c>
       <c r="L1120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N1120" t="n">
         <v>15482.98</v>
       </c>
       <c r="O1120" t="n">
-        <v>15482.98</v>
+        <v>0</v>
       </c>
       <c r="P1120" t="n">
         <v>18500</v>
       </c>
       <c r="Q1120" t="n">
-        <v>18500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1121">
@@ -49899,22 +49899,22 @@
         <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N1124" t="n">
         <v>3590.22</v>
       </c>
       <c r="O1124" t="n">
-        <v>3590.22</v>
+        <v>0</v>
       </c>
       <c r="P1124" t="n">
         <v>4100</v>
       </c>
       <c r="Q1124" t="n">
-        <v>4100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1125">
@@ -51452,13 +51452,13 @@
         </is>
       </c>
       <c r="J1158" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K1158" t="n">
         <v>0</v>
       </c>
       <c r="L1158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1158" t="n">
         <v>24</v>
@@ -51699,10 +51699,10 @@
         <v>116</v>
       </c>
       <c r="N1163" t="n">
-        <v>227.41596785975</v>
+        <v>227.41597222222</v>
       </c>
       <c r="O1163" t="n">
-        <v>26380.252271731</v>
+        <v>26380.25277777752</v>
       </c>
       <c r="P1163" t="n">
         <v>1200</v>
@@ -52639,22 +52639,22 @@
         <v>0</v>
       </c>
       <c r="L1184" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1184" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="N1184" t="n">
         <v>4550</v>
       </c>
       <c r="O1184" t="n">
-        <v>1474200</v>
+        <v>1446900</v>
       </c>
       <c r="P1184" t="n">
         <v>5500</v>
       </c>
       <c r="Q1184" t="n">
-        <v>1782000</v>
+        <v>1749000</v>
       </c>
     </row>
     <row r="1185">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1054,22 +1054,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N16" t="n">
         <v>27000</v>
       </c>
       <c r="O16" t="n">
-        <v>675000</v>
+        <v>648000</v>
       </c>
       <c r="P16" t="n">
         <v>20000</v>
       </c>
       <c r="Q16" t="n">
-        <v>500000</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="17">
@@ -1348,22 +1348,22 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M23" t="n">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="N23" t="n">
-        <v>1811.3043052838</v>
+        <v>1811.3044243338</v>
       </c>
       <c r="O23" t="n">
-        <v>382185.2084148818</v>
+        <v>347770.4494720896</v>
       </c>
       <c r="P23" t="n">
         <v>2600</v>
       </c>
       <c r="Q23" t="n">
-        <v>548600</v>
+        <v>499200</v>
       </c>
     </row>
     <row r="24">
@@ -2965,10 +2965,10 @@
         <v>41</v>
       </c>
       <c r="N63" t="n">
-        <v>6272.8544651163</v>
+        <v>6272.8545</v>
       </c>
       <c r="O63" t="n">
-        <v>257187.0330697683</v>
+        <v>257187.0345</v>
       </c>
       <c r="P63" t="n">
         <v>7900</v>
@@ -3082,10 +3082,10 @@
         <v>44</v>
       </c>
       <c r="N66" t="n">
-        <v>3926.8371267317</v>
+        <v>3926.8371237802</v>
       </c>
       <c r="O66" t="n">
-        <v>172780.8335761948</v>
+        <v>172780.8334463288</v>
       </c>
       <c r="P66" t="n">
         <v>4800</v>
@@ -4181,10 +4181,10 @@
         <v>60</v>
       </c>
       <c r="N93" t="n">
-        <v>3910.6282352941</v>
+        <v>3933.7680473373</v>
       </c>
       <c r="O93" t="n">
-        <v>234637.694117646</v>
+        <v>236026.082840238</v>
       </c>
       <c r="P93" t="n">
         <v>9100</v>
@@ -4770,10 +4770,10 @@
         <v>10</v>
       </c>
       <c r="N106" t="n">
-        <v>30708.882222222</v>
+        <v>30708.862857143</v>
       </c>
       <c r="O106" t="n">
-        <v>307088.82222222</v>
+        <v>307088.62857143</v>
       </c>
       <c r="P106" t="n">
         <v>53500</v>
@@ -4812,10 +4812,10 @@
         <v>17</v>
       </c>
       <c r="N107" t="n">
-        <v>12837.965507246</v>
+        <v>12837.966461538</v>
       </c>
       <c r="O107" t="n">
-        <v>218245.413623182</v>
+        <v>218245.429846146</v>
       </c>
       <c r="P107" t="n">
         <v>22900</v>
@@ -4901,10 +4901,10 @@
         <v>68</v>
       </c>
       <c r="N109" t="n">
-        <v>10994.353483146</v>
+        <v>10994.353793103</v>
       </c>
       <c r="O109" t="n">
-        <v>747616.036853928</v>
+        <v>747616.0579310041</v>
       </c>
       <c r="P109" t="n">
         <v>16900</v>
@@ -5032,10 +5032,10 @@
         <v>10</v>
       </c>
       <c r="N112" t="n">
-        <v>16486.409489051</v>
+        <v>16486.409172932</v>
       </c>
       <c r="O112" t="n">
-        <v>164864.09489051</v>
+        <v>164864.09172932</v>
       </c>
       <c r="P112" t="n">
         <v>30500</v>
@@ -5207,10 +5207,10 @@
         <v>11</v>
       </c>
       <c r="N116" t="n">
-        <v>30238.8124</v>
+        <v>30238.812535211</v>
       </c>
       <c r="O116" t="n">
-        <v>332626.9364</v>
+        <v>332626.937887321</v>
       </c>
       <c r="P116" t="n">
         <v>51100</v>
@@ -5618,10 +5618,10 @@
         <v>5</v>
       </c>
       <c r="N126" t="n">
-        <v>22267.552083333</v>
+        <v>23235.706521739</v>
       </c>
       <c r="O126" t="n">
-        <v>111337.760416665</v>
+        <v>116178.532608695</v>
       </c>
       <c r="P126" t="n">
         <v>46300</v>
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M135" t="n">
         <v>11</v>
@@ -6041,13 +6041,13 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M136" t="n">
         <v>4</v>
@@ -6182,13 +6182,13 @@
         </is>
       </c>
       <c r="J139" t="n">
+        <v>2</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
         <v>1</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
       </c>
       <c r="M139" t="n">
         <v>1</v>
@@ -6236,10 +6236,10 @@
         <v>12</v>
       </c>
       <c r="N140" t="n">
-        <v>200072.19977273</v>
+        <v>200072.19992308</v>
       </c>
       <c r="O140" t="n">
-        <v>2400866.39727276</v>
+        <v>2400866.39907696</v>
       </c>
       <c r="P140" t="n">
         <v>312000</v>
@@ -6372,10 +6372,10 @@
         <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>344599.17865385</v>
+        <v>344599.17862745</v>
       </c>
       <c r="O143" t="n">
-        <v>689198.3573077</v>
+        <v>689198.3572549</v>
       </c>
       <c r="P143" t="n">
         <v>532900</v>
@@ -6419,10 +6419,10 @@
         <v>3</v>
       </c>
       <c r="N144" t="n">
-        <v>263530.179</v>
+        <v>263530.17666667</v>
       </c>
       <c r="O144" t="n">
-        <v>790590.537</v>
+        <v>790590.53000001</v>
       </c>
       <c r="P144" t="n">
         <v>402900</v>
@@ -7201,22 +7201,22 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M163" t="n">
         <v>4</v>
       </c>
       <c r="N163" t="n">
-        <v>61666.873932292</v>
+        <v>61666.873994709</v>
       </c>
       <c r="O163" t="n">
-        <v>246667.495729168</v>
+        <v>246667.495978836</v>
       </c>
       <c r="P163" t="n">
         <v>98900</v>
@@ -9756,22 +9756,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M221" t="n">
-        <v>473</v>
+        <v>293</v>
       </c>
       <c r="N221" t="n">
-        <v>1950.2151724138</v>
+        <v>1950.2147262682</v>
       </c>
       <c r="O221" t="n">
-        <v>922451.7765517274</v>
+        <v>571412.9147965825</v>
       </c>
       <c r="P221" t="n">
         <v>2900</v>
       </c>
       <c r="Q221" t="n">
-        <v>1371700</v>
+        <v>849700</v>
       </c>
     </row>
     <row r="222">
@@ -9844,10 +9844,10 @@
         <v>216</v>
       </c>
       <c r="N223" t="n">
-        <v>2833</v>
+        <v>2837.5792025862</v>
       </c>
       <c r="O223" t="n">
-        <v>611928</v>
+        <v>612917.1077586192</v>
       </c>
       <c r="P223" t="n">
         <v>3500</v>
@@ -9920,22 +9920,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M225" t="n">
-        <v>1962</v>
+        <v>1943</v>
       </c>
       <c r="N225" t="n">
         <v>1726.32</v>
       </c>
       <c r="O225" t="n">
-        <v>3387039.84</v>
+        <v>3354239.76</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
       </c>
       <c r="Q225" t="n">
-        <v>2943000</v>
+        <v>2914500</v>
       </c>
     </row>
     <row r="226">
@@ -10176,22 +10176,22 @@
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M231" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="N231" t="n">
         <v>6513</v>
       </c>
       <c r="O231" t="n">
-        <v>384267</v>
+        <v>345189</v>
       </c>
       <c r="P231" t="n">
         <v>11500</v>
       </c>
       <c r="Q231" t="n">
-        <v>678500</v>
+        <v>609500</v>
       </c>
     </row>
     <row r="232">
@@ -10269,10 +10269,10 @@
         <v>1</v>
       </c>
       <c r="N233" t="n">
-        <v>3775.99</v>
+        <v>3826.6744295302</v>
       </c>
       <c r="O233" t="n">
-        <v>3775.99</v>
+        <v>3826.6744295302</v>
       </c>
       <c r="P233" t="n">
         <v>7300</v>
@@ -10506,28 +10506,28 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>659</v>
+        <v>731</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="M239" t="n">
-        <v>659</v>
+        <v>613</v>
       </c>
       <c r="N239" t="n">
-        <v>1098.0541801698</v>
+        <v>1098.0548595108</v>
       </c>
       <c r="O239" t="n">
-        <v>723617.7047318983</v>
+        <v>673107.6288801205</v>
       </c>
       <c r="P239" t="n">
         <v>1500</v>
       </c>
       <c r="Q239" t="n">
-        <v>988500</v>
+        <v>919500</v>
       </c>
     </row>
     <row r="240">
@@ -10646,10 +10646,10 @@
         <v>15</v>
       </c>
       <c r="N242" t="n">
-        <v>21084.771455026</v>
+        <v>21084.771458886</v>
       </c>
       <c r="O242" t="n">
-        <v>316271.57182539</v>
+        <v>316271.57188329</v>
       </c>
       <c r="P242" t="n">
         <v>30000</v>
@@ -11012,22 +11012,22 @@
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M251" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N251" t="n">
         <v>9032.719999999999</v>
       </c>
       <c r="O251" t="n">
-        <v>81294.48</v>
+        <v>54196.31999999999</v>
       </c>
       <c r="P251" t="n">
         <v>11900</v>
       </c>
       <c r="Q251" t="n">
-        <v>107100</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="252">
@@ -11279,10 +11279,10 @@
         <v>1</v>
       </c>
       <c r="N257" t="n">
-        <v>7569</v>
+        <v>7632.3389121339</v>
       </c>
       <c r="O257" t="n">
-        <v>7569</v>
+        <v>7632.3389121339</v>
       </c>
       <c r="P257" t="n">
         <v>12900</v>
@@ -11374,10 +11374,10 @@
         <v>2</v>
       </c>
       <c r="N259" t="n">
-        <v>324.81111111111</v>
+        <v>322.295</v>
       </c>
       <c r="O259" t="n">
-        <v>649.62222222222</v>
+        <v>644.59</v>
       </c>
       <c r="P259" t="n">
         <v>550</v>
@@ -12319,22 +12319,22 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M281" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N281" t="n">
         <v>10600</v>
       </c>
       <c r="O281" t="n">
-        <v>901000</v>
+        <v>879800</v>
       </c>
       <c r="P281" t="n">
         <v>17200</v>
       </c>
       <c r="Q281" t="n">
-        <v>1462000</v>
+        <v>1427600</v>
       </c>
     </row>
     <row r="282">
@@ -12365,22 +12365,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M282" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="N282" t="n">
-        <v>5216.8959762435</v>
+        <v>5216.8959678619</v>
       </c>
       <c r="O282" t="n">
-        <v>819052.6682702295</v>
+        <v>777317.4992114231</v>
       </c>
       <c r="P282" t="n">
         <v>8500</v>
       </c>
       <c r="Q282" t="n">
-        <v>1334500</v>
+        <v>1266500</v>
       </c>
     </row>
     <row r="283">
@@ -12667,22 +12667,22 @@
         <v>0</v>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M289" t="n">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="N289" t="n">
-        <v>3158.8608143857</v>
+        <v>3158.8608147003</v>
       </c>
       <c r="O289" t="n">
-        <v>3004076.6344808</v>
+        <v>2978805.748262383</v>
       </c>
       <c r="P289" t="n">
         <v>5600</v>
       </c>
       <c r="Q289" t="n">
-        <v>5325600</v>
+        <v>5280800</v>
       </c>
     </row>
     <row r="290">
@@ -12713,22 +12713,22 @@
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M290" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N290" t="n">
         <v>1903</v>
       </c>
       <c r="O290" t="n">
-        <v>323510</v>
+        <v>317801</v>
       </c>
       <c r="P290" t="n">
         <v>3200</v>
       </c>
       <c r="Q290" t="n">
-        <v>544000</v>
+        <v>534400</v>
       </c>
     </row>
     <row r="291">
@@ -13074,22 +13074,22 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M298" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="N298" t="n">
         <v>1337.34</v>
       </c>
       <c r="O298" t="n">
-        <v>391840.62</v>
+        <v>387828.6</v>
       </c>
       <c r="P298" t="n">
         <v>2500</v>
       </c>
       <c r="Q298" t="n">
-        <v>732500</v>
+        <v>725000</v>
       </c>
     </row>
     <row r="299">
@@ -13126,10 +13126,10 @@
         <v>109</v>
       </c>
       <c r="N299" t="n">
-        <v>2694.8234624043</v>
+        <v>2694.8234565119</v>
       </c>
       <c r="O299" t="n">
-        <v>293735.7574020687</v>
+        <v>293735.7567597971</v>
       </c>
       <c r="P299" t="n">
         <v>4900</v>
@@ -13582,10 +13582,10 @@
         <v>299</v>
       </c>
       <c r="N309" t="n">
-        <v>3795.7100070547</v>
+        <v>3795.7100070621</v>
       </c>
       <c r="O309" t="n">
-        <v>1134917.292109355</v>
+        <v>1134917.292111568</v>
       </c>
       <c r="P309" t="n">
         <v>6200</v>
@@ -13709,22 +13709,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M312" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N312" t="n">
         <v>4357.55</v>
       </c>
       <c r="O312" t="n">
-        <v>1172180.95</v>
+        <v>1163465.85</v>
       </c>
       <c r="P312" t="n">
         <v>7500</v>
       </c>
       <c r="Q312" t="n">
-        <v>2017500</v>
+        <v>2002500</v>
       </c>
     </row>
     <row r="313">
@@ -13842,22 +13842,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M315" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N315" t="n">
-        <v>4890.9300462963</v>
+        <v>4890.9300463499</v>
       </c>
       <c r="O315" t="n">
-        <v>264110.2225000002</v>
+        <v>259219.2924565447</v>
       </c>
       <c r="P315" t="n">
         <v>8200</v>
       </c>
       <c r="Q315" t="n">
-        <v>442800</v>
+        <v>434600</v>
       </c>
     </row>
     <row r="316">
@@ -13894,10 +13894,10 @@
         <v>72</v>
       </c>
       <c r="N316" t="n">
-        <v>5484.9484033613</v>
+        <v>5484.9487179487</v>
       </c>
       <c r="O316" t="n">
-        <v>394916.2850420136</v>
+        <v>394916.3076923063</v>
       </c>
       <c r="P316" t="n">
         <v>8500</v>
@@ -13937,22 +13937,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M317" t="n">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="N317" t="n">
         <v>1203.38</v>
       </c>
       <c r="O317" t="n">
-        <v>1111923.12</v>
+        <v>1097482.56</v>
       </c>
       <c r="P317" t="n">
         <v>1900</v>
       </c>
       <c r="Q317" t="n">
-        <v>1755600</v>
+        <v>1732800</v>
       </c>
     </row>
     <row r="318">
@@ -13983,22 +13983,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M318" t="n">
-        <v>910</v>
+        <v>893</v>
       </c>
       <c r="N318" t="n">
         <v>3472</v>
       </c>
       <c r="O318" t="n">
-        <v>3159520</v>
+        <v>3100496</v>
       </c>
       <c r="P318" t="n">
         <v>4800</v>
       </c>
       <c r="Q318" t="n">
-        <v>4368000</v>
+        <v>4286400</v>
       </c>
     </row>
     <row r="319">
@@ -14428,22 +14428,22 @@
         <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M328" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N328" t="n">
         <v>8662</v>
       </c>
       <c r="O328" t="n">
-        <v>346480</v>
+        <v>337818</v>
       </c>
       <c r="P328" t="n">
         <v>14200</v>
       </c>
       <c r="Q328" t="n">
-        <v>568000</v>
+        <v>553800</v>
       </c>
     </row>
     <row r="329">
@@ -14515,22 +14515,22 @@
         <v>0</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M330" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N330" t="n">
         <v>10716.34</v>
       </c>
       <c r="O330" t="n">
-        <v>375071.9</v>
+        <v>278624.84</v>
       </c>
       <c r="P330" t="n">
         <v>39000</v>
       </c>
       <c r="Q330" t="n">
-        <v>1365000</v>
+        <v>1014000</v>
       </c>
     </row>
     <row r="331">
@@ -14728,22 +14728,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M335" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N335" t="n">
-        <v>3594.2541747573</v>
+        <v>3594.25414277</v>
       </c>
       <c r="O335" t="n">
-        <v>237220.7755339818</v>
+        <v>230032.26513728</v>
       </c>
       <c r="P335" t="n">
         <v>6500</v>
       </c>
       <c r="Q335" t="n">
-        <v>429000</v>
+        <v>416000</v>
       </c>
     </row>
     <row r="336">
@@ -14903,10 +14903,10 @@
         <v>244</v>
       </c>
       <c r="N339" t="n">
-        <v>3240.8500295421</v>
+        <v>3240.850029985</v>
       </c>
       <c r="O339" t="n">
-        <v>790767.4072082724</v>
+        <v>790767.40731634</v>
       </c>
       <c r="P339" t="n">
         <v>5200</v>
@@ -14989,22 +14989,22 @@
         <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N341" t="n">
         <v>8154</v>
       </c>
       <c r="O341" t="n">
-        <v>252774</v>
+        <v>244620</v>
       </c>
       <c r="P341" t="n">
         <v>13500</v>
       </c>
       <c r="Q341" t="n">
-        <v>418500</v>
+        <v>405000</v>
       </c>
     </row>
     <row r="342">
@@ -15035,22 +15035,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N342" t="n">
-        <v>14822.378864577</v>
+        <v>14822.378863905</v>
       </c>
       <c r="O342" t="n">
-        <v>652184.670041388</v>
+        <v>637362.2911479149</v>
       </c>
       <c r="P342" t="n">
         <v>24900</v>
       </c>
       <c r="Q342" t="n">
-        <v>1095600</v>
+        <v>1070700</v>
       </c>
     </row>
     <row r="343">
@@ -15117,28 +15117,28 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>464</v>
+        <v>576</v>
       </c>
       <c r="K344" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="M344" t="n">
-        <v>464</v>
+        <v>590</v>
       </c>
       <c r="N344" t="n">
         <v>2090.85</v>
       </c>
       <c r="O344" t="n">
-        <v>970154.3999999999</v>
+        <v>1233601.5</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
       </c>
       <c r="Q344" t="n">
-        <v>1345600</v>
+        <v>1711000</v>
       </c>
     </row>
     <row r="345">
@@ -15345,22 +15345,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M349" t="n">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="N349" t="n">
         <v>1381.75</v>
       </c>
       <c r="O349" t="n">
-        <v>294312.75</v>
+        <v>265296</v>
       </c>
       <c r="P349" t="n">
         <v>2500</v>
       </c>
       <c r="Q349" t="n">
-        <v>532500</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="350">
@@ -15476,22 +15476,22 @@
         <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M352" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="N352" t="n">
         <v>3309</v>
       </c>
       <c r="O352" t="n">
-        <v>281265</v>
+        <v>261411</v>
       </c>
       <c r="P352" t="n">
         <v>5900</v>
       </c>
       <c r="Q352" t="n">
-        <v>501500</v>
+        <v>466100</v>
       </c>
     </row>
     <row r="353">
@@ -15520,22 +15520,22 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M353" t="n">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="N353" t="n">
         <v>1441.01</v>
       </c>
       <c r="O353" t="n">
-        <v>838667.8199999999</v>
+        <v>830021.76</v>
       </c>
       <c r="P353" t="n">
         <v>2100</v>
       </c>
       <c r="Q353" t="n">
-        <v>1222200</v>
+        <v>1209600</v>
       </c>
     </row>
     <row r="354">
@@ -15697,22 +15697,22 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M357" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N357" t="n">
-        <v>4372.2107869318</v>
+        <v>4372.2107876031</v>
       </c>
       <c r="O357" t="n">
-        <v>480943.186562498</v>
+        <v>472198.7650611348</v>
       </c>
       <c r="P357" t="n">
         <v>7500</v>
       </c>
       <c r="Q357" t="n">
-        <v>825000</v>
+        <v>810000</v>
       </c>
     </row>
     <row r="358">
@@ -15741,22 +15741,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M358" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="N358" t="n">
         <v>6441.03</v>
       </c>
       <c r="O358" t="n">
-        <v>740718.45</v>
+        <v>714954.33</v>
       </c>
       <c r="P358" t="n">
         <v>10500</v>
       </c>
       <c r="Q358" t="n">
-        <v>1207500</v>
+        <v>1165500</v>
       </c>
     </row>
     <row r="359">
@@ -15793,10 +15793,10 @@
         <v>19</v>
       </c>
       <c r="N359" t="n">
-        <v>1592.5675881262</v>
+        <v>1592.567520267</v>
       </c>
       <c r="O359" t="n">
-        <v>30258.7841743978</v>
+        <v>30258.782885073</v>
       </c>
       <c r="P359" t="n">
         <v>3900</v>
@@ -15869,22 +15869,22 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M361" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N361" t="n">
         <v>2224.56</v>
       </c>
       <c r="O361" t="n">
-        <v>220231.44</v>
+        <v>215782.32</v>
       </c>
       <c r="P361" t="n">
         <v>3900</v>
       </c>
       <c r="Q361" t="n">
-        <v>386100</v>
+        <v>378300</v>
       </c>
     </row>
     <row r="362">
@@ -15915,22 +15915,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M362" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="N362" t="n">
         <v>3655.96</v>
       </c>
       <c r="O362" t="n">
-        <v>325380.44</v>
+        <v>303444.68</v>
       </c>
       <c r="P362" t="n">
         <v>5500</v>
       </c>
       <c r="Q362" t="n">
-        <v>489500</v>
+        <v>456500</v>
       </c>
     </row>
     <row r="363">
@@ -16007,22 +16007,22 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N364" t="n">
         <v>4717</v>
       </c>
       <c r="O364" t="n">
-        <v>23585</v>
+        <v>18868</v>
       </c>
       <c r="P364" t="n">
         <v>7900</v>
       </c>
       <c r="Q364" t="n">
-        <v>39500</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="365">
@@ -16310,22 +16310,22 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N371" t="n">
         <v>6242.93</v>
       </c>
       <c r="O371" t="n">
-        <v>630535.9300000001</v>
+        <v>624293</v>
       </c>
       <c r="P371" t="n">
         <v>10400</v>
       </c>
       <c r="Q371" t="n">
-        <v>1050400</v>
+        <v>1040000</v>
       </c>
     </row>
     <row r="372">
@@ -16359,22 +16359,22 @@
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M372" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="N372" t="n">
         <v>4648.6</v>
       </c>
       <c r="O372" t="n">
-        <v>1510795</v>
+        <v>1487552</v>
       </c>
       <c r="P372" t="n">
         <v>8900</v>
       </c>
       <c r="Q372" t="n">
-        <v>2892500</v>
+        <v>2848000</v>
       </c>
     </row>
     <row r="373">
@@ -16491,22 +16491,22 @@
         <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M375" t="n">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="N375" t="n">
         <v>1312.43</v>
       </c>
       <c r="O375" t="n">
-        <v>1081442.32</v>
+        <v>1073567.74</v>
       </c>
       <c r="P375" t="n">
         <v>2300</v>
       </c>
       <c r="Q375" t="n">
-        <v>1895200</v>
+        <v>1881400</v>
       </c>
     </row>
     <row r="376">
@@ -16576,22 +16576,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M377" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="N377" t="n">
-        <v>1532.629028858</v>
+        <v>1532.6290284343</v>
       </c>
       <c r="O377" t="n">
-        <v>508832.8375808561</v>
+        <v>499637.0632695818</v>
       </c>
       <c r="P377" t="n">
         <v>1200</v>
       </c>
       <c r="Q377" t="n">
-        <v>398400</v>
+        <v>391200</v>
       </c>
     </row>
     <row r="378">
@@ -16749,22 +16749,22 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M381" t="n">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="N381" t="n">
         <v>1647.46</v>
       </c>
       <c r="O381" t="n">
-        <v>981886.16</v>
+        <v>972001.4</v>
       </c>
       <c r="P381" t="n">
         <v>2900</v>
       </c>
       <c r="Q381" t="n">
-        <v>1728400</v>
+        <v>1711000</v>
       </c>
     </row>
     <row r="382">
@@ -16837,22 +16837,22 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M383" t="n">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="N383" t="n">
         <v>1387.55</v>
       </c>
       <c r="O383" t="n">
-        <v>740951.7</v>
+        <v>724301.1</v>
       </c>
       <c r="P383" t="n">
         <v>2300</v>
       </c>
       <c r="Q383" t="n">
-        <v>1228200</v>
+        <v>1200600</v>
       </c>
     </row>
     <row r="384">
@@ -17007,22 +17007,22 @@
         <v>0</v>
       </c>
       <c r="L387" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M387" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N387" t="n">
         <v>13304.13</v>
       </c>
       <c r="O387" t="n">
-        <v>412428.03</v>
+        <v>372515.64</v>
       </c>
       <c r="P387" t="n">
         <v>20900</v>
       </c>
       <c r="Q387" t="n">
-        <v>647900</v>
+        <v>585200</v>
       </c>
     </row>
     <row r="388">
@@ -17062,10 +17062,10 @@
         <v>1</v>
       </c>
       <c r="N388" t="n">
-        <v>16897</v>
+        <v>17010.976391231</v>
       </c>
       <c r="O388" t="n">
-        <v>16897</v>
+        <v>17010.976391231</v>
       </c>
       <c r="P388" t="n">
         <v>27900</v>
@@ -17286,22 +17286,22 @@
         <v>0</v>
       </c>
       <c r="L393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N393" t="n">
         <v>3761.6</v>
       </c>
       <c r="O393" t="n">
-        <v>282120</v>
+        <v>278358.4</v>
       </c>
       <c r="P393" t="n">
         <v>6900</v>
       </c>
       <c r="Q393" t="n">
-        <v>517500</v>
+        <v>510600</v>
       </c>
     </row>
     <row r="394">
@@ -17422,22 +17422,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N396" t="n">
         <v>11921.4</v>
       </c>
       <c r="O396" t="n">
-        <v>1609389</v>
+        <v>1597467.6</v>
       </c>
       <c r="P396" t="n">
         <v>19900</v>
       </c>
       <c r="Q396" t="n">
-        <v>2686500</v>
+        <v>2666600</v>
       </c>
     </row>
     <row r="397">
@@ -17636,22 +17636,22 @@
         <v>0</v>
       </c>
       <c r="L401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N401" t="n">
-        <v>8296.6425714286</v>
+        <v>8296.642647058799</v>
       </c>
       <c r="O401" t="n">
-        <v>107856.3534285718</v>
+        <v>99559.7117647056</v>
       </c>
       <c r="P401" t="n">
         <v>15900</v>
       </c>
       <c r="Q401" t="n">
-        <v>206700</v>
+        <v>190800</v>
       </c>
     </row>
     <row r="402">
@@ -17762,22 +17762,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M404" t="n">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="N404" t="n">
         <v>3751</v>
       </c>
       <c r="O404" t="n">
-        <v>3390904</v>
+        <v>3379651</v>
       </c>
       <c r="P404" t="n">
         <v>6400</v>
       </c>
       <c r="Q404" t="n">
-        <v>5785600</v>
+        <v>5766400</v>
       </c>
     </row>
     <row r="405">
@@ -17857,22 +17857,22 @@
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M406" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="N406" t="n">
         <v>12754</v>
       </c>
       <c r="O406" t="n">
-        <v>306096</v>
+        <v>216818</v>
       </c>
       <c r="P406" t="n">
         <v>21500</v>
       </c>
       <c r="Q406" t="n">
-        <v>516000</v>
+        <v>365500</v>
       </c>
     </row>
     <row r="407">
@@ -17903,22 +17903,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M407" t="n">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="N407" t="n">
-        <v>1630.9231064431</v>
+        <v>1630.923147125</v>
       </c>
       <c r="O407" t="n">
-        <v>1405855.717753952</v>
+        <v>1391177.444497625</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
       </c>
       <c r="Q407" t="n">
-        <v>2155000</v>
+        <v>2132500</v>
       </c>
     </row>
     <row r="408">
@@ -17990,22 +17990,22 @@
         <v>0</v>
       </c>
       <c r="L409" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M409" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N409" t="n">
-        <v>1467.3275193798</v>
+        <v>1467.327254902</v>
       </c>
       <c r="O409" t="n">
-        <v>338952.6569767338</v>
+        <v>334550.614117656</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
       </c>
       <c r="Q409" t="n">
-        <v>577500</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="410">
@@ -18036,22 +18036,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M410" t="n">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="N410" t="n">
-        <v>1690.6033768352</v>
+        <v>1690.6028354857</v>
       </c>
       <c r="O410" t="n">
-        <v>787821.1736052032</v>
+        <v>747246.4532846794</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
       </c>
       <c r="Q410" t="n">
-        <v>1351400</v>
+        <v>1281800</v>
       </c>
     </row>
     <row r="411">
@@ -18082,22 +18082,22 @@
         <v>0</v>
       </c>
       <c r="L411" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M411" t="n">
-        <v>2166</v>
+        <v>2135</v>
       </c>
       <c r="N411" t="n">
-        <v>1550.1930735465</v>
+        <v>1550.1931350849</v>
       </c>
       <c r="O411" t="n">
-        <v>3357718.197301719</v>
+        <v>3309662.343406261</v>
       </c>
       <c r="P411" t="n">
         <v>2500</v>
       </c>
       <c r="Q411" t="n">
-        <v>5415000</v>
+        <v>5337500</v>
       </c>
     </row>
     <row r="412">
@@ -18174,22 +18174,22 @@
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M413" t="n">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="N413" t="n">
-        <v>2403.5102087442</v>
+        <v>2403.5103430475</v>
       </c>
       <c r="O413" t="n">
-        <v>2562141.882521317</v>
+        <v>2554931.494659493</v>
       </c>
       <c r="P413" t="n">
         <v>3500</v>
       </c>
       <c r="Q413" t="n">
-        <v>3731000</v>
+        <v>3720500</v>
       </c>
     </row>
     <row r="414">
@@ -18226,10 +18226,10 @@
         <v>29</v>
       </c>
       <c r="N414" t="n">
-        <v>2521.5455211726</v>
+        <v>2521.5446987952</v>
       </c>
       <c r="O414" t="n">
-        <v>73124.8201140054</v>
+        <v>73124.7962650608</v>
       </c>
       <c r="P414" t="n">
         <v>3900</v>
@@ -18264,22 +18264,22 @@
         <v>0</v>
       </c>
       <c r="L415" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M415" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N415" t="n">
         <v>24267.77</v>
       </c>
       <c r="O415" t="n">
-        <v>339748.78</v>
+        <v>291213.24</v>
       </c>
       <c r="P415" t="n">
         <v>33400</v>
       </c>
       <c r="Q415" t="n">
-        <v>467600</v>
+        <v>400800</v>
       </c>
     </row>
     <row r="416">
@@ -18478,22 +18478,22 @@
         <v>0</v>
       </c>
       <c r="L420" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M420" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N420" t="n">
-        <v>1232.8081659389</v>
+        <v>1232.8080088496</v>
       </c>
       <c r="O420" t="n">
-        <v>45613.9021397393</v>
+        <v>41915.47230088639</v>
       </c>
       <c r="P420" t="n">
         <v>2400</v>
       </c>
       <c r="Q420" t="n">
-        <v>88800</v>
+        <v>81600</v>
       </c>
     </row>
     <row r="421">
@@ -20960,22 +20960,22 @@
         <v>0</v>
       </c>
       <c r="L477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N477" t="n">
         <v>9338</v>
       </c>
       <c r="O477" t="n">
-        <v>56028</v>
+        <v>46690</v>
       </c>
       <c r="P477" t="n">
         <v>15500</v>
       </c>
       <c r="Q477" t="n">
-        <v>93000</v>
+        <v>77500</v>
       </c>
     </row>
     <row r="478">
@@ -21332,22 +21332,22 @@
         <v>0</v>
       </c>
       <c r="L486" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M486" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N486" t="n">
         <v>2661.82</v>
       </c>
       <c r="O486" t="n">
-        <v>154385.56</v>
+        <v>149061.92</v>
       </c>
       <c r="P486" t="n">
         <v>3200</v>
       </c>
       <c r="Q486" t="n">
-        <v>185600</v>
+        <v>179200</v>
       </c>
     </row>
     <row r="487">
@@ -21578,22 +21578,22 @@
         <v>0</v>
       </c>
       <c r="L492" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M492" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N492" t="n">
         <v>2286.55</v>
       </c>
       <c r="O492" t="n">
-        <v>160058.5</v>
+        <v>155485.4</v>
       </c>
       <c r="P492" t="n">
         <v>3200</v>
       </c>
       <c r="Q492" t="n">
-        <v>224000</v>
+        <v>217600</v>
       </c>
     </row>
     <row r="493">
@@ -21788,22 +21788,22 @@
         <v>0</v>
       </c>
       <c r="L497" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M497" t="n">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="N497" t="n">
         <v>2567</v>
       </c>
       <c r="O497" t="n">
-        <v>942089</v>
+        <v>885615</v>
       </c>
       <c r="P497" t="n">
         <v>4500</v>
       </c>
       <c r="Q497" t="n">
-        <v>1651500</v>
+        <v>1552500</v>
       </c>
     </row>
     <row r="498">
@@ -22163,10 +22163,10 @@
         <v>476</v>
       </c>
       <c r="N506" t="n">
-        <v>2029.8736549708</v>
+        <v>2029.8736782737</v>
       </c>
       <c r="O506" t="n">
-        <v>966219.8597661009</v>
+        <v>966219.8708582813</v>
       </c>
       <c r="P506" t="n">
         <v>3600</v>
@@ -22409,10 +22409,10 @@
         <v>59</v>
       </c>
       <c r="N512" t="n">
-        <v>22485.695904437</v>
+        <v>22511.306036446</v>
       </c>
       <c r="O512" t="n">
-        <v>1326656.058361783</v>
+        <v>1328167.056150314</v>
       </c>
       <c r="P512" t="n">
         <v>36500</v>
@@ -22786,10 +22786,10 @@
         <v>1374</v>
       </c>
       <c r="N521" t="n">
-        <v>880.32933581916</v>
+        <v>880.32935107376</v>
       </c>
       <c r="O521" t="n">
-        <v>1209572.507415526</v>
+        <v>1209572.528375346</v>
       </c>
       <c r="P521" t="n">
         <v>1200</v>
@@ -24532,22 +24532,22 @@
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M562" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N562" t="n">
         <v>11980</v>
       </c>
       <c r="O562" t="n">
-        <v>335440</v>
+        <v>323460</v>
       </c>
       <c r="P562" t="n">
         <v>19500</v>
       </c>
       <c r="Q562" t="n">
-        <v>546000</v>
+        <v>526500</v>
       </c>
     </row>
     <row r="563">
@@ -24578,22 +24578,22 @@
         <v>0</v>
       </c>
       <c r="L563" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M563" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N563" t="n">
-        <v>11562.038530184</v>
+        <v>11562.038526316</v>
       </c>
       <c r="O563" t="n">
-        <v>624350.080629936</v>
+        <v>612788.041894748</v>
       </c>
       <c r="P563" t="n">
         <v>18500</v>
       </c>
       <c r="Q563" t="n">
-        <v>999000</v>
+        <v>980500</v>
       </c>
     </row>
     <row r="564">
@@ -24624,22 +24624,22 @@
         <v>0</v>
       </c>
       <c r="L564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M564" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N564" t="n">
-        <v>13513.642971014</v>
+        <v>13513.642992701</v>
       </c>
       <c r="O564" t="n">
-        <v>810818.57826084</v>
+        <v>797304.9365693589</v>
       </c>
       <c r="P564" t="n">
         <v>21900</v>
       </c>
       <c r="Q564" t="n">
-        <v>1314000</v>
+        <v>1292100</v>
       </c>
     </row>
     <row r="565">
@@ -24670,22 +24670,22 @@
         <v>0</v>
       </c>
       <c r="L565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M565" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N565" t="n">
-        <v>12005.159832636</v>
+        <v>12005.159831933</v>
       </c>
       <c r="O565" t="n">
-        <v>792340.548953976</v>
+        <v>780335.389075645</v>
       </c>
       <c r="P565" t="n">
         <v>19500</v>
       </c>
       <c r="Q565" t="n">
-        <v>1287000</v>
+        <v>1267500</v>
       </c>
     </row>
     <row r="566">
@@ -25295,22 +25295,22 @@
         <v>0</v>
       </c>
       <c r="L580" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M580" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N580" t="n">
         <v>3754</v>
       </c>
       <c r="O580" t="n">
-        <v>536822</v>
+        <v>529314</v>
       </c>
       <c r="P580" t="n">
         <v>6400</v>
       </c>
       <c r="Q580" t="n">
-        <v>915200</v>
+        <v>902400</v>
       </c>
     </row>
     <row r="581">
@@ -25930,10 +25930,10 @@
         <v>41</v>
       </c>
       <c r="N594" t="n">
-        <v>27123.765241636</v>
+        <v>27123.765232775</v>
       </c>
       <c r="O594" t="n">
-        <v>1112074.374907076</v>
+        <v>1112074.374543775</v>
       </c>
       <c r="P594" t="n">
         <v>44500</v>
@@ -26186,10 +26186,10 @@
         <v>120</v>
       </c>
       <c r="N600" t="n">
-        <v>5431.12</v>
+        <v>5465.2779874214</v>
       </c>
       <c r="O600" t="n">
-        <v>651734.4</v>
+        <v>655833.358490568</v>
       </c>
       <c r="P600" t="n">
         <v>8900</v>
@@ -26267,22 +26267,22 @@
         <v>0</v>
       </c>
       <c r="L602" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M602" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N602" t="n">
-        <v>1560.9991607397</v>
+        <v>1560.999261745</v>
       </c>
       <c r="O602" t="n">
-        <v>179514.9034850655</v>
+        <v>177953.91583893</v>
       </c>
       <c r="P602" t="n">
         <v>2900</v>
       </c>
       <c r="Q602" t="n">
-        <v>333500</v>
+        <v>330600</v>
       </c>
     </row>
     <row r="603">
@@ -26482,22 +26482,22 @@
         <v>0</v>
       </c>
       <c r="L607" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N607" t="n">
         <v>2214.48</v>
       </c>
       <c r="O607" t="n">
-        <v>2214.48</v>
+        <v>0</v>
       </c>
       <c r="P607" t="n">
         <v>4700</v>
       </c>
       <c r="Q607" t="n">
-        <v>4700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="608">
@@ -26583,10 +26583,10 @@
         <v>141</v>
       </c>
       <c r="N609" t="n">
-        <v>7969.9501649175</v>
+        <v>7987.9139894816</v>
       </c>
       <c r="O609" t="n">
-        <v>1123762.973253367</v>
+        <v>1126295.872516906</v>
       </c>
       <c r="P609" t="n">
         <v>12900</v>
@@ -27723,22 +27723,22 @@
         <v>0</v>
       </c>
       <c r="L636" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M636" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N636" t="n">
-        <v>7374</v>
+        <v>0</v>
       </c>
       <c r="O636" t="n">
-        <v>29496</v>
+        <v>0</v>
       </c>
       <c r="P636" t="n">
         <v>12600</v>
       </c>
       <c r="Q636" t="n">
-        <v>50400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="637">
@@ -27769,22 +27769,22 @@
         <v>0</v>
       </c>
       <c r="L637" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M637" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N637" t="n">
         <v>5164.33</v>
       </c>
       <c r="O637" t="n">
-        <v>516433</v>
+        <v>506104.34</v>
       </c>
       <c r="P637" t="n">
         <v>10200</v>
       </c>
       <c r="Q637" t="n">
-        <v>1020000</v>
+        <v>999600</v>
       </c>
     </row>
     <row r="638">
@@ -27943,22 +27943,22 @@
         <v>0</v>
       </c>
       <c r="L641" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M641" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N641" t="n">
         <v>2634.61</v>
       </c>
       <c r="O641" t="n">
-        <v>115922.84</v>
+        <v>108019.01</v>
       </c>
       <c r="P641" t="n">
         <v>4200</v>
       </c>
       <c r="Q641" t="n">
-        <v>184800</v>
+        <v>172200</v>
       </c>
     </row>
     <row r="642">
@@ -27995,10 +27995,10 @@
         <v>71</v>
       </c>
       <c r="N642" t="n">
-        <v>3113.8900261438</v>
+        <v>3113.8900262812</v>
       </c>
       <c r="O642" t="n">
-        <v>221086.1918562098</v>
+        <v>221086.1918659652</v>
       </c>
       <c r="P642" t="n">
         <v>5000</v>
@@ -28173,22 +28173,22 @@
         <v>0</v>
       </c>
       <c r="L646" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M646" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N646" t="n">
-        <v>4163.1601724138</v>
+        <v>4163.1601818182</v>
       </c>
       <c r="O646" t="n">
-        <v>79100.0432758622</v>
+        <v>62447.40272727299</v>
       </c>
       <c r="P646" t="n">
         <v>6700</v>
       </c>
       <c r="Q646" t="n">
-        <v>127300</v>
+        <v>100500</v>
       </c>
     </row>
     <row r="647">
@@ -28219,22 +28219,22 @@
         <v>0</v>
       </c>
       <c r="L647" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M647" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="N647" t="n">
         <v>8878.450000000001</v>
       </c>
       <c r="O647" t="n">
-        <v>674762.2000000001</v>
+        <v>559342.3500000001</v>
       </c>
       <c r="P647" t="n">
         <v>14100</v>
       </c>
       <c r="Q647" t="n">
-        <v>1071600</v>
+        <v>888300</v>
       </c>
     </row>
     <row r="648">
@@ -28265,22 +28265,22 @@
         <v>0</v>
       </c>
       <c r="L648" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M648" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N648" t="n">
         <v>2495.98</v>
       </c>
       <c r="O648" t="n">
-        <v>87359.3</v>
+        <v>79871.36</v>
       </c>
       <c r="P648" t="n">
         <v>4100</v>
       </c>
       <c r="Q648" t="n">
-        <v>143500</v>
+        <v>131200</v>
       </c>
     </row>
     <row r="649">
@@ -28357,22 +28357,22 @@
         <v>0</v>
       </c>
       <c r="L650" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M650" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N650" t="n">
-        <v>5218.1705022831</v>
+        <v>5218.1705134189</v>
       </c>
       <c r="O650" t="n">
-        <v>125236.0920547944</v>
+        <v>109581.5807817969</v>
       </c>
       <c r="P650" t="n">
         <v>8500</v>
       </c>
       <c r="Q650" t="n">
-        <v>204000</v>
+        <v>178500</v>
       </c>
     </row>
     <row r="651">
@@ -28409,10 +28409,10 @@
         <v>140</v>
       </c>
       <c r="N651" t="n">
-        <v>1595.0094808743</v>
+        <v>1595.0094571429</v>
       </c>
       <c r="O651" t="n">
-        <v>223301.327322402</v>
+        <v>223301.324000006</v>
       </c>
       <c r="P651" t="n">
         <v>2600</v>
@@ -28455,10 +28455,10 @@
         <v>81</v>
       </c>
       <c r="N652" t="n">
-        <v>3610.6500238663</v>
+        <v>3610.6500248756</v>
       </c>
       <c r="O652" t="n">
-        <v>292462.6519331703</v>
+        <v>292462.6520149236</v>
       </c>
       <c r="P652" t="n">
         <v>5800</v>
@@ -28541,22 +28541,22 @@
         <v>0</v>
       </c>
       <c r="L654" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M654" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="N654" t="n">
         <v>4227.77</v>
       </c>
       <c r="O654" t="n">
-        <v>257893.97</v>
+        <v>240982.89</v>
       </c>
       <c r="P654" t="n">
         <v>6900</v>
       </c>
       <c r="Q654" t="n">
-        <v>420900</v>
+        <v>393300</v>
       </c>
     </row>
     <row r="655">
@@ -28869,10 +28869,10 @@
         <v>406</v>
       </c>
       <c r="N661" t="n">
-        <v>1664.360187234</v>
+        <v>1664.359264432</v>
       </c>
       <c r="O661" t="n">
-        <v>675730.236017004</v>
+        <v>675729.8613593919</v>
       </c>
       <c r="P661" t="n">
         <v>2900</v>
@@ -28909,22 +28909,22 @@
         <v>0</v>
       </c>
       <c r="L662" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M662" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N662" t="n">
         <v>15502</v>
       </c>
       <c r="O662" t="n">
-        <v>1131646</v>
+        <v>1116144</v>
       </c>
       <c r="P662" t="n">
         <v>25900</v>
       </c>
       <c r="Q662" t="n">
-        <v>1890700</v>
+        <v>1864800</v>
       </c>
     </row>
     <row r="663">
@@ -29197,10 +29197,10 @@
         <v>29</v>
       </c>
       <c r="N668" t="n">
-        <v>15824</v>
+        <v>15908.394666667</v>
       </c>
       <c r="O668" t="n">
-        <v>458896</v>
+        <v>461343.445333343</v>
       </c>
       <c r="P668" t="n">
         <v>26900</v>
@@ -29375,22 +29375,22 @@
         <v>0</v>
       </c>
       <c r="L672" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M672" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N672" t="n">
         <v>3646</v>
       </c>
       <c r="O672" t="n">
-        <v>510440</v>
+        <v>495856</v>
       </c>
       <c r="P672" t="n">
         <v>6900</v>
       </c>
       <c r="Q672" t="n">
-        <v>966000</v>
+        <v>938400</v>
       </c>
     </row>
     <row r="673">
@@ -29427,10 +29427,10 @@
         <v>4</v>
       </c>
       <c r="N673" t="n">
-        <v>23521.624776119</v>
+        <v>23878.013030303</v>
       </c>
       <c r="O673" t="n">
-        <v>94086.499104476</v>
+        <v>95512.05212121199</v>
       </c>
       <c r="P673" t="n">
         <v>39000</v>
@@ -29473,10 +29473,10 @@
         <v>96</v>
       </c>
       <c r="N674" t="n">
-        <v>3486</v>
+        <v>3502.5901249256</v>
       </c>
       <c r="O674" t="n">
-        <v>334656</v>
+        <v>336248.6519928576</v>
       </c>
       <c r="P674" t="n">
         <v>6900</v>
@@ -29513,22 +29513,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M675" t="n">
-        <v>1517</v>
+        <v>1508</v>
       </c>
       <c r="N675" t="n">
-        <v>1778.4725489051</v>
+        <v>1786.8332290289</v>
       </c>
       <c r="O675" t="n">
-        <v>2697942.856689037</v>
+        <v>2694544.509375581</v>
       </c>
       <c r="P675" t="n">
         <v>4900</v>
       </c>
       <c r="Q675" t="n">
-        <v>7433300</v>
+        <v>7389200</v>
       </c>
     </row>
     <row r="676">
@@ -29559,22 +29559,22 @@
         <v>0</v>
       </c>
       <c r="L676" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M676" t="n">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="N676" t="n">
         <v>1548</v>
       </c>
       <c r="O676" t="n">
-        <v>470592</v>
+        <v>445824</v>
       </c>
       <c r="P676" t="n">
         <v>3900</v>
       </c>
       <c r="Q676" t="n">
-        <v>1185600</v>
+        <v>1123200</v>
       </c>
     </row>
     <row r="677">
@@ -29605,22 +29605,22 @@
         <v>0</v>
       </c>
       <c r="L677" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M677" t="n">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="N677" t="n">
         <v>2325</v>
       </c>
       <c r="O677" t="n">
-        <v>1176450</v>
+        <v>1162500</v>
       </c>
       <c r="P677" t="n">
         <v>4900</v>
       </c>
       <c r="Q677" t="n">
-        <v>2479400</v>
+        <v>2450000</v>
       </c>
     </row>
     <row r="678">
@@ -30569,22 +30569,22 @@
         <v>0</v>
       </c>
       <c r="L698" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M698" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N698" t="n">
         <v>1817</v>
       </c>
       <c r="O698" t="n">
-        <v>285269</v>
+        <v>283452</v>
       </c>
       <c r="P698" t="n">
         <v>3100</v>
       </c>
       <c r="Q698" t="n">
-        <v>486700</v>
+        <v>483600</v>
       </c>
     </row>
     <row r="699">
@@ -30896,22 +30896,22 @@
         <v>0</v>
       </c>
       <c r="L705" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M705" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N705" t="n">
         <v>2720</v>
       </c>
       <c r="O705" t="n">
-        <v>8160</v>
+        <v>0</v>
       </c>
       <c r="P705" t="n">
         <v>4500</v>
       </c>
       <c r="Q705" t="n">
-        <v>13500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="706">
@@ -31503,10 +31503,10 @@
         <v>70</v>
       </c>
       <c r="N718" t="n">
-        <v>7713</v>
+        <v>7735.3565217391</v>
       </c>
       <c r="O718" t="n">
-        <v>539910</v>
+        <v>541474.9565217369</v>
       </c>
       <c r="P718" t="n">
         <v>12500</v>
@@ -31770,25 +31770,25 @@
         <v>271</v>
       </c>
       <c r="K724" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L724" t="n">
         <v>0</v>
       </c>
       <c r="M724" t="n">
-        <v>271</v>
+        <v>367</v>
       </c>
       <c r="N724" t="n">
         <v>8858.16</v>
       </c>
       <c r="O724" t="n">
-        <v>2400561.36</v>
+        <v>3250944.72</v>
       </c>
       <c r="P724" t="n">
         <v>15500</v>
       </c>
       <c r="Q724" t="n">
-        <v>4200500</v>
+        <v>5688500</v>
       </c>
     </row>
     <row r="725">
@@ -32009,10 +32009,10 @@
         <v>74</v>
       </c>
       <c r="N729" t="n">
-        <v>13019</v>
+        <v>13090.336986301</v>
       </c>
       <c r="O729" t="n">
-        <v>963406</v>
+        <v>968684.936986274</v>
       </c>
       <c r="P729" t="n">
         <v>20900</v>
@@ -32461,22 +32461,22 @@
         <v>0</v>
       </c>
       <c r="L739" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M739" t="n">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="N739" t="n">
-        <v>2328.1187507401</v>
+        <v>2328.1187488882</v>
       </c>
       <c r="O739" t="n">
-        <v>1632011.24426881</v>
+        <v>1620370.649226187</v>
       </c>
       <c r="P739" t="n">
         <v>4500</v>
       </c>
       <c r="Q739" t="n">
-        <v>3154500</v>
+        <v>3132000</v>
       </c>
     </row>
     <row r="740">
@@ -32691,22 +32691,22 @@
         <v>0</v>
       </c>
       <c r="L744" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M744" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N744" t="n">
         <v>16946</v>
       </c>
       <c r="O744" t="n">
-        <v>50838</v>
+        <v>16946</v>
       </c>
       <c r="P744" t="n">
         <v>27500</v>
       </c>
       <c r="Q744" t="n">
-        <v>82500</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="745">
@@ -33059,22 +33059,22 @@
         <v>0</v>
       </c>
       <c r="L752" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M752" t="n">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="N752" t="n">
         <v>4544</v>
       </c>
       <c r="O752" t="n">
-        <v>1476800</v>
+        <v>1463168</v>
       </c>
       <c r="P752" t="n">
         <v>7900</v>
       </c>
       <c r="Q752" t="n">
-        <v>2567500</v>
+        <v>2543800</v>
       </c>
     </row>
     <row r="753">
@@ -33295,10 +33295,10 @@
         <v>18</v>
       </c>
       <c r="N757" t="n">
-        <v>4907.8219330289</v>
+        <v>4907.821941896</v>
       </c>
       <c r="O757" t="n">
-        <v>88340.7947945202</v>
+        <v>88340.794954128</v>
       </c>
       <c r="P757" t="n">
         <v>8200</v>
@@ -33341,10 +33341,10 @@
         <v>189</v>
       </c>
       <c r="N758" t="n">
-        <v>6414</v>
+        <v>6426.7641791045</v>
       </c>
       <c r="O758" t="n">
-        <v>1212246</v>
+        <v>1214658.42985075</v>
       </c>
       <c r="P758" t="n">
         <v>10900</v>
@@ -33381,22 +33381,22 @@
         <v>0</v>
       </c>
       <c r="L759" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M759" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N759" t="n">
         <v>13210</v>
       </c>
       <c r="O759" t="n">
-        <v>2232490</v>
+        <v>2206070</v>
       </c>
       <c r="P759" t="n">
         <v>23900</v>
       </c>
       <c r="Q759" t="n">
-        <v>4039100</v>
+        <v>3991300</v>
       </c>
     </row>
     <row r="760">
@@ -33565,22 +33565,22 @@
         <v>0</v>
       </c>
       <c r="L763" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M763" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N763" t="n">
-        <v>3903.7361538462</v>
+        <v>3903.7361658031</v>
       </c>
       <c r="O763" t="n">
-        <v>402084.8238461586</v>
+        <v>398181.0889119162</v>
       </c>
       <c r="P763" t="n">
         <v>7500</v>
       </c>
       <c r="Q763" t="n">
-        <v>772500</v>
+        <v>765000</v>
       </c>
     </row>
     <row r="764">
@@ -33698,22 +33698,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M766" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N766" t="n">
         <v>12113</v>
       </c>
       <c r="O766" t="n">
-        <v>581424</v>
+        <v>557198</v>
       </c>
       <c r="P766" t="n">
         <v>19900</v>
       </c>
       <c r="Q766" t="n">
-        <v>955200</v>
+        <v>915400</v>
       </c>
     </row>
     <row r="767">
@@ -33842,10 +33842,10 @@
         <v>65</v>
       </c>
       <c r="N769" t="n">
-        <v>4202</v>
+        <v>4235.616</v>
       </c>
       <c r="O769" t="n">
-        <v>273130</v>
+        <v>275315.04</v>
       </c>
       <c r="P769" t="n">
         <v>7900</v>
@@ -34020,22 +34020,22 @@
         <v>0</v>
       </c>
       <c r="L773" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M773" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N773" t="n">
         <v>9839</v>
       </c>
       <c r="O773" t="n">
-        <v>747764</v>
+        <v>737925</v>
       </c>
       <c r="P773" t="n">
         <v>16900</v>
       </c>
       <c r="Q773" t="n">
-        <v>1284400</v>
+        <v>1267500</v>
       </c>
     </row>
     <row r="774">
@@ -34072,10 +34072,10 @@
         <v>96</v>
       </c>
       <c r="N774" t="n">
-        <v>2629</v>
+        <v>2655.7582697201</v>
       </c>
       <c r="O774" t="n">
-        <v>252384</v>
+        <v>254952.7938931296</v>
       </c>
       <c r="P774" t="n">
         <v>4500</v>
@@ -34250,22 +34250,22 @@
         <v>0</v>
       </c>
       <c r="L778" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M778" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N778" t="n">
-        <v>5772</v>
+        <v>5789.4673839946</v>
       </c>
       <c r="O778" t="n">
-        <v>842712</v>
+        <v>833683.3032952223</v>
       </c>
       <c r="P778" t="n">
         <v>9900</v>
       </c>
       <c r="Q778" t="n">
-        <v>1445400</v>
+        <v>1425600</v>
       </c>
     </row>
     <row r="779">
@@ -34296,22 +34296,22 @@
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M779" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N779" t="n">
         <v>6268</v>
       </c>
       <c r="O779" t="n">
-        <v>689480</v>
+        <v>676944</v>
       </c>
       <c r="P779" t="n">
         <v>10900</v>
       </c>
       <c r="Q779" t="n">
-        <v>1199000</v>
+        <v>1177200</v>
       </c>
     </row>
     <row r="780">
@@ -34382,7 +34382,7 @@
         </is>
       </c>
       <c r="J781" t="n">
-        <v>391</v>
+        <v>247</v>
       </c>
       <c r="K781" t="n">
         <v>0</v>
@@ -34391,19 +34391,19 @@
         <v>0</v>
       </c>
       <c r="M781" t="n">
-        <v>391</v>
+        <v>247</v>
       </c>
       <c r="N781" t="n">
-        <v>6645</v>
+        <v>6663.0865541644</v>
       </c>
       <c r="O781" t="n">
-        <v>2598195</v>
+        <v>1645782.378878607</v>
       </c>
       <c r="P781" t="n">
         <v>10900</v>
       </c>
       <c r="Q781" t="n">
-        <v>4261900</v>
+        <v>2692300</v>
       </c>
     </row>
     <row r="782">
@@ -34431,25 +34431,25 @@
         <v>37</v>
       </c>
       <c r="K782" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L782" t="n">
         <v>0</v>
       </c>
       <c r="M782" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="N782" t="n">
-        <v>13098</v>
+        <v>13167.485411141</v>
       </c>
       <c r="O782" t="n">
-        <v>484626</v>
+        <v>1277246.084880677</v>
       </c>
       <c r="P782" t="n">
         <v>21200</v>
       </c>
       <c r="Q782" t="n">
-        <v>784400</v>
+        <v>2056400</v>
       </c>
     </row>
     <row r="783">
@@ -34572,22 +34572,22 @@
         <v>0</v>
       </c>
       <c r="L785" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M785" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N785" t="n">
         <v>7562</v>
       </c>
       <c r="O785" t="n">
-        <v>461282</v>
+        <v>453720</v>
       </c>
       <c r="P785" t="n">
         <v>12900</v>
       </c>
       <c r="Q785" t="n">
-        <v>786900</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="786">
@@ -34624,10 +34624,10 @@
         <v>295</v>
       </c>
       <c r="N786" t="n">
-        <v>3898</v>
+        <v>3913.1437451437</v>
       </c>
       <c r="O786" t="n">
-        <v>1149910</v>
+        <v>1154377.404817391</v>
       </c>
       <c r="P786" t="n">
         <v>6900</v>
@@ -34802,22 +34802,22 @@
         <v>0</v>
       </c>
       <c r="L790" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M790" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N790" t="n">
         <v>5438</v>
       </c>
       <c r="O790" t="n">
-        <v>217520</v>
+        <v>206644</v>
       </c>
       <c r="P790" t="n">
         <v>8900</v>
       </c>
       <c r="Q790" t="n">
-        <v>356000</v>
+        <v>338200</v>
       </c>
     </row>
     <row r="791">
@@ -35127,22 +35127,22 @@
         <v>0</v>
       </c>
       <c r="L797" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M797" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N797" t="n">
         <v>11348</v>
       </c>
       <c r="O797" t="n">
-        <v>453920</v>
+        <v>442572</v>
       </c>
       <c r="P797" t="n">
         <v>19900</v>
       </c>
       <c r="Q797" t="n">
-        <v>796000</v>
+        <v>776100</v>
       </c>
     </row>
     <row r="798">
@@ -35536,22 +35536,22 @@
         <v>0</v>
       </c>
       <c r="L806" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M806" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="N806" t="n">
         <v>18001</v>
       </c>
       <c r="O806" t="n">
-        <v>504028</v>
+        <v>144008</v>
       </c>
       <c r="P806" t="n">
         <v>28900</v>
       </c>
       <c r="Q806" t="n">
-        <v>809200</v>
+        <v>231200</v>
       </c>
     </row>
     <row r="807">
@@ -35582,22 +35582,22 @@
         <v>0</v>
       </c>
       <c r="L807" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M807" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="N807" t="n">
-        <v>10219</v>
+        <v>10293.773170732</v>
       </c>
       <c r="O807" t="n">
-        <v>684673</v>
+        <v>483807.339024404</v>
       </c>
       <c r="P807" t="n">
         <v>16900</v>
       </c>
       <c r="Q807" t="n">
-        <v>1132300</v>
+        <v>794300</v>
       </c>
     </row>
     <row r="808">
@@ -35775,10 +35775,10 @@
         <v>91</v>
       </c>
       <c r="N811" t="n">
-        <v>27254</v>
+        <v>27323.703324808</v>
       </c>
       <c r="O811" t="n">
-        <v>2480114</v>
+        <v>2486457.002557528</v>
       </c>
       <c r="P811" t="n">
         <v>43900</v>
@@ -35861,22 +35861,22 @@
         <v>0</v>
       </c>
       <c r="L813" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M813" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N813" t="n">
-        <v>4268.7041295547</v>
+        <v>4268.7044813278</v>
       </c>
       <c r="O813" t="n">
-        <v>388452.0757894777</v>
+        <v>362839.880912863</v>
       </c>
       <c r="P813" t="n">
         <v>6900</v>
       </c>
       <c r="Q813" t="n">
-        <v>627900</v>
+        <v>586500</v>
       </c>
     </row>
     <row r="814">
@@ -35907,22 +35907,22 @@
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M814" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N814" t="n">
         <v>5215</v>
       </c>
       <c r="O814" t="n">
-        <v>469350</v>
+        <v>458920</v>
       </c>
       <c r="P814" t="n">
         <v>8900</v>
       </c>
       <c r="Q814" t="n">
-        <v>801000</v>
+        <v>783200</v>
       </c>
     </row>
     <row r="815">
@@ -36229,22 +36229,22 @@
         <v>0</v>
       </c>
       <c r="L821" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M821" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N821" t="n">
         <v>8700</v>
       </c>
       <c r="O821" t="n">
-        <v>687300</v>
+        <v>669900</v>
       </c>
       <c r="P821" t="n">
         <v>14900</v>
       </c>
       <c r="Q821" t="n">
-        <v>1177100</v>
+        <v>1147300</v>
       </c>
     </row>
     <row r="822">
@@ -36275,22 +36275,22 @@
         <v>0</v>
       </c>
       <c r="L822" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M822" t="n">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="N822" t="n">
         <v>1326</v>
       </c>
       <c r="O822" t="n">
-        <v>1524900</v>
+        <v>1520922</v>
       </c>
       <c r="P822" t="n">
         <v>2500</v>
       </c>
       <c r="Q822" t="n">
-        <v>2875000</v>
+        <v>2867500</v>
       </c>
     </row>
     <row r="823">
@@ -36413,22 +36413,22 @@
         <v>0</v>
       </c>
       <c r="L825" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M825" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N825" t="n">
-        <v>3821</v>
+        <v>3828.7583756345</v>
       </c>
       <c r="O825" t="n">
-        <v>832978</v>
+        <v>819354.292385783</v>
       </c>
       <c r="P825" t="n">
         <v>5900</v>
       </c>
       <c r="Q825" t="n">
-        <v>1286200</v>
+        <v>1262600</v>
       </c>
     </row>
     <row r="826">
@@ -36551,22 +36551,22 @@
         <v>0</v>
       </c>
       <c r="L828" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M828" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N828" t="n">
         <v>7253</v>
       </c>
       <c r="O828" t="n">
-        <v>471445</v>
+        <v>449686</v>
       </c>
       <c r="P828" t="n">
         <v>11900</v>
       </c>
       <c r="Q828" t="n">
-        <v>773500</v>
+        <v>737800</v>
       </c>
     </row>
     <row r="829">
@@ -36597,22 +36597,22 @@
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M829" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N829" t="n">
         <v>4118</v>
       </c>
       <c r="O829" t="n">
-        <v>420036</v>
+        <v>411800</v>
       </c>
       <c r="P829" t="n">
         <v>6900</v>
       </c>
       <c r="Q829" t="n">
-        <v>703800</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="830">
@@ -36643,22 +36643,22 @@
         <v>0</v>
       </c>
       <c r="L830" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M830" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="N830" t="n">
-        <v>5476</v>
+        <v>5504.4467532468</v>
       </c>
       <c r="O830" t="n">
-        <v>2518960</v>
+        <v>2510027.719480541</v>
       </c>
       <c r="P830" t="n">
         <v>8900</v>
       </c>
       <c r="Q830" t="n">
-        <v>4094000</v>
+        <v>4058400</v>
       </c>
     </row>
     <row r="831">
@@ -36784,22 +36784,22 @@
         <v>0</v>
       </c>
       <c r="L833" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M833" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="N833" t="n">
         <v>1803</v>
       </c>
       <c r="O833" t="n">
-        <v>364206</v>
+        <v>349782</v>
       </c>
       <c r="P833" t="n">
         <v>3900</v>
       </c>
       <c r="Q833" t="n">
-        <v>787800</v>
+        <v>756600</v>
       </c>
     </row>
     <row r="834">
@@ -36928,10 +36928,10 @@
         <v>604</v>
       </c>
       <c r="N836" t="n">
-        <v>1516.0388129219</v>
+        <v>1517.7951815022</v>
       </c>
       <c r="O836" t="n">
-        <v>915687.4430048276</v>
+        <v>916748.2896273287</v>
       </c>
       <c r="P836" t="n">
         <v>2300</v>
@@ -36968,22 +36968,22 @@
         <v>0</v>
       </c>
       <c r="L837" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M837" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="N837" t="n">
-        <v>4248.6214117647</v>
+        <v>4248.6224691358</v>
       </c>
       <c r="O837" t="n">
-        <v>616050.1047058814</v>
+        <v>565066.7883950614</v>
       </c>
       <c r="P837" t="n">
         <v>5900</v>
       </c>
       <c r="Q837" t="n">
-        <v>855500</v>
+        <v>784700</v>
       </c>
     </row>
     <row r="838">
@@ -37064,10 +37064,10 @@
         <v>363</v>
       </c>
       <c r="N839" t="n">
-        <v>2458.5134204724</v>
+        <v>2458.5134059343</v>
       </c>
       <c r="O839" t="n">
-        <v>892440.3716314812</v>
+        <v>892440.3663541509</v>
       </c>
       <c r="P839" t="n">
         <v>3500</v>
@@ -37110,10 +37110,10 @@
         <v>191</v>
       </c>
       <c r="N840" t="n">
-        <v>1907.3944245524</v>
+        <v>1907.3942832168</v>
       </c>
       <c r="O840" t="n">
-        <v>364312.3350895084</v>
+        <v>364312.3080944088</v>
       </c>
       <c r="P840" t="n">
         <v>2500</v>
@@ -37156,10 +37156,10 @@
         <v>189</v>
       </c>
       <c r="N841" t="n">
-        <v>1771.0912628399</v>
+        <v>1771.0911342735</v>
       </c>
       <c r="O841" t="n">
-        <v>334736.2486767411</v>
+        <v>334736.2243776915</v>
       </c>
       <c r="P841" t="n">
         <v>2500</v>
@@ -37202,10 +37202,10 @@
         <v>419</v>
       </c>
       <c r="N842" t="n">
-        <v>2079.384205911</v>
+        <v>2079.3842021449</v>
       </c>
       <c r="O842" t="n">
-        <v>871261.9822767091</v>
+        <v>871261.9806987131</v>
       </c>
       <c r="P842" t="n">
         <v>2900</v>
@@ -37242,22 +37242,22 @@
         <v>0</v>
       </c>
       <c r="L843" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M843" t="n">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="N843" t="n">
-        <v>1803.0150073855</v>
+        <v>1803.0151441578</v>
       </c>
       <c r="O843" t="n">
-        <v>795129.6182570055</v>
+        <v>787917.6179969587</v>
       </c>
       <c r="P843" t="n">
         <v>2500</v>
       </c>
       <c r="Q843" t="n">
-        <v>1102500</v>
+        <v>1092500</v>
       </c>
     </row>
     <row r="844">
@@ -37294,10 +37294,10 @@
         <v>72</v>
       </c>
       <c r="N844" t="n">
-        <v>3306.5954372624</v>
+        <v>3306.5953548387</v>
       </c>
       <c r="O844" t="n">
-        <v>238074.8714828928</v>
+        <v>238074.8655483864</v>
       </c>
       <c r="P844" t="n">
         <v>4900</v>
@@ -37340,10 +37340,10 @@
         <v>441</v>
       </c>
       <c r="N845" t="n">
-        <v>2122.1640959855</v>
+        <v>2126.0638621746</v>
       </c>
       <c r="O845" t="n">
-        <v>935874.3663296055</v>
+        <v>937594.1632189987</v>
       </c>
       <c r="P845" t="n">
         <v>2900</v>
@@ -37380,22 +37380,22 @@
         <v>0</v>
       </c>
       <c r="L846" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M846" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N846" t="n">
-        <v>2108.7899091941</v>
+        <v>2108.7899828473</v>
       </c>
       <c r="O846" t="n">
-        <v>90677.96609534629</v>
+        <v>86460.3892967393</v>
       </c>
       <c r="P846" t="n">
         <v>2900</v>
       </c>
       <c r="Q846" t="n">
-        <v>124700</v>
+        <v>118900</v>
       </c>
     </row>
     <row r="847">
@@ -37432,10 +37432,10 @@
         <v>908</v>
       </c>
       <c r="N847" t="n">
-        <v>2056.083871734</v>
+        <v>2059.7554464286</v>
       </c>
       <c r="O847" t="n">
-        <v>1866924.155534472</v>
+        <v>1870257.945357169</v>
       </c>
       <c r="P847" t="n">
         <v>2900</v>
@@ -37478,10 +37478,10 @@
         <v>249</v>
       </c>
       <c r="N848" t="n">
-        <v>3224.5680666967</v>
+        <v>3224.5682755432</v>
       </c>
       <c r="O848" t="n">
-        <v>802917.4486074783</v>
+        <v>802917.5006102568</v>
       </c>
       <c r="P848" t="n">
         <v>4500</v>
@@ -37524,10 +37524,10 @@
         <v>455</v>
       </c>
       <c r="N849" t="n">
-        <v>1655.9312964128</v>
+        <v>1657.5320592975</v>
       </c>
       <c r="O849" t="n">
-        <v>753448.739867824</v>
+        <v>754177.0869803624</v>
       </c>
       <c r="P849" t="n">
         <v>2500</v>
@@ -37751,22 +37751,22 @@
         <v>0</v>
       </c>
       <c r="L854" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M854" t="n">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="N854" t="n">
         <v>1662</v>
       </c>
       <c r="O854" t="n">
-        <v>1103568</v>
+        <v>1086948</v>
       </c>
       <c r="P854" t="n">
         <v>2900</v>
       </c>
       <c r="Q854" t="n">
-        <v>1925600</v>
+        <v>1896600</v>
       </c>
     </row>
     <row r="855">
@@ -37889,22 +37889,22 @@
         <v>0</v>
       </c>
       <c r="L857" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M857" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="N857" t="n">
-        <v>1592.2752659892</v>
+        <v>1592.2754925187</v>
       </c>
       <c r="O857" t="n">
-        <v>199034.40824865</v>
+        <v>187888.5081172066</v>
       </c>
       <c r="P857" t="n">
         <v>2500</v>
       </c>
       <c r="Q857" t="n">
-        <v>312500</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="858">
@@ -37939,10 +37939,10 @@
         <v>5</v>
       </c>
       <c r="N858" t="n">
-        <v>5347.73</v>
+        <v>5393.6332618026</v>
       </c>
       <c r="O858" t="n">
-        <v>26738.65</v>
+        <v>26968.166309013</v>
       </c>
       <c r="P858" t="n">
         <v>9500</v>
@@ -37985,10 +37985,10 @@
         <v>63</v>
       </c>
       <c r="N859" t="n">
-        <v>2311.9257410562</v>
+        <v>2311.9248916968</v>
       </c>
       <c r="O859" t="n">
-        <v>145651.3216865406</v>
+        <v>145651.2681768984</v>
       </c>
       <c r="P859" t="n">
         <v>3500</v>
@@ -38031,10 +38031,10 @@
         <v>61</v>
       </c>
       <c r="N860" t="n">
-        <v>1906.1864705882</v>
+        <v>1906.1862686567</v>
       </c>
       <c r="O860" t="n">
-        <v>116277.3747058802</v>
+        <v>116277.3623880587</v>
       </c>
       <c r="P860" t="n">
         <v>2900</v>
@@ -38071,22 +38071,22 @@
         <v>0</v>
       </c>
       <c r="L861" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M861" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N861" t="n">
-        <v>2060.1606493506</v>
+        <v>2060.1606035889</v>
       </c>
       <c r="O861" t="n">
-        <v>208076.2255844106</v>
+        <v>201895.7391517122</v>
       </c>
       <c r="P861" t="n">
         <v>2900</v>
       </c>
       <c r="Q861" t="n">
-        <v>292900</v>
+        <v>284200</v>
       </c>
     </row>
     <row r="862">
@@ -38123,10 +38123,10 @@
         <v>75</v>
       </c>
       <c r="N862" t="n">
-        <v>2546.9851535836</v>
+        <v>2546.9851286449</v>
       </c>
       <c r="O862" t="n">
-        <v>191023.88651877</v>
+        <v>191023.8846483675</v>
       </c>
       <c r="P862" t="n">
         <v>3900</v>
@@ -38169,10 +38169,10 @@
         <v>281</v>
       </c>
       <c r="N863" t="n">
-        <v>1259.2744247206</v>
+        <v>1259.2744276316</v>
       </c>
       <c r="O863" t="n">
-        <v>353856.1133464886</v>
+        <v>353856.1141644796</v>
       </c>
       <c r="P863" t="n">
         <v>1900</v>
@@ -38255,22 +38255,22 @@
         <v>0</v>
       </c>
       <c r="L865" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M865" t="n">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="N865" t="n">
-        <v>1801</v>
+        <v>1803.2544202785</v>
       </c>
       <c r="O865" t="n">
-        <v>1082401</v>
+        <v>1062116.853544036</v>
       </c>
       <c r="P865" t="n">
         <v>2900</v>
       </c>
       <c r="Q865" t="n">
-        <v>1742900</v>
+        <v>1708100</v>
       </c>
     </row>
     <row r="866">
@@ -38305,10 +38305,10 @@
         <v>109</v>
       </c>
       <c r="N866" t="n">
-        <v>692.15206356312</v>
+        <v>692.15208975521</v>
       </c>
       <c r="O866" t="n">
-        <v>75444.57492838008</v>
+        <v>75444.57778331789</v>
       </c>
       <c r="P866" t="n">
         <v>1200</v>
@@ -39044,10 +39044,10 @@
         <v>467</v>
       </c>
       <c r="N882" t="n">
-        <v>2857.22</v>
+        <v>2865.3179310345</v>
       </c>
       <c r="O882" t="n">
-        <v>1334321.74</v>
+        <v>1338103.473793112</v>
       </c>
       <c r="P882" t="n">
         <v>4900</v>
@@ -39093,10 +39093,10 @@
         <v>298</v>
       </c>
       <c r="N883" t="n">
-        <v>8945.379999999999</v>
+        <v>8947.9898847557</v>
       </c>
       <c r="O883" t="n">
-        <v>2665723.24</v>
+        <v>2666500.985657198</v>
       </c>
       <c r="P883" t="n">
         <v>14900</v>
@@ -39460,10 +39460,10 @@
         <v>384</v>
       </c>
       <c r="N891" t="n">
-        <v>1530.4499204138</v>
+        <v>1530.4499206034</v>
       </c>
       <c r="O891" t="n">
-        <v>587692.7694388992</v>
+        <v>587692.7695117056</v>
       </c>
       <c r="P891" t="n">
         <v>2600</v>
@@ -39732,10 +39732,10 @@
         <v>39</v>
       </c>
       <c r="N897" t="n">
-        <v>6898.4</v>
+        <v>6979.7970501475</v>
       </c>
       <c r="O897" t="n">
-        <v>269037.6</v>
+        <v>272212.0849557525</v>
       </c>
       <c r="P897" t="n">
         <v>12900</v>
@@ -39906,22 +39906,22 @@
         <v>0</v>
       </c>
       <c r="L901" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M901" t="n">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="N901" t="n">
         <v>1828.64</v>
       </c>
       <c r="O901" t="n">
-        <v>1311134.88</v>
+        <v>1291019.84</v>
       </c>
       <c r="P901" t="n">
         <v>2000</v>
       </c>
       <c r="Q901" t="n">
-        <v>1434000</v>
+        <v>1412000</v>
       </c>
     </row>
     <row r="902">
@@ -40322,22 +40322,22 @@
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M910" t="n">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="N910" t="n">
-        <v>2286.1648782687</v>
+        <v>2286.1648643761</v>
       </c>
       <c r="O910" t="n">
-        <v>1051635.844003602</v>
+        <v>1044777.343019878</v>
       </c>
       <c r="P910" t="n">
         <v>3000</v>
       </c>
       <c r="Q910" t="n">
-        <v>1380000</v>
+        <v>1371000</v>
       </c>
     </row>
     <row r="911">
@@ -40978,22 +40978,22 @@
         <v>0</v>
       </c>
       <c r="L925" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="M925" t="n">
-        <v>538</v>
+        <v>308</v>
       </c>
       <c r="N925" t="n">
         <v>177.65</v>
       </c>
       <c r="O925" t="n">
-        <v>95575.7</v>
+        <v>54716.2</v>
       </c>
       <c r="P925" t="n">
         <v>300</v>
       </c>
       <c r="Q925" t="n">
-        <v>161400</v>
+        <v>92400</v>
       </c>
     </row>
     <row r="926">
@@ -41288,22 +41288,22 @@
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M932" t="n">
-        <v>3529</v>
+        <v>3467</v>
       </c>
       <c r="N932" t="n">
-        <v>517.2878865955601</v>
+        <v>523.15541944326</v>
       </c>
       <c r="O932" t="n">
-        <v>1825508.951795731</v>
+        <v>1813779.839209782</v>
       </c>
       <c r="P932" t="n">
         <v>900</v>
       </c>
       <c r="Q932" t="n">
-        <v>3176100</v>
+        <v>3120300</v>
       </c>
     </row>
     <row r="933">
@@ -41514,22 +41514,22 @@
         <v>0</v>
       </c>
       <c r="L937" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M937" t="n">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="N937" t="n">
-        <v>3110.8429819337</v>
+        <v>3110.8429525518</v>
       </c>
       <c r="O937" t="n">
-        <v>2134038.285606518</v>
+        <v>2096708.150019913</v>
       </c>
       <c r="P937" t="n">
         <v>4500</v>
       </c>
       <c r="Q937" t="n">
-        <v>3087000</v>
+        <v>3033000</v>
       </c>
     </row>
     <row r="938">
@@ -41730,28 +41730,28 @@
         </is>
       </c>
       <c r="J942" t="n">
-        <v>1259</v>
+        <v>1355</v>
       </c>
       <c r="K942" t="n">
         <v>0</v>
       </c>
       <c r="L942" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="M942" t="n">
-        <v>1259</v>
+        <v>1098</v>
       </c>
       <c r="N942" t="n">
-        <v>703.79538564105</v>
+        <v>703.79534416571</v>
       </c>
       <c r="O942" t="n">
-        <v>886078.3905220819</v>
+        <v>772767.2878939497</v>
       </c>
       <c r="P942" t="n">
         <v>900</v>
       </c>
       <c r="Q942" t="n">
-        <v>1133100</v>
+        <v>988200</v>
       </c>
     </row>
     <row r="943">
@@ -42230,22 +42230,22 @@
         <v>0</v>
       </c>
       <c r="L953" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M953" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N953" t="n">
         <v>1300</v>
       </c>
       <c r="O953" t="n">
-        <v>271700</v>
+        <v>269100</v>
       </c>
       <c r="P953" t="n">
         <v>2200</v>
       </c>
       <c r="Q953" t="n">
-        <v>459800</v>
+        <v>455400</v>
       </c>
     </row>
     <row r="954">
@@ -42274,22 +42274,22 @@
         <v>0</v>
       </c>
       <c r="L954" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M954" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="N954" t="n">
         <v>1937</v>
       </c>
       <c r="O954" t="n">
-        <v>269243</v>
+        <v>255684</v>
       </c>
       <c r="P954" t="n">
         <v>3300</v>
       </c>
       <c r="Q954" t="n">
-        <v>458700</v>
+        <v>435600</v>
       </c>
     </row>
     <row r="955">
@@ -42318,22 +42318,22 @@
         <v>0</v>
       </c>
       <c r="L955" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M955" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="N955" t="n">
         <v>2525.02</v>
       </c>
       <c r="O955" t="n">
-        <v>118675.94</v>
+        <v>83325.66</v>
       </c>
       <c r="P955" t="n">
         <v>3000</v>
       </c>
       <c r="Q955" t="n">
-        <v>141000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="956">
@@ -42753,10 +42753,10 @@
         <v>74</v>
       </c>
       <c r="N965" t="n">
-        <v>1595.5190941049</v>
+        <v>1595.5190882035</v>
       </c>
       <c r="O965" t="n">
-        <v>118068.4129637626</v>
+        <v>118068.412527059</v>
       </c>
       <c r="P965" t="n">
         <v>2500</v>
@@ -43365,22 +43365,22 @@
         <v>0</v>
       </c>
       <c r="L978" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M978" t="n">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N978" t="n">
         <v>1669.6</v>
       </c>
       <c r="O978" t="n">
-        <v>961689.6</v>
+        <v>958350.3999999999</v>
       </c>
       <c r="P978" t="n">
         <v>2900</v>
       </c>
       <c r="Q978" t="n">
-        <v>1670400</v>
+        <v>1664600</v>
       </c>
     </row>
     <row r="979">
@@ -43507,22 +43507,22 @@
         <v>0</v>
       </c>
       <c r="L981" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M981" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="N981" t="n">
-        <v>3063.6218872672</v>
+        <v>3063.6218891688</v>
       </c>
       <c r="O981" t="n">
-        <v>3970453.965898291</v>
+        <v>3964326.724584427</v>
       </c>
       <c r="P981" t="n">
         <v>3500</v>
       </c>
       <c r="Q981" t="n">
-        <v>4536000</v>
+        <v>4529000</v>
       </c>
     </row>
     <row r="982">
@@ -43657,10 +43657,10 @@
         <v>1</v>
       </c>
       <c r="N984" t="n">
-        <v>3879.9757142857</v>
+        <v>3879.9761538462</v>
       </c>
       <c r="O984" t="n">
-        <v>3879.9757142857</v>
+        <v>3879.9761538462</v>
       </c>
       <c r="P984" t="n">
         <v>12500</v>
@@ -44492,10 +44492,10 @@
         <v>1</v>
       </c>
       <c r="N1002" t="n">
-        <v>10737.526666667</v>
+        <v>11369.145882353</v>
       </c>
       <c r="O1002" t="n">
-        <v>10737.526666667</v>
+        <v>11369.145882353</v>
       </c>
       <c r="P1002" t="n">
         <v>18900</v>
@@ -44863,10 +44863,10 @@
         <v>2</v>
       </c>
       <c r="N1010" t="n">
-        <v>2000.6595705521</v>
+        <v>2000.6614375</v>
       </c>
       <c r="O1010" t="n">
-        <v>4001.3191411042</v>
+        <v>4001.322875</v>
       </c>
       <c r="P1010" t="n">
         <v>2000</v>
@@ -46384,22 +46384,22 @@
         <v>0</v>
       </c>
       <c r="L1043" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1043" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N1043" t="n">
         <v>2459</v>
       </c>
       <c r="O1043" t="n">
-        <v>154917</v>
+        <v>147540</v>
       </c>
       <c r="P1043" t="n">
         <v>3900</v>
       </c>
       <c r="Q1043" t="n">
-        <v>245700</v>
+        <v>234000</v>
       </c>
     </row>
     <row r="1044">
@@ -47799,22 +47799,22 @@
         <v>0</v>
       </c>
       <c r="L1076" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1076" t="n">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="N1076" t="n">
-        <v>3181.9</v>
+        <v>3209.0377398721</v>
       </c>
       <c r="O1076" t="n">
-        <v>868658.7000000001</v>
+        <v>856813.0765458506</v>
       </c>
       <c r="P1076" t="n">
         <v>5100</v>
       </c>
       <c r="Q1076" t="n">
-        <v>1392300</v>
+        <v>1361700</v>
       </c>
     </row>
     <row r="1077">
@@ -47846,10 +47846,10 @@
         <v>3</v>
       </c>
       <c r="N1077" t="n">
-        <v>1213.6821442495</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O1077" t="n">
-        <v>3641.0464327485</v>
+        <v>3641.0463583815</v>
       </c>
       <c r="P1077" t="n">
         <v>1500</v>
@@ -47925,22 +47925,22 @@
         <v>0</v>
       </c>
       <c r="L1079" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1079" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="N1079" t="n">
-        <v>1794.2879767875</v>
+        <v>1794.2879750466</v>
       </c>
       <c r="O1079" t="n">
-        <v>342709.0035664125</v>
+        <v>331943.275383621</v>
       </c>
       <c r="P1079" t="n">
         <v>1600</v>
       </c>
       <c r="Q1079" t="n">
-        <v>305600</v>
+        <v>296000</v>
       </c>
     </row>
     <row r="1080">
@@ -48863,22 +48863,22 @@
         <v>0</v>
       </c>
       <c r="L1101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1101" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N1101" t="n">
         <v>7313</v>
       </c>
       <c r="O1101" t="n">
-        <v>138947</v>
+        <v>131634</v>
       </c>
       <c r="P1101" t="n">
         <v>9800</v>
       </c>
       <c r="Q1101" t="n">
-        <v>186200</v>
+        <v>176400</v>
       </c>
     </row>
     <row r="1102">
@@ -48953,22 +48953,22 @@
         <v>0</v>
       </c>
       <c r="L1103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1103" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N1103" t="n">
-        <v>5077</v>
+        <v>5337.8047945205</v>
       </c>
       <c r="O1103" t="n">
-        <v>741242</v>
+        <v>763306.0856164314</v>
       </c>
       <c r="P1103" t="n">
         <v>8500</v>
       </c>
       <c r="Q1103" t="n">
-        <v>1241000</v>
+        <v>1215500</v>
       </c>
     </row>
     <row r="1104">
@@ -49178,22 +49178,22 @@
         <v>0</v>
       </c>
       <c r="L1108" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1108" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N1108" t="n">
         <v>1757.3205360825</v>
       </c>
       <c r="O1108" t="n">
-        <v>101924.591092785</v>
+        <v>91380.66787629</v>
       </c>
       <c r="P1108" t="n">
         <v>2000</v>
       </c>
       <c r="Q1108" t="n">
-        <v>116000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="1109">
@@ -49543,10 +49543,10 @@
         <v>30615.38</v>
       </c>
       <c r="P1116" t="n">
-        <v>19900</v>
+        <v>15900</v>
       </c>
       <c r="Q1116" t="n">
-        <v>39800</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="1117">
@@ -49991,22 +49991,22 @@
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1126" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="N1126" t="n">
         <v>1800</v>
       </c>
       <c r="O1126" t="n">
-        <v>163800</v>
+        <v>142200</v>
       </c>
       <c r="P1126" t="n">
         <v>2200</v>
       </c>
       <c r="Q1126" t="n">
-        <v>200200</v>
+        <v>173800</v>
       </c>
     </row>
     <row r="1127">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1186"/>
+  <dimension ref="A1:Q1188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,22 +732,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>66707.97725</v>
+        <v>66707.977837838</v>
       </c>
       <c r="O8" t="n">
-        <v>266831.909</v>
+        <v>66707.977837838</v>
       </c>
       <c r="P8" t="n">
         <v>125900</v>
       </c>
       <c r="Q8" t="n">
-        <v>503600</v>
+        <v>125900</v>
       </c>
     </row>
     <row r="9">
@@ -1354,10 +1354,10 @@
         <v>192</v>
       </c>
       <c r="N23" t="n">
-        <v>1811.3044243338</v>
+        <v>1811.3044829343</v>
       </c>
       <c r="O23" t="n">
-        <v>347770.4494720896</v>
+        <v>347770.4607233856</v>
       </c>
       <c r="P23" t="n">
         <v>2600</v>
@@ -1432,10 +1432,10 @@
         <v>71</v>
       </c>
       <c r="N25" t="n">
-        <v>1990.0435660377</v>
+        <v>1990.0435416667</v>
       </c>
       <c r="O25" t="n">
-        <v>141293.0931886767</v>
+        <v>141293.0914583357</v>
       </c>
       <c r="P25" t="n">
         <v>4400</v>
@@ -1462,25 +1462,25 @@
         <v>56</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="N26" t="n">
-        <v>3376.7465014893</v>
+        <v>3376.746498645</v>
       </c>
       <c r="O26" t="n">
-        <v>189097.8040834008</v>
+        <v>523395.707289975</v>
       </c>
       <c r="P26" t="n">
         <v>4500</v>
       </c>
       <c r="Q26" t="n">
-        <v>252000</v>
+        <v>697500</v>
       </c>
     </row>
     <row r="27">
@@ -2062,10 +2062,10 @@
         <v>13</v>
       </c>
       <c r="N41" t="n">
-        <v>20826.676585366</v>
+        <v>20826.676923077</v>
       </c>
       <c r="O41" t="n">
-        <v>270746.795609758</v>
+        <v>270746.800000001</v>
       </c>
       <c r="P41" t="n">
         <v>39100</v>
@@ -2965,10 +2965,10 @@
         <v>41</v>
       </c>
       <c r="N63" t="n">
-        <v>6272.8545</v>
+        <v>6272.8545786963</v>
       </c>
       <c r="O63" t="n">
-        <v>257187.0345</v>
+        <v>257187.0377265483</v>
       </c>
       <c r="P63" t="n">
         <v>7900</v>
@@ -3288,10 +3288,10 @@
         <v>205</v>
       </c>
       <c r="N71" t="n">
-        <v>2413.001059322</v>
+        <v>2413.0010615711</v>
       </c>
       <c r="O71" t="n">
-        <v>494665.21716101</v>
+        <v>494665.2176220755</v>
       </c>
       <c r="P71" t="n">
         <v>4700</v>
@@ -3327,10 +3327,10 @@
         <v>74</v>
       </c>
       <c r="N72" t="n">
-        <v>2474.7042140468</v>
+        <v>2474.7042043551</v>
       </c>
       <c r="O72" t="n">
-        <v>183128.1118394632</v>
+        <v>183128.1111222774</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -4175,22 +4175,22 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M93" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="N93" t="n">
-        <v>3910.6282248521</v>
+        <v>3910.6281963928</v>
       </c>
       <c r="O93" t="n">
-        <v>234637.693491126</v>
+        <v>218995.1789979968</v>
       </c>
       <c r="P93" t="n">
         <v>9100</v>
       </c>
       <c r="Q93" t="n">
-        <v>546000</v>
+        <v>509600</v>
       </c>
     </row>
     <row r="94">
@@ -4942,22 +4942,22 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N110" t="n">
-        <v>18835.023125</v>
+        <v>18835.024666667</v>
       </c>
       <c r="O110" t="n">
-        <v>282525.346875</v>
+        <v>263690.345333338</v>
       </c>
       <c r="P110" t="n">
         <v>40500</v>
       </c>
       <c r="Q110" t="n">
-        <v>607500</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="111">
@@ -6236,10 +6236,10 @@
         <v>12</v>
       </c>
       <c r="N140" t="n">
-        <v>200072.19992308</v>
+        <v>200072.2</v>
       </c>
       <c r="O140" t="n">
-        <v>2400866.39907696</v>
+        <v>2400866.4</v>
       </c>
       <c r="P140" t="n">
         <v>312000</v>
@@ -7580,22 +7580,22 @@
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N171" t="n">
         <v>91480</v>
       </c>
       <c r="O171" t="n">
-        <v>365920</v>
+        <v>274440</v>
       </c>
       <c r="P171" t="n">
         <v>150900</v>
       </c>
       <c r="Q171" t="n">
-        <v>603600</v>
+        <v>452700</v>
       </c>
     </row>
     <row r="172">
@@ -7632,10 +7632,10 @@
         <v>5</v>
       </c>
       <c r="N172" t="n">
-        <v>408.26614457831</v>
+        <v>408.26584415584</v>
       </c>
       <c r="O172" t="n">
-        <v>2041.33072289155</v>
+        <v>2041.3292207792</v>
       </c>
       <c r="P172" t="n">
         <v>1600</v>
@@ -9096,22 +9096,22 @@
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N206" t="n">
-        <v>4333.604375</v>
+        <v>4333.6046666667</v>
       </c>
       <c r="O206" t="n">
-        <v>43336.04375</v>
+        <v>39002.4420000003</v>
       </c>
       <c r="P206" t="n">
         <v>7500</v>
       </c>
       <c r="Q206" t="n">
-        <v>75000</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="207">
@@ -10013,10 +10013,10 @@
         <v>122</v>
       </c>
       <c r="N227" t="n">
-        <v>4937.3101608187</v>
+        <v>4937.3101611722</v>
       </c>
       <c r="O227" t="n">
-        <v>602351.8396198814</v>
+        <v>602351.8396630085</v>
       </c>
       <c r="P227" t="n">
         <v>7500</v>
@@ -10176,22 +10176,22 @@
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M231" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N231" t="n">
         <v>6513</v>
       </c>
       <c r="O231" t="n">
-        <v>345189</v>
+        <v>325650</v>
       </c>
       <c r="P231" t="n">
         <v>11500</v>
       </c>
       <c r="Q231" t="n">
-        <v>609500</v>
+        <v>575000</v>
       </c>
     </row>
     <row r="232">
@@ -10512,22 +10512,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N239" t="n">
-        <v>1098.0548595108</v>
+        <v>1098.0555939754</v>
       </c>
       <c r="O239" t="n">
-        <v>673107.6288801205</v>
+        <v>672010.0235129447</v>
       </c>
       <c r="P239" t="n">
         <v>1500</v>
       </c>
       <c r="Q239" t="n">
-        <v>919500</v>
+        <v>918000</v>
       </c>
     </row>
     <row r="240">
@@ -10599,22 +10599,22 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M241" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N241" t="n">
         <v>61675.37</v>
       </c>
       <c r="O241" t="n">
-        <v>2590365.54</v>
+        <v>2343664.06</v>
       </c>
       <c r="P241" t="n">
         <v>80000</v>
       </c>
       <c r="Q241" t="n">
-        <v>3360000</v>
+        <v>3040000</v>
       </c>
     </row>
     <row r="242">
@@ -11181,22 +11181,22 @@
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M255" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="N255" t="n">
         <v>2613</v>
       </c>
       <c r="O255" t="n">
-        <v>425919</v>
+        <v>410241</v>
       </c>
       <c r="P255" t="n">
         <v>5100</v>
       </c>
       <c r="Q255" t="n">
-        <v>831300</v>
+        <v>800700</v>
       </c>
     </row>
     <row r="256">
@@ -11827,22 +11827,22 @@
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M270" t="n">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="N270" t="n">
         <v>2913</v>
       </c>
       <c r="O270" t="n">
-        <v>812727</v>
+        <v>769032</v>
       </c>
       <c r="P270" t="n">
         <v>4950</v>
       </c>
       <c r="Q270" t="n">
-        <v>1381050</v>
+        <v>1306800</v>
       </c>
     </row>
     <row r="271">
@@ -11917,22 +11917,22 @@
         <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M272" t="n">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N272" t="n">
         <v>2804.33</v>
       </c>
       <c r="O272" t="n">
-        <v>1629315.73</v>
+        <v>1623707.07</v>
       </c>
       <c r="P272" t="n">
         <v>4900</v>
       </c>
       <c r="Q272" t="n">
-        <v>2846900</v>
+        <v>2837100</v>
       </c>
     </row>
     <row r="273">
@@ -12279,10 +12279,10 @@
         <v>247</v>
       </c>
       <c r="N280" t="n">
-        <v>2582.2560231583</v>
+        <v>2582.2560112135</v>
       </c>
       <c r="O280" t="n">
-        <v>637817.2377201001</v>
+        <v>637817.2347697346</v>
       </c>
       <c r="P280" t="n">
         <v>4500</v>
@@ -12365,22 +12365,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M282" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N282" t="n">
-        <v>5216.8959678619</v>
+        <v>5216.8959654608</v>
       </c>
       <c r="O282" t="n">
-        <v>777317.4992114231</v>
+        <v>756449.9149918159</v>
       </c>
       <c r="P282" t="n">
         <v>8500</v>
       </c>
       <c r="Q282" t="n">
-        <v>1266500</v>
+        <v>1232500</v>
       </c>
     </row>
     <row r="283">
@@ -12673,10 +12673,10 @@
         <v>943</v>
       </c>
       <c r="N289" t="n">
-        <v>3158.8608147003</v>
+        <v>3158.860814779</v>
       </c>
       <c r="O289" t="n">
-        <v>2978805.748262383</v>
+        <v>2978805.748336597</v>
       </c>
       <c r="P289" t="n">
         <v>5600</v>
@@ -12759,22 +12759,22 @@
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M291" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N291" t="n">
-        <v>3841.6247184466</v>
+        <v>3841.6247414634</v>
       </c>
       <c r="O291" t="n">
-        <v>88357.36852427181</v>
+        <v>69149.24534634119</v>
       </c>
       <c r="P291" t="n">
         <v>6900</v>
       </c>
       <c r="Q291" t="n">
-        <v>158700</v>
+        <v>124200</v>
       </c>
     </row>
     <row r="292">
@@ -12895,22 +12895,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M294" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N294" t="n">
-        <v>3230.067752443</v>
+        <v>3230.0677414075</v>
       </c>
       <c r="O294" t="n">
-        <v>478050.027361564</v>
+        <v>471589.890245495</v>
       </c>
       <c r="P294" t="n">
         <v>6200</v>
       </c>
       <c r="Q294" t="n">
-        <v>917600</v>
+        <v>905200</v>
       </c>
     </row>
     <row r="295">
@@ -13207,22 +13207,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M301" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N301" t="n">
         <v>1026.13</v>
       </c>
       <c r="O301" t="n">
-        <v>692637.7500000001</v>
+        <v>691611.6200000001</v>
       </c>
       <c r="P301" t="n">
         <v>1900</v>
       </c>
       <c r="Q301" t="n">
-        <v>1282500</v>
+        <v>1280600</v>
       </c>
     </row>
     <row r="302">
@@ -13709,22 +13709,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M312" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N312" t="n">
         <v>4357.55</v>
       </c>
       <c r="O312" t="n">
-        <v>1163465.85</v>
+        <v>1154750.75</v>
       </c>
       <c r="P312" t="n">
         <v>7500</v>
       </c>
       <c r="Q312" t="n">
-        <v>2002500</v>
+        <v>1987500</v>
       </c>
     </row>
     <row r="313">
@@ -13848,10 +13848,10 @@
         <v>53</v>
       </c>
       <c r="N315" t="n">
-        <v>4890.9300463499</v>
+        <v>4890.9300464306</v>
       </c>
       <c r="O315" t="n">
-        <v>259219.2924565447</v>
+        <v>259219.2924608218</v>
       </c>
       <c r="P315" t="n">
         <v>8200</v>
@@ -13894,10 +13894,10 @@
         <v>72</v>
       </c>
       <c r="N316" t="n">
-        <v>5484.9487179487</v>
+        <v>5484.9490434783</v>
       </c>
       <c r="O316" t="n">
-        <v>394916.3076923063</v>
+        <v>394916.3311304376</v>
       </c>
       <c r="P316" t="n">
         <v>8500</v>
@@ -13937,22 +13937,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M317" t="n">
-        <v>912</v>
+        <v>895</v>
       </c>
       <c r="N317" t="n">
         <v>1203.38</v>
       </c>
       <c r="O317" t="n">
-        <v>1097482.56</v>
+        <v>1077025.1</v>
       </c>
       <c r="P317" t="n">
         <v>1900</v>
       </c>
       <c r="Q317" t="n">
-        <v>1732800</v>
+        <v>1700500</v>
       </c>
     </row>
     <row r="318">
@@ -14512,25 +14512,25 @@
         <v>26</v>
       </c>
       <c r="K330" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M330" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="N330" t="n">
         <v>10716.34</v>
       </c>
       <c r="O330" t="n">
-        <v>278624.84</v>
+        <v>417937.26</v>
       </c>
       <c r="P330" t="n">
         <v>39000</v>
       </c>
       <c r="Q330" t="n">
-        <v>1014000</v>
+        <v>1521000</v>
       </c>
     </row>
     <row r="331">
@@ -14728,22 +14728,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N335" t="n">
-        <v>3594.25414277</v>
+        <v>3594.2541391941</v>
       </c>
       <c r="O335" t="n">
-        <v>230032.26513728</v>
+        <v>226438.0107692283</v>
       </c>
       <c r="P335" t="n">
         <v>6500</v>
       </c>
       <c r="Q335" t="n">
-        <v>416000</v>
+        <v>409500</v>
       </c>
     </row>
     <row r="336">
@@ -14856,22 +14856,22 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M338" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N338" t="n">
         <v>2953.73</v>
       </c>
       <c r="O338" t="n">
-        <v>599607.1900000001</v>
+        <v>587792.27</v>
       </c>
       <c r="P338" t="n">
         <v>4900</v>
       </c>
       <c r="Q338" t="n">
-        <v>994700</v>
+        <v>975100</v>
       </c>
     </row>
     <row r="339">
@@ -14897,22 +14897,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M339" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="N339" t="n">
-        <v>3240.850029985</v>
+        <v>3240.8500301659</v>
       </c>
       <c r="O339" t="n">
-        <v>790767.40731634</v>
+        <v>777804.007239816</v>
       </c>
       <c r="P339" t="n">
         <v>5200</v>
       </c>
       <c r="Q339" t="n">
-        <v>1268800</v>
+        <v>1248000</v>
       </c>
     </row>
     <row r="340">
@@ -15041,10 +15041,10 @@
         <v>43</v>
       </c>
       <c r="N342" t="n">
-        <v>14822.378863905</v>
+        <v>14822.378862559</v>
       </c>
       <c r="O342" t="n">
-        <v>637362.2911479149</v>
+        <v>637362.291090037</v>
       </c>
       <c r="P342" t="n">
         <v>24900</v>
@@ -15123,22 +15123,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M344" t="n">
-        <v>590</v>
+        <v>426</v>
       </c>
       <c r="N344" t="n">
         <v>2090.85</v>
       </c>
       <c r="O344" t="n">
-        <v>1233601.5</v>
+        <v>890702.1</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
       </c>
       <c r="Q344" t="n">
-        <v>1711000</v>
+        <v>1235400</v>
       </c>
     </row>
     <row r="345">
@@ -15345,22 +15345,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M349" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="N349" t="n">
         <v>1381.75</v>
       </c>
       <c r="O349" t="n">
-        <v>265296</v>
+        <v>255623.75</v>
       </c>
       <c r="P349" t="n">
         <v>2500</v>
       </c>
       <c r="Q349" t="n">
-        <v>480000</v>
+        <v>462500</v>
       </c>
     </row>
     <row r="350">
@@ -15616,10 +15616,10 @@
         <v>427</v>
       </c>
       <c r="N355" t="n">
-        <v>3041.6600125945</v>
+        <v>3041.6600126502</v>
       </c>
       <c r="O355" t="n">
-        <v>1298788.825377851</v>
+        <v>1298788.825401635</v>
       </c>
       <c r="P355" t="n">
         <v>5500</v>
@@ -15648,25 +15648,25 @@
         <v>90</v>
       </c>
       <c r="K356" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
       </c>
       <c r="M356" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="N356" t="n">
         <v>3981.47</v>
       </c>
       <c r="O356" t="n">
-        <v>358332.3</v>
+        <v>716664.6</v>
       </c>
       <c r="P356" t="n">
         <v>7000</v>
       </c>
       <c r="Q356" t="n">
-        <v>630000</v>
+        <v>1260000</v>
       </c>
     </row>
     <row r="357">
@@ -15694,25 +15694,25 @@
         <v>108</v>
       </c>
       <c r="K357" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M357" t="n">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="N357" t="n">
-        <v>4372.2107876031</v>
+        <v>4372.2107877711</v>
       </c>
       <c r="O357" t="n">
-        <v>472198.7650611348</v>
+        <v>913792.0546441599</v>
       </c>
       <c r="P357" t="n">
         <v>7500</v>
       </c>
       <c r="Q357" t="n">
-        <v>810000</v>
+        <v>1567500</v>
       </c>
     </row>
     <row r="358">
@@ -15741,22 +15741,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M358" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="N358" t="n">
         <v>6441.03</v>
       </c>
       <c r="O358" t="n">
-        <v>714954.33</v>
+        <v>586133.73</v>
       </c>
       <c r="P358" t="n">
         <v>10500</v>
       </c>
       <c r="Q358" t="n">
-        <v>1165500</v>
+        <v>955500</v>
       </c>
     </row>
     <row r="359">
@@ -15793,10 +15793,10 @@
         <v>19</v>
       </c>
       <c r="N359" t="n">
-        <v>1592.567520267</v>
+        <v>1592.5674522293</v>
       </c>
       <c r="O359" t="n">
-        <v>30258.782885073</v>
+        <v>30258.7815923567</v>
       </c>
       <c r="P359" t="n">
         <v>3900</v>
@@ -15915,22 +15915,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M362" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N362" t="n">
         <v>3655.96</v>
       </c>
       <c r="O362" t="n">
-        <v>303444.68</v>
+        <v>292476.8</v>
       </c>
       <c r="P362" t="n">
         <v>5500</v>
       </c>
       <c r="Q362" t="n">
-        <v>456500</v>
+        <v>440000</v>
       </c>
     </row>
     <row r="363">
@@ -16359,22 +16359,22 @@
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M372" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N372" t="n">
         <v>4648.6</v>
       </c>
       <c r="O372" t="n">
-        <v>1487552</v>
+        <v>1478254.8</v>
       </c>
       <c r="P372" t="n">
         <v>8900</v>
       </c>
       <c r="Q372" t="n">
-        <v>2848000</v>
+        <v>2830200</v>
       </c>
     </row>
     <row r="373">
@@ -16790,25 +16790,25 @@
         <v>38</v>
       </c>
       <c r="K382" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="N382" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O382" t="n">
-        <v>357743.78</v>
+        <v>677830.3199999999</v>
       </c>
       <c r="P382" t="n">
         <v>16900</v>
       </c>
       <c r="Q382" t="n">
-        <v>642200</v>
+        <v>1216800</v>
       </c>
     </row>
     <row r="383">
@@ -16837,22 +16837,22 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M383" t="n">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="N383" t="n">
         <v>1387.55</v>
       </c>
       <c r="O383" t="n">
-        <v>724301.1</v>
+        <v>714588.25</v>
       </c>
       <c r="P383" t="n">
         <v>2300</v>
       </c>
       <c r="Q383" t="n">
-        <v>1200600</v>
+        <v>1184500</v>
       </c>
     </row>
     <row r="384">
@@ -16969,10 +16969,10 @@
         <v>180</v>
       </c>
       <c r="N386" t="n">
-        <v>2021.7211218335</v>
+        <v>2021.7211225106</v>
       </c>
       <c r="O386" t="n">
-        <v>363909.80193003</v>
+        <v>363909.802051908</v>
       </c>
       <c r="P386" t="n">
         <v>2400</v>
@@ -17371,22 +17371,22 @@
         <v>0</v>
       </c>
       <c r="L395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N395" t="n">
         <v>45945</v>
       </c>
       <c r="O395" t="n">
-        <v>781065</v>
+        <v>735120</v>
       </c>
       <c r="P395" t="n">
         <v>73900</v>
       </c>
       <c r="Q395" t="n">
-        <v>1256300</v>
+        <v>1182400</v>
       </c>
     </row>
     <row r="396">
@@ -17419,25 +17419,25 @@
         <v>134</v>
       </c>
       <c r="K396" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M396" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="N396" t="n">
         <v>11921.4</v>
       </c>
       <c r="O396" t="n">
-        <v>1597467.6</v>
+        <v>1728603</v>
       </c>
       <c r="P396" t="n">
         <v>19900</v>
       </c>
       <c r="Q396" t="n">
-        <v>2666600</v>
+        <v>2885500</v>
       </c>
     </row>
     <row r="397">
@@ -17762,22 +17762,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M404" t="n">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="N404" t="n">
         <v>3751</v>
       </c>
       <c r="O404" t="n">
-        <v>3379651</v>
+        <v>3349643</v>
       </c>
       <c r="P404" t="n">
         <v>6400</v>
       </c>
       <c r="Q404" t="n">
-        <v>5766400</v>
+        <v>5715200</v>
       </c>
     </row>
     <row r="405">
@@ -17854,25 +17854,25 @@
         <v>17</v>
       </c>
       <c r="K406" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L406" t="n">
         <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="N406" t="n">
         <v>12754</v>
       </c>
       <c r="O406" t="n">
-        <v>216818</v>
+        <v>1033074</v>
       </c>
       <c r="P406" t="n">
         <v>21500</v>
       </c>
       <c r="Q406" t="n">
-        <v>365500</v>
+        <v>1741500</v>
       </c>
     </row>
     <row r="407">
@@ -17903,22 +17903,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M407" t="n">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="N407" t="n">
-        <v>1630.923147125</v>
+        <v>1630.9231587595</v>
       </c>
       <c r="O407" t="n">
-        <v>1391177.444497625</v>
+        <v>1381391.915469297</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
       </c>
       <c r="Q407" t="n">
-        <v>2132500</v>
+        <v>2117500</v>
       </c>
     </row>
     <row r="408">
@@ -18036,22 +18036,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M410" t="n">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="N410" t="n">
-        <v>1690.6028354857</v>
+        <v>1690.6026503973</v>
       </c>
       <c r="O410" t="n">
-        <v>747246.4532846794</v>
+        <v>742174.5635244148</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
       </c>
       <c r="Q410" t="n">
-        <v>1281800</v>
+        <v>1273100</v>
       </c>
     </row>
     <row r="411">
@@ -18082,22 +18082,22 @@
         <v>0</v>
       </c>
       <c r="L411" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M411" t="n">
-        <v>2135</v>
+        <v>2124</v>
       </c>
       <c r="N411" t="n">
-        <v>1550.1931350849</v>
+        <v>1550.1931558806</v>
       </c>
       <c r="O411" t="n">
-        <v>3309662.343406261</v>
+        <v>3292610.263090394</v>
       </c>
       <c r="P411" t="n">
         <v>2500</v>
       </c>
       <c r="Q411" t="n">
-        <v>5337500</v>
+        <v>5310000</v>
       </c>
     </row>
     <row r="412">
@@ -18134,10 +18134,10 @@
         <v>3</v>
       </c>
       <c r="N412" t="n">
-        <v>1579.3910473815</v>
+        <v>1579.391025</v>
       </c>
       <c r="O412" t="n">
-        <v>4738.1731421445</v>
+        <v>4738.173075</v>
       </c>
       <c r="P412" t="n">
         <v>2900</v>
@@ -18174,22 +18174,22 @@
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M413" t="n">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="N413" t="n">
-        <v>2403.5103430475</v>
+        <v>2403.5103724115</v>
       </c>
       <c r="O413" t="n">
-        <v>2554931.494659493</v>
+        <v>2552528.015501013</v>
       </c>
       <c r="P413" t="n">
         <v>3500</v>
       </c>
       <c r="Q413" t="n">
-        <v>3720500</v>
+        <v>3717000</v>
       </c>
     </row>
     <row r="414">
@@ -18226,10 +18226,10 @@
         <v>29</v>
       </c>
       <c r="N414" t="n">
-        <v>2521.5446987952</v>
+        <v>2521.5439240506</v>
       </c>
       <c r="O414" t="n">
-        <v>73124.7962650608</v>
+        <v>73124.77379746739</v>
       </c>
       <c r="P414" t="n">
         <v>3900</v>
@@ -19044,22 +19044,22 @@
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M433" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N433" t="n">
         <v>2973.29</v>
       </c>
       <c r="O433" t="n">
-        <v>404367.44</v>
+        <v>398420.86</v>
       </c>
       <c r="P433" t="n">
         <v>4900</v>
       </c>
       <c r="Q433" t="n">
-        <v>666400</v>
+        <v>656600</v>
       </c>
     </row>
     <row r="434">
@@ -19536,22 +19536,22 @@
         <v>0</v>
       </c>
       <c r="L444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N444" t="n">
         <v>3253</v>
       </c>
       <c r="O444" t="n">
-        <v>374095</v>
+        <v>370842</v>
       </c>
       <c r="P444" t="n">
         <v>3900</v>
       </c>
       <c r="Q444" t="n">
-        <v>448500</v>
+        <v>444600</v>
       </c>
     </row>
     <row r="445">
@@ -19582,22 +19582,22 @@
         <v>0</v>
       </c>
       <c r="L445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N445" t="n">
         <v>17328</v>
       </c>
       <c r="O445" t="n">
-        <v>710448</v>
+        <v>693120</v>
       </c>
       <c r="P445" t="n">
         <v>32900</v>
       </c>
       <c r="Q445" t="n">
-        <v>1348900</v>
+        <v>1316000</v>
       </c>
     </row>
     <row r="446">
@@ -19928,22 +19928,22 @@
         <v>0</v>
       </c>
       <c r="L453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M453" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N453" t="n">
         <v>3253</v>
       </c>
       <c r="O453" t="n">
-        <v>409878</v>
+        <v>406625</v>
       </c>
       <c r="P453" t="n">
         <v>3900</v>
       </c>
       <c r="Q453" t="n">
-        <v>491400</v>
+        <v>487500</v>
       </c>
     </row>
     <row r="454">
@@ -20960,22 +20960,22 @@
         <v>0</v>
       </c>
       <c r="L477" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M477" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N477" t="n">
         <v>9338</v>
       </c>
       <c r="O477" t="n">
-        <v>46690</v>
+        <v>18676</v>
       </c>
       <c r="P477" t="n">
         <v>15500</v>
       </c>
       <c r="Q477" t="n">
-        <v>77500</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="478">
@@ -21788,22 +21788,22 @@
         <v>0</v>
       </c>
       <c r="L497" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M497" t="n">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="N497" t="n">
         <v>2567</v>
       </c>
       <c r="O497" t="n">
-        <v>885615</v>
+        <v>880481</v>
       </c>
       <c r="P497" t="n">
         <v>4500</v>
       </c>
       <c r="Q497" t="n">
-        <v>1552500</v>
+        <v>1543500</v>
       </c>
     </row>
     <row r="498">
@@ -22157,22 +22157,22 @@
         <v>0</v>
       </c>
       <c r="L506" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M506" t="n">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="N506" t="n">
-        <v>2029.8736782737</v>
+        <v>2029.8737073653</v>
       </c>
       <c r="O506" t="n">
-        <v>966219.8708582813</v>
+        <v>935771.7790954034</v>
       </c>
       <c r="P506" t="n">
         <v>3600</v>
       </c>
       <c r="Q506" t="n">
-        <v>1713600</v>
+        <v>1659600</v>
       </c>
     </row>
     <row r="507">
@@ -22780,22 +22780,22 @@
         <v>0</v>
       </c>
       <c r="L521" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M521" t="n">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="N521" t="n">
-        <v>880.32935107376</v>
+        <v>880.3293685687599</v>
       </c>
       <c r="O521" t="n">
-        <v>1209572.528375346</v>
+        <v>1208692.223044907</v>
       </c>
       <c r="P521" t="n">
         <v>1200</v>
       </c>
       <c r="Q521" t="n">
-        <v>1648800</v>
+        <v>1647600</v>
       </c>
     </row>
     <row r="522">
@@ -23412,25 +23412,25 @@
         <v>53</v>
       </c>
       <c r="K536" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L536" t="n">
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="N536" t="n">
         <v>1651</v>
       </c>
       <c r="O536" t="n">
-        <v>87503</v>
+        <v>186563</v>
       </c>
       <c r="P536" t="n">
         <v>2500</v>
       </c>
       <c r="Q536" t="n">
-        <v>132500</v>
+        <v>282500</v>
       </c>
     </row>
     <row r="537">
@@ -24483,25 +24483,25 @@
         <v>84</v>
       </c>
       <c r="K561" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L561" t="n">
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="N561" t="n">
         <v>3591.13</v>
       </c>
       <c r="O561" t="n">
-        <v>301654.92</v>
+        <v>531487.24</v>
       </c>
       <c r="P561" t="n">
         <v>6300</v>
       </c>
       <c r="Q561" t="n">
-        <v>529200</v>
+        <v>932400</v>
       </c>
     </row>
     <row r="562">
@@ -25430,25 +25430,25 @@
         <v>6</v>
       </c>
       <c r="K583" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L583" t="n">
         <v>0</v>
       </c>
       <c r="M583" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="N583" t="n">
         <v>21418.04</v>
       </c>
       <c r="O583" t="n">
-        <v>128508.24</v>
+        <v>771049.4400000001</v>
       </c>
       <c r="P583" t="n">
         <v>34900</v>
       </c>
       <c r="Q583" t="n">
-        <v>209400</v>
+        <v>1256400</v>
       </c>
     </row>
     <row r="584">
@@ -25786,22 +25786,22 @@
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M591" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N591" t="n">
         <v>45409.74</v>
       </c>
       <c r="O591" t="n">
-        <v>1226062.98</v>
+        <v>1135243.5</v>
       </c>
       <c r="P591" t="n">
         <v>72900</v>
       </c>
       <c r="Q591" t="n">
-        <v>1968300</v>
+        <v>1822500</v>
       </c>
     </row>
     <row r="592">
@@ -26090,25 +26090,25 @@
         <v>7</v>
       </c>
       <c r="K598" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L598" t="n">
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="N598" t="n">
         <v>4100.45</v>
       </c>
       <c r="O598" t="n">
-        <v>28703.15</v>
+        <v>127113.95</v>
       </c>
       <c r="P598" t="n">
         <v>26900</v>
       </c>
       <c r="Q598" t="n">
-        <v>188300</v>
+        <v>833900</v>
       </c>
     </row>
     <row r="599">
@@ -26273,10 +26273,10 @@
         <v>114</v>
       </c>
       <c r="N602" t="n">
-        <v>1560.999261745</v>
+        <v>1560.9993877551</v>
       </c>
       <c r="O602" t="n">
-        <v>177953.91583893</v>
+        <v>177953.9302040814</v>
       </c>
       <c r="P602" t="n">
         <v>2900</v>
@@ -27592,22 +27592,22 @@
         <v>0</v>
       </c>
       <c r="L633" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M633" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N633" t="n">
         <v>4437</v>
       </c>
       <c r="O633" t="n">
-        <v>159732</v>
+        <v>150858</v>
       </c>
       <c r="P633" t="n">
         <v>4900</v>
       </c>
       <c r="Q633" t="n">
-        <v>176400</v>
+        <v>166600</v>
       </c>
     </row>
     <row r="634">
@@ -28281,10 +28281,10 @@
         <v>21</v>
       </c>
       <c r="N648" t="n">
-        <v>5218.1705134189</v>
+        <v>5218.1705164319</v>
       </c>
       <c r="O648" t="n">
-        <v>109581.5807817969</v>
+        <v>109581.5808450699</v>
       </c>
       <c r="P648" t="n">
         <v>8500</v>
@@ -28327,10 +28327,10 @@
         <v>140</v>
       </c>
       <c r="N649" t="n">
-        <v>1595.0094571429</v>
+        <v>1595.0094492754</v>
       </c>
       <c r="O649" t="n">
-        <v>223301.324000006</v>
+        <v>223301.322898556</v>
       </c>
       <c r="P649" t="n">
         <v>2600</v>
@@ -28689,22 +28689,22 @@
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M657" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N657" t="n">
         <v>6058.52</v>
       </c>
       <c r="O657" t="n">
-        <v>96936.32000000001</v>
+        <v>54526.68000000001</v>
       </c>
       <c r="P657" t="n">
         <v>9700</v>
       </c>
       <c r="Q657" t="n">
-        <v>155200</v>
+        <v>87300</v>
       </c>
     </row>
     <row r="658">
@@ -28781,22 +28781,22 @@
         <v>0</v>
       </c>
       <c r="L659" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M659" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N659" t="n">
-        <v>1664.359264432</v>
+        <v>1664.3592041199</v>
       </c>
       <c r="O659" t="n">
-        <v>675729.8613593919</v>
+        <v>674065.4776685594</v>
       </c>
       <c r="P659" t="n">
         <v>2900</v>
       </c>
       <c r="Q659" t="n">
-        <v>1177400</v>
+        <v>1174500</v>
       </c>
     </row>
     <row r="660">
@@ -28827,22 +28827,22 @@
         <v>0</v>
       </c>
       <c r="L660" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M660" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N660" t="n">
         <v>15502</v>
       </c>
       <c r="O660" t="n">
-        <v>1116144</v>
+        <v>1069638</v>
       </c>
       <c r="P660" t="n">
         <v>25900</v>
       </c>
       <c r="Q660" t="n">
-        <v>1864800</v>
+        <v>1787100</v>
       </c>
     </row>
     <row r="661">
@@ -29345,10 +29345,10 @@
         <v>4</v>
       </c>
       <c r="N671" t="n">
-        <v>23521.62469697</v>
+        <v>23521.62453125</v>
       </c>
       <c r="O671" t="n">
-        <v>94086.49878788</v>
+        <v>94086.498125</v>
       </c>
       <c r="P671" t="n">
         <v>39000</v>
@@ -29437,10 +29437,10 @@
         <v>1508</v>
       </c>
       <c r="N673" t="n">
-        <v>1778.4725650066</v>
+        <v>1778.4725680247</v>
       </c>
       <c r="O673" t="n">
-        <v>2681936.628029953</v>
+        <v>2681936.632581247</v>
       </c>
       <c r="P673" t="n">
         <v>4900</v>
@@ -29523,22 +29523,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M675" t="n">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="N675" t="n">
         <v>2325</v>
       </c>
       <c r="O675" t="n">
-        <v>1162500</v>
+        <v>1148550</v>
       </c>
       <c r="P675" t="n">
         <v>4900</v>
       </c>
       <c r="Q675" t="n">
-        <v>2450000</v>
+        <v>2420600</v>
       </c>
     </row>
     <row r="676">
@@ -29566,25 +29566,25 @@
         <v>7</v>
       </c>
       <c r="K676" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L676" t="n">
         <v>0</v>
       </c>
       <c r="M676" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="N676" t="n">
         <v>22739</v>
       </c>
       <c r="O676" t="n">
-        <v>159173</v>
+        <v>704909</v>
       </c>
       <c r="P676" t="n">
         <v>36900</v>
       </c>
       <c r="Q676" t="n">
-        <v>258300</v>
+        <v>1143900</v>
       </c>
     </row>
     <row r="677">
@@ -33023,22 +33023,22 @@
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M751" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N751" t="n">
         <v>13922</v>
       </c>
       <c r="O751" t="n">
-        <v>403738</v>
+        <v>375894</v>
       </c>
       <c r="P751" t="n">
         <v>22900</v>
       </c>
       <c r="Q751" t="n">
-        <v>664100</v>
+        <v>618300</v>
       </c>
     </row>
     <row r="752">
@@ -33167,10 +33167,10 @@
         <v>18</v>
       </c>
       <c r="N754" t="n">
-        <v>4907.821941896</v>
+        <v>4907.8219448698</v>
       </c>
       <c r="O754" t="n">
-        <v>88340.794954128</v>
+        <v>88340.7950076564</v>
       </c>
       <c r="P754" t="n">
         <v>8200</v>
@@ -33437,22 +33437,22 @@
         <v>0</v>
       </c>
       <c r="L760" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M760" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N760" t="n">
-        <v>3903.7361658031</v>
+        <v>3903.7362017804</v>
       </c>
       <c r="O760" t="n">
-        <v>398181.0889119162</v>
+        <v>390373.62017804</v>
       </c>
       <c r="P760" t="n">
         <v>7500</v>
       </c>
       <c r="Q760" t="n">
-        <v>765000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="761">
@@ -34674,22 +34674,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M787" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N787" t="n">
         <v>5438</v>
       </c>
       <c r="O787" t="n">
-        <v>206644</v>
+        <v>201206</v>
       </c>
       <c r="P787" t="n">
         <v>8900</v>
       </c>
       <c r="Q787" t="n">
-        <v>338200</v>
+        <v>329300</v>
       </c>
     </row>
     <row r="788">
@@ -34815,22 +34815,22 @@
         <v>0</v>
       </c>
       <c r="L790" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M790" t="n">
-        <v>751</v>
+        <v>716</v>
       </c>
       <c r="N790" t="n">
         <v>753</v>
       </c>
       <c r="O790" t="n">
-        <v>565503</v>
+        <v>539148</v>
       </c>
       <c r="P790" t="n">
         <v>1600</v>
       </c>
       <c r="Q790" t="n">
-        <v>1201600</v>
+        <v>1145600</v>
       </c>
     </row>
     <row r="791">
@@ -35313,25 +35313,25 @@
         <v>136</v>
       </c>
       <c r="K801" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="L801" t="n">
         <v>0</v>
       </c>
       <c r="M801" t="n">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="N801" t="n">
         <v>59834</v>
       </c>
       <c r="O801" t="n">
-        <v>8137424</v>
+        <v>14180658</v>
       </c>
       <c r="P801" t="n">
         <v>7900</v>
       </c>
       <c r="Q801" t="n">
-        <v>1074400</v>
+        <v>1872300</v>
       </c>
     </row>
     <row r="802">
@@ -35405,25 +35405,25 @@
         <v>8</v>
       </c>
       <c r="K803" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L803" t="n">
         <v>0</v>
       </c>
       <c r="M803" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N803" t="n">
         <v>18001</v>
       </c>
       <c r="O803" t="n">
-        <v>144008</v>
+        <v>576032</v>
       </c>
       <c r="P803" t="n">
         <v>28900</v>
       </c>
       <c r="Q803" t="n">
-        <v>231200</v>
+        <v>924800</v>
       </c>
     </row>
     <row r="804">
@@ -35451,25 +35451,25 @@
         <v>47</v>
       </c>
       <c r="K804" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L804" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M804" t="n">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="N804" t="n">
         <v>10219</v>
       </c>
       <c r="O804" t="n">
-        <v>480293</v>
+        <v>1440879</v>
       </c>
       <c r="P804" t="n">
         <v>16900</v>
       </c>
       <c r="Q804" t="n">
-        <v>794300</v>
+        <v>2382900</v>
       </c>
     </row>
     <row r="805">
@@ -35503,22 +35503,22 @@
         <v>0</v>
       </c>
       <c r="L805" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M805" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N805" t="n">
         <v>10755</v>
       </c>
       <c r="O805" t="n">
-        <v>924930</v>
+        <v>914175</v>
       </c>
       <c r="P805" t="n">
         <v>17900</v>
       </c>
       <c r="Q805" t="n">
-        <v>1539400</v>
+        <v>1521500</v>
       </c>
     </row>
     <row r="806">
@@ -35739,10 +35739,10 @@
         <v>85</v>
       </c>
       <c r="N810" t="n">
-        <v>4268.7044813278</v>
+        <v>4268.7047257384</v>
       </c>
       <c r="O810" t="n">
-        <v>362839.880912863</v>
+        <v>362839.901687764</v>
       </c>
       <c r="P810" t="n">
         <v>6900</v>
@@ -35825,22 +35825,22 @@
         <v>0</v>
       </c>
       <c r="L812" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M812" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N812" t="n">
         <v>29835</v>
       </c>
       <c r="O812" t="n">
-        <v>1044225</v>
+        <v>1014390</v>
       </c>
       <c r="P812" t="n">
         <v>47900</v>
       </c>
       <c r="Q812" t="n">
-        <v>1676500</v>
+        <v>1628600</v>
       </c>
     </row>
     <row r="813">
@@ -36055,22 +36055,22 @@
         <v>0</v>
       </c>
       <c r="L817" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M817" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N817" t="n">
         <v>16282</v>
       </c>
       <c r="O817" t="n">
-        <v>325640</v>
+        <v>309358</v>
       </c>
       <c r="P817" t="n">
         <v>27900</v>
       </c>
       <c r="Q817" t="n">
-        <v>558000</v>
+        <v>530100</v>
       </c>
     </row>
     <row r="818">
@@ -36800,10 +36800,10 @@
         <v>604</v>
       </c>
       <c r="N833" t="n">
-        <v>1516.0388115466</v>
+        <v>1516.0388110875</v>
       </c>
       <c r="O833" t="n">
-        <v>915687.4421741464</v>
+        <v>915687.44189685</v>
       </c>
       <c r="P833" t="n">
         <v>2300</v>
@@ -36840,22 +36840,22 @@
         <v>0</v>
       </c>
       <c r="L834" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M834" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="N834" t="n">
-        <v>4248.6224691358</v>
+        <v>4248.6238427948</v>
       </c>
       <c r="O834" t="n">
-        <v>565066.7883950614</v>
+        <v>505586.2372925812</v>
       </c>
       <c r="P834" t="n">
         <v>5900</v>
       </c>
       <c r="Q834" t="n">
-        <v>784700</v>
+        <v>702100</v>
       </c>
     </row>
     <row r="835">
@@ -36936,10 +36936,10 @@
         <v>363</v>
       </c>
       <c r="N836" t="n">
-        <v>2458.5134059343</v>
+        <v>2458.5133829585</v>
       </c>
       <c r="O836" t="n">
-        <v>892440.3663541509</v>
+        <v>892440.3580139356</v>
       </c>
       <c r="P836" t="n">
         <v>3500</v>
@@ -36982,10 +36982,10 @@
         <v>191</v>
       </c>
       <c r="N837" t="n">
-        <v>1907.3942832168</v>
+        <v>1907.3941918295</v>
       </c>
       <c r="O837" t="n">
-        <v>364312.3080944088</v>
+        <v>364312.2906394345</v>
       </c>
       <c r="P837" t="n">
         <v>2500</v>
@@ -37068,22 +37068,22 @@
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M839" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N839" t="n">
-        <v>2079.3842021449</v>
+        <v>2079.3841889251</v>
       </c>
       <c r="O839" t="n">
-        <v>871261.9806987131</v>
+        <v>869182.5909706918</v>
       </c>
       <c r="P839" t="n">
         <v>2900</v>
       </c>
       <c r="Q839" t="n">
-        <v>1215100</v>
+        <v>1212200</v>
       </c>
     </row>
     <row r="840">
@@ -37120,10 +37120,10 @@
         <v>437</v>
       </c>
       <c r="N840" t="n">
-        <v>1803.0151441578</v>
+        <v>1803.0151566778</v>
       </c>
       <c r="O840" t="n">
-        <v>787917.6179969587</v>
+        <v>787917.6234681986</v>
       </c>
       <c r="P840" t="n">
         <v>2500</v>
@@ -37160,22 +37160,22 @@
         <v>0</v>
       </c>
       <c r="L841" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M841" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N841" t="n">
-        <v>3306.5953548387</v>
+        <v>3306.5953488372</v>
       </c>
       <c r="O841" t="n">
-        <v>238074.8655483864</v>
+        <v>234768.2697674412</v>
       </c>
       <c r="P841" t="n">
         <v>4900</v>
       </c>
       <c r="Q841" t="n">
-        <v>352800</v>
+        <v>347900</v>
       </c>
     </row>
     <row r="842">
@@ -37206,22 +37206,22 @@
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M842" t="n">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N842" t="n">
-        <v>2122.1640091884</v>
+        <v>2122.1640073529</v>
       </c>
       <c r="O842" t="n">
-        <v>935874.3280520844</v>
+        <v>933752.1632352761</v>
       </c>
       <c r="P842" t="n">
         <v>2900</v>
       </c>
       <c r="Q842" t="n">
-        <v>1278900</v>
+        <v>1276000</v>
       </c>
     </row>
     <row r="843">
@@ -37252,22 +37252,22 @@
         <v>0</v>
       </c>
       <c r="L843" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M843" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N843" t="n">
-        <v>2108.7899828473</v>
+        <v>2108.7899885584</v>
       </c>
       <c r="O843" t="n">
-        <v>86460.3892967393</v>
+        <v>84351.59954233601</v>
       </c>
       <c r="P843" t="n">
         <v>2900</v>
       </c>
       <c r="Q843" t="n">
-        <v>118900</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="844">
@@ -37298,22 +37298,22 @@
         <v>0</v>
       </c>
       <c r="L844" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M844" t="n">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="N844" t="n">
-        <v>2056.0838571429</v>
+        <v>2056.0838222089</v>
       </c>
       <c r="O844" t="n">
-        <v>1866924.142285753</v>
+        <v>1864868.026743472</v>
       </c>
       <c r="P844" t="n">
         <v>2900</v>
       </c>
       <c r="Q844" t="n">
-        <v>2633200</v>
+        <v>2630300</v>
       </c>
     </row>
     <row r="845">
@@ -37344,22 +37344,22 @@
         <v>0</v>
       </c>
       <c r="L845" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M845" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N845" t="n">
-        <v>3224.5682755432</v>
+        <v>3224.568287037</v>
       </c>
       <c r="O845" t="n">
-        <v>802917.5006102568</v>
+        <v>796468.366898139</v>
       </c>
       <c r="P845" t="n">
         <v>4500</v>
       </c>
       <c r="Q845" t="n">
-        <v>1120500</v>
+        <v>1111500</v>
       </c>
     </row>
     <row r="846">
@@ -37396,10 +37396,10 @@
         <v>455</v>
       </c>
       <c r="N846" t="n">
-        <v>1655.9310860458</v>
+        <v>1655.931057226</v>
       </c>
       <c r="O846" t="n">
-        <v>753448.644150839</v>
+        <v>753448.6310378299</v>
       </c>
       <c r="P846" t="n">
         <v>2500</v>
@@ -37577,22 +37577,22 @@
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M850" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N850" t="n">
         <v>1871</v>
       </c>
       <c r="O850" t="n">
-        <v>520138</v>
+        <v>518267</v>
       </c>
       <c r="P850" t="n">
         <v>3900</v>
       </c>
       <c r="Q850" t="n">
-        <v>1084200</v>
+        <v>1080300</v>
       </c>
     </row>
     <row r="851">
@@ -37623,22 +37623,22 @@
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M851" t="n">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="N851" t="n">
         <v>1662</v>
       </c>
       <c r="O851" t="n">
-        <v>1086948</v>
+        <v>1081962</v>
       </c>
       <c r="P851" t="n">
         <v>2900</v>
       </c>
       <c r="Q851" t="n">
-        <v>1896600</v>
+        <v>1887900</v>
       </c>
     </row>
     <row r="852">
@@ -37669,22 +37669,22 @@
         <v>0</v>
       </c>
       <c r="L852" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M852" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N852" t="n">
         <v>2003</v>
       </c>
       <c r="O852" t="n">
-        <v>348522</v>
+        <v>344516</v>
       </c>
       <c r="P852" t="n">
         <v>3900</v>
       </c>
       <c r="Q852" t="n">
-        <v>678600</v>
+        <v>670800</v>
       </c>
     </row>
     <row r="853">
@@ -37761,22 +37761,22 @@
         <v>0</v>
       </c>
       <c r="L854" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M854" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N854" t="n">
-        <v>1592.2754925187</v>
+        <v>1592.2755269762</v>
       </c>
       <c r="O854" t="n">
-        <v>187888.5081172066</v>
+        <v>184703.9611292392</v>
       </c>
       <c r="P854" t="n">
         <v>2500</v>
       </c>
       <c r="Q854" t="n">
-        <v>295000</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="855">
@@ -37851,22 +37851,22 @@
         <v>0</v>
       </c>
       <c r="L856" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M856" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N856" t="n">
-        <v>2311.9248916968</v>
+        <v>2311.9247818182</v>
       </c>
       <c r="O856" t="n">
-        <v>145651.2681768984</v>
+        <v>141027.4116909102</v>
       </c>
       <c r="P856" t="n">
         <v>3500</v>
       </c>
       <c r="Q856" t="n">
-        <v>220500</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="857">
@@ -37903,10 +37903,10 @@
         <v>61</v>
       </c>
       <c r="N857" t="n">
-        <v>1906.1862686567</v>
+        <v>1906.18625</v>
       </c>
       <c r="O857" t="n">
-        <v>116277.3623880587</v>
+        <v>116277.36125</v>
       </c>
       <c r="P857" t="n">
         <v>2900</v>
@@ -37943,22 +37943,22 @@
         <v>0</v>
       </c>
       <c r="L858" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M858" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="N858" t="n">
-        <v>2060.1606035889</v>
+        <v>2060.160557377</v>
       </c>
       <c r="O858" t="n">
-        <v>201895.7391517122</v>
+        <v>195715.252950815</v>
       </c>
       <c r="P858" t="n">
         <v>2900</v>
       </c>
       <c r="Q858" t="n">
-        <v>284200</v>
+        <v>275500</v>
       </c>
     </row>
     <row r="859">
@@ -37995,10 +37995,10 @@
         <v>75</v>
       </c>
       <c r="N859" t="n">
-        <v>2546.9851286449</v>
+        <v>2546.9850949914</v>
       </c>
       <c r="O859" t="n">
-        <v>191023.8846483675</v>
+        <v>191023.882124355</v>
       </c>
       <c r="P859" t="n">
         <v>3900</v>
@@ -38041,10 +38041,10 @@
         <v>281</v>
       </c>
       <c r="N860" t="n">
-        <v>1259.2744276316</v>
+        <v>1259.2744422442</v>
       </c>
       <c r="O860" t="n">
-        <v>353856.1141644796</v>
+        <v>353856.1182706202</v>
       </c>
       <c r="P860" t="n">
         <v>1900</v>
@@ -38127,22 +38127,22 @@
         <v>0</v>
       </c>
       <c r="L862" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M862" t="n">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="N862" t="n">
         <v>1801</v>
       </c>
       <c r="O862" t="n">
-        <v>1060789</v>
+        <v>1049983</v>
       </c>
       <c r="P862" t="n">
         <v>2900</v>
       </c>
       <c r="Q862" t="n">
-        <v>1708100</v>
+        <v>1690700</v>
       </c>
     </row>
     <row r="863">
@@ -39644,22 +39644,22 @@
         <v>0</v>
       </c>
       <c r="L895" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M895" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="N895" t="n">
         <v>2357.74</v>
       </c>
       <c r="O895" t="n">
-        <v>273497.84</v>
+        <v>254635.92</v>
       </c>
       <c r="P895" t="n">
         <v>3000</v>
       </c>
       <c r="Q895" t="n">
-        <v>348000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="896">
@@ -40112,10 +40112,10 @@
         <v>309</v>
       </c>
       <c r="N905" t="n">
-        <v>345.55838640256</v>
+        <v>345.55838633169</v>
       </c>
       <c r="O905" t="n">
-        <v>106777.541398391</v>
+        <v>106777.5413764922</v>
       </c>
       <c r="P905" t="n">
         <v>600</v>
@@ -40194,22 +40194,22 @@
         <v>0</v>
       </c>
       <c r="L907" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M907" t="n">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="N907" t="n">
-        <v>2286.1648643761</v>
+        <v>2286.164845735</v>
       </c>
       <c r="O907" t="n">
-        <v>1044777.343019878</v>
+        <v>1035632.675117955</v>
       </c>
       <c r="P907" t="n">
         <v>3000</v>
       </c>
       <c r="Q907" t="n">
-        <v>1371000</v>
+        <v>1359000</v>
       </c>
     </row>
     <row r="908">
@@ -40460,10 +40460,10 @@
         <v>1</v>
       </c>
       <c r="N913" t="n">
-        <v>1283.6540655738</v>
+        <v>1283.653986711</v>
       </c>
       <c r="O913" t="n">
-        <v>1283.6540655738</v>
+        <v>1283.653986711</v>
       </c>
       <c r="P913" t="n">
         <v>1900</v>
@@ -40850,22 +40850,22 @@
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M922" t="n">
-        <v>308</v>
+        <v>68</v>
       </c>
       <c r="N922" t="n">
         <v>177.65</v>
       </c>
       <c r="O922" t="n">
-        <v>54716.2</v>
+        <v>12080.2</v>
       </c>
       <c r="P922" t="n">
         <v>300</v>
       </c>
       <c r="Q922" t="n">
-        <v>92400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="923">
@@ -41160,22 +41160,22 @@
         <v>0</v>
       </c>
       <c r="L929" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M929" t="n">
-        <v>3467</v>
+        <v>3385</v>
       </c>
       <c r="N929" t="n">
-        <v>517.28807221513</v>
+        <v>517.28815469086</v>
       </c>
       <c r="O929" t="n">
-        <v>1793437.746369856</v>
+        <v>1751020.403628561</v>
       </c>
       <c r="P929" t="n">
         <v>900</v>
       </c>
       <c r="Q929" t="n">
-        <v>3120300</v>
+        <v>3046500</v>
       </c>
     </row>
     <row r="930">
@@ -41386,22 +41386,22 @@
         <v>0</v>
       </c>
       <c r="L934" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M934" t="n">
-        <v>674</v>
+        <v>609</v>
       </c>
       <c r="N934" t="n">
-        <v>3110.8429525518</v>
+        <v>3110.8427709611</v>
       </c>
       <c r="O934" t="n">
-        <v>2096708.150019913</v>
+        <v>1894503.24751531</v>
       </c>
       <c r="P934" t="n">
         <v>4500</v>
       </c>
       <c r="Q934" t="n">
-        <v>3033000</v>
+        <v>2740500</v>
       </c>
     </row>
     <row r="935">
@@ -41608,22 +41608,22 @@
         <v>0</v>
       </c>
       <c r="L939" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M939" t="n">
-        <v>1098</v>
+        <v>1058</v>
       </c>
       <c r="N939" t="n">
-        <v>703.79534416571</v>
+        <v>703.79533220158</v>
       </c>
       <c r="O939" t="n">
-        <v>772767.2878939497</v>
+        <v>744615.4614692716</v>
       </c>
       <c r="P939" t="n">
         <v>900</v>
       </c>
       <c r="Q939" t="n">
-        <v>988200</v>
+        <v>952200</v>
       </c>
     </row>
     <row r="940">
@@ -41841,10 +41841,10 @@
         <v>3</v>
       </c>
       <c r="N944" t="n">
-        <v>2501.3854237288</v>
+        <v>2501.3852212389</v>
       </c>
       <c r="O944" t="n">
-        <v>7504.156271186401</v>
+        <v>7504.1556637167</v>
       </c>
       <c r="P944" t="n">
         <v>4100</v>
@@ -42242,10 +42242,10 @@
         <v>14</v>
       </c>
       <c r="N953" t="n">
-        <v>712.6285492228</v>
+        <v>712.62853403141</v>
       </c>
       <c r="O953" t="n">
-        <v>9976.7996891192</v>
+        <v>9976.799476439741</v>
       </c>
       <c r="P953" t="n">
         <v>700</v>
@@ -42359,22 +42359,22 @@
         <v>0</v>
       </c>
       <c r="L956" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M956" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="N956" t="n">
-        <v>2077.4945520231</v>
+        <v>2077.4945652174</v>
       </c>
       <c r="O956" t="n">
-        <v>542226.0780780291</v>
+        <v>538071.0923913067</v>
       </c>
       <c r="P956" t="n">
         <v>2900</v>
       </c>
       <c r="Q956" t="n">
-        <v>756900</v>
+        <v>751100</v>
       </c>
     </row>
     <row r="957">
@@ -42616,19 +42616,19 @@
         <v>74</v>
       </c>
       <c r="K962" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="L962" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="M962" t="n">
         <v>74</v>
       </c>
       <c r="N962" t="n">
-        <v>1595.5190882035</v>
+        <v>1595.5155551576</v>
       </c>
       <c r="O962" t="n">
-        <v>118068.412527059</v>
+        <v>118068.1510816624</v>
       </c>
       <c r="P962" t="n">
         <v>2500</v>
@@ -43150,10 +43150,10 @@
         <v>3</v>
       </c>
       <c r="N973" t="n">
-        <v>2098.4049008499</v>
+        <v>2098.4049147727</v>
       </c>
       <c r="O973" t="n">
-        <v>6295.2147025497</v>
+        <v>6295.2147443181</v>
       </c>
       <c r="P973" t="n">
         <v>9500</v>
@@ -43812,10 +43812,10 @@
         <v>16</v>
       </c>
       <c r="N987" t="n">
-        <v>3414.5660805577</v>
+        <v>3414.5660775194</v>
       </c>
       <c r="O987" t="n">
-        <v>54633.0572889232</v>
+        <v>54633.0572403104</v>
       </c>
       <c r="P987" t="n">
         <v>3500</v>
@@ -44262,16 +44262,16 @@
         <v>107</v>
       </c>
       <c r="K997" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="L997" t="n">
         <v>0</v>
       </c>
       <c r="M997" t="n">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="N997" t="n">
-        <v>1759.84</v>
+        <v>801.28885106383</v>
       </c>
       <c r="O997" t="n">
         <v>188302.88</v>
@@ -44280,7 +44280,7 @@
         <v>3300</v>
       </c>
       <c r="Q997" t="n">
-        <v>353100</v>
+        <v>775500</v>
       </c>
     </row>
     <row r="998">
@@ -44735,10 +44735,10 @@
         <v>2</v>
       </c>
       <c r="N1007" t="n">
-        <v>2000.6614375</v>
+        <v>2000.6660784314</v>
       </c>
       <c r="O1007" t="n">
-        <v>4001.322875</v>
+        <v>4001.3321568628</v>
       </c>
       <c r="P1007" t="n">
         <v>2000</v>
@@ -45015,22 +45015,22 @@
         <v>0</v>
       </c>
       <c r="L1013" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1013" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N1013" t="n">
         <v>7465.9</v>
       </c>
       <c r="O1013" t="n">
-        <v>179181.6</v>
+        <v>156783.9</v>
       </c>
       <c r="P1013" t="n">
         <v>11900</v>
       </c>
       <c r="Q1013" t="n">
-        <v>285600</v>
+        <v>249900</v>
       </c>
     </row>
     <row r="1014">
@@ -45114,10 +45114,10 @@
         <v>215</v>
       </c>
       <c r="N1015" t="n">
-        <v>7046.9398299681</v>
+        <v>7046.939829932</v>
       </c>
       <c r="O1015" t="n">
-        <v>1515092.063443142</v>
+        <v>1515092.06343538</v>
       </c>
       <c r="P1015" t="n">
         <v>9900</v>
@@ -46045,22 +46045,22 @@
         <v>0</v>
       </c>
       <c r="L1035" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1035" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N1035" t="n">
         <v>2752.52</v>
       </c>
       <c r="O1035" t="n">
-        <v>41287.8</v>
+        <v>38535.28</v>
       </c>
       <c r="P1035" t="n">
         <v>4500</v>
       </c>
       <c r="Q1035" t="n">
-        <v>67500</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="1036">
@@ -46511,22 +46511,22 @@
         <v>0</v>
       </c>
       <c r="L1046" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1046" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N1046" t="n">
         <v>110520.77</v>
       </c>
       <c r="O1046" t="n">
-        <v>4531351.57</v>
+        <v>4420830.8</v>
       </c>
       <c r="P1046" t="n">
         <v>176900</v>
       </c>
       <c r="Q1046" t="n">
-        <v>7252900</v>
+        <v>7076000</v>
       </c>
     </row>
     <row r="1047">
@@ -46725,10 +46725,10 @@
         <v>57</v>
       </c>
       <c r="N1051" t="n">
-        <v>5577.2680778032</v>
+        <v>5577.2680733945</v>
       </c>
       <c r="O1051" t="n">
-        <v>317904.2804347824</v>
+        <v>317904.2801834865</v>
       </c>
       <c r="P1051" t="n">
         <v>6500</v>
@@ -47668,25 +47668,25 @@
         <v>267</v>
       </c>
       <c r="K1073" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L1073" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M1073" t="n">
-        <v>267</v>
+        <v>454</v>
       </c>
       <c r="N1073" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1073" t="n">
-        <v>849567.3</v>
+        <v>1444582.6</v>
       </c>
       <c r="P1073" t="n">
         <v>5100</v>
       </c>
       <c r="Q1073" t="n">
-        <v>1361700</v>
+        <v>2315400</v>
       </c>
     </row>
     <row r="1074">
@@ -48149,22 +48149,22 @@
         <v>0</v>
       </c>
       <c r="L1084" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1084" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N1084" t="n">
-        <v>2523.3377476715</v>
+        <v>2523.3377470356</v>
       </c>
       <c r="O1084" t="n">
-        <v>103456.8476545315</v>
+        <v>100933.509881424</v>
       </c>
       <c r="P1084" t="n">
         <v>2800</v>
       </c>
       <c r="Q1084" t="n">
-        <v>114800</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="1085">
@@ -48735,22 +48735,22 @@
         <v>0</v>
       </c>
       <c r="L1098" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1098" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N1098" t="n">
         <v>7313</v>
       </c>
       <c r="O1098" t="n">
-        <v>131634</v>
+        <v>95069</v>
       </c>
       <c r="P1098" t="n">
         <v>9800</v>
       </c>
       <c r="Q1098" t="n">
-        <v>176400</v>
+        <v>127400</v>
       </c>
     </row>
     <row r="1099">
@@ -48825,22 +48825,22 @@
         <v>0</v>
       </c>
       <c r="L1100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1100" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N1100" t="n">
         <v>5077</v>
       </c>
       <c r="O1100" t="n">
-        <v>726011</v>
+        <v>705703</v>
       </c>
       <c r="P1100" t="n">
         <v>8500</v>
       </c>
       <c r="Q1100" t="n">
-        <v>1215500</v>
+        <v>1181500</v>
       </c>
     </row>
     <row r="1101">
@@ -49409,10 +49409,10 @@
         <v>2</v>
       </c>
       <c r="N1113" t="n">
-        <v>12601.098571429</v>
+        <v>12601.0975</v>
       </c>
       <c r="O1113" t="n">
-        <v>25202.197142858</v>
+        <v>25202.195</v>
       </c>
       <c r="P1113" t="n">
         <v>15900</v>
@@ -49746,12 +49746,12 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>J-556</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>VUVUCELA 25CM J-556</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
@@ -49765,39 +49765,39 @@
         </is>
       </c>
       <c r="J1121" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K1121" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="L1121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1121" t="n">
-        <v>18</v>
+        <v>429</v>
       </c>
       <c r="N1121" t="n">
-        <v>1260</v>
+        <v>7480</v>
       </c>
       <c r="O1121" t="n">
-        <v>22680</v>
+        <v>3208920</v>
       </c>
       <c r="P1121" t="n">
-        <v>1700</v>
+        <v>9500</v>
       </c>
       <c r="Q1121" t="n">
-        <v>30600</v>
+        <v>4075500</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>J-557</t>
+          <t>J-556</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>VUVUCELA 50 cm J-557</t>
+          <t>VUVUCELA 25CM J-556</t>
         </is>
       </c>
       <c r="E1122" t="inlineStr">
@@ -49811,7 +49811,7 @@
         </is>
       </c>
       <c r="J1122" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K1122" t="n">
         <v>0</v>
@@ -49820,30 +49820,30 @@
         <v>0</v>
       </c>
       <c r="M1122" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N1122" t="n">
-        <v>2250</v>
+        <v>1260</v>
       </c>
       <c r="O1122" t="n">
-        <v>6750</v>
+        <v>22680</v>
       </c>
       <c r="P1122" t="n">
-        <v>3000</v>
+        <v>1700</v>
       </c>
       <c r="Q1122" t="n">
-        <v>9000</v>
+        <v>30600</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>J-984</t>
+          <t>J-557</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>PELOTA LUNAR J-984</t>
+          <t>VUVUCELA 50 cm J-557</t>
         </is>
       </c>
       <c r="E1123" t="inlineStr">
@@ -49857,7 +49857,7 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
@@ -49866,30 +49866,30 @@
         <v>0</v>
       </c>
       <c r="M1123" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="N1123" t="n">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="O1123" t="n">
-        <v>142200</v>
+        <v>6750</v>
       </c>
       <c r="P1123" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="Q1123" t="n">
-        <v>173800</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>JBL0531</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>RESALTADORES FLUORESCENTE X6 JBL0531</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E1124" t="inlineStr">
@@ -49903,39 +49903,39 @@
         </is>
       </c>
       <c r="J1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1124" t="n">
+        <v>720</v>
+      </c>
+      <c r="L1124" t="n">
         <v>11</v>
       </c>
-      <c r="K1124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1124" t="n">
-        <v>0</v>
-      </c>
       <c r="M1124" t="n">
-        <v>11</v>
+        <v>709</v>
       </c>
       <c r="N1124" t="n">
-        <v>4200</v>
+        <v>9240</v>
       </c>
       <c r="O1124" t="n">
-        <v>46200</v>
+        <v>6551160</v>
       </c>
       <c r="P1124" t="n">
-        <v>5100</v>
+        <v>11500</v>
       </c>
       <c r="Q1124" t="n">
-        <v>56100</v>
+        <v>8153500</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>JBL0536</t>
+          <t>J-984</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>SET DE REGLAS X7PCS JBL0536</t>
+          <t>PELOTA LUNAR J-984</t>
         </is>
       </c>
       <c r="E1125" t="inlineStr">
@@ -49949,7 +49949,7 @@
         </is>
       </c>
       <c r="J1125" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="K1125" t="n">
         <v>0</v>
@@ -49958,30 +49958,30 @@
         <v>0</v>
       </c>
       <c r="M1125" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="N1125" t="n">
-        <v>5900</v>
+        <v>1800</v>
       </c>
       <c r="O1125" t="n">
-        <v>59000</v>
+        <v>142200</v>
       </c>
       <c r="P1125" t="n">
-        <v>7100</v>
+        <v>2200</v>
       </c>
       <c r="Q1125" t="n">
-        <v>71000</v>
+        <v>173800</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>JBL0538</t>
+          <t>JBL0531</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA X12JBL0538</t>
+          <t>RESALTADORES FLUORESCENTE X6 JBL0531</t>
         </is>
       </c>
       <c r="E1126" t="inlineStr">
@@ -49995,7 +49995,7 @@
         </is>
       </c>
       <c r="J1126" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K1126" t="n">
         <v>0</v>
@@ -50004,30 +50004,30 @@
         <v>0</v>
       </c>
       <c r="M1126" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N1126" t="n">
-        <v>9500</v>
+        <v>4200</v>
       </c>
       <c r="O1126" t="n">
-        <v>47500</v>
+        <v>46200</v>
       </c>
       <c r="P1126" t="n">
-        <v>11400</v>
+        <v>5100</v>
       </c>
       <c r="Q1126" t="n">
-        <v>57000</v>
+        <v>56100</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>JBL0539</t>
+          <t>JBL0536</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA PLASTICA X24 JBL0539</t>
+          <t>SET DE REGLAS X7PCS JBL0536</t>
         </is>
       </c>
       <c r="E1127" t="inlineStr">
@@ -50041,7 +50041,7 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
@@ -50050,30 +50050,30 @@
         <v>0</v>
       </c>
       <c r="M1127" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N1127" t="n">
-        <v>17500</v>
+        <v>5900</v>
       </c>
       <c r="O1127" t="n">
-        <v>210000</v>
+        <v>59000</v>
       </c>
       <c r="P1127" t="n">
-        <v>21000</v>
+        <v>7100</v>
       </c>
       <c r="Q1127" t="n">
-        <v>252000</v>
+        <v>71000</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>JBL0540</t>
+          <t>JBL0538</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA PLASTICA X36 JBL0540</t>
+          <t>MARCADORES CAJA X12JBL0538</t>
         </is>
       </c>
       <c r="E1128" t="inlineStr">
@@ -50087,7 +50087,7 @@
         </is>
       </c>
       <c r="J1128" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K1128" t="n">
         <v>0</v>
@@ -50096,30 +50096,30 @@
         <v>0</v>
       </c>
       <c r="M1128" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="N1128" t="n">
-        <v>25000</v>
+        <v>9500</v>
       </c>
       <c r="O1128" t="n">
-        <v>575000</v>
+        <v>47500</v>
       </c>
       <c r="P1128" t="n">
-        <v>30000</v>
+        <v>11400</v>
       </c>
       <c r="Q1128" t="n">
-        <v>690000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>JBL0541</t>
+          <t>JBL0539</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>ESFERO DE COLOR LAVABLE OSITOS JBL0541</t>
+          <t>MARCADORES CAJA PLASTICA X24 JBL0539</t>
         </is>
       </c>
       <c r="E1129" t="inlineStr">
@@ -50133,7 +50133,7 @@
         </is>
       </c>
       <c r="J1129" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K1129" t="n">
         <v>0</v>
@@ -50142,30 +50142,30 @@
         <v>0</v>
       </c>
       <c r="M1129" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N1129" t="n">
-        <v>4500</v>
+        <v>17500</v>
       </c>
       <c r="O1129" t="n">
-        <v>9000</v>
+        <v>210000</v>
       </c>
       <c r="P1129" t="n">
-        <v>5400</v>
+        <v>21000</v>
       </c>
       <c r="Q1129" t="n">
-        <v>10800</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>JBL0554</t>
+          <t>JBL0540</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>CAJA DE COLORES X 12 PCS JBL0554</t>
+          <t>MARCADORES CAJA PLASTICA X36 JBL0540</t>
         </is>
       </c>
       <c r="E1130" t="inlineStr">
@@ -50179,7 +50179,7 @@
         </is>
       </c>
       <c r="J1130" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K1130" t="n">
         <v>0</v>
@@ -50188,30 +50188,30 @@
         <v>0</v>
       </c>
       <c r="M1130" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N1130" t="n">
-        <v>9500</v>
+        <v>25000</v>
       </c>
       <c r="O1130" t="n">
-        <v>161500</v>
+        <v>575000</v>
       </c>
       <c r="P1130" t="n">
-        <v>11400</v>
+        <v>30000</v>
       </c>
       <c r="Q1130" t="n">
-        <v>193800</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>JBL0557</t>
+          <t>JBL0541</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>CAJA COLORES MINI X 12 PCS  JBL0557</t>
+          <t>ESFERO DE COLOR LAVABLE OSITOS JBL0541</t>
         </is>
       </c>
       <c r="E1131" t="inlineStr">
@@ -50225,7 +50225,7 @@
         </is>
       </c>
       <c r="J1131" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="K1131" t="n">
         <v>0</v>
@@ -50234,30 +50234,30 @@
         <v>0</v>
       </c>
       <c r="M1131" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="N1131" t="n">
-        <v>2900</v>
+        <v>4500</v>
       </c>
       <c r="O1131" t="n">
-        <v>124700</v>
+        <v>9000</v>
       </c>
       <c r="P1131" t="n">
-        <v>3500</v>
+        <v>5400</v>
       </c>
       <c r="Q1131" t="n">
-        <v>150500</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>JBL0657</t>
+          <t>JBL0554</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>TAJALAPIZ CON DEPOSITO JBL0657</t>
+          <t>CAJA DE COLORES X 12 PCS JBL0554</t>
         </is>
       </c>
       <c r="E1132" t="inlineStr">
@@ -50271,7 +50271,7 @@
         </is>
       </c>
       <c r="J1132" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K1132" t="n">
         <v>0</v>
@@ -50280,30 +50280,30 @@
         <v>0</v>
       </c>
       <c r="M1132" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="N1132" t="n">
-        <v>1000</v>
+        <v>9500</v>
       </c>
       <c r="O1132" t="n">
-        <v>29000</v>
+        <v>161500</v>
       </c>
       <c r="P1132" t="n">
-        <v>1200</v>
+        <v>11400</v>
       </c>
       <c r="Q1132" t="n">
-        <v>34800</v>
+        <v>193800</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>JBL0707</t>
+          <t>JBL0557</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>SET GEOMETRICO FLEXIBLE X 4 PCS JBL0707</t>
+          <t>CAJA COLORES MINI X 12 PCS  JBL0557</t>
         </is>
       </c>
       <c r="E1133" t="inlineStr">
@@ -50317,7 +50317,7 @@
         </is>
       </c>
       <c r="J1133" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="K1133" t="n">
         <v>0</v>
@@ -50326,30 +50326,30 @@
         <v>0</v>
       </c>
       <c r="M1133" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="N1133" t="n">
-        <v>3600</v>
+        <v>2900</v>
       </c>
       <c r="O1133" t="n">
-        <v>64800</v>
+        <v>124700</v>
       </c>
       <c r="P1133" t="n">
-        <v>4400</v>
+        <v>3500</v>
       </c>
       <c r="Q1133" t="n">
-        <v>79200</v>
+        <v>150500</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>JBL0729</t>
+          <t>JBL0657</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>LONCHERA INFANTIL MODELOS STD 22,5cm JBL0729</t>
+          <t>TAJALAPIZ CON DEPOSITO JBL0657</t>
         </is>
       </c>
       <c r="E1134" t="inlineStr">
@@ -50363,7 +50363,7 @@
         </is>
       </c>
       <c r="J1134" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="K1134" t="n">
         <v>0</v>
@@ -50372,30 +50372,30 @@
         <v>0</v>
       </c>
       <c r="M1134" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1134" t="n">
-        <v>9300</v>
+        <v>1000</v>
       </c>
       <c r="O1134" t="n">
-        <v>65100</v>
+        <v>29000</v>
       </c>
       <c r="P1134" t="n">
-        <v>11200</v>
+        <v>1200</v>
       </c>
       <c r="Q1134" t="n">
-        <v>78400</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>JO-129</t>
+          <t>JBL0707</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>LAPICES COLORES X12 DOBLE PUNTA JO-129</t>
+          <t>SET GEOMETRICO FLEXIBLE X 4 PCS JBL0707</t>
         </is>
       </c>
       <c r="E1135" t="inlineStr">
@@ -50409,7 +50409,7 @@
         </is>
       </c>
       <c r="J1135" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K1135" t="n">
         <v>0</v>
@@ -50418,30 +50418,30 @@
         <v>0</v>
       </c>
       <c r="M1135" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N1135" t="n">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="O1135" t="n">
-        <v>63000</v>
+        <v>64800</v>
       </c>
       <c r="P1135" t="n">
-        <v>5400</v>
+        <v>4400</v>
       </c>
       <c r="Q1135" t="n">
-        <v>75600</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>JO-139</t>
+          <t>JBL0729</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>ESFERO GIRATORIO 10 MINAS MUÑECA JO-139</t>
+          <t>LONCHERA INFANTIL MODELOS STD 22,5cm JBL0729</t>
         </is>
       </c>
       <c r="E1136" t="inlineStr">
@@ -50455,7 +50455,7 @@
         </is>
       </c>
       <c r="J1136" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="K1136" t="n">
         <v>0</v>
@@ -50464,30 +50464,30 @@
         <v>0</v>
       </c>
       <c r="M1136" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="N1136" t="n">
-        <v>2700</v>
+        <v>9300</v>
       </c>
       <c r="O1136" t="n">
-        <v>145800</v>
+        <v>65100</v>
       </c>
       <c r="P1136" t="n">
-        <v>3300</v>
+        <v>11200</v>
       </c>
       <c r="Q1136" t="n">
-        <v>178200</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>JO-141</t>
+          <t>JO-129</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE FAST FOOD JO-141</t>
+          <t>LAPICES COLORES X12 DOBLE PUNTA JO-129</t>
         </is>
       </c>
       <c r="E1137" t="inlineStr">
@@ -50501,7 +50501,7 @@
         </is>
       </c>
       <c r="J1137" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="K1137" t="n">
         <v>0</v>
@@ -50510,30 +50510,30 @@
         <v>0</v>
       </c>
       <c r="M1137" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="N1137" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="O1137" t="n">
-        <v>102000</v>
+        <v>63000</v>
       </c>
       <c r="P1137" t="n">
-        <v>1800</v>
+        <v>5400</v>
       </c>
       <c r="Q1137" t="n">
-        <v>122400</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>JO-142</t>
+          <t>JO-139</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR ASTRONAUTA JO-142</t>
+          <t>ESFERO GIRATORIO 10 MINAS MUÑECA JO-139</t>
         </is>
       </c>
       <c r="E1138" t="inlineStr">
@@ -50547,7 +50547,7 @@
         </is>
       </c>
       <c r="J1138" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="K1138" t="n">
         <v>0</v>
@@ -50556,30 +50556,30 @@
         <v>0</v>
       </c>
       <c r="M1138" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="N1138" t="n">
-        <v>1900</v>
+        <v>2700</v>
       </c>
       <c r="O1138" t="n">
-        <v>134900</v>
+        <v>145800</v>
       </c>
       <c r="P1138" t="n">
-        <v>2300</v>
+        <v>3300</v>
       </c>
       <c r="Q1138" t="n">
-        <v>163300</v>
+        <v>178200</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>JO-143</t>
+          <t>JO-141</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>ESFERO BORRABKLE CON BORRADOR ARCOIRIS JO-143</t>
+          <t>ESFERO BORRABLE FAST FOOD JO-141</t>
         </is>
       </c>
       <c r="E1139" t="inlineStr">
@@ -50605,27 +50605,27 @@
         <v>68</v>
       </c>
       <c r="N1139" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="O1139" t="n">
-        <v>95200</v>
+        <v>102000</v>
       </c>
       <c r="P1139" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="Q1139" t="n">
-        <v>115600</v>
+        <v>122400</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>JO-144</t>
+          <t>JO-142</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR PANDA JO-144</t>
+          <t>ESFERO BORRABLE CON BORRADOR ASTRONAUTA JO-142</t>
         </is>
       </c>
       <c r="E1140" t="inlineStr">
@@ -50639,7 +50639,7 @@
         </is>
       </c>
       <c r="J1140" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K1140" t="n">
         <v>0</v>
@@ -50648,30 +50648,30 @@
         <v>0</v>
       </c>
       <c r="M1140" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N1140" t="n">
         <v>1900</v>
       </c>
       <c r="O1140" t="n">
-        <v>133000</v>
+        <v>134900</v>
       </c>
       <c r="P1140" t="n">
         <v>2300</v>
       </c>
       <c r="Q1140" t="n">
-        <v>161000</v>
+        <v>163300</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>JO-145</t>
+          <t>JO-143</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR OSITO JO-145</t>
+          <t>ESFERO BORRABKLE CON BORRADOR ARCOIRIS JO-143</t>
         </is>
       </c>
       <c r="E1141" t="inlineStr">
@@ -50685,7 +50685,7 @@
         </is>
       </c>
       <c r="J1141" t="n">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="K1141" t="n">
         <v>0</v>
@@ -50694,30 +50694,30 @@
         <v>0</v>
       </c>
       <c r="M1141" t="n">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="N1141" t="n">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="O1141" t="n">
-        <v>262200</v>
+        <v>95200</v>
       </c>
       <c r="P1141" t="n">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="Q1141" t="n">
-        <v>317400</v>
+        <v>115600</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>JOE-1813</t>
+          <t>JO-144</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>SET MARCADORES ACUARELA LAVAVBLE TUBO X 18 PCS JOE-1813</t>
+          <t>ESFERO BORRABLE CON BORRADOR PANDA JO-144</t>
         </is>
       </c>
       <c r="E1142" t="inlineStr">
@@ -50731,7 +50731,7 @@
         </is>
       </c>
       <c r="J1142" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="K1142" t="n">
         <v>0</v>
@@ -50740,30 +50740,30 @@
         <v>0</v>
       </c>
       <c r="M1142" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="N1142" t="n">
-        <v>6000</v>
+        <v>1900</v>
       </c>
       <c r="O1142" t="n">
-        <v>102000</v>
+        <v>133000</v>
       </c>
       <c r="P1142" t="n">
-        <v>7200</v>
+        <v>2300</v>
       </c>
       <c r="Q1142" t="n">
-        <v>122400</v>
+        <v>161000</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>JOE-9812</t>
+          <t>JO-145</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>SET MARCADORES JUMBO ACUARELA X12/14cm</t>
+          <t>ESFERO BORRABLE CON BORRADOR OSITO JO-145</t>
         </is>
       </c>
       <c r="E1143" t="inlineStr">
@@ -50777,7 +50777,7 @@
         </is>
       </c>
       <c r="J1143" t="n">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="K1143" t="n">
         <v>0</v>
@@ -50786,30 +50786,30 @@
         <v>0</v>
       </c>
       <c r="M1143" t="n">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="N1143" t="n">
-        <v>5000</v>
+        <v>1900</v>
       </c>
       <c r="O1143" t="n">
-        <v>50000</v>
+        <v>262200</v>
       </c>
       <c r="P1143" t="n">
-        <v>6000</v>
+        <v>2300</v>
       </c>
       <c r="Q1143" t="n">
-        <v>60000</v>
+        <v>317400</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>JT-13</t>
+          <t>JOE-1813</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>CORRECTOR EN CINTA JT-13</t>
+          <t>SET MARCADORES ACUARELA LAVAVBLE TUBO X 18 PCS JOE-1813</t>
         </is>
       </c>
       <c r="E1144" t="inlineStr">
@@ -50823,7 +50823,7 @@
         </is>
       </c>
       <c r="J1144" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K1144" t="n">
         <v>0</v>
@@ -50832,39 +50832,44 @@
         <v>0</v>
       </c>
       <c r="M1144" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N1144" t="n">
-        <v>2400</v>
+        <v>6000</v>
       </c>
       <c r="O1144" t="n">
-        <v>55200</v>
+        <v>102000</v>
       </c>
       <c r="P1144" t="n">
-        <v>2900</v>
+        <v>7200</v>
       </c>
       <c r="Q1144" t="n">
-        <v>66700</v>
+        <v>122400</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>KBX-3088</t>
+          <t>JOE-9812</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>BORRADOR PORTAMINAS</t>
+          <t>SET MARCADORES JUMBO ACUARELA X12/14cm</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1145" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1145" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K1145" t="n">
         <v>0</v>
@@ -50873,30 +50878,30 @@
         <v>0</v>
       </c>
       <c r="M1145" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="N1145" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O1145" t="n">
-        <v>69000</v>
+        <v>50000</v>
       </c>
       <c r="P1145" t="n">
-        <v>3600</v>
+        <v>6000</v>
       </c>
       <c r="Q1145" t="n">
-        <v>82800</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>JT-13</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>CORRECTOR EN CINTA JT-13</t>
         </is>
       </c>
       <c r="E1146" t="inlineStr">
@@ -50910,7 +50915,7 @@
         </is>
       </c>
       <c r="J1146" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K1146" t="n">
         <v>0</v>
@@ -50919,44 +50924,39 @@
         <v>0</v>
       </c>
       <c r="M1146" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N1146" t="n">
-        <v>415.07</v>
+        <v>2400</v>
       </c>
       <c r="O1146" t="n">
-        <v>1245.21</v>
+        <v>55200</v>
       </c>
       <c r="P1146" t="n">
         <v>2900</v>
       </c>
       <c r="Q1146" t="n">
-        <v>8700</v>
+        <v>66700</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>MC121011-E</t>
+          <t>KBX-3088</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>SET LAPIZ CON BORRADOR OSITOS MC121011-E</t>
-        </is>
-      </c>
-      <c r="E1147" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>BORRADOR PORTAMINAS</t>
         </is>
       </c>
       <c r="I1147" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1147" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K1147" t="n">
         <v>0</v>
@@ -50965,30 +50965,30 @@
         <v>0</v>
       </c>
       <c r="M1147" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="N1147" t="n">
-        <v>6500</v>
+        <v>3000</v>
       </c>
       <c r="O1147" t="n">
-        <v>45500</v>
+        <v>69000</v>
       </c>
       <c r="P1147" t="n">
-        <v>7800</v>
+        <v>3600</v>
       </c>
       <c r="Q1147" t="n">
-        <v>54600</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>MC121206-E</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>SET DE LAPICES CON BORRADOR  MC121206-E</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E1148" t="inlineStr">
@@ -51002,7 +51002,7 @@
         </is>
       </c>
       <c r="J1148" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K1148" t="n">
         <v>0</v>
@@ -51011,30 +51011,30 @@
         <v>0</v>
       </c>
       <c r="M1148" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N1148" t="n">
-        <v>6500</v>
+        <v>415.07</v>
       </c>
       <c r="O1148" t="n">
-        <v>45500</v>
+        <v>1245.21</v>
       </c>
       <c r="P1148" t="n">
-        <v>7800</v>
+        <v>2900</v>
       </c>
       <c r="Q1148" t="n">
-        <v>54600</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>MC121212</t>
+          <t>MC121011-E</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
+          <t>SET LAPIZ CON BORRADOR OSITOS MC121011-E</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
@@ -51048,7 +51048,7 @@
         </is>
       </c>
       <c r="J1149" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K1149" t="n">
         <v>0</v>
@@ -51057,35 +51057,35 @@
         <v>0</v>
       </c>
       <c r="M1149" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N1149" t="n">
         <v>6500</v>
       </c>
       <c r="O1149" t="n">
-        <v>104000</v>
+        <v>45500</v>
       </c>
       <c r="P1149" t="n">
         <v>7800</v>
       </c>
       <c r="Q1149" t="n">
-        <v>124800</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>MG21714</t>
+          <t>MC121206-E</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
+          <t>SET DE LAPICES CON BORRADOR  MC121206-E</t>
         </is>
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1150" t="inlineStr">
@@ -51094,7 +51094,7 @@
         </is>
       </c>
       <c r="J1150" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="K1150" t="n">
         <v>0</v>
@@ -51103,35 +51103,35 @@
         <v>0</v>
       </c>
       <c r="M1150" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="N1150" t="n">
-        <v>576.58</v>
+        <v>6500</v>
       </c>
       <c r="O1150" t="n">
-        <v>13837.92</v>
+        <v>45500</v>
       </c>
       <c r="P1150" t="n">
-        <v>5900</v>
+        <v>7800</v>
       </c>
       <c r="Q1150" t="n">
-        <v>141600</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>MG22440</t>
+          <t>MC121212</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
+          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
         </is>
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1151" t="inlineStr">
@@ -51140,7 +51140,7 @@
         </is>
       </c>
       <c r="J1151" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K1151" t="n">
         <v>0</v>
@@ -51149,40 +51149,35 @@
         <v>0</v>
       </c>
       <c r="M1151" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N1151" t="n">
-        <v>8174.05</v>
+        <v>6500</v>
       </c>
       <c r="O1151" t="n">
-        <v>8174.05</v>
+        <v>104000</v>
       </c>
       <c r="P1151" t="n">
-        <v>8900</v>
+        <v>7800</v>
       </c>
       <c r="Q1151" t="n">
-        <v>8900</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B1152" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG21714</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
         </is>
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I1152" t="inlineStr">
@@ -51191,7 +51186,7 @@
         </is>
       </c>
       <c r="J1152" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K1152" t="n">
         <v>0</v>
@@ -51200,35 +51195,35 @@
         <v>0</v>
       </c>
       <c r="M1152" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N1152" t="n">
-        <v>751.45</v>
+        <v>576.58</v>
       </c>
       <c r="O1152" t="n">
-        <v>751.45</v>
+        <v>13837.92</v>
       </c>
       <c r="P1152" t="n">
-        <v>2500</v>
+        <v>5900</v>
       </c>
       <c r="Q1152" t="n">
-        <v>2500</v>
+        <v>141600</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>MG40207</t>
+          <t>MG22440</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>SONAJERO DOBLE HELICE MG40207</t>
+          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
         </is>
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I1153" t="inlineStr">
@@ -51249,32 +51244,37 @@
         <v>1</v>
       </c>
       <c r="N1153" t="n">
-        <v>323.9775</v>
+        <v>8174.05</v>
       </c>
       <c r="O1153" t="n">
-        <v>323.9775</v>
+        <v>8174.05</v>
       </c>
       <c r="P1153" t="n">
-        <v>1500</v>
+        <v>8900</v>
       </c>
       <c r="Q1153" t="n">
-        <v>1500</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>MG40226</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>ATARY COCODRILO MG40226</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I1154" t="inlineStr">
@@ -51283,7 +51283,7 @@
         </is>
       </c>
       <c r="J1154" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K1154" t="n">
         <v>0</v>
@@ -51292,35 +51292,35 @@
         <v>0</v>
       </c>
       <c r="M1154" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N1154" t="n">
-        <v>310.41666666667</v>
+        <v>751.45</v>
       </c>
       <c r="O1154" t="n">
-        <v>2172.91666666669</v>
+        <v>751.45</v>
       </c>
       <c r="P1154" t="n">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="Q1154" t="n">
-        <v>12600</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40207</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>SONAJERO DOBLE HELICE MG40207</t>
         </is>
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I1155" t="inlineStr">
@@ -51329,7 +51329,7 @@
         </is>
       </c>
       <c r="J1155" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="K1155" t="n">
         <v>0</v>
@@ -51338,35 +51338,35 @@
         <v>0</v>
       </c>
       <c r="M1155" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="N1155" t="n">
-        <v>227.41597222222</v>
+        <v>323.9775</v>
       </c>
       <c r="O1155" t="n">
-        <v>26380.25277777752</v>
+        <v>323.9775</v>
       </c>
       <c r="P1155" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="Q1155" t="n">
-        <v>139200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>MG40836</t>
+          <t>MG40226</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>MUÑECO GUERRERO BOLSA MG40836</t>
+          <t>ATARY COCODRILO MG40226</t>
         </is>
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>MUÑECOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1156" t="inlineStr">
@@ -51375,7 +51375,7 @@
         </is>
       </c>
       <c r="J1156" t="n">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="K1156" t="n">
         <v>0</v>
@@ -51384,40 +51384,35 @@
         <v>0</v>
       </c>
       <c r="M1156" t="n">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="N1156" t="n">
-        <v>1441.78</v>
+        <v>310.41666666667</v>
       </c>
       <c r="O1156" t="n">
-        <v>149945.12</v>
+        <v>2172.91666666669</v>
       </c>
       <c r="P1156" t="n">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="Q1156" t="n">
-        <v>249600</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>MG40952</t>
-        </is>
-      </c>
-      <c r="B1157" t="inlineStr">
-        <is>
-          <t>MG40952</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>CAMIONETA BLACK MG40952</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I1157" t="inlineStr">
@@ -51426,7 +51421,7 @@
         </is>
       </c>
       <c r="J1157" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="K1157" t="n">
         <v>0</v>
@@ -51435,39 +51430,44 @@
         <v>0</v>
       </c>
       <c r="M1157" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="N1157" t="n">
-        <v>38043.57</v>
+        <v>227.41597222222</v>
       </c>
       <c r="O1157" t="n">
-        <v>38043.57</v>
+        <v>26380.25277777752</v>
       </c>
       <c r="P1157" t="n">
-        <v>70900</v>
+        <v>1200</v>
       </c>
       <c r="Q1157" t="n">
-        <v>70900</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>P155</t>
+          <t>MG40836</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>BT-3002 LAPIZ PORTAMINAS CONEJO</t>
+          <t>MUÑECO GUERRERO BOLSA MG40836</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I1158" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1158" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="K1158" t="n">
         <v>0</v>
@@ -51476,35 +51476,45 @@
         <v>0</v>
       </c>
       <c r="M1158" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="N1158" t="n">
-        <v>1461.53</v>
+        <v>1441.78</v>
       </c>
       <c r="O1158" t="n">
-        <v>1461.53</v>
+        <v>149945.12</v>
       </c>
       <c r="P1158" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="Q1158" t="n">
-        <v>1900</v>
+        <v>249600</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>P214</t>
+          <t>MG40952</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>MG40952</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLOBO FELIZ CUMPLEAÑOS COLORES VIVOS </t>
+          <t>CAMIONETA BLACK MG40952</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I1159" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1159" t="n">
@@ -51520,27 +51530,27 @@
         <v>1</v>
       </c>
       <c r="N1159" t="n">
-        <v>3153.85</v>
+        <v>38043.57</v>
       </c>
       <c r="O1159" t="n">
-        <v>3153.85</v>
+        <v>38043.57</v>
       </c>
       <c r="P1159" t="n">
-        <v>4100</v>
+        <v>70900</v>
       </c>
       <c r="Q1159" t="n">
-        <v>4100</v>
+        <v>70900</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>P458</t>
+          <t>P155</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>IF2826 VELAS COLRES SURTIDOSX6 P548</t>
+          <t>BT-3002 LAPIZ PORTAMINAS CONEJO</t>
         </is>
       </c>
       <c r="I1160" t="inlineStr">
@@ -51549,7 +51559,7 @@
         </is>
       </c>
       <c r="J1160" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K1160" t="n">
         <v>0</v>
@@ -51558,40 +51568,35 @@
         <v>0</v>
       </c>
       <c r="M1160" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="N1160" t="n">
-        <v>1230.76</v>
+        <v>1461.53</v>
       </c>
       <c r="O1160" t="n">
-        <v>39384.32</v>
+        <v>1461.53</v>
       </c>
       <c r="P1160" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="Q1160" t="n">
-        <v>51200</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>PT14026</t>
+          <t>P214</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
-        </is>
-      </c>
-      <c r="E1161" t="inlineStr">
-        <is>
-          <t>DIDACTICOS</t>
+          <t xml:space="preserve">GLOBO FELIZ CUMPLEAÑOS COLORES VIVOS </t>
         </is>
       </c>
       <c r="I1161" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1161" t="n">
@@ -51607,27 +51612,27 @@
         <v>1</v>
       </c>
       <c r="N1161" t="n">
-        <v>2690.69</v>
+        <v>3153.85</v>
       </c>
       <c r="O1161" t="n">
-        <v>2690.69</v>
+        <v>3153.85</v>
       </c>
       <c r="P1161" t="n">
-        <v>5900</v>
+        <v>4100</v>
       </c>
       <c r="Q1161" t="n">
-        <v>5900</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>Q1241</t>
+          <t>P458</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>RESALTADOR BOTELLA</t>
+          <t>IF2826 VELAS COLRES SURTIDOSX6 P548</t>
         </is>
       </c>
       <c r="I1162" t="inlineStr">
@@ -51636,7 +51641,7 @@
         </is>
       </c>
       <c r="J1162" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="K1162" t="n">
         <v>0</v>
@@ -51645,35 +51650,35 @@
         <v>0</v>
       </c>
       <c r="M1162" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="N1162" t="n">
-        <v>5000</v>
+        <v>1230.76</v>
       </c>
       <c r="O1162" t="n">
-        <v>30000</v>
+        <v>39384.32</v>
       </c>
       <c r="P1162" t="n">
-        <v>6000</v>
+        <v>1600</v>
       </c>
       <c r="Q1162" t="n">
-        <v>36000</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>QH-8308</t>
+          <t>PT14026</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
+          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
         </is>
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I1163" t="inlineStr">
@@ -51682,7 +51687,7 @@
         </is>
       </c>
       <c r="J1163" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K1163" t="n">
         <v>0</v>
@@ -51691,44 +51696,39 @@
         <v>0</v>
       </c>
       <c r="M1163" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N1163" t="n">
-        <v>2200</v>
+        <v>2690.69</v>
       </c>
       <c r="O1163" t="n">
-        <v>26400</v>
+        <v>2690.69</v>
       </c>
       <c r="P1163" t="n">
-        <v>2700</v>
+        <v>5900</v>
       </c>
       <c r="Q1163" t="n">
-        <v>32400</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>QH-8311</t>
+          <t>Q1241</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>SET BORRADORES ANIMALES QH-8311</t>
-        </is>
-      </c>
-      <c r="E1164" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>RESALTADOR BOTELLA</t>
         </is>
       </c>
       <c r="I1164" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1164" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K1164" t="n">
         <v>0</v>
@@ -51737,30 +51737,30 @@
         <v>0</v>
       </c>
       <c r="M1164" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N1164" t="n">
-        <v>2200</v>
+        <v>5000</v>
       </c>
       <c r="O1164" t="n">
-        <v>26400</v>
+        <v>30000</v>
       </c>
       <c r="P1164" t="n">
-        <v>2700</v>
+        <v>6000</v>
       </c>
       <c r="Q1164" t="n">
-        <v>32400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>QH-8314</t>
+          <t>QH-8308</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>SET BORRADORES DEPORTES QH-8314</t>
+          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
@@ -51774,7 +51774,7 @@
         </is>
       </c>
       <c r="J1165" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K1165" t="n">
         <v>0</v>
@@ -51783,30 +51783,30 @@
         <v>0</v>
       </c>
       <c r="M1165" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="N1165" t="n">
         <v>2200</v>
       </c>
       <c r="O1165" t="n">
-        <v>41800</v>
+        <v>26400</v>
       </c>
       <c r="P1165" t="n">
         <v>2700</v>
       </c>
       <c r="Q1165" t="n">
-        <v>51300</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>QH-8317</t>
+          <t>QH-8311</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>SET BORRADORES POSTRES QH-8317</t>
+          <t>SET BORRADORES ANIMALES QH-8311</t>
         </is>
       </c>
       <c r="E1166" t="inlineStr">
@@ -51847,12 +51847,12 @@
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>QH-8385</t>
+          <t>QH-8314</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>SET BORRADORES ESPACIAL QH-8385</t>
+          <t>SET BORRADORES DEPORTES QH-8314</t>
         </is>
       </c>
       <c r="E1167" t="inlineStr">
@@ -51866,7 +51866,7 @@
         </is>
       </c>
       <c r="J1167" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K1167" t="n">
         <v>0</v>
@@ -51875,30 +51875,30 @@
         <v>0</v>
       </c>
       <c r="M1167" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N1167" t="n">
         <v>2200</v>
       </c>
       <c r="O1167" t="n">
-        <v>6600</v>
+        <v>41800</v>
       </c>
       <c r="P1167" t="n">
         <v>2700</v>
       </c>
       <c r="Q1167" t="n">
-        <v>8100</v>
+        <v>51300</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>QQ-1502</t>
+          <t>QH-8317</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
+          <t>SET BORRADORES POSTRES QH-8317</t>
         </is>
       </c>
       <c r="E1168" t="inlineStr">
@@ -51912,7 +51912,7 @@
         </is>
       </c>
       <c r="J1168" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="K1168" t="n">
         <v>0</v>
@@ -51921,30 +51921,30 @@
         <v>0</v>
       </c>
       <c r="M1168" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="N1168" t="n">
         <v>2200</v>
       </c>
       <c r="O1168" t="n">
-        <v>158400</v>
+        <v>26400</v>
       </c>
       <c r="P1168" t="n">
         <v>2700</v>
       </c>
       <c r="Q1168" t="n">
-        <v>194400</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>QQ-1503</t>
+          <t>QH-8385</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
+          <t>SET BORRADORES ESPACIAL QH-8385</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
@@ -51958,7 +51958,7 @@
         </is>
       </c>
       <c r="J1169" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="K1169" t="n">
         <v>0</v>
@@ -51967,30 +51967,30 @@
         <v>0</v>
       </c>
       <c r="M1169" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="N1169" t="n">
         <v>2200</v>
       </c>
       <c r="O1169" t="n">
-        <v>151800</v>
+        <v>6600</v>
       </c>
       <c r="P1169" t="n">
         <v>2700</v>
       </c>
       <c r="Q1169" t="n">
-        <v>186300</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>QQ-1525</t>
+          <t>QQ-1502</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
+          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
@@ -52004,7 +52004,7 @@
         </is>
       </c>
       <c r="J1170" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K1170" t="n">
         <v>0</v>
@@ -52013,30 +52013,30 @@
         <v>0</v>
       </c>
       <c r="M1170" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N1170" t="n">
         <v>2200</v>
       </c>
       <c r="O1170" t="n">
-        <v>154000</v>
+        <v>158400</v>
       </c>
       <c r="P1170" t="n">
         <v>2700</v>
       </c>
       <c r="Q1170" t="n">
-        <v>189000</v>
+        <v>194400</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>QT511252-E</t>
+          <t>QQ-1503</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
+          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
         </is>
       </c>
       <c r="E1171" t="inlineStr">
@@ -52050,7 +52050,7 @@
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
@@ -52059,30 +52059,30 @@
         <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="N1171" t="n">
-        <v>5026.666</v>
+        <v>2200</v>
       </c>
       <c r="O1171" t="n">
-        <v>80426.656</v>
+        <v>151800</v>
       </c>
       <c r="P1171" t="n">
-        <v>6300</v>
+        <v>2700</v>
       </c>
       <c r="Q1171" t="n">
-        <v>100800</v>
+        <v>186300</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>QT511253-E</t>
+          <t>QQ-1525</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
+          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
         </is>
       </c>
       <c r="E1172" t="inlineStr">
@@ -52096,7 +52096,7 @@
         </is>
       </c>
       <c r="J1172" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="K1172" t="n">
         <v>0</v>
@@ -52105,30 +52105,30 @@
         <v>0</v>
       </c>
       <c r="M1172" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="N1172" t="n">
-        <v>5200</v>
+        <v>2200</v>
       </c>
       <c r="O1172" t="n">
-        <v>88400</v>
+        <v>154000</v>
       </c>
       <c r="P1172" t="n">
-        <v>6300</v>
+        <v>2700</v>
       </c>
       <c r="Q1172" t="n">
-        <v>107100</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>QT512452-E</t>
+          <t>QT511252-E</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
         </is>
       </c>
       <c r="E1173" t="inlineStr">
@@ -52142,7 +52142,7 @@
         </is>
       </c>
       <c r="J1173" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K1173" t="n">
         <v>0</v>
@@ -52151,30 +52151,30 @@
         <v>0</v>
       </c>
       <c r="M1173" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N1173" t="n">
-        <v>8800</v>
+        <v>5026.666</v>
       </c>
       <c r="O1173" t="n">
-        <v>149600</v>
+        <v>80426.656</v>
       </c>
       <c r="P1173" t="n">
-        <v>10600</v>
+        <v>6300</v>
       </c>
       <c r="Q1173" t="n">
-        <v>180200</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>QT512453-E</t>
+          <t>QT511253-E</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
+          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
         </is>
       </c>
       <c r="E1174" t="inlineStr">
@@ -52200,36 +52200,41 @@
         <v>17</v>
       </c>
       <c r="N1174" t="n">
-        <v>8800</v>
+        <v>5200</v>
       </c>
       <c r="O1174" t="n">
-        <v>149600</v>
+        <v>88400</v>
       </c>
       <c r="P1174" t="n">
-        <v>10600</v>
+        <v>6300</v>
       </c>
       <c r="Q1174" t="n">
-        <v>180200</v>
+        <v>107100</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>S145</t>
+          <t>QT512452-E</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR SIN CAJA MEDIANAS</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1175" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1175" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K1175" t="n">
         <v>0</v>
@@ -52238,30 +52243,30 @@
         <v>0</v>
       </c>
       <c r="M1175" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N1175" t="n">
-        <v>11538.4</v>
+        <v>8800</v>
       </c>
       <c r="O1175" t="n">
-        <v>11538.4</v>
+        <v>149600</v>
       </c>
       <c r="P1175" t="n">
-        <v>15000</v>
+        <v>10600</v>
       </c>
       <c r="Q1175" t="n">
-        <v>15000</v>
+        <v>180200</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>QT512453-E</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
         </is>
       </c>
       <c r="E1176" t="inlineStr">
@@ -52275,7 +52280,7 @@
         </is>
       </c>
       <c r="J1176" t="n">
-        <v>318</v>
+        <v>17</v>
       </c>
       <c r="K1176" t="n">
         <v>0</v>
@@ -52284,44 +52289,39 @@
         <v>0</v>
       </c>
       <c r="M1176" t="n">
-        <v>318</v>
+        <v>17</v>
       </c>
       <c r="N1176" t="n">
-        <v>4550</v>
+        <v>8800</v>
       </c>
       <c r="O1176" t="n">
-        <v>1446900</v>
+        <v>149600</v>
       </c>
       <c r="P1176" t="n">
-        <v>5500</v>
+        <v>10600</v>
       </c>
       <c r="Q1176" t="n">
-        <v>1749000</v>
+        <v>180200</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>SLT2640</t>
+          <t>S145</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
-        </is>
-      </c>
-      <c r="E1177" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>FICHAS DE ARMAR SIN CAJA MEDIANAS</t>
         </is>
       </c>
       <c r="I1177" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1177" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K1177" t="n">
         <v>0</v>
@@ -52330,80 +52330,90 @@
         <v>0</v>
       </c>
       <c r="M1177" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N1177" t="n">
-        <v>1059.1847727273</v>
+        <v>11538.4</v>
       </c>
       <c r="O1177" t="n">
-        <v>8473.4781818184</v>
+        <v>11538.4</v>
       </c>
       <c r="P1177" t="n">
-        <v>9500</v>
+        <v>15000</v>
       </c>
       <c r="Q1177" t="n">
-        <v>76000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>SY-661-A08</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>RESALTADOR SUPER HEROES</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1178" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1178" t="n">
-        <v>7</v>
+        <v>318</v>
       </c>
       <c r="K1178" t="n">
         <v>0</v>
       </c>
       <c r="L1178" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1178" t="n">
-        <v>7</v>
+        <v>314</v>
       </c>
       <c r="N1178" t="n">
-        <v>7500</v>
+        <v>4550</v>
       </c>
       <c r="O1178" t="n">
-        <v>52500</v>
+        <v>1428700</v>
       </c>
       <c r="P1178" t="n">
-        <v>9000</v>
+        <v>5500</v>
       </c>
       <c r="Q1178" t="n">
-        <v>63000</v>
+        <v>1727000</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>SY-661-A09</t>
+          <t>SLT2640</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>RESALTADOR SUPER MARIO</t>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1179" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1179" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K1179" t="n">
         <v>0</v>
@@ -52412,44 +52422,39 @@
         <v>0</v>
       </c>
       <c r="M1179" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N1179" t="n">
-        <v>7500</v>
+        <v>1059.1847727273</v>
       </c>
       <c r="O1179" t="n">
-        <v>105000</v>
+        <v>8473.4781818184</v>
       </c>
       <c r="P1179" t="n">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="Q1179" t="n">
-        <v>126000</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>T061-LJ</t>
+          <t>SY-661-A08</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
-        </is>
-      </c>
-      <c r="E1180" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
+          <t>RESALTADOR SUPER HEROES</t>
         </is>
       </c>
       <c r="I1180" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1180" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K1180" t="n">
         <v>0</v>
@@ -52458,44 +52463,39 @@
         <v>0</v>
       </c>
       <c r="M1180" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N1180" t="n">
-        <v>12392.16</v>
+        <v>7500</v>
       </c>
       <c r="O1180" t="n">
-        <v>24784.32</v>
+        <v>52500</v>
       </c>
       <c r="P1180" t="n">
-        <v>15900</v>
+        <v>9000</v>
       </c>
       <c r="Q1180" t="n">
-        <v>31800</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>SY-661-A09</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
-        </is>
-      </c>
-      <c r="E1181" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
+          <t>RESALTADOR SUPER MARIO</t>
         </is>
       </c>
       <c r="I1181" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1181" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K1181" t="n">
         <v>0</v>
@@ -52504,30 +52504,30 @@
         <v>0</v>
       </c>
       <c r="M1181" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="N1181" t="n">
-        <v>5186.45</v>
+        <v>7500</v>
       </c>
       <c r="O1181" t="n">
-        <v>10372.9</v>
+        <v>105000</v>
       </c>
       <c r="P1181" t="n">
-        <v>7200</v>
+        <v>9000</v>
       </c>
       <c r="Q1181" t="n">
-        <v>14400</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>T219</t>
+          <t>T061-LJ</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
+          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
@@ -52541,7 +52541,7 @@
         </is>
       </c>
       <c r="J1182" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K1182" t="n">
         <v>0</v>
@@ -52550,39 +52550,44 @@
         <v>0</v>
       </c>
       <c r="M1182" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N1182" t="n">
-        <v>8746.92</v>
+        <v>12392.16</v>
       </c>
       <c r="O1182" t="n">
-        <v>96216.12</v>
+        <v>24784.32</v>
       </c>
       <c r="P1182" t="n">
-        <v>11000</v>
+        <v>15900</v>
       </c>
       <c r="Q1182" t="n">
-        <v>121000</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>WT-E170</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>WT-E170 RODILLO PARA ABDOMINALES</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1183" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1183" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K1183" t="n">
         <v>0</v>
@@ -52591,35 +52596,35 @@
         <v>0</v>
       </c>
       <c r="M1183" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N1183" t="n">
-        <v>73405.77</v>
+        <v>5186.45</v>
       </c>
       <c r="O1183" t="n">
-        <v>440434.62</v>
+        <v>10372.9</v>
       </c>
       <c r="P1183" t="n">
-        <v>77900</v>
+        <v>7200</v>
       </c>
       <c r="Q1183" t="n">
-        <v>467400</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>XP-2984</t>
+          <t>T219</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>BORRADOR RETRACTIL XP-2984</t>
+          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
         </is>
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1184" t="inlineStr">
@@ -52628,7 +52633,7 @@
         </is>
       </c>
       <c r="J1184" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="K1184" t="n">
         <v>0</v>
@@ -52637,44 +52642,39 @@
         <v>0</v>
       </c>
       <c r="M1184" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="N1184" t="n">
-        <v>2403.9774324324</v>
+        <v>8746.92</v>
       </c>
       <c r="O1184" t="n">
-        <v>105775.0070270256</v>
+        <v>96216.12</v>
       </c>
       <c r="P1184" t="n">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="Q1184" t="n">
-        <v>132000</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>XP-2986</t>
+          <t>WT-E170</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
-        </is>
-      </c>
-      <c r="E1185" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>WT-E170 RODILLO PARA ABDOMINALES</t>
         </is>
       </c>
       <c r="I1185" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1185" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="K1185" t="n">
         <v>0</v>
@@ -52683,59 +52683,151 @@
         <v>0</v>
       </c>
       <c r="M1185" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="N1185" t="n">
-        <v>2402.6744966443</v>
+        <v>73405.77</v>
       </c>
       <c r="O1185" t="n">
-        <v>103315.0033557049</v>
+        <v>440434.62</v>
       </c>
       <c r="P1185" t="n">
-        <v>3000</v>
+        <v>77900</v>
       </c>
       <c r="Q1185" t="n">
-        <v>129000</v>
+        <v>467400</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
+          <t>XP-2984</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>BORRADOR RETRACTIL XP-2984</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J1186" t="n">
+        <v>44</v>
+      </c>
+      <c r="K1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1186" t="n">
+        <v>44</v>
+      </c>
+      <c r="N1186" t="n">
+        <v>2403.9774324324</v>
+      </c>
+      <c r="O1186" t="n">
+        <v>105775.0070270256</v>
+      </c>
+      <c r="P1186" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q1186" t="n">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>XP-2986</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J1187" t="n">
+        <v>43</v>
+      </c>
+      <c r="K1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1187" t="n">
+        <v>43</v>
+      </c>
+      <c r="N1187" t="n">
+        <v>2402.6744966443</v>
+      </c>
+      <c r="O1187" t="n">
+        <v>103315.0033557049</v>
+      </c>
+      <c r="P1187" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q1187" t="n">
+        <v>129000</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
           <t>YOYO2001</t>
         </is>
       </c>
-      <c r="C1186" t="inlineStr">
+      <c r="C1188" t="inlineStr">
         <is>
           <t>ZET LAPIZ</t>
         </is>
       </c>
-      <c r="I1186" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J1186" t="n">
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J1188" t="n">
         <v>41</v>
       </c>
-      <c r="K1186" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1186" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1186" t="n">
+      <c r="K1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1188" t="n">
         <v>41</v>
       </c>
-      <c r="N1186" t="n">
+      <c r="N1188" t="n">
         <v>6000</v>
       </c>
-      <c r="O1186" t="n">
+      <c r="O1188" t="n">
         <v>246000</v>
       </c>
-      <c r="P1186" t="n">
+      <c r="P1188" t="n">
         <v>7200</v>
       </c>
-      <c r="Q1186" t="n">
+      <c r="Q1188" t="n">
         <v>295200</v>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="K26" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>56</v>
@@ -4936,13 +4936,13 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
         <v>14</v>
@@ -7574,13 +7574,13 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
         <v>3</v>
@@ -9090,13 +9090,13 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
         <v>9</v>
@@ -10170,13 +10170,13 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
         <v>50</v>
@@ -10506,13 +10506,13 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
         <v>612</v>
@@ -10593,13 +10593,13 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
         <v>38</v>
@@ -11175,13 +11175,13 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
         <v>157</v>
@@ -11821,13 +11821,13 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M270" t="n">
         <v>264</v>
@@ -11911,13 +11911,13 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
         <v>579</v>
@@ -12359,13 +12359,13 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
         <v>145</v>
@@ -12753,13 +12753,13 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
         <v>18</v>
@@ -12889,13 +12889,13 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
         <v>146</v>
@@ -13201,13 +13201,13 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
         <v>674</v>
@@ -13703,13 +13703,13 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
         <v>265</v>
@@ -13931,13 +13931,13 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>912</v>
+        <v>895</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M317" t="n">
         <v>895</v>
@@ -14509,13 +14509,13 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="K330" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L330" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M330" t="n">
         <v>39</v>
@@ -14722,13 +14722,13 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M335" t="n">
         <v>63</v>
@@ -14850,13 +14850,13 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
         <v>199</v>
@@ -14891,13 +14891,13 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
         <v>240</v>
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>590</v>
+        <v>426</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M344" t="n">
         <v>426</v>
@@ -15339,13 +15339,13 @@
         </is>
       </c>
       <c r="J349" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K349" t="n">
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M349" t="n">
         <v>185</v>
@@ -15645,10 +15645,10 @@
         </is>
       </c>
       <c r="J356" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="K356" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="K357" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M357" t="n">
         <v>209</v>
@@ -15735,13 +15735,13 @@
         </is>
       </c>
       <c r="J358" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="K358" t="n">
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M358" t="n">
         <v>91</v>
@@ -15909,13 +15909,13 @@
         </is>
       </c>
       <c r="J362" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M362" t="n">
         <v>80</v>
@@ -16353,13 +16353,13 @@
         </is>
       </c>
       <c r="J372" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M372" t="n">
         <v>318</v>
@@ -16787,10 +16787,10 @@
         </is>
       </c>
       <c r="J382" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="K382" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -16831,13 +16831,13 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M383" t="n">
         <v>515</v>
@@ -17365,13 +17365,13 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K395" t="n">
         <v>0</v>
       </c>
       <c r="L395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M395" t="n">
         <v>16</v>
@@ -17416,13 +17416,13 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="K396" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M396" t="n">
         <v>145</v>
@@ -17756,13 +17756,13 @@
         </is>
       </c>
       <c r="J404" t="n">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="K404" t="n">
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M404" t="n">
         <v>893</v>
@@ -17851,10 +17851,10 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="K406" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L406" t="n">
         <v>0</v>
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M407" t="n">
         <v>847</v>
@@ -18030,13 +18030,13 @@
         </is>
       </c>
       <c r="J410" t="n">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="K410" t="n">
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M410" t="n">
         <v>439</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>2135</v>
+        <v>2124</v>
       </c>
       <c r="K411" t="n">
         <v>0</v>
       </c>
       <c r="L411" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M411" t="n">
         <v>2124</v>
@@ -18168,13 +18168,13 @@
         </is>
       </c>
       <c r="J413" t="n">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="K413" t="n">
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M413" t="n">
         <v>1062</v>
@@ -19038,13 +19038,13 @@
         </is>
       </c>
       <c r="J433" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K433" t="n">
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M433" t="n">
         <v>134</v>
@@ -19530,13 +19530,13 @@
         </is>
       </c>
       <c r="J444" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K444" t="n">
         <v>0</v>
       </c>
       <c r="L444" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M444" t="n">
         <v>114</v>
@@ -19576,13 +19576,13 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
       </c>
       <c r="L445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M445" t="n">
         <v>40</v>
@@ -19922,13 +19922,13 @@
         </is>
       </c>
       <c r="J453" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K453" t="n">
         <v>0</v>
       </c>
       <c r="L453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M453" t="n">
         <v>125</v>
@@ -20954,13 +20954,13 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
       </c>
       <c r="L477" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M477" t="n">
         <v>2</v>
@@ -21782,13 +21782,13 @@
         </is>
       </c>
       <c r="J497" t="n">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
       </c>
       <c r="L497" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M497" t="n">
         <v>343</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
       </c>
       <c r="L506" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M506" t="n">
         <v>461</v>
@@ -22774,13 +22774,13 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
       </c>
       <c r="L521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M521" t="n">
         <v>1373</v>
@@ -23409,10 +23409,10 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="K536" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L536" t="n">
         <v>0</v>
@@ -24480,10 +24480,10 @@
         </is>
       </c>
       <c r="J561" t="n">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="K561" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L561" t="n">
         <v>0</v>
@@ -25427,10 +25427,10 @@
         </is>
       </c>
       <c r="J583" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="K583" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L583" t="n">
         <v>0</v>
@@ -25780,13 +25780,13 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M591" t="n">
         <v>25</v>
@@ -26087,10 +26087,10 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="K598" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L598" t="n">
         <v>0</v>
@@ -27586,13 +27586,13 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
       </c>
       <c r="L633" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M633" t="n">
         <v>34</v>
@@ -28683,13 +28683,13 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M657" t="n">
         <v>9</v>
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="J659" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K659" t="n">
         <v>0</v>
       </c>
       <c r="L659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M659" t="n">
         <v>405</v>
@@ -28821,13 +28821,13 @@
         </is>
       </c>
       <c r="J660" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K660" t="n">
         <v>0</v>
       </c>
       <c r="L660" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M660" t="n">
         <v>69</v>
@@ -29517,13 +29517,13 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M675" t="n">
         <v>494</v>
@@ -29563,10 +29563,10 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="K676" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L676" t="n">
         <v>0</v>
@@ -33017,13 +33017,13 @@
         </is>
       </c>
       <c r="J751" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K751" t="n">
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M751" t="n">
         <v>27</v>
@@ -33431,13 +33431,13 @@
         </is>
       </c>
       <c r="J760" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K760" t="n">
         <v>0</v>
       </c>
       <c r="L760" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M760" t="n">
         <v>100</v>
@@ -34668,13 +34668,13 @@
         </is>
       </c>
       <c r="J787" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K787" t="n">
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M787" t="n">
         <v>37</v>
@@ -34809,13 +34809,13 @@
         </is>
       </c>
       <c r="J790" t="n">
-        <v>751</v>
+        <v>716</v>
       </c>
       <c r="K790" t="n">
         <v>0</v>
       </c>
       <c r="L790" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M790" t="n">
         <v>716</v>
@@ -35310,10 +35310,10 @@
         </is>
       </c>
       <c r="J801" t="n">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="K801" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="L801" t="n">
         <v>0</v>
@@ -35402,10 +35402,10 @@
         </is>
       </c>
       <c r="J803" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K803" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L803" t="n">
         <v>0</v>
@@ -35448,13 +35448,13 @@
         </is>
       </c>
       <c r="J804" t="n">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="K804" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="L804" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M804" t="n">
         <v>141</v>
@@ -35497,13 +35497,13 @@
         </is>
       </c>
       <c r="J805" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K805" t="n">
         <v>0</v>
       </c>
       <c r="L805" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M805" t="n">
         <v>85</v>
@@ -35819,13 +35819,13 @@
         </is>
       </c>
       <c r="J812" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K812" t="n">
         <v>0</v>
       </c>
       <c r="L812" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M812" t="n">
         <v>34</v>
@@ -36049,13 +36049,13 @@
         </is>
       </c>
       <c r="J817" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K817" t="n">
         <v>0</v>
       </c>
       <c r="L817" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M817" t="n">
         <v>19</v>
@@ -36834,13 +36834,13 @@
         </is>
       </c>
       <c r="J834" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K834" t="n">
         <v>0</v>
       </c>
       <c r="L834" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M834" t="n">
         <v>119</v>
@@ -37062,13 +37062,13 @@
         </is>
       </c>
       <c r="J839" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K839" t="n">
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M839" t="n">
         <v>418</v>
@@ -37154,13 +37154,13 @@
         </is>
       </c>
       <c r="J841" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K841" t="n">
         <v>0</v>
       </c>
       <c r="L841" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M841" t="n">
         <v>71</v>
@@ -37200,13 +37200,13 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M842" t="n">
         <v>440</v>
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="J843" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K843" t="n">
         <v>0</v>
       </c>
       <c r="L843" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M843" t="n">
         <v>40</v>
@@ -37292,13 +37292,13 @@
         </is>
       </c>
       <c r="J844" t="n">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K844" t="n">
         <v>0</v>
       </c>
       <c r="L844" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M844" t="n">
         <v>907</v>
@@ -37338,13 +37338,13 @@
         </is>
       </c>
       <c r="J845" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K845" t="n">
         <v>0</v>
       </c>
       <c r="L845" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M845" t="n">
         <v>247</v>
@@ -37571,13 +37571,13 @@
         </is>
       </c>
       <c r="J850" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K850" t="n">
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M850" t="n">
         <v>277</v>
@@ -37617,13 +37617,13 @@
         </is>
       </c>
       <c r="J851" t="n">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="K851" t="n">
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M851" t="n">
         <v>651</v>
@@ -37663,13 +37663,13 @@
         </is>
       </c>
       <c r="J852" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K852" t="n">
         <v>0</v>
       </c>
       <c r="L852" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M852" t="n">
         <v>172</v>
@@ -37755,13 +37755,13 @@
         </is>
       </c>
       <c r="J854" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K854" t="n">
         <v>0</v>
       </c>
       <c r="L854" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M854" t="n">
         <v>116</v>
@@ -37845,13 +37845,13 @@
         </is>
       </c>
       <c r="J856" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K856" t="n">
         <v>0</v>
       </c>
       <c r="L856" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M856" t="n">
         <v>61</v>
@@ -37937,13 +37937,13 @@
         </is>
       </c>
       <c r="J858" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K858" t="n">
         <v>0</v>
       </c>
       <c r="L858" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M858" t="n">
         <v>95</v>
@@ -38121,13 +38121,13 @@
         </is>
       </c>
       <c r="J862" t="n">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="K862" t="n">
         <v>0</v>
       </c>
       <c r="L862" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M862" t="n">
         <v>583</v>
@@ -39638,13 +39638,13 @@
         </is>
       </c>
       <c r="J895" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="K895" t="n">
         <v>0</v>
       </c>
       <c r="L895" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M895" t="n">
         <v>108</v>
@@ -40188,13 +40188,13 @@
         </is>
       </c>
       <c r="J907" t="n">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K907" t="n">
         <v>0</v>
       </c>
       <c r="L907" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M907" t="n">
         <v>453</v>
@@ -40844,13 +40844,13 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>308</v>
+        <v>68</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="M922" t="n">
         <v>68</v>
@@ -41154,13 +41154,13 @@
         </is>
       </c>
       <c r="J929" t="n">
-        <v>3467</v>
+        <v>3385</v>
       </c>
       <c r="K929" t="n">
         <v>0</v>
       </c>
       <c r="L929" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M929" t="n">
         <v>3385</v>
@@ -41380,13 +41380,13 @@
         </is>
       </c>
       <c r="J934" t="n">
-        <v>674</v>
+        <v>609</v>
       </c>
       <c r="K934" t="n">
         <v>0</v>
       </c>
       <c r="L934" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M934" t="n">
         <v>609</v>
@@ -41602,13 +41602,13 @@
         </is>
       </c>
       <c r="J939" t="n">
-        <v>1098</v>
+        <v>1058</v>
       </c>
       <c r="K939" t="n">
         <v>0</v>
       </c>
       <c r="L939" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M939" t="n">
         <v>1058</v>
@@ -42353,13 +42353,13 @@
         </is>
       </c>
       <c r="J956" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K956" t="n">
         <v>0</v>
       </c>
       <c r="L956" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M956" t="n">
         <v>259</v>
@@ -42616,10 +42616,10 @@
         <v>74</v>
       </c>
       <c r="K962" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="L962" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="M962" t="n">
         <v>74</v>
@@ -44259,10 +44259,10 @@
         </is>
       </c>
       <c r="J997" t="n">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="K997" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="L997" t="n">
         <v>0</v>
@@ -44271,10 +44271,10 @@
         <v>235</v>
       </c>
       <c r="N997" t="n">
-        <v>801.28885106383</v>
+        <v>1759.84</v>
       </c>
       <c r="O997" t="n">
-        <v>188302.88</v>
+        <v>413562.4</v>
       </c>
       <c r="P997" t="n">
         <v>3300</v>
@@ -45009,13 +45009,13 @@
         </is>
       </c>
       <c r="J1013" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K1013" t="n">
         <v>0</v>
       </c>
       <c r="L1013" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1013" t="n">
         <v>21</v>
@@ -46039,13 +46039,13 @@
         </is>
       </c>
       <c r="J1035" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K1035" t="n">
         <v>0</v>
       </c>
       <c r="L1035" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1035" t="n">
         <v>14</v>
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="J1046" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1046" t="n">
         <v>0</v>
       </c>
       <c r="L1046" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1046" t="n">
         <v>40</v>
@@ -47665,13 +47665,13 @@
         </is>
       </c>
       <c r="J1073" t="n">
-        <v>267</v>
+        <v>454</v>
       </c>
       <c r="K1073" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L1073" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M1073" t="n">
         <v>454</v>
@@ -48143,13 +48143,13 @@
         </is>
       </c>
       <c r="J1084" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1084" t="n">
         <v>0</v>
       </c>
       <c r="L1084" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1084" t="n">
         <v>40</v>
@@ -48729,13 +48729,13 @@
         </is>
       </c>
       <c r="J1098" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K1098" t="n">
         <v>0</v>
       </c>
       <c r="L1098" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M1098" t="n">
         <v>13</v>
@@ -48819,13 +48819,13 @@
         </is>
       </c>
       <c r="J1100" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K1100" t="n">
         <v>0</v>
       </c>
       <c r="L1100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1100" t="n">
         <v>139</v>
@@ -49765,22 +49765,22 @@
         </is>
       </c>
       <c r="J1121" t="n">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="K1121" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1121" t="n">
         <v>429</v>
       </c>
       <c r="N1121" t="n">
-        <v>7480</v>
+        <v>788.1365841161401</v>
       </c>
       <c r="O1121" t="n">
-        <v>3208920</v>
+        <v>338110.5945858241</v>
       </c>
       <c r="P1121" t="n">
         <v>9500</v>
@@ -49903,13 +49903,13 @@
         </is>
       </c>
       <c r="J1124" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="K1124" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M1124" t="n">
         <v>709</v>
@@ -52367,13 +52367,13 @@
         </is>
       </c>
       <c r="J1178" t="n">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="K1178" t="n">
         <v>0</v>
       </c>
       <c r="L1178" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1178" t="n">
         <v>314</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1354,10 +1354,10 @@
         <v>192</v>
       </c>
       <c r="N23" t="n">
-        <v>1811.3044829343</v>
+        <v>1811.3047800109</v>
       </c>
       <c r="O23" t="n">
-        <v>347770.4607233856</v>
+        <v>347770.5177620928</v>
       </c>
       <c r="P23" t="n">
         <v>2600</v>
@@ -1471,10 +1471,10 @@
         <v>155</v>
       </c>
       <c r="N26" t="n">
-        <v>3376.746498645</v>
+        <v>3376.7464976959</v>
       </c>
       <c r="O26" t="n">
-        <v>523395.707289975</v>
+        <v>523395.7071428645</v>
       </c>
       <c r="P26" t="n">
         <v>4500</v>
@@ -3288,10 +3288,10 @@
         <v>205</v>
       </c>
       <c r="N71" t="n">
-        <v>2413.0010615711</v>
+        <v>2413.0010626993</v>
       </c>
       <c r="O71" t="n">
-        <v>494665.2176220755</v>
+        <v>494665.2178533564</v>
       </c>
       <c r="P71" t="n">
         <v>4700</v>
@@ -3327,10 +3327,10 @@
         <v>74</v>
       </c>
       <c r="N72" t="n">
-        <v>2474.7042043551</v>
+        <v>2474.7041652614</v>
       </c>
       <c r="O72" t="n">
-        <v>183128.1111222774</v>
+        <v>183128.1082293436</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3873,10 +3873,10 @@
         <v>24</v>
       </c>
       <c r="N86" t="n">
-        <v>14857.623185841</v>
+        <v>14857.6232</v>
       </c>
       <c r="O86" t="n">
-        <v>356582.956460184</v>
+        <v>356582.9568</v>
       </c>
       <c r="P86" t="n">
         <v>34900</v>
@@ -4181,10 +4181,10 @@
         <v>56</v>
       </c>
       <c r="N93" t="n">
-        <v>3910.6281963928</v>
+        <v>3910.6281927711</v>
       </c>
       <c r="O93" t="n">
-        <v>218995.1789979968</v>
+        <v>218995.1787951816</v>
       </c>
       <c r="P93" t="n">
         <v>9100</v>
@@ -4538,22 +4538,22 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N101" t="n">
-        <v>28751.742258065</v>
+        <v>28751.742333333</v>
       </c>
       <c r="O101" t="n">
-        <v>57503.48451613</v>
+        <v>28751.742333333</v>
       </c>
       <c r="P101" t="n">
         <v>34800</v>
       </c>
       <c r="Q101" t="n">
-        <v>69600</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="102">
@@ -4942,22 +4942,22 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N110" t="n">
-        <v>18835.024666667</v>
+        <v>18835.026428571</v>
       </c>
       <c r="O110" t="n">
-        <v>263690.345333338</v>
+        <v>244855.343571423</v>
       </c>
       <c r="P110" t="n">
         <v>40500</v>
       </c>
       <c r="Q110" t="n">
-        <v>567000</v>
+        <v>526500</v>
       </c>
     </row>
     <row r="111">
@@ -5293,10 +5293,10 @@
         <v>89</v>
       </c>
       <c r="N118" t="n">
-        <v>7407.7300524934</v>
+        <v>7407.7300526316</v>
       </c>
       <c r="O118" t="n">
-        <v>659287.9746719126</v>
+        <v>659287.9746842125</v>
       </c>
       <c r="P118" t="n">
         <v>10900</v>
@@ -6236,10 +6236,10 @@
         <v>12</v>
       </c>
       <c r="N140" t="n">
-        <v>200072.2</v>
+        <v>200072.20007812</v>
       </c>
       <c r="O140" t="n">
-        <v>2400866.4</v>
+        <v>2400866.40093744</v>
       </c>
       <c r="P140" t="n">
         <v>312000</v>
@@ -7213,10 +7213,10 @@
         <v>4</v>
       </c>
       <c r="N163" t="n">
-        <v>61666.873994709</v>
+        <v>61666.874005305</v>
       </c>
       <c r="O163" t="n">
-        <v>246667.495978836</v>
+        <v>246667.49602122</v>
       </c>
       <c r="P163" t="n">
         <v>98900</v>
@@ -9537,10 +9537,10 @@
         <v>2</v>
       </c>
       <c r="N216" t="n">
-        <v>732.63413793103</v>
+        <v>732.63415224913</v>
       </c>
       <c r="O216" t="n">
-        <v>1465.26827586206</v>
+        <v>1465.26830449826</v>
       </c>
       <c r="P216" t="n">
         <v>6200</v>
@@ -9920,22 +9920,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M225" t="n">
-        <v>1943</v>
+        <v>1786</v>
       </c>
       <c r="N225" t="n">
         <v>1726.32</v>
       </c>
       <c r="O225" t="n">
-        <v>3354239.76</v>
+        <v>3083207.52</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
       </c>
       <c r="Q225" t="n">
-        <v>2914500</v>
+        <v>2679000</v>
       </c>
     </row>
     <row r="226">
@@ -10013,10 +10013,10 @@
         <v>122</v>
       </c>
       <c r="N227" t="n">
-        <v>4937.3101611722</v>
+        <v>4937.3101612903</v>
       </c>
       <c r="O227" t="n">
-        <v>602351.8396630085</v>
+        <v>602351.8396774166</v>
       </c>
       <c r="P227" t="n">
         <v>7500</v>
@@ -10512,22 +10512,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M239" t="n">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="N239" t="n">
-        <v>1098.0555939754</v>
+        <v>1098.055952691</v>
       </c>
       <c r="O239" t="n">
-        <v>672010.0235129447</v>
+        <v>665421.9073307459</v>
       </c>
       <c r="P239" t="n">
         <v>1500</v>
       </c>
       <c r="Q239" t="n">
-        <v>918000</v>
+        <v>909000</v>
       </c>
     </row>
     <row r="240">
@@ -12279,10 +12279,10 @@
         <v>247</v>
       </c>
       <c r="N280" t="n">
-        <v>2582.2560112135</v>
+        <v>2582.2559895309</v>
       </c>
       <c r="O280" t="n">
-        <v>637817.2347697346</v>
+        <v>637817.2294141323</v>
       </c>
       <c r="P280" t="n">
         <v>4500</v>
@@ -12365,22 +12365,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M282" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="N282" t="n">
-        <v>5216.8959654608</v>
+        <v>5216.8959618537</v>
       </c>
       <c r="O282" t="n">
-        <v>756449.9149918159</v>
+        <v>725148.5386976643</v>
       </c>
       <c r="P282" t="n">
         <v>8500</v>
       </c>
       <c r="Q282" t="n">
-        <v>1232500</v>
+        <v>1181500</v>
       </c>
     </row>
     <row r="283">
@@ -12621,22 +12621,22 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M288" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N288" t="n">
         <v>6713.08</v>
       </c>
       <c r="O288" t="n">
-        <v>67130.8</v>
+        <v>53704.64</v>
       </c>
       <c r="P288" t="n">
         <v>9900</v>
       </c>
       <c r="Q288" t="n">
-        <v>99000</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="289">
@@ -12667,22 +12667,22 @@
         <v>0</v>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M289" t="n">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="N289" t="n">
-        <v>3158.860814779</v>
+        <v>3158.8608154486</v>
       </c>
       <c r="O289" t="n">
-        <v>2978805.748336597</v>
+        <v>2928263.975920852</v>
       </c>
       <c r="P289" t="n">
         <v>5600</v>
       </c>
       <c r="Q289" t="n">
-        <v>5280800</v>
+        <v>5191200</v>
       </c>
     </row>
     <row r="290">
@@ -12901,10 +12901,10 @@
         <v>146</v>
       </c>
       <c r="N294" t="n">
-        <v>3230.0677414075</v>
+        <v>3230.0677302632</v>
       </c>
       <c r="O294" t="n">
-        <v>471589.890245495</v>
+        <v>471589.8886184272</v>
       </c>
       <c r="P294" t="n">
         <v>6200</v>
@@ -13126,10 +13126,10 @@
         <v>109</v>
       </c>
       <c r="N299" t="n">
-        <v>2694.8234565119</v>
+        <v>2694.8234059946</v>
       </c>
       <c r="O299" t="n">
-        <v>293735.7567597971</v>
+        <v>293735.7512534114</v>
       </c>
       <c r="P299" t="n">
         <v>4900</v>
@@ -13207,22 +13207,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M301" t="n">
-        <v>674</v>
+        <v>601</v>
       </c>
       <c r="N301" t="n">
         <v>1026.13</v>
       </c>
       <c r="O301" t="n">
-        <v>691611.6200000001</v>
+        <v>616704.1300000001</v>
       </c>
       <c r="P301" t="n">
         <v>1900</v>
       </c>
       <c r="Q301" t="n">
-        <v>1280600</v>
+        <v>1141900</v>
       </c>
     </row>
     <row r="302">
@@ -13582,10 +13582,10 @@
         <v>299</v>
       </c>
       <c r="N309" t="n">
-        <v>3795.7100070621</v>
+        <v>3795.7100070671</v>
       </c>
       <c r="O309" t="n">
-        <v>1134917.292111568</v>
+        <v>1134917.292113063</v>
       </c>
       <c r="P309" t="n">
         <v>6200</v>
@@ -13842,22 +13842,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M315" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N315" t="n">
-        <v>4890.9300464306</v>
+        <v>4890.9300465929</v>
       </c>
       <c r="O315" t="n">
-        <v>259219.2924608218</v>
+        <v>244546.502329645</v>
       </c>
       <c r="P315" t="n">
         <v>8200</v>
       </c>
       <c r="Q315" t="n">
-        <v>434600</v>
+        <v>410000</v>
       </c>
     </row>
     <row r="316">
@@ -13937,22 +13937,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M317" t="n">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="N317" t="n">
         <v>1203.38</v>
       </c>
       <c r="O317" t="n">
-        <v>1077025.1</v>
+        <v>1062584.54</v>
       </c>
       <c r="P317" t="n">
         <v>1900</v>
       </c>
       <c r="Q317" t="n">
-        <v>1700500</v>
+        <v>1677700</v>
       </c>
     </row>
     <row r="318">
@@ -13983,22 +13983,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="N318" t="n">
         <v>3472</v>
       </c>
       <c r="O318" t="n">
-        <v>3100496</v>
+        <v>3097024</v>
       </c>
       <c r="P318" t="n">
         <v>4800</v>
       </c>
       <c r="Q318" t="n">
-        <v>4286400</v>
+        <v>4281600</v>
       </c>
     </row>
     <row r="319">
@@ -14029,22 +14029,22 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M319" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N319" t="n">
         <v>5888</v>
       </c>
       <c r="O319" t="n">
-        <v>288512</v>
+        <v>276736</v>
       </c>
       <c r="P319" t="n">
         <v>9500</v>
       </c>
       <c r="Q319" t="n">
-        <v>465500</v>
+        <v>446500</v>
       </c>
     </row>
     <row r="320">
@@ -14168,10 +14168,10 @@
         <v>1580</v>
       </c>
       <c r="N322" t="n">
-        <v>2267.0481598668</v>
+        <v>2267.0481583333</v>
       </c>
       <c r="O322" t="n">
-        <v>3581936.092589544</v>
+        <v>3581936.090166614</v>
       </c>
       <c r="P322" t="n">
         <v>3900</v>
@@ -14290,22 +14290,22 @@
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M325" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="N325" t="n">
         <v>7041</v>
       </c>
       <c r="O325" t="n">
-        <v>274599</v>
+        <v>218271</v>
       </c>
       <c r="P325" t="n">
         <v>11500</v>
       </c>
       <c r="Q325" t="n">
-        <v>448500</v>
+        <v>356500</v>
       </c>
     </row>
     <row r="326">
@@ -14428,22 +14428,22 @@
         <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M328" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N328" t="n">
         <v>8662</v>
       </c>
       <c r="O328" t="n">
-        <v>337818</v>
+        <v>329156</v>
       </c>
       <c r="P328" t="n">
         <v>14200</v>
       </c>
       <c r="Q328" t="n">
-        <v>553800</v>
+        <v>539600</v>
       </c>
     </row>
     <row r="329">
@@ -14512,25 +14512,25 @@
         <v>39</v>
       </c>
       <c r="K330" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M330" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="N330" t="n">
         <v>10716.34</v>
       </c>
       <c r="O330" t="n">
-        <v>417937.26</v>
+        <v>471518.96</v>
       </c>
       <c r="P330" t="n">
         <v>39000</v>
       </c>
       <c r="Q330" t="n">
-        <v>1521000</v>
+        <v>1716000</v>
       </c>
     </row>
     <row r="331">
@@ -14728,22 +14728,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N335" t="n">
-        <v>3594.2541391941</v>
+        <v>3594.254124847</v>
       </c>
       <c r="O335" t="n">
-        <v>226438.0107692283</v>
+        <v>222843.755740514</v>
       </c>
       <c r="P335" t="n">
         <v>6500</v>
       </c>
       <c r="Q335" t="n">
-        <v>409500</v>
+        <v>403000</v>
       </c>
     </row>
     <row r="336">
@@ -14903,10 +14903,10 @@
         <v>240</v>
       </c>
       <c r="N339" t="n">
-        <v>3240.8500301659</v>
+        <v>3240.8500302572</v>
       </c>
       <c r="O339" t="n">
-        <v>777804.007239816</v>
+        <v>777804.0072617281</v>
       </c>
       <c r="P339" t="n">
         <v>5200</v>
@@ -14943,22 +14943,22 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M340" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="N340" t="n">
         <v>4891</v>
       </c>
       <c r="O340" t="n">
-        <v>562465</v>
+        <v>542901</v>
       </c>
       <c r="P340" t="n">
         <v>8200</v>
       </c>
       <c r="Q340" t="n">
-        <v>943000</v>
+        <v>910200</v>
       </c>
     </row>
     <row r="341">
@@ -15035,22 +15035,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N342" t="n">
-        <v>14822.378862559</v>
+        <v>14822.378861885</v>
       </c>
       <c r="O342" t="n">
-        <v>637362.291090037</v>
+        <v>622539.91219917</v>
       </c>
       <c r="P342" t="n">
         <v>24900</v>
       </c>
       <c r="Q342" t="n">
-        <v>1070700</v>
+        <v>1045800</v>
       </c>
     </row>
     <row r="343">
@@ -15120,25 +15120,25 @@
         <v>426</v>
       </c>
       <c r="K344" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="M344" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="N344" t="n">
         <v>2090.85</v>
       </c>
       <c r="O344" t="n">
-        <v>890702.1</v>
+        <v>903247.2</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
       </c>
       <c r="Q344" t="n">
-        <v>1235400</v>
+        <v>1252800</v>
       </c>
     </row>
     <row r="345">
@@ -15345,22 +15345,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M349" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="N349" t="n">
         <v>1381.75</v>
       </c>
       <c r="O349" t="n">
-        <v>255623.75</v>
+        <v>239042.75</v>
       </c>
       <c r="P349" t="n">
         <v>2500</v>
       </c>
       <c r="Q349" t="n">
-        <v>462500</v>
+        <v>432500</v>
       </c>
     </row>
     <row r="350">
@@ -15520,22 +15520,22 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M353" t="n">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N353" t="n">
         <v>1441.01</v>
       </c>
       <c r="O353" t="n">
-        <v>830021.76</v>
+        <v>827139.74</v>
       </c>
       <c r="P353" t="n">
         <v>2100</v>
       </c>
       <c r="Q353" t="n">
-        <v>1209600</v>
+        <v>1205400</v>
       </c>
     </row>
     <row r="354">
@@ -15616,10 +15616,10 @@
         <v>427</v>
       </c>
       <c r="N355" t="n">
-        <v>3041.6600126502</v>
+        <v>3041.6600127551</v>
       </c>
       <c r="O355" t="n">
-        <v>1298788.825401635</v>
+        <v>1298788.825446428</v>
       </c>
       <c r="P355" t="n">
         <v>5500</v>
@@ -15741,22 +15741,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M358" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N358" t="n">
         <v>6441.03</v>
       </c>
       <c r="O358" t="n">
-        <v>586133.73</v>
+        <v>534605.49</v>
       </c>
       <c r="P358" t="n">
         <v>10500</v>
       </c>
       <c r="Q358" t="n">
-        <v>955500</v>
+        <v>871500</v>
       </c>
     </row>
     <row r="359">
@@ -15793,10 +15793,10 @@
         <v>19</v>
       </c>
       <c r="N359" t="n">
-        <v>1592.5674522293</v>
+        <v>1592.5674</v>
       </c>
       <c r="O359" t="n">
-        <v>30258.7815923567</v>
+        <v>30258.7806</v>
       </c>
       <c r="P359" t="n">
         <v>3900</v>
@@ -16310,22 +16310,22 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M371" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="N371" t="n">
         <v>6242.93</v>
       </c>
       <c r="O371" t="n">
-        <v>624293</v>
+        <v>549377.8400000001</v>
       </c>
       <c r="P371" t="n">
         <v>10400</v>
       </c>
       <c r="Q371" t="n">
-        <v>1040000</v>
+        <v>915200</v>
       </c>
     </row>
     <row r="372">
@@ -16793,22 +16793,22 @@
         <v>0</v>
       </c>
       <c r="L382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M382" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N382" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O382" t="n">
-        <v>677830.3199999999</v>
+        <v>659001.7</v>
       </c>
       <c r="P382" t="n">
         <v>16900</v>
       </c>
       <c r="Q382" t="n">
-        <v>1216800</v>
+        <v>1183000</v>
       </c>
     </row>
     <row r="383">
@@ -16837,22 +16837,22 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M383" t="n">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="N383" t="n">
         <v>1387.55</v>
       </c>
       <c r="O383" t="n">
-        <v>714588.25</v>
+        <v>706262.95</v>
       </c>
       <c r="P383" t="n">
         <v>2300</v>
       </c>
       <c r="Q383" t="n">
-        <v>1184500</v>
+        <v>1170700</v>
       </c>
     </row>
     <row r="384">
@@ -17422,22 +17422,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M396" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="N396" t="n">
         <v>11921.4</v>
       </c>
       <c r="O396" t="n">
-        <v>1728603</v>
+        <v>1645153.2</v>
       </c>
       <c r="P396" t="n">
         <v>19900</v>
       </c>
       <c r="Q396" t="n">
-        <v>2885500</v>
+        <v>2746200</v>
       </c>
     </row>
     <row r="397">
@@ -17762,22 +17762,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M404" t="n">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="N404" t="n">
         <v>3751</v>
       </c>
       <c r="O404" t="n">
-        <v>3349643</v>
+        <v>3323386</v>
       </c>
       <c r="P404" t="n">
         <v>6400</v>
       </c>
       <c r="Q404" t="n">
-        <v>5715200</v>
+        <v>5670400</v>
       </c>
     </row>
     <row r="405">
@@ -17808,25 +17808,25 @@
         <v>63</v>
       </c>
       <c r="K405" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L405" t="n">
         <v>0</v>
       </c>
       <c r="M405" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N405" t="n">
         <v>9903</v>
       </c>
       <c r="O405" t="n">
-        <v>623889</v>
+        <v>742725</v>
       </c>
       <c r="P405" t="n">
         <v>15900</v>
       </c>
       <c r="Q405" t="n">
-        <v>1001700</v>
+        <v>1192500</v>
       </c>
     </row>
     <row r="406">
@@ -17903,22 +17903,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M407" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="N407" t="n">
-        <v>1630.9231587595</v>
+        <v>1630.9231730968</v>
       </c>
       <c r="O407" t="n">
-        <v>1381391.915469297</v>
+        <v>1379761.004439893</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
       </c>
       <c r="Q407" t="n">
-        <v>2117500</v>
+        <v>2115000</v>
       </c>
     </row>
     <row r="408">
@@ -17990,22 +17990,22 @@
         <v>0</v>
       </c>
       <c r="L409" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M409" t="n">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="N409" t="n">
-        <v>1467.327254902</v>
+        <v>1467.3264227642</v>
       </c>
       <c r="O409" t="n">
-        <v>334550.614117656</v>
+        <v>321344.4865853598</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
       </c>
       <c r="Q409" t="n">
-        <v>570000</v>
+        <v>547500</v>
       </c>
     </row>
     <row r="410">
@@ -18036,22 +18036,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M410" t="n">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="N410" t="n">
-        <v>1690.6026503973</v>
+        <v>1690.6023498845</v>
       </c>
       <c r="O410" t="n">
-        <v>742174.5635244148</v>
+        <v>718505.9987009125</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
       </c>
       <c r="Q410" t="n">
-        <v>1273100</v>
+        <v>1232500</v>
       </c>
     </row>
     <row r="411">
@@ -18082,22 +18082,22 @@
         <v>0</v>
       </c>
       <c r="L411" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M411" t="n">
-        <v>2124</v>
+        <v>2101</v>
       </c>
       <c r="N411" t="n">
-        <v>1550.1931558806</v>
+        <v>1550.193183768</v>
       </c>
       <c r="O411" t="n">
-        <v>3292610.263090394</v>
+        <v>3256955.879096568</v>
       </c>
       <c r="P411" t="n">
         <v>2500</v>
       </c>
       <c r="Q411" t="n">
-        <v>5310000</v>
+        <v>5252500</v>
       </c>
     </row>
     <row r="412">
@@ -18134,10 +18134,10 @@
         <v>3</v>
       </c>
       <c r="N412" t="n">
-        <v>1579.391025</v>
+        <v>1579.3909343434</v>
       </c>
       <c r="O412" t="n">
-        <v>4738.173075</v>
+        <v>4738.1728030302</v>
       </c>
       <c r="P412" t="n">
         <v>2900</v>
@@ -18174,22 +18174,22 @@
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M413" t="n">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="N413" t="n">
-        <v>2403.5103724115</v>
+        <v>2403.5104597508</v>
       </c>
       <c r="O413" t="n">
-        <v>2552528.015501013</v>
+        <v>2538107.045496845</v>
       </c>
       <c r="P413" t="n">
         <v>3500</v>
       </c>
       <c r="Q413" t="n">
-        <v>3717000</v>
+        <v>3696000</v>
       </c>
     </row>
     <row r="414">
@@ -18220,22 +18220,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M414" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="N414" t="n">
-        <v>2521.5439240506</v>
+        <v>2521.5426705653</v>
       </c>
       <c r="O414" t="n">
-        <v>73124.77379746739</v>
+        <v>42866.2253996101</v>
       </c>
       <c r="P414" t="n">
         <v>3900</v>
       </c>
       <c r="Q414" t="n">
-        <v>113100</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="415">
@@ -19403,22 +19403,22 @@
         <v>0</v>
       </c>
       <c r="L441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N441" t="n">
         <v>1965</v>
       </c>
       <c r="O441" t="n">
-        <v>129690</v>
+        <v>127725</v>
       </c>
       <c r="P441" t="n">
         <v>3700</v>
       </c>
       <c r="Q441" t="n">
-        <v>244200</v>
+        <v>240500</v>
       </c>
     </row>
     <row r="442">
@@ -21332,22 +21332,22 @@
         <v>0</v>
       </c>
       <c r="L486" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M486" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N486" t="n">
         <v>2661.82</v>
       </c>
       <c r="O486" t="n">
-        <v>149061.92</v>
+        <v>138414.64</v>
       </c>
       <c r="P486" t="n">
         <v>3200</v>
       </c>
       <c r="Q486" t="n">
-        <v>179200</v>
+        <v>166400</v>
       </c>
     </row>
     <row r="487">
@@ -21455,22 +21455,22 @@
         <v>0</v>
       </c>
       <c r="L489" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M489" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N489" t="n">
         <v>2610</v>
       </c>
       <c r="O489" t="n">
-        <v>255780</v>
+        <v>250560</v>
       </c>
       <c r="P489" t="n">
         <v>3200</v>
       </c>
       <c r="Q489" t="n">
-        <v>313600</v>
+        <v>307200</v>
       </c>
     </row>
     <row r="490">
@@ -21496,22 +21496,22 @@
         <v>0</v>
       </c>
       <c r="L490" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M490" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="N490" t="n">
         <v>2081</v>
       </c>
       <c r="O490" t="n">
-        <v>195614</v>
+        <v>189371</v>
       </c>
       <c r="P490" t="n">
         <v>3200</v>
       </c>
       <c r="Q490" t="n">
-        <v>300800</v>
+        <v>291200</v>
       </c>
     </row>
     <row r="491">
@@ -22034,22 +22034,22 @@
         <v>0</v>
       </c>
       <c r="L503" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M503" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N503" t="n">
         <v>2517.22</v>
       </c>
       <c r="O503" t="n">
-        <v>571408.9399999999</v>
+        <v>566374.5</v>
       </c>
       <c r="P503" t="n">
         <v>4200</v>
       </c>
       <c r="Q503" t="n">
-        <v>953400</v>
+        <v>945000</v>
       </c>
     </row>
     <row r="504">
@@ -22163,10 +22163,10 @@
         <v>461</v>
       </c>
       <c r="N506" t="n">
-        <v>2029.8737073653</v>
+        <v>2029.8737091988</v>
       </c>
       <c r="O506" t="n">
-        <v>935771.7790954034</v>
+        <v>935771.7799406468</v>
       </c>
       <c r="P506" t="n">
         <v>3600</v>
@@ -22608,22 +22608,22 @@
         <v>0</v>
       </c>
       <c r="L517" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M517" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N517" t="n">
         <v>7103</v>
       </c>
       <c r="O517" t="n">
-        <v>902081</v>
+        <v>887875</v>
       </c>
       <c r="P517" t="n">
         <v>10700</v>
       </c>
       <c r="Q517" t="n">
-        <v>1358900</v>
+        <v>1337500</v>
       </c>
     </row>
     <row r="518">
@@ -22786,10 +22786,10 @@
         <v>1373</v>
       </c>
       <c r="N521" t="n">
-        <v>880.3293685687599</v>
+        <v>880.32937295274</v>
       </c>
       <c r="O521" t="n">
-        <v>1208692.223044907</v>
+        <v>1208692.229064112</v>
       </c>
       <c r="P521" t="n">
         <v>1200</v>
@@ -23467,10 +23467,10 @@
         <v>194</v>
       </c>
       <c r="N537" t="n">
-        <v>998.76125988546</v>
+        <v>998.76126091703</v>
       </c>
       <c r="O537" t="n">
-        <v>193759.6844177792</v>
+        <v>193759.6846179038</v>
       </c>
       <c r="P537" t="n">
         <v>1600</v>
@@ -23772,10 +23772,10 @@
         <v>280</v>
       </c>
       <c r="N544" t="n">
-        <v>4285.1952751817</v>
+        <v>4285.1952806653</v>
       </c>
       <c r="O544" t="n">
-        <v>1199854.677050876</v>
+        <v>1199854.678586284</v>
       </c>
       <c r="P544" t="n">
         <v>6900</v>
@@ -24670,22 +24670,22 @@
         <v>0</v>
       </c>
       <c r="L565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M565" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N565" t="n">
-        <v>12005.159831933</v>
+        <v>12005.159831224</v>
       </c>
       <c r="O565" t="n">
-        <v>780335.389075645</v>
+        <v>768330.229198336</v>
       </c>
       <c r="P565" t="n">
         <v>19500</v>
       </c>
       <c r="Q565" t="n">
-        <v>1267500</v>
+        <v>1248000</v>
       </c>
     </row>
     <row r="566">
@@ -25740,22 +25740,22 @@
         <v>0</v>
       </c>
       <c r="L590" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M590" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N590" t="n">
         <v>22730.48</v>
       </c>
       <c r="O590" t="n">
-        <v>545531.52</v>
+        <v>522801.04</v>
       </c>
       <c r="P590" t="n">
         <v>36900</v>
       </c>
       <c r="Q590" t="n">
-        <v>885600</v>
+        <v>848700</v>
       </c>
     </row>
     <row r="591">
@@ -25970,22 +25970,22 @@
         <v>0</v>
       </c>
       <c r="L595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M595" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N595" t="n">
         <v>16974.69</v>
       </c>
       <c r="O595" t="n">
-        <v>1476798.03</v>
+        <v>1459823.34</v>
       </c>
       <c r="P595" t="n">
         <v>26900</v>
       </c>
       <c r="Q595" t="n">
-        <v>2340300</v>
+        <v>2313400</v>
       </c>
     </row>
     <row r="596">
@@ -26273,10 +26273,10 @@
         <v>114</v>
       </c>
       <c r="N602" t="n">
-        <v>1560.9993877551</v>
+        <v>1560.9994428152</v>
       </c>
       <c r="O602" t="n">
-        <v>177953.9302040814</v>
+        <v>177953.9364809328</v>
       </c>
       <c r="P602" t="n">
         <v>2900</v>
@@ -27953,22 +27953,22 @@
         <v>0</v>
       </c>
       <c r="L641" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M641" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N641" t="n">
         <v>5569.98</v>
       </c>
       <c r="O641" t="n">
-        <v>139249.5</v>
+        <v>128109.54</v>
       </c>
       <c r="P641" t="n">
         <v>8900</v>
       </c>
       <c r="Q641" t="n">
-        <v>222500</v>
+        <v>204700</v>
       </c>
     </row>
     <row r="642">
@@ -27999,22 +27999,22 @@
         <v>0</v>
       </c>
       <c r="L642" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M642" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="N642" t="n">
         <v>4690.64</v>
       </c>
       <c r="O642" t="n">
-        <v>154791.12</v>
+        <v>103194.08</v>
       </c>
       <c r="P642" t="n">
         <v>7500</v>
       </c>
       <c r="Q642" t="n">
-        <v>247500</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="643">
@@ -28229,22 +28229,22 @@
         <v>0</v>
       </c>
       <c r="L647" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M647" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N647" t="n">
         <v>3254.49</v>
       </c>
       <c r="O647" t="n">
-        <v>110652.66</v>
+        <v>104143.68</v>
       </c>
       <c r="P647" t="n">
         <v>5200</v>
       </c>
       <c r="Q647" t="n">
-        <v>176800</v>
+        <v>166400</v>
       </c>
     </row>
     <row r="648">
@@ -28281,10 +28281,10 @@
         <v>21</v>
       </c>
       <c r="N648" t="n">
-        <v>5218.1705164319</v>
+        <v>5218.170521327</v>
       </c>
       <c r="O648" t="n">
-        <v>109581.5808450699</v>
+        <v>109581.580947867</v>
       </c>
       <c r="P648" t="n">
         <v>8500</v>
@@ -28327,10 +28327,10 @@
         <v>140</v>
       </c>
       <c r="N649" t="n">
-        <v>1595.0094492754</v>
+        <v>1595.0094476744</v>
       </c>
       <c r="O649" t="n">
-        <v>223301.322898556</v>
+        <v>223301.322674416</v>
       </c>
       <c r="P649" t="n">
         <v>2600</v>
@@ -28373,10 +28373,10 @@
         <v>81</v>
       </c>
       <c r="N650" t="n">
-        <v>3610.6500248756</v>
+        <v>3610.6500249688</v>
       </c>
       <c r="O650" t="n">
-        <v>292462.6520149236</v>
+        <v>292462.6520224728</v>
       </c>
       <c r="P650" t="n">
         <v>5800</v>
@@ -28459,22 +28459,22 @@
         <v>0</v>
       </c>
       <c r="L652" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M652" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N652" t="n">
         <v>4227.77</v>
       </c>
       <c r="O652" t="n">
-        <v>240982.89</v>
+        <v>232527.35</v>
       </c>
       <c r="P652" t="n">
         <v>6900</v>
       </c>
       <c r="Q652" t="n">
-        <v>393300</v>
+        <v>379500</v>
       </c>
     </row>
     <row r="653">
@@ -28686,25 +28686,25 @@
         <v>9</v>
       </c>
       <c r="K657" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L657" t="n">
         <v>0</v>
       </c>
       <c r="M657" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="N657" t="n">
         <v>6058.52</v>
       </c>
       <c r="O657" t="n">
-        <v>54526.68000000001</v>
+        <v>357452.6800000001</v>
       </c>
       <c r="P657" t="n">
         <v>9700</v>
       </c>
       <c r="Q657" t="n">
-        <v>87300</v>
+        <v>572300</v>
       </c>
     </row>
     <row r="658">
@@ -28781,22 +28781,22 @@
         <v>0</v>
       </c>
       <c r="L659" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M659" t="n">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="N659" t="n">
-        <v>1664.3592041199</v>
+        <v>1664.3590294957</v>
       </c>
       <c r="O659" t="n">
-        <v>674065.4776685594</v>
+        <v>664079.2527687843</v>
       </c>
       <c r="P659" t="n">
         <v>2900</v>
       </c>
       <c r="Q659" t="n">
-        <v>1174500</v>
+        <v>1157100</v>
       </c>
     </row>
     <row r="660">
@@ -30487,22 +30487,22 @@
         <v>0</v>
       </c>
       <c r="L696" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M696" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N696" t="n">
         <v>1817</v>
       </c>
       <c r="O696" t="n">
-        <v>283452</v>
+        <v>279818</v>
       </c>
       <c r="P696" t="n">
         <v>3100</v>
       </c>
       <c r="Q696" t="n">
-        <v>483600</v>
+        <v>477400</v>
       </c>
     </row>
     <row r="697">
@@ -31553,22 +31553,22 @@
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M719" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N719" t="n">
         <v>3424</v>
       </c>
       <c r="O719" t="n">
-        <v>650560</v>
+        <v>643712</v>
       </c>
       <c r="P719" t="n">
         <v>5900</v>
       </c>
       <c r="Q719" t="n">
-        <v>1121000</v>
+        <v>1109200</v>
       </c>
     </row>
     <row r="720">
@@ -31645,22 +31645,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M721" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N721" t="n">
         <v>8858.16</v>
       </c>
       <c r="O721" t="n">
-        <v>3250944.72</v>
+        <v>3242086.56</v>
       </c>
       <c r="P721" t="n">
         <v>15500</v>
       </c>
       <c r="Q721" t="n">
-        <v>5688500</v>
+        <v>5673000</v>
       </c>
     </row>
     <row r="722">
@@ -31967,22 +31967,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M728" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="N728" t="n">
         <v>5014</v>
       </c>
       <c r="O728" t="n">
-        <v>361008</v>
+        <v>310868</v>
       </c>
       <c r="P728" t="n">
         <v>8200</v>
       </c>
       <c r="Q728" t="n">
-        <v>590400</v>
+        <v>508400</v>
       </c>
     </row>
     <row r="729">
@@ -32013,22 +32013,22 @@
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M729" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N729" t="n">
         <v>5858</v>
       </c>
       <c r="O729" t="n">
-        <v>5858</v>
+        <v>0</v>
       </c>
       <c r="P729" t="n">
         <v>9500</v>
       </c>
       <c r="Q729" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="730">
@@ -32747,22 +32747,22 @@
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M745" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N745" t="n">
         <v>3519</v>
       </c>
       <c r="O745" t="n">
-        <v>904383</v>
+        <v>897345</v>
       </c>
       <c r="P745" t="n">
         <v>5900</v>
       </c>
       <c r="Q745" t="n">
-        <v>1516300</v>
+        <v>1504500</v>
       </c>
     </row>
     <row r="746">
@@ -32931,22 +32931,22 @@
         <v>0</v>
       </c>
       <c r="L749" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M749" t="n">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="N749" t="n">
         <v>4544</v>
       </c>
       <c r="O749" t="n">
-        <v>1463168</v>
+        <v>1435904</v>
       </c>
       <c r="P749" t="n">
         <v>7900</v>
       </c>
       <c r="Q749" t="n">
-        <v>2543800</v>
+        <v>2496400</v>
       </c>
     </row>
     <row r="750">
@@ -33167,10 +33167,10 @@
         <v>18</v>
       </c>
       <c r="N754" t="n">
-        <v>4907.8219448698</v>
+        <v>4907.8219751166</v>
       </c>
       <c r="O754" t="n">
-        <v>88340.7950076564</v>
+        <v>88340.7955520988</v>
       </c>
       <c r="P754" t="n">
         <v>8200</v>
@@ -33299,22 +33299,22 @@
         <v>0</v>
       </c>
       <c r="L757" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M757" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N757" t="n">
         <v>100129</v>
       </c>
       <c r="O757" t="n">
-        <v>200258</v>
+        <v>100129</v>
       </c>
       <c r="P757" t="n">
         <v>159900</v>
       </c>
       <c r="Q757" t="n">
-        <v>319800</v>
+        <v>159900</v>
       </c>
     </row>
     <row r="758">
@@ -34030,22 +34030,22 @@
         <v>0</v>
       </c>
       <c r="L773" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M773" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N773" t="n">
         <v>6849.2</v>
       </c>
       <c r="O773" t="n">
-        <v>828753.2</v>
+        <v>815054.7999999999</v>
       </c>
       <c r="P773" t="n">
         <v>11500</v>
       </c>
       <c r="Q773" t="n">
-        <v>1391500</v>
+        <v>1368500</v>
       </c>
     </row>
     <row r="774">
@@ -34122,22 +34122,22 @@
         <v>0</v>
       </c>
       <c r="L775" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M775" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N775" t="n">
         <v>5772</v>
       </c>
       <c r="O775" t="n">
-        <v>831168</v>
+        <v>819624</v>
       </c>
       <c r="P775" t="n">
         <v>9900</v>
       </c>
       <c r="Q775" t="n">
-        <v>1425600</v>
+        <v>1405800</v>
       </c>
     </row>
     <row r="776">
@@ -34168,22 +34168,22 @@
         <v>0</v>
       </c>
       <c r="L776" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M776" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N776" t="n">
         <v>6268</v>
       </c>
       <c r="O776" t="n">
-        <v>676944</v>
+        <v>664408</v>
       </c>
       <c r="P776" t="n">
         <v>10900</v>
       </c>
       <c r="Q776" t="n">
-        <v>1177200</v>
+        <v>1155400</v>
       </c>
     </row>
     <row r="777">
@@ -34444,22 +34444,22 @@
         <v>0</v>
       </c>
       <c r="L782" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M782" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N782" t="n">
         <v>7562</v>
       </c>
       <c r="O782" t="n">
-        <v>453720</v>
+        <v>446158</v>
       </c>
       <c r="P782" t="n">
         <v>12900</v>
       </c>
       <c r="Q782" t="n">
-        <v>774000</v>
+        <v>761100</v>
       </c>
     </row>
     <row r="783">
@@ -34490,22 +34490,22 @@
         <v>0</v>
       </c>
       <c r="L783" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M783" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="N783" t="n">
         <v>3898</v>
       </c>
       <c r="O783" t="n">
-        <v>1149910</v>
+        <v>1134318</v>
       </c>
       <c r="P783" t="n">
         <v>6900</v>
       </c>
       <c r="Q783" t="n">
-        <v>2035500</v>
+        <v>2007900</v>
       </c>
     </row>
     <row r="784">
@@ -34674,22 +34674,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M787" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="N787" t="n">
         <v>5438</v>
       </c>
       <c r="O787" t="n">
-        <v>201206</v>
+        <v>163140</v>
       </c>
       <c r="P787" t="n">
         <v>8900</v>
       </c>
       <c r="Q787" t="n">
-        <v>329300</v>
+        <v>267000</v>
       </c>
     </row>
     <row r="788">
@@ -34815,22 +34815,22 @@
         <v>0</v>
       </c>
       <c r="L790" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M790" t="n">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="N790" t="n">
         <v>753</v>
       </c>
       <c r="O790" t="n">
-        <v>539148</v>
+        <v>533124</v>
       </c>
       <c r="P790" t="n">
         <v>1600</v>
       </c>
       <c r="Q790" t="n">
-        <v>1145600</v>
+        <v>1132800</v>
       </c>
     </row>
     <row r="791">
@@ -35310,7 +35310,7 @@
         </is>
       </c>
       <c r="J801" t="n">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="K801" t="n">
         <v>0</v>
@@ -35319,19 +35319,19 @@
         <v>0</v>
       </c>
       <c r="M801" t="n">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="N801" t="n">
         <v>59834</v>
       </c>
       <c r="O801" t="n">
-        <v>14180658</v>
+        <v>8137424</v>
       </c>
       <c r="P801" t="n">
         <v>7900</v>
       </c>
       <c r="Q801" t="n">
-        <v>1872300</v>
+        <v>1074400</v>
       </c>
     </row>
     <row r="802">
@@ -35595,22 +35595,22 @@
         <v>0</v>
       </c>
       <c r="L807" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M807" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N807" t="n">
         <v>20014</v>
       </c>
       <c r="O807" t="n">
-        <v>460322</v>
+        <v>440308</v>
       </c>
       <c r="P807" t="n">
         <v>33900</v>
       </c>
       <c r="Q807" t="n">
-        <v>779700</v>
+        <v>745800</v>
       </c>
     </row>
     <row r="808">
@@ -35779,22 +35779,22 @@
         <v>0</v>
       </c>
       <c r="L811" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M811" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N811" t="n">
         <v>5215</v>
       </c>
       <c r="O811" t="n">
-        <v>458920</v>
+        <v>448490</v>
       </c>
       <c r="P811" t="n">
         <v>8900</v>
       </c>
       <c r="Q811" t="n">
-        <v>783200</v>
+        <v>765400</v>
       </c>
     </row>
     <row r="812">
@@ -36101,22 +36101,22 @@
         <v>0</v>
       </c>
       <c r="L818" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M818" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N818" t="n">
         <v>8700</v>
       </c>
       <c r="O818" t="n">
-        <v>669900</v>
+        <v>652500</v>
       </c>
       <c r="P818" t="n">
         <v>14900</v>
       </c>
       <c r="Q818" t="n">
-        <v>1147300</v>
+        <v>1117500</v>
       </c>
     </row>
     <row r="819">
@@ -36147,22 +36147,22 @@
         <v>0</v>
       </c>
       <c r="L819" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M819" t="n">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="N819" t="n">
         <v>1326</v>
       </c>
       <c r="O819" t="n">
-        <v>1520922</v>
+        <v>1515618</v>
       </c>
       <c r="P819" t="n">
         <v>2500</v>
       </c>
       <c r="Q819" t="n">
-        <v>2867500</v>
+        <v>2857500</v>
       </c>
     </row>
     <row r="820">
@@ -36193,22 +36193,22 @@
         <v>0</v>
       </c>
       <c r="L820" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M820" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="N820" t="n">
         <v>2573</v>
       </c>
       <c r="O820" t="n">
-        <v>396242</v>
+        <v>383377</v>
       </c>
       <c r="P820" t="n">
         <v>4500</v>
       </c>
       <c r="Q820" t="n">
-        <v>693000</v>
+        <v>670500</v>
       </c>
     </row>
     <row r="821">
@@ -36702,22 +36702,22 @@
         <v>0</v>
       </c>
       <c r="L831" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M831" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N831" t="n">
         <v>64612</v>
       </c>
       <c r="O831" t="n">
-        <v>3230600</v>
+        <v>3165988</v>
       </c>
       <c r="P831" t="n">
         <v>103900</v>
       </c>
       <c r="Q831" t="n">
-        <v>5195000</v>
+        <v>5091100</v>
       </c>
     </row>
     <row r="832">
@@ -36794,22 +36794,22 @@
         <v>0</v>
       </c>
       <c r="L833" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M833" t="n">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="N833" t="n">
-        <v>1516.0388110875</v>
+        <v>1516.0388102832</v>
       </c>
       <c r="O833" t="n">
-        <v>915687.44189685</v>
+        <v>906591.2085493536</v>
       </c>
       <c r="P833" t="n">
         <v>2300</v>
       </c>
       <c r="Q833" t="n">
-        <v>1389200</v>
+        <v>1375400</v>
       </c>
     </row>
     <row r="834">
@@ -36840,22 +36840,22 @@
         <v>0</v>
       </c>
       <c r="L834" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M834" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="N834" t="n">
-        <v>4248.6238427948</v>
+        <v>4248.635</v>
       </c>
       <c r="O834" t="n">
-        <v>505586.2372925812</v>
+        <v>433360.77</v>
       </c>
       <c r="P834" t="n">
         <v>5900</v>
       </c>
       <c r="Q834" t="n">
-        <v>702100</v>
+        <v>601800</v>
       </c>
     </row>
     <row r="835">
@@ -36936,10 +36936,10 @@
         <v>363</v>
       </c>
       <c r="N836" t="n">
-        <v>2458.5133829585</v>
+        <v>2458.5133724619</v>
       </c>
       <c r="O836" t="n">
-        <v>892440.3580139356</v>
+        <v>892440.3542036697</v>
       </c>
       <c r="P836" t="n">
         <v>3500</v>
@@ -36976,22 +36976,22 @@
         <v>0</v>
       </c>
       <c r="L837" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M837" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N837" t="n">
-        <v>1907.3941918295</v>
+        <v>1907.3940437158</v>
       </c>
       <c r="O837" t="n">
-        <v>364312.2906394345</v>
+        <v>362404.868306002</v>
       </c>
       <c r="P837" t="n">
         <v>2500</v>
       </c>
       <c r="Q837" t="n">
-        <v>477500</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="838">
@@ -37028,10 +37028,10 @@
         <v>189</v>
       </c>
       <c r="N838" t="n">
-        <v>1771.0911342735</v>
+        <v>1771.0911179361</v>
       </c>
       <c r="O838" t="n">
-        <v>334736.2243776915</v>
+        <v>334736.2212899229</v>
       </c>
       <c r="P838" t="n">
         <v>2500</v>
@@ -37074,10 +37074,10 @@
         <v>418</v>
       </c>
       <c r="N839" t="n">
-        <v>2079.3841889251</v>
+        <v>2079.3841813438</v>
       </c>
       <c r="O839" t="n">
-        <v>869182.5909706918</v>
+        <v>869182.5878017084</v>
       </c>
       <c r="P839" t="n">
         <v>2900</v>
@@ -37114,22 +37114,22 @@
         <v>0</v>
       </c>
       <c r="L840" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M840" t="n">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="N840" t="n">
-        <v>1803.0151566778</v>
+        <v>1803.0151724138</v>
       </c>
       <c r="O840" t="n">
-        <v>787917.6234681986</v>
+        <v>775296.524137934</v>
       </c>
       <c r="P840" t="n">
         <v>2500</v>
       </c>
       <c r="Q840" t="n">
-        <v>1092500</v>
+        <v>1075000</v>
       </c>
     </row>
     <row r="841">
@@ -37212,10 +37212,10 @@
         <v>440</v>
       </c>
       <c r="N842" t="n">
-        <v>2122.1640073529</v>
+        <v>2122.1640036787</v>
       </c>
       <c r="O842" t="n">
-        <v>933752.1632352761</v>
+        <v>933752.161618628</v>
       </c>
       <c r="P842" t="n">
         <v>2900</v>
@@ -37252,22 +37252,22 @@
         <v>0</v>
       </c>
       <c r="L843" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M843" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N843" t="n">
-        <v>2108.7899885584</v>
+        <v>2108.7900518135</v>
       </c>
       <c r="O843" t="n">
-        <v>84351.59954233601</v>
+        <v>69590.07170984551</v>
       </c>
       <c r="P843" t="n">
         <v>2900</v>
       </c>
       <c r="Q843" t="n">
-        <v>116000</v>
+        <v>95700</v>
       </c>
     </row>
     <row r="844">
@@ -37298,22 +37298,22 @@
         <v>0</v>
       </c>
       <c r="L844" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M844" t="n">
-        <v>907</v>
+        <v>893</v>
       </c>
       <c r="N844" t="n">
-        <v>2056.0838222089</v>
+        <v>2056.0837188071</v>
       </c>
       <c r="O844" t="n">
-        <v>1864868.026743472</v>
+        <v>1836082.76089474</v>
       </c>
       <c r="P844" t="n">
         <v>2900</v>
       </c>
       <c r="Q844" t="n">
-        <v>2630300</v>
+        <v>2589700</v>
       </c>
     </row>
     <row r="845">
@@ -37344,22 +37344,22 @@
         <v>0</v>
       </c>
       <c r="L845" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M845" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N845" t="n">
-        <v>3224.568287037</v>
+        <v>3224.5683024119</v>
       </c>
       <c r="O845" t="n">
-        <v>796468.366898139</v>
+        <v>786794.6657885036</v>
       </c>
       <c r="P845" t="n">
         <v>4500</v>
       </c>
       <c r="Q845" t="n">
-        <v>1111500</v>
+        <v>1098000</v>
       </c>
     </row>
     <row r="846">
@@ -37396,10 +37396,10 @@
         <v>455</v>
       </c>
       <c r="N846" t="n">
-        <v>1655.931057226</v>
+        <v>1655.9310223953</v>
       </c>
       <c r="O846" t="n">
-        <v>753448.6310378299</v>
+        <v>753448.6151898615</v>
       </c>
       <c r="P846" t="n">
         <v>2500</v>
@@ -37761,22 +37761,22 @@
         <v>0</v>
       </c>
       <c r="L854" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M854" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="N854" t="n">
-        <v>1592.2755269762</v>
+        <v>1592.2756948933</v>
       </c>
       <c r="O854" t="n">
-        <v>184703.9611292392</v>
+        <v>170373.4993535831</v>
       </c>
       <c r="P854" t="n">
         <v>2500</v>
       </c>
       <c r="Q854" t="n">
-        <v>290000</v>
+        <v>267500</v>
       </c>
     </row>
     <row r="855">
@@ -37857,10 +37857,10 @@
         <v>61</v>
       </c>
       <c r="N856" t="n">
-        <v>2311.9247818182</v>
+        <v>2311.9246983547</v>
       </c>
       <c r="O856" t="n">
-        <v>141027.4116909102</v>
+        <v>141027.4065996367</v>
       </c>
       <c r="P856" t="n">
         <v>3500</v>
@@ -37943,22 +37943,22 @@
         <v>0</v>
       </c>
       <c r="L858" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M858" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="N858" t="n">
-        <v>2060.160557377</v>
+        <v>2060.1604635762</v>
       </c>
       <c r="O858" t="n">
-        <v>195715.252950815</v>
+        <v>183354.2812582818</v>
       </c>
       <c r="P858" t="n">
         <v>2900</v>
       </c>
       <c r="Q858" t="n">
-        <v>275500</v>
+        <v>258100</v>
       </c>
     </row>
     <row r="859">
@@ -37995,10 +37995,10 @@
         <v>75</v>
       </c>
       <c r="N859" t="n">
-        <v>2546.9850949914</v>
+        <v>2546.985</v>
       </c>
       <c r="O859" t="n">
-        <v>191023.882124355</v>
+        <v>191023.875</v>
       </c>
       <c r="P859" t="n">
         <v>3900</v>
@@ -38041,10 +38041,10 @@
         <v>281</v>
       </c>
       <c r="N860" t="n">
-        <v>1259.2744422442</v>
+        <v>1259.2744638514</v>
       </c>
       <c r="O860" t="n">
-        <v>353856.1182706202</v>
+        <v>353856.1243422434</v>
       </c>
       <c r="P860" t="n">
         <v>1900</v>
@@ -38127,22 +38127,22 @@
         <v>0</v>
       </c>
       <c r="L862" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M862" t="n">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="N862" t="n">
         <v>1801</v>
       </c>
       <c r="O862" t="n">
-        <v>1049983</v>
+        <v>1042779</v>
       </c>
       <c r="P862" t="n">
         <v>2900</v>
       </c>
       <c r="Q862" t="n">
-        <v>1690700</v>
+        <v>1679100</v>
       </c>
     </row>
     <row r="863">
@@ -38171,22 +38171,22 @@
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M863" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="N863" t="n">
-        <v>692.15208975521</v>
+        <v>692.15209736124</v>
       </c>
       <c r="O863" t="n">
-        <v>75444.57778331789</v>
+        <v>67138.75344404028</v>
       </c>
       <c r="P863" t="n">
         <v>1200</v>
       </c>
       <c r="Q863" t="n">
-        <v>130800</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="864">
@@ -39778,22 +39778,22 @@
         <v>0</v>
       </c>
       <c r="L898" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M898" t="n">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="N898" t="n">
         <v>1828.64</v>
       </c>
       <c r="O898" t="n">
-        <v>1291019.84</v>
+        <v>1276390.72</v>
       </c>
       <c r="P898" t="n">
         <v>2000</v>
       </c>
       <c r="Q898" t="n">
-        <v>1412000</v>
+        <v>1396000</v>
       </c>
     </row>
     <row r="899">
@@ -40410,22 +40410,22 @@
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M912" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N912" t="n">
         <v>6213.51</v>
       </c>
       <c r="O912" t="n">
-        <v>372810.6</v>
+        <v>360383.58</v>
       </c>
       <c r="P912" t="n">
         <v>10300</v>
       </c>
       <c r="Q912" t="n">
-        <v>618000</v>
+        <v>597400</v>
       </c>
     </row>
     <row r="913">
@@ -40850,22 +40850,22 @@
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M922" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="N922" t="n">
         <v>177.65</v>
       </c>
       <c r="O922" t="n">
-        <v>12080.2</v>
+        <v>3197.7</v>
       </c>
       <c r="P922" t="n">
         <v>300</v>
       </c>
       <c r="Q922" t="n">
-        <v>20400</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="923">
@@ -41073,10 +41073,10 @@
         <v>60</v>
       </c>
       <c r="N927" t="n">
-        <v>4032.3968542199</v>
+        <v>4032.3968461538</v>
       </c>
       <c r="O927" t="n">
-        <v>241943.811253194</v>
+        <v>241943.810769228</v>
       </c>
       <c r="P927" t="n">
         <v>4200</v>
@@ -41160,22 +41160,22 @@
         <v>0</v>
       </c>
       <c r="L929" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M929" t="n">
-        <v>3385</v>
+        <v>3347</v>
       </c>
       <c r="N929" t="n">
-        <v>517.28815469086</v>
+        <v>517.28824762181</v>
       </c>
       <c r="O929" t="n">
-        <v>1751020.403628561</v>
+        <v>1731363.764790198</v>
       </c>
       <c r="P929" t="n">
         <v>900</v>
       </c>
       <c r="Q929" t="n">
-        <v>3046500</v>
+        <v>3012300</v>
       </c>
     </row>
     <row r="930">
@@ -41386,22 +41386,22 @@
         <v>0</v>
       </c>
       <c r="L934" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M934" t="n">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="N934" t="n">
-        <v>3110.8427709611</v>
+        <v>3110.8426932617</v>
       </c>
       <c r="O934" t="n">
-        <v>1894503.24751531</v>
+        <v>1822953.818251356</v>
       </c>
       <c r="P934" t="n">
         <v>4500</v>
       </c>
       <c r="Q934" t="n">
-        <v>2740500</v>
+        <v>2637000</v>
       </c>
     </row>
     <row r="935">
@@ -41608,22 +41608,22 @@
         <v>0</v>
       </c>
       <c r="L939" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M939" t="n">
-        <v>1058</v>
+        <v>1034</v>
       </c>
       <c r="N939" t="n">
-        <v>703.79533220158</v>
+        <v>703.7953201758</v>
       </c>
       <c r="O939" t="n">
-        <v>744615.4614692716</v>
+        <v>727724.3610617772</v>
       </c>
       <c r="P939" t="n">
         <v>900</v>
       </c>
       <c r="Q939" t="n">
-        <v>952200</v>
+        <v>930600</v>
       </c>
     </row>
     <row r="940">
@@ -41841,10 +41841,10 @@
         <v>3</v>
       </c>
       <c r="N944" t="n">
-        <v>2501.3852212389</v>
+        <v>2501.3851351351</v>
       </c>
       <c r="O944" t="n">
-        <v>7504.1556637167</v>
+        <v>7504.155405405299</v>
       </c>
       <c r="P944" t="n">
         <v>4100</v>
@@ -42190,22 +42190,22 @@
         <v>0</v>
       </c>
       <c r="L952" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M952" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="N952" t="n">
         <v>2525.02</v>
       </c>
       <c r="O952" t="n">
-        <v>83325.66</v>
+        <v>58075.46</v>
       </c>
       <c r="P952" t="n">
         <v>3000</v>
       </c>
       <c r="Q952" t="n">
-        <v>99000</v>
+        <v>69000</v>
       </c>
     </row>
     <row r="953">
@@ -42365,10 +42365,10 @@
         <v>259</v>
       </c>
       <c r="N956" t="n">
-        <v>2077.4945652174</v>
+        <v>2077.4945784884</v>
       </c>
       <c r="O956" t="n">
-        <v>538071.0923913067</v>
+        <v>538071.0958284956</v>
       </c>
       <c r="P956" t="n">
         <v>2900</v>
@@ -42625,10 +42625,10 @@
         <v>74</v>
       </c>
       <c r="N962" t="n">
-        <v>1595.5155551576</v>
+        <v>1595.5155292429</v>
       </c>
       <c r="O962" t="n">
-        <v>118068.1510816624</v>
+        <v>118068.1491639746</v>
       </c>
       <c r="P962" t="n">
         <v>2500</v>
@@ -43237,22 +43237,22 @@
         <v>0</v>
       </c>
       <c r="L975" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M975" t="n">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="N975" t="n">
         <v>1669.6</v>
       </c>
       <c r="O975" t="n">
-        <v>958350.3999999999</v>
+        <v>948332.7999999999</v>
       </c>
       <c r="P975" t="n">
         <v>2900</v>
       </c>
       <c r="Q975" t="n">
-        <v>1664600</v>
+        <v>1647200</v>
       </c>
     </row>
     <row r="976">
@@ -43379,22 +43379,22 @@
         <v>0</v>
       </c>
       <c r="L978" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M978" t="n">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="N978" t="n">
-        <v>3063.6218891688</v>
+        <v>3063.6218939394</v>
       </c>
       <c r="O978" t="n">
-        <v>3964326.724584427</v>
+        <v>3955135.865075765</v>
       </c>
       <c r="P978" t="n">
         <v>3500</v>
       </c>
       <c r="Q978" t="n">
-        <v>4529000</v>
+        <v>4518500</v>
       </c>
     </row>
     <row r="979">
@@ -43477,22 +43477,22 @@
         <v>0</v>
       </c>
       <c r="L980" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M980" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N980" t="n">
         <v>10296.29</v>
       </c>
       <c r="O980" t="n">
-        <v>247110.96</v>
+        <v>236814.67</v>
       </c>
       <c r="P980" t="n">
         <v>16900</v>
       </c>
       <c r="Q980" t="n">
-        <v>405600</v>
+        <v>388700</v>
       </c>
     </row>
     <row r="981">
@@ -43529,10 +43529,10 @@
         <v>1</v>
       </c>
       <c r="N981" t="n">
-        <v>3879.9761538462</v>
+        <v>3879.9772727273</v>
       </c>
       <c r="O981" t="n">
-        <v>3879.9761538462</v>
+        <v>3879.9772727273</v>
       </c>
       <c r="P981" t="n">
         <v>12500</v>
@@ -43861,10 +43861,10 @@
         <v>55</v>
       </c>
       <c r="N988" t="n">
-        <v>3067.0905389222</v>
+        <v>3067.0905454545</v>
       </c>
       <c r="O988" t="n">
-        <v>168689.979640721</v>
+        <v>168689.9799999975</v>
       </c>
       <c r="P988" t="n">
         <v>7200</v>
@@ -44364,10 +44364,10 @@
         <v>1</v>
       </c>
       <c r="N999" t="n">
-        <v>10737.526470588</v>
+        <v>10737.5264</v>
       </c>
       <c r="O999" t="n">
-        <v>10737.526470588</v>
+        <v>10737.5264</v>
       </c>
       <c r="P999" t="n">
         <v>18900</v>
@@ -45114,10 +45114,10 @@
         <v>215</v>
       </c>
       <c r="N1015" t="n">
-        <v>7046.939829932</v>
+        <v>7046.9398298958</v>
       </c>
       <c r="O1015" t="n">
-        <v>1515092.06343538</v>
+        <v>1515092.063427597</v>
       </c>
       <c r="P1015" t="n">
         <v>9900</v>
@@ -45154,22 +45154,22 @@
         <v>0</v>
       </c>
       <c r="L1016" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M1016" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N1016" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1016" t="n">
-        <v>1582000.55</v>
+        <v>1411631.26</v>
       </c>
       <c r="P1016" t="n">
         <v>27900</v>
       </c>
       <c r="Q1016" t="n">
-        <v>1813500</v>
+        <v>1618200</v>
       </c>
     </row>
     <row r="1017">
@@ -45871,10 +45871,10 @@
         <v>196</v>
       </c>
       <c r="N1031" t="n">
-        <v>430.60997670355</v>
+        <v>430.60997668998</v>
       </c>
       <c r="O1031" t="n">
-        <v>84399.5554338958</v>
+        <v>84399.55543123608</v>
       </c>
       <c r="P1031" t="n">
         <v>2200</v>
@@ -47627,22 +47627,22 @@
         <v>0</v>
       </c>
       <c r="L1072" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1072" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="N1072" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1072" t="n">
-        <v>36473.67</v>
+        <v>22354.83</v>
       </c>
       <c r="P1072" t="n">
         <v>1900</v>
       </c>
       <c r="Q1072" t="n">
-        <v>58900</v>
+        <v>36100</v>
       </c>
     </row>
     <row r="1073">
@@ -47671,22 +47671,22 @@
         <v>0</v>
       </c>
       <c r="L1073" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M1073" t="n">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="N1073" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1073" t="n">
-        <v>1444582.6</v>
+        <v>1336398</v>
       </c>
       <c r="P1073" t="n">
         <v>5100</v>
       </c>
       <c r="Q1073" t="n">
-        <v>2315400</v>
+        <v>2142000</v>
       </c>
     </row>
     <row r="1074">
@@ -47979,10 +47979,10 @@
         <v>92</v>
       </c>
       <c r="N1080" t="n">
-        <v>2830.2251183432</v>
+        <v>2830.2251488095</v>
       </c>
       <c r="O1080" t="n">
-        <v>260380.7108875744</v>
+        <v>260380.713690474</v>
       </c>
       <c r="P1080" t="n">
         <v>2400</v>
@@ -48023,10 +48023,10 @@
         <v>9</v>
       </c>
       <c r="N1081" t="n">
-        <v>15219.155340909</v>
+        <v>15219.155287356</v>
       </c>
       <c r="O1081" t="n">
-        <v>136972.398068181</v>
+        <v>136972.397586204</v>
       </c>
       <c r="P1081" t="n">
         <v>16000</v>
@@ -48404,10 +48404,10 @@
         <v>66</v>
       </c>
       <c r="N1090" t="n">
-        <v>3153.2320501475</v>
+        <v>3153.2320511559</v>
       </c>
       <c r="O1090" t="n">
-        <v>208113.315309735</v>
+        <v>208113.3153762894</v>
       </c>
       <c r="P1090" t="n">
         <v>3300</v>
@@ -48825,22 +48825,22 @@
         <v>0</v>
       </c>
       <c r="L1100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1100" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N1100" t="n">
         <v>5077</v>
       </c>
       <c r="O1100" t="n">
-        <v>705703</v>
+        <v>690472</v>
       </c>
       <c r="P1100" t="n">
         <v>8500</v>
       </c>
       <c r="Q1100" t="n">
-        <v>1181500</v>
+        <v>1156000</v>
       </c>
     </row>
     <row r="1101">
@@ -48999,22 +48999,22 @@
         <v>0</v>
       </c>
       <c r="L1104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1104" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N1104" t="n">
-        <v>4985.4046511628</v>
+        <v>4985.4047058824</v>
       </c>
       <c r="O1104" t="n">
-        <v>523467.4883720941</v>
+        <v>513496.6847058872</v>
       </c>
       <c r="P1104" t="n">
         <v>7900</v>
       </c>
       <c r="Q1104" t="n">
-        <v>829500</v>
+        <v>813700</v>
       </c>
     </row>
     <row r="1105">
@@ -49050,22 +49050,22 @@
         <v>0</v>
       </c>
       <c r="L1105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1105" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N1105" t="n">
-        <v>1757.3205360825</v>
+        <v>1757.3205416667</v>
       </c>
       <c r="O1105" t="n">
-        <v>91380.66787629</v>
+        <v>87866.02708333499</v>
       </c>
       <c r="P1105" t="n">
         <v>2000</v>
       </c>
       <c r="Q1105" t="n">
-        <v>104000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="1106">
@@ -49096,22 +49096,22 @@
         <v>0</v>
       </c>
       <c r="L1106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1106" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="N1106" t="n">
         <v>1561.33</v>
       </c>
       <c r="O1106" t="n">
-        <v>441856.39</v>
+        <v>435611.07</v>
       </c>
       <c r="P1106" t="n">
         <v>2000</v>
       </c>
       <c r="Q1106" t="n">
-        <v>566000</v>
+        <v>558000</v>
       </c>
     </row>
     <row r="1107">
@@ -49541,22 +49541,22 @@
         <v>0</v>
       </c>
       <c r="L1116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1116" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N1116" t="n">
         <v>1952.66</v>
       </c>
       <c r="O1116" t="n">
-        <v>331952.2</v>
+        <v>328046.88</v>
       </c>
       <c r="P1116" t="n">
         <v>3500</v>
       </c>
       <c r="Q1116" t="n">
-        <v>595000</v>
+        <v>588000</v>
       </c>
     </row>
     <row r="1117">
@@ -49771,22 +49771,22 @@
         <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M1121" t="n">
-        <v>429</v>
+        <v>375</v>
       </c>
       <c r="N1121" t="n">
-        <v>788.1365841161401</v>
+        <v>7480</v>
       </c>
       <c r="O1121" t="n">
-        <v>338110.5945858241</v>
+        <v>2805000</v>
       </c>
       <c r="P1121" t="n">
         <v>9500</v>
       </c>
       <c r="Q1121" t="n">
-        <v>4075500</v>
+        <v>3562500</v>
       </c>
     </row>
     <row r="1122">
@@ -49909,22 +49909,22 @@
         <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M1124" t="n">
-        <v>709</v>
+        <v>583</v>
       </c>
       <c r="N1124" t="n">
         <v>9240</v>
       </c>
       <c r="O1124" t="n">
-        <v>6551160</v>
+        <v>5386920</v>
       </c>
       <c r="P1124" t="n">
         <v>11500</v>
       </c>
       <c r="Q1124" t="n">
-        <v>8153500</v>
+        <v>6704500</v>
       </c>
     </row>
     <row r="1125">
@@ -52778,10 +52778,10 @@
         <v>43</v>
       </c>
       <c r="N1187" t="n">
-        <v>2402.6744966443</v>
+        <v>2402.6744594595</v>
       </c>
       <c r="O1187" t="n">
-        <v>103315.0033557049</v>
+        <v>103315.0017567585</v>
       </c>
       <c r="P1187" t="n">
         <v>3000</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1354,10 +1354,10 @@
         <v>192</v>
       </c>
       <c r="N23" t="n">
-        <v>1811.3047800109</v>
+        <v>1811.3053012048</v>
       </c>
       <c r="O23" t="n">
-        <v>347770.5177620928</v>
+        <v>347770.6178313215</v>
       </c>
       <c r="P23" t="n">
         <v>2600</v>
@@ -1471,10 +1471,10 @@
         <v>155</v>
       </c>
       <c r="N26" t="n">
-        <v>3376.7464976959</v>
+        <v>3376.7464891304</v>
       </c>
       <c r="O26" t="n">
-        <v>523395.7071428645</v>
+        <v>523395.705815212</v>
       </c>
       <c r="P26" t="n">
         <v>4500</v>
@@ -2965,10 +2965,10 @@
         <v>41</v>
       </c>
       <c r="N63" t="n">
-        <v>6272.8545786963</v>
+        <v>6272.8545933014</v>
       </c>
       <c r="O63" t="n">
-        <v>257187.0377265483</v>
+        <v>257187.0383253574</v>
       </c>
       <c r="P63" t="n">
         <v>7900</v>
@@ -3082,10 +3082,10 @@
         <v>44</v>
       </c>
       <c r="N66" t="n">
-        <v>3926.8371237802</v>
+        <v>3926.8371059432</v>
       </c>
       <c r="O66" t="n">
-        <v>172780.8334463288</v>
+        <v>172780.8326615008</v>
       </c>
       <c r="P66" t="n">
         <v>4800</v>
@@ -3288,10 +3288,10 @@
         <v>205</v>
       </c>
       <c r="N71" t="n">
-        <v>2413.0010626993</v>
+        <v>2413.0010683761</v>
       </c>
       <c r="O71" t="n">
-        <v>494665.2178533564</v>
+        <v>494665.2190171005</v>
       </c>
       <c r="P71" t="n">
         <v>4700</v>
@@ -3483,10 +3483,10 @@
         <v>167</v>
       </c>
       <c r="N76" t="n">
-        <v>3716.3301892744</v>
+        <v>3716.3301923077</v>
       </c>
       <c r="O76" t="n">
-        <v>620627.1416088247</v>
+        <v>620627.142115386</v>
       </c>
       <c r="P76" t="n">
         <v>9500</v>
@@ -4181,10 +4181,10 @@
         <v>56</v>
       </c>
       <c r="N93" t="n">
-        <v>3910.6281927711</v>
+        <v>3910.6281818182</v>
       </c>
       <c r="O93" t="n">
-        <v>218995.1787951816</v>
+        <v>218995.1781818192</v>
       </c>
       <c r="P93" t="n">
         <v>9100</v>
@@ -5026,22 +5026,22 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N112" t="n">
-        <v>16486.409172932</v>
+        <v>16486.409090909</v>
       </c>
       <c r="O112" t="n">
-        <v>164864.09172932</v>
+        <v>148377.681818181</v>
       </c>
       <c r="P112" t="n">
         <v>30500</v>
       </c>
       <c r="Q112" t="n">
-        <v>305000</v>
+        <v>274500</v>
       </c>
     </row>
     <row r="113">
@@ -5365,22 +5365,22 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M120" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="N120" t="n">
         <v>6321.94</v>
       </c>
       <c r="O120" t="n">
-        <v>246555.66</v>
+        <v>189658.2</v>
       </c>
       <c r="P120" t="n">
         <v>14100</v>
       </c>
       <c r="Q120" t="n">
-        <v>549900</v>
+        <v>423000</v>
       </c>
     </row>
     <row r="121">
@@ -6236,10 +6236,10 @@
         <v>12</v>
       </c>
       <c r="N140" t="n">
-        <v>200072.20007812</v>
+        <v>200072.20015748</v>
       </c>
       <c r="O140" t="n">
-        <v>2400866.40093744</v>
+        <v>2400866.40188976</v>
       </c>
       <c r="P140" t="n">
         <v>312000</v>
@@ -7213,10 +7213,10 @@
         <v>4</v>
       </c>
       <c r="N163" t="n">
-        <v>61666.874005305</v>
+        <v>61666.874015957</v>
       </c>
       <c r="O163" t="n">
-        <v>246667.49602122</v>
+        <v>246667.496063828</v>
       </c>
       <c r="P163" t="n">
         <v>98900</v>
@@ -9762,10 +9762,10 @@
         <v>293</v>
       </c>
       <c r="N221" t="n">
-        <v>1950.2147262682</v>
+        <v>1950.2147103275</v>
       </c>
       <c r="O221" t="n">
-        <v>571412.9147965825</v>
+        <v>571412.9101259575</v>
       </c>
       <c r="P221" t="n">
         <v>2900</v>
@@ -10468,22 +10468,22 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M238" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
         <v>32420</v>
       </c>
       <c r="O238" t="n">
-        <v>97260</v>
+        <v>0</v>
       </c>
       <c r="P238" t="n">
         <v>16900</v>
       </c>
       <c r="Q238" t="n">
-        <v>50700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -10518,10 +10518,10 @@
         <v>606</v>
       </c>
       <c r="N239" t="n">
-        <v>1098.055952691</v>
+        <v>1098.0561100153</v>
       </c>
       <c r="O239" t="n">
-        <v>665421.9073307459</v>
+        <v>665422.0026692718</v>
       </c>
       <c r="P239" t="n">
         <v>1500</v>
@@ -12227,22 +12227,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M279" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="N279" t="n">
         <v>3247</v>
       </c>
       <c r="O279" t="n">
-        <v>347429</v>
+        <v>327947</v>
       </c>
       <c r="P279" t="n">
         <v>5200</v>
       </c>
       <c r="Q279" t="n">
-        <v>556400</v>
+        <v>525200</v>
       </c>
     </row>
     <row r="280">
@@ -12279,10 +12279,10 @@
         <v>247</v>
       </c>
       <c r="N280" t="n">
-        <v>2582.2559895309</v>
+        <v>2582.2559749444</v>
       </c>
       <c r="O280" t="n">
-        <v>637817.2294141323</v>
+        <v>637817.2258112668</v>
       </c>
       <c r="P280" t="n">
         <v>4500</v>
@@ -12365,22 +12365,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M282" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N282" t="n">
-        <v>5216.8959618537</v>
+        <v>5216.8962134973</v>
       </c>
       <c r="O282" t="n">
-        <v>725148.5386976643</v>
+        <v>704280.9888221355</v>
       </c>
       <c r="P282" t="n">
         <v>8500</v>
       </c>
       <c r="Q282" t="n">
-        <v>1181500</v>
+        <v>1147500</v>
       </c>
     </row>
     <row r="283">
@@ -12667,22 +12667,22 @@
         <v>0</v>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M289" t="n">
-        <v>927</v>
+        <v>735</v>
       </c>
       <c r="N289" t="n">
-        <v>3158.8608154486</v>
+        <v>3158.8608230874</v>
       </c>
       <c r="O289" t="n">
-        <v>2928263.975920852</v>
+        <v>2321762.704969239</v>
       </c>
       <c r="P289" t="n">
         <v>5600</v>
       </c>
       <c r="Q289" t="n">
-        <v>5191200</v>
+        <v>4116000</v>
       </c>
     </row>
     <row r="290">
@@ -12805,22 +12805,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M292" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="N292" t="n">
         <v>5081</v>
       </c>
       <c r="O292" t="n">
-        <v>467452</v>
+        <v>386156</v>
       </c>
       <c r="P292" t="n">
         <v>8200</v>
       </c>
       <c r="Q292" t="n">
-        <v>754400</v>
+        <v>623200</v>
       </c>
     </row>
     <row r="293">
@@ -12895,22 +12895,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M294" t="n">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="N294" t="n">
-        <v>3230.0677302632</v>
+        <v>3230.0675874126</v>
       </c>
       <c r="O294" t="n">
-        <v>471589.8886184272</v>
+        <v>355307.434615386</v>
       </c>
       <c r="P294" t="n">
         <v>6200</v>
       </c>
       <c r="Q294" t="n">
-        <v>905200</v>
+        <v>682000</v>
       </c>
     </row>
     <row r="295">
@@ -13126,10 +13126,10 @@
         <v>109</v>
       </c>
       <c r="N299" t="n">
-        <v>2694.8234059946</v>
+        <v>2694.8233333333</v>
       </c>
       <c r="O299" t="n">
-        <v>293735.7512534114</v>
+        <v>293735.7433333297</v>
       </c>
       <c r="P299" t="n">
         <v>4900</v>
@@ -13207,22 +13207,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M301" t="n">
-        <v>601</v>
+        <v>501</v>
       </c>
       <c r="N301" t="n">
         <v>1026.13</v>
       </c>
       <c r="O301" t="n">
-        <v>616704.1300000001</v>
+        <v>514091.1300000001</v>
       </c>
       <c r="P301" t="n">
         <v>1900</v>
       </c>
       <c r="Q301" t="n">
-        <v>1141900</v>
+        <v>951900</v>
       </c>
     </row>
     <row r="302">
@@ -13299,22 +13299,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M303" t="n">
-        <v>5495</v>
+        <v>5195</v>
       </c>
       <c r="N303" t="n">
         <v>156.25</v>
       </c>
       <c r="O303" t="n">
-        <v>858593.75</v>
+        <v>811718.75</v>
       </c>
       <c r="P303" t="n">
         <v>250</v>
       </c>
       <c r="Q303" t="n">
-        <v>1373750</v>
+        <v>1298750</v>
       </c>
     </row>
     <row r="304">
@@ -13582,10 +13582,10 @@
         <v>299</v>
       </c>
       <c r="N309" t="n">
-        <v>3795.7100070671</v>
+        <v>3795.7100070822</v>
       </c>
       <c r="O309" t="n">
-        <v>1134917.292113063</v>
+        <v>1134917.292117578</v>
       </c>
       <c r="P309" t="n">
         <v>6200</v>
@@ -13842,22 +13842,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M315" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="N315" t="n">
-        <v>4890.9300465929</v>
+        <v>4890.9300467563</v>
       </c>
       <c r="O315" t="n">
-        <v>244546.502329645</v>
+        <v>215200.9220572772</v>
       </c>
       <c r="P315" t="n">
         <v>8200</v>
       </c>
       <c r="Q315" t="n">
-        <v>410000</v>
+        <v>360800</v>
       </c>
     </row>
     <row r="316">
@@ -13937,22 +13937,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M317" t="n">
-        <v>883</v>
+        <v>873</v>
       </c>
       <c r="N317" t="n">
         <v>1203.38</v>
       </c>
       <c r="O317" t="n">
-        <v>1062584.54</v>
+        <v>1050550.74</v>
       </c>
       <c r="P317" t="n">
         <v>1900</v>
       </c>
       <c r="Q317" t="n">
-        <v>1677700</v>
+        <v>1658700</v>
       </c>
     </row>
     <row r="318">
@@ -14029,22 +14029,22 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M319" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N319" t="n">
         <v>5888</v>
       </c>
       <c r="O319" t="n">
-        <v>276736</v>
+        <v>241408</v>
       </c>
       <c r="P319" t="n">
         <v>9500</v>
       </c>
       <c r="Q319" t="n">
-        <v>446500</v>
+        <v>389500</v>
       </c>
     </row>
     <row r="320">
@@ -14290,22 +14290,22 @@
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M325" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="N325" t="n">
         <v>7041</v>
       </c>
       <c r="O325" t="n">
-        <v>218271</v>
+        <v>133779</v>
       </c>
       <c r="P325" t="n">
         <v>11500</v>
       </c>
       <c r="Q325" t="n">
-        <v>356500</v>
+        <v>218500</v>
       </c>
     </row>
     <row r="326">
@@ -14336,22 +14336,22 @@
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M326" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N326" t="n">
         <v>5667.94</v>
       </c>
       <c r="O326" t="n">
-        <v>294732.88</v>
+        <v>260725.24</v>
       </c>
       <c r="P326" t="n">
         <v>9500</v>
       </c>
       <c r="Q326" t="n">
-        <v>494000</v>
+        <v>437000</v>
       </c>
     </row>
     <row r="327">
@@ -14382,22 +14382,22 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M327" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N327" t="n">
         <v>156</v>
       </c>
       <c r="O327" t="n">
-        <v>46800</v>
+        <v>31200</v>
       </c>
       <c r="P327" t="n">
         <v>195</v>
       </c>
       <c r="Q327" t="n">
-        <v>58500</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="328">
@@ -14515,22 +14515,22 @@
         <v>0</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M330" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N330" t="n">
         <v>10716.34</v>
       </c>
       <c r="O330" t="n">
-        <v>471518.96</v>
+        <v>460802.62</v>
       </c>
       <c r="P330" t="n">
         <v>39000</v>
       </c>
       <c r="Q330" t="n">
-        <v>1716000</v>
+        <v>1677000</v>
       </c>
     </row>
     <row r="331">
@@ -14728,22 +14728,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N335" t="n">
-        <v>3594.254124847</v>
+        <v>3594.2541140405</v>
       </c>
       <c r="O335" t="n">
-        <v>222843.755740514</v>
+        <v>219249.5009564705</v>
       </c>
       <c r="P335" t="n">
         <v>6500</v>
       </c>
       <c r="Q335" t="n">
-        <v>403000</v>
+        <v>396500</v>
       </c>
     </row>
     <row r="336">
@@ -14903,10 +14903,10 @@
         <v>240</v>
       </c>
       <c r="N339" t="n">
-        <v>3240.8500302572</v>
+        <v>3240.8500303951</v>
       </c>
       <c r="O339" t="n">
-        <v>777804.0072617281</v>
+        <v>777804.007294824</v>
       </c>
       <c r="P339" t="n">
         <v>5200</v>
@@ -15616,10 +15616,10 @@
         <v>427</v>
       </c>
       <c r="N355" t="n">
-        <v>3041.6600127551</v>
+        <v>3041.6600128617</v>
       </c>
       <c r="O355" t="n">
-        <v>1298788.825446428</v>
+        <v>1298788.825491946</v>
       </c>
       <c r="P355" t="n">
         <v>5500</v>
@@ -15703,10 +15703,10 @@
         <v>209</v>
       </c>
       <c r="N357" t="n">
-        <v>4372.2107877711</v>
+        <v>4372.2107879391</v>
       </c>
       <c r="O357" t="n">
-        <v>913792.0546441599</v>
+        <v>913792.0546792719</v>
       </c>
       <c r="P357" t="n">
         <v>7500</v>
@@ -15741,22 +15741,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M358" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="N358" t="n">
         <v>6441.03</v>
       </c>
       <c r="O358" t="n">
-        <v>534605.49</v>
+        <v>386461.8</v>
       </c>
       <c r="P358" t="n">
         <v>10500</v>
       </c>
       <c r="Q358" t="n">
-        <v>871500</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="359">
@@ -15793,10 +15793,10 @@
         <v>19</v>
       </c>
       <c r="N359" t="n">
-        <v>1592.5674</v>
+        <v>1592.5673455845</v>
       </c>
       <c r="O359" t="n">
-        <v>30258.7806</v>
+        <v>30258.7795661055</v>
       </c>
       <c r="P359" t="n">
         <v>3900</v>
@@ -16310,22 +16310,22 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N371" t="n">
         <v>6242.93</v>
       </c>
       <c r="O371" t="n">
-        <v>549377.8400000001</v>
+        <v>543134.91</v>
       </c>
       <c r="P371" t="n">
         <v>10400</v>
       </c>
       <c r="Q371" t="n">
-        <v>915200</v>
+        <v>904800</v>
       </c>
     </row>
     <row r="372">
@@ -16661,22 +16661,22 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M379" t="n">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="N379" t="n">
         <v>1343.77</v>
       </c>
       <c r="O379" t="n">
-        <v>237847.29</v>
+        <v>221722.05</v>
       </c>
       <c r="P379" t="n">
         <v>2500</v>
       </c>
       <c r="Q379" t="n">
-        <v>442500</v>
+        <v>412500</v>
       </c>
     </row>
     <row r="380">
@@ -17056,22 +17056,22 @@
         <v>0</v>
       </c>
       <c r="L388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M388" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N388" t="n">
         <v>16897</v>
       </c>
       <c r="O388" t="n">
-        <v>16897</v>
+        <v>0</v>
       </c>
       <c r="P388" t="n">
         <v>27900</v>
       </c>
       <c r="Q388" t="n">
-        <v>27900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -17422,22 +17422,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M396" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N396" t="n">
         <v>11921.4</v>
       </c>
       <c r="O396" t="n">
-        <v>1645153.2</v>
+        <v>1573624.8</v>
       </c>
       <c r="P396" t="n">
         <v>19900</v>
       </c>
       <c r="Q396" t="n">
-        <v>2746200</v>
+        <v>2626800</v>
       </c>
     </row>
     <row r="397">
@@ -17592,22 +17592,22 @@
         <v>0</v>
       </c>
       <c r="L400" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M400" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N400" t="n">
         <v>9678.9</v>
       </c>
       <c r="O400" t="n">
-        <v>348440.4</v>
+        <v>319403.7</v>
       </c>
       <c r="P400" t="n">
         <v>15500</v>
       </c>
       <c r="Q400" t="n">
-        <v>558000</v>
+        <v>511500</v>
       </c>
     </row>
     <row r="401">
@@ -17762,22 +17762,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M404" t="n">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="N404" t="n">
         <v>3751</v>
       </c>
       <c r="O404" t="n">
-        <v>3323386</v>
+        <v>3315884</v>
       </c>
       <c r="P404" t="n">
         <v>6400</v>
       </c>
       <c r="Q404" t="n">
-        <v>5670400</v>
+        <v>5657600</v>
       </c>
     </row>
     <row r="405">
@@ -17903,22 +17903,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M407" t="n">
-        <v>846</v>
+        <v>678</v>
       </c>
       <c r="N407" t="n">
-        <v>1630.9231730968</v>
+        <v>1630.9233118002</v>
       </c>
       <c r="O407" t="n">
-        <v>1379761.004439893</v>
+        <v>1105766.005400536</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
       </c>
       <c r="Q407" t="n">
-        <v>2115000</v>
+        <v>1695000</v>
       </c>
     </row>
     <row r="408">
@@ -18036,22 +18036,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M410" t="n">
-        <v>425</v>
+        <v>286</v>
       </c>
       <c r="N410" t="n">
-        <v>1690.6023498845</v>
+        <v>1690.6006518987</v>
       </c>
       <c r="O410" t="n">
-        <v>718505.9987009125</v>
+        <v>483511.7864430282</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
       </c>
       <c r="Q410" t="n">
-        <v>1232500</v>
+        <v>829400</v>
       </c>
     </row>
     <row r="411">
@@ -18082,22 +18082,22 @@
         <v>0</v>
       </c>
       <c r="L411" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="M411" t="n">
-        <v>2101</v>
+        <v>1756</v>
       </c>
       <c r="N411" t="n">
-        <v>1550.193183768</v>
+        <v>1550.1933219945</v>
       </c>
       <c r="O411" t="n">
-        <v>3256955.879096568</v>
+        <v>2722139.473422342</v>
       </c>
       <c r="P411" t="n">
         <v>2500</v>
       </c>
       <c r="Q411" t="n">
-        <v>5252500</v>
+        <v>4390000</v>
       </c>
     </row>
     <row r="412">
@@ -18134,10 +18134,10 @@
         <v>3</v>
       </c>
       <c r="N412" t="n">
-        <v>1579.3909343434</v>
+        <v>1579.3908883249</v>
       </c>
       <c r="O412" t="n">
-        <v>4738.1728030302</v>
+        <v>4738.1726649747</v>
       </c>
       <c r="P412" t="n">
         <v>2900</v>
@@ -18174,22 +18174,22 @@
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M413" t="n">
-        <v>1056</v>
+        <v>948</v>
       </c>
       <c r="N413" t="n">
-        <v>2403.5104597508</v>
+        <v>2403.5107961064</v>
       </c>
       <c r="O413" t="n">
-        <v>2538107.045496845</v>
+        <v>2278528.234708867</v>
       </c>
       <c r="P413" t="n">
         <v>3500</v>
       </c>
       <c r="Q413" t="n">
-        <v>3696000</v>
+        <v>3318000</v>
       </c>
     </row>
     <row r="414">
@@ -18220,22 +18220,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M414" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N414" t="n">
-        <v>2521.5426705653</v>
+        <v>2521.5415942029</v>
       </c>
       <c r="O414" t="n">
-        <v>42866.2253996101</v>
+        <v>0</v>
       </c>
       <c r="P414" t="n">
         <v>3900</v>
       </c>
       <c r="Q414" t="n">
-        <v>66300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
@@ -19495,22 +19495,22 @@
         <v>0</v>
       </c>
       <c r="L443" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M443" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N443" t="n">
         <v>10034.5</v>
       </c>
       <c r="O443" t="n">
-        <v>541863</v>
+        <v>421449</v>
       </c>
       <c r="P443" t="n">
         <v>12900</v>
       </c>
       <c r="Q443" t="n">
-        <v>696600</v>
+        <v>541800</v>
       </c>
     </row>
     <row r="444">
@@ -19928,22 +19928,22 @@
         <v>0</v>
       </c>
       <c r="L453" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M453" t="n">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="N453" t="n">
         <v>3253</v>
       </c>
       <c r="O453" t="n">
-        <v>406625</v>
+        <v>172409</v>
       </c>
       <c r="P453" t="n">
         <v>3900</v>
       </c>
       <c r="Q453" t="n">
-        <v>487500</v>
+        <v>206700</v>
       </c>
     </row>
     <row r="454">
@@ -21788,22 +21788,22 @@
         <v>0</v>
       </c>
       <c r="L497" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M497" t="n">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="N497" t="n">
         <v>2567</v>
       </c>
       <c r="O497" t="n">
-        <v>880481</v>
+        <v>849677</v>
       </c>
       <c r="P497" t="n">
         <v>4500</v>
       </c>
       <c r="Q497" t="n">
-        <v>1543500</v>
+        <v>1489500</v>
       </c>
     </row>
     <row r="498">
@@ -21911,22 +21911,22 @@
         <v>0</v>
       </c>
       <c r="L500" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M500" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N500" t="n">
         <v>6652</v>
       </c>
       <c r="O500" t="n">
-        <v>485596</v>
+        <v>458988</v>
       </c>
       <c r="P500" t="n">
         <v>5900</v>
       </c>
       <c r="Q500" t="n">
-        <v>430700</v>
+        <v>407100</v>
       </c>
     </row>
     <row r="501">
@@ -23380,10 +23380,10 @@
         <v>19</v>
       </c>
       <c r="N535" t="n">
-        <v>3731.0243377483</v>
+        <v>3731.0243521595</v>
       </c>
       <c r="O535" t="n">
-        <v>70889.4624172177</v>
+        <v>70889.46269103049</v>
       </c>
       <c r="P535" t="n">
         <v>5200</v>
@@ -23772,10 +23772,10 @@
         <v>280</v>
       </c>
       <c r="N544" t="n">
-        <v>4285.1952806653</v>
+        <v>4285.1953699789</v>
       </c>
       <c r="O544" t="n">
-        <v>1199854.678586284</v>
+        <v>1199854.703594092</v>
       </c>
       <c r="P544" t="n">
         <v>6900</v>
@@ -26267,22 +26267,22 @@
         <v>0</v>
       </c>
       <c r="L602" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M602" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="N602" t="n">
-        <v>1560.9994428152</v>
+        <v>1560.9995548961</v>
       </c>
       <c r="O602" t="n">
-        <v>177953.9364809328</v>
+        <v>140489.959940649</v>
       </c>
       <c r="P602" t="n">
         <v>2900</v>
       </c>
       <c r="Q602" t="n">
-        <v>330600</v>
+        <v>261000</v>
       </c>
     </row>
     <row r="603">
@@ -27913,10 +27913,10 @@
         <v>71</v>
       </c>
       <c r="N640" t="n">
-        <v>3113.8900262812</v>
+        <v>3113.8900265957</v>
       </c>
       <c r="O640" t="n">
-        <v>221086.1918659652</v>
+        <v>221086.1918882947</v>
       </c>
       <c r="P640" t="n">
         <v>5000</v>
@@ -27999,22 +27999,22 @@
         <v>0</v>
       </c>
       <c r="L642" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M642" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="N642" t="n">
         <v>4690.64</v>
       </c>
       <c r="O642" t="n">
-        <v>103194.08</v>
+        <v>23453.2</v>
       </c>
       <c r="P642" t="n">
         <v>7500</v>
       </c>
       <c r="Q642" t="n">
-        <v>165000</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="643">
@@ -28045,22 +28045,22 @@
         <v>0</v>
       </c>
       <c r="L643" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M643" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="N643" t="n">
         <v>5410.72</v>
       </c>
       <c r="O643" t="n">
-        <v>351696.8</v>
+        <v>319232.48</v>
       </c>
       <c r="P643" t="n">
         <v>8700</v>
       </c>
       <c r="Q643" t="n">
-        <v>565500</v>
+        <v>513300</v>
       </c>
     </row>
     <row r="644">
@@ -28229,22 +28229,22 @@
         <v>0</v>
       </c>
       <c r="L647" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M647" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N647" t="n">
         <v>3254.49</v>
       </c>
       <c r="O647" t="n">
-        <v>104143.68</v>
+        <v>84616.73999999999</v>
       </c>
       <c r="P647" t="n">
         <v>5200</v>
       </c>
       <c r="Q647" t="n">
-        <v>166400</v>
+        <v>135200</v>
       </c>
     </row>
     <row r="648">
@@ -28281,10 +28281,10 @@
         <v>21</v>
       </c>
       <c r="N648" t="n">
-        <v>5218.170521327</v>
+        <v>5218.1705238095</v>
       </c>
       <c r="O648" t="n">
-        <v>109581.580947867</v>
+        <v>109581.5809999995</v>
       </c>
       <c r="P648" t="n">
         <v>8500</v>
@@ -28327,10 +28327,10 @@
         <v>140</v>
       </c>
       <c r="N649" t="n">
-        <v>1595.0094476744</v>
+        <v>1595.0094378698</v>
       </c>
       <c r="O649" t="n">
-        <v>223301.322674416</v>
+        <v>223301.321301772</v>
       </c>
       <c r="P649" t="n">
         <v>2600</v>
@@ -28373,10 +28373,10 @@
         <v>81</v>
       </c>
       <c r="N650" t="n">
-        <v>3610.6500249688</v>
+        <v>3610.6500252207</v>
       </c>
       <c r="O650" t="n">
-        <v>292462.6520224728</v>
+        <v>292462.6520428767</v>
       </c>
       <c r="P650" t="n">
         <v>5800</v>
@@ -28413,22 +28413,22 @@
         <v>0</v>
       </c>
       <c r="L651" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M651" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="N651" t="n">
         <v>5194</v>
       </c>
       <c r="O651" t="n">
-        <v>394744</v>
+        <v>270088</v>
       </c>
       <c r="P651" t="n">
         <v>9000</v>
       </c>
       <c r="Q651" t="n">
-        <v>684000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="652">
@@ -28689,22 +28689,22 @@
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M657" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N657" t="n">
         <v>6058.52</v>
       </c>
       <c r="O657" t="n">
-        <v>357452.6800000001</v>
+        <v>302926</v>
       </c>
       <c r="P657" t="n">
         <v>9700</v>
       </c>
       <c r="Q657" t="n">
-        <v>572300</v>
+        <v>485000</v>
       </c>
     </row>
     <row r="658">
@@ -28781,22 +28781,22 @@
         <v>0</v>
       </c>
       <c r="L659" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M659" t="n">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="N659" t="n">
-        <v>1664.3590294957</v>
+        <v>1664.3585273632</v>
       </c>
       <c r="O659" t="n">
-        <v>664079.2527687843</v>
+        <v>629127.5233432896</v>
       </c>
       <c r="P659" t="n">
         <v>2900</v>
       </c>
       <c r="Q659" t="n">
-        <v>1157100</v>
+        <v>1096200</v>
       </c>
     </row>
     <row r="660">
@@ -29293,22 +29293,22 @@
         <v>0</v>
       </c>
       <c r="L670" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M670" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="N670" t="n">
         <v>3646</v>
       </c>
       <c r="O670" t="n">
-        <v>495856</v>
+        <v>466688</v>
       </c>
       <c r="P670" t="n">
         <v>6900</v>
       </c>
       <c r="Q670" t="n">
-        <v>938400</v>
+        <v>883200</v>
       </c>
     </row>
     <row r="671">
@@ -29431,22 +29431,22 @@
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M673" t="n">
-        <v>1508</v>
+        <v>1492</v>
       </c>
       <c r="N673" t="n">
-        <v>1778.4725680247</v>
+        <v>1778.4725740823</v>
       </c>
       <c r="O673" t="n">
-        <v>2681936.632581247</v>
+        <v>2653481.080530792</v>
       </c>
       <c r="P673" t="n">
         <v>4900</v>
       </c>
       <c r="Q673" t="n">
-        <v>7389200</v>
+        <v>7310800</v>
       </c>
     </row>
     <row r="674">
@@ -29477,22 +29477,22 @@
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M674" t="n">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="N674" t="n">
         <v>1548</v>
       </c>
       <c r="O674" t="n">
-        <v>445824</v>
+        <v>408672</v>
       </c>
       <c r="P674" t="n">
         <v>3900</v>
       </c>
       <c r="Q674" t="n">
-        <v>1123200</v>
+        <v>1029600</v>
       </c>
     </row>
     <row r="675">
@@ -29523,22 +29523,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M675" t="n">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="N675" t="n">
         <v>2325</v>
       </c>
       <c r="O675" t="n">
-        <v>1148550</v>
+        <v>1134600</v>
       </c>
       <c r="P675" t="n">
         <v>4900</v>
       </c>
       <c r="Q675" t="n">
-        <v>2420600</v>
+        <v>2391200</v>
       </c>
     </row>
     <row r="676">
@@ -31645,22 +31645,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M721" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N721" t="n">
         <v>8858.16</v>
       </c>
       <c r="O721" t="n">
-        <v>3242086.56</v>
+        <v>3224370.24</v>
       </c>
       <c r="P721" t="n">
         <v>15500</v>
       </c>
       <c r="Q721" t="n">
-        <v>5673000</v>
+        <v>5642000</v>
       </c>
     </row>
     <row r="722">
@@ -33121,10 +33121,10 @@
         <v>18</v>
       </c>
       <c r="N753" t="n">
-        <v>4907.8219751166</v>
+        <v>4907.8219812793</v>
       </c>
       <c r="O753" t="n">
-        <v>88340.7955520988</v>
+        <v>88340.79566302741</v>
       </c>
       <c r="P753" t="n">
         <v>8200</v>
@@ -34398,22 +34398,22 @@
         <v>0</v>
       </c>
       <c r="L781" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M781" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="N781" t="n">
         <v>7562</v>
       </c>
       <c r="O781" t="n">
-        <v>446158</v>
+        <v>393224</v>
       </c>
       <c r="P781" t="n">
         <v>12900</v>
       </c>
       <c r="Q781" t="n">
-        <v>761100</v>
+        <v>670800</v>
       </c>
     </row>
     <row r="782">
@@ -34582,22 +34582,22 @@
         <v>0</v>
       </c>
       <c r="L785" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M785" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N785" t="n">
         <v>5682</v>
       </c>
       <c r="O785" t="n">
-        <v>1250040</v>
+        <v>1238676</v>
       </c>
       <c r="P785" t="n">
         <v>9900</v>
       </c>
       <c r="Q785" t="n">
-        <v>2178000</v>
+        <v>2158200</v>
       </c>
     </row>
     <row r="786">
@@ -36009,22 +36009,22 @@
         <v>0</v>
       </c>
       <c r="L816" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M816" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N816" t="n">
         <v>16282</v>
       </c>
       <c r="O816" t="n">
-        <v>309358</v>
+        <v>260512</v>
       </c>
       <c r="P816" t="n">
         <v>27900</v>
       </c>
       <c r="Q816" t="n">
-        <v>530100</v>
+        <v>446400</v>
       </c>
     </row>
     <row r="817">
@@ -36754,10 +36754,10 @@
         <v>598</v>
       </c>
       <c r="N832" t="n">
-        <v>1516.0388102832</v>
+        <v>1516.0388052024</v>
       </c>
       <c r="O832" t="n">
-        <v>906591.2085493536</v>
+        <v>906591.2055110352</v>
       </c>
       <c r="P832" t="n">
         <v>2300</v>
@@ -36794,22 +36794,22 @@
         <v>0</v>
       </c>
       <c r="L833" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M833" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="N833" t="n">
-        <v>4248.635</v>
+        <v>4248.6401470588</v>
       </c>
       <c r="O833" t="n">
-        <v>433360.77</v>
+        <v>348388.4920588216</v>
       </c>
       <c r="P833" t="n">
         <v>5900</v>
       </c>
       <c r="Q833" t="n">
-        <v>601800</v>
+        <v>483800</v>
       </c>
     </row>
     <row r="834">
@@ -36936,10 +36936,10 @@
         <v>190</v>
       </c>
       <c r="N836" t="n">
-        <v>1907.3940437158</v>
+        <v>1907.394010989</v>
       </c>
       <c r="O836" t="n">
-        <v>362404.868306002</v>
+        <v>362404.86208791</v>
       </c>
       <c r="P836" t="n">
         <v>2500</v>
@@ -36982,10 +36982,10 @@
         <v>189</v>
       </c>
       <c r="N837" t="n">
-        <v>1771.0911179361</v>
+        <v>1771.0908132147</v>
       </c>
       <c r="O837" t="n">
-        <v>334736.2212899229</v>
+        <v>334736.1636975783</v>
       </c>
       <c r="P837" t="n">
         <v>2500</v>
@@ -37028,10 +37028,10 @@
         <v>418</v>
       </c>
       <c r="N838" t="n">
-        <v>2079.3841813438</v>
+        <v>2079.3841354372</v>
       </c>
       <c r="O838" t="n">
-        <v>869182.5878017084</v>
+        <v>869182.5686127496</v>
       </c>
       <c r="P838" t="n">
         <v>2900</v>
@@ -37074,10 +37074,10 @@
         <v>430</v>
       </c>
       <c r="N839" t="n">
-        <v>1803.0151724138</v>
+        <v>1803.0152234206</v>
       </c>
       <c r="O839" t="n">
-        <v>775296.524137934</v>
+        <v>775296.546070858</v>
       </c>
       <c r="P839" t="n">
         <v>2500</v>
@@ -37120,10 +37120,10 @@
         <v>71</v>
       </c>
       <c r="N840" t="n">
-        <v>3306.5953488372</v>
+        <v>3306.5953246753</v>
       </c>
       <c r="O840" t="n">
-        <v>234768.2697674412</v>
+        <v>234768.2680519463</v>
       </c>
       <c r="P840" t="n">
         <v>4900</v>
@@ -37166,10 +37166,10 @@
         <v>440</v>
       </c>
       <c r="N841" t="n">
-        <v>2122.1640036787</v>
+        <v>2122.164</v>
       </c>
       <c r="O841" t="n">
-        <v>933752.161618628</v>
+        <v>933752.1600000001</v>
       </c>
       <c r="P841" t="n">
         <v>2900</v>
@@ -37212,10 +37212,10 @@
         <v>33</v>
       </c>
       <c r="N842" t="n">
-        <v>2108.7900518135</v>
+        <v>2108.7900692042</v>
       </c>
       <c r="O842" t="n">
-        <v>69590.07170984551</v>
+        <v>69590.0722837386</v>
       </c>
       <c r="P842" t="n">
         <v>2900</v>
@@ -37258,10 +37258,10 @@
         <v>893</v>
       </c>
       <c r="N843" t="n">
-        <v>2056.0837188071</v>
+        <v>2056.0837111517</v>
       </c>
       <c r="O843" t="n">
-        <v>1836082.76089474</v>
+        <v>1836082.754058468</v>
       </c>
       <c r="P843" t="n">
         <v>2900</v>
@@ -37350,10 +37350,10 @@
         <v>455</v>
       </c>
       <c r="N845" t="n">
-        <v>1655.9310223953</v>
+        <v>1655.9309931618</v>
       </c>
       <c r="O845" t="n">
-        <v>753448.6151898615</v>
+        <v>753448.601888619</v>
       </c>
       <c r="P845" t="n">
         <v>2500</v>
@@ -37531,22 +37531,22 @@
         <v>0</v>
       </c>
       <c r="L849" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M849" t="n">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="N849" t="n">
         <v>1871</v>
       </c>
       <c r="O849" t="n">
-        <v>518267</v>
+        <v>473363</v>
       </c>
       <c r="P849" t="n">
         <v>3900</v>
       </c>
       <c r="Q849" t="n">
-        <v>1080300</v>
+        <v>986700</v>
       </c>
     </row>
     <row r="850">
@@ -37715,22 +37715,22 @@
         <v>0</v>
       </c>
       <c r="L853" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M853" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="N853" t="n">
-        <v>1592.2756948933</v>
+        <v>1592.27610957</v>
       </c>
       <c r="O853" t="n">
-        <v>170373.4993535831</v>
+        <v>141712.57375173</v>
       </c>
       <c r="P853" t="n">
         <v>2500</v>
       </c>
       <c r="Q853" t="n">
-        <v>267500</v>
+        <v>222500</v>
       </c>
     </row>
     <row r="854">
@@ -37759,22 +37759,22 @@
         <v>0</v>
       </c>
       <c r="L854" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M854" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N854" t="n">
         <v>5347.73</v>
       </c>
       <c r="O854" t="n">
-        <v>26738.65</v>
+        <v>10695.46</v>
       </c>
       <c r="P854" t="n">
         <v>9500</v>
       </c>
       <c r="Q854" t="n">
-        <v>47500</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="855">
@@ -37802,25 +37802,25 @@
         <v>61</v>
       </c>
       <c r="K855" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L855" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M855" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N855" t="n">
-        <v>2311.9246983547</v>
+        <v>2311.9221535181</v>
       </c>
       <c r="O855" t="n">
-        <v>141027.4065996367</v>
+        <v>0</v>
       </c>
       <c r="P855" t="n">
         <v>3500</v>
       </c>
       <c r="Q855" t="n">
-        <v>213500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="856">
@@ -37851,22 +37851,22 @@
         <v>0</v>
       </c>
       <c r="L856" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M856" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="N856" t="n">
-        <v>1906.18625</v>
+        <v>1906.1853846154</v>
       </c>
       <c r="O856" t="n">
-        <v>116277.36125</v>
+        <v>3812.3707692308</v>
       </c>
       <c r="P856" t="n">
         <v>2900</v>
       </c>
       <c r="Q856" t="n">
-        <v>176900</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="857">
@@ -37949,10 +37949,10 @@
         <v>75</v>
       </c>
       <c r="N858" t="n">
-        <v>2546.985</v>
+        <v>2546.9846915888</v>
       </c>
       <c r="O858" t="n">
-        <v>191023.875</v>
+        <v>191023.85186916</v>
       </c>
       <c r="P858" t="n">
         <v>3900</v>
@@ -38081,22 +38081,22 @@
         <v>0</v>
       </c>
       <c r="L861" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M861" t="n">
-        <v>579</v>
+        <v>531</v>
       </c>
       <c r="N861" t="n">
         <v>1801</v>
       </c>
       <c r="O861" t="n">
-        <v>1042779</v>
+        <v>956331</v>
       </c>
       <c r="P861" t="n">
         <v>2900</v>
       </c>
       <c r="Q861" t="n">
-        <v>1679100</v>
+        <v>1539900</v>
       </c>
     </row>
     <row r="862">
@@ -38131,10 +38131,10 @@
         <v>97</v>
       </c>
       <c r="N862" t="n">
-        <v>692.15209736124</v>
+        <v>692.15211662075</v>
       </c>
       <c r="O862" t="n">
-        <v>67138.75344404028</v>
+        <v>67138.75531221276</v>
       </c>
       <c r="P862" t="n">
         <v>1200</v>
@@ -39286,10 +39286,10 @@
         <v>384</v>
       </c>
       <c r="N887" t="n">
-        <v>1530.4499206034</v>
+        <v>1530.4499195171</v>
       </c>
       <c r="O887" t="n">
-        <v>587692.7695117056</v>
+        <v>587692.7690945663</v>
       </c>
       <c r="P887" t="n">
         <v>2600</v>
@@ -39732,22 +39732,22 @@
         <v>0</v>
       </c>
       <c r="L897" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M897" t="n">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="N897" t="n">
         <v>1828.64</v>
       </c>
       <c r="O897" t="n">
-        <v>1276390.72</v>
+        <v>1267247.52</v>
       </c>
       <c r="P897" t="n">
         <v>2000</v>
       </c>
       <c r="Q897" t="n">
-        <v>1396000</v>
+        <v>1386000</v>
       </c>
     </row>
     <row r="898">
@@ -39787,10 +39787,10 @@
         <v>19</v>
       </c>
       <c r="N898" t="n">
-        <v>2270.3211494253</v>
+        <v>2270.3211627907</v>
       </c>
       <c r="O898" t="n">
-        <v>43136.1018390807</v>
+        <v>43136.1020930233</v>
       </c>
       <c r="P898" t="n">
         <v>3900</v>
@@ -41114,22 +41114,22 @@
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M928" t="n">
-        <v>3347</v>
+        <v>3323</v>
       </c>
       <c r="N928" t="n">
-        <v>517.28824762181</v>
+        <v>517.28836312001</v>
       </c>
       <c r="O928" t="n">
-        <v>1731363.764790198</v>
+        <v>1718949.230647793</v>
       </c>
       <c r="P928" t="n">
         <v>900</v>
       </c>
       <c r="Q928" t="n">
-        <v>3012300</v>
+        <v>2990700</v>
       </c>
     </row>
     <row r="929">
@@ -41340,22 +41340,22 @@
         <v>0</v>
       </c>
       <c r="L933" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M933" t="n">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="N933" t="n">
-        <v>3110.8426932617</v>
+        <v>3110.8426185007</v>
       </c>
       <c r="O933" t="n">
-        <v>1822953.818251356</v>
+        <v>1804288.718730406</v>
       </c>
       <c r="P933" t="n">
         <v>4500</v>
       </c>
       <c r="Q933" t="n">
-        <v>2637000</v>
+        <v>2610000</v>
       </c>
     </row>
     <row r="934">
@@ -41562,22 +41562,22 @@
         <v>0</v>
       </c>
       <c r="L938" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M938" t="n">
-        <v>1034</v>
+        <v>842</v>
       </c>
       <c r="N938" t="n">
-        <v>703.7953201758</v>
+        <v>703.79529676406</v>
       </c>
       <c r="O938" t="n">
-        <v>727724.3610617772</v>
+        <v>592595.6398753385</v>
       </c>
       <c r="P938" t="n">
         <v>900</v>
       </c>
       <c r="Q938" t="n">
-        <v>930600</v>
+        <v>757800</v>
       </c>
     </row>
     <row r="939">
@@ -42056,22 +42056,22 @@
         <v>0</v>
       </c>
       <c r="L949" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M949" t="n">
-        <v>207</v>
+        <v>63</v>
       </c>
       <c r="N949" t="n">
         <v>1300</v>
       </c>
       <c r="O949" t="n">
-        <v>269100</v>
+        <v>81900</v>
       </c>
       <c r="P949" t="n">
         <v>2200</v>
       </c>
       <c r="Q949" t="n">
-        <v>455400</v>
+        <v>138600</v>
       </c>
     </row>
     <row r="950">
@@ -42144,22 +42144,22 @@
         <v>0</v>
       </c>
       <c r="L951" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M951" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N951" t="n">
         <v>2525.02</v>
       </c>
       <c r="O951" t="n">
-        <v>58075.46</v>
+        <v>45450.36</v>
       </c>
       <c r="P951" t="n">
         <v>3000</v>
       </c>
       <c r="Q951" t="n">
-        <v>69000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="952">
@@ -42319,10 +42319,10 @@
         <v>259</v>
       </c>
       <c r="N955" t="n">
-        <v>2077.4945784884</v>
+        <v>2077.4945851528</v>
       </c>
       <c r="O955" t="n">
-        <v>538071.0958284956</v>
+        <v>538071.0975545752</v>
       </c>
       <c r="P955" t="n">
         <v>2900</v>
@@ -42579,10 +42579,10 @@
         <v>74</v>
       </c>
       <c r="N961" t="n">
-        <v>1595.5155292429</v>
+        <v>1595.5153131828</v>
       </c>
       <c r="O961" t="n">
-        <v>118068.1491639746</v>
+        <v>118068.1331755272</v>
       </c>
       <c r="P961" t="n">
         <v>2500</v>
@@ -43104,10 +43104,10 @@
         <v>3</v>
       </c>
       <c r="N972" t="n">
-        <v>2098.4049147727</v>
+        <v>2098.4049570201</v>
       </c>
       <c r="O972" t="n">
-        <v>6295.2147443181</v>
+        <v>6295.2148710603</v>
       </c>
       <c r="P972" t="n">
         <v>9500</v>
@@ -43339,10 +43339,10 @@
         <v>1291</v>
       </c>
       <c r="N977" t="n">
-        <v>3063.6218939394</v>
+        <v>3063.6218958544</v>
       </c>
       <c r="O977" t="n">
-        <v>3955135.865075765</v>
+        <v>3955135.86754803</v>
       </c>
       <c r="P977" t="n">
         <v>3500</v>
@@ -43990,10 +43990,10 @@
         <v>1</v>
       </c>
       <c r="N991" t="n">
-        <v>1783.7988843537</v>
+        <v>1783.7988833409</v>
       </c>
       <c r="O991" t="n">
-        <v>1783.7988843537</v>
+        <v>1783.7988833409</v>
       </c>
       <c r="P991" t="n">
         <v>1500</v>
@@ -44449,22 +44449,22 @@
         <v>0</v>
       </c>
       <c r="L1001" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1001" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N1001" t="n">
         <v>3436.36</v>
       </c>
       <c r="O1001" t="n">
-        <v>13745.44</v>
+        <v>3436.36</v>
       </c>
       <c r="P1001" t="n">
         <v>2400</v>
       </c>
       <c r="Q1001" t="n">
-        <v>9600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="1002">
@@ -44689,10 +44689,10 @@
         <v>2</v>
       </c>
       <c r="N1006" t="n">
-        <v>2000.6660784314</v>
+        <v>2000.6711643836</v>
       </c>
       <c r="O1006" t="n">
-        <v>4001.3321568628</v>
+        <v>4001.3423287672</v>
       </c>
       <c r="P1006" t="n">
         <v>2000</v>
@@ -45062,22 +45062,22 @@
         <v>0</v>
       </c>
       <c r="L1014" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1014" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="N1014" t="n">
-        <v>7046.9398298958</v>
+        <v>7046.9398286204</v>
       </c>
       <c r="O1014" t="n">
-        <v>1515092.063427597</v>
+        <v>1345965.507266496</v>
       </c>
       <c r="P1014" t="n">
         <v>9900</v>
       </c>
       <c r="Q1014" t="n">
-        <v>2128500</v>
+        <v>1890900</v>
       </c>
     </row>
     <row r="1015">
@@ -45108,22 +45108,22 @@
         <v>0</v>
       </c>
       <c r="L1015" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1015" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N1015" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1015" t="n">
-        <v>1411631.26</v>
+        <v>1338615.85</v>
       </c>
       <c r="P1015" t="n">
         <v>27900</v>
       </c>
       <c r="Q1015" t="n">
-        <v>1618200</v>
+        <v>1534500</v>
       </c>
     </row>
     <row r="1016">
@@ -46673,22 +46673,22 @@
         <v>0</v>
       </c>
       <c r="L1050" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1050" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N1050" t="n">
-        <v>5577.2680733945</v>
+        <v>5577.2680465116</v>
       </c>
       <c r="O1050" t="n">
-        <v>317904.2801834865</v>
+        <v>284440.6703720916</v>
       </c>
       <c r="P1050" t="n">
         <v>6500</v>
       </c>
       <c r="Q1050" t="n">
-        <v>370500</v>
+        <v>331500</v>
       </c>
     </row>
     <row r="1051">
@@ -46723,10 +46723,10 @@
         <v>42</v>
       </c>
       <c r="N1051" t="n">
-        <v>6243.3530555556</v>
+        <v>6243.3531428571</v>
       </c>
       <c r="O1051" t="n">
-        <v>262220.8283333352</v>
+        <v>262220.8319999982</v>
       </c>
       <c r="P1051" t="n">
         <v>9900</v>
@@ -47625,22 +47625,22 @@
         <v>0</v>
       </c>
       <c r="L1072" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M1072" t="n">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="N1072" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1072" t="n">
-        <v>1336398</v>
+        <v>1279123.8</v>
       </c>
       <c r="P1072" t="n">
         <v>5100</v>
       </c>
       <c r="Q1072" t="n">
-        <v>2142000</v>
+        <v>2050200</v>
       </c>
     </row>
     <row r="1073">
@@ -48779,22 +48779,22 @@
         <v>0</v>
       </c>
       <c r="L1099" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1099" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N1099" t="n">
         <v>5077</v>
       </c>
       <c r="O1099" t="n">
-        <v>690472</v>
+        <v>670164</v>
       </c>
       <c r="P1099" t="n">
         <v>8500</v>
       </c>
       <c r="Q1099" t="n">
-        <v>1156000</v>
+        <v>1122000</v>
       </c>
     </row>
     <row r="1100">
@@ -48953,22 +48953,22 @@
         <v>0</v>
       </c>
       <c r="L1103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1103" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="N1103" t="n">
-        <v>4985.4047058824</v>
+        <v>4985.4047808765</v>
       </c>
       <c r="O1103" t="n">
-        <v>513496.6847058872</v>
+        <v>493555.0733067735</v>
       </c>
       <c r="P1103" t="n">
         <v>7900</v>
       </c>
       <c r="Q1103" t="n">
-        <v>813700</v>
+        <v>782100</v>
       </c>
     </row>
     <row r="1104">
@@ -49725,22 +49725,22 @@
         <v>0</v>
       </c>
       <c r="L1120" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M1120" t="n">
-        <v>375</v>
+        <v>327</v>
       </c>
       <c r="N1120" t="n">
         <v>7480</v>
       </c>
       <c r="O1120" t="n">
-        <v>2805000</v>
+        <v>2445960</v>
       </c>
       <c r="P1120" t="n">
         <v>9500</v>
       </c>
       <c r="Q1120" t="n">
-        <v>3562500</v>
+        <v>3106500</v>
       </c>
     </row>
     <row r="1121">
@@ -49857,28 +49857,28 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>583</v>
+        <v>703</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M1123" t="n">
-        <v>583</v>
+        <v>343</v>
       </c>
       <c r="N1123" t="n">
         <v>9240</v>
       </c>
       <c r="O1123" t="n">
-        <v>5386920</v>
+        <v>3169320</v>
       </c>
       <c r="P1123" t="n">
         <v>11500</v>
       </c>
       <c r="Q1123" t="n">
-        <v>6704500</v>
+        <v>3944500</v>
       </c>
     </row>
     <row r="1124">
@@ -52327,22 +52327,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1177" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N1177" t="n">
         <v>4550</v>
       </c>
       <c r="O1177" t="n">
-        <v>1428700</v>
+        <v>1410500</v>
       </c>
       <c r="P1177" t="n">
         <v>5500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>1727000</v>
+        <v>1705000</v>
       </c>
     </row>
     <row r="1178">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -547,25 +547,25 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N4" t="n">
         <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>189000</v>
+        <v>351000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
       </c>
       <c r="Q4" t="n">
-        <v>140000</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="5">
@@ -1345,25 +1345,25 @@
         <v>192</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="N23" t="n">
-        <v>1811.3053012048</v>
+        <v>1811.3053333333</v>
       </c>
       <c r="O23" t="n">
-        <v>347770.6178313215</v>
+        <v>673805.5839999876</v>
       </c>
       <c r="P23" t="n">
         <v>2600</v>
       </c>
       <c r="Q23" t="n">
-        <v>499200</v>
+        <v>967200</v>
       </c>
     </row>
     <row r="24">
@@ -1819,22 +1819,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N35" t="n">
         <v>37131</v>
       </c>
       <c r="O35" t="n">
-        <v>668358</v>
+        <v>594096</v>
       </c>
       <c r="P35" t="n">
         <v>54600</v>
       </c>
       <c r="Q35" t="n">
-        <v>982800</v>
+        <v>873600</v>
       </c>
     </row>
     <row r="36">
@@ -3483,10 +3483,10 @@
         <v>167</v>
       </c>
       <c r="N76" t="n">
-        <v>3716.3301923077</v>
+        <v>3716.3301935484</v>
       </c>
       <c r="O76" t="n">
-        <v>620627.142115386</v>
+        <v>620627.1423225828</v>
       </c>
       <c r="P76" t="n">
         <v>9500</v>
@@ -4770,10 +4770,10 @@
         <v>10</v>
       </c>
       <c r="N106" t="n">
-        <v>30708.862857143</v>
+        <v>30708.856153846</v>
       </c>
       <c r="O106" t="n">
-        <v>307088.62857143</v>
+        <v>307088.56153846</v>
       </c>
       <c r="P106" t="n">
         <v>53500</v>
@@ -5065,22 +5065,22 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M113" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N113" t="n">
         <v>36762.36</v>
       </c>
       <c r="O113" t="n">
-        <v>735247.2</v>
+        <v>624960.12</v>
       </c>
       <c r="P113" t="n">
         <v>57100</v>
       </c>
       <c r="Q113" t="n">
-        <v>1142000</v>
+        <v>970700</v>
       </c>
     </row>
     <row r="114">
@@ -5207,10 +5207,10 @@
         <v>11</v>
       </c>
       <c r="N116" t="n">
-        <v>30238.812535211</v>
+        <v>30238.812571429</v>
       </c>
       <c r="O116" t="n">
-        <v>332626.937887321</v>
+        <v>332626.938285719</v>
       </c>
       <c r="P116" t="n">
         <v>51100</v>
@@ -5287,22 +5287,22 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M118" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="N118" t="n">
-        <v>7407.7300526316</v>
+        <v>7407.7300533333</v>
       </c>
       <c r="O118" t="n">
-        <v>659287.9746842125</v>
+        <v>622249.3244799972</v>
       </c>
       <c r="P118" t="n">
         <v>10900</v>
       </c>
       <c r="Q118" t="n">
-        <v>970100</v>
+        <v>915600</v>
       </c>
     </row>
     <row r="119">
@@ -5787,10 +5787,10 @@
         <v>16</v>
       </c>
       <c r="N130" t="n">
-        <v>36574.852142857</v>
+        <v>36574.852195122</v>
       </c>
       <c r="O130" t="n">
-        <v>585197.634285712</v>
+        <v>585197.635121952</v>
       </c>
       <c r="P130" t="n">
         <v>65900</v>
@@ -6194,10 +6194,10 @@
         <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>141416.88454545</v>
+        <v>141416.88456026</v>
       </c>
       <c r="O139" t="n">
-        <v>141416.88454545</v>
+        <v>141416.88456026</v>
       </c>
       <c r="P139" t="n">
         <v>251900</v>
@@ -8223,22 +8223,22 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M186" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="N186" t="n">
         <v>3865.67</v>
       </c>
       <c r="O186" t="n">
-        <v>707417.61</v>
+        <v>684223.59</v>
       </c>
       <c r="P186" t="n">
         <v>5500</v>
       </c>
       <c r="Q186" t="n">
-        <v>1006500</v>
+        <v>973500</v>
       </c>
     </row>
     <row r="187">
@@ -9096,22 +9096,22 @@
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M206" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>4333.6046666667</v>
+        <v>4333.6116666667</v>
       </c>
       <c r="O206" t="n">
-        <v>39002.4420000003</v>
+        <v>0</v>
       </c>
       <c r="P206" t="n">
         <v>7500</v>
       </c>
       <c r="Q206" t="n">
-        <v>67500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -9756,22 +9756,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M221" t="n">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="N221" t="n">
-        <v>1950.2147103275</v>
+        <v>1950.21469429</v>
       </c>
       <c r="O221" t="n">
-        <v>571412.9101259575</v>
+        <v>559711.61726123</v>
       </c>
       <c r="P221" t="n">
         <v>2900</v>
       </c>
       <c r="Q221" t="n">
-        <v>849700</v>
+        <v>832300</v>
       </c>
     </row>
     <row r="222">
@@ -9920,22 +9920,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M225" t="n">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="N225" t="n">
         <v>1726.32</v>
       </c>
       <c r="O225" t="n">
-        <v>3083207.52</v>
+        <v>3057312.72</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
       </c>
       <c r="Q225" t="n">
-        <v>2679000</v>
+        <v>2656500</v>
       </c>
     </row>
     <row r="226">
@@ -10477,10 +10477,10 @@
         <v>606</v>
       </c>
       <c r="N238" t="n">
-        <v>1098.0561100153</v>
+        <v>1098.0566124294</v>
       </c>
       <c r="O238" t="n">
-        <v>665422.0026692718</v>
+        <v>665422.3071322164</v>
       </c>
       <c r="P238" t="n">
         <v>1500</v>
@@ -10605,10 +10605,10 @@
         <v>15</v>
       </c>
       <c r="N241" t="n">
-        <v>21084.771458886</v>
+        <v>21084.771462766</v>
       </c>
       <c r="O241" t="n">
-        <v>316271.57188329</v>
+        <v>316271.57194149</v>
       </c>
       <c r="P241" t="n">
         <v>30000</v>
@@ -10687,10 +10687,10 @@
         <v>43</v>
       </c>
       <c r="N243" t="n">
-        <v>31233.611793893</v>
+        <v>31233.611800766</v>
       </c>
       <c r="O243" t="n">
-        <v>1343045.307137399</v>
+        <v>1343045.307432938</v>
       </c>
       <c r="P243" t="n">
         <v>45500</v>
@@ -11140,22 +11140,22 @@
         <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M254" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="N254" t="n">
         <v>2613</v>
       </c>
       <c r="O254" t="n">
-        <v>410241</v>
+        <v>384111</v>
       </c>
       <c r="P254" t="n">
         <v>5100</v>
       </c>
       <c r="Q254" t="n">
-        <v>800700</v>
+        <v>749700</v>
       </c>
     </row>
     <row r="255">
@@ -12238,10 +12238,10 @@
         <v>247</v>
       </c>
       <c r="N279" t="n">
-        <v>2582.2559749444</v>
+        <v>2582.255965161</v>
       </c>
       <c r="O279" t="n">
-        <v>637817.2258112668</v>
+        <v>637817.223394767</v>
       </c>
       <c r="P279" t="n">
         <v>4500</v>
@@ -12370,22 +12370,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M282" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N282" t="n">
         <v>5182.57</v>
       </c>
       <c r="O282" t="n">
-        <v>352414.76</v>
+        <v>342049.62</v>
       </c>
       <c r="P282" t="n">
         <v>6500</v>
       </c>
       <c r="Q282" t="n">
-        <v>442000</v>
+        <v>429000</v>
       </c>
     </row>
     <row r="283">
@@ -12626,22 +12626,22 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M288" t="n">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="N288" t="n">
-        <v>3158.8608230874</v>
+        <v>3158.86082365</v>
       </c>
       <c r="O288" t="n">
-        <v>2321762.704969239</v>
+        <v>2277538.65385165</v>
       </c>
       <c r="P288" t="n">
         <v>5600</v>
       </c>
       <c r="Q288" t="n">
-        <v>4116000</v>
+        <v>4037600</v>
       </c>
     </row>
     <row r="289">
@@ -12672,22 +12672,22 @@
         <v>0</v>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M289" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="N289" t="n">
         <v>1903</v>
       </c>
       <c r="O289" t="n">
-        <v>317801</v>
+        <v>283547</v>
       </c>
       <c r="P289" t="n">
         <v>3200</v>
       </c>
       <c r="Q289" t="n">
-        <v>534400</v>
+        <v>476800</v>
       </c>
     </row>
     <row r="290">
@@ -12718,22 +12718,22 @@
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M290" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N290" t="n">
-        <v>3841.6247414634</v>
+        <v>3841.6247693817</v>
       </c>
       <c r="O290" t="n">
-        <v>69149.24534634119</v>
+        <v>46099.4972325804</v>
       </c>
       <c r="P290" t="n">
         <v>6900</v>
       </c>
       <c r="Q290" t="n">
-        <v>124200</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="291">
@@ -12764,22 +12764,22 @@
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M291" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="N291" t="n">
         <v>5081</v>
       </c>
       <c r="O291" t="n">
-        <v>386156</v>
+        <v>223564</v>
       </c>
       <c r="P291" t="n">
         <v>8200</v>
       </c>
       <c r="Q291" t="n">
-        <v>623200</v>
+        <v>360800</v>
       </c>
     </row>
     <row r="292">
@@ -12854,22 +12854,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M293" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="N293" t="n">
-        <v>3230.0675874126</v>
+        <v>3230.0675313059</v>
       </c>
       <c r="O293" t="n">
-        <v>355307.434615386</v>
+        <v>335927.0232558136</v>
       </c>
       <c r="P293" t="n">
         <v>6200</v>
       </c>
       <c r="Q293" t="n">
-        <v>682000</v>
+        <v>644800</v>
       </c>
     </row>
     <row r="294">
@@ -12941,22 +12941,22 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M295" t="n">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="N295" t="n">
         <v>1480</v>
       </c>
       <c r="O295" t="n">
-        <v>1352720</v>
+        <v>1343840</v>
       </c>
       <c r="P295" t="n">
         <v>2600</v>
       </c>
       <c r="Q295" t="n">
-        <v>2376400</v>
+        <v>2360800</v>
       </c>
     </row>
     <row r="296">
@@ -13085,10 +13085,10 @@
         <v>109</v>
       </c>
       <c r="N298" t="n">
-        <v>2694.8233333333</v>
+        <v>2694.8232839963</v>
       </c>
       <c r="O298" t="n">
-        <v>293735.7433333297</v>
+        <v>293735.7379555966</v>
       </c>
       <c r="P298" t="n">
         <v>4900</v>
@@ -13120,22 +13120,22 @@
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M299" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N299" t="n">
         <v>2742</v>
       </c>
       <c r="O299" t="n">
-        <v>16452</v>
+        <v>13710</v>
       </c>
       <c r="P299" t="n">
         <v>3500</v>
       </c>
       <c r="Q299" t="n">
-        <v>21000</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="300">
@@ -13258,22 +13258,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M302" t="n">
-        <v>5195</v>
+        <v>4985</v>
       </c>
       <c r="N302" t="n">
         <v>156.25</v>
       </c>
       <c r="O302" t="n">
-        <v>811718.75</v>
+        <v>778906.25</v>
       </c>
       <c r="P302" t="n">
         <v>250</v>
       </c>
       <c r="Q302" t="n">
-        <v>1298750</v>
+        <v>1246250</v>
       </c>
     </row>
     <row r="303">
@@ -13541,10 +13541,10 @@
         <v>299</v>
       </c>
       <c r="N308" t="n">
-        <v>3795.7100070822</v>
+        <v>3795.7100070872</v>
       </c>
       <c r="O308" t="n">
-        <v>1134917.292117578</v>
+        <v>1134917.292119073</v>
       </c>
       <c r="P308" t="n">
         <v>6200</v>
@@ -13668,22 +13668,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M311" t="n">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="N311" t="n">
         <v>4357.55</v>
       </c>
       <c r="O311" t="n">
-        <v>1154750.75</v>
+        <v>1111175.25</v>
       </c>
       <c r="P311" t="n">
         <v>7500</v>
       </c>
       <c r="Q311" t="n">
-        <v>1987500</v>
+        <v>1912500</v>
       </c>
     </row>
     <row r="312">
@@ -13801,22 +13801,22 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M314" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N314" t="n">
-        <v>4890.9300467563</v>
+        <v>4890.9300468384</v>
       </c>
       <c r="O314" t="n">
-        <v>215200.9220572772</v>
+        <v>205419.0619672128</v>
       </c>
       <c r="P314" t="n">
         <v>8200</v>
       </c>
       <c r="Q314" t="n">
-        <v>360800</v>
+        <v>344400</v>
       </c>
     </row>
     <row r="315">
@@ -13942,22 +13942,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M317" t="n">
-        <v>892</v>
+        <v>834</v>
       </c>
       <c r="N317" t="n">
         <v>3472</v>
       </c>
       <c r="O317" t="n">
-        <v>3097024</v>
+        <v>2895648</v>
       </c>
       <c r="P317" t="n">
         <v>4800</v>
       </c>
       <c r="Q317" t="n">
-        <v>4281600</v>
+        <v>4003200</v>
       </c>
     </row>
     <row r="318">
@@ -13988,22 +13988,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M318" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N318" t="n">
         <v>5888</v>
       </c>
       <c r="O318" t="n">
-        <v>241408</v>
+        <v>223744</v>
       </c>
       <c r="P318" t="n">
         <v>9500</v>
       </c>
       <c r="Q318" t="n">
-        <v>389500</v>
+        <v>361000</v>
       </c>
     </row>
     <row r="319">
@@ -14292,25 +14292,25 @@
         <v>46</v>
       </c>
       <c r="K325" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="N325" t="n">
         <v>5667.94</v>
       </c>
       <c r="O325" t="n">
-        <v>260725.24</v>
+        <v>521450.48</v>
       </c>
       <c r="P325" t="n">
         <v>9500</v>
       </c>
       <c r="Q325" t="n">
-        <v>437000</v>
+        <v>874000</v>
       </c>
     </row>
     <row r="326">
@@ -14474,22 +14474,22 @@
         <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M329" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="N329" t="n">
         <v>10716.34</v>
       </c>
       <c r="O329" t="n">
-        <v>460802.62</v>
+        <v>353639.22</v>
       </c>
       <c r="P329" t="n">
         <v>39000</v>
       </c>
       <c r="Q329" t="n">
-        <v>1677000</v>
+        <v>1287000</v>
       </c>
     </row>
     <row r="330">
@@ -14862,10 +14862,10 @@
         <v>240</v>
       </c>
       <c r="N338" t="n">
-        <v>3240.8500303951</v>
+        <v>3240.8500305344</v>
       </c>
       <c r="O338" t="n">
-        <v>777804.007294824</v>
+        <v>777804.007328256</v>
       </c>
       <c r="P338" t="n">
         <v>5200</v>
@@ -14994,22 +14994,22 @@
         <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M341" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N341" t="n">
-        <v>14822.378861885</v>
+        <v>14822.378858502</v>
       </c>
       <c r="O341" t="n">
-        <v>622539.91219917</v>
+        <v>548428.0177645739</v>
       </c>
       <c r="P341" t="n">
         <v>24900</v>
       </c>
       <c r="Q341" t="n">
-        <v>1045800</v>
+        <v>921300</v>
       </c>
     </row>
     <row r="342">
@@ -15079,25 +15079,25 @@
         <v>432</v>
       </c>
       <c r="K343" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M343" t="n">
-        <v>432</v>
+        <v>668</v>
       </c>
       <c r="N343" t="n">
         <v>2090.85</v>
       </c>
       <c r="O343" t="n">
-        <v>903247.2</v>
+        <v>1396687.8</v>
       </c>
       <c r="P343" t="n">
         <v>2900</v>
       </c>
       <c r="Q343" t="n">
-        <v>1252800</v>
+        <v>1937200</v>
       </c>
     </row>
     <row r="344">
@@ -15575,10 +15575,10 @@
         <v>427</v>
       </c>
       <c r="N354" t="n">
-        <v>3041.6600128617</v>
+        <v>3041.660012945</v>
       </c>
       <c r="O354" t="n">
-        <v>1298788.825491946</v>
+        <v>1298788.825527515</v>
       </c>
       <c r="P354" t="n">
         <v>5500</v>
@@ -15746,22 +15746,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M358" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N358" t="n">
-        <v>1592.5673455845</v>
+        <v>1592.5672645976</v>
       </c>
       <c r="O358" t="n">
-        <v>30258.7795661055</v>
+        <v>20703.3744397688</v>
       </c>
       <c r="P358" t="n">
         <v>3900</v>
       </c>
       <c r="Q358" t="n">
-        <v>74100</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="359">
@@ -15874,22 +15874,22 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M361" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N361" t="n">
         <v>3655.96</v>
       </c>
       <c r="O361" t="n">
-        <v>292476.8</v>
+        <v>277852.96</v>
       </c>
       <c r="P361" t="n">
         <v>5500</v>
       </c>
       <c r="Q361" t="n">
-        <v>440000</v>
+        <v>418000</v>
       </c>
     </row>
     <row r="362">
@@ -16269,22 +16269,22 @@
         <v>0</v>
       </c>
       <c r="L370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M370" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N370" t="n">
         <v>6242.93</v>
       </c>
       <c r="O370" t="n">
-        <v>543134.91</v>
+        <v>530649.05</v>
       </c>
       <c r="P370" t="n">
         <v>10400</v>
       </c>
       <c r="Q370" t="n">
-        <v>904800</v>
+        <v>884000</v>
       </c>
     </row>
     <row r="371">
@@ -16928,10 +16928,10 @@
         <v>180</v>
       </c>
       <c r="N385" t="n">
-        <v>2021.7211225106</v>
+        <v>2021.7211231884</v>
       </c>
       <c r="O385" t="n">
-        <v>363909.802051908</v>
+        <v>363909.802173912</v>
       </c>
       <c r="P385" t="n">
         <v>2400</v>
@@ -17010,22 +17010,22 @@
         <v>0</v>
       </c>
       <c r="L387" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M387" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N387" t="n">
         <v>2204</v>
       </c>
       <c r="O387" t="n">
-        <v>220400</v>
+        <v>198360</v>
       </c>
       <c r="P387" t="n">
         <v>1500</v>
       </c>
       <c r="Q387" t="n">
-        <v>150000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="388">
@@ -17332,22 +17332,22 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M394" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N394" t="n">
         <v>11921.4</v>
       </c>
       <c r="O394" t="n">
-        <v>1573624.8</v>
+        <v>1502096.4</v>
       </c>
       <c r="P394" t="n">
         <v>19900</v>
       </c>
       <c r="Q394" t="n">
-        <v>2626800</v>
+        <v>2507400</v>
       </c>
     </row>
     <row r="395">
@@ -17458,22 +17458,22 @@
         <v>0</v>
       </c>
       <c r="L397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N397" t="n">
         <v>12230.77</v>
       </c>
       <c r="O397" t="n">
-        <v>36692.31</v>
+        <v>24461.54</v>
       </c>
       <c r="P397" t="n">
         <v>15900</v>
       </c>
       <c r="Q397" t="n">
-        <v>47700</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="398">
@@ -17672,22 +17672,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M402" t="n">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="N402" t="n">
         <v>3751</v>
       </c>
       <c r="O402" t="n">
-        <v>3315884</v>
+        <v>3297129</v>
       </c>
       <c r="P402" t="n">
         <v>6400</v>
       </c>
       <c r="Q402" t="n">
-        <v>5657600</v>
+        <v>5625600</v>
       </c>
     </row>
     <row r="403">
@@ -17813,22 +17813,22 @@
         <v>0</v>
       </c>
       <c r="L405" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M405" t="n">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="N405" t="n">
-        <v>1630.9233118002</v>
+        <v>1630.9233376736</v>
       </c>
       <c r="O405" t="n">
-        <v>1105766.005400536</v>
+        <v>1076409.402864576</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
       </c>
       <c r="Q405" t="n">
-        <v>1695000</v>
+        <v>1650000</v>
       </c>
     </row>
     <row r="406">
@@ -17900,22 +17900,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M407" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="N407" t="n">
-        <v>1467.3264227642</v>
+        <v>1467.3258333333</v>
       </c>
       <c r="O407" t="n">
-        <v>321344.4865853598</v>
+        <v>312540.4024999929</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
       </c>
       <c r="Q407" t="n">
-        <v>547500</v>
+        <v>532500</v>
       </c>
     </row>
     <row r="408">
@@ -17946,22 +17946,22 @@
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M408" t="n">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="N408" t="n">
-        <v>1690.6006518987</v>
+        <v>1690.6000587084</v>
       </c>
       <c r="O408" t="n">
-        <v>483511.7864430282</v>
+        <v>439556.015264184</v>
       </c>
       <c r="P408" t="n">
         <v>2900</v>
       </c>
       <c r="Q408" t="n">
-        <v>829400</v>
+        <v>754000</v>
       </c>
     </row>
     <row r="409">
@@ -17992,22 +17992,22 @@
         <v>0</v>
       </c>
       <c r="L409" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M409" t="n">
-        <v>1756</v>
+        <v>1721</v>
       </c>
       <c r="N409" t="n">
-        <v>1550.1933219945</v>
+        <v>1550.1933547279</v>
       </c>
       <c r="O409" t="n">
-        <v>2722139.473422342</v>
+        <v>2667882.763486716</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
       </c>
       <c r="Q409" t="n">
-        <v>4390000</v>
+        <v>4302500</v>
       </c>
     </row>
     <row r="410">
@@ -18044,10 +18044,10 @@
         <v>3</v>
       </c>
       <c r="N410" t="n">
-        <v>1579.3908883249</v>
+        <v>1579.3908418367</v>
       </c>
       <c r="O410" t="n">
-        <v>4738.1726649747</v>
+        <v>4738.1725255101</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
@@ -18090,10 +18090,10 @@
         <v>948</v>
       </c>
       <c r="N411" t="n">
-        <v>2403.5107961064</v>
+        <v>2403.5109560769</v>
       </c>
       <c r="O411" t="n">
-        <v>2278528.234708867</v>
+        <v>2278528.386360901</v>
       </c>
       <c r="P411" t="n">
         <v>3500</v>
@@ -18128,22 +18128,22 @@
         <v>0</v>
       </c>
       <c r="L412" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M412" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N412" t="n">
         <v>24267.77</v>
       </c>
       <c r="O412" t="n">
-        <v>291213.24</v>
+        <v>145606.62</v>
       </c>
       <c r="P412" t="n">
         <v>33400</v>
       </c>
       <c r="Q412" t="n">
-        <v>400800</v>
+        <v>200400</v>
       </c>
     </row>
     <row r="413">
@@ -18342,22 +18342,22 @@
         <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M417" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N417" t="n">
-        <v>1232.8080088496</v>
+        <v>1232.8076255708</v>
       </c>
       <c r="O417" t="n">
-        <v>41915.47230088639</v>
+        <v>33285.8058904116</v>
       </c>
       <c r="P417" t="n">
         <v>2400</v>
       </c>
       <c r="Q417" t="n">
-        <v>81600</v>
+        <v>64800</v>
       </c>
     </row>
     <row r="418">
@@ -18380,25 +18380,25 @@
         <v>4</v>
       </c>
       <c r="K418" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L418" t="n">
         <v>0</v>
       </c>
       <c r="M418" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N418" t="n">
         <v>101770.01727273</v>
       </c>
       <c r="O418" t="n">
-        <v>407080.06909092</v>
+        <v>1017700.1727273</v>
       </c>
       <c r="P418" t="n">
         <v>136900</v>
       </c>
       <c r="Q418" t="n">
-        <v>547600</v>
+        <v>1369000</v>
       </c>
     </row>
     <row r="419">
@@ -22027,10 +22027,10 @@
         <v>461</v>
       </c>
       <c r="N503" t="n">
-        <v>2029.8737091988</v>
+        <v>2029.8737110341</v>
       </c>
       <c r="O503" t="n">
-        <v>935771.7799406468</v>
+        <v>935771.7807867201</v>
       </c>
       <c r="P503" t="n">
         <v>3600</v>
@@ -22308,22 +22308,22 @@
         <v>0</v>
       </c>
       <c r="L510" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M510" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N510" t="n">
         <v>2673</v>
       </c>
       <c r="O510" t="n">
-        <v>727056</v>
+        <v>724383</v>
       </c>
       <c r="P510" t="n">
         <v>2500</v>
       </c>
       <c r="Q510" t="n">
-        <v>680000</v>
+        <v>677500</v>
       </c>
     </row>
     <row r="511">
@@ -24099,22 +24099,22 @@
         <v>0</v>
       </c>
       <c r="L552" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M552" t="n">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="N552" t="n">
         <v>1106</v>
       </c>
       <c r="O552" t="n">
-        <v>627102</v>
+        <v>614936</v>
       </c>
       <c r="P552" t="n">
         <v>2100</v>
       </c>
       <c r="Q552" t="n">
-        <v>1190700</v>
+        <v>1167600</v>
       </c>
     </row>
     <row r="553">
@@ -24448,10 +24448,10 @@
         <v>53</v>
       </c>
       <c r="N560" t="n">
-        <v>11562.038526316</v>
+        <v>11562.038522427</v>
       </c>
       <c r="O560" t="n">
-        <v>612788.041894748</v>
+        <v>612788.0416886309</v>
       </c>
       <c r="P560" t="n">
         <v>18500</v>
@@ -25834,22 +25834,22 @@
         <v>0</v>
       </c>
       <c r="L592" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M592" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N592" t="n">
         <v>16974.69</v>
       </c>
       <c r="O592" t="n">
-        <v>1459823.34</v>
+        <v>1442848.65</v>
       </c>
       <c r="P592" t="n">
         <v>26900</v>
       </c>
       <c r="Q592" t="n">
-        <v>2313400</v>
+        <v>2286500</v>
       </c>
     </row>
     <row r="593">
@@ -26131,22 +26131,22 @@
         <v>0</v>
       </c>
       <c r="L599" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M599" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="N599" t="n">
-        <v>1560.9995548961</v>
+        <v>1560.9996939288</v>
       </c>
       <c r="O599" t="n">
-        <v>140489.959940649</v>
+        <v>121757.9761264464</v>
       </c>
       <c r="P599" t="n">
         <v>2900</v>
       </c>
       <c r="Q599" t="n">
-        <v>261000</v>
+        <v>226200</v>
       </c>
     </row>
     <row r="600">
@@ -27420,22 +27420,22 @@
         <v>0</v>
       </c>
       <c r="L629" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M629" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N629" t="n">
         <v>20504</v>
       </c>
       <c r="O629" t="n">
-        <v>676632</v>
+        <v>594616</v>
       </c>
       <c r="P629" t="n">
         <v>32900</v>
       </c>
       <c r="Q629" t="n">
-        <v>1085700</v>
+        <v>954100</v>
       </c>
     </row>
     <row r="630">
@@ -27771,22 +27771,22 @@
         <v>0</v>
       </c>
       <c r="L637" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M637" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="N637" t="n">
-        <v>3113.8900265957</v>
+        <v>3113.890027137</v>
       </c>
       <c r="O637" t="n">
-        <v>221086.1918882947</v>
+        <v>205516.741791042</v>
       </c>
       <c r="P637" t="n">
         <v>5000</v>
       </c>
       <c r="Q637" t="n">
-        <v>355000</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="638">
@@ -27817,22 +27817,22 @@
         <v>0</v>
       </c>
       <c r="L638" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M638" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N638" t="n">
         <v>5569.98</v>
       </c>
       <c r="O638" t="n">
-        <v>128109.54</v>
+        <v>122539.56</v>
       </c>
       <c r="P638" t="n">
         <v>8900</v>
       </c>
       <c r="Q638" t="n">
-        <v>204700</v>
+        <v>195800</v>
       </c>
     </row>
     <row r="639">
@@ -27863,22 +27863,22 @@
         <v>0</v>
       </c>
       <c r="L639" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M639" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N639" t="n">
         <v>4690.64</v>
       </c>
       <c r="O639" t="n">
-        <v>23453.2</v>
+        <v>9381.280000000001</v>
       </c>
       <c r="P639" t="n">
         <v>7500</v>
       </c>
       <c r="Q639" t="n">
-        <v>37500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="640">
@@ -27909,22 +27909,22 @@
         <v>0</v>
       </c>
       <c r="L640" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M640" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="N640" t="n">
         <v>5410.72</v>
       </c>
       <c r="O640" t="n">
-        <v>319232.48</v>
+        <v>286768.16</v>
       </c>
       <c r="P640" t="n">
         <v>8700</v>
       </c>
       <c r="Q640" t="n">
-        <v>513300</v>
+        <v>461100</v>
       </c>
     </row>
     <row r="641">
@@ -27961,10 +27961,10 @@
         <v>15</v>
       </c>
       <c r="N641" t="n">
-        <v>4163.1601818182</v>
+        <v>4163.1601960784</v>
       </c>
       <c r="O641" t="n">
-        <v>62447.40272727299</v>
+        <v>62447.402941176</v>
       </c>
       <c r="P641" t="n">
         <v>6700</v>
@@ -28001,22 +28001,22 @@
         <v>0</v>
       </c>
       <c r="L642" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M642" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N642" t="n">
         <v>8878.450000000001</v>
       </c>
       <c r="O642" t="n">
-        <v>559342.3500000001</v>
+        <v>541585.4500000001</v>
       </c>
       <c r="P642" t="n">
         <v>14100</v>
       </c>
       <c r="Q642" t="n">
-        <v>888300</v>
+        <v>860100</v>
       </c>
     </row>
     <row r="643">
@@ -28047,22 +28047,22 @@
         <v>0</v>
       </c>
       <c r="L643" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M643" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N643" t="n">
         <v>2495.98</v>
       </c>
       <c r="O643" t="n">
-        <v>79871.36</v>
+        <v>72383.42</v>
       </c>
       <c r="P643" t="n">
         <v>4100</v>
       </c>
       <c r="Q643" t="n">
-        <v>131200</v>
+        <v>118900</v>
       </c>
     </row>
     <row r="644">
@@ -28139,22 +28139,22 @@
         <v>0</v>
       </c>
       <c r="L645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M645" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N645" t="n">
-        <v>5218.1705238095</v>
+        <v>5218.1705269461</v>
       </c>
       <c r="O645" t="n">
-        <v>109581.5809999995</v>
+        <v>104363.410538922</v>
       </c>
       <c r="P645" t="n">
         <v>8500</v>
       </c>
       <c r="Q645" t="n">
-        <v>178500</v>
+        <v>170000</v>
       </c>
     </row>
     <row r="646">
@@ -28185,22 +28185,22 @@
         <v>0</v>
       </c>
       <c r="L646" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M646" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="N646" t="n">
-        <v>1595.0094378698</v>
+        <v>1595.0094189602</v>
       </c>
       <c r="O646" t="n">
-        <v>223301.321301772</v>
+        <v>212136.2527217066</v>
       </c>
       <c r="P646" t="n">
         <v>2600</v>
       </c>
       <c r="Q646" t="n">
-        <v>364000</v>
+        <v>345800</v>
       </c>
     </row>
     <row r="647">
@@ -28231,22 +28231,22 @@
         <v>0</v>
       </c>
       <c r="L647" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M647" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="N647" t="n">
-        <v>3610.6500252207</v>
+        <v>3610.6500253807</v>
       </c>
       <c r="O647" t="n">
-        <v>292462.6520428767</v>
+        <v>274409.4019289332</v>
       </c>
       <c r="P647" t="n">
         <v>5800</v>
       </c>
       <c r="Q647" t="n">
-        <v>469800</v>
+        <v>440800</v>
       </c>
     </row>
     <row r="648">
@@ -28277,22 +28277,22 @@
         <v>0</v>
       </c>
       <c r="L648" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M648" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N648" t="n">
         <v>5194</v>
       </c>
       <c r="O648" t="n">
-        <v>270088</v>
+        <v>264894</v>
       </c>
       <c r="P648" t="n">
         <v>9000</v>
       </c>
       <c r="Q648" t="n">
-        <v>468000</v>
+        <v>459000</v>
       </c>
     </row>
     <row r="649">
@@ -28323,22 +28323,22 @@
         <v>0</v>
       </c>
       <c r="L649" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M649" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N649" t="n">
         <v>4227.77</v>
       </c>
       <c r="O649" t="n">
-        <v>232527.35</v>
+        <v>211388.5</v>
       </c>
       <c r="P649" t="n">
         <v>6900</v>
       </c>
       <c r="Q649" t="n">
-        <v>379500</v>
+        <v>345000</v>
       </c>
     </row>
     <row r="650">
@@ -28369,22 +28369,22 @@
         <v>0</v>
       </c>
       <c r="L650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M650" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N650" t="n">
         <v>3965.02</v>
       </c>
       <c r="O650" t="n">
-        <v>218076.1</v>
+        <v>214111.08</v>
       </c>
       <c r="P650" t="n">
         <v>6500</v>
       </c>
       <c r="Q650" t="n">
-        <v>357500</v>
+        <v>351000</v>
       </c>
     </row>
     <row r="651">
@@ -28415,22 +28415,22 @@
         <v>0</v>
       </c>
       <c r="L651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M651" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N651" t="n">
         <v>5791.05</v>
       </c>
       <c r="O651" t="n">
-        <v>393791.4</v>
+        <v>388000.35</v>
       </c>
       <c r="P651" t="n">
         <v>9300</v>
       </c>
       <c r="Q651" t="n">
-        <v>632400</v>
+        <v>623100</v>
       </c>
     </row>
     <row r="652">
@@ -28461,22 +28461,22 @@
         <v>0</v>
       </c>
       <c r="L652" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M652" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="N652" t="n">
         <v>10977.27</v>
       </c>
       <c r="O652" t="n">
-        <v>252477.21</v>
+        <v>175636.32</v>
       </c>
       <c r="P652" t="n">
         <v>17900</v>
       </c>
       <c r="Q652" t="n">
-        <v>411700</v>
+        <v>286400</v>
       </c>
     </row>
     <row r="653">
@@ -28504,25 +28504,25 @@
         <v>1</v>
       </c>
       <c r="K653" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L653" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M653" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="N653" t="n">
         <v>1812.57</v>
       </c>
       <c r="O653" t="n">
-        <v>1812.57</v>
+        <v>172194.15</v>
       </c>
       <c r="P653" t="n">
         <v>2900</v>
       </c>
       <c r="Q653" t="n">
-        <v>2900</v>
+        <v>275500</v>
       </c>
     </row>
     <row r="654">
@@ -28553,22 +28553,22 @@
         <v>0</v>
       </c>
       <c r="L654" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M654" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N654" t="n">
         <v>6058.52</v>
       </c>
       <c r="O654" t="n">
-        <v>302926</v>
+        <v>260516.36</v>
       </c>
       <c r="P654" t="n">
         <v>9700</v>
       </c>
       <c r="Q654" t="n">
-        <v>485000</v>
+        <v>417100</v>
       </c>
     </row>
     <row r="655">
@@ -28599,22 +28599,22 @@
         <v>0</v>
       </c>
       <c r="L655" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M655" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N655" t="n">
         <v>14380</v>
       </c>
       <c r="O655" t="n">
-        <v>1423620</v>
+        <v>1409240</v>
       </c>
       <c r="P655" t="n">
         <v>23000</v>
       </c>
       <c r="Q655" t="n">
-        <v>2277000</v>
+        <v>2254000</v>
       </c>
     </row>
     <row r="656">
@@ -28651,10 +28651,10 @@
         <v>378</v>
       </c>
       <c r="N656" t="n">
-        <v>1664.3585273632</v>
+        <v>1664.3584236948</v>
       </c>
       <c r="O656" t="n">
-        <v>629127.5233432896</v>
+        <v>629127.4841566344</v>
       </c>
       <c r="P656" t="n">
         <v>2900</v>
@@ -28691,22 +28691,22 @@
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M657" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N657" t="n">
         <v>15502</v>
       </c>
       <c r="O657" t="n">
-        <v>1069638</v>
+        <v>1023132</v>
       </c>
       <c r="P657" t="n">
         <v>25900</v>
       </c>
       <c r="Q657" t="n">
-        <v>1787100</v>
+        <v>1709400</v>
       </c>
     </row>
     <row r="658">
@@ -28835,22 +28835,22 @@
         <v>0</v>
       </c>
       <c r="L660" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M660" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N660" t="n">
         <v>38449</v>
       </c>
       <c r="O660" t="n">
-        <v>230694</v>
+        <v>153796</v>
       </c>
       <c r="P660" t="n">
         <v>62900</v>
       </c>
       <c r="Q660" t="n">
-        <v>377400</v>
+        <v>251600</v>
       </c>
     </row>
     <row r="661">
@@ -29157,22 +29157,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M667" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="N667" t="n">
         <v>3646</v>
       </c>
       <c r="O667" t="n">
-        <v>466688</v>
+        <v>437520</v>
       </c>
       <c r="P667" t="n">
         <v>6900</v>
       </c>
       <c r="Q667" t="n">
-        <v>883200</v>
+        <v>828000</v>
       </c>
     </row>
     <row r="668">
@@ -29209,10 +29209,10 @@
         <v>4</v>
       </c>
       <c r="N668" t="n">
-        <v>23521.62453125</v>
+        <v>23521.624354839</v>
       </c>
       <c r="O668" t="n">
-        <v>94086.498125</v>
+        <v>94086.497419356</v>
       </c>
       <c r="P668" t="n">
         <v>39000</v>
@@ -29301,10 +29301,10 @@
         <v>1492</v>
       </c>
       <c r="N670" t="n">
-        <v>1778.4725740823</v>
+        <v>1778.4725809313</v>
       </c>
       <c r="O670" t="n">
-        <v>2653481.080530792</v>
+        <v>2653481.090749499</v>
       </c>
       <c r="P670" t="n">
         <v>4900</v>
@@ -31322,25 +31322,25 @@
         <v>19</v>
       </c>
       <c r="K714" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L714" t="n">
         <v>0</v>
       </c>
       <c r="M714" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="N714" t="n">
         <v>28116</v>
       </c>
       <c r="O714" t="n">
-        <v>534204</v>
+        <v>1068408</v>
       </c>
       <c r="P714" t="n">
         <v>45900</v>
       </c>
       <c r="Q714" t="n">
-        <v>872100</v>
+        <v>1744200</v>
       </c>
     </row>
     <row r="715">
@@ -31417,22 +31417,22 @@
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M716" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="N716" t="n">
         <v>3424</v>
       </c>
       <c r="O716" t="n">
-        <v>643712</v>
+        <v>630016</v>
       </c>
       <c r="P716" t="n">
         <v>5900</v>
       </c>
       <c r="Q716" t="n">
-        <v>1109200</v>
+        <v>1085600</v>
       </c>
     </row>
     <row r="717">
@@ -32157,10 +32157,10 @@
         <v>696</v>
       </c>
       <c r="N732" t="n">
-        <v>2328.1187488882</v>
+        <v>2328.118739546</v>
       </c>
       <c r="O732" t="n">
-        <v>1620370.649226187</v>
+        <v>1620370.642724016</v>
       </c>
       <c r="P732" t="n">
         <v>4500</v>
@@ -32565,22 +32565,22 @@
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M741" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N741" t="n">
         <v>3519</v>
       </c>
       <c r="O741" t="n">
-        <v>897345</v>
+        <v>883269</v>
       </c>
       <c r="P741" t="n">
         <v>5900</v>
       </c>
       <c r="Q741" t="n">
-        <v>1504500</v>
+        <v>1480900</v>
       </c>
     </row>
     <row r="742">
@@ -32749,22 +32749,22 @@
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M745" t="n">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="N745" t="n">
         <v>4544</v>
       </c>
       <c r="O745" t="n">
-        <v>1435904</v>
+        <v>1408640</v>
       </c>
       <c r="P745" t="n">
         <v>7900</v>
       </c>
       <c r="Q745" t="n">
-        <v>2496400</v>
+        <v>2449000</v>
       </c>
     </row>
     <row r="746">
@@ -33114,25 +33114,25 @@
         <v>1</v>
       </c>
       <c r="K753" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L753" t="n">
         <v>0</v>
       </c>
       <c r="M753" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N753" t="n">
         <v>100129</v>
       </c>
       <c r="O753" t="n">
-        <v>100129</v>
+        <v>901161</v>
       </c>
       <c r="P753" t="n">
         <v>159900</v>
       </c>
       <c r="Q753" t="n">
-        <v>159900</v>
+        <v>1439100</v>
       </c>
     </row>
     <row r="754">
@@ -33261,10 +33261,10 @@
         <v>100</v>
       </c>
       <c r="N756" t="n">
-        <v>3903.7362017804</v>
+        <v>3903.736812933</v>
       </c>
       <c r="O756" t="n">
-        <v>390373.62017804</v>
+        <v>390373.6812933</v>
       </c>
       <c r="P756" t="n">
         <v>7500</v>
@@ -33526,22 +33526,22 @@
         <v>0</v>
       </c>
       <c r="L762" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M762" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N762" t="n">
         <v>4202</v>
       </c>
       <c r="O762" t="n">
-        <v>273130</v>
+        <v>268928</v>
       </c>
       <c r="P762" t="n">
         <v>7900</v>
       </c>
       <c r="Q762" t="n">
-        <v>513500</v>
+        <v>505600</v>
       </c>
     </row>
     <row r="763">
@@ -33808,10 +33808,10 @@
         <v>494</v>
       </c>
       <c r="N768" t="n">
-        <v>5869.1727464789</v>
+        <v>5869.1727391742</v>
       </c>
       <c r="O768" t="n">
-        <v>2899371.336760577</v>
+        <v>2899371.333152055</v>
       </c>
       <c r="P768" t="n">
         <v>9500</v>
@@ -33894,22 +33894,22 @@
         <v>0</v>
       </c>
       <c r="L770" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M770" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N770" t="n">
         <v>4984</v>
       </c>
       <c r="O770" t="n">
-        <v>184408</v>
+        <v>174440</v>
       </c>
       <c r="P770" t="n">
         <v>7900</v>
       </c>
       <c r="Q770" t="n">
-        <v>292300</v>
+        <v>276500</v>
       </c>
     </row>
     <row r="771">
@@ -34633,22 +34633,22 @@
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M786" t="n">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="N786" t="n">
         <v>753</v>
       </c>
       <c r="O786" t="n">
-        <v>533124</v>
+        <v>527100</v>
       </c>
       <c r="P786" t="n">
         <v>1600</v>
       </c>
       <c r="Q786" t="n">
-        <v>1132800</v>
+        <v>1120000</v>
       </c>
     </row>
     <row r="787">
@@ -35088,22 +35088,22 @@
         <v>0</v>
       </c>
       <c r="L796" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M796" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N796" t="n">
         <v>11015</v>
       </c>
       <c r="O796" t="n">
-        <v>793080</v>
+        <v>782065</v>
       </c>
       <c r="P796" t="n">
         <v>17900</v>
       </c>
       <c r="Q796" t="n">
-        <v>1288800</v>
+        <v>1270900</v>
       </c>
     </row>
     <row r="797">
@@ -35413,22 +35413,22 @@
         <v>0</v>
       </c>
       <c r="L803" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M803" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N803" t="n">
         <v>20014</v>
       </c>
       <c r="O803" t="n">
-        <v>440308</v>
+        <v>360252</v>
       </c>
       <c r="P803" t="n">
         <v>33900</v>
       </c>
       <c r="Q803" t="n">
-        <v>745800</v>
+        <v>610200</v>
       </c>
     </row>
     <row r="804">
@@ -35557,10 +35557,10 @@
         <v>85</v>
       </c>
       <c r="N806" t="n">
-        <v>4268.7047257384</v>
+        <v>4268.7051082251</v>
       </c>
       <c r="O806" t="n">
-        <v>362839.901687764</v>
+        <v>362839.9341991335</v>
       </c>
       <c r="P806" t="n">
         <v>6900</v>
@@ -35643,22 +35643,22 @@
         <v>0</v>
       </c>
       <c r="L808" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M808" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N808" t="n">
         <v>29835</v>
       </c>
       <c r="O808" t="n">
-        <v>1014390</v>
+        <v>895050</v>
       </c>
       <c r="P808" t="n">
         <v>47900</v>
       </c>
       <c r="Q808" t="n">
-        <v>1628600</v>
+        <v>1437000</v>
       </c>
     </row>
     <row r="809">
@@ -35873,22 +35873,22 @@
         <v>0</v>
       </c>
       <c r="L813" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M813" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N813" t="n">
         <v>16282</v>
       </c>
       <c r="O813" t="n">
-        <v>260512</v>
+        <v>195384</v>
       </c>
       <c r="P813" t="n">
         <v>27900</v>
       </c>
       <c r="Q813" t="n">
-        <v>446400</v>
+        <v>334800</v>
       </c>
     </row>
     <row r="814">
@@ -35916,25 +35916,25 @@
         <v>75</v>
       </c>
       <c r="K814" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L814" t="n">
         <v>0</v>
       </c>
       <c r="M814" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="N814" t="n">
         <v>8700</v>
       </c>
       <c r="O814" t="n">
-        <v>652500</v>
+        <v>826500</v>
       </c>
       <c r="P814" t="n">
         <v>14900</v>
       </c>
       <c r="Q814" t="n">
-        <v>1117500</v>
+        <v>1415500</v>
       </c>
     </row>
     <row r="815">
@@ -36149,22 +36149,22 @@
         <v>0</v>
       </c>
       <c r="L819" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M819" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N819" t="n">
         <v>15472</v>
       </c>
       <c r="O819" t="n">
-        <v>417744</v>
+        <v>309440</v>
       </c>
       <c r="P819" t="n">
         <v>25900</v>
       </c>
       <c r="Q819" t="n">
-        <v>699300</v>
+        <v>518000</v>
       </c>
     </row>
     <row r="820">
@@ -36658,22 +36658,22 @@
         <v>0</v>
       </c>
       <c r="L830" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M830" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="N830" t="n">
-        <v>4248.6401470588</v>
+        <v>4248.6496363636</v>
       </c>
       <c r="O830" t="n">
-        <v>348388.4920588216</v>
+        <v>237924.3796363616</v>
       </c>
       <c r="P830" t="n">
         <v>5900</v>
       </c>
       <c r="Q830" t="n">
-        <v>483800</v>
+        <v>330400</v>
       </c>
     </row>
     <row r="831">
@@ -36886,22 +36886,22 @@
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M835" t="n">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="N835" t="n">
-        <v>2079.3841354372</v>
+        <v>2079.384121911</v>
       </c>
       <c r="O835" t="n">
-        <v>869182.5686127496</v>
+        <v>862944.410593065</v>
       </c>
       <c r="P835" t="n">
         <v>2900</v>
       </c>
       <c r="Q835" t="n">
-        <v>1212200</v>
+        <v>1203500</v>
       </c>
     </row>
     <row r="836">
@@ -36932,22 +36932,22 @@
         <v>0</v>
       </c>
       <c r="L836" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M836" t="n">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="N836" t="n">
-        <v>1803.0152234206</v>
+        <v>1803.0152282542</v>
       </c>
       <c r="O836" t="n">
-        <v>775296.546070858</v>
+        <v>769887.5024645434</v>
       </c>
       <c r="P836" t="n">
         <v>2500</v>
       </c>
       <c r="Q836" t="n">
-        <v>1075000</v>
+        <v>1067500</v>
       </c>
     </row>
     <row r="837">
@@ -36984,10 +36984,10 @@
         <v>71</v>
       </c>
       <c r="N837" t="n">
-        <v>3306.5953246753</v>
+        <v>3306.5952380952</v>
       </c>
       <c r="O837" t="n">
-        <v>234768.2680519463</v>
+        <v>234768.2619047592</v>
       </c>
       <c r="P837" t="n">
         <v>4900</v>
@@ -37024,22 +37024,22 @@
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M838" t="n">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="N838" t="n">
-        <v>2122.164</v>
+        <v>2122.1639833897</v>
       </c>
       <c r="O838" t="n">
-        <v>933752.1600000001</v>
+        <v>914652.6768409607</v>
       </c>
       <c r="P838" t="n">
         <v>2900</v>
       </c>
       <c r="Q838" t="n">
-        <v>1276000</v>
+        <v>1249900</v>
       </c>
     </row>
     <row r="839">
@@ -37070,22 +37070,22 @@
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M839" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N839" t="n">
-        <v>2108.7900692042</v>
+        <v>2108.7902645503</v>
       </c>
       <c r="O839" t="n">
-        <v>69590.0722837386</v>
+        <v>63263.707936509</v>
       </c>
       <c r="P839" t="n">
         <v>2900</v>
       </c>
       <c r="Q839" t="n">
-        <v>95700</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="840">
@@ -37116,22 +37116,22 @@
         <v>0</v>
       </c>
       <c r="L840" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M840" t="n">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="N840" t="n">
-        <v>2056.0837111517</v>
+        <v>2056.0836725935</v>
       </c>
       <c r="O840" t="n">
-        <v>1836082.754058468</v>
+        <v>1829914.468608215</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
       </c>
       <c r="Q840" t="n">
-        <v>2589700</v>
+        <v>2581000</v>
       </c>
     </row>
     <row r="841">
@@ -37441,22 +37441,22 @@
         <v>0</v>
       </c>
       <c r="L847" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M847" t="n">
-        <v>651</v>
+        <v>603</v>
       </c>
       <c r="N847" t="n">
         <v>1662</v>
       </c>
       <c r="O847" t="n">
-        <v>1081962</v>
+        <v>1002186</v>
       </c>
       <c r="P847" t="n">
         <v>2900</v>
       </c>
       <c r="Q847" t="n">
-        <v>1887900</v>
+        <v>1748700</v>
       </c>
     </row>
     <row r="848">
@@ -37579,22 +37579,22 @@
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M850" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="N850" t="n">
-        <v>1592.27610957</v>
+        <v>1592.2763108883</v>
       </c>
       <c r="O850" t="n">
-        <v>141712.57375173</v>
+        <v>121012.9996275108</v>
       </c>
       <c r="P850" t="n">
         <v>2500</v>
       </c>
       <c r="Q850" t="n">
-        <v>222500</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="851">
@@ -37623,22 +37623,22 @@
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M851" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N851" t="n">
         <v>5347.73</v>
       </c>
       <c r="O851" t="n">
-        <v>10695.46</v>
+        <v>5347.73</v>
       </c>
       <c r="P851" t="n">
         <v>9500</v>
       </c>
       <c r="Q851" t="n">
-        <v>19000</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="852">
@@ -37675,10 +37675,10 @@
         <v>2</v>
       </c>
       <c r="N852" t="n">
-        <v>1906.1853846154</v>
+        <v>1906.1853271028</v>
       </c>
       <c r="O852" t="n">
-        <v>3812.3707692308</v>
+        <v>3812.3706542056</v>
       </c>
       <c r="P852" t="n">
         <v>2900</v>
@@ -37721,10 +37721,10 @@
         <v>89</v>
       </c>
       <c r="N853" t="n">
-        <v>2060.1604635762</v>
+        <v>2060.1603355705</v>
       </c>
       <c r="O853" t="n">
-        <v>183354.2812582818</v>
+        <v>183354.2698657745</v>
       </c>
       <c r="P853" t="n">
         <v>2900</v>
@@ -37767,10 +37767,10 @@
         <v>75</v>
       </c>
       <c r="N854" t="n">
-        <v>2546.9846915888</v>
+        <v>2546.9846816479</v>
       </c>
       <c r="O854" t="n">
-        <v>191023.85186916</v>
+        <v>191023.8511235925</v>
       </c>
       <c r="P854" t="n">
         <v>3900</v>
@@ -37813,10 +37813,10 @@
         <v>281</v>
       </c>
       <c r="N855" t="n">
-        <v>1259.2744638514</v>
+        <v>1259.2745016722</v>
       </c>
       <c r="O855" t="n">
-        <v>353856.1243422434</v>
+        <v>353856.1349698882</v>
       </c>
       <c r="P855" t="n">
         <v>1900</v>
@@ -37949,10 +37949,10 @@
         <v>97</v>
       </c>
       <c r="N858" t="n">
-        <v>692.15211662075</v>
+        <v>692.1521205151799</v>
       </c>
       <c r="O858" t="n">
-        <v>67138.75531221276</v>
+        <v>67138.75568997246</v>
       </c>
       <c r="P858" t="n">
         <v>1200</v>
@@ -40232,10 +40232,10 @@
         <v>1</v>
       </c>
       <c r="N908" t="n">
-        <v>1283.653986711</v>
+        <v>1283.6539464883</v>
       </c>
       <c r="O908" t="n">
-        <v>1283.653986711</v>
+        <v>1283.6539464883</v>
       </c>
       <c r="P908" t="n">
         <v>1900</v>
@@ -40932,22 +40932,22 @@
         <v>0</v>
       </c>
       <c r="L924" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M924" t="n">
-        <v>3323</v>
+        <v>3299</v>
       </c>
       <c r="N924" t="n">
-        <v>517.28836312001</v>
+        <v>517.2884408203601</v>
       </c>
       <c r="O924" t="n">
-        <v>1718949.230647793</v>
+        <v>1706534.566266368</v>
       </c>
       <c r="P924" t="n">
         <v>900</v>
       </c>
       <c r="Q924" t="n">
-        <v>2990700</v>
+        <v>2969100</v>
       </c>
     </row>
     <row r="925">
@@ -41158,22 +41158,22 @@
         <v>0</v>
       </c>
       <c r="L929" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M929" t="n">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="N929" t="n">
-        <v>3110.8426185007</v>
+        <v>3110.8425641565</v>
       </c>
       <c r="O929" t="n">
-        <v>1804288.718730406</v>
+        <v>1776291.104133361</v>
       </c>
       <c r="P929" t="n">
         <v>4500</v>
       </c>
       <c r="Q929" t="n">
-        <v>2610000</v>
+        <v>2569500</v>
       </c>
     </row>
     <row r="930">
@@ -41292,22 +41292,22 @@
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M932" t="n">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="N932" t="n">
         <v>2030.02</v>
       </c>
       <c r="O932" t="n">
-        <v>1033280.18</v>
+        <v>1021100.06</v>
       </c>
       <c r="P932" t="n">
         <v>3600</v>
       </c>
       <c r="Q932" t="n">
-        <v>1832400</v>
+        <v>1810800</v>
       </c>
     </row>
     <row r="933">
@@ -41377,25 +41377,25 @@
         <v>842</v>
       </c>
       <c r="K934" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="L934" t="n">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="M934" t="n">
-        <v>842</v>
+        <v>1658</v>
       </c>
       <c r="N934" t="n">
-        <v>703.79529676406</v>
+        <v>703.79526826968</v>
       </c>
       <c r="O934" t="n">
-        <v>592595.6398753385</v>
+        <v>1166892.554791129</v>
       </c>
       <c r="P934" t="n">
         <v>900</v>
       </c>
       <c r="Q934" t="n">
-        <v>757800</v>
+        <v>1492200</v>
       </c>
     </row>
     <row r="935">
@@ -41613,10 +41613,10 @@
         <v>3</v>
       </c>
       <c r="N939" t="n">
-        <v>2501.3851351351</v>
+        <v>2501.3850684932</v>
       </c>
       <c r="O939" t="n">
-        <v>7504.155405405299</v>
+        <v>7504.155205479599</v>
       </c>
       <c r="P939" t="n">
         <v>4100</v>
@@ -41962,22 +41962,22 @@
         <v>0</v>
       </c>
       <c r="L947" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M947" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="N947" t="n">
         <v>2525.02</v>
       </c>
       <c r="O947" t="n">
-        <v>45450.36</v>
+        <v>12625.1</v>
       </c>
       <c r="P947" t="n">
         <v>3000</v>
       </c>
       <c r="Q947" t="n">
-        <v>54000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="948">
@@ -42397,10 +42397,10 @@
         <v>74</v>
       </c>
       <c r="N957" t="n">
-        <v>1595.5153131828</v>
+        <v>1595.5151400147</v>
       </c>
       <c r="O957" t="n">
-        <v>118068.1331755272</v>
+        <v>118068.1203610878</v>
       </c>
       <c r="P957" t="n">
         <v>2500</v>
@@ -44136,10 +44136,10 @@
         <v>1</v>
       </c>
       <c r="N994" t="n">
-        <v>10737.5264</v>
+        <v>10737.526326531</v>
       </c>
       <c r="O994" t="n">
-        <v>10737.5264</v>
+        <v>10737.526326531</v>
       </c>
       <c r="P994" t="n">
         <v>18900</v>
@@ -44926,22 +44926,22 @@
         <v>0</v>
       </c>
       <c r="L1011" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1011" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N1011" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1011" t="n">
-        <v>1338615.85</v>
+        <v>1289938.91</v>
       </c>
       <c r="P1011" t="n">
         <v>27900</v>
       </c>
       <c r="Q1011" t="n">
-        <v>1534500</v>
+        <v>1478700</v>
       </c>
     </row>
     <row r="1012">
@@ -45643,10 +45643,10 @@
         <v>196</v>
       </c>
       <c r="N1026" t="n">
-        <v>430.60997668998</v>
+        <v>430.6099765808</v>
       </c>
       <c r="O1026" t="n">
-        <v>84399.55543123608</v>
+        <v>84399.5554098368</v>
       </c>
       <c r="P1026" t="n">
         <v>2200</v>
@@ -45692,10 +45692,10 @@
         <v>6</v>
       </c>
       <c r="N1027" t="n">
-        <v>315.02679218968</v>
+        <v>315.02685915493</v>
       </c>
       <c r="O1027" t="n">
-        <v>1890.16075313808</v>
+        <v>1890.16115492958</v>
       </c>
       <c r="P1027" t="n">
         <v>2200</v>
@@ -47833,22 +47833,22 @@
         <v>0</v>
       </c>
       <c r="L1077" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1077" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="N1077" t="n">
         <v>1464</v>
       </c>
       <c r="O1077" t="n">
-        <v>159576</v>
+        <v>142008</v>
       </c>
       <c r="P1077" t="n">
         <v>1500</v>
       </c>
       <c r="Q1077" t="n">
-        <v>163500</v>
+        <v>145500</v>
       </c>
     </row>
     <row r="1078">
@@ -48597,22 +48597,22 @@
         <v>0</v>
       </c>
       <c r="L1095" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1095" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N1095" t="n">
         <v>5077</v>
       </c>
       <c r="O1095" t="n">
-        <v>670164</v>
+        <v>660010</v>
       </c>
       <c r="P1095" t="n">
         <v>8500</v>
       </c>
       <c r="Q1095" t="n">
-        <v>1122000</v>
+        <v>1105000</v>
       </c>
     </row>
     <row r="1096">
@@ -48771,22 +48771,22 @@
         <v>0</v>
       </c>
       <c r="L1099" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1099" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="N1099" t="n">
-        <v>4985.4047808765</v>
+        <v>4985.4050632911</v>
       </c>
       <c r="O1099" t="n">
-        <v>493555.0733067735</v>
+        <v>468628.0759493634</v>
       </c>
       <c r="P1099" t="n">
         <v>7900</v>
       </c>
       <c r="Q1099" t="n">
-        <v>782100</v>
+        <v>742600</v>
       </c>
     </row>
     <row r="1100">
@@ -48822,22 +48822,22 @@
         <v>0</v>
       </c>
       <c r="L1100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1100" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N1100" t="n">
-        <v>1757.3205416667</v>
+        <v>1757.3205462185</v>
       </c>
       <c r="O1100" t="n">
-        <v>87866.02708333499</v>
+        <v>80836.745126051</v>
       </c>
       <c r="P1100" t="n">
         <v>2000</v>
       </c>
       <c r="Q1100" t="n">
-        <v>100000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="1101">
@@ -48868,22 +48868,22 @@
         <v>0</v>
       </c>
       <c r="L1101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1101" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N1101" t="n">
         <v>1561.33</v>
       </c>
       <c r="O1101" t="n">
-        <v>435611.07</v>
+        <v>432488.41</v>
       </c>
       <c r="P1101" t="n">
         <v>2000</v>
       </c>
       <c r="Q1101" t="n">
-        <v>558000</v>
+        <v>554000</v>
       </c>
     </row>
     <row r="1102">
@@ -48914,22 +48914,22 @@
         <v>0</v>
       </c>
       <c r="L1102" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M1102" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N1102" t="n">
         <v>5700</v>
       </c>
       <c r="O1102" t="n">
-        <v>51300</v>
+        <v>0</v>
       </c>
       <c r="P1102" t="n">
         <v>6900</v>
       </c>
       <c r="Q1102" t="n">
-        <v>62100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1103">
@@ -49457,10 +49457,10 @@
         <v>2</v>
       </c>
       <c r="N1114" t="n">
-        <v>21664.371428571</v>
+        <v>21664.371538462</v>
       </c>
       <c r="O1114" t="n">
-        <v>43328.742857142</v>
+        <v>43328.743076924</v>
       </c>
       <c r="P1114" t="n">
         <v>30000</v>
@@ -49543,22 +49543,22 @@
         <v>0</v>
       </c>
       <c r="L1116" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1116" t="n">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="N1116" t="n">
         <v>7480</v>
       </c>
       <c r="O1116" t="n">
-        <v>2445960</v>
+        <v>2356200</v>
       </c>
       <c r="P1116" t="n">
         <v>9500</v>
       </c>
       <c r="Q1116" t="n">
-        <v>3106500</v>
+        <v>2992500</v>
       </c>
     </row>
     <row r="1117">
@@ -49681,22 +49681,22 @@
         <v>0</v>
       </c>
       <c r="L1119" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="M1119" t="n">
-        <v>343</v>
+        <v>139</v>
       </c>
       <c r="N1119" t="n">
         <v>9240</v>
       </c>
       <c r="O1119" t="n">
-        <v>3169320</v>
+        <v>1284360</v>
       </c>
       <c r="P1119" t="n">
         <v>11500</v>
       </c>
       <c r="Q1119" t="n">
-        <v>3944500</v>
+        <v>1598500</v>
       </c>
     </row>
     <row r="1120">
@@ -51506,22 +51506,22 @@
         <v>0</v>
       </c>
       <c r="L1159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1159" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N1159" t="n">
         <v>5000</v>
       </c>
       <c r="O1159" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="P1159" t="n">
         <v>6000</v>
       </c>
       <c r="Q1159" t="n">
-        <v>36000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1160">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -691,10 +691,10 @@
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>96741.407402597</v>
+        <v>96741.407702703</v>
       </c>
       <c r="O7" t="n">
-        <v>290224.222207791</v>
+        <v>290224.223108109</v>
       </c>
       <c r="P7" t="n">
         <v>188900</v>
@@ -732,22 +732,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>66707.977837838</v>
+        <v>66707.978055556</v>
       </c>
       <c r="O8" t="n">
-        <v>66707.977837838</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>125900</v>
       </c>
       <c r="Q8" t="n">
-        <v>125900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -812,25 +812,25 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
         <v>27000</v>
       </c>
       <c r="O10" t="n">
-        <v>27000</v>
+        <v>108000</v>
       </c>
       <c r="P10" t="n">
         <v>92000</v>
       </c>
       <c r="Q10" t="n">
-        <v>92000</v>
+        <v>368000</v>
       </c>
     </row>
     <row r="11">
@@ -1054,22 +1054,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N16" t="n">
         <v>27000</v>
       </c>
       <c r="O16" t="n">
-        <v>648000</v>
+        <v>621000</v>
       </c>
       <c r="P16" t="n">
         <v>20000</v>
       </c>
       <c r="Q16" t="n">
-        <v>480000</v>
+        <v>460000</v>
       </c>
     </row>
     <row r="17">
@@ -1313,10 +1313,10 @@
         <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>14490.385</v>
+        <v>14490.384964539</v>
       </c>
       <c r="O22" t="n">
-        <v>304298.085</v>
+        <v>304298.084255319</v>
       </c>
       <c r="P22" t="n">
         <v>23600</v>
@@ -1354,10 +1354,10 @@
         <v>372</v>
       </c>
       <c r="N23" t="n">
-        <v>1811.3053333333</v>
+        <v>1811.3054760423</v>
       </c>
       <c r="O23" t="n">
-        <v>673805.5839999876</v>
+        <v>673805.6370877356</v>
       </c>
       <c r="P23" t="n">
         <v>2600</v>
@@ -2965,10 +2965,10 @@
         <v>41</v>
       </c>
       <c r="N63" t="n">
-        <v>6272.8545933014</v>
+        <v>6272.854608</v>
       </c>
       <c r="O63" t="n">
-        <v>257187.0383253574</v>
+        <v>257187.038928</v>
       </c>
       <c r="P63" t="n">
         <v>7900</v>
@@ -3867,22 +3867,22 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N86" t="n">
-        <v>14857.6232</v>
+        <v>14857.623214286</v>
       </c>
       <c r="O86" t="n">
-        <v>356582.9568</v>
+        <v>341725.333928578</v>
       </c>
       <c r="P86" t="n">
         <v>34900</v>
       </c>
       <c r="Q86" t="n">
-        <v>837600</v>
+        <v>802700</v>
       </c>
     </row>
     <row r="87">
@@ -4090,22 +4090,22 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N91" t="n">
         <v>1800</v>
       </c>
       <c r="O91" t="n">
-        <v>162000</v>
+        <v>158400</v>
       </c>
       <c r="P91" t="n">
         <v>2200</v>
       </c>
       <c r="Q91" t="n">
-        <v>198000</v>
+        <v>193600</v>
       </c>
     </row>
     <row r="92">
@@ -4136,22 +4136,22 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N92" t="n">
         <v>1800</v>
       </c>
       <c r="O92" t="n">
-        <v>131400</v>
+        <v>129600</v>
       </c>
       <c r="P92" t="n">
         <v>2200</v>
       </c>
       <c r="Q92" t="n">
-        <v>160600</v>
+        <v>158400</v>
       </c>
     </row>
     <row r="93">
@@ -4895,22 +4895,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M109" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="N109" t="n">
-        <v>10994.353793103</v>
+        <v>10994.359047619</v>
       </c>
       <c r="O109" t="n">
-        <v>747616.0579310041</v>
+        <v>483751.798095236</v>
       </c>
       <c r="P109" t="n">
         <v>16900</v>
       </c>
       <c r="Q109" t="n">
-        <v>1149200</v>
+        <v>743600</v>
       </c>
     </row>
     <row r="110">
@@ -4942,22 +4942,22 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M110" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>18835.026428571</v>
+        <v>18835.37</v>
       </c>
       <c r="O110" t="n">
-        <v>244855.343571423</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
         <v>40500</v>
       </c>
       <c r="Q110" t="n">
-        <v>526500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -5293,10 +5293,10 @@
         <v>84</v>
       </c>
       <c r="N118" t="n">
-        <v>7407.7300533333</v>
+        <v>7407.7300536193</v>
       </c>
       <c r="O118" t="n">
-        <v>622249.3244799972</v>
+        <v>622249.3245040212</v>
       </c>
       <c r="P118" t="n">
         <v>10900</v>
@@ -5958,22 +5958,22 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>66440.72</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>66440.72</v>
+        <v>0</v>
       </c>
       <c r="P134" t="n">
         <v>102900</v>
       </c>
       <c r="Q134" t="n">
-        <v>102900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -6000,22 +6000,22 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M135" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N135" t="n">
-        <v>36306.306666667</v>
+        <v>36306.345</v>
       </c>
       <c r="O135" t="n">
-        <v>399369.373333337</v>
+        <v>254144.415</v>
       </c>
       <c r="P135" t="n">
         <v>64900</v>
       </c>
       <c r="Q135" t="n">
-        <v>713900</v>
+        <v>454300</v>
       </c>
     </row>
     <row r="136">
@@ -6047,22 +6047,22 @@
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M136" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>56906.801935484</v>
+        <v>56906.802333333</v>
       </c>
       <c r="O136" t="n">
-        <v>227627.207741936</v>
+        <v>113813.604666666</v>
       </c>
       <c r="P136" t="n">
         <v>95900</v>
       </c>
       <c r="Q136" t="n">
-        <v>383600</v>
+        <v>191800</v>
       </c>
     </row>
     <row r="137">
@@ -6236,10 +6236,10 @@
         <v>12</v>
       </c>
       <c r="N140" t="n">
-        <v>200072.20015748</v>
+        <v>200072.20040323</v>
       </c>
       <c r="O140" t="n">
-        <v>2400866.40188976</v>
+        <v>2400866.40483876</v>
       </c>
       <c r="P140" t="n">
         <v>312000</v>
@@ -6278,10 +6278,10 @@
         <v>1</v>
       </c>
       <c r="N141" t="n">
-        <v>174389.79241379</v>
+        <v>174389.79407407</v>
       </c>
       <c r="O141" t="n">
-        <v>174389.79241379</v>
+        <v>174389.79407407</v>
       </c>
       <c r="P141" t="n">
         <v>368200</v>
@@ -7392,22 +7392,22 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N167" t="n">
         <v>47917.5</v>
       </c>
       <c r="O167" t="n">
-        <v>575010</v>
+        <v>527092.5</v>
       </c>
       <c r="P167" t="n">
         <v>72900</v>
       </c>
       <c r="Q167" t="n">
-        <v>874800</v>
+        <v>801900</v>
       </c>
     </row>
     <row r="168">
@@ -8145,22 +8145,22 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N184" t="n">
         <v>27000</v>
       </c>
       <c r="O184" t="n">
-        <v>918000</v>
+        <v>891000</v>
       </c>
       <c r="P184" t="n">
         <v>20000</v>
       </c>
       <c r="Q184" t="n">
-        <v>680000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="185">
@@ -9710,22 +9710,22 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M220" t="n">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="N220" t="n">
-        <v>1950.21469429</v>
+        <v>1950.2146835443</v>
       </c>
       <c r="O220" t="n">
-        <v>559711.61726123</v>
+        <v>551910.7554430369</v>
       </c>
       <c r="P220" t="n">
         <v>2900</v>
       </c>
       <c r="Q220" t="n">
-        <v>832300</v>
+        <v>820700</v>
       </c>
     </row>
     <row r="221">
@@ -9792,22 +9792,22 @@
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M222" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="N222" t="n">
         <v>2833</v>
       </c>
       <c r="O222" t="n">
-        <v>611928</v>
+        <v>603429</v>
       </c>
       <c r="P222" t="n">
         <v>3500</v>
       </c>
       <c r="Q222" t="n">
-        <v>756000</v>
+        <v>745500</v>
       </c>
     </row>
     <row r="223">
@@ -9967,10 +9967,10 @@
         <v>122</v>
       </c>
       <c r="N226" t="n">
-        <v>4937.3101612903</v>
+        <v>4937.3101616458</v>
       </c>
       <c r="O226" t="n">
-        <v>602351.8396774166</v>
+        <v>602351.8397207876</v>
       </c>
       <c r="P226" t="n">
         <v>7500</v>
@@ -10130,22 +10130,22 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M230" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N230" t="n">
         <v>6513</v>
       </c>
       <c r="O230" t="n">
-        <v>325650</v>
+        <v>306111</v>
       </c>
       <c r="P230" t="n">
         <v>11500</v>
       </c>
       <c r="Q230" t="n">
-        <v>575000</v>
+        <v>540500</v>
       </c>
     </row>
     <row r="231">
@@ -10425,22 +10425,22 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M237" t="n">
-        <v>606</v>
+        <v>527</v>
       </c>
       <c r="N237" t="n">
-        <v>1098.0566124294</v>
+        <v>1098.0571872808</v>
       </c>
       <c r="O237" t="n">
-        <v>665422.3071322164</v>
+        <v>578676.1376969815</v>
       </c>
       <c r="P237" t="n">
         <v>1500</v>
       </c>
       <c r="Q237" t="n">
-        <v>909000</v>
+        <v>790500</v>
       </c>
     </row>
     <row r="238">
@@ -11740,22 +11740,22 @@
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N268" t="n">
         <v>2913</v>
       </c>
       <c r="O268" t="n">
-        <v>769032</v>
+        <v>766119</v>
       </c>
       <c r="P268" t="n">
         <v>4950</v>
       </c>
       <c r="Q268" t="n">
-        <v>1306800</v>
+        <v>1301850</v>
       </c>
     </row>
     <row r="269">
@@ -11830,22 +11830,22 @@
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N270" t="n">
         <v>2804.33</v>
       </c>
       <c r="O270" t="n">
-        <v>1623707.07</v>
+        <v>1620902.74</v>
       </c>
       <c r="P270" t="n">
         <v>4900</v>
       </c>
       <c r="Q270" t="n">
-        <v>2837100</v>
+        <v>2832200</v>
       </c>
     </row>
     <row r="271">
@@ -11871,22 +11871,22 @@
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M271" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N271" t="n">
         <v>2850.95</v>
       </c>
       <c r="O271" t="n">
-        <v>461853.9</v>
+        <v>456152</v>
       </c>
       <c r="P271" t="n">
         <v>4900</v>
       </c>
       <c r="Q271" t="n">
-        <v>793800</v>
+        <v>784000</v>
       </c>
     </row>
     <row r="272">
@@ -11953,22 +11953,22 @@
         <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M273" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="N273" t="n">
         <v>2745.81</v>
       </c>
       <c r="O273" t="n">
-        <v>186715.08</v>
+        <v>170240.22</v>
       </c>
       <c r="P273" t="n">
         <v>5600</v>
       </c>
       <c r="Q273" t="n">
-        <v>380800</v>
+        <v>347200</v>
       </c>
     </row>
     <row r="274">
@@ -11999,22 +11999,22 @@
         <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M274" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N274" t="n">
-        <v>3381.2523076923</v>
+        <v>3381.262</v>
       </c>
       <c r="O274" t="n">
-        <v>27050.0184615384</v>
+        <v>20287.572</v>
       </c>
       <c r="P274" t="n">
         <v>5900</v>
       </c>
       <c r="Q274" t="n">
-        <v>47200</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="275">
@@ -12140,22 +12140,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M277" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N277" t="n">
-        <v>3247</v>
+        <v>3250.4653148346</v>
       </c>
       <c r="O277" t="n">
-        <v>327947</v>
+        <v>318545.6008537908</v>
       </c>
       <c r="P277" t="n">
         <v>5200</v>
       </c>
       <c r="Q277" t="n">
-        <v>525200</v>
+        <v>509600</v>
       </c>
     </row>
     <row r="278">
@@ -12192,10 +12192,10 @@
         <v>247</v>
       </c>
       <c r="N278" t="n">
-        <v>2582.255965161</v>
+        <v>2582.2559238797</v>
       </c>
       <c r="O278" t="n">
-        <v>637817.223394767</v>
+        <v>637817.2131982859</v>
       </c>
       <c r="P278" t="n">
         <v>4500</v>
@@ -12278,22 +12278,22 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M280" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="N280" t="n">
-        <v>5216.8962134973</v>
+        <v>5216.8961954233</v>
       </c>
       <c r="O280" t="n">
-        <v>704280.9888221355</v>
+        <v>631244.4396462193</v>
       </c>
       <c r="P280" t="n">
         <v>8500</v>
       </c>
       <c r="Q280" t="n">
-        <v>1147500</v>
+        <v>1028500</v>
       </c>
     </row>
     <row r="281">
@@ -12580,22 +12580,22 @@
         <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M287" t="n">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="N287" t="n">
-        <v>3158.86082365</v>
+        <v>3158.860824576</v>
       </c>
       <c r="O287" t="n">
-        <v>2277538.65385165</v>
+        <v>2226996.88132608</v>
       </c>
       <c r="P287" t="n">
         <v>5600</v>
       </c>
       <c r="Q287" t="n">
-        <v>4037600</v>
+        <v>3948000</v>
       </c>
     </row>
     <row r="288">
@@ -12678,10 +12678,10 @@
         <v>12</v>
       </c>
       <c r="N289" t="n">
-        <v>3841.6247693817</v>
+        <v>3841.6247787611</v>
       </c>
       <c r="O289" t="n">
-        <v>46099.4972325804</v>
+        <v>46099.4973451332</v>
       </c>
       <c r="P289" t="n">
         <v>6900</v>
@@ -12814,10 +12814,10 @@
         <v>104</v>
       </c>
       <c r="N292" t="n">
-        <v>3230.0675313059</v>
+        <v>3230.0675179856</v>
       </c>
       <c r="O292" t="n">
-        <v>335927.0232558136</v>
+        <v>335927.0218705024</v>
       </c>
       <c r="P292" t="n">
         <v>6200</v>
@@ -12987,22 +12987,22 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M296" t="n">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="N296" t="n">
         <v>1337.34</v>
       </c>
       <c r="O296" t="n">
-        <v>387828.6</v>
+        <v>382479.24</v>
       </c>
       <c r="P296" t="n">
         <v>2500</v>
       </c>
       <c r="Q296" t="n">
-        <v>725000</v>
+        <v>715000</v>
       </c>
     </row>
     <row r="297">
@@ -13033,22 +13033,22 @@
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M297" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="N297" t="n">
-        <v>2694.8232839963</v>
+        <v>2694.8232527881</v>
       </c>
       <c r="O297" t="n">
-        <v>293735.7379555966</v>
+        <v>269482.32527881</v>
       </c>
       <c r="P297" t="n">
         <v>4900</v>
       </c>
       <c r="Q297" t="n">
-        <v>534100</v>
+        <v>490000</v>
       </c>
     </row>
     <row r="298">
@@ -13120,22 +13120,22 @@
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M299" t="n">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="N299" t="n">
         <v>1026.13</v>
       </c>
       <c r="O299" t="n">
-        <v>514091.1300000001</v>
+        <v>509986.61</v>
       </c>
       <c r="P299" t="n">
         <v>1900</v>
       </c>
       <c r="Q299" t="n">
-        <v>951900</v>
+        <v>944300</v>
       </c>
     </row>
     <row r="300">
@@ -13212,22 +13212,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="M301" t="n">
-        <v>4985</v>
+        <v>4605</v>
       </c>
       <c r="N301" t="n">
         <v>156.25</v>
       </c>
       <c r="O301" t="n">
-        <v>778906.25</v>
+        <v>719531.25</v>
       </c>
       <c r="P301" t="n">
         <v>250</v>
       </c>
       <c r="Q301" t="n">
-        <v>1246250</v>
+        <v>1151250</v>
       </c>
     </row>
     <row r="302">
@@ -13258,22 +13258,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N302" t="n">
         <v>7507.39</v>
       </c>
       <c r="O302" t="n">
-        <v>1216197.18</v>
+        <v>1208689.79</v>
       </c>
       <c r="P302" t="n">
         <v>13500</v>
       </c>
       <c r="Q302" t="n">
-        <v>2187000</v>
+        <v>2173500</v>
       </c>
     </row>
     <row r="303">
@@ -13307,22 +13307,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M303" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N303" t="n">
         <v>8796</v>
       </c>
       <c r="O303" t="n">
-        <v>791640</v>
+        <v>765252</v>
       </c>
       <c r="P303" t="n">
         <v>14900</v>
       </c>
       <c r="Q303" t="n">
-        <v>1341000</v>
+        <v>1296300</v>
       </c>
     </row>
     <row r="304">
@@ -13489,22 +13489,22 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M307" t="n">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="N307" t="n">
-        <v>3795.7100070872</v>
+        <v>3795.7100071023</v>
       </c>
       <c r="O307" t="n">
-        <v>1134917.292119073</v>
+        <v>1089368.77203836</v>
       </c>
       <c r="P307" t="n">
         <v>6200</v>
       </c>
       <c r="Q307" t="n">
-        <v>1853800</v>
+        <v>1779400</v>
       </c>
     </row>
     <row r="308">
@@ -13622,22 +13622,22 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M310" t="n">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="N310" t="n">
         <v>4357.55</v>
       </c>
       <c r="O310" t="n">
-        <v>1111175.25</v>
+        <v>1076314.85</v>
       </c>
       <c r="P310" t="n">
         <v>7500</v>
       </c>
       <c r="Q310" t="n">
-        <v>1912500</v>
+        <v>1852500</v>
       </c>
     </row>
     <row r="311">
@@ -13668,22 +13668,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M311" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N311" t="n">
         <v>2379.63</v>
       </c>
       <c r="O311" t="n">
-        <v>138018.54</v>
+        <v>130879.65</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
       </c>
       <c r="Q311" t="n">
-        <v>261000</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="312">
@@ -13761,10 +13761,10 @@
         <v>42</v>
       </c>
       <c r="N313" t="n">
-        <v>4890.9300468384</v>
+        <v>4890.9300473934</v>
       </c>
       <c r="O313" t="n">
-        <v>205419.0619672128</v>
+        <v>205419.0619905228</v>
       </c>
       <c r="P313" t="n">
         <v>8200</v>
@@ -13850,22 +13850,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M315" t="n">
-        <v>873</v>
+        <v>849</v>
       </c>
       <c r="N315" t="n">
         <v>1203.38</v>
       </c>
       <c r="O315" t="n">
-        <v>1050550.74</v>
+        <v>1021669.62</v>
       </c>
       <c r="P315" t="n">
         <v>1900</v>
       </c>
       <c r="Q315" t="n">
-        <v>1658700</v>
+        <v>1613100</v>
       </c>
     </row>
     <row r="316">
@@ -14075,22 +14075,22 @@
         <v>0</v>
       </c>
       <c r="L320" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M320" t="n">
-        <v>1580</v>
+        <v>1572</v>
       </c>
       <c r="N320" t="n">
-        <v>2267.0481583333</v>
+        <v>2267.0481475272</v>
       </c>
       <c r="O320" t="n">
-        <v>3581936.090166614</v>
+        <v>3563799.687912758</v>
       </c>
       <c r="P320" t="n">
         <v>3900</v>
       </c>
       <c r="Q320" t="n">
-        <v>6162000</v>
+        <v>6130800</v>
       </c>
     </row>
     <row r="321">
@@ -14341,22 +14341,22 @@
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M326" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N326" t="n">
         <v>8662</v>
       </c>
       <c r="O326" t="n">
-        <v>329156</v>
+        <v>320494</v>
       </c>
       <c r="P326" t="n">
         <v>14200</v>
       </c>
       <c r="Q326" t="n">
-        <v>539600</v>
+        <v>525400</v>
       </c>
     </row>
     <row r="327">
@@ -14428,22 +14428,22 @@
         <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M328" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="N328" t="n">
         <v>10716.34</v>
       </c>
       <c r="O328" t="n">
-        <v>353639.22</v>
+        <v>289341.18</v>
       </c>
       <c r="P328" t="n">
         <v>39000</v>
       </c>
       <c r="Q328" t="n">
-        <v>1287000</v>
+        <v>1053000</v>
       </c>
     </row>
     <row r="329">
@@ -14469,22 +14469,22 @@
         <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M329" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N329" t="n">
-        <v>9047</v>
+        <v>9237.463157894699</v>
       </c>
       <c r="O329" t="n">
-        <v>805183</v>
+        <v>785184.3684210494</v>
       </c>
       <c r="P329" t="n">
         <v>5900</v>
       </c>
       <c r="Q329" t="n">
-        <v>525100</v>
+        <v>501500</v>
       </c>
     </row>
     <row r="330">
@@ -14510,22 +14510,22 @@
         <v>0</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M330" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N330" t="n">
         <v>7180.21</v>
       </c>
       <c r="O330" t="n">
-        <v>157964.62</v>
+        <v>136423.99</v>
       </c>
       <c r="P330" t="n">
         <v>15900</v>
       </c>
       <c r="Q330" t="n">
-        <v>349800</v>
+        <v>302100</v>
       </c>
     </row>
     <row r="331">
@@ -14592,22 +14592,22 @@
         <v>0</v>
       </c>
       <c r="L332" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M332" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N332" t="n">
-        <v>8500</v>
+        <v>10625</v>
       </c>
       <c r="O332" t="n">
-        <v>110500</v>
+        <v>106250</v>
       </c>
       <c r="P332" t="n">
         <v>9900</v>
       </c>
       <c r="Q332" t="n">
-        <v>128700</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="333">
@@ -14641,22 +14641,22 @@
         <v>0</v>
       </c>
       <c r="L333" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M333" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="N333" t="n">
-        <v>3594.2541140405</v>
+        <v>3594.2540923077</v>
       </c>
       <c r="O333" t="n">
-        <v>219249.5009564705</v>
+        <v>197683.9750769235</v>
       </c>
       <c r="P333" t="n">
         <v>6500</v>
       </c>
       <c r="Q333" t="n">
-        <v>396500</v>
+        <v>357500</v>
       </c>
     </row>
     <row r="334">
@@ -14769,22 +14769,22 @@
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M336" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N336" t="n">
         <v>2953.73</v>
       </c>
       <c r="O336" t="n">
-        <v>587792.27</v>
+        <v>581884.8100000001</v>
       </c>
       <c r="P336" t="n">
         <v>4900</v>
       </c>
       <c r="Q336" t="n">
-        <v>975100</v>
+        <v>965300</v>
       </c>
     </row>
     <row r="337">
@@ -14810,22 +14810,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N337" t="n">
-        <v>3240.8500305344</v>
+        <v>3240.850030581</v>
       </c>
       <c r="O337" t="n">
-        <v>777804.007328256</v>
+        <v>774563.1573088589</v>
       </c>
       <c r="P337" t="n">
         <v>5200</v>
       </c>
       <c r="Q337" t="n">
-        <v>1248000</v>
+        <v>1242800</v>
       </c>
     </row>
     <row r="338">
@@ -14954,10 +14954,10 @@
         <v>37</v>
       </c>
       <c r="N340" t="n">
-        <v>14822.378858502</v>
+        <v>14822.378857823</v>
       </c>
       <c r="O340" t="n">
-        <v>548428.0177645739</v>
+        <v>548428.017739451</v>
       </c>
       <c r="P340" t="n">
         <v>24900</v>
@@ -15036,22 +15036,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M342" t="n">
-        <v>668</v>
+        <v>521</v>
       </c>
       <c r="N342" t="n">
         <v>2090.85</v>
       </c>
       <c r="O342" t="n">
-        <v>1396687.8</v>
+        <v>1089332.85</v>
       </c>
       <c r="P342" t="n">
         <v>2900</v>
       </c>
       <c r="Q342" t="n">
-        <v>1937200</v>
+        <v>1510900</v>
       </c>
     </row>
     <row r="343">
@@ -15121,22 +15121,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M344" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N344" t="n">
-        <v>5191.4800270636</v>
+        <v>5191.4800271739</v>
       </c>
       <c r="O344" t="n">
-        <v>1733954.329039242</v>
+        <v>1723571.369021735</v>
       </c>
       <c r="P344" t="n">
         <v>9100</v>
       </c>
       <c r="Q344" t="n">
-        <v>3039400</v>
+        <v>3021200</v>
       </c>
     </row>
     <row r="345">
@@ -15258,22 +15258,22 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M347" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N347" t="n">
         <v>1381.75</v>
       </c>
       <c r="O347" t="n">
-        <v>239042.75</v>
+        <v>233515.75</v>
       </c>
       <c r="P347" t="n">
         <v>2500</v>
       </c>
       <c r="Q347" t="n">
-        <v>432500</v>
+        <v>422500</v>
       </c>
     </row>
     <row r="348">
@@ -15433,22 +15433,22 @@
         <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M351" t="n">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="N351" t="n">
         <v>1441.01</v>
       </c>
       <c r="O351" t="n">
-        <v>827139.74</v>
+        <v>824257.72</v>
       </c>
       <c r="P351" t="n">
         <v>2100</v>
       </c>
       <c r="Q351" t="n">
-        <v>1205400</v>
+        <v>1201200</v>
       </c>
     </row>
     <row r="352">
@@ -15610,22 +15610,22 @@
         <v>0</v>
       </c>
       <c r="L355" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M355" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="N355" t="n">
-        <v>4372.2107879391</v>
+        <v>4372.210788556</v>
       </c>
       <c r="O355" t="n">
-        <v>913792.0546792719</v>
+        <v>900675.422442536</v>
       </c>
       <c r="P355" t="n">
         <v>7500</v>
       </c>
       <c r="Q355" t="n">
-        <v>1567500</v>
+        <v>1545000</v>
       </c>
     </row>
     <row r="356">
@@ -15706,10 +15706,10 @@
         <v>13</v>
       </c>
       <c r="N357" t="n">
-        <v>1592.5672645976</v>
+        <v>1592.5670868347</v>
       </c>
       <c r="O357" t="n">
-        <v>20703.3744397688</v>
+        <v>20703.3721288511</v>
       </c>
       <c r="P357" t="n">
         <v>3900</v>
@@ -15782,22 +15782,22 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M359" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="N359" t="n">
         <v>2224.56</v>
       </c>
       <c r="O359" t="n">
-        <v>215782.32</v>
+        <v>209108.64</v>
       </c>
       <c r="P359" t="n">
         <v>3900</v>
       </c>
       <c r="Q359" t="n">
-        <v>378300</v>
+        <v>366600</v>
       </c>
     </row>
     <row r="360">
@@ -16272,22 +16272,22 @@
         <v>0</v>
       </c>
       <c r="L370" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M370" t="n">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="N370" t="n">
         <v>4648.6</v>
       </c>
       <c r="O370" t="n">
-        <v>1478254.8</v>
+        <v>1431768.8</v>
       </c>
       <c r="P370" t="n">
         <v>8900</v>
       </c>
       <c r="Q370" t="n">
-        <v>2830200</v>
+        <v>2741200</v>
       </c>
     </row>
     <row r="371">
@@ -16706,22 +16706,22 @@
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M380" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N380" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O380" t="n">
-        <v>659001.7</v>
+        <v>649587.39</v>
       </c>
       <c r="P380" t="n">
         <v>16900</v>
       </c>
       <c r="Q380" t="n">
-        <v>1183000</v>
+        <v>1166100</v>
       </c>
     </row>
     <row r="381">
@@ -16750,22 +16750,22 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M381" t="n">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="N381" t="n">
         <v>1387.55</v>
       </c>
       <c r="O381" t="n">
-        <v>706262.95</v>
+        <v>678511.95</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
       </c>
       <c r="Q381" t="n">
-        <v>1170700</v>
+        <v>1124700</v>
       </c>
     </row>
     <row r="382">
@@ -16920,22 +16920,22 @@
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M385" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N385" t="n">
         <v>13304.13</v>
       </c>
       <c r="O385" t="n">
-        <v>372515.64</v>
+        <v>332603.25</v>
       </c>
       <c r="P385" t="n">
         <v>20900</v>
       </c>
       <c r="Q385" t="n">
-        <v>585200</v>
+        <v>522500</v>
       </c>
     </row>
     <row r="386">
@@ -17101,22 +17101,22 @@
         <v>0</v>
       </c>
       <c r="L389" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M389" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N389" t="n">
         <v>5853</v>
       </c>
       <c r="O389" t="n">
-        <v>1053540</v>
+        <v>1030128</v>
       </c>
       <c r="P389" t="n">
         <v>9900</v>
       </c>
       <c r="Q389" t="n">
-        <v>1782000</v>
+        <v>1742400</v>
       </c>
     </row>
     <row r="390">
@@ -17150,22 +17150,22 @@
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M390" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N390" t="n">
         <v>3761.6</v>
       </c>
       <c r="O390" t="n">
-        <v>278358.4</v>
+        <v>255788.8</v>
       </c>
       <c r="P390" t="n">
         <v>6900</v>
       </c>
       <c r="Q390" t="n">
-        <v>510600</v>
+        <v>469200</v>
       </c>
     </row>
     <row r="391">
@@ -17235,22 +17235,22 @@
         <v>0</v>
       </c>
       <c r="L392" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M392" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N392" t="n">
         <v>45945</v>
       </c>
       <c r="O392" t="n">
-        <v>735120</v>
+        <v>689175</v>
       </c>
       <c r="P392" t="n">
         <v>73900</v>
       </c>
       <c r="Q392" t="n">
-        <v>1182400</v>
+        <v>1108500</v>
       </c>
     </row>
     <row r="393">
@@ -17286,22 +17286,22 @@
         <v>0</v>
       </c>
       <c r="L393" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M393" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="N393" t="n">
         <v>11921.4</v>
       </c>
       <c r="O393" t="n">
-        <v>1502096.4</v>
+        <v>1168297.2</v>
       </c>
       <c r="P393" t="n">
         <v>19900</v>
       </c>
       <c r="Q393" t="n">
-        <v>2507400</v>
+        <v>1950200</v>
       </c>
     </row>
     <row r="394">
@@ -17456,22 +17456,22 @@
         <v>0</v>
       </c>
       <c r="L397" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M397" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N397" t="n">
         <v>9678.9</v>
       </c>
       <c r="O397" t="n">
-        <v>319403.7</v>
+        <v>300045.9</v>
       </c>
       <c r="P397" t="n">
         <v>15500</v>
       </c>
       <c r="Q397" t="n">
-        <v>511500</v>
+        <v>480500</v>
       </c>
     </row>
     <row r="398">
@@ -17626,22 +17626,22 @@
         <v>0</v>
       </c>
       <c r="L401" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M401" t="n">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="N401" t="n">
         <v>3751</v>
       </c>
       <c r="O401" t="n">
-        <v>3297129</v>
+        <v>3289627</v>
       </c>
       <c r="P401" t="n">
         <v>6400</v>
       </c>
       <c r="Q401" t="n">
-        <v>5625600</v>
+        <v>5612800</v>
       </c>
     </row>
     <row r="402">
@@ -17675,22 +17675,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M402" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N402" t="n">
         <v>9903</v>
       </c>
       <c r="O402" t="n">
-        <v>742725</v>
+        <v>713016</v>
       </c>
       <c r="P402" t="n">
         <v>15900</v>
       </c>
       <c r="Q402" t="n">
-        <v>1192500</v>
+        <v>1144800</v>
       </c>
     </row>
     <row r="403">
@@ -17721,22 +17721,22 @@
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M403" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N403" t="n">
         <v>12754</v>
       </c>
       <c r="O403" t="n">
-        <v>1033074</v>
+        <v>1007566</v>
       </c>
       <c r="P403" t="n">
         <v>21500</v>
       </c>
       <c r="Q403" t="n">
-        <v>1741500</v>
+        <v>1698500</v>
       </c>
     </row>
     <row r="404">
@@ -17767,22 +17767,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M404" t="n">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="N404" t="n">
-        <v>1630.9233376736</v>
+        <v>1630.9233676374</v>
       </c>
       <c r="O404" t="n">
-        <v>1076409.402864576</v>
+        <v>1058469.265596672</v>
       </c>
       <c r="P404" t="n">
         <v>2500</v>
       </c>
       <c r="Q404" t="n">
-        <v>1650000</v>
+        <v>1622500</v>
       </c>
     </row>
     <row r="405">
@@ -17854,22 +17854,22 @@
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M406" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N406" t="n">
-        <v>1467.3258333333</v>
+        <v>1467.3254237288</v>
       </c>
       <c r="O406" t="n">
-        <v>312540.4024999929</v>
+        <v>306671.0135593192</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
       </c>
       <c r="Q406" t="n">
-        <v>532500</v>
+        <v>522500</v>
       </c>
     </row>
     <row r="407">
@@ -17900,22 +17900,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M407" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="N407" t="n">
-        <v>1690.6000587084</v>
+        <v>1690.5998749177</v>
       </c>
       <c r="O407" t="n">
-        <v>439556.015264184</v>
+        <v>420959.3688545073</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
       </c>
       <c r="Q407" t="n">
-        <v>754000</v>
+        <v>722100</v>
       </c>
     </row>
     <row r="408">
@@ -17946,22 +17946,22 @@
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M408" t="n">
-        <v>1721</v>
+        <v>1692</v>
       </c>
       <c r="N408" t="n">
-        <v>1550.1933547279</v>
+        <v>1550.1933908991</v>
       </c>
       <c r="O408" t="n">
-        <v>2667882.763486716</v>
+        <v>2622927.217401277</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
       </c>
       <c r="Q408" t="n">
-        <v>4302500</v>
+        <v>4230000</v>
       </c>
     </row>
     <row r="409">
@@ -18038,22 +18038,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M410" t="n">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="N410" t="n">
-        <v>2403.5109560769</v>
+        <v>2403.5111708633</v>
       </c>
       <c r="O410" t="n">
-        <v>2278528.386360901</v>
+        <v>2268914.545294955</v>
       </c>
       <c r="P410" t="n">
         <v>3500</v>
       </c>
       <c r="Q410" t="n">
-        <v>3318000</v>
+        <v>3304000</v>
       </c>
     </row>
     <row r="411">
@@ -18337,22 +18337,22 @@
         <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M417" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N417" t="n">
-        <v>101770.01727273</v>
+        <v>101770.01666667</v>
       </c>
       <c r="O417" t="n">
-        <v>1017700.1727273</v>
+        <v>610620.10000002</v>
       </c>
       <c r="P417" t="n">
         <v>136900</v>
       </c>
       <c r="Q417" t="n">
-        <v>1369000</v>
+        <v>821400</v>
       </c>
     </row>
     <row r="418">
@@ -18906,22 +18906,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M430" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N430" t="n">
         <v>59880</v>
       </c>
       <c r="O430" t="n">
-        <v>239520</v>
+        <v>119760</v>
       </c>
       <c r="P430" t="n">
         <v>40000</v>
       </c>
       <c r="Q430" t="n">
-        <v>160000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="431">
@@ -19487,22 +19487,22 @@
         <v>0</v>
       </c>
       <c r="L443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N443" t="n">
         <v>9306</v>
       </c>
       <c r="O443" t="n">
-        <v>65142</v>
+        <v>55836</v>
       </c>
       <c r="P443" t="n">
         <v>14900</v>
       </c>
       <c r="Q443" t="n">
-        <v>104300</v>
+        <v>89400</v>
       </c>
     </row>
     <row r="444">
@@ -19615,22 +19615,22 @@
         <v>0</v>
       </c>
       <c r="L446" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M446" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="N446" t="n">
-        <v>204.05079096045</v>
+        <v>204.05083832335</v>
       </c>
       <c r="O446" t="n">
-        <v>32240.0249717511</v>
+        <v>30199.5240718558</v>
       </c>
       <c r="P446" t="n">
         <v>500</v>
       </c>
       <c r="Q446" t="n">
-        <v>79000</v>
+        <v>74000</v>
       </c>
     </row>
     <row r="447">
@@ -19661,22 +19661,22 @@
         <v>0</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N447" t="n">
         <v>7028</v>
       </c>
       <c r="O447" t="n">
-        <v>217868</v>
+        <v>210840</v>
       </c>
       <c r="P447" t="n">
         <v>15900</v>
       </c>
       <c r="Q447" t="n">
-        <v>492900</v>
+        <v>477000</v>
       </c>
     </row>
     <row r="448">
@@ -21150,22 +21150,22 @@
         <v>0</v>
       </c>
       <c r="L482" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M482" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N482" t="n">
-        <v>2661.82</v>
+        <v>2679.7246188341</v>
       </c>
       <c r="O482" t="n">
-        <v>138414.64</v>
+        <v>131306.5063228709</v>
       </c>
       <c r="P482" t="n">
         <v>3200</v>
       </c>
       <c r="Q482" t="n">
-        <v>166400</v>
+        <v>156800</v>
       </c>
     </row>
     <row r="483">
@@ -21396,22 +21396,22 @@
         <v>0</v>
       </c>
       <c r="L488" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M488" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N488" t="n">
         <v>2286.55</v>
       </c>
       <c r="O488" t="n">
-        <v>155485.4</v>
+        <v>146339.2</v>
       </c>
       <c r="P488" t="n">
         <v>3200</v>
       </c>
       <c r="Q488" t="n">
-        <v>217600</v>
+        <v>204800</v>
       </c>
     </row>
     <row r="489">
@@ -21437,22 +21437,22 @@
         <v>0</v>
       </c>
       <c r="L489" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M489" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="N489" t="n">
         <v>1969</v>
       </c>
       <c r="O489" t="n">
-        <v>309133</v>
+        <v>297319</v>
       </c>
       <c r="P489" t="n">
         <v>1500</v>
       </c>
       <c r="Q489" t="n">
-        <v>235500</v>
+        <v>226500</v>
       </c>
     </row>
     <row r="490">
@@ -21519,22 +21519,22 @@
         <v>0</v>
       </c>
       <c r="L491" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M491" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N491" t="n">
-        <v>8794.48</v>
+        <v>8799.395863611</v>
       </c>
       <c r="O491" t="n">
-        <v>1389527.84</v>
+        <v>1381505.150586927</v>
       </c>
       <c r="P491" t="n">
         <v>14500</v>
       </c>
       <c r="Q491" t="n">
-        <v>2291000</v>
+        <v>2276500</v>
       </c>
     </row>
     <row r="492">
@@ -21770,22 +21770,22 @@
         <v>0</v>
       </c>
       <c r="L497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M497" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N497" t="n">
-        <v>14975</v>
+        <v>15723.75</v>
       </c>
       <c r="O497" t="n">
-        <v>299500</v>
+        <v>298751.25</v>
       </c>
       <c r="P497" t="n">
         <v>19900</v>
       </c>
       <c r="Q497" t="n">
-        <v>398000</v>
+        <v>378100</v>
       </c>
     </row>
     <row r="498">
@@ -21852,22 +21852,22 @@
         <v>0</v>
       </c>
       <c r="L499" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M499" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="N499" t="n">
         <v>2517.22</v>
       </c>
       <c r="O499" t="n">
-        <v>566374.5</v>
+        <v>543719.5199999999</v>
       </c>
       <c r="P499" t="n">
         <v>4200</v>
       </c>
       <c r="Q499" t="n">
-        <v>945000</v>
+        <v>907200</v>
       </c>
     </row>
     <row r="500">
@@ -21981,10 +21981,10 @@
         <v>461</v>
       </c>
       <c r="N502" t="n">
-        <v>2029.8737110341</v>
+        <v>2029.8737332006</v>
       </c>
       <c r="O502" t="n">
-        <v>935771.7807867201</v>
+        <v>935771.7910054766</v>
       </c>
       <c r="P502" t="n">
         <v>3600</v>
@@ -22767,22 +22767,22 @@
         <v>0</v>
       </c>
       <c r="L521" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M521" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N521" t="n">
-        <v>11431.604819277</v>
+        <v>11431.604756098</v>
       </c>
       <c r="O521" t="n">
-        <v>102884.443373493</v>
+        <v>91452.838048784</v>
       </c>
       <c r="P521" t="n">
         <v>48900</v>
       </c>
       <c r="Q521" t="n">
-        <v>440100</v>
+        <v>391200</v>
       </c>
     </row>
     <row r="522">
@@ -22972,22 +22972,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M526" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N526" t="n">
-        <v>1732.9153666245</v>
+        <v>1733.4632374328</v>
       </c>
       <c r="O526" t="n">
-        <v>306726.0198925365</v>
+        <v>305089.5297881728</v>
       </c>
       <c r="P526" t="n">
         <v>1900</v>
       </c>
       <c r="Q526" t="n">
-        <v>336300</v>
+        <v>334400</v>
       </c>
     </row>
     <row r="527">
@@ -23233,22 +23233,22 @@
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M532" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="N532" t="n">
         <v>1651</v>
       </c>
       <c r="O532" t="n">
-        <v>186563</v>
+        <v>179959</v>
       </c>
       <c r="P532" t="n">
         <v>2500</v>
       </c>
       <c r="Q532" t="n">
-        <v>282500</v>
+        <v>272500</v>
       </c>
     </row>
     <row r="533">
@@ -23590,10 +23590,10 @@
         <v>280</v>
       </c>
       <c r="N540" t="n">
-        <v>4285.1953699789</v>
+        <v>4285.1953813559</v>
       </c>
       <c r="O540" t="n">
-        <v>1199854.703594092</v>
+        <v>1199854.706779652</v>
       </c>
       <c r="P540" t="n">
         <v>6900</v>
@@ -23756,22 +23756,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M544" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N544" t="n">
-        <v>12132.858175439</v>
+        <v>12132.858149466</v>
       </c>
       <c r="O544" t="n">
-        <v>448915.752491243</v>
+        <v>400384.318932378</v>
       </c>
       <c r="P544" t="n">
         <v>15900</v>
       </c>
       <c r="Q544" t="n">
-        <v>588300</v>
+        <v>524700</v>
       </c>
     </row>
     <row r="545">
@@ -24012,22 +24012,22 @@
         <v>0</v>
       </c>
       <c r="L550" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M550" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N550" t="n">
         <v>23030</v>
       </c>
       <c r="O550" t="n">
-        <v>1289680</v>
+        <v>1243620</v>
       </c>
       <c r="P550" t="n">
         <v>37500</v>
       </c>
       <c r="Q550" t="n">
-        <v>2100000</v>
+        <v>2025000</v>
       </c>
     </row>
     <row r="551">
@@ -24182,10 +24182,10 @@
         <v>10</v>
       </c>
       <c r="N554" t="n">
-        <v>78951.191923077</v>
+        <v>78951.191162791</v>
       </c>
       <c r="O554" t="n">
-        <v>789511.91923077</v>
+        <v>789511.91162791</v>
       </c>
       <c r="P554" t="n">
         <v>108000</v>
@@ -25251,22 +25251,22 @@
         <v>0</v>
       </c>
       <c r="L579" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M579" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N579" t="n">
         <v>21418.04</v>
       </c>
       <c r="O579" t="n">
-        <v>771049.4400000001</v>
+        <v>749631.4</v>
       </c>
       <c r="P579" t="n">
         <v>34900</v>
       </c>
       <c r="Q579" t="n">
-        <v>1256400</v>
+        <v>1221500</v>
       </c>
     </row>
     <row r="580">
@@ -25384,22 +25384,22 @@
         <v>0</v>
       </c>
       <c r="L582" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M582" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N582" t="n">
         <v>4793.53</v>
       </c>
       <c r="O582" t="n">
-        <v>1337394.87</v>
+        <v>1327807.81</v>
       </c>
       <c r="P582" t="n">
         <v>7900</v>
       </c>
       <c r="Q582" t="n">
-        <v>2204100</v>
+        <v>2188300</v>
       </c>
     </row>
     <row r="583">
@@ -25788,22 +25788,22 @@
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M591" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N591" t="n">
         <v>16974.69</v>
       </c>
       <c r="O591" t="n">
-        <v>1442848.65</v>
+        <v>1391924.58</v>
       </c>
       <c r="P591" t="n">
         <v>26900</v>
       </c>
       <c r="Q591" t="n">
-        <v>2286500</v>
+        <v>2205800</v>
       </c>
     </row>
     <row r="592">
@@ -25911,22 +25911,22 @@
         <v>0</v>
       </c>
       <c r="L594" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M594" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="N594" t="n">
         <v>4100.45</v>
       </c>
       <c r="O594" t="n">
-        <v>127113.95</v>
+        <v>77908.55</v>
       </c>
       <c r="P594" t="n">
         <v>26900</v>
       </c>
       <c r="Q594" t="n">
-        <v>833900</v>
+        <v>511100</v>
       </c>
     </row>
     <row r="595">
@@ -26085,22 +26085,22 @@
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M598" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="N598" t="n">
-        <v>1560.9996939288</v>
+        <v>1560.9997428139</v>
       </c>
       <c r="O598" t="n">
-        <v>121757.9761264464</v>
+        <v>112391.9814826008</v>
       </c>
       <c r="P598" t="n">
         <v>2900</v>
       </c>
       <c r="Q598" t="n">
-        <v>226200</v>
+        <v>208800</v>
       </c>
     </row>
     <row r="599">
@@ -26172,22 +26172,22 @@
         <v>0</v>
       </c>
       <c r="L600" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M600" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N600" t="n">
         <v>5668</v>
       </c>
       <c r="O600" t="n">
-        <v>124696</v>
+        <v>113360</v>
       </c>
       <c r="P600" t="n">
         <v>9900</v>
       </c>
       <c r="Q600" t="n">
-        <v>217800</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="601">
@@ -26354,22 +26354,22 @@
         <v>0</v>
       </c>
       <c r="L604" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M604" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="N604" t="n">
-        <v>7969.9501652893</v>
+        <v>7969.9501660377</v>
       </c>
       <c r="O604" t="n">
-        <v>1123762.973305791</v>
+        <v>1083913.222581127</v>
       </c>
       <c r="P604" t="n">
         <v>12900</v>
       </c>
       <c r="Q604" t="n">
-        <v>1818900</v>
+        <v>1754400</v>
       </c>
     </row>
     <row r="605">
@@ -26605,22 +26605,22 @@
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M610" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N610" t="n">
         <v>21508</v>
       </c>
       <c r="O610" t="n">
-        <v>172064</v>
+        <v>129048</v>
       </c>
       <c r="P610" t="n">
         <v>36900</v>
       </c>
       <c r="Q610" t="n">
-        <v>295200</v>
+        <v>221400</v>
       </c>
     </row>
     <row r="611">
@@ -26646,22 +26646,22 @@
         <v>0</v>
       </c>
       <c r="L611" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M611" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N611" t="n">
         <v>14954</v>
       </c>
       <c r="O611" t="n">
-        <v>643022</v>
+        <v>628068</v>
       </c>
       <c r="P611" t="n">
         <v>25500</v>
       </c>
       <c r="Q611" t="n">
-        <v>1096500</v>
+        <v>1071000</v>
       </c>
     </row>
     <row r="612">
@@ -26815,22 +26815,22 @@
         <v>0</v>
       </c>
       <c r="L615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M615" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N615" t="n">
         <v>12981.59</v>
       </c>
       <c r="O615" t="n">
-        <v>350502.93</v>
+        <v>337521.34</v>
       </c>
       <c r="P615" t="n">
         <v>21900</v>
       </c>
       <c r="Q615" t="n">
-        <v>591300</v>
+        <v>569400</v>
       </c>
     </row>
     <row r="616">
@@ -26861,22 +26861,22 @@
         <v>0</v>
       </c>
       <c r="L616" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M616" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N616" t="n">
         <v>13878.97</v>
       </c>
       <c r="O616" t="n">
-        <v>749464.38</v>
+        <v>735585.4099999999</v>
       </c>
       <c r="P616" t="n">
         <v>21900</v>
       </c>
       <c r="Q616" t="n">
-        <v>1182600</v>
+        <v>1160700</v>
       </c>
     </row>
     <row r="617">
@@ -26908,10 +26908,10 @@
         <v>22</v>
       </c>
       <c r="N617" t="n">
-        <v>3501.3963636364</v>
+        <v>3501.3965217391</v>
       </c>
       <c r="O617" t="n">
-        <v>77030.7200000008</v>
+        <v>77030.7234782602</v>
       </c>
       <c r="P617" t="n">
         <v>4600</v>
@@ -27148,22 +27148,22 @@
         <v>0</v>
       </c>
       <c r="L623" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M623" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N623" t="n">
         <v>7836</v>
       </c>
       <c r="O623" t="n">
-        <v>86196</v>
+        <v>70524</v>
       </c>
       <c r="P623" t="n">
         <v>13400</v>
       </c>
       <c r="Q623" t="n">
-        <v>147400</v>
+        <v>120600</v>
       </c>
     </row>
     <row r="624">
@@ -27410,22 +27410,22 @@
         <v>0</v>
       </c>
       <c r="L629" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M629" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N629" t="n">
-        <v>4437</v>
+        <v>4634.2</v>
       </c>
       <c r="O629" t="n">
-        <v>150858</v>
+        <v>148294.4</v>
       </c>
       <c r="P629" t="n">
         <v>4900</v>
       </c>
       <c r="Q629" t="n">
-        <v>166600</v>
+        <v>156800</v>
       </c>
     </row>
     <row r="630">
@@ -27459,22 +27459,22 @@
         <v>0</v>
       </c>
       <c r="L630" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M630" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N630" t="n">
-        <v>3590.77</v>
+        <v>3656.0567272727</v>
       </c>
       <c r="O630" t="n">
-        <v>100541.56</v>
+        <v>91401.4181818175</v>
       </c>
       <c r="P630" t="n">
         <v>3900</v>
       </c>
       <c r="Q630" t="n">
-        <v>109200</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="631">
@@ -27909,22 +27909,22 @@
         <v>0</v>
       </c>
       <c r="L640" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M640" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N640" t="n">
-        <v>4163.1601960784</v>
+        <v>4163.1601980198</v>
       </c>
       <c r="O640" t="n">
-        <v>62447.402941176</v>
+        <v>58284.2427722772</v>
       </c>
       <c r="P640" t="n">
         <v>6700</v>
       </c>
       <c r="Q640" t="n">
-        <v>100500</v>
+        <v>93800</v>
       </c>
     </row>
     <row r="641">
@@ -27955,22 +27955,22 @@
         <v>0</v>
       </c>
       <c r="L641" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M641" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N641" t="n">
         <v>8878.450000000001</v>
       </c>
       <c r="O641" t="n">
-        <v>541585.4500000001</v>
+        <v>514950.1</v>
       </c>
       <c r="P641" t="n">
         <v>14100</v>
       </c>
       <c r="Q641" t="n">
-        <v>860100</v>
+        <v>817800</v>
       </c>
     </row>
     <row r="642">
@@ -28099,10 +28099,10 @@
         <v>20</v>
       </c>
       <c r="N644" t="n">
-        <v>5218.1705269461</v>
+        <v>5218.1705339806</v>
       </c>
       <c r="O644" t="n">
-        <v>104363.410538922</v>
+        <v>104363.410679612</v>
       </c>
       <c r="P644" t="n">
         <v>8500</v>
@@ -28145,10 +28145,10 @@
         <v>133</v>
       </c>
       <c r="N645" t="n">
-        <v>1595.0094189602</v>
+        <v>1595.0094144838</v>
       </c>
       <c r="O645" t="n">
-        <v>212136.2527217066</v>
+        <v>212136.2521263454</v>
       </c>
       <c r="P645" t="n">
         <v>2600</v>
@@ -28185,22 +28185,22 @@
         <v>0</v>
       </c>
       <c r="L646" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M646" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N646" t="n">
-        <v>3610.6500253807</v>
+        <v>3610.6500255754</v>
       </c>
       <c r="O646" t="n">
-        <v>274409.4019289332</v>
+        <v>270798.751918155</v>
       </c>
       <c r="P646" t="n">
         <v>5800</v>
       </c>
       <c r="Q646" t="n">
-        <v>440800</v>
+        <v>435000</v>
       </c>
     </row>
     <row r="647">
@@ -28231,22 +28231,22 @@
         <v>0</v>
       </c>
       <c r="L647" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M647" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N647" t="n">
         <v>5194</v>
       </c>
       <c r="O647" t="n">
-        <v>264894</v>
+        <v>249312</v>
       </c>
       <c r="P647" t="n">
         <v>9000</v>
       </c>
       <c r="Q647" t="n">
-        <v>459000</v>
+        <v>432000</v>
       </c>
     </row>
     <row r="648">
@@ -28277,22 +28277,22 @@
         <v>0</v>
       </c>
       <c r="L648" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M648" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N648" t="n">
         <v>4227.77</v>
       </c>
       <c r="O648" t="n">
-        <v>211388.5</v>
+        <v>207160.73</v>
       </c>
       <c r="P648" t="n">
         <v>6900</v>
       </c>
       <c r="Q648" t="n">
-        <v>345000</v>
+        <v>338100</v>
       </c>
     </row>
     <row r="649">
@@ -28599,22 +28599,22 @@
         <v>0</v>
       </c>
       <c r="L655" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M655" t="n">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="N655" t="n">
-        <v>1664.3584236948</v>
+        <v>1664.358174359</v>
       </c>
       <c r="O655" t="n">
-        <v>629127.4841566344</v>
+        <v>619141.240861548</v>
       </c>
       <c r="P655" t="n">
         <v>2900</v>
       </c>
       <c r="Q655" t="n">
-        <v>1096200</v>
+        <v>1078800</v>
       </c>
     </row>
     <row r="656">
@@ -28645,22 +28645,22 @@
         <v>0</v>
       </c>
       <c r="L656" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M656" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N656" t="n">
         <v>15502</v>
       </c>
       <c r="O656" t="n">
-        <v>1023132</v>
+        <v>1007630</v>
       </c>
       <c r="P656" t="n">
         <v>25900</v>
       </c>
       <c r="Q656" t="n">
-        <v>1709400</v>
+        <v>1683500</v>
       </c>
     </row>
     <row r="657">
@@ -29163,10 +29163,10 @@
         <v>4</v>
       </c>
       <c r="N667" t="n">
-        <v>23521.624354839</v>
+        <v>23521.624262295</v>
       </c>
       <c r="O667" t="n">
-        <v>94086.497419356</v>
+        <v>94086.49704918</v>
       </c>
       <c r="P667" t="n">
         <v>39000</v>
@@ -29249,22 +29249,22 @@
         <v>0</v>
       </c>
       <c r="L669" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M669" t="n">
-        <v>1492</v>
+        <v>1484</v>
       </c>
       <c r="N669" t="n">
-        <v>1778.4725809313</v>
+        <v>1778.4725908889</v>
       </c>
       <c r="O669" t="n">
-        <v>2653481.090749499</v>
+        <v>2639253.324879128</v>
       </c>
       <c r="P669" t="n">
         <v>4900</v>
       </c>
       <c r="Q669" t="n">
-        <v>7310800</v>
+        <v>7271600</v>
       </c>
     </row>
     <row r="670">
@@ -29341,22 +29341,22 @@
         <v>0</v>
       </c>
       <c r="L671" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M671" t="n">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="N671" t="n">
         <v>2325</v>
       </c>
       <c r="O671" t="n">
-        <v>1134600</v>
+        <v>1120650</v>
       </c>
       <c r="P671" t="n">
         <v>4900</v>
       </c>
       <c r="Q671" t="n">
-        <v>2391200</v>
+        <v>2361800</v>
       </c>
     </row>
     <row r="672">
@@ -29433,22 +29433,22 @@
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M673" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N673" t="n">
         <v>18016</v>
       </c>
       <c r="O673" t="n">
-        <v>270240</v>
+        <v>234208</v>
       </c>
       <c r="P673" t="n">
         <v>29900</v>
       </c>
       <c r="Q673" t="n">
-        <v>448500</v>
+        <v>388700</v>
       </c>
     </row>
     <row r="674">
@@ -29479,22 +29479,22 @@
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M674" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N674" t="n">
         <v>16058</v>
       </c>
       <c r="O674" t="n">
-        <v>963480</v>
+        <v>931364</v>
       </c>
       <c r="P674" t="n">
         <v>25900</v>
       </c>
       <c r="Q674" t="n">
-        <v>1554000</v>
+        <v>1502200</v>
       </c>
     </row>
     <row r="675">
@@ -30218,22 +30218,22 @@
         <v>0</v>
       </c>
       <c r="L690" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M690" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N690" t="n">
         <v>6000</v>
       </c>
       <c r="O690" t="n">
-        <v>462000</v>
+        <v>444000</v>
       </c>
       <c r="P690" t="n">
         <v>10000</v>
       </c>
       <c r="Q690" t="n">
-        <v>770000</v>
+        <v>740000</v>
       </c>
     </row>
     <row r="691">
@@ -31095,22 +31095,22 @@
         <v>0</v>
       </c>
       <c r="L709" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M709" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="N709" t="n">
         <v>13687</v>
       </c>
       <c r="O709" t="n">
-        <v>1464509</v>
+        <v>1382387</v>
       </c>
       <c r="P709" t="n">
         <v>21900</v>
       </c>
       <c r="Q709" t="n">
-        <v>2343300</v>
+        <v>2211900</v>
       </c>
     </row>
     <row r="710">
@@ -31463,22 +31463,22 @@
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M717" t="n">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="N717" t="n">
         <v>8858.16</v>
       </c>
       <c r="O717" t="n">
-        <v>3224370.24</v>
+        <v>3171221.28</v>
       </c>
       <c r="P717" t="n">
         <v>15500</v>
       </c>
       <c r="Q717" t="n">
-        <v>5642000</v>
+        <v>5549000</v>
       </c>
     </row>
     <row r="718">
@@ -31555,22 +31555,22 @@
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M719" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N719" t="n">
         <v>10411</v>
       </c>
       <c r="O719" t="n">
-        <v>270686</v>
+        <v>218631</v>
       </c>
       <c r="P719" t="n">
         <v>16900</v>
       </c>
       <c r="Q719" t="n">
-        <v>439400</v>
+        <v>354900</v>
       </c>
     </row>
     <row r="720">
@@ -31739,22 +31739,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M723" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N723" t="n">
         <v>11376</v>
       </c>
       <c r="O723" t="n">
-        <v>580176</v>
+        <v>534672</v>
       </c>
       <c r="P723" t="n">
         <v>18500</v>
       </c>
       <c r="Q723" t="n">
-        <v>943500</v>
+        <v>869500</v>
       </c>
     </row>
     <row r="724">
@@ -31785,22 +31785,22 @@
         <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M724" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N724" t="n">
         <v>5014</v>
       </c>
       <c r="O724" t="n">
-        <v>310868</v>
+        <v>295826</v>
       </c>
       <c r="P724" t="n">
         <v>8200</v>
       </c>
       <c r="Q724" t="n">
-        <v>508400</v>
+        <v>483800</v>
       </c>
     </row>
     <row r="725">
@@ -31923,22 +31923,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M727" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N727" t="n">
         <v>27218</v>
       </c>
       <c r="O727" t="n">
-        <v>816540</v>
+        <v>762104</v>
       </c>
       <c r="P727" t="n">
         <v>43900</v>
       </c>
       <c r="Q727" t="n">
-        <v>1317000</v>
+        <v>1229200</v>
       </c>
     </row>
     <row r="728">
@@ -32105,22 +32105,22 @@
         <v>0</v>
       </c>
       <c r="L731" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M731" t="n">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="N731" t="n">
-        <v>2328.118739546</v>
+        <v>2328.1187258454</v>
       </c>
       <c r="O731" t="n">
-        <v>1620370.642724016</v>
+        <v>1592433.208478254</v>
       </c>
       <c r="P731" t="n">
         <v>4500</v>
       </c>
       <c r="Q731" t="n">
-        <v>3132000</v>
+        <v>3078000</v>
       </c>
     </row>
     <row r="732">
@@ -32427,22 +32427,22 @@
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M738" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N738" t="n">
-        <v>50153.86</v>
+        <v>50770.505819672</v>
       </c>
       <c r="O738" t="n">
-        <v>6419694.08</v>
+        <v>6346313.227458999</v>
       </c>
       <c r="P738" t="n">
         <v>11500</v>
       </c>
       <c r="Q738" t="n">
-        <v>1472000</v>
+        <v>1437500</v>
       </c>
     </row>
     <row r="739">
@@ -32519,22 +32519,22 @@
         <v>0</v>
       </c>
       <c r="L740" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M740" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N740" t="n">
         <v>3519</v>
       </c>
       <c r="O740" t="n">
-        <v>883269</v>
+        <v>869193</v>
       </c>
       <c r="P740" t="n">
         <v>5900</v>
       </c>
       <c r="Q740" t="n">
-        <v>1480900</v>
+        <v>1457300</v>
       </c>
     </row>
     <row r="741">
@@ -32611,22 +32611,22 @@
         <v>0</v>
       </c>
       <c r="L742" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M742" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="N742" t="n">
         <v>9003</v>
       </c>
       <c r="O742" t="n">
-        <v>666222</v>
+        <v>621207</v>
       </c>
       <c r="P742" t="n">
         <v>14900</v>
       </c>
       <c r="Q742" t="n">
-        <v>1102600</v>
+        <v>1028100</v>
       </c>
     </row>
     <row r="743">
@@ -32657,22 +32657,22 @@
         <v>0</v>
       </c>
       <c r="L743" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M743" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N743" t="n">
         <v>9178</v>
       </c>
       <c r="O743" t="n">
-        <v>293696</v>
+        <v>266162</v>
       </c>
       <c r="P743" t="n">
         <v>14900</v>
       </c>
       <c r="Q743" t="n">
-        <v>476800</v>
+        <v>432100</v>
       </c>
     </row>
     <row r="744">
@@ -32703,22 +32703,22 @@
         <v>0</v>
       </c>
       <c r="L744" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M744" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="N744" t="n">
         <v>4544</v>
       </c>
       <c r="O744" t="n">
-        <v>1408640</v>
+        <v>1390464</v>
       </c>
       <c r="P744" t="n">
         <v>7900</v>
       </c>
       <c r="Q744" t="n">
-        <v>2449000</v>
+        <v>2417400</v>
       </c>
     </row>
     <row r="745">
@@ -32841,22 +32841,22 @@
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M747" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N747" t="n">
-        <v>3396.38</v>
+        <v>3418.6270305677</v>
       </c>
       <c r="O747" t="n">
-        <v>404169.22</v>
+        <v>396560.7355458532</v>
       </c>
       <c r="P747" t="n">
         <v>6500</v>
       </c>
       <c r="Q747" t="n">
-        <v>773500</v>
+        <v>754000</v>
       </c>
     </row>
     <row r="748">
@@ -32933,22 +32933,22 @@
         <v>0</v>
       </c>
       <c r="L749" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M749" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N749" t="n">
-        <v>4907.8219812793</v>
+        <v>4907.8220190779</v>
       </c>
       <c r="O749" t="n">
-        <v>88340.79566302741</v>
+        <v>78525.1523052464</v>
       </c>
       <c r="P749" t="n">
         <v>8200</v>
       </c>
       <c r="Q749" t="n">
-        <v>147600</v>
+        <v>131200</v>
       </c>
     </row>
     <row r="750">
@@ -33025,22 +33025,22 @@
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M751" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="N751" t="n">
         <v>13210</v>
       </c>
       <c r="O751" t="n">
-        <v>2206070</v>
+        <v>2113600</v>
       </c>
       <c r="P751" t="n">
         <v>23900</v>
       </c>
       <c r="Q751" t="n">
-        <v>3991300</v>
+        <v>3824000</v>
       </c>
     </row>
     <row r="752">
@@ -33209,22 +33209,22 @@
         <v>0</v>
       </c>
       <c r="L755" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M755" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N755" t="n">
-        <v>3903.736812933</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O755" t="n">
-        <v>390373.6812933</v>
+        <v>382566.1430769276</v>
       </c>
       <c r="P755" t="n">
         <v>7500</v>
       </c>
       <c r="Q755" t="n">
-        <v>750000</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="756">
@@ -33342,22 +33342,22 @@
         <v>0</v>
       </c>
       <c r="L758" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M758" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N758" t="n">
         <v>12113</v>
       </c>
       <c r="O758" t="n">
-        <v>557198</v>
+        <v>508746</v>
       </c>
       <c r="P758" t="n">
         <v>19900</v>
       </c>
       <c r="Q758" t="n">
-        <v>915400</v>
+        <v>835800</v>
       </c>
     </row>
     <row r="759">
@@ -33710,22 +33710,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M766" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N766" t="n">
-        <v>2629</v>
+        <v>2637.9574105622</v>
       </c>
       <c r="O766" t="n">
-        <v>252384</v>
+        <v>242692.0817717224</v>
       </c>
       <c r="P766" t="n">
         <v>4500</v>
       </c>
       <c r="Q766" t="n">
-        <v>432000</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="767">
@@ -33756,22 +33756,22 @@
         <v>0</v>
       </c>
       <c r="L767" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M767" t="n">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="N767" t="n">
-        <v>5869.1727391742</v>
+        <v>5869.1727171717</v>
       </c>
       <c r="O767" t="n">
-        <v>2899371.333152055</v>
+        <v>2887632.976848477</v>
       </c>
       <c r="P767" t="n">
         <v>9500</v>
       </c>
       <c r="Q767" t="n">
-        <v>4693000</v>
+        <v>4674000</v>
       </c>
     </row>
     <row r="768">
@@ -33802,22 +33802,22 @@
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M768" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="N768" t="n">
         <v>6849.2</v>
       </c>
       <c r="O768" t="n">
-        <v>815054.7999999999</v>
+        <v>780808.7999999999</v>
       </c>
       <c r="P768" t="n">
         <v>11500</v>
       </c>
       <c r="Q768" t="n">
-        <v>1368500</v>
+        <v>1311000</v>
       </c>
     </row>
     <row r="769">
@@ -33848,22 +33848,22 @@
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M769" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N769" t="n">
         <v>4984</v>
       </c>
       <c r="O769" t="n">
-        <v>174440</v>
+        <v>169456</v>
       </c>
       <c r="P769" t="n">
         <v>7900</v>
       </c>
       <c r="Q769" t="n">
-        <v>276500</v>
+        <v>268600</v>
       </c>
     </row>
     <row r="770">
@@ -33894,22 +33894,22 @@
         <v>0</v>
       </c>
       <c r="L770" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M770" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N770" t="n">
-        <v>5772</v>
+        <v>5775.9026369168</v>
       </c>
       <c r="O770" t="n">
-        <v>819624</v>
+        <v>808626.369168352</v>
       </c>
       <c r="P770" t="n">
         <v>9900</v>
       </c>
       <c r="Q770" t="n">
-        <v>1405800</v>
+        <v>1386000</v>
       </c>
     </row>
     <row r="771">
@@ -33940,22 +33940,22 @@
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M771" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="N771" t="n">
-        <v>6268</v>
+        <v>6283.164516129</v>
       </c>
       <c r="O771" t="n">
-        <v>664408</v>
+        <v>647165.945161287</v>
       </c>
       <c r="P771" t="n">
         <v>10900</v>
       </c>
       <c r="Q771" t="n">
-        <v>1155400</v>
+        <v>1122700</v>
       </c>
     </row>
     <row r="772">
@@ -34078,22 +34078,22 @@
         <v>0</v>
       </c>
       <c r="L774" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M774" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N774" t="n">
         <v>13098</v>
       </c>
       <c r="O774" t="n">
-        <v>1270506</v>
+        <v>1257408</v>
       </c>
       <c r="P774" t="n">
         <v>21200</v>
       </c>
       <c r="Q774" t="n">
-        <v>2056400</v>
+        <v>2035200</v>
       </c>
     </row>
     <row r="775">
@@ -34216,22 +34216,22 @@
         <v>0</v>
       </c>
       <c r="L777" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M777" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N777" t="n">
         <v>7562</v>
       </c>
       <c r="O777" t="n">
-        <v>393224</v>
+        <v>370538</v>
       </c>
       <c r="P777" t="n">
         <v>12900</v>
       </c>
       <c r="Q777" t="n">
-        <v>670800</v>
+        <v>632100</v>
       </c>
     </row>
     <row r="778">
@@ -34262,22 +34262,22 @@
         <v>0</v>
       </c>
       <c r="L778" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M778" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N778" t="n">
-        <v>3898</v>
+        <v>3904.1097178683</v>
       </c>
       <c r="O778" t="n">
-        <v>1134318</v>
+        <v>1128287.708463939</v>
       </c>
       <c r="P778" t="n">
         <v>6900</v>
       </c>
       <c r="Q778" t="n">
-        <v>2007900</v>
+        <v>1994100</v>
       </c>
     </row>
     <row r="779">
@@ -34354,22 +34354,22 @@
         <v>0</v>
       </c>
       <c r="L780" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M780" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N780" t="n">
         <v>7635</v>
       </c>
       <c r="O780" t="n">
-        <v>595530</v>
+        <v>572625</v>
       </c>
       <c r="P780" t="n">
         <v>13900</v>
       </c>
       <c r="Q780" t="n">
-        <v>1084200</v>
+        <v>1042500</v>
       </c>
     </row>
     <row r="781">
@@ -34446,22 +34446,22 @@
         <v>0</v>
       </c>
       <c r="L782" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M782" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N782" t="n">
         <v>5438</v>
       </c>
       <c r="O782" t="n">
-        <v>163140</v>
+        <v>135950</v>
       </c>
       <c r="P782" t="n">
         <v>8900</v>
       </c>
       <c r="Q782" t="n">
-        <v>267000</v>
+        <v>222500</v>
       </c>
     </row>
     <row r="783">
@@ -34587,22 +34587,22 @@
         <v>0</v>
       </c>
       <c r="L785" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M785" t="n">
-        <v>700</v>
+        <v>661</v>
       </c>
       <c r="N785" t="n">
         <v>753</v>
       </c>
       <c r="O785" t="n">
-        <v>527100</v>
+        <v>497733</v>
       </c>
       <c r="P785" t="n">
         <v>1600</v>
       </c>
       <c r="Q785" t="n">
-        <v>1120000</v>
+        <v>1057600</v>
       </c>
     </row>
     <row r="786">
@@ -34633,22 +34633,22 @@
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M786" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N786" t="n">
         <v>11302</v>
       </c>
       <c r="O786" t="n">
-        <v>1378844</v>
+        <v>1367542</v>
       </c>
       <c r="P786" t="n">
         <v>18900</v>
       </c>
       <c r="Q786" t="n">
-        <v>2305800</v>
+        <v>2286900</v>
       </c>
     </row>
     <row r="787">
@@ -34679,22 +34679,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M787" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N787" t="n">
         <v>17992</v>
       </c>
       <c r="O787" t="n">
-        <v>2015104</v>
+        <v>1997112</v>
       </c>
       <c r="P787" t="n">
         <v>28900</v>
       </c>
       <c r="Q787" t="n">
-        <v>3236800</v>
+        <v>3207900</v>
       </c>
     </row>
     <row r="788">
@@ -34771,22 +34771,22 @@
         <v>0</v>
       </c>
       <c r="L789" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M789" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N789" t="n">
         <v>11348</v>
       </c>
       <c r="O789" t="n">
-        <v>442572</v>
+        <v>431224</v>
       </c>
       <c r="P789" t="n">
         <v>19900</v>
       </c>
       <c r="Q789" t="n">
-        <v>776100</v>
+        <v>756200</v>
       </c>
     </row>
     <row r="790">
@@ -35134,22 +35134,22 @@
         <v>0</v>
       </c>
       <c r="L797" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M797" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N797" t="n">
         <v>21346</v>
       </c>
       <c r="O797" t="n">
-        <v>213460</v>
+        <v>192114</v>
       </c>
       <c r="P797" t="n">
         <v>34900</v>
       </c>
       <c r="Q797" t="n">
-        <v>349000</v>
+        <v>314100</v>
       </c>
     </row>
     <row r="798">
@@ -35226,22 +35226,22 @@
         <v>0</v>
       </c>
       <c r="L799" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M799" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="N799" t="n">
         <v>10219</v>
       </c>
       <c r="O799" t="n">
-        <v>1440879</v>
+        <v>1410222</v>
       </c>
       <c r="P799" t="n">
         <v>16900</v>
       </c>
       <c r="Q799" t="n">
-        <v>2382900</v>
+        <v>2332200</v>
       </c>
     </row>
     <row r="800">
@@ -35827,22 +35827,22 @@
         <v>0</v>
       </c>
       <c r="L812" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M812" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N812" t="n">
         <v>16282</v>
       </c>
       <c r="O812" t="n">
-        <v>195384</v>
+        <v>0</v>
       </c>
       <c r="P812" t="n">
         <v>27900</v>
       </c>
       <c r="Q812" t="n">
-        <v>334800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="813">
@@ -35873,22 +35873,22 @@
         <v>0</v>
       </c>
       <c r="L813" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M813" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N813" t="n">
         <v>8700</v>
       </c>
       <c r="O813" t="n">
-        <v>826500</v>
+        <v>783000</v>
       </c>
       <c r="P813" t="n">
         <v>14900</v>
       </c>
       <c r="Q813" t="n">
-        <v>1415500</v>
+        <v>1341000</v>
       </c>
     </row>
     <row r="814">
@@ -35919,22 +35919,22 @@
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M814" t="n">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="N814" t="n">
         <v>1326</v>
       </c>
       <c r="O814" t="n">
-        <v>1515618</v>
+        <v>1511640</v>
       </c>
       <c r="P814" t="n">
         <v>2500</v>
       </c>
       <c r="Q814" t="n">
-        <v>2857500</v>
+        <v>2850000</v>
       </c>
     </row>
     <row r="815">
@@ -35965,22 +35965,22 @@
         <v>0</v>
       </c>
       <c r="L815" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M815" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N815" t="n">
         <v>2573</v>
       </c>
       <c r="O815" t="n">
-        <v>383377</v>
+        <v>373085</v>
       </c>
       <c r="P815" t="n">
         <v>4500</v>
       </c>
       <c r="Q815" t="n">
-        <v>670500</v>
+        <v>652500</v>
       </c>
     </row>
     <row r="816">
@@ -36057,22 +36057,22 @@
         <v>0</v>
       </c>
       <c r="L817" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M817" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N817" t="n">
         <v>3821</v>
       </c>
       <c r="O817" t="n">
-        <v>817694</v>
+        <v>806231</v>
       </c>
       <c r="P817" t="n">
         <v>5900</v>
       </c>
       <c r="Q817" t="n">
-        <v>1262600</v>
+        <v>1244900</v>
       </c>
     </row>
     <row r="818">
@@ -36103,22 +36103,22 @@
         <v>0</v>
       </c>
       <c r="L818" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M818" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N818" t="n">
         <v>15472</v>
       </c>
       <c r="O818" t="n">
-        <v>309440</v>
+        <v>263024</v>
       </c>
       <c r="P818" t="n">
         <v>25900</v>
       </c>
       <c r="Q818" t="n">
-        <v>518000</v>
+        <v>440300</v>
       </c>
     </row>
     <row r="819">
@@ -36195,22 +36195,22 @@
         <v>0</v>
       </c>
       <c r="L820" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M820" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N820" t="n">
         <v>7253</v>
       </c>
       <c r="O820" t="n">
-        <v>449686</v>
+        <v>442433</v>
       </c>
       <c r="P820" t="n">
         <v>11900</v>
       </c>
       <c r="Q820" t="n">
-        <v>737800</v>
+        <v>725900</v>
       </c>
     </row>
     <row r="821">
@@ -36241,22 +36241,22 @@
         <v>0</v>
       </c>
       <c r="L821" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M821" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N821" t="n">
         <v>4118</v>
       </c>
       <c r="O821" t="n">
-        <v>411800</v>
+        <v>399446</v>
       </c>
       <c r="P821" t="n">
         <v>6900</v>
       </c>
       <c r="Q821" t="n">
-        <v>690000</v>
+        <v>669300</v>
       </c>
     </row>
     <row r="822">
@@ -36287,22 +36287,22 @@
         <v>0</v>
       </c>
       <c r="L822" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M822" t="n">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="N822" t="n">
         <v>5476</v>
       </c>
       <c r="O822" t="n">
-        <v>2497056</v>
+        <v>2409440</v>
       </c>
       <c r="P822" t="n">
         <v>8900</v>
       </c>
       <c r="Q822" t="n">
-        <v>4058400</v>
+        <v>3916000</v>
       </c>
     </row>
     <row r="823">
@@ -36520,22 +36520,22 @@
         <v>0</v>
       </c>
       <c r="L827" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M827" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N827" t="n">
         <v>38252</v>
       </c>
       <c r="O827" t="n">
-        <v>765040</v>
+        <v>726788</v>
       </c>
       <c r="P827" t="n">
         <v>61900</v>
       </c>
       <c r="Q827" t="n">
-        <v>1238000</v>
+        <v>1176100</v>
       </c>
     </row>
     <row r="828">
@@ -36572,10 +36572,10 @@
         <v>598</v>
       </c>
       <c r="N828" t="n">
-        <v>1516.0388052024</v>
+        <v>1516.0388047383</v>
       </c>
       <c r="O828" t="n">
-        <v>906591.2055110352</v>
+        <v>906591.2052335035</v>
       </c>
       <c r="P828" t="n">
         <v>2300</v>
@@ -36612,22 +36612,22 @@
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M829" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N829" t="n">
-        <v>4248.6496363636</v>
+        <v>4248.6505555556</v>
       </c>
       <c r="O829" t="n">
-        <v>237924.3796363616</v>
+        <v>220929.8288888912</v>
       </c>
       <c r="P829" t="n">
         <v>5900</v>
       </c>
       <c r="Q829" t="n">
-        <v>330400</v>
+        <v>306800</v>
       </c>
     </row>
     <row r="830">
@@ -36702,22 +36702,22 @@
         <v>0</v>
       </c>
       <c r="L831" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M831" t="n">
-        <v>363</v>
+        <v>335</v>
       </c>
       <c r="N831" t="n">
-        <v>2458.5133724619</v>
+        <v>2458.5132807977</v>
       </c>
       <c r="O831" t="n">
-        <v>892440.3542036697</v>
+        <v>823601.9490672295</v>
       </c>
       <c r="P831" t="n">
         <v>3500</v>
       </c>
       <c r="Q831" t="n">
-        <v>1270500</v>
+        <v>1172500</v>
       </c>
     </row>
     <row r="832">
@@ -36748,22 +36748,22 @@
         <v>0</v>
       </c>
       <c r="L832" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M832" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N832" t="n">
-        <v>1907.394010989</v>
+        <v>1907.3939779006</v>
       </c>
       <c r="O832" t="n">
-        <v>362404.86208791</v>
+        <v>354775.2798895116</v>
       </c>
       <c r="P832" t="n">
         <v>2500</v>
       </c>
       <c r="Q832" t="n">
-        <v>475000</v>
+        <v>465000</v>
       </c>
     </row>
     <row r="833">
@@ -36794,22 +36794,22 @@
         <v>0</v>
       </c>
       <c r="L833" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M833" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N833" t="n">
-        <v>1771.0908132147</v>
+        <v>1775.6031464968</v>
       </c>
       <c r="O833" t="n">
-        <v>334736.1636975783</v>
+        <v>328486.582101908</v>
       </c>
       <c r="P833" t="n">
         <v>2500</v>
       </c>
       <c r="Q833" t="n">
-        <v>472500</v>
+        <v>462500</v>
       </c>
     </row>
     <row r="834">
@@ -36840,22 +36840,22 @@
         <v>0</v>
       </c>
       <c r="L834" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M834" t="n">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N834" t="n">
-        <v>2079.384121911</v>
+        <v>2079.3840612517</v>
       </c>
       <c r="O834" t="n">
-        <v>862944.410593065</v>
+        <v>854626.8491744488</v>
       </c>
       <c r="P834" t="n">
         <v>2900</v>
       </c>
       <c r="Q834" t="n">
-        <v>1203500</v>
+        <v>1191900</v>
       </c>
     </row>
     <row r="835">
@@ -36886,22 +36886,22 @@
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M835" t="n">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="N835" t="n">
-        <v>1803.0152282542</v>
+        <v>1803.015492547</v>
       </c>
       <c r="O835" t="n">
-        <v>769887.5024645434</v>
+        <v>748251.429407005</v>
       </c>
       <c r="P835" t="n">
         <v>2500</v>
       </c>
       <c r="Q835" t="n">
-        <v>1067500</v>
+        <v>1037500</v>
       </c>
     </row>
     <row r="836">
@@ -36978,22 +36978,22 @@
         <v>0</v>
       </c>
       <c r="L837" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M837" t="n">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="N837" t="n">
-        <v>2122.1639833897</v>
+        <v>2122.163972265</v>
       </c>
       <c r="O837" t="n">
-        <v>914652.6768409607</v>
+        <v>906164.016157155</v>
       </c>
       <c r="P837" t="n">
         <v>2900</v>
       </c>
       <c r="Q837" t="n">
-        <v>1249900</v>
+        <v>1238300</v>
       </c>
     </row>
     <row r="838">
@@ -37024,22 +37024,22 @@
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M838" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N838" t="n">
-        <v>2108.7902645503</v>
+        <v>2108.7909398496</v>
       </c>
       <c r="O838" t="n">
-        <v>63263.707936509</v>
+        <v>46393.4006766912</v>
       </c>
       <c r="P838" t="n">
         <v>2900</v>
       </c>
       <c r="Q838" t="n">
-        <v>87000</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="839">
@@ -37070,22 +37070,22 @@
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M839" t="n">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="N839" t="n">
-        <v>2056.0836725935</v>
+        <v>2056.0835600624</v>
       </c>
       <c r="O839" t="n">
-        <v>1829914.468608215</v>
+        <v>1821690.034215286</v>
       </c>
       <c r="P839" t="n">
         <v>2900</v>
       </c>
       <c r="Q839" t="n">
-        <v>2581000</v>
+        <v>2569400</v>
       </c>
     </row>
     <row r="840">
@@ -37116,22 +37116,22 @@
         <v>0</v>
       </c>
       <c r="L840" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M840" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N840" t="n">
-        <v>3224.5683024119</v>
+        <v>3224.5684753788</v>
       </c>
       <c r="O840" t="n">
-        <v>786794.6657885036</v>
+        <v>783570.1395170484</v>
       </c>
       <c r="P840" t="n">
         <v>4500</v>
       </c>
       <c r="Q840" t="n">
-        <v>1098000</v>
+        <v>1093500</v>
       </c>
     </row>
     <row r="841">
@@ -37533,22 +37533,22 @@
         <v>0</v>
       </c>
       <c r="L849" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M849" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="N849" t="n">
-        <v>1592.2763108883</v>
+        <v>1592.2766843703</v>
       </c>
       <c r="O849" t="n">
-        <v>121012.9996275108</v>
+        <v>105090.2611684398</v>
       </c>
       <c r="P849" t="n">
         <v>2500</v>
       </c>
       <c r="Q849" t="n">
-        <v>190000</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="850">
@@ -37577,22 +37577,22 @@
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M850" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N850" t="n">
         <v>5347.73</v>
       </c>
       <c r="O850" t="n">
-        <v>5347.73</v>
+        <v>0</v>
       </c>
       <c r="P850" t="n">
         <v>9500</v>
       </c>
       <c r="Q850" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="851">
@@ -37629,10 +37629,10 @@
         <v>2</v>
       </c>
       <c r="N851" t="n">
-        <v>1906.1853271028</v>
+        <v>1906.1850980392</v>
       </c>
       <c r="O851" t="n">
-        <v>3812.3706542056</v>
+        <v>3812.3701960784</v>
       </c>
       <c r="P851" t="n">
         <v>2900</v>
@@ -37767,10 +37767,10 @@
         <v>281</v>
       </c>
       <c r="N854" t="n">
-        <v>1259.2745016722</v>
+        <v>1259.2745137492</v>
       </c>
       <c r="O854" t="n">
-        <v>353856.1349698882</v>
+        <v>353856.1383635252</v>
       </c>
       <c r="P854" t="n">
         <v>1900</v>
@@ -37853,22 +37853,22 @@
         <v>0</v>
       </c>
       <c r="L856" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M856" t="n">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="N856" t="n">
         <v>1801</v>
       </c>
       <c r="O856" t="n">
-        <v>956331</v>
+        <v>945525</v>
       </c>
       <c r="P856" t="n">
         <v>2900</v>
       </c>
       <c r="Q856" t="n">
-        <v>1539900</v>
+        <v>1522500</v>
       </c>
     </row>
     <row r="857">
@@ -39144,22 +39144,22 @@
         <v>0</v>
       </c>
       <c r="L884" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M884" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N884" t="n">
         <v>3629.36</v>
       </c>
       <c r="O884" t="n">
-        <v>21776.16</v>
+        <v>10888.08</v>
       </c>
       <c r="P884" t="n">
         <v>3900</v>
       </c>
       <c r="Q884" t="n">
-        <v>23400</v>
+        <v>11700</v>
       </c>
     </row>
     <row r="885">
@@ -39324,22 +39324,22 @@
         <v>0</v>
       </c>
       <c r="L888" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M888" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N888" t="n">
-        <v>6898.4</v>
+        <v>6939.3400593472</v>
       </c>
       <c r="O888" t="n">
-        <v>269037.6</v>
+        <v>256755.5821958464</v>
       </c>
       <c r="P888" t="n">
         <v>12900</v>
       </c>
       <c r="Q888" t="n">
-        <v>503100</v>
+        <v>477300</v>
       </c>
     </row>
     <row r="889">
@@ -39370,22 +39370,22 @@
         <v>0</v>
       </c>
       <c r="L889" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M889" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="N889" t="n">
-        <v>2357.74</v>
+        <v>2474.8947826087</v>
       </c>
       <c r="O889" t="n">
-        <v>254635.92</v>
+        <v>247489.47826087</v>
       </c>
       <c r="P889" t="n">
         <v>3000</v>
       </c>
       <c r="Q889" t="n">
-        <v>324000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="890">
@@ -39504,22 +39504,22 @@
         <v>0</v>
       </c>
       <c r="L892" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M892" t="n">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="N892" t="n">
         <v>1828.64</v>
       </c>
       <c r="O892" t="n">
-        <v>1267247.52</v>
+        <v>1263590.24</v>
       </c>
       <c r="P892" t="n">
         <v>2000</v>
       </c>
       <c r="Q892" t="n">
-        <v>1386000</v>
+        <v>1382000</v>
       </c>
     </row>
     <row r="893">
@@ -40048,22 +40048,22 @@
         <v>0</v>
       </c>
       <c r="L904" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M904" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="N904" t="n">
-        <v>5050</v>
+        <v>5100.8048289738</v>
       </c>
       <c r="O904" t="n">
-        <v>585800</v>
+        <v>566189.3360160918</v>
       </c>
       <c r="P904" t="n">
         <v>2000</v>
       </c>
       <c r="Q904" t="n">
-        <v>232000</v>
+        <v>222000</v>
       </c>
     </row>
     <row r="905">
@@ -40092,22 +40092,22 @@
         <v>0</v>
       </c>
       <c r="L905" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M905" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N905" t="n">
         <v>1684.79</v>
       </c>
       <c r="O905" t="n">
-        <v>168479</v>
+        <v>158370.26</v>
       </c>
       <c r="P905" t="n">
         <v>2900</v>
       </c>
       <c r="Q905" t="n">
-        <v>290000</v>
+        <v>272600</v>
       </c>
     </row>
     <row r="906">
@@ -40576,22 +40576,22 @@
         <v>0</v>
       </c>
       <c r="L916" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M916" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N916" t="n">
         <v>177.65</v>
       </c>
       <c r="O916" t="n">
-        <v>3197.7</v>
+        <v>1421.2</v>
       </c>
       <c r="P916" t="n">
         <v>300</v>
       </c>
       <c r="Q916" t="n">
-        <v>5400</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="917">
@@ -40886,22 +40886,22 @@
         <v>0</v>
       </c>
       <c r="L923" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M923" t="n">
-        <v>3299</v>
+        <v>3175</v>
       </c>
       <c r="N923" t="n">
-        <v>517.2884408203601</v>
+        <v>517.28876931766</v>
       </c>
       <c r="O923" t="n">
-        <v>1706534.566266368</v>
+        <v>1642391.842583571</v>
       </c>
       <c r="P923" t="n">
         <v>900</v>
       </c>
       <c r="Q923" t="n">
-        <v>2969100</v>
+        <v>2857500</v>
       </c>
     </row>
     <row r="924">
@@ -41112,22 +41112,22 @@
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M928" t="n">
-        <v>571</v>
+        <v>535</v>
       </c>
       <c r="N928" t="n">
-        <v>3110.8425641565</v>
+        <v>3110.8424546425</v>
       </c>
       <c r="O928" t="n">
-        <v>1776291.104133361</v>
+        <v>1664300.713233738</v>
       </c>
       <c r="P928" t="n">
         <v>4500</v>
       </c>
       <c r="Q928" t="n">
-        <v>2569500</v>
+        <v>2407500</v>
       </c>
     </row>
     <row r="929">
@@ -41334,22 +41334,22 @@
         <v>0</v>
       </c>
       <c r="L933" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="M933" t="n">
-        <v>1658</v>
+        <v>1513</v>
       </c>
       <c r="N933" t="n">
-        <v>703.79526826968</v>
+        <v>703.7952483310401</v>
       </c>
       <c r="O933" t="n">
-        <v>1166892.554791129</v>
+        <v>1064842.210724864</v>
       </c>
       <c r="P933" t="n">
         <v>900</v>
       </c>
       <c r="Q933" t="n">
-        <v>1492200</v>
+        <v>1361700</v>
       </c>
     </row>
     <row r="934">
@@ -41427,22 +41427,22 @@
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M935" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N935" t="n">
-        <v>3182.2511009174</v>
+        <v>3182.2511070111</v>
       </c>
       <c r="O935" t="n">
-        <v>111378.788532109</v>
+        <v>105014.2865313663</v>
       </c>
       <c r="P935" t="n">
         <v>6900</v>
       </c>
       <c r="Q935" t="n">
-        <v>241500</v>
+        <v>227700</v>
       </c>
     </row>
     <row r="936">
@@ -41567,10 +41567,10 @@
         <v>3</v>
       </c>
       <c r="N938" t="n">
-        <v>2501.3850684932</v>
+        <v>2501.3850230415</v>
       </c>
       <c r="O938" t="n">
-        <v>7504.155205479599</v>
+        <v>7504.1550691245</v>
       </c>
       <c r="P938" t="n">
         <v>4100</v>
@@ -41872,22 +41872,22 @@
         <v>0</v>
       </c>
       <c r="L945" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M945" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N945" t="n">
         <v>1937</v>
       </c>
       <c r="O945" t="n">
-        <v>255684</v>
+        <v>251810</v>
       </c>
       <c r="P945" t="n">
         <v>3300</v>
       </c>
       <c r="Q945" t="n">
-        <v>435600</v>
+        <v>429000</v>
       </c>
     </row>
     <row r="946">
@@ -42342,19 +42342,19 @@
         <v>74</v>
       </c>
       <c r="K956" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L956" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M956" t="n">
         <v>74</v>
       </c>
       <c r="N956" t="n">
-        <v>1595.5151400147</v>
+        <v>1595.5132932891</v>
       </c>
       <c r="O956" t="n">
-        <v>118068.1203610878</v>
+        <v>118067.9837033934</v>
       </c>
       <c r="P956" t="n">
         <v>2500</v>
@@ -42391,22 +42391,22 @@
         <v>0</v>
       </c>
       <c r="L957" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M957" t="n">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="N957" t="n">
         <v>1567.02</v>
       </c>
       <c r="O957" t="n">
-        <v>374517.78</v>
+        <v>355713.54</v>
       </c>
       <c r="P957" t="n">
         <v>2900</v>
       </c>
       <c r="Q957" t="n">
-        <v>693100</v>
+        <v>658300</v>
       </c>
     </row>
     <row r="958">
@@ -42435,22 +42435,22 @@
         <v>0</v>
       </c>
       <c r="L958" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M958" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N958" t="n">
-        <v>2421</v>
+        <v>3081.2727272727</v>
       </c>
       <c r="O958" t="n">
-        <v>67788</v>
+        <v>67787.9999999994</v>
       </c>
       <c r="P958" t="n">
         <v>4200</v>
       </c>
       <c r="Q958" t="n">
-        <v>117600</v>
+        <v>92400</v>
       </c>
     </row>
     <row r="959">
@@ -43581,22 +43581,22 @@
         <v>0</v>
       </c>
       <c r="L982" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M982" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N982" t="n">
-        <v>3067.0905454545</v>
+        <v>3067.0905844156</v>
       </c>
       <c r="O982" t="n">
-        <v>168689.9799999975</v>
+        <v>165622.8915584424</v>
       </c>
       <c r="P982" t="n">
         <v>7200</v>
       </c>
       <c r="Q982" t="n">
-        <v>396000</v>
+        <v>388800</v>
       </c>
     </row>
     <row r="983">
@@ -43762,10 +43762,10 @@
         <v>1</v>
       </c>
       <c r="N986" t="n">
-        <v>1783.7988833409</v>
+        <v>1783.798877225</v>
       </c>
       <c r="O986" t="n">
-        <v>1783.7988833409</v>
+        <v>1783.798877225</v>
       </c>
       <c r="P986" t="n">
         <v>1500</v>
@@ -43991,22 +43991,22 @@
         <v>0</v>
       </c>
       <c r="L991" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M991" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N991" t="n">
-        <v>1759.84</v>
+        <v>1782.5965517241</v>
       </c>
       <c r="O991" t="n">
-        <v>413562.4</v>
+        <v>413562.3999999912</v>
       </c>
       <c r="P991" t="n">
         <v>3300</v>
       </c>
       <c r="Q991" t="n">
-        <v>775500</v>
+        <v>765600</v>
       </c>
     </row>
     <row r="992">
@@ -44741,22 +44741,22 @@
         <v>0</v>
       </c>
       <c r="L1007" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1007" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N1007" t="n">
         <v>7465.9</v>
       </c>
       <c r="O1007" t="n">
-        <v>156783.9</v>
+        <v>141852.1</v>
       </c>
       <c r="P1007" t="n">
         <v>11900</v>
       </c>
       <c r="Q1007" t="n">
-        <v>249900</v>
+        <v>226100</v>
       </c>
     </row>
     <row r="1008">
@@ -44834,22 +44834,22 @@
         <v>0</v>
       </c>
       <c r="L1009" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1009" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="N1009" t="n">
-        <v>7046.9398286204</v>
+        <v>7046.9398281418</v>
       </c>
       <c r="O1009" t="n">
-        <v>1345965.507266496</v>
+        <v>1275496.108893666</v>
       </c>
       <c r="P1009" t="n">
         <v>9900</v>
       </c>
       <c r="Q1009" t="n">
-        <v>1890900</v>
+        <v>1791900</v>
       </c>
     </row>
     <row r="1010">
@@ -44880,22 +44880,22 @@
         <v>0</v>
       </c>
       <c r="L1010" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1010" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N1010" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1010" t="n">
-        <v>1289938.91</v>
+        <v>1216923.5</v>
       </c>
       <c r="P1010" t="n">
         <v>27900</v>
       </c>
       <c r="Q1010" t="n">
-        <v>1478700</v>
+        <v>1395000</v>
       </c>
     </row>
     <row r="1011">
@@ -45248,22 +45248,22 @@
         <v>0</v>
       </c>
       <c r="L1018" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1018" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N1018" t="n">
-        <v>424.99</v>
+        <v>432.57910714286</v>
       </c>
       <c r="O1018" t="n">
-        <v>16999.6</v>
+        <v>16438.00607142868</v>
       </c>
       <c r="P1018" t="n">
         <v>2300</v>
       </c>
       <c r="Q1018" t="n">
-        <v>92000</v>
+        <v>87400</v>
       </c>
     </row>
     <row r="1019">
@@ -45646,10 +45646,10 @@
         <v>6</v>
       </c>
       <c r="N1026" t="n">
-        <v>315.02685915493</v>
+        <v>315.02694721826</v>
       </c>
       <c r="O1026" t="n">
-        <v>1890.16115492958</v>
+        <v>1890.16168330956</v>
       </c>
       <c r="P1026" t="n">
         <v>2200</v>
@@ -46322,22 +46322,22 @@
         <v>0</v>
       </c>
       <c r="L1042" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1042" t="n">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="N1042" t="n">
         <v>6761.25</v>
       </c>
       <c r="O1042" t="n">
-        <v>3536133.75</v>
+        <v>3529372.5</v>
       </c>
       <c r="P1042" t="n">
         <v>5200</v>
       </c>
       <c r="Q1042" t="n">
-        <v>2719600</v>
+        <v>2714400</v>
       </c>
     </row>
     <row r="1043">
@@ -47397,22 +47397,22 @@
         <v>0</v>
       </c>
       <c r="L1067" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1067" t="n">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="N1067" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1067" t="n">
-        <v>1279123.8</v>
+        <v>1266396.2</v>
       </c>
       <c r="P1067" t="n">
         <v>5100</v>
       </c>
       <c r="Q1067" t="n">
-        <v>2050200</v>
+        <v>2029800</v>
       </c>
     </row>
     <row r="1068">
@@ -47523,22 +47523,22 @@
         <v>0</v>
       </c>
       <c r="L1070" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1070" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="N1070" t="n">
-        <v>1794.2879750466</v>
+        <v>1794.2879721384</v>
       </c>
       <c r="O1070" t="n">
-        <v>331943.275383621</v>
+        <v>314000.39512422</v>
       </c>
       <c r="P1070" t="n">
         <v>1600</v>
       </c>
       <c r="Q1070" t="n">
-        <v>296000</v>
+        <v>280000</v>
       </c>
     </row>
     <row r="1071">
@@ -47655,22 +47655,22 @@
         <v>0</v>
       </c>
       <c r="L1073" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1073" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="N1073" t="n">
         <v>1727.31</v>
       </c>
       <c r="O1073" t="n">
-        <v>304006.56</v>
+        <v>293642.7</v>
       </c>
       <c r="P1073" t="n">
         <v>2850</v>
       </c>
       <c r="Q1073" t="n">
-        <v>501600</v>
+        <v>484500</v>
       </c>
     </row>
     <row r="1074">
@@ -47787,22 +47787,22 @@
         <v>0</v>
       </c>
       <c r="L1076" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1076" t="n">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="N1076" t="n">
-        <v>1464</v>
+        <v>1908.7594936709</v>
       </c>
       <c r="O1076" t="n">
-        <v>142008</v>
+        <v>139339.4430379757</v>
       </c>
       <c r="P1076" t="n">
         <v>1500</v>
       </c>
       <c r="Q1076" t="n">
-        <v>145500</v>
+        <v>109500</v>
       </c>
     </row>
     <row r="1077">
@@ -48551,22 +48551,22 @@
         <v>0</v>
       </c>
       <c r="L1094" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1094" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="N1094" t="n">
         <v>5077</v>
       </c>
       <c r="O1094" t="n">
-        <v>660010</v>
+        <v>634625</v>
       </c>
       <c r="P1094" t="n">
         <v>8500</v>
       </c>
       <c r="Q1094" t="n">
-        <v>1105000</v>
+        <v>1062500</v>
       </c>
     </row>
     <row r="1095">
@@ -48731,10 +48731,10 @@
         <v>94</v>
       </c>
       <c r="N1098" t="n">
-        <v>4985.4050632911</v>
+        <v>4985.4051948052</v>
       </c>
       <c r="O1098" t="n">
-        <v>468628.0759493634</v>
+        <v>468628.0883116888</v>
       </c>
       <c r="P1098" t="n">
         <v>7900</v>
@@ -48776,22 +48776,22 @@
         <v>0</v>
       </c>
       <c r="L1099" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1099" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N1099" t="n">
-        <v>1757.3205462185</v>
+        <v>1775.9757537155</v>
       </c>
       <c r="O1099" t="n">
-        <v>80836.745126051</v>
+        <v>72815.0059023355</v>
       </c>
       <c r="P1099" t="n">
         <v>2000</v>
       </c>
       <c r="Q1099" t="n">
-        <v>92000</v>
+        <v>82000</v>
       </c>
     </row>
     <row r="1100">
@@ -49089,10 +49089,10 @@
         <v>2</v>
       </c>
       <c r="N1106" t="n">
-        <v>12601.0975</v>
+        <v>12601.09</v>
       </c>
       <c r="O1106" t="n">
-        <v>25202.195</v>
+        <v>25202.18</v>
       </c>
       <c r="P1106" t="n">
         <v>15900</v>
@@ -49221,22 +49221,22 @@
         <v>0</v>
       </c>
       <c r="L1109" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1109" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="N1109" t="n">
         <v>1952.66</v>
       </c>
       <c r="O1109" t="n">
-        <v>328046.88</v>
+        <v>316330.92</v>
       </c>
       <c r="P1109" t="n">
         <v>3500</v>
       </c>
       <c r="Q1109" t="n">
-        <v>588000</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="1110">
@@ -49451,22 +49451,22 @@
         <v>0</v>
       </c>
       <c r="L1114" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M1114" t="n">
-        <v>315</v>
+        <v>167</v>
       </c>
       <c r="N1114" t="n">
         <v>7480</v>
       </c>
       <c r="O1114" t="n">
-        <v>2356200</v>
+        <v>1249160</v>
       </c>
       <c r="P1114" t="n">
         <v>9500</v>
       </c>
       <c r="Q1114" t="n">
-        <v>2992500</v>
+        <v>1586500</v>
       </c>
     </row>
     <row r="1115">
@@ -49589,22 +49589,22 @@
         <v>0</v>
       </c>
       <c r="L1117" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M1117" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="N1117" t="n">
         <v>9240</v>
       </c>
       <c r="O1117" t="n">
-        <v>1284360</v>
+        <v>1099560</v>
       </c>
       <c r="P1117" t="n">
         <v>11500</v>
       </c>
       <c r="Q1117" t="n">
-        <v>1598500</v>
+        <v>1368500</v>
       </c>
     </row>
     <row r="1118">
@@ -50003,22 +50003,22 @@
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1126" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N1126" t="n">
         <v>2900</v>
       </c>
       <c r="O1126" t="n">
-        <v>124700</v>
+        <v>110200</v>
       </c>
       <c r="P1126" t="n">
         <v>3500</v>
       </c>
       <c r="Q1126" t="n">
-        <v>150500</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="1127">
@@ -50509,22 +50509,22 @@
         <v>0</v>
       </c>
       <c r="L1137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1137" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N1137" t="n">
-        <v>6000</v>
+        <v>6214.2857142857</v>
       </c>
       <c r="O1137" t="n">
-        <v>102000</v>
+        <v>99428.5714285712</v>
       </c>
       <c r="P1137" t="n">
         <v>7200</v>
       </c>
       <c r="Q1137" t="n">
-        <v>122400</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="1138">
@@ -51107,22 +51107,22 @@
         <v>0</v>
       </c>
       <c r="L1150" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1150" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="N1150" t="n">
-        <v>227.41597222222</v>
+        <v>229.09061119293</v>
       </c>
       <c r="O1150" t="n">
-        <v>26380.25277777752</v>
+        <v>24283.60478645058</v>
       </c>
       <c r="P1150" t="n">
         <v>1200</v>
       </c>
       <c r="Q1150" t="n">
-        <v>139200</v>
+        <v>127200</v>
       </c>
     </row>
     <row r="1151">
@@ -51828,22 +51828,22 @@
         <v>0</v>
       </c>
       <c r="L1166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1166" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N1166" t="n">
-        <v>5026.666</v>
+        <v>5026.6659322034</v>
       </c>
       <c r="O1166" t="n">
-        <v>80426.656</v>
+        <v>70373.3230508476</v>
       </c>
       <c r="P1166" t="n">
         <v>6300</v>
       </c>
       <c r="Q1166" t="n">
-        <v>100800</v>
+        <v>88200</v>
       </c>
     </row>
     <row r="1167">
@@ -51874,22 +51874,22 @@
         <v>0</v>
       </c>
       <c r="L1167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1167" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N1167" t="n">
         <v>5200</v>
       </c>
       <c r="O1167" t="n">
-        <v>88400</v>
+        <v>78000</v>
       </c>
       <c r="P1167" t="n">
         <v>6300</v>
       </c>
       <c r="Q1167" t="n">
-        <v>107100</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="1168">
@@ -52412,10 +52412,10 @@
         <v>44</v>
       </c>
       <c r="N1179" t="n">
-        <v>2403.9774324324</v>
+        <v>2403.9772661871</v>
       </c>
       <c r="O1179" t="n">
-        <v>105775.0070270256</v>
+        <v>105774.9997122324</v>
       </c>
       <c r="P1179" t="n">
         <v>3000</v>
@@ -52458,10 +52458,10 @@
         <v>43</v>
       </c>
       <c r="N1180" t="n">
-        <v>2402.6744594595</v>
+        <v>2402.6741428571</v>
       </c>
       <c r="O1180" t="n">
-        <v>103315.0017567585</v>
+        <v>103314.9881428553</v>
       </c>
       <c r="P1180" t="n">
         <v>3000</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1007,22 +1007,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N15" t="n">
         <v>27000</v>
       </c>
       <c r="O15" t="n">
-        <v>594000</v>
+        <v>567000</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
       </c>
       <c r="Q15" t="n">
-        <v>440000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="16">
@@ -1307,10 +1307,10 @@
         <v>360</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.3058666667</v>
+        <v>1811.3059701493</v>
       </c>
       <c r="O22" t="n">
-        <v>652070.112000012</v>
+        <v>652070.149253748</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
@@ -1424,10 +1424,10 @@
         <v>155</v>
       </c>
       <c r="N25" t="n">
-        <v>3376.7464891304</v>
+        <v>3376.7464843537</v>
       </c>
       <c r="O25" t="n">
-        <v>523395.705815212</v>
+        <v>523395.7050748235</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
@@ -1583,10 +1583,10 @@
         <v>55</v>
       </c>
       <c r="N29" t="n">
-        <v>5758.9597787611</v>
+        <v>5758.9597782705</v>
       </c>
       <c r="O29" t="n">
-        <v>316742.7878318605</v>
+        <v>316742.7878048775</v>
       </c>
       <c r="P29" t="n">
         <v>16900</v>
@@ -2918,10 +2918,10 @@
         <v>41</v>
       </c>
       <c r="N62" t="n">
-        <v>6272.8546153846</v>
+        <v>6272.8546302251</v>
       </c>
       <c r="O62" t="n">
-        <v>257187.0392307686</v>
+        <v>257187.0398392291</v>
       </c>
       <c r="P62" t="n">
         <v>7900</v>
@@ -3241,10 +3241,10 @@
         <v>205</v>
       </c>
       <c r="N70" t="n">
-        <v>2413.0010683761</v>
+        <v>2413.0010706638</v>
       </c>
       <c r="O70" t="n">
-        <v>494665.2190171005</v>
+        <v>494665.219486079</v>
       </c>
       <c r="P70" t="n">
         <v>4700</v>
@@ -3547,22 +3547,22 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M78" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N78" t="n">
         <v>2681</v>
       </c>
       <c r="O78" t="n">
-        <v>214480</v>
+        <v>206437</v>
       </c>
       <c r="P78" t="n">
         <v>3500</v>
       </c>
       <c r="Q78" t="n">
-        <v>280000</v>
+        <v>269500</v>
       </c>
     </row>
     <row r="79">
@@ -4128,22 +4128,22 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M92" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N92" t="n">
-        <v>3910.6281818182</v>
+        <v>3910.6281707317</v>
       </c>
       <c r="O92" t="n">
-        <v>218995.1781818192</v>
+        <v>207263.2930487801</v>
       </c>
       <c r="P92" t="n">
         <v>9100</v>
       </c>
       <c r="Q92" t="n">
-        <v>509600</v>
+        <v>482300</v>
       </c>
     </row>
     <row r="93">
@@ -4723,10 +4723,10 @@
         <v>10</v>
       </c>
       <c r="N105" t="n">
-        <v>30708.856153846</v>
+        <v>30708.848333333</v>
       </c>
       <c r="O105" t="n">
-        <v>307088.56153846</v>
+        <v>307088.48333333</v>
       </c>
       <c r="P105" t="n">
         <v>53500</v>
@@ -4765,10 +4765,10 @@
         <v>17</v>
       </c>
       <c r="N106" t="n">
-        <v>12837.966461538</v>
+        <v>12837.967258065</v>
       </c>
       <c r="O106" t="n">
-        <v>218245.429846146</v>
+        <v>218245.443387105</v>
       </c>
       <c r="P106" t="n">
         <v>22900</v>
@@ -4854,10 +4854,10 @@
         <v>39</v>
       </c>
       <c r="N108" t="n">
-        <v>10994.360689655</v>
+        <v>10994.361428571</v>
       </c>
       <c r="O108" t="n">
-        <v>428780.0668965451</v>
+        <v>428780.095714269</v>
       </c>
       <c r="P108" t="n">
         <v>16900</v>
@@ -5013,22 +5013,22 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N112" t="n">
-        <v>15711.966041667</v>
+        <v>15711.966008403</v>
       </c>
       <c r="O112" t="n">
-        <v>455647.015208343</v>
+        <v>439935.048235284</v>
       </c>
       <c r="P112" t="n">
         <v>28500</v>
       </c>
       <c r="Q112" t="n">
-        <v>826500</v>
+        <v>798000</v>
       </c>
     </row>
     <row r="113">
@@ -5271,22 +5271,22 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M118" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N118" t="n">
         <v>6321.94</v>
       </c>
       <c r="O118" t="n">
-        <v>189658.2</v>
+        <v>126438.8</v>
       </c>
       <c r="P118" t="n">
         <v>14100</v>
       </c>
       <c r="Q118" t="n">
-        <v>423000</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="119">
@@ -5859,22 +5859,22 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N132" t="n">
-        <v>36306.345</v>
+        <v>36306.361428571</v>
       </c>
       <c r="O132" t="n">
-        <v>254144.415</v>
+        <v>217838.168571426</v>
       </c>
       <c r="P132" t="n">
         <v>64900</v>
       </c>
       <c r="Q132" t="n">
-        <v>454300</v>
+        <v>389400</v>
       </c>
     </row>
     <row r="133">
@@ -5906,22 +5906,22 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N133" t="n">
-        <v>56906.802542373</v>
+        <v>56906.802982456</v>
       </c>
       <c r="O133" t="n">
-        <v>569068.02542373</v>
+        <v>512161.226842104</v>
       </c>
       <c r="P133" t="n">
         <v>95900</v>
       </c>
       <c r="Q133" t="n">
-        <v>959000</v>
+        <v>863100</v>
       </c>
     </row>
     <row r="134">
@@ -5959,10 +5959,10 @@
         <v>7</v>
       </c>
       <c r="N134" t="n">
-        <v>62349.658857143</v>
+        <v>62349.657575758</v>
       </c>
       <c r="O134" t="n">
-        <v>436447.612000001</v>
+        <v>436447.603030306</v>
       </c>
       <c r="P134" t="n">
         <v>109900</v>
@@ -6095,10 +6095,10 @@
         <v>12</v>
       </c>
       <c r="N137" t="n">
-        <v>200072.2004878</v>
+        <v>200072.20057377</v>
       </c>
       <c r="O137" t="n">
-        <v>2400866.4058536</v>
+        <v>2400866.40688524</v>
       </c>
       <c r="P137" t="n">
         <v>312000</v>
@@ -9569,22 +9569,22 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M217" t="n">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="N217" t="n">
-        <v>1950.2146835443</v>
+        <v>1950.2146537678</v>
       </c>
       <c r="O217" t="n">
-        <v>551910.7554430369</v>
+        <v>534358.8151323772</v>
       </c>
       <c r="P217" t="n">
         <v>2900</v>
       </c>
       <c r="Q217" t="n">
-        <v>820700</v>
+        <v>794600</v>
       </c>
     </row>
     <row r="218">
@@ -9733,22 +9733,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M221" t="n">
-        <v>1764</v>
+        <v>1747</v>
       </c>
       <c r="N221" t="n">
         <v>1726.32</v>
       </c>
       <c r="O221" t="n">
-        <v>3045228.48</v>
+        <v>3015881.04</v>
       </c>
       <c r="P221" t="n">
         <v>1500</v>
       </c>
       <c r="Q221" t="n">
-        <v>2646000</v>
+        <v>2620500</v>
       </c>
     </row>
     <row r="222">
@@ -9820,22 +9820,22 @@
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M223" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="N223" t="n">
-        <v>4937.3101616458</v>
+        <v>4937.3101623616</v>
       </c>
       <c r="O223" t="n">
-        <v>602351.8397207876</v>
+        <v>572727.9788339456</v>
       </c>
       <c r="P223" t="n">
         <v>7500</v>
       </c>
       <c r="Q223" t="n">
-        <v>915000</v>
+        <v>870000</v>
       </c>
     </row>
     <row r="224">
@@ -10284,22 +10284,22 @@
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M234" t="n">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="N234" t="n">
-        <v>1098.0574483741</v>
+        <v>1098.0580436917</v>
       </c>
       <c r="O234" t="n">
-        <v>578676.2752931507</v>
+        <v>575382.4148944508</v>
       </c>
       <c r="P234" t="n">
         <v>1500</v>
       </c>
       <c r="Q234" t="n">
-        <v>790500</v>
+        <v>786000</v>
       </c>
     </row>
     <row r="235">
@@ -10412,22 +10412,22 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M237" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N237" t="n">
-        <v>21084.771462766</v>
+        <v>21084.771466667</v>
       </c>
       <c r="O237" t="n">
-        <v>316271.57194149</v>
+        <v>295186.800533338</v>
       </c>
       <c r="P237" t="n">
         <v>30000</v>
       </c>
       <c r="Q237" t="n">
-        <v>450000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="238">
@@ -11394,22 +11394,22 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M260" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N260" t="n">
         <v>12114.32</v>
       </c>
       <c r="O260" t="n">
-        <v>72685.92</v>
+        <v>48457.28</v>
       </c>
       <c r="P260" t="n">
         <v>20900</v>
       </c>
       <c r="Q260" t="n">
-        <v>125400</v>
+        <v>83600</v>
       </c>
     </row>
     <row r="261">
@@ -11645,22 +11645,22 @@
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M266" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N266" t="n">
         <v>2913</v>
       </c>
       <c r="O266" t="n">
-        <v>719511</v>
+        <v>704946</v>
       </c>
       <c r="P266" t="n">
         <v>4950</v>
       </c>
       <c r="Q266" t="n">
-        <v>1222650</v>
+        <v>1197900</v>
       </c>
     </row>
     <row r="267">
@@ -11735,22 +11735,22 @@
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M268" t="n">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="N268" t="n">
         <v>2804.33</v>
       </c>
       <c r="O268" t="n">
-        <v>1576033.46</v>
+        <v>1564816.14</v>
       </c>
       <c r="P268" t="n">
         <v>4900</v>
       </c>
       <c r="Q268" t="n">
-        <v>2753800</v>
+        <v>2734200</v>
       </c>
     </row>
     <row r="269">
@@ -11776,22 +11776,22 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M269" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N269" t="n">
         <v>2850.95</v>
       </c>
       <c r="O269" t="n">
-        <v>456152</v>
+        <v>450450.1</v>
       </c>
       <c r="P269" t="n">
         <v>4900</v>
       </c>
       <c r="Q269" t="n">
-        <v>784000</v>
+        <v>774200</v>
       </c>
     </row>
     <row r="270">
@@ -12091,22 +12091,22 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M276" t="n">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="N276" t="n">
-        <v>2582.2558919365</v>
+        <v>2582.2558569052</v>
       </c>
       <c r="O276" t="n">
-        <v>637817.2053083156</v>
+        <v>606830.126372722</v>
       </c>
       <c r="P276" t="n">
         <v>4500</v>
       </c>
       <c r="Q276" t="n">
-        <v>1111500</v>
+        <v>1057500</v>
       </c>
     </row>
     <row r="277">
@@ -12137,22 +12137,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M277" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="N277" t="n">
         <v>10600</v>
       </c>
       <c r="O277" t="n">
-        <v>869200</v>
+        <v>657200</v>
       </c>
       <c r="P277" t="n">
         <v>17200</v>
       </c>
       <c r="Q277" t="n">
-        <v>1410400</v>
+        <v>1066400</v>
       </c>
     </row>
     <row r="278">
@@ -12189,10 +12189,10 @@
         <v>106</v>
       </c>
       <c r="N278" t="n">
-        <v>5216.8961798703</v>
+        <v>5216.8961652752</v>
       </c>
       <c r="O278" t="n">
-        <v>552990.9950662518</v>
+        <v>552990.9935191711</v>
       </c>
       <c r="P278" t="n">
         <v>8500</v>
@@ -12526,22 +12526,22 @@
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M286" t="n">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="N286" t="n">
-        <v>3158.8608246566</v>
+        <v>3158.8608249792</v>
       </c>
       <c r="O286" t="n">
-        <v>2220679.15973359</v>
+        <v>2195408.273360544</v>
       </c>
       <c r="P286" t="n">
         <v>5600</v>
       </c>
       <c r="Q286" t="n">
-        <v>3936800</v>
+        <v>3892000</v>
       </c>
     </row>
     <row r="287">
@@ -12754,22 +12754,22 @@
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M291" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="N291" t="n">
-        <v>3230.0674725275</v>
+        <v>3230.0674157303</v>
       </c>
       <c r="O291" t="n">
-        <v>323006.74725275</v>
+        <v>284245.9325842664</v>
       </c>
       <c r="P291" t="n">
         <v>6200</v>
       </c>
       <c r="Q291" t="n">
-        <v>620000</v>
+        <v>545600</v>
       </c>
     </row>
     <row r="292">
@@ -12933,22 +12933,22 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M295" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N295" t="n">
         <v>1337.34</v>
       </c>
       <c r="O295" t="n">
-        <v>382479.24</v>
+        <v>379804.56</v>
       </c>
       <c r="P295" t="n">
         <v>2500</v>
       </c>
       <c r="Q295" t="n">
-        <v>715000</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="296">
@@ -12979,22 +12979,22 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M296" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N296" t="n">
-        <v>2694.8232527881</v>
+        <v>2694.823243369</v>
       </c>
       <c r="O296" t="n">
-        <v>269482.32527881</v>
+        <v>261397.854606793</v>
       </c>
       <c r="P296" t="n">
         <v>4900</v>
       </c>
       <c r="Q296" t="n">
-        <v>490000</v>
+        <v>475300</v>
       </c>
     </row>
     <row r="297">
@@ -13066,22 +13066,22 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M298" t="n">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="N298" t="n">
         <v>1026.13</v>
       </c>
       <c r="O298" t="n">
-        <v>505882.09</v>
+        <v>486385.6200000001</v>
       </c>
       <c r="P298" t="n">
         <v>1900</v>
       </c>
       <c r="Q298" t="n">
-        <v>936700</v>
+        <v>900600</v>
       </c>
     </row>
     <row r="299">
@@ -13158,22 +13158,22 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M300" t="n">
-        <v>4265</v>
+        <v>4255</v>
       </c>
       <c r="N300" t="n">
         <v>156.25</v>
       </c>
       <c r="O300" t="n">
-        <v>666406.25</v>
+        <v>664843.75</v>
       </c>
       <c r="P300" t="n">
         <v>250</v>
       </c>
       <c r="Q300" t="n">
-        <v>1066250</v>
+        <v>1063750</v>
       </c>
     </row>
     <row r="301">
@@ -13204,22 +13204,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M301" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="N301" t="n">
         <v>7507.39</v>
       </c>
       <c r="O301" t="n">
-        <v>1208689.79</v>
+        <v>1118601.11</v>
       </c>
       <c r="P301" t="n">
         <v>13500</v>
       </c>
       <c r="Q301" t="n">
-        <v>2173500</v>
+        <v>2011500</v>
       </c>
     </row>
     <row r="302">
@@ -13253,22 +13253,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N302" t="n">
         <v>8796</v>
       </c>
       <c r="O302" t="n">
-        <v>765252</v>
+        <v>756456</v>
       </c>
       <c r="P302" t="n">
         <v>14900</v>
       </c>
       <c r="Q302" t="n">
-        <v>1296300</v>
+        <v>1281400</v>
       </c>
     </row>
     <row r="303">
@@ -13568,22 +13568,22 @@
         <v>0</v>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M309" t="n">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="N309" t="n">
         <v>4357.55</v>
       </c>
       <c r="O309" t="n">
-        <v>1032739.35</v>
+        <v>1002236.5</v>
       </c>
       <c r="P309" t="n">
         <v>7500</v>
       </c>
       <c r="Q309" t="n">
-        <v>1777500</v>
+        <v>1725000</v>
       </c>
     </row>
     <row r="310">
@@ -13701,22 +13701,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M312" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N312" t="n">
-        <v>4890.9300476474</v>
+        <v>4890.9300481348</v>
       </c>
       <c r="O312" t="n">
-        <v>195637.201905896</v>
+        <v>180964.4117809876</v>
       </c>
       <c r="P312" t="n">
         <v>8200</v>
       </c>
       <c r="Q312" t="n">
-        <v>328000</v>
+        <v>303400</v>
       </c>
     </row>
     <row r="313">
@@ -13796,22 +13796,22 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M314" t="n">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="N314" t="n">
         <v>1203.38</v>
       </c>
       <c r="O314" t="n">
-        <v>969924.2800000001</v>
+        <v>950670.2000000001</v>
       </c>
       <c r="P314" t="n">
         <v>1900</v>
       </c>
       <c r="Q314" t="n">
-        <v>1531400</v>
+        <v>1501000</v>
       </c>
     </row>
     <row r="315">
@@ -13842,22 +13842,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M315" t="n">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="N315" t="n">
         <v>3472</v>
       </c>
       <c r="O315" t="n">
-        <v>2794960</v>
+        <v>2784544</v>
       </c>
       <c r="P315" t="n">
         <v>4800</v>
       </c>
       <c r="Q315" t="n">
-        <v>3864000</v>
+        <v>3849600</v>
       </c>
     </row>
     <row r="316">
@@ -13888,22 +13888,22 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M316" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N316" t="n">
         <v>5888</v>
       </c>
       <c r="O316" t="n">
-        <v>194304</v>
+        <v>170752</v>
       </c>
       <c r="P316" t="n">
         <v>9500</v>
       </c>
       <c r="Q316" t="n">
-        <v>313500</v>
+        <v>275500</v>
       </c>
     </row>
     <row r="317">
@@ -14149,22 +14149,22 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M322" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="N322" t="n">
         <v>7041</v>
       </c>
       <c r="O322" t="n">
-        <v>274599</v>
+        <v>218271</v>
       </c>
       <c r="P322" t="n">
         <v>11500</v>
       </c>
       <c r="Q322" t="n">
-        <v>448500</v>
+        <v>356500</v>
       </c>
     </row>
     <row r="323">
@@ -14587,22 +14587,22 @@
         <v>0</v>
       </c>
       <c r="L332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M332" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N332" t="n">
-        <v>3594.25408867</v>
+        <v>3594.2540740741</v>
       </c>
       <c r="O332" t="n">
-        <v>194089.72078818</v>
+        <v>190495.4659259273</v>
       </c>
       <c r="P332" t="n">
         <v>6500</v>
       </c>
       <c r="Q332" t="n">
-        <v>351000</v>
+        <v>344500</v>
       </c>
     </row>
     <row r="333">
@@ -14715,22 +14715,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M335" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="N335" t="n">
         <v>2953.73</v>
       </c>
       <c r="O335" t="n">
-        <v>567116.16</v>
+        <v>558254.97</v>
       </c>
       <c r="P335" t="n">
         <v>4900</v>
       </c>
       <c r="Q335" t="n">
-        <v>940800</v>
+        <v>926100</v>
       </c>
     </row>
     <row r="336">
@@ -14762,10 +14762,10 @@
         <v>222</v>
       </c>
       <c r="N336" t="n">
-        <v>3240.8500313972</v>
+        <v>3240.8500314961</v>
       </c>
       <c r="O336" t="n">
-        <v>719468.7069701784</v>
+        <v>719468.7069921342</v>
       </c>
       <c r="P336" t="n">
         <v>5200</v>
@@ -14894,22 +14894,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N339" t="n">
-        <v>14822.378855098</v>
+        <v>14822.378854415</v>
       </c>
       <c r="O339" t="n">
-        <v>874520.3524507821</v>
+        <v>859697.97355607</v>
       </c>
       <c r="P339" t="n">
         <v>24900</v>
       </c>
       <c r="Q339" t="n">
-        <v>1469100</v>
+        <v>1444200</v>
       </c>
     </row>
     <row r="340">
@@ -14976,28 +14976,28 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>432</v>
+        <v>528</v>
       </c>
       <c r="K341" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="M341" t="n">
-        <v>432</v>
+        <v>629</v>
       </c>
       <c r="N341" t="n">
         <v>2090.85</v>
       </c>
       <c r="O341" t="n">
-        <v>903247.2</v>
+        <v>1315144.65</v>
       </c>
       <c r="P341" t="n">
         <v>2900</v>
       </c>
       <c r="Q341" t="n">
-        <v>1252800</v>
+        <v>1824100</v>
       </c>
     </row>
     <row r="342">
@@ -15073,10 +15073,10 @@
         <v>321</v>
       </c>
       <c r="N343" t="n">
-        <v>5191.4800275862</v>
+        <v>5191.4800277778</v>
       </c>
       <c r="O343" t="n">
-        <v>1666465.08885517</v>
+        <v>1666465.088916674</v>
       </c>
       <c r="P343" t="n">
         <v>9100</v>
@@ -15204,22 +15204,22 @@
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M346" t="n">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="N346" t="n">
         <v>1381.75</v>
       </c>
       <c r="O346" t="n">
-        <v>233515.75</v>
+        <v>204499</v>
       </c>
       <c r="P346" t="n">
         <v>2500</v>
       </c>
       <c r="Q346" t="n">
-        <v>422500</v>
+        <v>370000</v>
       </c>
     </row>
     <row r="347">
@@ -15519,10 +15519,10 @@
         <v>426</v>
       </c>
       <c r="N353" t="n">
-        <v>3041.6600129618</v>
+        <v>3041.6600129786</v>
       </c>
       <c r="O353" t="n">
-        <v>1295747.165521727</v>
+        <v>1295747.165528884</v>
       </c>
       <c r="P353" t="n">
         <v>5500</v>
@@ -15606,10 +15606,10 @@
         <v>206</v>
       </c>
       <c r="N355" t="n">
-        <v>4372.210788556</v>
+        <v>4372.2107886682</v>
       </c>
       <c r="O355" t="n">
-        <v>900675.422442536</v>
+        <v>900675.4224656491</v>
       </c>
       <c r="P355" t="n">
         <v>7500</v>
@@ -15644,22 +15644,22 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M356" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N356" t="n">
         <v>6441.03</v>
       </c>
       <c r="O356" t="n">
-        <v>328492.53</v>
+        <v>251200.17</v>
       </c>
       <c r="P356" t="n">
         <v>10500</v>
       </c>
       <c r="Q356" t="n">
-        <v>535500</v>
+        <v>409500</v>
       </c>
     </row>
     <row r="357">
@@ -15696,10 +15696,10 @@
         <v>13</v>
       </c>
       <c r="N357" t="n">
-        <v>1592.5670028818</v>
+        <v>1592.5669608416</v>
       </c>
       <c r="O357" t="n">
-        <v>20703.3710374634</v>
+        <v>20703.3704909408</v>
       </c>
       <c r="P357" t="n">
         <v>3900</v>
@@ -16479,22 +16479,22 @@
         <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M375" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="N375" t="n">
-        <v>1532.6290283636</v>
+        <v>1532.6290281516</v>
       </c>
       <c r="O375" t="n">
-        <v>499637.0632465336</v>
+        <v>495039.1760929668</v>
       </c>
       <c r="P375" t="n">
         <v>1200</v>
       </c>
       <c r="Q375" t="n">
-        <v>391200</v>
+        <v>387600</v>
       </c>
     </row>
     <row r="376">
@@ -16652,22 +16652,22 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M379" t="n">
-        <v>590</v>
+        <v>320</v>
       </c>
       <c r="N379" t="n">
         <v>1647.46</v>
       </c>
       <c r="O379" t="n">
-        <v>972001.4</v>
+        <v>527187.2</v>
       </c>
       <c r="P379" t="n">
         <v>2900</v>
       </c>
       <c r="Q379" t="n">
-        <v>1711000</v>
+        <v>928000</v>
       </c>
     </row>
     <row r="380">
@@ -16740,22 +16740,22 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M381" t="n">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="N381" t="n">
         <v>1387.55</v>
       </c>
       <c r="O381" t="n">
-        <v>678511.95</v>
+        <v>647985.85</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
       </c>
       <c r="Q381" t="n">
-        <v>1124700</v>
+        <v>1074100</v>
       </c>
     </row>
     <row r="382">
@@ -16910,22 +16910,22 @@
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M385" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N385" t="n">
         <v>13304.13</v>
       </c>
       <c r="O385" t="n">
-        <v>478948.68</v>
+        <v>465644.55</v>
       </c>
       <c r="P385" t="n">
         <v>20900</v>
       </c>
       <c r="Q385" t="n">
-        <v>752400</v>
+        <v>731500</v>
       </c>
     </row>
     <row r="386">
@@ -16954,22 +16954,22 @@
         <v>0</v>
       </c>
       <c r="L386" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M386" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N386" t="n">
         <v>2204</v>
       </c>
       <c r="O386" t="n">
-        <v>185136</v>
+        <v>178524</v>
       </c>
       <c r="P386" t="n">
         <v>1500</v>
       </c>
       <c r="Q386" t="n">
-        <v>126000</v>
+        <v>121500</v>
       </c>
     </row>
     <row r="387">
@@ -17757,22 +17757,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M404" t="n">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="N404" t="n">
-        <v>1630.9234162594</v>
+        <v>1630.9234624043</v>
       </c>
       <c r="O404" t="n">
-        <v>1004648.82441579</v>
+        <v>976923.1539801756</v>
       </c>
       <c r="P404" t="n">
         <v>2500</v>
       </c>
       <c r="Q404" t="n">
-        <v>1540000</v>
+        <v>1497500</v>
       </c>
     </row>
     <row r="405">
@@ -17844,22 +17844,22 @@
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M406" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N406" t="n">
-        <v>1467.3247826087</v>
+        <v>1467.3243362832</v>
       </c>
       <c r="O406" t="n">
-        <v>297866.9308695661</v>
+        <v>291997.5429203568</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
       </c>
       <c r="Q406" t="n">
-        <v>507500</v>
+        <v>497500</v>
       </c>
     </row>
     <row r="407">
@@ -17890,22 +17890,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M407" t="n">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N407" t="n">
-        <v>1690.5995518395</v>
+        <v>1690.5992886179</v>
       </c>
       <c r="O407" t="n">
-        <v>382075.498715727</v>
+        <v>361788.2477642306</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
       </c>
       <c r="Q407" t="n">
-        <v>655400</v>
+        <v>620600</v>
       </c>
     </row>
     <row r="408">
@@ -17936,22 +17936,22 @@
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M408" t="n">
-        <v>1622</v>
+        <v>1568</v>
       </c>
       <c r="N408" t="n">
-        <v>1550.1934418475</v>
+        <v>1550.1935205388</v>
       </c>
       <c r="O408" t="n">
-        <v>2514413.762676645</v>
+        <v>2430703.440204838</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
       </c>
       <c r="Q408" t="n">
-        <v>4055000</v>
+        <v>3920000</v>
       </c>
     </row>
     <row r="409">
@@ -17988,10 +17988,10 @@
         <v>3</v>
       </c>
       <c r="N409" t="n">
-        <v>1579.3908418367</v>
+        <v>1579.3907948718</v>
       </c>
       <c r="O409" t="n">
-        <v>4738.1725255101</v>
+        <v>4738.1723846154</v>
       </c>
       <c r="P409" t="n">
         <v>2900</v>
@@ -18028,22 +18028,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M410" t="n">
-        <v>933</v>
+        <v>912</v>
       </c>
       <c r="N410" t="n">
-        <v>2403.5113112366</v>
+        <v>2403.5114869613</v>
       </c>
       <c r="O410" t="n">
-        <v>2242476.053383748</v>
+        <v>2192002.476108706</v>
       </c>
       <c r="P410" t="n">
         <v>3500</v>
       </c>
       <c r="Q410" t="n">
-        <v>3265500</v>
+        <v>3192000</v>
       </c>
     </row>
     <row r="411">
@@ -18072,22 +18072,22 @@
         <v>0</v>
       </c>
       <c r="L411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M411" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N411" t="n">
         <v>24267.77</v>
       </c>
       <c r="O411" t="n">
-        <v>121338.85</v>
+        <v>97071.08</v>
       </c>
       <c r="P411" t="n">
         <v>33400</v>
       </c>
       <c r="Q411" t="n">
-        <v>167000</v>
+        <v>133600</v>
       </c>
     </row>
     <row r="412">
@@ -19390,22 +19390,22 @@
         <v>0</v>
       </c>
       <c r="L441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N441" t="n">
         <v>17328</v>
       </c>
       <c r="O441" t="n">
-        <v>693120</v>
+        <v>675792</v>
       </c>
       <c r="P441" t="n">
         <v>32900</v>
       </c>
       <c r="Q441" t="n">
-        <v>1316000</v>
+        <v>1283100</v>
       </c>
     </row>
     <row r="442">
@@ -19648,25 +19648,25 @@
         <v>95</v>
       </c>
       <c r="K447" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L447" t="n">
         <v>0</v>
       </c>
       <c r="M447" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="N447" t="n">
         <v>7028</v>
       </c>
       <c r="O447" t="n">
-        <v>667660</v>
+        <v>695772</v>
       </c>
       <c r="P447" t="n">
         <v>15900</v>
       </c>
       <c r="Q447" t="n">
-        <v>1510500</v>
+        <v>1574100</v>
       </c>
     </row>
     <row r="448">
@@ -21468,22 +21468,22 @@
         <v>0</v>
       </c>
       <c r="L490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M490" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N490" t="n">
         <v>1969</v>
       </c>
       <c r="O490" t="n">
-        <v>277629</v>
+        <v>275660</v>
       </c>
       <c r="P490" t="n">
         <v>1500</v>
       </c>
       <c r="Q490" t="n">
-        <v>211500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="491">
@@ -21637,22 +21637,22 @@
         <v>0</v>
       </c>
       <c r="L494" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M494" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="N494" t="n">
         <v>2567</v>
       </c>
       <c r="O494" t="n">
-        <v>813739</v>
+        <v>803471</v>
       </c>
       <c r="P494" t="n">
         <v>4500</v>
       </c>
       <c r="Q494" t="n">
-        <v>1426500</v>
+        <v>1408500</v>
       </c>
     </row>
     <row r="495">
@@ -22012,10 +22012,10 @@
         <v>461</v>
       </c>
       <c r="N503" t="n">
-        <v>2029.8737332006</v>
+        <v>2029.8737350598</v>
       </c>
       <c r="O503" t="n">
-        <v>935771.7910054766</v>
+        <v>935771.7918625679</v>
       </c>
       <c r="P503" t="n">
         <v>3600</v>
@@ -22252,22 +22252,22 @@
         <v>0</v>
       </c>
       <c r="L509" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M509" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N509" t="n">
-        <v>22485.695890411</v>
+        <v>22485.695885714</v>
       </c>
       <c r="O509" t="n">
-        <v>1281684.665753427</v>
+        <v>1259198.969599984</v>
       </c>
       <c r="P509" t="n">
         <v>36500</v>
       </c>
       <c r="Q509" t="n">
-        <v>2080500</v>
+        <v>2044000</v>
       </c>
     </row>
     <row r="510">
@@ -22594,10 +22594,10 @@
         <v>169</v>
       </c>
       <c r="N517" t="n">
-        <v>2680.7396999388</v>
+        <v>2680.7396995708</v>
       </c>
       <c r="O517" t="n">
-        <v>453045.0092896572</v>
+        <v>453045.0092274652</v>
       </c>
       <c r="P517" t="n">
         <v>4900</v>
@@ -22629,22 +22629,22 @@
         <v>0</v>
       </c>
       <c r="L518" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M518" t="n">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="N518" t="n">
-        <v>880.32945034206</v>
+        <v>880.3295131797699</v>
       </c>
       <c r="O518" t="n">
-        <v>1188444.757961781</v>
+        <v>1185803.85425315</v>
       </c>
       <c r="P518" t="n">
         <v>1200</v>
       </c>
       <c r="Q518" t="n">
-        <v>1620000</v>
+        <v>1616400</v>
       </c>
     </row>
     <row r="519">
@@ -23136,22 +23136,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M530" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N530" t="n">
         <v>30611</v>
       </c>
       <c r="O530" t="n">
-        <v>1836660</v>
+        <v>1806049</v>
       </c>
       <c r="P530" t="n">
         <v>38900</v>
       </c>
       <c r="Q530" t="n">
-        <v>2334000</v>
+        <v>2295100</v>
       </c>
     </row>
     <row r="531">
@@ -23621,10 +23621,10 @@
         <v>278</v>
       </c>
       <c r="N541" t="n">
-        <v>4285.1953927813</v>
+        <v>4285.1954215582</v>
       </c>
       <c r="O541" t="n">
-        <v>1191284.319193201</v>
+        <v>1191284.32719318</v>
       </c>
       <c r="P541" t="n">
         <v>6900</v>
@@ -23705,22 +23705,22 @@
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M543" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N543" t="n">
         <v>9776.99</v>
       </c>
       <c r="O543" t="n">
-        <v>2072721.88</v>
+        <v>2043390.91</v>
       </c>
       <c r="P543" t="n">
         <v>15900</v>
       </c>
       <c r="Q543" t="n">
-        <v>3370800</v>
+        <v>3323100</v>
       </c>
     </row>
     <row r="544">
@@ -23787,22 +23787,22 @@
         <v>0</v>
       </c>
       <c r="L545" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M545" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N545" t="n">
-        <v>12132.858149466</v>
+        <v>12132.858122744</v>
       </c>
       <c r="O545" t="n">
-        <v>400384.318932378</v>
+        <v>351852.885559576</v>
       </c>
       <c r="P545" t="n">
         <v>15900</v>
       </c>
       <c r="Q545" t="n">
-        <v>524700</v>
+        <v>461100</v>
       </c>
     </row>
     <row r="546">
@@ -24427,22 +24427,22 @@
         <v>0</v>
       </c>
       <c r="L560" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M560" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N560" t="n">
-        <v>11562.038522427</v>
+        <v>11562.038518519</v>
       </c>
       <c r="O560" t="n">
-        <v>612788.0416886309</v>
+        <v>601226.002962988</v>
       </c>
       <c r="P560" t="n">
         <v>18500</v>
       </c>
       <c r="Q560" t="n">
-        <v>980500</v>
+        <v>962000</v>
       </c>
     </row>
     <row r="561">
@@ -24519,22 +24519,22 @@
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M562" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N562" t="n">
-        <v>12005.159831224</v>
+        <v>12005.159830508</v>
       </c>
       <c r="O562" t="n">
-        <v>768330.229198336</v>
+        <v>756325.069322004</v>
       </c>
       <c r="P562" t="n">
         <v>19500</v>
       </c>
       <c r="Q562" t="n">
-        <v>1248000</v>
+        <v>1228500</v>
       </c>
     </row>
     <row r="563">
@@ -25103,22 +25103,22 @@
         <v>0</v>
       </c>
       <c r="L576" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M576" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N576" t="n">
         <v>39596.9</v>
       </c>
       <c r="O576" t="n">
-        <v>475162.8</v>
+        <v>435565.9</v>
       </c>
       <c r="P576" t="n">
         <v>64900</v>
       </c>
       <c r="Q576" t="n">
-        <v>778800</v>
+        <v>713900</v>
       </c>
     </row>
     <row r="577">
@@ -25282,22 +25282,22 @@
         <v>0</v>
       </c>
       <c r="L580" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M580" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N580" t="n">
         <v>21418.04</v>
       </c>
       <c r="O580" t="n">
-        <v>706795.3200000001</v>
+        <v>663959.24</v>
       </c>
       <c r="P580" t="n">
         <v>34900</v>
       </c>
       <c r="Q580" t="n">
-        <v>1151700</v>
+        <v>1081900</v>
       </c>
     </row>
     <row r="581">
@@ -25630,22 +25630,22 @@
         <v>0</v>
       </c>
       <c r="L588" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M588" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N588" t="n">
         <v>22730.48</v>
       </c>
       <c r="O588" t="n">
-        <v>522801.04</v>
+        <v>500070.56</v>
       </c>
       <c r="P588" t="n">
         <v>36900</v>
       </c>
       <c r="Q588" t="n">
-        <v>848700</v>
+        <v>811800</v>
       </c>
     </row>
     <row r="589">
@@ -25860,22 +25860,22 @@
         <v>0</v>
       </c>
       <c r="L593" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M593" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N593" t="n">
         <v>16974.69</v>
       </c>
       <c r="O593" t="n">
-        <v>1357975.2</v>
+        <v>1324025.82</v>
       </c>
       <c r="P593" t="n">
         <v>26900</v>
       </c>
       <c r="Q593" t="n">
-        <v>2152000</v>
+        <v>2098200</v>
       </c>
     </row>
     <row r="594">
@@ -26244,22 +26244,22 @@
         <v>0</v>
       </c>
       <c r="L602" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M602" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="N602" t="n">
-        <v>1561</v>
+        <v>1561.0000887728</v>
       </c>
       <c r="O602" t="n">
-        <v>112392</v>
+        <v>106148.0060365504</v>
       </c>
       <c r="P602" t="n">
         <v>2900</v>
       </c>
       <c r="Q602" t="n">
-        <v>208800</v>
+        <v>197200</v>
       </c>
     </row>
     <row r="603">
@@ -26513,22 +26513,22 @@
         <v>0</v>
       </c>
       <c r="L608" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M608" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N608" t="n">
-        <v>7969.9501660377</v>
+        <v>7969.9501665405</v>
       </c>
       <c r="O608" t="n">
-        <v>1083913.222581127</v>
+        <v>1067973.322316427</v>
       </c>
       <c r="P608" t="n">
         <v>12900</v>
       </c>
       <c r="Q608" t="n">
-        <v>1754400</v>
+        <v>1728600</v>
       </c>
     </row>
     <row r="609">
@@ -27972,10 +27972,10 @@
         <v>66</v>
       </c>
       <c r="N642" t="n">
-        <v>3113.8900273598</v>
+        <v>3113.8900274725</v>
       </c>
       <c r="O642" t="n">
-        <v>205516.7418057468</v>
+        <v>205516.741813185</v>
       </c>
       <c r="P642" t="n">
         <v>5000</v>
@@ -28156,10 +28156,10 @@
         <v>14</v>
       </c>
       <c r="N646" t="n">
-        <v>4163.1602</v>
+        <v>4163.1602061856</v>
       </c>
       <c r="O646" t="n">
-        <v>58284.24280000001</v>
+        <v>58284.2428865984</v>
       </c>
       <c r="P646" t="n">
         <v>6700</v>
@@ -28340,10 +28340,10 @@
         <v>20</v>
       </c>
       <c r="N650" t="n">
-        <v>5218.1705346294</v>
+        <v>5218.1705412054</v>
       </c>
       <c r="O650" t="n">
-        <v>104363.410692588</v>
+        <v>104363.410824108</v>
       </c>
       <c r="P650" t="n">
         <v>8500</v>
@@ -28386,10 +28386,10 @@
         <v>133</v>
       </c>
       <c r="N651" t="n">
-        <v>1595.0094090202</v>
+        <v>1595.0093958665</v>
       </c>
       <c r="O651" t="n">
-        <v>212136.2513996866</v>
+        <v>212136.2496502445</v>
       </c>
       <c r="P651" t="n">
         <v>2600</v>
@@ -28794,22 +28794,22 @@
         <v>0</v>
       </c>
       <c r="L660" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M660" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N660" t="n">
         <v>14380</v>
       </c>
       <c r="O660" t="n">
-        <v>1409240</v>
+        <v>1394860</v>
       </c>
       <c r="P660" t="n">
         <v>23000</v>
       </c>
       <c r="Q660" t="n">
-        <v>2254000</v>
+        <v>2231000</v>
       </c>
     </row>
     <row r="661">
@@ -28840,22 +28840,22 @@
         <v>0</v>
       </c>
       <c r="L661" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M661" t="n">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="N661" t="n">
-        <v>1664.3579393305</v>
+        <v>1664.3571460424</v>
       </c>
       <c r="O661" t="n">
-        <v>609155.005794963</v>
+        <v>537587.3581716953</v>
       </c>
       <c r="P661" t="n">
         <v>2900</v>
       </c>
       <c r="Q661" t="n">
-        <v>1061400</v>
+        <v>936700</v>
       </c>
     </row>
     <row r="662">
@@ -29496,10 +29496,10 @@
         <v>1468</v>
       </c>
       <c r="N675" t="n">
-        <v>1778.4725974412</v>
+        <v>1778.4725978277</v>
       </c>
       <c r="O675" t="n">
-        <v>2610797.773043681</v>
+        <v>2610797.773611064</v>
       </c>
       <c r="P675" t="n">
         <v>4900</v>
@@ -29536,22 +29536,22 @@
         <v>0</v>
       </c>
       <c r="L676" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M676" t="n">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="N676" t="n">
         <v>1548</v>
       </c>
       <c r="O676" t="n">
-        <v>383904</v>
+        <v>371520</v>
       </c>
       <c r="P676" t="n">
         <v>3900</v>
       </c>
       <c r="Q676" t="n">
-        <v>967200</v>
+        <v>936000</v>
       </c>
     </row>
     <row r="677">
@@ -29999,22 +29999,22 @@
         <v>0</v>
       </c>
       <c r="L686" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M686" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N686" t="n">
         <v>4800</v>
       </c>
       <c r="O686" t="n">
-        <v>134400</v>
+        <v>120000</v>
       </c>
       <c r="P686" t="n">
         <v>7900</v>
       </c>
       <c r="Q686" t="n">
-        <v>221200</v>
+        <v>197500</v>
       </c>
     </row>
     <row r="687">
@@ -31011,22 +31011,22 @@
         <v>0</v>
       </c>
       <c r="L708" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M708" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N708" t="n">
         <v>1550</v>
       </c>
       <c r="O708" t="n">
-        <v>96100</v>
+        <v>94550</v>
       </c>
       <c r="P708" t="n">
         <v>2500</v>
       </c>
       <c r="Q708" t="n">
-        <v>155000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="709">
@@ -31106,22 +31106,22 @@
         <v>0</v>
       </c>
       <c r="L710" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M710" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N710" t="n">
         <v>44055</v>
       </c>
       <c r="O710" t="n">
-        <v>1057320</v>
+        <v>1013265</v>
       </c>
       <c r="P710" t="n">
         <v>70900</v>
       </c>
       <c r="Q710" t="n">
-        <v>1701600</v>
+        <v>1630700</v>
       </c>
     </row>
     <row r="711">
@@ -31612,22 +31612,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M721" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N721" t="n">
         <v>3424</v>
       </c>
       <c r="O721" t="n">
-        <v>606048</v>
+        <v>602624</v>
       </c>
       <c r="P721" t="n">
         <v>5900</v>
       </c>
       <c r="Q721" t="n">
-        <v>1044300</v>
+        <v>1038400</v>
       </c>
     </row>
     <row r="722">
@@ -31704,22 +31704,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M723" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="N723" t="n">
         <v>8858.16</v>
       </c>
       <c r="O723" t="n">
-        <v>3171221.28</v>
+        <v>3135788.64</v>
       </c>
       <c r="P723" t="n">
         <v>15500</v>
       </c>
       <c r="Q723" t="n">
-        <v>5549000</v>
+        <v>5487000</v>
       </c>
     </row>
     <row r="724">
@@ -31980,22 +31980,22 @@
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M729" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N729" t="n">
         <v>11376</v>
       </c>
       <c r="O729" t="n">
-        <v>534672</v>
+        <v>511920</v>
       </c>
       <c r="P729" t="n">
         <v>18500</v>
       </c>
       <c r="Q729" t="n">
-        <v>869500</v>
+        <v>832500</v>
       </c>
     </row>
     <row r="730">
@@ -32714,22 +32714,22 @@
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M745" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N745" t="n">
         <v>3519</v>
       </c>
       <c r="O745" t="n">
-        <v>848079</v>
+        <v>844560</v>
       </c>
       <c r="P745" t="n">
         <v>5900</v>
       </c>
       <c r="Q745" t="n">
-        <v>1421900</v>
+        <v>1416000</v>
       </c>
     </row>
     <row r="746">
@@ -32806,22 +32806,22 @@
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M747" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N747" t="n">
         <v>9003</v>
       </c>
       <c r="O747" t="n">
-        <v>603201</v>
+        <v>594198</v>
       </c>
       <c r="P747" t="n">
         <v>14900</v>
       </c>
       <c r="Q747" t="n">
-        <v>998300</v>
+        <v>983400</v>
       </c>
     </row>
     <row r="748">
@@ -33134,10 +33134,10 @@
         <v>16</v>
       </c>
       <c r="N754" t="n">
-        <v>4907.8220483871</v>
+        <v>4907.8220583468</v>
       </c>
       <c r="O754" t="n">
-        <v>78525.1527741936</v>
+        <v>78525.1529335488</v>
       </c>
       <c r="P754" t="n">
         <v>8200</v>
@@ -33220,22 +33220,22 @@
         <v>0</v>
       </c>
       <c r="L756" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M756" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N756" t="n">
         <v>13210</v>
       </c>
       <c r="O756" t="n">
-        <v>2087180</v>
+        <v>2060760</v>
       </c>
       <c r="P756" t="n">
         <v>23900</v>
       </c>
       <c r="Q756" t="n">
-        <v>3776200</v>
+        <v>3728400</v>
       </c>
     </row>
     <row r="757">
@@ -33404,22 +33404,22 @@
         <v>0</v>
       </c>
       <c r="L760" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M760" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="N760" t="n">
-        <v>3903.7363106796</v>
+        <v>3903.7364457831</v>
       </c>
       <c r="O760" t="n">
-        <v>577752.9739805808</v>
+        <v>558234.3117469833</v>
       </c>
       <c r="P760" t="n">
         <v>7500</v>
       </c>
       <c r="Q760" t="n">
-        <v>1110000</v>
+        <v>1072500</v>
       </c>
     </row>
     <row r="761">
@@ -33813,22 +33813,22 @@
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M769" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N769" t="n">
         <v>12556</v>
       </c>
       <c r="O769" t="n">
-        <v>1318380</v>
+        <v>1293268</v>
       </c>
       <c r="P769" t="n">
         <v>21900</v>
       </c>
       <c r="Q769" t="n">
-        <v>2299500</v>
+        <v>2255700</v>
       </c>
     </row>
     <row r="770">
@@ -33859,22 +33859,22 @@
         <v>0</v>
       </c>
       <c r="L770" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M770" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N770" t="n">
         <v>9839</v>
       </c>
       <c r="O770" t="n">
-        <v>737925</v>
+        <v>718247</v>
       </c>
       <c r="P770" t="n">
         <v>16900</v>
       </c>
       <c r="Q770" t="n">
-        <v>1267500</v>
+        <v>1233700</v>
       </c>
     </row>
     <row r="771">
@@ -34135,22 +34135,22 @@
         <v>0</v>
       </c>
       <c r="L776" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M776" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N776" t="n">
         <v>6268</v>
       </c>
       <c r="O776" t="n">
-        <v>582924</v>
+        <v>570388</v>
       </c>
       <c r="P776" t="n">
         <v>10900</v>
       </c>
       <c r="Q776" t="n">
-        <v>1013700</v>
+        <v>991900</v>
       </c>
     </row>
     <row r="777">
@@ -34273,22 +34273,22 @@
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M779" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="N779" t="n">
         <v>13098</v>
       </c>
       <c r="O779" t="n">
-        <v>1257408</v>
+        <v>1178820</v>
       </c>
       <c r="P779" t="n">
         <v>21200</v>
       </c>
       <c r="Q779" t="n">
-        <v>2035200</v>
+        <v>1908000</v>
       </c>
     </row>
     <row r="780">
@@ -34457,22 +34457,22 @@
         <v>0</v>
       </c>
       <c r="L783" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M783" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N783" t="n">
         <v>3898</v>
       </c>
       <c r="O783" t="n">
-        <v>1126522</v>
+        <v>1122624</v>
       </c>
       <c r="P783" t="n">
         <v>6900</v>
       </c>
       <c r="Q783" t="n">
-        <v>1994100</v>
+        <v>1987200</v>
       </c>
     </row>
     <row r="784">
@@ -34641,22 +34641,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M787" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N787" t="n">
         <v>5438</v>
       </c>
       <c r="O787" t="n">
-        <v>135950</v>
+        <v>114198</v>
       </c>
       <c r="P787" t="n">
         <v>8900</v>
       </c>
       <c r="Q787" t="n">
-        <v>222500</v>
+        <v>186900</v>
       </c>
     </row>
     <row r="788">
@@ -34782,22 +34782,22 @@
         <v>0</v>
       </c>
       <c r="L790" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M790" t="n">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="N790" t="n">
         <v>753</v>
       </c>
       <c r="O790" t="n">
-        <v>497733</v>
+        <v>490203</v>
       </c>
       <c r="P790" t="n">
         <v>1600</v>
       </c>
       <c r="Q790" t="n">
-        <v>1057600</v>
+        <v>1041600</v>
       </c>
     </row>
     <row r="791">
@@ -34966,22 +34966,22 @@
         <v>0</v>
       </c>
       <c r="L794" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M794" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N794" t="n">
         <v>11348</v>
       </c>
       <c r="O794" t="n">
-        <v>385832</v>
+        <v>363136</v>
       </c>
       <c r="P794" t="n">
         <v>19900</v>
       </c>
       <c r="Q794" t="n">
-        <v>676600</v>
+        <v>636800</v>
       </c>
     </row>
     <row r="795">
@@ -35012,22 +35012,22 @@
         <v>0</v>
       </c>
       <c r="L795" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M795" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N795" t="n">
-        <v>17075.98952381</v>
+        <v>17075.989523481</v>
       </c>
       <c r="O795" t="n">
-        <v>2937070.19809532</v>
+        <v>2919994.208515251</v>
       </c>
       <c r="P795" t="n">
         <v>27500</v>
       </c>
       <c r="Q795" t="n">
-        <v>4730000</v>
+        <v>4702500</v>
       </c>
     </row>
     <row r="796">
@@ -35237,22 +35237,22 @@
         <v>0</v>
       </c>
       <c r="L800" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M800" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N800" t="n">
         <v>11015</v>
       </c>
       <c r="O800" t="n">
-        <v>782065</v>
+        <v>771050</v>
       </c>
       <c r="P800" t="n">
         <v>17900</v>
       </c>
       <c r="Q800" t="n">
-        <v>1270900</v>
+        <v>1253000</v>
       </c>
     </row>
     <row r="801">
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="L807" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M807" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N807" t="n">
         <v>20014</v>
       </c>
       <c r="O807" t="n">
-        <v>360252</v>
+        <v>340238</v>
       </c>
       <c r="P807" t="n">
         <v>33900</v>
       </c>
       <c r="Q807" t="n">
-        <v>610200</v>
+        <v>576300</v>
       </c>
     </row>
     <row r="808">
@@ -36022,22 +36022,22 @@
         <v>0</v>
       </c>
       <c r="L817" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M817" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N817" t="n">
         <v>8700</v>
       </c>
       <c r="O817" t="n">
-        <v>765600</v>
+        <v>756900</v>
       </c>
       <c r="P817" t="n">
         <v>14900</v>
       </c>
       <c r="Q817" t="n">
-        <v>1311200</v>
+        <v>1296300</v>
       </c>
     </row>
     <row r="818">
@@ -36206,22 +36206,22 @@
         <v>0</v>
       </c>
       <c r="L821" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M821" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="N821" t="n">
         <v>3821</v>
       </c>
       <c r="O821" t="n">
-        <v>794768</v>
+        <v>764200</v>
       </c>
       <c r="P821" t="n">
         <v>5900</v>
       </c>
       <c r="Q821" t="n">
-        <v>1227200</v>
+        <v>1180000</v>
       </c>
     </row>
     <row r="822">
@@ -36531,22 +36531,22 @@
         <v>0</v>
       </c>
       <c r="L828" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M828" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N828" t="n">
         <v>1337.29</v>
       </c>
       <c r="O828" t="n">
-        <v>66864.5</v>
+        <v>60178.05</v>
       </c>
       <c r="P828" t="n">
         <v>2600</v>
       </c>
       <c r="Q828" t="n">
-        <v>130000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="829">
@@ -36721,10 +36721,10 @@
         <v>598</v>
       </c>
       <c r="N832" t="n">
-        <v>1516.0388031113</v>
+        <v>1516.0388018299</v>
       </c>
       <c r="O832" t="n">
-        <v>906591.2042605574</v>
+        <v>906591.2034942802</v>
       </c>
       <c r="P832" t="n">
         <v>2300</v>
@@ -36761,22 +36761,22 @@
         <v>0</v>
       </c>
       <c r="L833" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M833" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="N833" t="n">
-        <v>4248.652</v>
+        <v>4248.6728</v>
       </c>
       <c r="O833" t="n">
-        <v>220929.904</v>
+        <v>93470.80160000001</v>
       </c>
       <c r="P833" t="n">
         <v>5900</v>
       </c>
       <c r="Q833" t="n">
-        <v>306800</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="834">
@@ -36851,22 +36851,22 @@
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M835" t="n">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N835" t="n">
-        <v>2458.5132807977</v>
+        <v>2458.5132504039</v>
       </c>
       <c r="O835" t="n">
-        <v>823601.9490672295</v>
+        <v>799016.8063812676</v>
       </c>
       <c r="P835" t="n">
         <v>3500</v>
       </c>
       <c r="Q835" t="n">
-        <v>1172500</v>
+        <v>1137500</v>
       </c>
     </row>
     <row r="836">
@@ -36897,22 +36897,22 @@
         <v>0</v>
       </c>
       <c r="L836" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M836" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N836" t="n">
-        <v>1907.3938243626</v>
+        <v>1907.3938009479</v>
       </c>
       <c r="O836" t="n">
-        <v>308997.7995467412</v>
+        <v>305183.008151664</v>
       </c>
       <c r="P836" t="n">
         <v>2500</v>
       </c>
       <c r="Q836" t="n">
-        <v>405000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="837">
@@ -36949,10 +36949,10 @@
         <v>185</v>
       </c>
       <c r="N837" t="n">
-        <v>1771.0906468305</v>
+        <v>1771.0905981795</v>
       </c>
       <c r="O837" t="n">
-        <v>327651.7696636425</v>
+        <v>327651.7606632075</v>
       </c>
       <c r="P837" t="n">
         <v>2500</v>
@@ -36995,10 +36995,10 @@
         <v>411</v>
       </c>
       <c r="N838" t="n">
-        <v>2079.3840533333</v>
+        <v>2079.3840473807</v>
       </c>
       <c r="O838" t="n">
-        <v>854626.8459199863</v>
+        <v>854626.8434734676</v>
       </c>
       <c r="P838" t="n">
         <v>2900</v>
@@ -37035,22 +37035,22 @@
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M839" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="N839" t="n">
-        <v>1803.0155537353</v>
+        <v>1803.0155591997</v>
       </c>
       <c r="O839" t="n">
-        <v>746448.4392464142</v>
+        <v>741039.3948310767</v>
       </c>
       <c r="P839" t="n">
         <v>2500</v>
       </c>
       <c r="Q839" t="n">
-        <v>1035000</v>
+        <v>1027500</v>
       </c>
     </row>
     <row r="840">
@@ -37087,10 +37087,10 @@
         <v>71</v>
       </c>
       <c r="N840" t="n">
-        <v>3306.5952380952</v>
+        <v>3306.5951935915</v>
       </c>
       <c r="O840" t="n">
-        <v>234768.2619047592</v>
+        <v>234768.2587449965</v>
       </c>
       <c r="P840" t="n">
         <v>4900</v>
@@ -37127,22 +37127,22 @@
         <v>0</v>
       </c>
       <c r="L841" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M841" t="n">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N841" t="n">
-        <v>2122.1639235788</v>
+        <v>2122.1639198011</v>
       </c>
       <c r="O841" t="n">
-        <v>901919.6675209901</v>
+        <v>897675.3380758652</v>
       </c>
       <c r="P841" t="n">
         <v>2900</v>
       </c>
       <c r="Q841" t="n">
-        <v>1232500</v>
+        <v>1226700</v>
       </c>
     </row>
     <row r="842">
@@ -37170,25 +37170,25 @@
         <v>21</v>
       </c>
       <c r="K842" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L842" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M842" t="n">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="N842" t="n">
-        <v>2108.7910927573</v>
+        <v>2108.7914267016</v>
       </c>
       <c r="O842" t="n">
-        <v>44284.6129479033</v>
+        <v>360603.3339659736</v>
       </c>
       <c r="P842" t="n">
         <v>2900</v>
       </c>
       <c r="Q842" t="n">
-        <v>60900</v>
+        <v>495900</v>
       </c>
     </row>
     <row r="843">
@@ -37219,22 +37219,22 @@
         <v>0</v>
       </c>
       <c r="L843" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M843" t="n">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="N843" t="n">
-        <v>2056.0834704208</v>
+        <v>2056.0834183673</v>
       </c>
       <c r="O843" t="n">
-        <v>1821689.954792829</v>
+        <v>1811409.491581591</v>
       </c>
       <c r="P843" t="n">
         <v>2900</v>
       </c>
       <c r="Q843" t="n">
-        <v>2569400</v>
+        <v>2554900</v>
       </c>
     </row>
     <row r="844">
@@ -37271,10 +37271,10 @@
         <v>243</v>
       </c>
       <c r="N844" t="n">
-        <v>3224.5685035629</v>
+        <v>3224.5685238095</v>
       </c>
       <c r="O844" t="n">
-        <v>783570.1463657847</v>
+        <v>783570.1512857085</v>
       </c>
       <c r="P844" t="n">
         <v>4500</v>
@@ -37317,10 +37317,10 @@
         <v>455</v>
       </c>
       <c r="N845" t="n">
-        <v>1655.9309755302</v>
+        <v>1655.9309666884</v>
       </c>
       <c r="O845" t="n">
-        <v>753448.5938662409</v>
+        <v>753448.5898432221</v>
       </c>
       <c r="P845" t="n">
         <v>2500</v>
@@ -37452,22 +37452,22 @@
         <v>0</v>
       </c>
       <c r="L848" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M848" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N848" t="n">
         <v>3684</v>
       </c>
       <c r="O848" t="n">
-        <v>209988</v>
+        <v>206304</v>
       </c>
       <c r="P848" t="n">
         <v>6500</v>
       </c>
       <c r="Q848" t="n">
-        <v>370500</v>
+        <v>364000</v>
       </c>
     </row>
     <row r="849">
@@ -37544,22 +37544,22 @@
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M850" t="n">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="N850" t="n">
         <v>1662</v>
       </c>
       <c r="O850" t="n">
-        <v>992214</v>
+        <v>968946</v>
       </c>
       <c r="P850" t="n">
         <v>2900</v>
       </c>
       <c r="Q850" t="n">
-        <v>1731300</v>
+        <v>1690700</v>
       </c>
     </row>
     <row r="851">
@@ -37590,22 +37590,22 @@
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M851" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N851" t="n">
         <v>2003</v>
       </c>
       <c r="O851" t="n">
-        <v>344516</v>
+        <v>342513</v>
       </c>
       <c r="P851" t="n">
         <v>3900</v>
       </c>
       <c r="Q851" t="n">
-        <v>670800</v>
+        <v>666900</v>
       </c>
     </row>
     <row r="852">
@@ -37682,22 +37682,22 @@
         <v>0</v>
       </c>
       <c r="L853" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M853" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N853" t="n">
-        <v>1592.276898982</v>
+        <v>1592.2773416667</v>
       </c>
       <c r="O853" t="n">
-        <v>62098.799060298</v>
+        <v>52545.1522750011</v>
       </c>
       <c r="P853" t="n">
         <v>2500</v>
       </c>
       <c r="Q853" t="n">
-        <v>97500</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="854">
@@ -37734,10 +37734,10 @@
         <v>2</v>
       </c>
       <c r="N854" t="n">
-        <v>1906.1850980392</v>
+        <v>1906.1849324324</v>
       </c>
       <c r="O854" t="n">
-        <v>3812.3701960784</v>
+        <v>3812.3698648648</v>
       </c>
       <c r="P854" t="n">
         <v>2900</v>
@@ -37774,22 +37774,22 @@
         <v>0</v>
       </c>
       <c r="L855" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M855" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="N855" t="n">
-        <v>2060.1603030303</v>
+        <v>2060.1601200686</v>
       </c>
       <c r="O855" t="n">
-        <v>183354.2669696967</v>
+        <v>166872.9697255566</v>
       </c>
       <c r="P855" t="n">
         <v>2900</v>
       </c>
       <c r="Q855" t="n">
-        <v>258100</v>
+        <v>234900</v>
       </c>
     </row>
     <row r="856">
@@ -37820,22 +37820,22 @@
         <v>0</v>
       </c>
       <c r="L856" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M856" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N856" t="n">
-        <v>2546.9846516008</v>
+        <v>2546.9843873518</v>
       </c>
       <c r="O856" t="n">
-        <v>191023.84887006</v>
+        <v>170647.9539525706</v>
       </c>
       <c r="P856" t="n">
         <v>3900</v>
       </c>
       <c r="Q856" t="n">
-        <v>292500</v>
+        <v>261300</v>
       </c>
     </row>
     <row r="857">
@@ -37866,22 +37866,22 @@
         <v>0</v>
       </c>
       <c r="L857" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M857" t="n">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="N857" t="n">
-        <v>1259.2745137492</v>
+        <v>1259.2745258911</v>
       </c>
       <c r="O857" t="n">
-        <v>353856.1383635252</v>
+        <v>338744.8474647059</v>
       </c>
       <c r="P857" t="n">
         <v>1900</v>
       </c>
       <c r="Q857" t="n">
-        <v>533900</v>
+        <v>511100</v>
       </c>
     </row>
     <row r="858">
@@ -37958,22 +37958,22 @@
         <v>0</v>
       </c>
       <c r="L859" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M859" t="n">
-        <v>525</v>
+        <v>498</v>
       </c>
       <c r="N859" t="n">
         <v>1801</v>
       </c>
       <c r="O859" t="n">
-        <v>945525</v>
+        <v>896898</v>
       </c>
       <c r="P859" t="n">
         <v>2900</v>
       </c>
       <c r="Q859" t="n">
-        <v>1522500</v>
+        <v>1444200</v>
       </c>
     </row>
     <row r="860">
@@ -38008,10 +38008,10 @@
         <v>97</v>
       </c>
       <c r="N860" t="n">
-        <v>692.15220363289</v>
+        <v>692.15222061657</v>
       </c>
       <c r="O860" t="n">
-        <v>67138.76375239032</v>
+        <v>67138.76539980729</v>
       </c>
       <c r="P860" t="n">
         <v>1200</v>
@@ -38790,22 +38790,22 @@
         <v>0</v>
       </c>
       <c r="L877" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M877" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N877" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O877" t="n">
-        <v>2612050.96</v>
+        <v>2576269.44</v>
       </c>
       <c r="P877" t="n">
         <v>14900</v>
       </c>
       <c r="Q877" t="n">
-        <v>4350800</v>
+        <v>4291200</v>
       </c>
     </row>
     <row r="878">
@@ -40025,22 +40025,22 @@
         <v>0</v>
       </c>
       <c r="L904" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M904" t="n">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="N904" t="n">
-        <v>2286.1648032937</v>
+        <v>2286.1647937672</v>
       </c>
       <c r="O904" t="n">
-        <v>1015057.172662403</v>
+        <v>1010484.838845102</v>
       </c>
       <c r="P904" t="n">
         <v>3000</v>
       </c>
       <c r="Q904" t="n">
-        <v>1332000</v>
+        <v>1326000</v>
       </c>
     </row>
     <row r="905">
@@ -40947,22 +40947,22 @@
         <v>0</v>
       </c>
       <c r="L925" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M925" t="n">
-        <v>3074</v>
+        <v>2990</v>
       </c>
       <c r="N925" t="n">
-        <v>517.28896164542</v>
+        <v>517.28908220781</v>
       </c>
       <c r="O925" t="n">
-        <v>1590146.268098021</v>
+        <v>1546694.355801352</v>
       </c>
       <c r="P925" t="n">
         <v>900</v>
       </c>
       <c r="Q925" t="n">
-        <v>2766600</v>
+        <v>2691000</v>
       </c>
     </row>
     <row r="926">
@@ -41179,10 +41179,10 @@
         <v>500</v>
       </c>
       <c r="N930" t="n">
-        <v>3110.8423302235</v>
+        <v>3110.842321894</v>
       </c>
       <c r="O930" t="n">
-        <v>1555421.16511175</v>
+        <v>1555421.160947</v>
       </c>
       <c r="P930" t="n">
         <v>4500</v>
@@ -41307,22 +41307,22 @@
         <v>0</v>
       </c>
       <c r="L933" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M933" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N933" t="n">
         <v>2030.02</v>
       </c>
       <c r="O933" t="n">
-        <v>1021100.06</v>
+        <v>1019070.04</v>
       </c>
       <c r="P933" t="n">
         <v>3600</v>
       </c>
       <c r="Q933" t="n">
-        <v>1810800</v>
+        <v>1807200</v>
       </c>
     </row>
     <row r="934">
@@ -41389,28 +41389,28 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>1245</v>
+        <v>1365</v>
       </c>
       <c r="K935" t="n">
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M935" t="n">
-        <v>1245</v>
+        <v>1217</v>
       </c>
       <c r="N935" t="n">
-        <v>703.79522697548</v>
+        <v>703.79521051815</v>
       </c>
       <c r="O935" t="n">
-        <v>876225.0575844726</v>
+        <v>856518.7712005886</v>
       </c>
       <c r="P935" t="n">
         <v>900</v>
       </c>
       <c r="Q935" t="n">
-        <v>1120500</v>
+        <v>1095300</v>
       </c>
     </row>
     <row r="936">
@@ -41494,10 +41494,10 @@
         <v>33</v>
       </c>
       <c r="N937" t="n">
-        <v>3182.2511070111</v>
+        <v>3182.2511214953</v>
       </c>
       <c r="O937" t="n">
-        <v>105014.2865313663</v>
+        <v>105014.2870093449</v>
       </c>
       <c r="P937" t="n">
         <v>6900</v>
@@ -41935,22 +41935,22 @@
         <v>0</v>
       </c>
       <c r="L947" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M947" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N947" t="n">
         <v>1300</v>
       </c>
       <c r="O947" t="n">
-        <v>81900</v>
+        <v>80600</v>
       </c>
       <c r="P947" t="n">
         <v>2200</v>
       </c>
       <c r="Q947" t="n">
-        <v>138600</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="948">
@@ -41979,22 +41979,22 @@
         <v>0</v>
       </c>
       <c r="L948" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M948" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="N948" t="n">
         <v>1937</v>
       </c>
       <c r="O948" t="n">
-        <v>247936</v>
+        <v>228566</v>
       </c>
       <c r="P948" t="n">
         <v>3300</v>
       </c>
       <c r="Q948" t="n">
-        <v>422400</v>
+        <v>389400</v>
       </c>
     </row>
     <row r="949">
@@ -42452,22 +42452,22 @@
         <v>0</v>
       </c>
       <c r="L959" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M959" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="N959" t="n">
-        <v>1595.5132863655</v>
+        <v>1595.513125523</v>
       </c>
       <c r="O959" t="n">
-        <v>118067.983191047</v>
+        <v>103708.353158995</v>
       </c>
       <c r="P959" t="n">
         <v>2500</v>
       </c>
       <c r="Q959" t="n">
-        <v>185000</v>
+        <v>162500</v>
       </c>
     </row>
     <row r="960">
@@ -43026,22 +43026,22 @@
         <v>0</v>
       </c>
       <c r="L971" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M971" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N971" t="n">
         <v>10548.76</v>
       </c>
       <c r="O971" t="n">
-        <v>189877.68</v>
+        <v>179328.92</v>
       </c>
       <c r="P971" t="n">
         <v>35900</v>
       </c>
       <c r="Q971" t="n">
-        <v>646200</v>
+        <v>610300</v>
       </c>
     </row>
     <row r="972">
@@ -44005,22 +44005,22 @@
         <v>0</v>
       </c>
       <c r="L992" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M992" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N992" t="n">
-        <v>4159.0002941176</v>
+        <v>4159.000295203</v>
       </c>
       <c r="O992" t="n">
-        <v>253699.0179411736</v>
+        <v>249540.01771218</v>
       </c>
       <c r="P992" t="n">
         <v>8900</v>
       </c>
       <c r="Q992" t="n">
-        <v>542900</v>
+        <v>534000</v>
       </c>
     </row>
     <row r="993">
@@ -44568,10 +44568,10 @@
         <v>2</v>
       </c>
       <c r="N1004" t="n">
-        <v>2000.6734965035</v>
+        <v>2000.6767625899</v>
       </c>
       <c r="O1004" t="n">
-        <v>4001.346993007</v>
+        <v>4001.3535251798</v>
       </c>
       <c r="P1004" t="n">
         <v>2000</v>
@@ -45075,22 +45075,22 @@
         <v>0</v>
       </c>
       <c r="L1015" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1015" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N1015" t="n">
         <v>10301.17</v>
       </c>
       <c r="O1015" t="n">
-        <v>257529.25</v>
+        <v>226625.74</v>
       </c>
       <c r="P1015" t="n">
         <v>14300</v>
       </c>
       <c r="Q1015" t="n">
-        <v>357500</v>
+        <v>314600</v>
       </c>
     </row>
     <row r="1016">
@@ -45704,10 +45704,10 @@
         <v>186</v>
       </c>
       <c r="N1028" t="n">
-        <v>430.60997630332</v>
+        <v>430.60997624703</v>
       </c>
       <c r="O1028" t="n">
-        <v>80093.45559241752</v>
+        <v>80093.45558194758</v>
       </c>
       <c r="P1028" t="n">
         <v>2200</v>
@@ -45753,10 +45753,10 @@
         <v>6</v>
       </c>
       <c r="N1029" t="n">
-        <v>315.02694721826</v>
+        <v>315.02697707736</v>
       </c>
       <c r="O1029" t="n">
-        <v>1890.16168330956</v>
+        <v>1890.16186246416</v>
       </c>
       <c r="P1029" t="n">
         <v>2200</v>
@@ -46596,22 +46596,22 @@
         <v>0</v>
       </c>
       <c r="L1049" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1049" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N1049" t="n">
-        <v>6243.3531428571</v>
+        <v>6243.3531578947</v>
       </c>
       <c r="O1049" t="n">
-        <v>262220.8319999982</v>
+        <v>255977.4794736827</v>
       </c>
       <c r="P1049" t="n">
         <v>9900</v>
       </c>
       <c r="Q1049" t="n">
-        <v>415800</v>
+        <v>405900</v>
       </c>
     </row>
     <row r="1050">
@@ -47155,22 +47155,22 @@
         <v>0</v>
       </c>
       <c r="L1062" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1062" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N1062" t="n">
-        <v>2129.8331598174</v>
+        <v>2129.8331627057</v>
       </c>
       <c r="O1062" t="n">
-        <v>91582.8258721482</v>
+        <v>89452.99283363941</v>
       </c>
       <c r="P1062" t="n">
         <v>2700</v>
       </c>
       <c r="Q1062" t="n">
-        <v>116100</v>
+        <v>113400</v>
       </c>
     </row>
     <row r="1063">
@@ -47460,22 +47460,22 @@
         <v>0</v>
       </c>
       <c r="L1069" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1069" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="N1069" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1069" t="n">
-        <v>22354.83</v>
+        <v>8235.99</v>
       </c>
       <c r="P1069" t="n">
         <v>1900</v>
       </c>
       <c r="Q1069" t="n">
-        <v>36100</v>
+        <v>13300</v>
       </c>
     </row>
     <row r="1070">
@@ -47504,22 +47504,22 @@
         <v>0</v>
       </c>
       <c r="L1070" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M1070" t="n">
-        <v>371</v>
+        <v>337</v>
       </c>
       <c r="N1070" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1070" t="n">
-        <v>1180484.9</v>
+        <v>1072300.3</v>
       </c>
       <c r="P1070" t="n">
         <v>5100</v>
       </c>
       <c r="Q1070" t="n">
-        <v>1892100</v>
+        <v>1718700</v>
       </c>
     </row>
     <row r="1071">
@@ -47856,10 +47856,10 @@
         <v>9</v>
       </c>
       <c r="N1078" t="n">
-        <v>15219.155232558</v>
+        <v>15219.155176471</v>
       </c>
       <c r="O1078" t="n">
-        <v>136972.397093022</v>
+        <v>136972.396588239</v>
       </c>
       <c r="P1078" t="n">
         <v>16000</v>
@@ -48407,10 +48407,10 @@
         <v>76</v>
       </c>
       <c r="N1091" t="n">
-        <v>6035.6648529412</v>
+        <v>6035.665</v>
       </c>
       <c r="O1091" t="n">
-        <v>458710.5288235312</v>
+        <v>458710.54</v>
       </c>
       <c r="P1091" t="n">
         <v>8500</v>
@@ -48442,22 +48442,22 @@
         <v>0</v>
       </c>
       <c r="L1092" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1092" t="n">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="N1092" t="n">
-        <v>389.72776942356</v>
+        <v>389.72776241358</v>
       </c>
       <c r="O1092" t="n">
-        <v>466114.4122305778</v>
+        <v>464165.7650345738</v>
       </c>
       <c r="P1092" t="n">
         <v>500</v>
       </c>
       <c r="Q1092" t="n">
-        <v>598000</v>
+        <v>595500</v>
       </c>
     </row>
     <row r="1093">
@@ -48797,10 +48797,10 @@
         <v>289</v>
       </c>
       <c r="N1100" t="n">
-        <v>705.52801204819</v>
+        <v>705.52800453515</v>
       </c>
       <c r="O1100" t="n">
-        <v>203897.5954819269</v>
+        <v>203897.5933106584</v>
       </c>
       <c r="P1100" t="n">
         <v>1500</v>
@@ -48832,22 +48832,22 @@
         <v>0</v>
       </c>
       <c r="L1101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1101" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="N1101" t="n">
-        <v>4985.4051948052</v>
+        <v>4985.4053097345</v>
       </c>
       <c r="O1101" t="n">
-        <v>468628.0883116888</v>
+        <v>443701.0725663705</v>
       </c>
       <c r="P1101" t="n">
         <v>7900</v>
       </c>
       <c r="Q1101" t="n">
-        <v>742600</v>
+        <v>703100</v>
       </c>
     </row>
     <row r="1102">
@@ -48889,10 +48889,10 @@
         <v>41</v>
       </c>
       <c r="N1102" t="n">
-        <v>1757.3205567452</v>
+        <v>1757.3205591398</v>
       </c>
       <c r="O1102" t="n">
-        <v>72050.1428265532</v>
+        <v>72050.1429247318</v>
       </c>
       <c r="P1102" t="n">
         <v>2000</v>
@@ -49558,22 +49558,22 @@
         <v>0</v>
       </c>
       <c r="L1117" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M1117" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="N1117" t="n">
         <v>7480</v>
       </c>
       <c r="O1117" t="n">
-        <v>1024760</v>
+        <v>800360</v>
       </c>
       <c r="P1117" t="n">
         <v>9500</v>
       </c>
       <c r="Q1117" t="n">
-        <v>1301500</v>
+        <v>1016500</v>
       </c>
     </row>
     <row r="1118">
@@ -49696,22 +49696,22 @@
         <v>0</v>
       </c>
       <c r="L1120" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M1120" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="N1120" t="n">
         <v>9240</v>
       </c>
       <c r="O1120" t="n">
-        <v>637560</v>
+        <v>332640</v>
       </c>
       <c r="P1120" t="n">
         <v>11500</v>
       </c>
       <c r="Q1120" t="n">
-        <v>793500</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="1121">
@@ -49880,22 +49880,22 @@
         <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N1124" t="n">
         <v>9500</v>
       </c>
       <c r="O1124" t="n">
-        <v>47500</v>
+        <v>38000</v>
       </c>
       <c r="P1124" t="n">
         <v>11400</v>
       </c>
       <c r="Q1124" t="n">
-        <v>57000</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="1125">
@@ -52160,22 +52160,22 @@
         <v>0</v>
       </c>
       <c r="L1174" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1174" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N1174" t="n">
         <v>4550</v>
       </c>
       <c r="O1174" t="n">
-        <v>1396850</v>
+        <v>1374100</v>
       </c>
       <c r="P1174" t="n">
         <v>5500</v>
       </c>
       <c r="Q1174" t="n">
-        <v>1688500</v>
+        <v>1661000</v>
       </c>
     </row>
     <row r="1175">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-22</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>21</v>
@@ -3541,13 +3541,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>77</v>
@@ -4122,13 +4122,13 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>53</v>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
         <v>28</v>
@@ -5265,13 +5265,13 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
         <v>20</v>
@@ -5853,13 +5853,13 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
         <v>6</v>
@@ -5900,13 +5900,13 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>9</v>
@@ -9563,13 +9563,13 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
         <v>274</v>
@@ -9727,13 +9727,13 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>1764</v>
+        <v>1747</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
         <v>1747</v>
@@ -9814,13 +9814,13 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
         <v>116</v>
@@ -10278,13 +10278,13 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
         <v>524</v>
@@ -10406,13 +10406,13 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
         <v>14</v>
@@ -11388,13 +11388,13 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
         <v>4</v>
@@ -11639,13 +11639,13 @@
         </is>
       </c>
       <c r="J266" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
         <v>242</v>
@@ -11729,13 +11729,13 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M268" t="n">
         <v>558</v>
@@ -11770,13 +11770,13 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M269" t="n">
         <v>158</v>
@@ -12085,13 +12085,13 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
         <v>235</v>
@@ -12131,13 +12131,13 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
         <v>62</v>
@@ -12520,13 +12520,13 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
         <v>695</v>
@@ -12748,13 +12748,13 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
         <v>88</v>
@@ -12927,13 +12927,13 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
         <v>284</v>
@@ -12973,13 +12973,13 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
         <v>97</v>
@@ -13060,13 +13060,13 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M298" t="n">
         <v>474</v>
@@ -13152,13 +13152,13 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>4265</v>
+        <v>4255</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M300" t="n">
         <v>4255</v>
@@ -13198,13 +13198,13 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
         <v>149</v>
@@ -13247,13 +13247,13 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M302" t="n">
         <v>86</v>
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
       </c>
       <c r="L309" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M309" t="n">
         <v>230</v>
@@ -13695,13 +13695,13 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
         <v>37</v>
@@ -13790,13 +13790,13 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
         <v>790</v>
@@ -13836,13 +13836,13 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
         <v>802</v>
@@ -13882,13 +13882,13 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
         <v>29</v>
@@ -14143,13 +14143,13 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M322" t="n">
         <v>31</v>
@@ -14581,13 +14581,13 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
       </c>
       <c r="L332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M332" t="n">
         <v>53</v>
@@ -14709,13 +14709,13 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M335" t="n">
         <v>189</v>
@@ -14888,13 +14888,13 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
         <v>58</v>
@@ -14976,13 +14976,13 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>528</v>
+        <v>629</v>
       </c>
       <c r="K341" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="M341" t="n">
         <v>629</v>
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="J346" t="n">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="K346" t="n">
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M346" t="n">
         <v>148</v>
@@ -15638,13 +15638,13 @@
         </is>
       </c>
       <c r="J356" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K356" t="n">
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M356" t="n">
         <v>39</v>
@@ -16473,13 +16473,13 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M375" t="n">
         <v>323</v>
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="J379" t="n">
-        <v>590</v>
+        <v>320</v>
       </c>
       <c r="K379" t="n">
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M379" t="n">
         <v>320</v>
@@ -16734,13 +16734,13 @@
         </is>
       </c>
       <c r="J381" t="n">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="K381" t="n">
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M381" t="n">
         <v>467</v>
@@ -16904,13 +16904,13 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M385" t="n">
         <v>35</v>
@@ -16948,13 +16948,13 @@
         </is>
       </c>
       <c r="J386" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K386" t="n">
         <v>0</v>
       </c>
       <c r="L386" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M386" t="n">
         <v>81</v>
@@ -17751,13 +17751,13 @@
         </is>
       </c>
       <c r="J404" t="n">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="K404" t="n">
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M404" t="n">
         <v>599</v>
@@ -17838,13 +17838,13 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M406" t="n">
         <v>199</v>
@@ -17884,13 +17884,13 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M407" t="n">
         <v>214</v>
@@ -17930,13 +17930,13 @@
         </is>
       </c>
       <c r="J408" t="n">
-        <v>1622</v>
+        <v>1568</v>
       </c>
       <c r="K408" t="n">
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M408" t="n">
         <v>1568</v>
@@ -18022,13 +18022,13 @@
         </is>
       </c>
       <c r="J410" t="n">
-        <v>933</v>
+        <v>912</v>
       </c>
       <c r="K410" t="n">
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M410" t="n">
         <v>912</v>
@@ -18066,13 +18066,13 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K411" t="n">
         <v>0</v>
       </c>
       <c r="L411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M411" t="n">
         <v>4</v>
@@ -19384,13 +19384,13 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
       </c>
       <c r="L441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M441" t="n">
         <v>39</v>
@@ -19645,10 +19645,10 @@
         </is>
       </c>
       <c r="J447" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K447" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L447" t="n">
         <v>0</v>
@@ -21462,13 +21462,13 @@
         </is>
       </c>
       <c r="J490" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K490" t="n">
         <v>0</v>
       </c>
       <c r="L490" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M490" t="n">
         <v>140</v>
@@ -21631,13 +21631,13 @@
         </is>
       </c>
       <c r="J494" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K494" t="n">
         <v>0</v>
       </c>
       <c r="L494" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M494" t="n">
         <v>313</v>
@@ -22246,13 +22246,13 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
       </c>
       <c r="L509" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M509" t="n">
         <v>56</v>
@@ -22623,13 +22623,13 @@
         </is>
       </c>
       <c r="J518" t="n">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
       </c>
       <c r="L518" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M518" t="n">
         <v>1347</v>
@@ -23130,13 +23130,13 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M530" t="n">
         <v>59</v>
@@ -23699,13 +23699,13 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M543" t="n">
         <v>209</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
       </c>
       <c r="L545" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M545" t="n">
         <v>29</v>
@@ -24421,13 +24421,13 @@
         </is>
       </c>
       <c r="J560" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K560" t="n">
         <v>0</v>
       </c>
       <c r="L560" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M560" t="n">
         <v>52</v>
@@ -24513,13 +24513,13 @@
         </is>
       </c>
       <c r="J562" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K562" t="n">
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M562" t="n">
         <v>63</v>
@@ -25097,13 +25097,13 @@
         </is>
       </c>
       <c r="J576" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K576" t="n">
         <v>0</v>
       </c>
       <c r="L576" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M576" t="n">
         <v>11</v>
@@ -25276,13 +25276,13 @@
         </is>
       </c>
       <c r="J580" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K580" t="n">
         <v>0</v>
       </c>
       <c r="L580" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M580" t="n">
         <v>31</v>
@@ -25624,13 +25624,13 @@
         </is>
       </c>
       <c r="J588" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K588" t="n">
         <v>0</v>
       </c>
       <c r="L588" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M588" t="n">
         <v>22</v>
@@ -25854,13 +25854,13 @@
         </is>
       </c>
       <c r="J593" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K593" t="n">
         <v>0</v>
       </c>
       <c r="L593" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M593" t="n">
         <v>78</v>
@@ -26238,13 +26238,13 @@
         </is>
       </c>
       <c r="J602" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K602" t="n">
         <v>0</v>
       </c>
       <c r="L602" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M602" t="n">
         <v>68</v>
@@ -26507,13 +26507,13 @@
         </is>
       </c>
       <c r="J608" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K608" t="n">
         <v>0</v>
       </c>
       <c r="L608" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M608" t="n">
         <v>134</v>
@@ -28788,13 +28788,13 @@
         </is>
       </c>
       <c r="J660" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K660" t="n">
         <v>0</v>
       </c>
       <c r="L660" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M660" t="n">
         <v>97</v>
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="J661" t="n">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="K661" t="n">
         <v>0</v>
       </c>
       <c r="L661" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M661" t="n">
         <v>323</v>
@@ -29530,13 +29530,13 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="K676" t="n">
         <v>0</v>
       </c>
       <c r="L676" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M676" t="n">
         <v>240</v>
@@ -29993,13 +29993,13 @@
         </is>
       </c>
       <c r="J686" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K686" t="n">
         <v>0</v>
       </c>
       <c r="L686" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M686" t="n">
         <v>25</v>
@@ -31005,13 +31005,13 @@
         </is>
       </c>
       <c r="J708" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K708" t="n">
         <v>0</v>
       </c>
       <c r="L708" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M708" t="n">
         <v>61</v>
@@ -31100,13 +31100,13 @@
         </is>
       </c>
       <c r="J710" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K710" t="n">
         <v>0</v>
       </c>
       <c r="L710" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M710" t="n">
         <v>23</v>
@@ -31606,13 +31606,13 @@
         </is>
       </c>
       <c r="J721" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K721" t="n">
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M721" t="n">
         <v>176</v>
@@ -31698,13 +31698,13 @@
         </is>
       </c>
       <c r="J723" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="K723" t="n">
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M723" t="n">
         <v>354</v>
@@ -31974,13 +31974,13 @@
         </is>
       </c>
       <c r="J729" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K729" t="n">
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M729" t="n">
         <v>45</v>
@@ -32708,13 +32708,13 @@
         </is>
       </c>
       <c r="J745" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K745" t="n">
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M745" t="n">
         <v>240</v>
@@ -32800,13 +32800,13 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M747" t="n">
         <v>66</v>
@@ -33214,13 +33214,13 @@
         </is>
       </c>
       <c r="J756" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K756" t="n">
         <v>0</v>
       </c>
       <c r="L756" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M756" t="n">
         <v>156</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="J760" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K760" t="n">
         <v>0</v>
       </c>
       <c r="L760" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M760" t="n">
         <v>143</v>
@@ -33807,13 +33807,13 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K769" t="n">
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M769" t="n">
         <v>103</v>
@@ -33853,13 +33853,13 @@
         </is>
       </c>
       <c r="J770" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K770" t="n">
         <v>0</v>
       </c>
       <c r="L770" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M770" t="n">
         <v>73</v>
@@ -34129,13 +34129,13 @@
         </is>
       </c>
       <c r="J776" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K776" t="n">
         <v>0</v>
       </c>
       <c r="L776" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M776" t="n">
         <v>91</v>
@@ -34267,13 +34267,13 @@
         </is>
       </c>
       <c r="J779" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K779" t="n">
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M779" t="n">
         <v>90</v>
@@ -34451,13 +34451,13 @@
         </is>
       </c>
       <c r="J783" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K783" t="n">
         <v>0</v>
       </c>
       <c r="L783" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M783" t="n">
         <v>288</v>
@@ -34635,13 +34635,13 @@
         </is>
       </c>
       <c r="J787" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K787" t="n">
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M787" t="n">
         <v>21</v>
@@ -34776,13 +34776,13 @@
         </is>
       </c>
       <c r="J790" t="n">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="K790" t="n">
         <v>0</v>
       </c>
       <c r="L790" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M790" t="n">
         <v>651</v>
@@ -34960,13 +34960,13 @@
         </is>
       </c>
       <c r="J794" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K794" t="n">
         <v>0</v>
       </c>
       <c r="L794" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M794" t="n">
         <v>32</v>
@@ -35006,13 +35006,13 @@
         </is>
       </c>
       <c r="J795" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K795" t="n">
         <v>0</v>
       </c>
       <c r="L795" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M795" t="n">
         <v>171</v>
@@ -35231,13 +35231,13 @@
         </is>
       </c>
       <c r="J800" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K800" t="n">
         <v>0</v>
       </c>
       <c r="L800" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M800" t="n">
         <v>70</v>
@@ -35556,13 +35556,13 @@
         </is>
       </c>
       <c r="J807" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K807" t="n">
         <v>0</v>
       </c>
       <c r="L807" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M807" t="n">
         <v>17</v>
@@ -36016,13 +36016,13 @@
         </is>
       </c>
       <c r="J817" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K817" t="n">
         <v>0</v>
       </c>
       <c r="L817" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M817" t="n">
         <v>87</v>
@@ -36200,13 +36200,13 @@
         </is>
       </c>
       <c r="J821" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="K821" t="n">
         <v>0</v>
       </c>
       <c r="L821" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M821" t="n">
         <v>200</v>
@@ -36525,13 +36525,13 @@
         </is>
       </c>
       <c r="J828" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K828" t="n">
         <v>0</v>
       </c>
       <c r="L828" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M828" t="n">
         <v>45</v>
@@ -36755,13 +36755,13 @@
         </is>
       </c>
       <c r="J833" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="K833" t="n">
         <v>0</v>
       </c>
       <c r="L833" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M833" t="n">
         <v>22</v>
@@ -36845,13 +36845,13 @@
         </is>
       </c>
       <c r="J835" t="n">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="K835" t="n">
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M835" t="n">
         <v>325</v>
@@ -36891,13 +36891,13 @@
         </is>
       </c>
       <c r="J836" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K836" t="n">
         <v>0</v>
       </c>
       <c r="L836" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M836" t="n">
         <v>160</v>
@@ -37029,13 +37029,13 @@
         </is>
       </c>
       <c r="J839" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="K839" t="n">
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M839" t="n">
         <v>411</v>
@@ -37121,13 +37121,13 @@
         </is>
       </c>
       <c r="J841" t="n">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K841" t="n">
         <v>0</v>
       </c>
       <c r="L841" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M841" t="n">
         <v>423</v>
@@ -37167,13 +37167,13 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="K842" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M842" t="n">
         <v>171</v>
@@ -37213,13 +37213,13 @@
         </is>
       </c>
       <c r="J843" t="n">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="K843" t="n">
         <v>0</v>
       </c>
       <c r="L843" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M843" t="n">
         <v>881</v>
@@ -37446,13 +37446,13 @@
         </is>
       </c>
       <c r="J848" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K848" t="n">
         <v>0</v>
       </c>
       <c r="L848" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M848" t="n">
         <v>56</v>
@@ -37538,13 +37538,13 @@
         </is>
       </c>
       <c r="J850" t="n">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="K850" t="n">
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M850" t="n">
         <v>583</v>
@@ -37584,13 +37584,13 @@
         </is>
       </c>
       <c r="J851" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K851" t="n">
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M851" t="n">
         <v>171</v>
@@ -37676,13 +37676,13 @@
         </is>
       </c>
       <c r="J853" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K853" t="n">
         <v>0</v>
       </c>
       <c r="L853" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M853" t="n">
         <v>33</v>
@@ -37768,13 +37768,13 @@
         </is>
       </c>
       <c r="J855" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K855" t="n">
         <v>0</v>
       </c>
       <c r="L855" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M855" t="n">
         <v>81</v>
@@ -37814,13 +37814,13 @@
         </is>
       </c>
       <c r="J856" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K856" t="n">
         <v>0</v>
       </c>
       <c r="L856" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M856" t="n">
         <v>67</v>
@@ -37860,13 +37860,13 @@
         </is>
       </c>
       <c r="J857" t="n">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="K857" t="n">
         <v>0</v>
       </c>
       <c r="L857" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M857" t="n">
         <v>269</v>
@@ -37952,13 +37952,13 @@
         </is>
       </c>
       <c r="J859" t="n">
-        <v>525</v>
+        <v>498</v>
       </c>
       <c r="K859" t="n">
         <v>0</v>
       </c>
       <c r="L859" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M859" t="n">
         <v>498</v>
@@ -38784,13 +38784,13 @@
         </is>
       </c>
       <c r="J877" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="K877" t="n">
         <v>0</v>
       </c>
       <c r="L877" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M877" t="n">
         <v>288</v>
@@ -40019,13 +40019,13 @@
         </is>
       </c>
       <c r="J904" t="n">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K904" t="n">
         <v>0</v>
       </c>
       <c r="L904" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M904" t="n">
         <v>442</v>
@@ -40941,13 +40941,13 @@
         </is>
       </c>
       <c r="J925" t="n">
-        <v>3074</v>
+        <v>2990</v>
       </c>
       <c r="K925" t="n">
         <v>0</v>
       </c>
       <c r="L925" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M925" t="n">
         <v>2990</v>
@@ -41301,13 +41301,13 @@
         </is>
       </c>
       <c r="J933" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K933" t="n">
         <v>0</v>
       </c>
       <c r="L933" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M933" t="n">
         <v>502</v>
@@ -41389,13 +41389,13 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>1365</v>
+        <v>1217</v>
       </c>
       <c r="K935" t="n">
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M935" t="n">
         <v>1217</v>
@@ -41929,13 +41929,13 @@
         </is>
       </c>
       <c r="J947" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K947" t="n">
         <v>0</v>
       </c>
       <c r="L947" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M947" t="n">
         <v>62</v>
@@ -41973,13 +41973,13 @@
         </is>
       </c>
       <c r="J948" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="K948" t="n">
         <v>0</v>
       </c>
       <c r="L948" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M948" t="n">
         <v>118</v>
@@ -42446,13 +42446,13 @@
         </is>
       </c>
       <c r="J959" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K959" t="n">
         <v>0</v>
       </c>
       <c r="L959" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M959" t="n">
         <v>65</v>
@@ -43020,13 +43020,13 @@
         </is>
       </c>
       <c r="J971" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K971" t="n">
         <v>0</v>
       </c>
       <c r="L971" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M971" t="n">
         <v>17</v>
@@ -43999,13 +43999,13 @@
         </is>
       </c>
       <c r="J992" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K992" t="n">
         <v>0</v>
       </c>
       <c r="L992" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M992" t="n">
         <v>60</v>
@@ -45069,13 +45069,13 @@
         </is>
       </c>
       <c r="J1015" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K1015" t="n">
         <v>0</v>
       </c>
       <c r="L1015" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1015" t="n">
         <v>22</v>
@@ -46590,13 +46590,13 @@
         </is>
       </c>
       <c r="J1049" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K1049" t="n">
         <v>0</v>
       </c>
       <c r="L1049" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1049" t="n">
         <v>41</v>
@@ -47149,13 +47149,13 @@
         </is>
       </c>
       <c r="J1062" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1062" t="n">
         <v>0</v>
       </c>
       <c r="L1062" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1062" t="n">
         <v>42</v>
@@ -47454,13 +47454,13 @@
         </is>
       </c>
       <c r="J1069" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K1069" t="n">
         <v>0</v>
       </c>
       <c r="L1069" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M1069" t="n">
         <v>7</v>
@@ -47498,13 +47498,13 @@
         </is>
       </c>
       <c r="J1070" t="n">
-        <v>371</v>
+        <v>337</v>
       </c>
       <c r="K1070" t="n">
         <v>0</v>
       </c>
       <c r="L1070" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M1070" t="n">
         <v>337</v>
@@ -48436,13 +48436,13 @@
         </is>
       </c>
       <c r="J1092" t="n">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="K1092" t="n">
         <v>0</v>
       </c>
       <c r="L1092" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M1092" t="n">
         <v>1191</v>
@@ -48826,13 +48826,13 @@
         </is>
       </c>
       <c r="J1101" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K1101" t="n">
         <v>0</v>
       </c>
       <c r="L1101" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M1101" t="n">
         <v>89</v>
@@ -49552,13 +49552,13 @@
         </is>
       </c>
       <c r="J1117" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="K1117" t="n">
         <v>0</v>
       </c>
       <c r="L1117" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M1117" t="n">
         <v>107</v>
@@ -49690,13 +49690,13 @@
         </is>
       </c>
       <c r="J1120" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="K1120" t="n">
         <v>0</v>
       </c>
       <c r="L1120" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M1120" t="n">
         <v>36</v>
@@ -49874,13 +49874,13 @@
         </is>
       </c>
       <c r="J1124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K1124" t="n">
         <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1124" t="n">
         <v>4</v>
@@ -52154,13 +52154,13 @@
         </is>
       </c>
       <c r="J1174" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="K1174" t="n">
         <v>0</v>
       </c>
       <c r="L1174" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M1174" t="n">
         <v>302</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-26</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1051,19 +1051,19 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N16" t="n">
-        <v>8642.2268253968</v>
+        <v>8642.226774193499</v>
       </c>
       <c r="O16" t="n">
-        <v>337046.8461904752</v>
+        <v>328404.617419353</v>
       </c>
       <c r="P16" t="n">
         <v>13900</v>
       </c>
       <c r="Q16" t="n">
-        <v>542100</v>
+        <v>528200</v>
       </c>
     </row>
     <row r="17">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1304,19 +1304,19 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.3067953668</v>
+        <v>1811.3069785884</v>
       </c>
       <c r="O22" t="n">
-        <v>652070.446332048</v>
+        <v>597731.302934172</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
       </c>
       <c r="Q22" t="n">
-        <v>936000</v>
+        <v>858000</v>
       </c>
     </row>
     <row r="23">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1421,19 +1421,19 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N25" t="n">
-        <v>3376.7464728365</v>
+        <v>3376.7464699454</v>
       </c>
       <c r="O25" t="n">
-        <v>523395.7032896575</v>
+        <v>513265.4634317008</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
       </c>
       <c r="Q25" t="n">
-        <v>697500</v>
+        <v>684000</v>
       </c>
     </row>
     <row r="26">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2712,19 +2712,19 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N57" t="n">
         <v>4604.2</v>
       </c>
       <c r="O57" t="n">
-        <v>174959.6</v>
+        <v>161147</v>
       </c>
       <c r="P57" t="n">
         <v>7500</v>
       </c>
       <c r="Q57" t="n">
-        <v>285000</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="58">
@@ -2918,10 +2918,10 @@
         <v>41</v>
       </c>
       <c r="N62" t="n">
-        <v>6272.8546451613</v>
+        <v>6272.8546905537</v>
       </c>
       <c r="O62" t="n">
-        <v>257187.0404516133</v>
+        <v>257187.0423127017</v>
       </c>
       <c r="P62" t="n">
         <v>7900</v>
@@ -4134,10 +4134,10 @@
         <v>53</v>
       </c>
       <c r="N92" t="n">
-        <v>3910.6281632653</v>
+        <v>3910.6281595092</v>
       </c>
       <c r="O92" t="n">
-        <v>207263.2926530609</v>
+        <v>207263.2924539876</v>
       </c>
       <c r="P92" t="n">
         <v>9100</v>
@@ -4770,10 +4770,10 @@
         <v>17</v>
       </c>
       <c r="N106" t="n">
-        <v>12837.967258065</v>
+        <v>12837.967540984</v>
       </c>
       <c r="O106" t="n">
-        <v>218245.443387105</v>
+        <v>218245.448196728</v>
       </c>
       <c r="P106" t="n">
         <v>22900</v>
@@ -4859,10 +4859,10 @@
         <v>39</v>
       </c>
       <c r="N108" t="n">
-        <v>10994.361428571</v>
+        <v>10994.361818182</v>
       </c>
       <c r="O108" t="n">
-        <v>428780.095714269</v>
+        <v>428780.110909098</v>
       </c>
       <c r="P108" t="n">
         <v>16900</v>
@@ -5024,10 +5024,10 @@
         <v>28</v>
       </c>
       <c r="N112" t="n">
-        <v>15711.965957447</v>
+        <v>15711.965922747</v>
       </c>
       <c r="O112" t="n">
-        <v>439935.046808516</v>
+        <v>439935.045836916</v>
       </c>
       <c r="P112" t="n">
         <v>28500</v>
@@ -5165,10 +5165,10 @@
         <v>22</v>
       </c>
       <c r="N115" t="n">
-        <v>13712.844516129</v>
+        <v>13712.844</v>
       </c>
       <c r="O115" t="n">
-        <v>301682.579354838</v>
+        <v>301682.568</v>
       </c>
       <c r="P115" t="n">
         <v>22600</v>
@@ -5204,10 +5204,10 @@
         <v>80</v>
       </c>
       <c r="N116" t="n">
-        <v>7407.7300542005</v>
+        <v>7407.7300543478</v>
       </c>
       <c r="O116" t="n">
-        <v>592618.4043360399</v>
+        <v>592618.404347824</v>
       </c>
       <c r="P116" t="n">
         <v>10900</v>
@@ -5529,10 +5529,10 @@
         <v>5</v>
       </c>
       <c r="N124" t="n">
-        <v>22267.552173913</v>
+        <v>22267.5525</v>
       </c>
       <c r="O124" t="n">
-        <v>111337.760869565</v>
+        <v>111337.7625</v>
       </c>
       <c r="P124" t="n">
         <v>46300</v>
@@ -6100,10 +6100,10 @@
         <v>12</v>
       </c>
       <c r="N137" t="n">
-        <v>200072.20057377</v>
+        <v>200072.20066116</v>
       </c>
       <c r="O137" t="n">
-        <v>2400866.40688524</v>
+        <v>2400866.40793392</v>
       </c>
       <c r="P137" t="n">
         <v>312000</v>
@@ -6142,10 +6142,10 @@
         <v>1</v>
       </c>
       <c r="N138" t="n">
-        <v>174389.79407407</v>
+        <v>174389.795</v>
       </c>
       <c r="O138" t="n">
-        <v>174389.79407407</v>
+        <v>174389.795</v>
       </c>
       <c r="P138" t="n">
         <v>368200</v>
@@ -6189,10 +6189,10 @@
         <v>3</v>
       </c>
       <c r="N139" t="n">
-        <v>251809.29393939</v>
+        <v>251809.29375</v>
       </c>
       <c r="O139" t="n">
-        <v>755427.88181817</v>
+        <v>755427.8812500001</v>
       </c>
       <c r="P139" t="n">
         <v>584000</v>
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -6677,19 +6677,19 @@
         <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N150" t="n">
         <v>27000</v>
       </c>
       <c r="O150" t="n">
-        <v>324000</v>
+        <v>297000</v>
       </c>
       <c r="P150" t="n">
         <v>20000</v>
       </c>
       <c r="Q150" t="n">
-        <v>240000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="151">
@@ -7077,10 +7077,10 @@
         <v>7</v>
       </c>
       <c r="N160" t="n">
-        <v>61666.874048257</v>
+        <v>61666.874070081</v>
       </c>
       <c r="O160" t="n">
-        <v>431668.118337799</v>
+        <v>431668.118490567</v>
       </c>
       <c r="P160" t="n">
         <v>98900</v>
@@ -8408,10 +8408,10 @@
         <v>18</v>
       </c>
       <c r="N190" t="n">
-        <v>6303.1779439252</v>
+        <v>6303.1779245283</v>
       </c>
       <c r="O190" t="n">
-        <v>113457.2029906536</v>
+        <v>113457.2026415094</v>
       </c>
       <c r="P190" t="n">
         <v>13500</v>
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>1743</v>
+        <v>1733</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -9741,19 +9741,19 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>1743</v>
+        <v>1733</v>
       </c>
       <c r="N221" t="n">
         <v>1726.32</v>
       </c>
       <c r="O221" t="n">
-        <v>3008975.76</v>
+        <v>2991712.56</v>
       </c>
       <c r="P221" t="n">
         <v>1500</v>
       </c>
       <c r="Q221" t="n">
-        <v>2614500</v>
+        <v>2599500</v>
       </c>
     </row>
     <row r="222">
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -10292,19 +10292,19 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="N234" t="n">
-        <v>1098.0591631908</v>
+        <v>1098.0593600211</v>
       </c>
       <c r="O234" t="n">
-        <v>562206.2915536896</v>
+        <v>554519.9768106556</v>
       </c>
       <c r="P234" t="n">
         <v>1500</v>
       </c>
       <c r="Q234" t="n">
-        <v>768000</v>
+        <v>757500</v>
       </c>
     </row>
     <row r="235">
@@ -11562,7 +11562,7 @@
         </is>
       </c>
       <c r="J264" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -11571,19 +11571,19 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N264" t="n">
         <v>5000</v>
       </c>
       <c r="O264" t="n">
-        <v>490000</v>
+        <v>480000</v>
       </c>
       <c r="P264" t="n">
         <v>4900</v>
       </c>
       <c r="Q264" t="n">
-        <v>480200</v>
+        <v>470400</v>
       </c>
     </row>
     <row r="265">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="J265" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -11612,19 +11612,19 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N265" t="n">
         <v>4065.61</v>
       </c>
       <c r="O265" t="n">
-        <v>182952.45</v>
+        <v>166690.01</v>
       </c>
       <c r="P265" t="n">
         <v>5000</v>
       </c>
       <c r="Q265" t="n">
-        <v>225000</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="266">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="J266" t="n">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -11653,19 +11653,19 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="N266" t="n">
         <v>2913</v>
       </c>
       <c r="O266" t="n">
-        <v>693294</v>
+        <v>623382</v>
       </c>
       <c r="P266" t="n">
         <v>4950</v>
       </c>
       <c r="Q266" t="n">
-        <v>1178100</v>
+        <v>1059300</v>
       </c>
     </row>
     <row r="267">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -11743,19 +11743,19 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="N268" t="n">
         <v>2804.33</v>
       </c>
       <c r="O268" t="n">
-        <v>1562011.81</v>
+        <v>1494707.89</v>
       </c>
       <c r="P268" t="n">
         <v>4900</v>
       </c>
       <c r="Q268" t="n">
-        <v>2729300</v>
+        <v>2611700</v>
       </c>
     </row>
     <row r="269">
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -12099,19 +12099,19 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N276" t="n">
-        <v>2582.2557662062</v>
+        <v>2582.2557508532</v>
       </c>
       <c r="O276" t="n">
-        <v>534526.9436046834</v>
+        <v>521615.6616723464</v>
       </c>
       <c r="P276" t="n">
         <v>4500</v>
       </c>
       <c r="Q276" t="n">
-        <v>931500</v>
+        <v>909000</v>
       </c>
     </row>
     <row r="277">
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12191,19 +12191,19 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="N278" t="n">
-        <v>5216.8961467368</v>
+        <v>5216.8961296772</v>
       </c>
       <c r="O278" t="n">
-        <v>469520.653206312</v>
+        <v>344315.1445586952</v>
       </c>
       <c r="P278" t="n">
         <v>8500</v>
       </c>
       <c r="Q278" t="n">
-        <v>765000</v>
+        <v>561000</v>
       </c>
     </row>
     <row r="279">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -12534,19 +12534,19 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="N286" t="n">
-        <v>3158.860825504</v>
+        <v>3158.8608260699</v>
       </c>
       <c r="O286" t="n">
-        <v>2195408.27372528</v>
+        <v>2176455.109162161</v>
       </c>
       <c r="P286" t="n">
         <v>5600</v>
       </c>
       <c r="Q286" t="n">
-        <v>3892000</v>
+        <v>3858400</v>
       </c>
     </row>
     <row r="287">
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -12762,19 +12762,19 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="N291" t="n">
-        <v>3230.0673814042</v>
+        <v>3230.0672564612</v>
       </c>
       <c r="O291" t="n">
-        <v>264865.5252751444</v>
+        <v>226104.707952284</v>
       </c>
       <c r="P291" t="n">
         <v>6200</v>
       </c>
       <c r="Q291" t="n">
-        <v>508400</v>
+        <v>434000</v>
       </c>
     </row>
     <row r="292">
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -12987,19 +12987,19 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="N296" t="n">
-        <v>2694.8232244517</v>
+        <v>2694.8231862975</v>
       </c>
       <c r="O296" t="n">
-        <v>261397.8527718149</v>
+        <v>229059.9708352875</v>
       </c>
       <c r="P296" t="n">
         <v>4900</v>
       </c>
       <c r="Q296" t="n">
-        <v>475300</v>
+        <v>416500</v>
       </c>
     </row>
     <row r="297">
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13074,19 +13074,19 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N298" t="n">
         <v>1026.13</v>
       </c>
       <c r="O298" t="n">
-        <v>472019.8</v>
+        <v>469967.54</v>
       </c>
       <c r="P298" t="n">
         <v>1900</v>
       </c>
       <c r="Q298" t="n">
-        <v>874000</v>
+        <v>870200</v>
       </c>
     </row>
     <row r="299">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>4145</v>
+        <v>4085</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13166,19 +13166,19 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>4145</v>
+        <v>4085</v>
       </c>
       <c r="N300" t="n">
         <v>156.25</v>
       </c>
       <c r="O300" t="n">
-        <v>647656.25</v>
+        <v>638281.25</v>
       </c>
       <c r="P300" t="n">
         <v>250</v>
       </c>
       <c r="Q300" t="n">
-        <v>1036250</v>
+        <v>1021250</v>
       </c>
     </row>
     <row r="301">
@@ -13446,10 +13446,10 @@
         <v>287</v>
       </c>
       <c r="N306" t="n">
-        <v>3795.7100075415</v>
+        <v>3795.7100075514</v>
       </c>
       <c r="O306" t="n">
-        <v>1089368.77216441</v>
+        <v>1089368.772167252</v>
       </c>
       <c r="P306" t="n">
         <v>6200</v>
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -13576,19 +13576,19 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="N309" t="n">
         <v>4357.55</v>
       </c>
       <c r="O309" t="n">
-        <v>1002236.5</v>
+        <v>976091.2000000001</v>
       </c>
       <c r="P309" t="n">
         <v>7500</v>
       </c>
       <c r="Q309" t="n">
-        <v>1725000</v>
+        <v>1680000</v>
       </c>
     </row>
     <row r="310">
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -13709,19 +13709,19 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N312" t="n">
-        <v>4890.9300485437</v>
+        <v>4890.9300486322</v>
       </c>
       <c r="O312" t="n">
-        <v>180964.4117961169</v>
+        <v>166291.6216534948</v>
       </c>
       <c r="P312" t="n">
         <v>8200</v>
       </c>
       <c r="Q312" t="n">
-        <v>303400</v>
+        <v>278800</v>
       </c>
     </row>
     <row r="313">
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>766</v>
+        <v>726</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -13804,19 +13804,19 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>766</v>
+        <v>726</v>
       </c>
       <c r="N314" t="n">
         <v>1203.38</v>
       </c>
       <c r="O314" t="n">
-        <v>921789.0800000001</v>
+        <v>873653.8800000001</v>
       </c>
       <c r="P314" t="n">
         <v>1900</v>
       </c>
       <c r="Q314" t="n">
-        <v>1455400</v>
+        <v>1379400</v>
       </c>
     </row>
     <row r="315">
@@ -13841,7 +13841,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -13850,19 +13850,19 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="N315" t="n">
         <v>3472</v>
       </c>
       <c r="O315" t="n">
-        <v>2437344</v>
+        <v>2395680</v>
       </c>
       <c r="P315" t="n">
         <v>4800</v>
       </c>
       <c r="Q315" t="n">
-        <v>3369600</v>
+        <v>3312000</v>
       </c>
     </row>
     <row r="316">
@@ -13887,7 +13887,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -13896,19 +13896,19 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N316" t="n">
         <v>5888</v>
       </c>
       <c r="O316" t="n">
-        <v>488704</v>
+        <v>476928</v>
       </c>
       <c r="P316" t="n">
         <v>9500</v>
       </c>
       <c r="Q316" t="n">
-        <v>788500</v>
+        <v>769500</v>
       </c>
     </row>
     <row r="317">
@@ -14194,7 +14194,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14203,19 +14203,19 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N323" t="n">
         <v>5667.94</v>
       </c>
       <c r="O323" t="n">
-        <v>527118.4199999999</v>
+        <v>521450.48</v>
       </c>
       <c r="P323" t="n">
         <v>9500</v>
       </c>
       <c r="Q323" t="n">
-        <v>883500</v>
+        <v>874000</v>
       </c>
     </row>
     <row r="324">
@@ -14586,7 +14586,7 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -14595,19 +14595,19 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N332" t="n">
-        <v>3594.2540372671</v>
+        <v>3594.2540224159</v>
       </c>
       <c r="O332" t="n">
-        <v>172524.1937888208</v>
+        <v>161741.4310087155</v>
       </c>
       <c r="P332" t="n">
         <v>6500</v>
       </c>
       <c r="Q332" t="n">
-        <v>312000</v>
+        <v>292500</v>
       </c>
     </row>
     <row r="333">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -14764,19 +14764,19 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="N336" t="n">
-        <v>3240.850031746</v>
+        <v>3240.8500325733</v>
       </c>
       <c r="O336" t="n">
-        <v>703264.456888882</v>
+        <v>651410.8565472333</v>
       </c>
       <c r="P336" t="n">
         <v>5200</v>
       </c>
       <c r="Q336" t="n">
-        <v>1128400</v>
+        <v>1045200</v>
       </c>
     </row>
     <row r="337">
@@ -14801,7 +14801,7 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -14810,19 +14810,19 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N337" t="n">
         <v>4891</v>
       </c>
       <c r="O337" t="n">
-        <v>538010</v>
+        <v>528228</v>
       </c>
       <c r="P337" t="n">
         <v>8200</v>
       </c>
       <c r="Q337" t="n">
-        <v>902000</v>
+        <v>885600</v>
       </c>
     </row>
     <row r="338">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -14856,19 +14856,19 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N338" t="n">
         <v>8154</v>
       </c>
       <c r="O338" t="n">
-        <v>611550</v>
+        <v>578934</v>
       </c>
       <c r="P338" t="n">
         <v>13500</v>
       </c>
       <c r="Q338" t="n">
-        <v>1012500</v>
+        <v>958500</v>
       </c>
     </row>
     <row r="339">
@@ -14893,7 +14893,7 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
@@ -14902,19 +14902,19 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N339" t="n">
-        <v>14822.378852361</v>
+        <v>14822.378850987</v>
       </c>
       <c r="O339" t="n">
-        <v>844875.594584577</v>
+        <v>815230.8368042849</v>
       </c>
       <c r="P339" t="n">
         <v>24900</v>
       </c>
       <c r="Q339" t="n">
-        <v>1419300</v>
+        <v>1369500</v>
       </c>
     </row>
     <row r="340">
@@ -14981,7 +14981,7 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>597</v>
+        <v>377</v>
       </c>
       <c r="K341" t="n">
         <v>0</v>
@@ -14990,19 +14990,19 @@
         <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>597</v>
+        <v>377</v>
       </c>
       <c r="N341" t="n">
         <v>2090.85</v>
       </c>
       <c r="O341" t="n">
-        <v>1248237.45</v>
+        <v>788250.45</v>
       </c>
       <c r="P341" t="n">
         <v>2900</v>
       </c>
       <c r="Q341" t="n">
-        <v>1731300</v>
+        <v>1093300</v>
       </c>
     </row>
     <row r="342">
@@ -15154,7 +15154,7 @@
         </is>
       </c>
       <c r="J345" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K345" t="n">
         <v>0</v>
@@ -15163,19 +15163,19 @@
         <v>0</v>
       </c>
       <c r="M345" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N345" t="n">
         <v>2665.4</v>
       </c>
       <c r="O345" t="n">
-        <v>74631.2</v>
+        <v>63969.60000000001</v>
       </c>
       <c r="P345" t="n">
         <v>20900</v>
       </c>
       <c r="Q345" t="n">
-        <v>585200</v>
+        <v>501600</v>
       </c>
     </row>
     <row r="346">
@@ -15463,7 +15463,7 @@
         </is>
       </c>
       <c r="J352" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
@@ -15472,19 +15472,19 @@
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N352" t="n">
         <v>4193.85</v>
       </c>
       <c r="O352" t="n">
-        <v>494874.3</v>
+        <v>490680.4500000001</v>
       </c>
       <c r="P352" t="n">
         <v>7500</v>
       </c>
       <c r="Q352" t="n">
-        <v>885000</v>
+        <v>877500</v>
       </c>
     </row>
     <row r="353">
@@ -15524,10 +15524,10 @@
         <v>426</v>
       </c>
       <c r="N353" t="n">
-        <v>3041.6600130804</v>
+        <v>3041.6600131579</v>
       </c>
       <c r="O353" t="n">
-        <v>1295747.16557225</v>
+        <v>1295747.165605265</v>
       </c>
       <c r="P353" t="n">
         <v>5500</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -15698,19 +15698,19 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N357" t="n">
-        <v>1592.5668955224</v>
+        <v>1592.5668693558</v>
       </c>
       <c r="O357" t="n">
-        <v>20703.3696417912</v>
+        <v>3185.1337387116</v>
       </c>
       <c r="P357" t="n">
         <v>3900</v>
       </c>
       <c r="Q357" t="n">
-        <v>50700</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="358">
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
@@ -15826,19 +15826,19 @@
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="N360" t="n">
         <v>3655.96</v>
       </c>
       <c r="O360" t="n">
-        <v>201077.8</v>
+        <v>106022.84</v>
       </c>
       <c r="P360" t="n">
         <v>5500</v>
       </c>
       <c r="Q360" t="n">
-        <v>302500</v>
+        <v>159500</v>
       </c>
     </row>
     <row r="361">
@@ -16212,7 +16212,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -16221,19 +16221,19 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N369" t="n">
         <v>6242.93</v>
       </c>
       <c r="O369" t="n">
-        <v>499434.4</v>
+        <v>486948.54</v>
       </c>
       <c r="P369" t="n">
         <v>10400</v>
       </c>
       <c r="Q369" t="n">
-        <v>832000</v>
+        <v>811200</v>
       </c>
     </row>
     <row r="370">
@@ -16261,7 +16261,7 @@
         </is>
       </c>
       <c r="J370" t="n">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K370" t="n">
         <v>0</v>
@@ -16270,19 +16270,19 @@
         <v>0</v>
       </c>
       <c r="M370" t="n">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="N370" t="n">
         <v>4648.6</v>
       </c>
       <c r="O370" t="n">
-        <v>1738576.4</v>
+        <v>1710684.8</v>
       </c>
       <c r="P370" t="n">
         <v>8900</v>
       </c>
       <c r="Q370" t="n">
-        <v>3328600</v>
+        <v>3275200</v>
       </c>
     </row>
     <row r="371">
@@ -16490,10 +16490,10 @@
         <v>323</v>
       </c>
       <c r="N375" t="n">
-        <v>1532.6290281516</v>
+        <v>1532.62902709</v>
       </c>
       <c r="O375" t="n">
-        <v>495039.1760929668</v>
+        <v>495039.17575007</v>
       </c>
       <c r="P375" t="n">
         <v>1200</v>
@@ -16739,7 +16739,7 @@
         </is>
       </c>
       <c r="J381" t="n">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="K381" t="n">
         <v>0</v>
@@ -16748,19 +16748,19 @@
         <v>0</v>
       </c>
       <c r="M381" t="n">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="N381" t="n">
         <v>1387.55</v>
       </c>
       <c r="O381" t="n">
-        <v>596646.5</v>
+        <v>588321.2</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
       </c>
       <c r="Q381" t="n">
-        <v>989000</v>
+        <v>975200</v>
       </c>
     </row>
     <row r="382">
@@ -16877,10 +16877,10 @@
         <v>180</v>
       </c>
       <c r="N384" t="n">
-        <v>2021.7211231884</v>
+        <v>2021.7211300122</v>
       </c>
       <c r="O384" t="n">
-        <v>363909.802173912</v>
+        <v>363909.803402196</v>
       </c>
       <c r="P384" t="n">
         <v>2400</v>
@@ -16909,7 +16909,7 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
@@ -16918,19 +16918,19 @@
         <v>0</v>
       </c>
       <c r="M385" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N385" t="n">
         <v>13304.13</v>
       </c>
       <c r="O385" t="n">
-        <v>465644.55</v>
+        <v>452340.42</v>
       </c>
       <c r="P385" t="n">
         <v>20900</v>
       </c>
       <c r="Q385" t="n">
-        <v>731500</v>
+        <v>710600</v>
       </c>
     </row>
     <row r="386">
@@ -17275,7 +17275,7 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K393" t="n">
         <v>0</v>
@@ -17284,19 +17284,19 @@
         <v>0</v>
       </c>
       <c r="M393" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N393" t="n">
         <v>11921.4</v>
       </c>
       <c r="O393" t="n">
-        <v>1573624.8</v>
+        <v>1549782</v>
       </c>
       <c r="P393" t="n">
         <v>19900</v>
       </c>
       <c r="Q393" t="n">
-        <v>2626800</v>
+        <v>2587000</v>
       </c>
     </row>
     <row r="394">
@@ -17615,7 +17615,7 @@
         </is>
       </c>
       <c r="J401" t="n">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="K401" t="n">
         <v>0</v>
@@ -17624,19 +17624,19 @@
         <v>0</v>
       </c>
       <c r="M401" t="n">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="N401" t="n">
         <v>3751</v>
       </c>
       <c r="O401" t="n">
-        <v>3263370</v>
+        <v>3240864</v>
       </c>
       <c r="P401" t="n">
         <v>6400</v>
       </c>
       <c r="Q401" t="n">
-        <v>5568000</v>
+        <v>5529600</v>
       </c>
     </row>
     <row r="402">
@@ -17664,7 +17664,7 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
@@ -17673,19 +17673,19 @@
         <v>0</v>
       </c>
       <c r="M402" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N402" t="n">
         <v>9903</v>
       </c>
       <c r="O402" t="n">
-        <v>713016</v>
+        <v>693210</v>
       </c>
       <c r="P402" t="n">
         <v>15900</v>
       </c>
       <c r="Q402" t="n">
-        <v>1144800</v>
+        <v>1113000</v>
       </c>
     </row>
     <row r="403">
@@ -17756,7 +17756,7 @@
         </is>
       </c>
       <c r="J404" t="n">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="K404" t="n">
         <v>0</v>
@@ -17765,19 +17765,19 @@
         <v>0</v>
       </c>
       <c r="M404" t="n">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="N404" t="n">
-        <v>1630.9235527836</v>
+        <v>1630.9235742505</v>
       </c>
       <c r="O404" t="n">
-        <v>947566.5841672715</v>
+        <v>919840.895877282</v>
       </c>
       <c r="P404" t="n">
         <v>2500</v>
       </c>
       <c r="Q404" t="n">
-        <v>1452500</v>
+        <v>1410000</v>
       </c>
     </row>
     <row r="405">
@@ -17843,7 +17843,7 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
@@ -17852,19 +17852,19 @@
         <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N406" t="n">
-        <v>1467.3243362832</v>
+        <v>1467.3242222222</v>
       </c>
       <c r="O406" t="n">
-        <v>291997.5429203568</v>
+        <v>290530.1959999956</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
       </c>
       <c r="Q406" t="n">
-        <v>497500</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="407">
@@ -17889,7 +17889,7 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
@@ -17898,19 +17898,19 @@
         <v>0</v>
       </c>
       <c r="M407" t="n">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="N407" t="n">
-        <v>1690.5981330472</v>
+        <v>1690.5974723655</v>
       </c>
       <c r="O407" t="n">
-        <v>316141.8508798264</v>
+        <v>263733.205689018</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
       </c>
       <c r="Q407" t="n">
-        <v>542300</v>
+        <v>452400</v>
       </c>
     </row>
     <row r="408">
@@ -17935,7 +17935,7 @@
         </is>
       </c>
       <c r="J408" t="n">
-        <v>1507</v>
+        <v>1371</v>
       </c>
       <c r="K408" t="n">
         <v>0</v>
@@ -17944,19 +17944,19 @@
         <v>0</v>
       </c>
       <c r="M408" t="n">
-        <v>1507</v>
+        <v>1371</v>
       </c>
       <c r="N408" t="n">
-        <v>1550.1935823921</v>
+        <v>1550.1936350279</v>
       </c>
       <c r="O408" t="n">
-        <v>2336141.728664895</v>
+        <v>2125315.473623251</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
       </c>
       <c r="Q408" t="n">
-        <v>3767500</v>
+        <v>3427500</v>
       </c>
     </row>
     <row r="409">
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="J410" t="n">
-        <v>912</v>
+        <v>835</v>
       </c>
       <c r="K410" t="n">
         <v>0</v>
@@ -18036,19 +18036,19 @@
         <v>0</v>
       </c>
       <c r="M410" t="n">
-        <v>912</v>
+        <v>835</v>
       </c>
       <c r="N410" t="n">
-        <v>2403.5116616598</v>
+        <v>2403.5118666412</v>
       </c>
       <c r="O410" t="n">
-        <v>2192002.635433738</v>
+        <v>2006932.408645402</v>
       </c>
       <c r="P410" t="n">
         <v>3500</v>
       </c>
       <c r="Q410" t="n">
-        <v>3192000</v>
+        <v>2922500</v>
       </c>
     </row>
     <row r="411">
@@ -18071,7 +18071,7 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K411" t="n">
         <v>0</v>
@@ -18080,19 +18080,19 @@
         <v>0</v>
       </c>
       <c r="M411" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N411" t="n">
         <v>24267.77</v>
       </c>
       <c r="O411" t="n">
-        <v>97071.08</v>
+        <v>48535.54</v>
       </c>
       <c r="P411" t="n">
         <v>33400</v>
       </c>
       <c r="Q411" t="n">
-        <v>133600</v>
+        <v>66800</v>
       </c>
     </row>
     <row r="412">
@@ -19120,7 +19120,7 @@
         </is>
       </c>
       <c r="J435" t="n">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="K435" t="n">
         <v>0</v>
@@ -19129,19 +19129,19 @@
         <v>0</v>
       </c>
       <c r="M435" t="n">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N435" t="n">
         <v>5067.21</v>
       </c>
       <c r="O435" t="n">
-        <v>1616439.99</v>
+        <v>1586036.73</v>
       </c>
       <c r="P435" t="n">
         <v>4200</v>
       </c>
       <c r="Q435" t="n">
-        <v>1339800</v>
+        <v>1314600</v>
       </c>
     </row>
     <row r="436">
@@ -19176,10 +19176,10 @@
         <v>23</v>
       </c>
       <c r="N436" t="n">
-        <v>2651.8557072368</v>
+        <v>2651.8556930693</v>
       </c>
       <c r="O436" t="n">
-        <v>60992.68126644639</v>
+        <v>60992.6809405939</v>
       </c>
       <c r="P436" t="n">
         <v>3800</v>
@@ -19343,7 +19343,7 @@
         </is>
       </c>
       <c r="J440" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K440" t="n">
         <v>0</v>
@@ -19352,19 +19352,19 @@
         <v>0</v>
       </c>
       <c r="M440" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N440" t="n">
         <v>3253</v>
       </c>
       <c r="O440" t="n">
-        <v>361083</v>
+        <v>357830</v>
       </c>
       <c r="P440" t="n">
         <v>3900</v>
       </c>
       <c r="Q440" t="n">
-        <v>432900</v>
+        <v>429000</v>
       </c>
     </row>
     <row r="441">
@@ -19735,7 +19735,7 @@
         </is>
       </c>
       <c r="J449" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K449" t="n">
         <v>0</v>
@@ -19744,19 +19744,19 @@
         <v>0</v>
       </c>
       <c r="M449" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N449" t="n">
         <v>3253</v>
       </c>
       <c r="O449" t="n">
-        <v>162650</v>
+        <v>146385</v>
       </c>
       <c r="P449" t="n">
         <v>3900</v>
       </c>
       <c r="Q449" t="n">
-        <v>195000</v>
+        <v>175500</v>
       </c>
     </row>
     <row r="450">
@@ -20893,7 +20893,7 @@
         </is>
       </c>
       <c r="J476" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K476" t="n">
         <v>0</v>
@@ -20902,19 +20902,19 @@
         <v>0</v>
       </c>
       <c r="M476" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N476" t="n">
-        <v>4196.872528417</v>
+        <v>4196.8725291181</v>
       </c>
       <c r="O476" t="n">
-        <v>625334.0067341329</v>
+        <v>621137.1343094788</v>
       </c>
       <c r="P476" t="n">
         <v>5900</v>
       </c>
       <c r="Q476" t="n">
-        <v>879100</v>
+        <v>873200</v>
       </c>
     </row>
     <row r="477">
@@ -21221,7 +21221,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -21230,19 +21230,19 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="N484" t="n">
         <v>4488</v>
       </c>
       <c r="O484" t="n">
-        <v>646272</v>
+        <v>632808</v>
       </c>
       <c r="P484" t="n">
         <v>6200</v>
       </c>
       <c r="Q484" t="n">
-        <v>892800</v>
+        <v>874200</v>
       </c>
     </row>
     <row r="485">
@@ -21303,7 +21303,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -21312,19 +21312,19 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N486" t="n">
         <v>2081</v>
       </c>
       <c r="O486" t="n">
-        <v>189371</v>
+        <v>185209</v>
       </c>
       <c r="P486" t="n">
         <v>3200</v>
       </c>
       <c r="Q486" t="n">
-        <v>291200</v>
+        <v>284800</v>
       </c>
     </row>
     <row r="487">
@@ -21344,7 +21344,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -21353,19 +21353,19 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="N487" t="n">
         <v>2916</v>
       </c>
       <c r="O487" t="n">
-        <v>326592</v>
+        <v>312012</v>
       </c>
       <c r="P487" t="n">
         <v>3200</v>
       </c>
       <c r="Q487" t="n">
-        <v>358400</v>
+        <v>342400</v>
       </c>
     </row>
     <row r="488">
@@ -21385,7 +21385,7 @@
         </is>
       </c>
       <c r="J488" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K488" t="n">
         <v>0</v>
@@ -21394,19 +21394,19 @@
         <v>0</v>
       </c>
       <c r="M488" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N488" t="n">
         <v>2286.55</v>
       </c>
       <c r="O488" t="n">
-        <v>134906.45</v>
+        <v>130333.35</v>
       </c>
       <c r="P488" t="n">
         <v>3200</v>
       </c>
       <c r="Q488" t="n">
-        <v>188800</v>
+        <v>182400</v>
       </c>
     </row>
     <row r="489">
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
@@ -21604,19 +21604,19 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N493" t="n">
         <v>2567</v>
       </c>
       <c r="O493" t="n">
-        <v>664853</v>
+        <v>649451</v>
       </c>
       <c r="P493" t="n">
         <v>4500</v>
       </c>
       <c r="Q493" t="n">
-        <v>1165500</v>
+        <v>1138500</v>
       </c>
     </row>
     <row r="494">
@@ -21976,10 +21976,10 @@
         <v>461</v>
       </c>
       <c r="N502" t="n">
-        <v>2029.8737443834</v>
+        <v>2029.8737669513</v>
       </c>
       <c r="O502" t="n">
-        <v>935771.7961607474</v>
+        <v>935771.8065645493</v>
       </c>
       <c r="P502" t="n">
         <v>3600</v>
@@ -22210,7 +22210,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -22219,19 +22219,19 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N508" t="n">
-        <v>22485.695577396</v>
+        <v>22485.695571956</v>
       </c>
       <c r="O508" t="n">
-        <v>1236713.25675678</v>
+        <v>1214227.560885624</v>
       </c>
       <c r="P508" t="n">
         <v>36500</v>
       </c>
       <c r="Q508" t="n">
-        <v>2007500</v>
+        <v>1971000</v>
       </c>
     </row>
     <row r="509">
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -22473,19 +22473,19 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N514" t="n">
         <v>24538.02</v>
       </c>
       <c r="O514" t="n">
-        <v>809754.66</v>
+        <v>760678.62</v>
       </c>
       <c r="P514" t="n">
         <v>52900</v>
       </c>
       <c r="Q514" t="n">
-        <v>1745700</v>
+        <v>1639900</v>
       </c>
     </row>
     <row r="515">
@@ -22599,10 +22599,10 @@
         <v>1347</v>
       </c>
       <c r="N517" t="n">
-        <v>880.3295131797699</v>
+        <v>880.32952448883</v>
       </c>
       <c r="O517" t="n">
-        <v>1185803.85425315</v>
+        <v>1185803.869486454</v>
       </c>
       <c r="P517" t="n">
         <v>1200</v>
@@ -22768,10 +22768,10 @@
         <v>8</v>
       </c>
       <c r="N521" t="n">
-        <v>11431.604756098</v>
+        <v>11431.604691358</v>
       </c>
       <c r="O521" t="n">
-        <v>91452.838048784</v>
+        <v>91452.837530864</v>
       </c>
       <c r="P521" t="n">
         <v>48900</v>
@@ -23002,7 +23002,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -23011,19 +23011,19 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N527" t="n">
-        <v>19810.3524</v>
+        <v>19810.352608696</v>
       </c>
       <c r="O527" t="n">
-        <v>79241.4096</v>
+        <v>39620.705217392</v>
       </c>
       <c r="P527" t="n">
         <v>37900</v>
       </c>
       <c r="Q527" t="n">
-        <v>151600</v>
+        <v>75800</v>
       </c>
     </row>
     <row r="528">
@@ -23585,10 +23585,10 @@
         <v>278</v>
       </c>
       <c r="N540" t="n">
-        <v>4285.1954741379</v>
+        <v>4285.1954859611</v>
       </c>
       <c r="O540" t="n">
-        <v>1191284.341810336</v>
+        <v>1191284.345097186</v>
       </c>
       <c r="P540" t="n">
         <v>6900</v>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -24261,19 +24261,19 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N556" t="n">
-        <v>30244.600034722</v>
+        <v>30244.600034762</v>
       </c>
       <c r="O556" t="n">
-        <v>423424.400486108</v>
+        <v>362935.200417144</v>
       </c>
       <c r="P556" t="n">
         <v>48900</v>
       </c>
       <c r="Q556" t="n">
-        <v>684600</v>
+        <v>586800</v>
       </c>
     </row>
     <row r="557">
@@ -24385,7 +24385,7 @@
         </is>
       </c>
       <c r="J559" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K559" t="n">
         <v>0</v>
@@ -24394,19 +24394,19 @@
         <v>0</v>
       </c>
       <c r="M559" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N559" t="n">
-        <v>11562.038494624</v>
+        <v>11562.038478261</v>
       </c>
       <c r="O559" t="n">
-        <v>601226.0017204479</v>
+        <v>578101.92391305</v>
       </c>
       <c r="P559" t="n">
         <v>18500</v>
       </c>
       <c r="Q559" t="n">
-        <v>962000</v>
+        <v>925000</v>
       </c>
     </row>
     <row r="560">
@@ -24431,7 +24431,7 @@
         </is>
       </c>
       <c r="J560" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K560" t="n">
         <v>0</v>
@@ -24440,19 +24440,19 @@
         <v>0</v>
       </c>
       <c r="M560" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N560" t="n">
-        <v>13513.642992701</v>
+        <v>13513.643014706</v>
       </c>
       <c r="O560" t="n">
-        <v>797304.9365693589</v>
+        <v>783791.294852948</v>
       </c>
       <c r="P560" t="n">
         <v>21900</v>
       </c>
       <c r="Q560" t="n">
-        <v>1292100</v>
+        <v>1270200</v>
       </c>
     </row>
     <row r="561">
@@ -25772,7 +25772,7 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
@@ -25781,19 +25781,19 @@
         <v>0</v>
       </c>
       <c r="M591" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N591" t="n">
-        <v>27123.765232775</v>
+        <v>27123.765223881</v>
       </c>
       <c r="O591" t="n">
-        <v>1112074.374543775</v>
+        <v>1084950.60895524</v>
       </c>
       <c r="P591" t="n">
         <v>44500</v>
       </c>
       <c r="Q591" t="n">
-        <v>1824500</v>
+        <v>1780000</v>
       </c>
     </row>
     <row r="592">
@@ -26069,7 +26069,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -26078,19 +26078,19 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N598" t="n">
-        <v>31771.063719008</v>
+        <v>31771.063781513</v>
       </c>
       <c r="O598" t="n">
-        <v>953131.91157024</v>
+        <v>889589.785882364</v>
       </c>
       <c r="P598" t="n">
         <v>68900</v>
       </c>
       <c r="Q598" t="n">
-        <v>2067000</v>
+        <v>1929200</v>
       </c>
     </row>
     <row r="599">
@@ -26214,10 +26214,10 @@
         <v>68</v>
       </c>
       <c r="N601" t="n">
-        <v>1561.0001684211</v>
+        <v>1561.0002330508</v>
       </c>
       <c r="O601" t="n">
-        <v>106148.0114526348</v>
+        <v>106148.0158474544</v>
       </c>
       <c r="P601" t="n">
         <v>2900</v>
@@ -26335,7 +26335,7 @@
         </is>
       </c>
       <c r="J604" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K604" t="n">
         <v>0</v>
@@ -26344,19 +26344,19 @@
         <v>0</v>
       </c>
       <c r="M604" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N604" t="n">
         <v>26854</v>
       </c>
       <c r="O604" t="n">
-        <v>993598</v>
+        <v>966744</v>
       </c>
       <c r="P604" t="n">
         <v>43900</v>
       </c>
       <c r="Q604" t="n">
-        <v>1624300</v>
+        <v>1580400</v>
       </c>
     </row>
     <row r="605">
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="J607" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K607" t="n">
         <v>0</v>
@@ -26480,19 +26480,19 @@
         <v>0</v>
       </c>
       <c r="M607" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N607" t="n">
-        <v>7969.9501665405</v>
+        <v>7969.9501669196</v>
       </c>
       <c r="O607" t="n">
-        <v>1067973.322316427</v>
+        <v>1044063.471866468</v>
       </c>
       <c r="P607" t="n">
         <v>12900</v>
       </c>
       <c r="Q607" t="n">
-        <v>1728600</v>
+        <v>1689900</v>
       </c>
     </row>
     <row r="608">
@@ -26804,7 +26804,7 @@
         </is>
       </c>
       <c r="J615" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K615" t="n">
         <v>0</v>
@@ -26813,19 +26813,19 @@
         <v>0</v>
       </c>
       <c r="M615" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N615" t="n">
         <v>14954</v>
       </c>
       <c r="O615" t="n">
-        <v>628068</v>
+        <v>613114</v>
       </c>
       <c r="P615" t="n">
         <v>25500</v>
       </c>
       <c r="Q615" t="n">
-        <v>1071000</v>
+        <v>1045500</v>
       </c>
     </row>
     <row r="616">
@@ -28350,10 +28350,10 @@
         <v>133</v>
       </c>
       <c r="N650" t="n">
-        <v>1595.0093780687</v>
+        <v>1595.009375</v>
       </c>
       <c r="O650" t="n">
-        <v>212136.2472831371</v>
+        <v>212136.246875</v>
       </c>
       <c r="P650" t="n">
         <v>2600</v>
@@ -28396,10 +28396,10 @@
         <v>75</v>
       </c>
       <c r="N651" t="n">
-        <v>3610.65002574</v>
+        <v>3610.6500258065</v>
       </c>
       <c r="O651" t="n">
-        <v>270798.7519305</v>
+        <v>270798.7519354875</v>
       </c>
       <c r="P651" t="n">
         <v>5800</v>
@@ -28798,7 +28798,7 @@
         </is>
       </c>
       <c r="J660" t="n">
-        <v>303</v>
+        <v>251</v>
       </c>
       <c r="K660" t="n">
         <v>0</v>
@@ -28807,19 +28807,19 @@
         <v>0</v>
       </c>
       <c r="M660" t="n">
-        <v>303</v>
+        <v>251</v>
       </c>
       <c r="N660" t="n">
-        <v>1664.3568077803</v>
+        <v>1664.355973236</v>
       </c>
       <c r="O660" t="n">
-        <v>504300.1127574309</v>
+        <v>417753.349282236</v>
       </c>
       <c r="P660" t="n">
         <v>2900</v>
       </c>
       <c r="Q660" t="n">
-        <v>878700</v>
+        <v>727900</v>
       </c>
     </row>
     <row r="661">
@@ -29310,7 +29310,7 @@
         </is>
       </c>
       <c r="J671" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K671" t="n">
         <v>0</v>
@@ -29319,19 +29319,19 @@
         <v>0</v>
       </c>
       <c r="M671" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N671" t="n">
         <v>3646</v>
       </c>
       <c r="O671" t="n">
-        <v>379184</v>
+        <v>364600</v>
       </c>
       <c r="P671" t="n">
         <v>6900</v>
       </c>
       <c r="Q671" t="n">
-        <v>717600</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="672">
@@ -29448,7 +29448,7 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>1420</v>
+        <v>1400</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
@@ -29457,19 +29457,19 @@
         <v>0</v>
       </c>
       <c r="M674" t="n">
-        <v>1420</v>
+        <v>1400</v>
       </c>
       <c r="N674" t="n">
-        <v>1778.4726172988</v>
+        <v>1778.4726251691</v>
       </c>
       <c r="O674" t="n">
-        <v>2525431.116564296</v>
+        <v>2489861.67523674</v>
       </c>
       <c r="P674" t="n">
         <v>4900</v>
       </c>
       <c r="Q674" t="n">
-        <v>6958000</v>
+        <v>6860000</v>
       </c>
     </row>
     <row r="675">
@@ -29494,7 +29494,7 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
@@ -29503,19 +29503,19 @@
         <v>0</v>
       </c>
       <c r="M675" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="N675" t="n">
         <v>1548</v>
       </c>
       <c r="O675" t="n">
-        <v>321984</v>
+        <v>309600</v>
       </c>
       <c r="P675" t="n">
         <v>3900</v>
       </c>
       <c r="Q675" t="n">
-        <v>811200</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="676">
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="J694" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K694" t="n">
         <v>0</v>
@@ -30380,19 +30380,19 @@
         <v>0</v>
       </c>
       <c r="M694" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N694" t="n">
         <v>6000</v>
       </c>
       <c r="O694" t="n">
-        <v>444000</v>
+        <v>438000</v>
       </c>
       <c r="P694" t="n">
         <v>10000</v>
       </c>
       <c r="Q694" t="n">
-        <v>740000</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="695">
@@ -31248,7 +31248,7 @@
         </is>
       </c>
       <c r="J713" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K713" t="n">
         <v>0</v>
@@ -31257,19 +31257,19 @@
         <v>0</v>
       </c>
       <c r="M713" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N713" t="n">
         <v>13687</v>
       </c>
       <c r="O713" t="n">
-        <v>1327639</v>
+        <v>1300265</v>
       </c>
       <c r="P713" t="n">
         <v>21900</v>
       </c>
       <c r="Q713" t="n">
-        <v>2124300</v>
+        <v>2080500</v>
       </c>
     </row>
     <row r="714">
@@ -32270,10 +32270,10 @@
         <v>684</v>
       </c>
       <c r="N735" t="n">
-        <v>2328.1187184938</v>
+        <v>2328.1187161545</v>
       </c>
       <c r="O735" t="n">
-        <v>1592433.203449759</v>
+        <v>1592433.201849678</v>
       </c>
       <c r="P735" t="n">
         <v>4500</v>
@@ -32810,7 +32810,7 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
@@ -32819,19 +32819,19 @@
         <v>0</v>
       </c>
       <c r="M747" t="n">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="N747" t="n">
         <v>4544</v>
       </c>
       <c r="O747" t="n">
-        <v>2217472</v>
+        <v>2181120</v>
       </c>
       <c r="P747" t="n">
         <v>7900</v>
       </c>
       <c r="Q747" t="n">
-        <v>3855200</v>
+        <v>3792000</v>
       </c>
     </row>
     <row r="748">
@@ -33052,10 +33052,10 @@
         <v>16</v>
       </c>
       <c r="N752" t="n">
-        <v>4907.8220751634</v>
+        <v>4907.822092257</v>
       </c>
       <c r="O752" t="n">
-        <v>78525.1532026144</v>
+        <v>78525.153476112</v>
       </c>
       <c r="P752" t="n">
         <v>8200</v>
@@ -33178,7 +33178,7 @@
         </is>
       </c>
       <c r="J755" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K755" t="n">
         <v>0</v>
@@ -33187,19 +33187,19 @@
         <v>0</v>
       </c>
       <c r="M755" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N755" t="n">
         <v>100129</v>
       </c>
       <c r="O755" t="n">
-        <v>901161</v>
+        <v>801032</v>
       </c>
       <c r="P755" t="n">
         <v>159900</v>
       </c>
       <c r="Q755" t="n">
-        <v>1439100</v>
+        <v>1279200</v>
       </c>
     </row>
     <row r="756">
@@ -33224,7 +33224,7 @@
         </is>
       </c>
       <c r="J756" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K756" t="n">
         <v>0</v>
@@ -33233,19 +33233,19 @@
         <v>0</v>
       </c>
       <c r="M756" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N756" t="n">
         <v>76839</v>
       </c>
       <c r="O756" t="n">
-        <v>1306263</v>
+        <v>1229424</v>
       </c>
       <c r="P756" t="n">
         <v>122900</v>
       </c>
       <c r="Q756" t="n">
-        <v>2089300</v>
+        <v>1966400</v>
       </c>
     </row>
     <row r="757">
@@ -33316,7 +33316,7 @@
         </is>
       </c>
       <c r="J758" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="K758" t="n">
         <v>0</v>
@@ -33325,19 +33325,19 @@
         <v>0</v>
       </c>
       <c r="M758" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="N758" t="n">
-        <v>3903.7364581763</v>
+        <v>3903.7365705615</v>
       </c>
       <c r="O758" t="n">
-        <v>558234.3135192109</v>
+        <v>534811.9101669255</v>
       </c>
       <c r="P758" t="n">
         <v>7500</v>
       </c>
       <c r="Q758" t="n">
-        <v>1072500</v>
+        <v>1027500</v>
       </c>
     </row>
     <row r="759">
@@ -33357,7 +33357,7 @@
         </is>
       </c>
       <c r="J759" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K759" t="n">
         <v>0</v>
@@ -33366,19 +33366,19 @@
         <v>0</v>
       </c>
       <c r="M759" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N759" t="n">
         <v>20726</v>
       </c>
       <c r="O759" t="n">
-        <v>559602</v>
+        <v>518150</v>
       </c>
       <c r="P759" t="n">
         <v>33900</v>
       </c>
       <c r="Q759" t="n">
-        <v>915300</v>
+        <v>847500</v>
       </c>
     </row>
     <row r="760">
@@ -33863,7 +33863,7 @@
         </is>
       </c>
       <c r="J770" t="n">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="K770" t="n">
         <v>0</v>
@@ -33872,19 +33872,19 @@
         <v>0</v>
       </c>
       <c r="M770" t="n">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="N770" t="n">
-        <v>5869.1726653103</v>
+        <v>5869.1726202661</v>
       </c>
       <c r="O770" t="n">
-        <v>2870025.433336737</v>
+        <v>2834810.375588526</v>
       </c>
       <c r="P770" t="n">
         <v>9500</v>
       </c>
       <c r="Q770" t="n">
-        <v>4645500</v>
+        <v>4588500</v>
       </c>
     </row>
     <row r="771">
@@ -34047,7 +34047,7 @@
         </is>
       </c>
       <c r="J774" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K774" t="n">
         <v>0</v>
@@ -34056,19 +34056,19 @@
         <v>0</v>
       </c>
       <c r="M774" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="N774" t="n">
         <v>6268</v>
       </c>
       <c r="O774" t="n">
-        <v>488904</v>
+        <v>432492</v>
       </c>
       <c r="P774" t="n">
         <v>10900</v>
       </c>
       <c r="Q774" t="n">
-        <v>850200</v>
+        <v>752100</v>
       </c>
     </row>
     <row r="775">
@@ -34139,7 +34139,7 @@
         </is>
       </c>
       <c r="J776" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K776" t="n">
         <v>0</v>
@@ -34148,19 +34148,19 @@
         <v>0</v>
       </c>
       <c r="M776" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N776" t="n">
         <v>6645</v>
       </c>
       <c r="O776" t="n">
-        <v>1641315</v>
+        <v>1634670</v>
       </c>
       <c r="P776" t="n">
         <v>10900</v>
       </c>
       <c r="Q776" t="n">
-        <v>2692300</v>
+        <v>2681400</v>
       </c>
     </row>
     <row r="777">
@@ -34185,7 +34185,7 @@
         </is>
       </c>
       <c r="J777" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K777" t="n">
         <v>0</v>
@@ -34194,19 +34194,19 @@
         <v>0</v>
       </c>
       <c r="M777" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N777" t="n">
         <v>13098</v>
       </c>
       <c r="O777" t="n">
-        <v>1178820</v>
+        <v>1152624</v>
       </c>
       <c r="P777" t="n">
         <v>21200</v>
       </c>
       <c r="Q777" t="n">
-        <v>1908000</v>
+        <v>1865600</v>
       </c>
     </row>
     <row r="778">
@@ -34369,7 +34369,7 @@
         </is>
       </c>
       <c r="J781" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="K781" t="n">
         <v>0</v>
@@ -34378,19 +34378,19 @@
         <v>0</v>
       </c>
       <c r="M781" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N781" t="n">
         <v>3898</v>
       </c>
       <c r="O781" t="n">
-        <v>1122624</v>
+        <v>1110930</v>
       </c>
       <c r="P781" t="n">
         <v>6900</v>
       </c>
       <c r="Q781" t="n">
-        <v>1987200</v>
+        <v>1966500</v>
       </c>
     </row>
     <row r="782">
@@ -34415,7 +34415,7 @@
         </is>
       </c>
       <c r="J782" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K782" t="n">
         <v>0</v>
@@ -34424,19 +34424,19 @@
         <v>0</v>
       </c>
       <c r="M782" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N782" t="n">
         <v>13565</v>
       </c>
       <c r="O782" t="n">
-        <v>1370065</v>
+        <v>1342935</v>
       </c>
       <c r="P782" t="n">
         <v>22500</v>
       </c>
       <c r="Q782" t="n">
-        <v>2272500</v>
+        <v>2227500</v>
       </c>
     </row>
     <row r="783">
@@ -34461,7 +34461,7 @@
         </is>
       </c>
       <c r="J783" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K783" t="n">
         <v>0</v>
@@ -34470,19 +34470,19 @@
         <v>0</v>
       </c>
       <c r="M783" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N783" t="n">
         <v>7635</v>
       </c>
       <c r="O783" t="n">
-        <v>564990</v>
+        <v>549720</v>
       </c>
       <c r="P783" t="n">
         <v>13900</v>
       </c>
       <c r="Q783" t="n">
-        <v>1028600</v>
+        <v>1000800</v>
       </c>
     </row>
     <row r="784">
@@ -34694,7 +34694,7 @@
         </is>
       </c>
       <c r="J788" t="n">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="K788" t="n">
         <v>0</v>
@@ -34703,19 +34703,19 @@
         <v>0</v>
       </c>
       <c r="M788" t="n">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="N788" t="n">
         <v>753</v>
       </c>
       <c r="O788" t="n">
-        <v>467613</v>
+        <v>463095</v>
       </c>
       <c r="P788" t="n">
         <v>1600</v>
       </c>
       <c r="Q788" t="n">
-        <v>993600</v>
+        <v>984000</v>
       </c>
     </row>
     <row r="789">
@@ -34740,7 +34740,7 @@
         </is>
       </c>
       <c r="J789" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K789" t="n">
         <v>0</v>
@@ -34749,19 +34749,19 @@
         <v>0</v>
       </c>
       <c r="M789" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N789" t="n">
         <v>11302</v>
       </c>
       <c r="O789" t="n">
-        <v>1356240</v>
+        <v>1344938</v>
       </c>
       <c r="P789" t="n">
         <v>18900</v>
       </c>
       <c r="Q789" t="n">
-        <v>2268000</v>
+        <v>2249100</v>
       </c>
     </row>
     <row r="790">
@@ -34878,7 +34878,7 @@
         </is>
       </c>
       <c r="J792" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K792" t="n">
         <v>0</v>
@@ -34887,19 +34887,19 @@
         <v>0</v>
       </c>
       <c r="M792" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N792" t="n">
         <v>11348</v>
       </c>
       <c r="O792" t="n">
-        <v>363136</v>
+        <v>351788</v>
       </c>
       <c r="P792" t="n">
         <v>19900</v>
       </c>
       <c r="Q792" t="n">
-        <v>636800</v>
+        <v>616900</v>
       </c>
     </row>
     <row r="793">
@@ -35474,7 +35474,7 @@
         </is>
       </c>
       <c r="J805" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K805" t="n">
         <v>0</v>
@@ -35483,19 +35483,19 @@
         <v>0</v>
       </c>
       <c r="M805" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N805" t="n">
         <v>20014</v>
       </c>
       <c r="O805" t="n">
-        <v>280196</v>
+        <v>240168</v>
       </c>
       <c r="P805" t="n">
         <v>33900</v>
       </c>
       <c r="Q805" t="n">
-        <v>474600</v>
+        <v>406800</v>
       </c>
     </row>
     <row r="806">
@@ -35658,7 +35658,7 @@
         </is>
       </c>
       <c r="J809" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="K809" t="n">
         <v>0</v>
@@ -35667,19 +35667,19 @@
         <v>0</v>
       </c>
       <c r="M809" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="N809" t="n">
         <v>5215</v>
       </c>
       <c r="O809" t="n">
-        <v>380695</v>
+        <v>318115</v>
       </c>
       <c r="P809" t="n">
         <v>8900</v>
       </c>
       <c r="Q809" t="n">
-        <v>649700</v>
+        <v>542900</v>
       </c>
     </row>
     <row r="810">
@@ -35888,7 +35888,7 @@
         </is>
       </c>
       <c r="J814" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K814" t="n">
         <v>0</v>
@@ -35897,19 +35897,19 @@
         <v>0</v>
       </c>
       <c r="M814" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N814" t="n">
         <v>5588</v>
       </c>
       <c r="O814" t="n">
-        <v>396748</v>
+        <v>379984</v>
       </c>
       <c r="P814" t="n">
         <v>9500</v>
       </c>
       <c r="Q814" t="n">
-        <v>674500</v>
+        <v>646000</v>
       </c>
     </row>
     <row r="815">
@@ -35980,7 +35980,7 @@
         </is>
       </c>
       <c r="J816" t="n">
-        <v>1130</v>
+        <v>1100</v>
       </c>
       <c r="K816" t="n">
         <v>0</v>
@@ -35989,19 +35989,19 @@
         <v>0</v>
       </c>
       <c r="M816" t="n">
-        <v>1130</v>
+        <v>1100</v>
       </c>
       <c r="N816" t="n">
         <v>1326</v>
       </c>
       <c r="O816" t="n">
-        <v>1498380</v>
+        <v>1458600</v>
       </c>
       <c r="P816" t="n">
         <v>2500</v>
       </c>
       <c r="Q816" t="n">
-        <v>2825000</v>
+        <v>2750000</v>
       </c>
     </row>
     <row r="817">
@@ -36026,7 +36026,7 @@
         </is>
       </c>
       <c r="J817" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K817" t="n">
         <v>0</v>
@@ -36035,19 +36035,19 @@
         <v>0</v>
       </c>
       <c r="M817" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="N817" t="n">
         <v>2573</v>
       </c>
       <c r="O817" t="n">
-        <v>373085</v>
+        <v>365366</v>
       </c>
       <c r="P817" t="n">
         <v>4500</v>
       </c>
       <c r="Q817" t="n">
-        <v>652500</v>
+        <v>639000</v>
       </c>
     </row>
     <row r="818">
@@ -36072,7 +36072,7 @@
         </is>
       </c>
       <c r="J818" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K818" t="n">
         <v>0</v>
@@ -36081,19 +36081,19 @@
         <v>0</v>
       </c>
       <c r="M818" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N818" t="n">
         <v>21762</v>
       </c>
       <c r="O818" t="n">
-        <v>326430</v>
+        <v>282906</v>
       </c>
       <c r="P818" t="n">
         <v>35900</v>
       </c>
       <c r="Q818" t="n">
-        <v>538500</v>
+        <v>466700</v>
       </c>
     </row>
     <row r="819">
@@ -36118,7 +36118,7 @@
         </is>
       </c>
       <c r="J819" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K819" t="n">
         <v>0</v>
@@ -36127,19 +36127,19 @@
         <v>0</v>
       </c>
       <c r="M819" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="N819" t="n">
         <v>3821</v>
       </c>
       <c r="O819" t="n">
-        <v>764200</v>
+        <v>752737</v>
       </c>
       <c r="P819" t="n">
         <v>5900</v>
       </c>
       <c r="Q819" t="n">
-        <v>1180000</v>
+        <v>1162300</v>
       </c>
     </row>
     <row r="820">
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="J824" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K824" t="n">
         <v>0</v>
@@ -36357,19 +36357,19 @@
         <v>0</v>
       </c>
       <c r="M824" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="N824" t="n">
         <v>5476</v>
       </c>
       <c r="O824" t="n">
-        <v>2409440</v>
+        <v>2403964</v>
       </c>
       <c r="P824" t="n">
         <v>8900</v>
       </c>
       <c r="Q824" t="n">
-        <v>3916000</v>
+        <v>3907100</v>
       </c>
     </row>
     <row r="825">
@@ -36627,7 +36627,7 @@
         </is>
       </c>
       <c r="J830" t="n">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="K830" t="n">
         <v>0</v>
@@ -36636,19 +36636,19 @@
         <v>0</v>
       </c>
       <c r="M830" t="n">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="N830" t="n">
-        <v>1516.038799961</v>
+        <v>1516.0387986728</v>
       </c>
       <c r="O830" t="n">
-        <v>906591.202376678</v>
+        <v>900527.0464116433</v>
       </c>
       <c r="P830" t="n">
         <v>2300</v>
       </c>
       <c r="Q830" t="n">
-        <v>1375400</v>
+        <v>1366200</v>
       </c>
     </row>
     <row r="831">
@@ -36809,7 +36809,7 @@
         </is>
       </c>
       <c r="J834" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="K834" t="n">
         <v>0</v>
@@ -36818,19 +36818,19 @@
         <v>0</v>
       </c>
       <c r="M834" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="N834" t="n">
-        <v>1907.393656644</v>
+        <v>1907.3930202775</v>
       </c>
       <c r="O834" t="n">
-        <v>305182.98506304</v>
+        <v>247961.092636075</v>
       </c>
       <c r="P834" t="n">
         <v>2500</v>
       </c>
       <c r="Q834" t="n">
-        <v>400000</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="835">
@@ -36901,7 +36901,7 @@
         </is>
       </c>
       <c r="J836" t="n">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="K836" t="n">
         <v>0</v>
@@ -36910,19 +36910,19 @@
         <v>0</v>
       </c>
       <c r="M836" t="n">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="N836" t="n">
-        <v>2079.3840374332</v>
+        <v>2079.3840254521</v>
       </c>
       <c r="O836" t="n">
-        <v>854626.8393850451</v>
+        <v>842150.5303081005</v>
       </c>
       <c r="P836" t="n">
         <v>2900</v>
       </c>
       <c r="Q836" t="n">
-        <v>1191900</v>
+        <v>1174500</v>
       </c>
     </row>
     <row r="837">
@@ -36993,7 +36993,7 @@
         </is>
       </c>
       <c r="J838" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K838" t="n">
         <v>0</v>
@@ -37002,19 +37002,19 @@
         <v>0</v>
       </c>
       <c r="M838" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="N838" t="n">
-        <v>3306.5951742627</v>
+        <v>3306.5951351351</v>
       </c>
       <c r="O838" t="n">
-        <v>234768.2573726517</v>
+        <v>214928.6837837815</v>
       </c>
       <c r="P838" t="n">
         <v>4900</v>
       </c>
       <c r="Q838" t="n">
-        <v>347900</v>
+        <v>318500</v>
       </c>
     </row>
     <row r="839">
@@ -37097,10 +37097,10 @@
         <v>372</v>
       </c>
       <c r="N840" t="n">
-        <v>2108.7917654987</v>
+        <v>2108.7918292683</v>
       </c>
       <c r="O840" t="n">
-        <v>784470.5367655164</v>
+        <v>784470.5604878075</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
@@ -37177,7 +37177,7 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
@@ -37186,19 +37186,19 @@
         <v>0</v>
       </c>
       <c r="M842" t="n">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="N842" t="n">
-        <v>3224.5685727969</v>
+        <v>3224.5688003933</v>
       </c>
       <c r="O842" t="n">
-        <v>783570.1631896467</v>
+        <v>667485.7416814131</v>
       </c>
       <c r="P842" t="n">
         <v>4500</v>
       </c>
       <c r="Q842" t="n">
-        <v>1093500</v>
+        <v>931500</v>
       </c>
     </row>
     <row r="843">
@@ -37223,7 +37223,7 @@
         </is>
       </c>
       <c r="J843" t="n">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="K843" t="n">
         <v>0</v>
@@ -37232,19 +37232,19 @@
         <v>0</v>
       </c>
       <c r="M843" t="n">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="N843" t="n">
-        <v>1655.9308833223</v>
+        <v>1655.9308652576</v>
       </c>
       <c r="O843" t="n">
-        <v>753448.5519116465</v>
+        <v>743512.9585006625</v>
       </c>
       <c r="P843" t="n">
         <v>2500</v>
       </c>
       <c r="Q843" t="n">
-        <v>1137500</v>
+        <v>1122500</v>
       </c>
     </row>
     <row r="844">
@@ -37456,7 +37456,7 @@
         </is>
       </c>
       <c r="J848" t="n">
-        <v>582</v>
+        <v>554</v>
       </c>
       <c r="K848" t="n">
         <v>0</v>
@@ -37465,19 +37465,19 @@
         <v>0</v>
       </c>
       <c r="M848" t="n">
-        <v>582</v>
+        <v>554</v>
       </c>
       <c r="N848" t="n">
         <v>1662</v>
       </c>
       <c r="O848" t="n">
-        <v>967284</v>
+        <v>920748</v>
       </c>
       <c r="P848" t="n">
         <v>2900</v>
       </c>
       <c r="Q848" t="n">
-        <v>1687800</v>
+        <v>1606600</v>
       </c>
     </row>
     <row r="849">
@@ -37502,7 +37502,7 @@
         </is>
       </c>
       <c r="J849" t="n">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="K849" t="n">
         <v>0</v>
@@ -37511,19 +37511,19 @@
         <v>0</v>
       </c>
       <c r="M849" t="n">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="N849" t="n">
         <v>2003</v>
       </c>
       <c r="O849" t="n">
-        <v>342513</v>
+        <v>330495</v>
       </c>
       <c r="P849" t="n">
         <v>3900</v>
       </c>
       <c r="Q849" t="n">
-        <v>666900</v>
+        <v>643500</v>
       </c>
     </row>
     <row r="850">
@@ -37650,10 +37650,10 @@
         <v>2</v>
       </c>
       <c r="N852" t="n">
-        <v>1906.183697479</v>
+        <v>1906.1836708861</v>
       </c>
       <c r="O852" t="n">
-        <v>3812.367394958</v>
+        <v>3812.3673417722</v>
       </c>
       <c r="P852" t="n">
         <v>2900</v>
@@ -37684,7 +37684,7 @@
         </is>
       </c>
       <c r="J853" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K853" t="n">
         <v>0</v>
@@ -37693,19 +37693,19 @@
         <v>0</v>
       </c>
       <c r="M853" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N853" t="n">
-        <v>2060.1601030928</v>
+        <v>2060.1598053097</v>
       </c>
       <c r="O853" t="n">
-        <v>166872.9683505168</v>
+        <v>162752.6246194663</v>
       </c>
       <c r="P853" t="n">
         <v>2900</v>
       </c>
       <c r="Q853" t="n">
-        <v>234900</v>
+        <v>229100</v>
       </c>
     </row>
     <row r="854">
@@ -38509,7 +38509,7 @@
         </is>
       </c>
       <c r="J871" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K871" t="n">
         <v>0</v>
@@ -38518,19 +38518,19 @@
         <v>0</v>
       </c>
       <c r="M871" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N871" t="n">
         <v>15423.36</v>
       </c>
       <c r="O871" t="n">
-        <v>30846.72</v>
+        <v>15423.36</v>
       </c>
       <c r="P871" t="n">
         <v>24900</v>
       </c>
       <c r="Q871" t="n">
-        <v>49800</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="872">
@@ -39385,7 +39385,7 @@
         </is>
       </c>
       <c r="J890" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K890" t="n">
         <v>0</v>
@@ -39394,19 +39394,19 @@
         <v>0</v>
       </c>
       <c r="M890" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N890" t="n">
         <v>2357.74</v>
       </c>
       <c r="O890" t="n">
-        <v>235774</v>
+        <v>223985.3</v>
       </c>
       <c r="P890" t="n">
         <v>3000</v>
       </c>
       <c r="Q890" t="n">
-        <v>300000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="891">
@@ -39568,7 +39568,7 @@
         </is>
       </c>
       <c r="J894" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K894" t="n">
         <v>0</v>
@@ -39577,19 +39577,19 @@
         <v>0</v>
       </c>
       <c r="M894" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N894" t="n">
-        <v>2270.3211627907</v>
+        <v>2270.3211764706</v>
       </c>
       <c r="O894" t="n">
-        <v>43136.1020930233</v>
+        <v>40865.7811764708</v>
       </c>
       <c r="P894" t="n">
         <v>3900</v>
       </c>
       <c r="Q894" t="n">
-        <v>74100</v>
+        <v>70200</v>
       </c>
     </row>
     <row r="895">
@@ -39624,10 +39624,10 @@
         <v>561</v>
       </c>
       <c r="N895" t="n">
-        <v>481.48791460674</v>
+        <v>481.48791273054</v>
       </c>
       <c r="O895" t="n">
-        <v>270114.7200943811</v>
+        <v>270114.719041833</v>
       </c>
       <c r="P895" t="n">
         <v>650</v>
@@ -39717,10 +39717,10 @@
         <v>575</v>
       </c>
       <c r="N897" t="n">
-        <v>872.15418521463</v>
+        <v>872.15418687873</v>
       </c>
       <c r="O897" t="n">
-        <v>501488.6564984123</v>
+        <v>501488.6574552698</v>
       </c>
       <c r="P897" t="n">
         <v>1200</v>
@@ -40857,7 +40857,7 @@
         </is>
       </c>
       <c r="J923" t="n">
-        <v>2942</v>
+        <v>2882</v>
       </c>
       <c r="K923" t="n">
         <v>0</v>
@@ -40866,19 +40866,19 @@
         <v>0</v>
       </c>
       <c r="M923" t="n">
-        <v>2942</v>
+        <v>2882</v>
       </c>
       <c r="N923" t="n">
-        <v>517.2892916984</v>
+        <v>517.28943177426</v>
       </c>
       <c r="O923" t="n">
-        <v>1521865.096176693</v>
+        <v>1490828.142373418</v>
       </c>
       <c r="P923" t="n">
         <v>900</v>
       </c>
       <c r="Q923" t="n">
-        <v>2647800</v>
+        <v>2593800</v>
       </c>
     </row>
     <row r="924">
@@ -41083,7 +41083,7 @@
         </is>
       </c>
       <c r="J928" t="n">
-        <v>663</v>
+        <v>596</v>
       </c>
       <c r="K928" t="n">
         <v>0</v>
@@ -41092,19 +41092,19 @@
         <v>0</v>
       </c>
       <c r="M928" t="n">
-        <v>663</v>
+        <v>596</v>
       </c>
       <c r="N928" t="n">
-        <v>3110.8418772978</v>
+        <v>3110.8416960301</v>
       </c>
       <c r="O928" t="n">
-        <v>2062488.164648441</v>
+        <v>1854061.65083394</v>
       </c>
       <c r="P928" t="n">
         <v>4500</v>
       </c>
       <c r="Q928" t="n">
-        <v>2983500</v>
+        <v>2682000</v>
       </c>
     </row>
     <row r="929">
@@ -41217,7 +41217,7 @@
         </is>
       </c>
       <c r="J931" t="n">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="K931" t="n">
         <v>0</v>
@@ -41226,19 +41226,19 @@
         <v>0</v>
       </c>
       <c r="M931" t="n">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="N931" t="n">
         <v>2030.02</v>
       </c>
       <c r="O931" t="n">
-        <v>1019070.04</v>
+        <v>964259.5</v>
       </c>
       <c r="P931" t="n">
         <v>3600</v>
       </c>
       <c r="Q931" t="n">
-        <v>1807200</v>
+        <v>1710000</v>
       </c>
     </row>
     <row r="932">
@@ -41273,10 +41273,10 @@
         <v>35</v>
       </c>
       <c r="N932" t="n">
-        <v>2973.0438002774</v>
+        <v>2973.0438055556</v>
       </c>
       <c r="O932" t="n">
-        <v>104056.533009709</v>
+        <v>104056.533194446</v>
       </c>
       <c r="P932" t="n">
         <v>4500</v>
@@ -41305,7 +41305,7 @@
         </is>
       </c>
       <c r="J933" t="n">
-        <v>1145</v>
+        <v>1089</v>
       </c>
       <c r="K933" t="n">
         <v>0</v>
@@ -41314,19 +41314,19 @@
         <v>0</v>
       </c>
       <c r="M933" t="n">
-        <v>1145</v>
+        <v>1089</v>
       </c>
       <c r="N933" t="n">
-        <v>703.79518726322</v>
+        <v>703.79518287415</v>
       </c>
       <c r="O933" t="n">
-        <v>805845.4894163869</v>
+        <v>766432.9541499494</v>
       </c>
       <c r="P933" t="n">
         <v>900</v>
       </c>
       <c r="Q933" t="n">
-        <v>1030500</v>
+        <v>980100</v>
       </c>
     </row>
     <row r="934">
@@ -42158,10 +42158,10 @@
         <v>23</v>
       </c>
       <c r="N952" t="n">
-        <v>3629.7161041667</v>
+        <v>3629.7160714286</v>
       </c>
       <c r="O952" t="n">
-        <v>83483.4703958341</v>
+        <v>83483.4696428578</v>
       </c>
       <c r="P952" t="n">
         <v>4900</v>
@@ -42374,10 +42374,10 @@
         <v>63</v>
       </c>
       <c r="N957" t="n">
-        <v>1595.5128965225</v>
+        <v>1595.5127943686</v>
       </c>
       <c r="O957" t="n">
-        <v>100517.3124809175</v>
+        <v>100517.3060452218</v>
       </c>
       <c r="P957" t="n">
         <v>2500</v>
@@ -43561,10 +43561,10 @@
         <v>16</v>
       </c>
       <c r="N982" t="n">
-        <v>3414.566049961</v>
+        <v>3414.5660344828</v>
       </c>
       <c r="O982" t="n">
-        <v>54633.056799376</v>
+        <v>54633.0565517248</v>
       </c>
       <c r="P982" t="n">
         <v>3500</v>
@@ -44064,10 +44064,10 @@
         <v>43</v>
       </c>
       <c r="N993" t="n">
-        <v>3979.1707142857</v>
+        <v>3979.1707189542</v>
       </c>
       <c r="O993" t="n">
-        <v>171104.3407142851</v>
+        <v>171104.3409150306</v>
       </c>
       <c r="P993" t="n">
         <v>5300</v>
@@ -44428,7 +44428,7 @@
         </is>
       </c>
       <c r="J1001" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K1001" t="n">
         <v>0</v>
@@ -44437,19 +44437,19 @@
         <v>0</v>
       </c>
       <c r="M1001" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N1001" t="n">
         <v>6529.54</v>
       </c>
       <c r="O1001" t="n">
-        <v>58765.86</v>
+        <v>52236.32</v>
       </c>
       <c r="P1001" t="n">
         <v>45000</v>
       </c>
       <c r="Q1001" t="n">
-        <v>405000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="1002">
@@ -44897,7 +44897,7 @@
         </is>
       </c>
       <c r="J1011" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K1011" t="n">
         <v>0</v>
@@ -44906,19 +44906,19 @@
         <v>0</v>
       </c>
       <c r="M1011" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N1011" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1011" t="n">
-        <v>2312154.65</v>
+        <v>2287816.18</v>
       </c>
       <c r="P1011" t="n">
         <v>27900</v>
       </c>
       <c r="Q1011" t="n">
-        <v>2650500</v>
+        <v>2622600</v>
       </c>
     </row>
     <row r="1012">
@@ -45967,10 +45967,10 @@
         <v>291</v>
       </c>
       <c r="N1034" t="n">
-        <v>2703.2000014447</v>
+        <v>2703.2000014448</v>
       </c>
       <c r="O1034" t="n">
-        <v>786631.2004204077</v>
+        <v>786631.2004204368</v>
       </c>
       <c r="P1034" t="n">
         <v>4500</v>
@@ -46433,10 +46433,10 @@
         <v>139</v>
       </c>
       <c r="N1045" t="n">
-        <v>4282.1072467371</v>
+        <v>4282.1072450249</v>
       </c>
       <c r="O1045" t="n">
-        <v>595212.9072964569</v>
+        <v>595212.9070584611</v>
       </c>
       <c r="P1045" t="n">
         <v>5300</v>
@@ -46474,10 +46474,10 @@
         <v>51</v>
       </c>
       <c r="N1046" t="n">
-        <v>5577.2680465116</v>
+        <v>5577.2680373832</v>
       </c>
       <c r="O1046" t="n">
-        <v>284440.6703720916</v>
+        <v>284440.6699065432</v>
       </c>
       <c r="P1046" t="n">
         <v>6500</v>
@@ -46518,10 +46518,10 @@
         <v>41</v>
       </c>
       <c r="N1047" t="n">
-        <v>6243.3531578947</v>
+        <v>6243.3531884058</v>
       </c>
       <c r="O1047" t="n">
-        <v>255977.4794736827</v>
+        <v>255977.4807246378</v>
       </c>
       <c r="P1047" t="n">
         <v>9900</v>
@@ -47077,10 +47077,10 @@
         <v>42</v>
       </c>
       <c r="N1060" t="n">
-        <v>2129.8331627057</v>
+        <v>2129.8331714024</v>
       </c>
       <c r="O1060" t="n">
-        <v>89452.99283363941</v>
+        <v>89452.99319890079</v>
       </c>
       <c r="P1060" t="n">
         <v>2700</v>
@@ -47121,10 +47121,10 @@
         <v>20</v>
       </c>
       <c r="N1061" t="n">
-        <v>2106.9511305147</v>
+        <v>2106.9511336406</v>
       </c>
       <c r="O1061" t="n">
-        <v>42139.02261029399</v>
+        <v>42139.022672812</v>
       </c>
       <c r="P1061" t="n">
         <v>2700</v>
@@ -47370,7 +47370,7 @@
         </is>
       </c>
       <c r="J1067" t="n">
-        <v>7</v>
+        <v>131</v>
       </c>
       <c r="K1067" t="n">
         <v>0</v>
@@ -47379,19 +47379,19 @@
         <v>0</v>
       </c>
       <c r="M1067" t="n">
-        <v>7</v>
+        <v>131</v>
       </c>
       <c r="N1067" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1067" t="n">
-        <v>8235.99</v>
+        <v>154130.67</v>
       </c>
       <c r="P1067" t="n">
         <v>1900</v>
       </c>
       <c r="Q1067" t="n">
-        <v>13300</v>
+        <v>248900</v>
       </c>
     </row>
     <row r="1068">
@@ -47414,7 +47414,7 @@
         </is>
       </c>
       <c r="J1068" t="n">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="K1068" t="n">
         <v>0</v>
@@ -47423,19 +47423,19 @@
         <v>0</v>
       </c>
       <c r="M1068" t="n">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="N1068" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1068" t="n">
-        <v>1072300.3</v>
+        <v>999116.6</v>
       </c>
       <c r="P1068" t="n">
         <v>5100</v>
       </c>
       <c r="Q1068" t="n">
-        <v>1718700</v>
+        <v>1601400</v>
       </c>
     </row>
     <row r="1069">
@@ -47552,10 +47552,10 @@
         <v>175</v>
       </c>
       <c r="N1071" t="n">
-        <v>1794.2879721384</v>
+        <v>1794.2879692219</v>
       </c>
       <c r="O1071" t="n">
-        <v>314000.39512422</v>
+        <v>314000.3946138325</v>
       </c>
       <c r="P1071" t="n">
         <v>1600</v>
@@ -47596,10 +47596,10 @@
         <v>277</v>
       </c>
       <c r="N1072" t="n">
-        <v>2181.4248974943</v>
+        <v>2181.4247785548</v>
       </c>
       <c r="O1072" t="n">
-        <v>604254.696605921</v>
+        <v>604254.6636596796</v>
       </c>
       <c r="P1072" t="n">
         <v>2900</v>
@@ -47640,10 +47640,10 @@
         <v>54</v>
       </c>
       <c r="N1073" t="n">
-        <v>2077.2846666667</v>
+        <v>2077.2842857143</v>
       </c>
       <c r="O1073" t="n">
-        <v>112173.3720000018</v>
+        <v>112173.3514285722</v>
       </c>
       <c r="P1073" t="n">
         <v>2900</v>
@@ -48568,7 +48568,7 @@
         </is>
       </c>
       <c r="J1095" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K1095" t="n">
         <v>0</v>
@@ -48577,19 +48577,19 @@
         <v>0</v>
       </c>
       <c r="M1095" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N1095" t="n">
         <v>5077</v>
       </c>
       <c r="O1095" t="n">
-        <v>619394</v>
+        <v>604163</v>
       </c>
       <c r="P1095" t="n">
         <v>8500</v>
       </c>
       <c r="Q1095" t="n">
-        <v>1037000</v>
+        <v>1011500</v>
       </c>
     </row>
     <row r="1096">
@@ -49468,7 +49468,7 @@
         </is>
       </c>
       <c r="J1115" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K1115" t="n">
         <v>0</v>
@@ -49477,19 +49477,19 @@
         <v>0</v>
       </c>
       <c r="M1115" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N1115" t="n">
         <v>7480</v>
       </c>
       <c r="O1115" t="n">
-        <v>261800</v>
+        <v>149600</v>
       </c>
       <c r="P1115" t="n">
         <v>9500</v>
       </c>
       <c r="Q1115" t="n">
-        <v>332500</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="1116">
@@ -49514,7 +49514,7 @@
         </is>
       </c>
       <c r="J1116" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="K1116" t="n">
         <v>0</v>
@@ -49523,19 +49523,19 @@
         <v>0</v>
       </c>
       <c r="M1116" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="N1116" t="n">
         <v>6336</v>
       </c>
       <c r="O1116" t="n">
-        <v>912384</v>
+        <v>849024</v>
       </c>
       <c r="P1116" t="n">
         <v>7500</v>
       </c>
       <c r="Q1116" t="n">
-        <v>1080000</v>
+        <v>1005000</v>
       </c>
     </row>
     <row r="1117">
@@ -49652,7 +49652,7 @@
         </is>
       </c>
       <c r="J1119" t="n">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="K1119" t="n">
         <v>0</v>
@@ -49661,19 +49661,19 @@
         <v>0</v>
       </c>
       <c r="M1119" t="n">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="N1119" t="n">
         <v>1584</v>
       </c>
       <c r="O1119" t="n">
-        <v>456192</v>
+        <v>408672</v>
       </c>
       <c r="P1119" t="n">
         <v>2000</v>
       </c>
       <c r="Q1119" t="n">
-        <v>576000</v>
+        <v>516000</v>
       </c>
     </row>
     <row r="1120">
@@ -49744,7 +49744,7 @@
         </is>
       </c>
       <c r="J1121" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="K1121" t="n">
         <v>0</v>
@@ -49753,19 +49753,19 @@
         <v>0</v>
       </c>
       <c r="M1121" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="N1121" t="n">
         <v>6160</v>
       </c>
       <c r="O1121" t="n">
-        <v>517440</v>
+        <v>406560</v>
       </c>
       <c r="P1121" t="n">
         <v>7900</v>
       </c>
       <c r="Q1121" t="n">
-        <v>663600</v>
+        <v>521400</v>
       </c>
     </row>
     <row r="1122">
@@ -49790,7 +49790,7 @@
         </is>
       </c>
       <c r="J1122" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="K1122" t="n">
         <v>0</v>
@@ -49799,19 +49799,19 @@
         <v>0</v>
       </c>
       <c r="M1122" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="N1122" t="n">
         <v>4400</v>
       </c>
       <c r="O1122" t="n">
-        <v>726000</v>
+        <v>638000</v>
       </c>
       <c r="P1122" t="n">
         <v>5900</v>
       </c>
       <c r="Q1122" t="n">
-        <v>973500</v>
+        <v>855500</v>
       </c>
     </row>
     <row r="1123">
@@ -49836,7 +49836,7 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
@@ -49845,19 +49845,19 @@
         <v>0</v>
       </c>
       <c r="M1123" t="n">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="N1123" t="n">
         <v>3520</v>
       </c>
       <c r="O1123" t="n">
-        <v>696960</v>
+        <v>658240</v>
       </c>
       <c r="P1123" t="n">
         <v>4500</v>
       </c>
       <c r="Q1123" t="n">
-        <v>891000</v>
+        <v>841500</v>
       </c>
     </row>
     <row r="1124">
@@ -49974,7 +49974,7 @@
         </is>
       </c>
       <c r="J1126" t="n">
-        <v>597</v>
+        <v>529</v>
       </c>
       <c r="K1126" t="n">
         <v>0</v>
@@ -49983,19 +49983,19 @@
         <v>0</v>
       </c>
       <c r="M1126" t="n">
-        <v>597</v>
+        <v>529</v>
       </c>
       <c r="N1126" t="n">
         <v>9240</v>
       </c>
       <c r="O1126" t="n">
-        <v>5516280</v>
+        <v>4887960</v>
       </c>
       <c r="P1126" t="n">
         <v>11500</v>
       </c>
       <c r="Q1126" t="n">
-        <v>6865500</v>
+        <v>6083500</v>
       </c>
     </row>
     <row r="1127">
@@ -50020,7 +50020,7 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
@@ -50029,19 +50029,19 @@
         <v>0</v>
       </c>
       <c r="M1127" t="n">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="N1127" t="n">
         <v>2288</v>
       </c>
       <c r="O1127" t="n">
-        <v>1317888</v>
+        <v>1285856</v>
       </c>
       <c r="P1127" t="n">
         <v>2900</v>
       </c>
       <c r="Q1127" t="n">
-        <v>1670400</v>
+        <v>1629800</v>
       </c>
     </row>
     <row r="1128">
@@ -50066,7 +50066,7 @@
         </is>
       </c>
       <c r="J1128" t="n">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="K1128" t="n">
         <v>0</v>
@@ -50075,19 +50075,19 @@
         <v>0</v>
       </c>
       <c r="M1128" t="n">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="N1128" t="n">
         <v>4576</v>
       </c>
       <c r="O1128" t="n">
-        <v>883168</v>
+        <v>841984</v>
       </c>
       <c r="P1128" t="n">
         <v>5900</v>
       </c>
       <c r="Q1128" t="n">
-        <v>1138700</v>
+        <v>1085600</v>
       </c>
     </row>
     <row r="1129">
@@ -51032,7 +51032,7 @@
         </is>
       </c>
       <c r="J1149" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K1149" t="n">
         <v>0</v>
@@ -51041,19 +51041,19 @@
         <v>0</v>
       </c>
       <c r="M1149" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N1149" t="n">
         <v>6000</v>
       </c>
       <c r="O1149" t="n">
-        <v>96000</v>
+        <v>90000</v>
       </c>
       <c r="P1149" t="n">
         <v>7200</v>
       </c>
       <c r="Q1149" t="n">
-        <v>115200</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="1150">
@@ -51395,7 +51395,7 @@
         </is>
       </c>
       <c r="J1157" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K1157" t="n">
         <v>0</v>
@@ -51404,19 +51404,19 @@
         <v>0</v>
       </c>
       <c r="M1157" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N1157" t="n">
         <v>576.58</v>
       </c>
       <c r="O1157" t="n">
-        <v>12108.18</v>
+        <v>10955.02</v>
       </c>
       <c r="P1157" t="n">
         <v>5900</v>
       </c>
       <c r="Q1157" t="n">
-        <v>123900</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="1158">
@@ -52576,7 +52576,7 @@
         </is>
       </c>
       <c r="J1183" t="n">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="K1183" t="n">
         <v>0</v>
@@ -52585,19 +52585,19 @@
         <v>0</v>
       </c>
       <c r="M1183" t="n">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="N1183" t="n">
         <v>4550</v>
       </c>
       <c r="O1183" t="n">
-        <v>1360450</v>
+        <v>1314950</v>
       </c>
       <c r="P1183" t="n">
         <v>5500</v>
       </c>
       <c r="Q1183" t="n">
-        <v>1644500</v>
+        <v>1589500</v>
       </c>
     </row>
     <row r="1184">
@@ -52941,10 +52941,10 @@
         <v>44</v>
       </c>
       <c r="N1191" t="n">
-        <v>2403.9772463768</v>
+        <v>2403.9772262774</v>
       </c>
       <c r="O1191" t="n">
-        <v>105774.9988405792</v>
+        <v>105774.9979562056</v>
       </c>
       <c r="P1191" t="n">
         <v>3000</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1004,25 +1004,25 @@
         <v>21</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="N15" t="n">
         <v>27000</v>
       </c>
       <c r="O15" t="n">
-        <v>567000</v>
+        <v>891000</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
       </c>
       <c r="Q15" t="n">
-        <v>420000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="16">
@@ -1307,10 +1307,10 @@
         <v>330</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.3069785884</v>
+        <v>1811.307219032</v>
       </c>
       <c r="O22" t="n">
-        <v>597731.302934172</v>
+        <v>597731.38228056</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
@@ -1424,10 +1424,10 @@
         <v>152</v>
       </c>
       <c r="N25" t="n">
-        <v>3376.7464699454</v>
+        <v>3376.7464660832</v>
       </c>
       <c r="O25" t="n">
-        <v>513265.4634317008</v>
+        <v>513265.4628446464</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
@@ -2015,10 +2015,10 @@
         <v>13</v>
       </c>
       <c r="N40" t="n">
-        <v>20826.677297297</v>
+        <v>20826.6775</v>
       </c>
       <c r="O40" t="n">
-        <v>270746.804864861</v>
+        <v>270746.8075</v>
       </c>
       <c r="P40" t="n">
         <v>39100</v>
@@ -4134,10 +4134,10 @@
         <v>53</v>
       </c>
       <c r="N92" t="n">
-        <v>3910.6281595092</v>
+        <v>3910.6281481481</v>
       </c>
       <c r="O92" t="n">
-        <v>207263.2924539876</v>
+        <v>207263.2918518493</v>
       </c>
       <c r="P92" t="n">
         <v>9100</v>
@@ -7077,10 +7077,10 @@
         <v>7</v>
       </c>
       <c r="N160" t="n">
-        <v>61666.874070081</v>
+        <v>61666.874081081</v>
       </c>
       <c r="O160" t="n">
-        <v>431668.118490567</v>
+        <v>431668.118567567</v>
       </c>
       <c r="P160" t="n">
         <v>98900</v>
@@ -10295,10 +10295,10 @@
         <v>505</v>
       </c>
       <c r="N234" t="n">
-        <v>1098.0593600211</v>
+        <v>1098.059452236</v>
       </c>
       <c r="O234" t="n">
-        <v>554519.9768106556</v>
+        <v>554520.02337918</v>
       </c>
       <c r="P234" t="n">
         <v>1500</v>
@@ -12102,10 +12102,10 @@
         <v>202</v>
       </c>
       <c r="N276" t="n">
-        <v>2582.2557508532</v>
+        <v>2582.2557353886</v>
       </c>
       <c r="O276" t="n">
-        <v>521615.6616723464</v>
+        <v>521615.6585484972</v>
       </c>
       <c r="P276" t="n">
         <v>4500</v>
@@ -12139,25 +12139,25 @@
         <v>62</v>
       </c>
       <c r="K277" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="N277" t="n">
         <v>10600</v>
       </c>
       <c r="O277" t="n">
-        <v>657200</v>
+        <v>1717200</v>
       </c>
       <c r="P277" t="n">
         <v>17200</v>
       </c>
       <c r="Q277" t="n">
-        <v>1066400</v>
+        <v>2786400</v>
       </c>
     </row>
     <row r="278">
@@ -12185,25 +12185,25 @@
         <v>66</v>
       </c>
       <c r="K278" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>66</v>
+        <v>154</v>
       </c>
       <c r="N278" t="n">
-        <v>5216.8961296772</v>
+        <v>5216.8961258041</v>
       </c>
       <c r="O278" t="n">
-        <v>344315.1445586952</v>
+        <v>803402.0033738314</v>
       </c>
       <c r="P278" t="n">
         <v>8500</v>
       </c>
       <c r="Q278" t="n">
-        <v>561000</v>
+        <v>1309000</v>
       </c>
     </row>
     <row r="279">
@@ -12765,10 +12765,10 @@
         <v>70</v>
       </c>
       <c r="N291" t="n">
-        <v>3230.0672564612</v>
+        <v>3230.067250996</v>
       </c>
       <c r="O291" t="n">
-        <v>226104.707952284</v>
+        <v>226104.70756972</v>
       </c>
       <c r="P291" t="n">
         <v>6200</v>
@@ -12846,22 +12846,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M293" t="n">
-        <v>908</v>
+        <v>872</v>
       </c>
       <c r="N293" t="n">
         <v>1480</v>
       </c>
       <c r="O293" t="n">
-        <v>1343840</v>
+        <v>1290560</v>
       </c>
       <c r="P293" t="n">
         <v>2600</v>
       </c>
       <c r="Q293" t="n">
-        <v>2360800</v>
+        <v>2267200</v>
       </c>
     </row>
     <row r="294">
@@ -13071,22 +13071,22 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M298" t="n">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="N298" t="n">
         <v>1026.13</v>
       </c>
       <c r="O298" t="n">
-        <v>469967.54</v>
+        <v>408399.74</v>
       </c>
       <c r="P298" t="n">
         <v>1900</v>
       </c>
       <c r="Q298" t="n">
-        <v>870200</v>
+        <v>756200</v>
       </c>
     </row>
     <row r="299">
@@ -13163,22 +13163,22 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M300" t="n">
-        <v>4085</v>
+        <v>4075</v>
       </c>
       <c r="N300" t="n">
         <v>156.25</v>
       </c>
       <c r="O300" t="n">
-        <v>638281.25</v>
+        <v>636718.75</v>
       </c>
       <c r="P300" t="n">
         <v>250</v>
       </c>
       <c r="Q300" t="n">
-        <v>1021250</v>
+        <v>1018750</v>
       </c>
     </row>
     <row r="301">
@@ -13446,10 +13446,10 @@
         <v>287</v>
       </c>
       <c r="N306" t="n">
-        <v>3795.7100075514</v>
+        <v>3795.7100075529</v>
       </c>
       <c r="O306" t="n">
-        <v>1089368.772167252</v>
+        <v>1089368.772167682</v>
       </c>
       <c r="P306" t="n">
         <v>6200</v>
@@ -13712,10 +13712,10 @@
         <v>34</v>
       </c>
       <c r="N312" t="n">
-        <v>4890.9300486322</v>
+        <v>4890.9300487805</v>
       </c>
       <c r="O312" t="n">
-        <v>166291.6216534948</v>
+        <v>166291.621658537</v>
       </c>
       <c r="P312" t="n">
         <v>8200</v>
@@ -13758,10 +13758,10 @@
         <v>72</v>
       </c>
       <c r="N313" t="n">
-        <v>5484.9492105263</v>
+        <v>5484.9500917431</v>
       </c>
       <c r="O313" t="n">
-        <v>394916.3431578936</v>
+        <v>394916.4066055032</v>
       </c>
       <c r="P313" t="n">
         <v>8500</v>
@@ -14032,10 +14032,10 @@
         <v>1571</v>
       </c>
       <c r="N319" t="n">
-        <v>2267.0481451951</v>
+        <v>2267.0481436371</v>
       </c>
       <c r="O319" t="n">
-        <v>3561532.636101502</v>
+        <v>3561532.633653884</v>
       </c>
       <c r="P319" t="n">
         <v>3900</v>
@@ -14761,22 +14761,22 @@
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M336" t="n">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="N336" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.8500369004</v>
       </c>
       <c r="O336" t="n">
-        <v>651410.8565472333</v>
+        <v>418069.6547601516</v>
       </c>
       <c r="P336" t="n">
         <v>5200</v>
       </c>
       <c r="Q336" t="n">
-        <v>1045200</v>
+        <v>670800</v>
       </c>
     </row>
     <row r="337">
@@ -14905,10 +14905,10 @@
         <v>55</v>
       </c>
       <c r="N339" t="n">
-        <v>14822.378850987</v>
+        <v>14822.378849611</v>
       </c>
       <c r="O339" t="n">
-        <v>815230.8368042849</v>
+        <v>815230.836728605</v>
       </c>
       <c r="P339" t="n">
         <v>24900</v>
@@ -15524,10 +15524,10 @@
         <v>426</v>
       </c>
       <c r="N353" t="n">
-        <v>3041.6600131579</v>
+        <v>3041.660013245</v>
       </c>
       <c r="O353" t="n">
-        <v>1295747.165605265</v>
+        <v>1295747.16564237</v>
       </c>
       <c r="P353" t="n">
         <v>5500</v>
@@ -15611,10 +15611,10 @@
         <v>206</v>
       </c>
       <c r="N355" t="n">
-        <v>4372.2107896237</v>
+        <v>4372.2107901305</v>
       </c>
       <c r="O355" t="n">
-        <v>900675.4226624822</v>
+        <v>900675.4227668829</v>
       </c>
       <c r="P355" t="n">
         <v>7500</v>
@@ -15701,10 +15701,10 @@
         <v>2</v>
       </c>
       <c r="N357" t="n">
-        <v>1592.5668693558</v>
+        <v>1592.5667761934</v>
       </c>
       <c r="O357" t="n">
-        <v>3185.1337387116</v>
+        <v>3185.1335523868</v>
       </c>
       <c r="P357" t="n">
         <v>3900</v>
@@ -15820,25 +15820,25 @@
         <v>29</v>
       </c>
       <c r="K360" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="L360" t="n">
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="N360" t="n">
         <v>3655.96</v>
       </c>
       <c r="O360" t="n">
-        <v>106022.84</v>
+        <v>720224.12</v>
       </c>
       <c r="P360" t="n">
         <v>5500</v>
       </c>
       <c r="Q360" t="n">
-        <v>159500</v>
+        <v>1083500</v>
       </c>
     </row>
     <row r="361">
@@ -16657,22 +16657,22 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M379" t="n">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="N379" t="n">
         <v>1647.46</v>
       </c>
       <c r="O379" t="n">
-        <v>527187.2</v>
+        <v>497532.92</v>
       </c>
       <c r="P379" t="n">
         <v>2900</v>
       </c>
       <c r="Q379" t="n">
-        <v>928000</v>
+        <v>875800</v>
       </c>
     </row>
     <row r="380">
@@ -16745,22 +16745,22 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M381" t="n">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="N381" t="n">
         <v>1387.55</v>
       </c>
       <c r="O381" t="n">
-        <v>588321.2</v>
+        <v>555020</v>
       </c>
       <c r="P381" t="n">
         <v>2300</v>
       </c>
       <c r="Q381" t="n">
-        <v>975200</v>
+        <v>920000</v>
       </c>
     </row>
     <row r="382">
@@ -17501,10 +17501,10 @@
         <v>12</v>
       </c>
       <c r="N398" t="n">
-        <v>8296.642647058799</v>
+        <v>8296.6427272727</v>
       </c>
       <c r="O398" t="n">
-        <v>99559.7117647056</v>
+        <v>99559.71272727239</v>
       </c>
       <c r="P398" t="n">
         <v>15900</v>
@@ -17762,22 +17762,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M404" t="n">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="N404" t="n">
-        <v>1630.9235742505</v>
+        <v>1630.9236077879</v>
       </c>
       <c r="O404" t="n">
-        <v>919840.895877282</v>
+        <v>880698.748205466</v>
       </c>
       <c r="P404" t="n">
         <v>2500</v>
       </c>
       <c r="Q404" t="n">
-        <v>1410000</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="405">
@@ -17901,10 +17901,10 @@
         <v>156</v>
       </c>
       <c r="N407" t="n">
-        <v>1690.5974723655</v>
+        <v>1690.5973219585</v>
       </c>
       <c r="O407" t="n">
-        <v>263733.205689018</v>
+        <v>263733.182225526</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
@@ -17941,22 +17941,22 @@
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M408" t="n">
-        <v>1371</v>
+        <v>1347</v>
       </c>
       <c r="N408" t="n">
-        <v>1550.1936350279</v>
+        <v>1550.1936746212</v>
       </c>
       <c r="O408" t="n">
-        <v>2125315.473623251</v>
+        <v>2088110.879714756</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
       </c>
       <c r="Q408" t="n">
-        <v>3427500</v>
+        <v>3367500</v>
       </c>
     </row>
     <row r="409">
@@ -17993,10 +17993,10 @@
         <v>3</v>
       </c>
       <c r="N409" t="n">
-        <v>1579.3906753247</v>
+        <v>1579.3905526316</v>
       </c>
       <c r="O409" t="n">
-        <v>4738.1720259741</v>
+        <v>4738.1716578948</v>
       </c>
       <c r="P409" t="n">
         <v>2900</v>
@@ -18039,10 +18039,10 @@
         <v>835</v>
       </c>
       <c r="N410" t="n">
-        <v>2403.5118666412</v>
+        <v>2403.5119649393</v>
       </c>
       <c r="O410" t="n">
-        <v>2006932.408645402</v>
+        <v>2006932.490724315</v>
       </c>
       <c r="P410" t="n">
         <v>3500</v>
@@ -19349,22 +19349,22 @@
         <v>0</v>
       </c>
       <c r="L440" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M440" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="N440" t="n">
         <v>3253</v>
       </c>
       <c r="O440" t="n">
-        <v>357830</v>
+        <v>123614</v>
       </c>
       <c r="P440" t="n">
         <v>3900</v>
       </c>
       <c r="Q440" t="n">
-        <v>429000</v>
+        <v>148200</v>
       </c>
     </row>
     <row r="441">
@@ -19741,22 +19741,22 @@
         <v>0</v>
       </c>
       <c r="L449" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M449" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N449" t="n">
         <v>3253</v>
       </c>
       <c r="O449" t="n">
-        <v>146385</v>
+        <v>0</v>
       </c>
       <c r="P449" t="n">
         <v>3900</v>
       </c>
       <c r="Q449" t="n">
-        <v>175500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450">
@@ -21601,22 +21601,22 @@
         <v>0</v>
       </c>
       <c r="L493" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M493" t="n">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="N493" t="n">
         <v>2567</v>
       </c>
       <c r="O493" t="n">
-        <v>649451</v>
+        <v>587843</v>
       </c>
       <c r="P493" t="n">
         <v>4500</v>
       </c>
       <c r="Q493" t="n">
-        <v>1138500</v>
+        <v>1030500</v>
       </c>
     </row>
     <row r="494">
@@ -21970,22 +21970,22 @@
         <v>0</v>
       </c>
       <c r="L502" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M502" t="n">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="N502" t="n">
-        <v>2029.8737669513</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O502" t="n">
-        <v>935771.8065645493</v>
+        <v>887054.8768245011</v>
       </c>
       <c r="P502" t="n">
         <v>3600</v>
       </c>
       <c r="Q502" t="n">
-        <v>1659600</v>
+        <v>1573200</v>
       </c>
     </row>
     <row r="503">
@@ -22558,10 +22558,10 @@
         <v>169</v>
       </c>
       <c r="N516" t="n">
-        <v>2680.7396995708</v>
+        <v>2680.739699202</v>
       </c>
       <c r="O516" t="n">
-        <v>453045.0092274652</v>
+        <v>453045.009165138</v>
       </c>
       <c r="P516" t="n">
         <v>4900</v>
@@ -23585,10 +23585,10 @@
         <v>278</v>
       </c>
       <c r="N540" t="n">
-        <v>4285.1954859611</v>
+        <v>4285.1954978355</v>
       </c>
       <c r="O540" t="n">
-        <v>1191284.345097186</v>
+        <v>1191284.348398269</v>
       </c>
       <c r="P540" t="n">
         <v>6900</v>
@@ -24397,10 +24397,10 @@
         <v>50</v>
       </c>
       <c r="N559" t="n">
-        <v>11562.038478261</v>
+        <v>11562.038474114</v>
       </c>
       <c r="O559" t="n">
-        <v>578101.92391305</v>
+        <v>578101.9237057001</v>
       </c>
       <c r="P559" t="n">
         <v>18500</v>
@@ -24443,10 +24443,10 @@
         <v>58</v>
       </c>
       <c r="N560" t="n">
-        <v>13513.643014706</v>
+        <v>13513.643059701</v>
       </c>
       <c r="O560" t="n">
-        <v>783791.294852948</v>
+        <v>783791.297462658</v>
       </c>
       <c r="P560" t="n">
         <v>21900</v>
@@ -25784,10 +25784,10 @@
         <v>40</v>
       </c>
       <c r="N591" t="n">
-        <v>27123.765223881</v>
+        <v>27123.765205993</v>
       </c>
       <c r="O591" t="n">
-        <v>1084950.60895524</v>
+        <v>1084950.60823972</v>
       </c>
       <c r="P591" t="n">
         <v>44500</v>
@@ -26214,10 +26214,10 @@
         <v>68</v>
       </c>
       <c r="N601" t="n">
-        <v>1561.0002330508</v>
+        <v>1561.0003094984</v>
       </c>
       <c r="O601" t="n">
-        <v>106148.0158474544</v>
+        <v>106148.0210458912</v>
       </c>
       <c r="P601" t="n">
         <v>2900</v>
@@ -26483,10 +26483,10 @@
         <v>131</v>
       </c>
       <c r="N607" t="n">
-        <v>7969.9501669196</v>
+        <v>7969.9501671733</v>
       </c>
       <c r="O607" t="n">
-        <v>1044063.471866468</v>
+        <v>1044063.471899702</v>
       </c>
       <c r="P607" t="n">
         <v>12900</v>
@@ -28304,10 +28304,10 @@
         <v>20</v>
       </c>
       <c r="N649" t="n">
-        <v>5218.1705520703</v>
+        <v>5218.1705541562</v>
       </c>
       <c r="O649" t="n">
-        <v>104363.411041406</v>
+        <v>104363.411083124</v>
       </c>
       <c r="P649" t="n">
         <v>8500</v>
@@ -28350,10 +28350,10 @@
         <v>133</v>
       </c>
       <c r="N650" t="n">
-        <v>1595.009375</v>
+        <v>1595.0093687708</v>
       </c>
       <c r="O650" t="n">
-        <v>212136.246875</v>
+        <v>212136.2460465164</v>
       </c>
       <c r="P650" t="n">
         <v>2600</v>
@@ -28396,10 +28396,10 @@
         <v>75</v>
       </c>
       <c r="N651" t="n">
-        <v>3610.6500258065</v>
+        <v>3610.6500258732</v>
       </c>
       <c r="O651" t="n">
-        <v>270798.7519354875</v>
+        <v>270798.75194049</v>
       </c>
       <c r="P651" t="n">
         <v>5800</v>
@@ -28810,10 +28810,10 @@
         <v>251</v>
       </c>
       <c r="N660" t="n">
-        <v>1664.355973236</v>
+        <v>1664.355782984</v>
       </c>
       <c r="O660" t="n">
-        <v>417753.349282236</v>
+        <v>417753.301528984</v>
       </c>
       <c r="P660" t="n">
         <v>2900</v>
@@ -29454,22 +29454,22 @@
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M674" t="n">
-        <v>1400</v>
+        <v>1376</v>
       </c>
       <c r="N674" t="n">
-        <v>1778.4726251691</v>
+        <v>1778.4726394558</v>
       </c>
       <c r="O674" t="n">
-        <v>2489861.67523674</v>
+        <v>2447178.351891181</v>
       </c>
       <c r="P674" t="n">
         <v>4900</v>
       </c>
       <c r="Q674" t="n">
-        <v>6860000</v>
+        <v>6742400</v>
       </c>
     </row>
     <row r="675">
@@ -29500,22 +29500,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M675" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="N675" t="n">
         <v>1548</v>
       </c>
       <c r="O675" t="n">
-        <v>309600</v>
+        <v>272448</v>
       </c>
       <c r="P675" t="n">
         <v>3900</v>
       </c>
       <c r="Q675" t="n">
-        <v>780000</v>
+        <v>686400</v>
       </c>
     </row>
     <row r="676">
@@ -32270,10 +32270,10 @@
         <v>684</v>
       </c>
       <c r="N735" t="n">
-        <v>2328.1187161545</v>
+        <v>2328.1187114504</v>
       </c>
       <c r="O735" t="n">
-        <v>1592433.201849678</v>
+        <v>1592433.198632074</v>
       </c>
       <c r="P735" t="n">
         <v>4500</v>
@@ -33328,10 +33328,10 @@
         <v>137</v>
       </c>
       <c r="N758" t="n">
-        <v>3903.7365705615</v>
+        <v>3903.736684492</v>
       </c>
       <c r="O758" t="n">
-        <v>534811.9101669255</v>
+        <v>534811.9257754041</v>
       </c>
       <c r="P758" t="n">
         <v>7500</v>
@@ -34936,10 +34936,10 @@
         <v>171</v>
       </c>
       <c r="N793" t="n">
-        <v>17075.989523481</v>
+        <v>17075.989523151</v>
       </c>
       <c r="O793" t="n">
-        <v>2919994.208515251</v>
+        <v>2919994.208458821</v>
       </c>
       <c r="P793" t="n">
         <v>27500</v>
@@ -36587,22 +36587,22 @@
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M829" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N829" t="n">
         <v>38252</v>
       </c>
       <c r="O829" t="n">
-        <v>726788</v>
+        <v>688536</v>
       </c>
       <c r="P829" t="n">
         <v>61900</v>
       </c>
       <c r="Q829" t="n">
-        <v>1176100</v>
+        <v>1114200</v>
       </c>
     </row>
     <row r="830">
@@ -36633,22 +36633,22 @@
         <v>0</v>
       </c>
       <c r="L830" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M830" t="n">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="N830" t="n">
-        <v>1516.0387986728</v>
+        <v>1516.0387953812</v>
       </c>
       <c r="O830" t="n">
-        <v>900527.0464116433</v>
+        <v>864142.1133672841</v>
       </c>
       <c r="P830" t="n">
         <v>2300</v>
       </c>
       <c r="Q830" t="n">
-        <v>1366200</v>
+        <v>1311000</v>
       </c>
     </row>
     <row r="831">
@@ -36769,22 +36769,22 @@
         <v>0</v>
       </c>
       <c r="L833" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M833" t="n">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="N833" t="n">
-        <v>2458.5131821149</v>
+        <v>2458.5130781975</v>
       </c>
       <c r="O833" t="n">
-        <v>799016.7841873424</v>
+        <v>740012.4365374475</v>
       </c>
       <c r="P833" t="n">
         <v>3500</v>
       </c>
       <c r="Q833" t="n">
-        <v>1137500</v>
+        <v>1053500</v>
       </c>
     </row>
     <row r="834">
@@ -36867,10 +36867,10 @@
         <v>185</v>
       </c>
       <c r="N835" t="n">
-        <v>1771.0904491413</v>
+        <v>1771.0904111406</v>
       </c>
       <c r="O835" t="n">
-        <v>327651.7330911405</v>
+        <v>327651.726061011</v>
       </c>
       <c r="P835" t="n">
         <v>2500</v>
@@ -36907,22 +36907,22 @@
         <v>0</v>
       </c>
       <c r="L836" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M836" t="n">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="N836" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839770425</v>
       </c>
       <c r="O836" t="n">
-        <v>842150.5303081005</v>
+        <v>792245.2952531925</v>
       </c>
       <c r="P836" t="n">
         <v>2900</v>
       </c>
       <c r="Q836" t="n">
-        <v>1174500</v>
+        <v>1104900</v>
       </c>
     </row>
     <row r="837">
@@ -36999,22 +36999,22 @@
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M838" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="N838" t="n">
-        <v>3306.5951351351</v>
+        <v>3306.5946902655</v>
       </c>
       <c r="O838" t="n">
-        <v>214928.6837837815</v>
+        <v>16532.9734513275</v>
       </c>
       <c r="P838" t="n">
         <v>4900</v>
       </c>
       <c r="Q838" t="n">
-        <v>318500</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="839">
@@ -37097,10 +37097,10 @@
         <v>372</v>
       </c>
       <c r="N840" t="n">
-        <v>2108.7918292683</v>
+        <v>2108.7920330806</v>
       </c>
       <c r="O840" t="n">
-        <v>784470.5604878075</v>
+        <v>784470.6363059832</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
@@ -37137,22 +37137,22 @@
         <v>0</v>
       </c>
       <c r="L841" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M841" t="n">
-        <v>881</v>
+        <v>809</v>
       </c>
       <c r="N841" t="n">
-        <v>2056.0833612094</v>
+        <v>2056.0831903662</v>
       </c>
       <c r="O841" t="n">
-        <v>1811409.441225482</v>
+        <v>1663371.301006256</v>
       </c>
       <c r="P841" t="n">
         <v>2900</v>
       </c>
       <c r="Q841" t="n">
-        <v>2554900</v>
+        <v>2346100</v>
       </c>
     </row>
     <row r="842">
@@ -37235,10 +37235,10 @@
         <v>449</v>
       </c>
       <c r="N843" t="n">
-        <v>1655.9308652576</v>
+        <v>1655.9308592201</v>
       </c>
       <c r="O843" t="n">
-        <v>743512.9585006625</v>
+        <v>743512.9557898249</v>
       </c>
       <c r="P843" t="n">
         <v>2500</v>
@@ -37788,10 +37788,10 @@
         <v>269</v>
       </c>
       <c r="N855" t="n">
-        <v>1259.2745452499</v>
+        <v>1259.2745472973</v>
       </c>
       <c r="O855" t="n">
-        <v>338744.8526722231</v>
+        <v>338744.8532229737</v>
       </c>
       <c r="P855" t="n">
         <v>1900</v>
@@ -37924,10 +37924,10 @@
         <v>97</v>
       </c>
       <c r="N858" t="n">
-        <v>692.15222061657</v>
+        <v>692.15222920696</v>
       </c>
       <c r="O858" t="n">
-        <v>67138.76539980729</v>
+        <v>67138.76623307512</v>
       </c>
       <c r="P858" t="n">
         <v>1200</v>
@@ -40863,22 +40863,22 @@
         <v>0</v>
       </c>
       <c r="L923" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M923" t="n">
-        <v>2882</v>
+        <v>2834</v>
       </c>
       <c r="N923" t="n">
-        <v>517.28943177426</v>
+        <v>517.28978235968</v>
       </c>
       <c r="O923" t="n">
-        <v>1490828.142373418</v>
+        <v>1465999.243207333</v>
       </c>
       <c r="P923" t="n">
         <v>900</v>
       </c>
       <c r="Q923" t="n">
-        <v>2593800</v>
+        <v>2550600</v>
       </c>
     </row>
     <row r="924">
@@ -41095,10 +41095,10 @@
         <v>596</v>
       </c>
       <c r="N928" t="n">
-        <v>3110.8416960301</v>
+        <v>3110.8415531661</v>
       </c>
       <c r="O928" t="n">
-        <v>1854061.65083394</v>
+        <v>1854061.565686996</v>
       </c>
       <c r="P928" t="n">
         <v>4500</v>
@@ -41311,22 +41311,22 @@
         <v>0</v>
       </c>
       <c r="L933" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M933" t="n">
-        <v>1089</v>
+        <v>1065</v>
       </c>
       <c r="N933" t="n">
-        <v>703.79518287415</v>
+        <v>703.79517569581</v>
       </c>
       <c r="O933" t="n">
-        <v>766432.9541499494</v>
+        <v>749541.8621160376</v>
       </c>
       <c r="P933" t="n">
         <v>900</v>
       </c>
       <c r="Q933" t="n">
-        <v>980100</v>
+        <v>958500</v>
       </c>
     </row>
     <row r="934">
@@ -42368,22 +42368,22 @@
         <v>0</v>
       </c>
       <c r="L957" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M957" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="N957" t="n">
-        <v>1595.5127943686</v>
+        <v>1595.5120596085</v>
       </c>
       <c r="O957" t="n">
-        <v>100517.3060452218</v>
+        <v>23932.6808941275</v>
       </c>
       <c r="P957" t="n">
         <v>2500</v>
       </c>
       <c r="Q957" t="n">
-        <v>157500</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="958">
@@ -42899,10 +42899,10 @@
         <v>3</v>
       </c>
       <c r="N968" t="n">
-        <v>2098.4049712644</v>
+        <v>2098.405</v>
       </c>
       <c r="O968" t="n">
-        <v>6295.2149137932</v>
+        <v>6295.215</v>
       </c>
       <c r="P968" t="n">
         <v>9500</v>
@@ -45620,10 +45620,10 @@
         <v>186</v>
       </c>
       <c r="N1026" t="n">
-        <v>430.60997624703</v>
+        <v>430.6099761621</v>
       </c>
       <c r="O1026" t="n">
-        <v>80093.45558194758</v>
+        <v>80093.4555661506</v>
       </c>
       <c r="P1026" t="n">
         <v>2200</v>
@@ -46433,10 +46433,10 @@
         <v>139</v>
       </c>
       <c r="N1045" t="n">
-        <v>4282.1072450249</v>
+        <v>4282.1072260488</v>
       </c>
       <c r="O1045" t="n">
-        <v>595212.9070584611</v>
+        <v>595212.9044207832</v>
       </c>
       <c r="P1045" t="n">
         <v>5300</v>
@@ -47420,22 +47420,22 @@
         <v>0</v>
       </c>
       <c r="L1068" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1068" t="n">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="N1068" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1068" t="n">
-        <v>999116.6</v>
+        <v>922751</v>
       </c>
       <c r="P1068" t="n">
         <v>5100</v>
       </c>
       <c r="Q1068" t="n">
-        <v>1601400</v>
+        <v>1479000</v>
       </c>
     </row>
     <row r="1069">
@@ -47467,10 +47467,10 @@
         <v>3</v>
       </c>
       <c r="N1069" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821359223</v>
       </c>
       <c r="O1069" t="n">
-        <v>3641.0463583815</v>
+        <v>3641.0464077669</v>
       </c>
       <c r="P1069" t="n">
         <v>1500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1307,10 +1307,10 @@
         <v>330</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.307219032</v>
+        <v>1811.307345576</v>
       </c>
       <c r="O22" t="n">
-        <v>597731.38228056</v>
+        <v>597731.42404008</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
@@ -1424,10 +1424,10 @@
         <v>152</v>
       </c>
       <c r="N25" t="n">
-        <v>3376.7464660832</v>
+        <v>3376.7464651163</v>
       </c>
       <c r="O25" t="n">
-        <v>513265.4628446464</v>
+        <v>513265.4626976776</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
@@ -2879,10 +2879,10 @@
         <v>41</v>
       </c>
       <c r="N61" t="n">
-        <v>6272.8547682119</v>
+        <v>6272.8547761194</v>
       </c>
       <c r="O61" t="n">
-        <v>257187.0454966879</v>
+        <v>257187.0458208954</v>
       </c>
       <c r="P61" t="n">
         <v>7900</v>
@@ -3124,10 +3124,10 @@
         <v>12</v>
       </c>
       <c r="N67" t="n">
-        <v>22510.483333333</v>
+        <v>22510.483207547</v>
       </c>
       <c r="O67" t="n">
-        <v>270125.799999996</v>
+        <v>270125.798490564</v>
       </c>
       <c r="P67" t="n">
         <v>44900</v>
@@ -4683,22 +4683,22 @@
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N104" t="n">
-        <v>30708.848333333</v>
+        <v>30708.828</v>
       </c>
       <c r="O104" t="n">
-        <v>307088.48333333</v>
+        <v>245670.624</v>
       </c>
       <c r="P104" t="n">
         <v>53500</v>
       </c>
       <c r="Q104" t="n">
-        <v>535000</v>
+        <v>428000</v>
       </c>
     </row>
     <row r="105">
@@ -6019,10 +6019,10 @@
         <v>2</v>
       </c>
       <c r="N135" t="n">
-        <v>141416.88456026</v>
+        <v>141416.88457516</v>
       </c>
       <c r="O135" t="n">
-        <v>282833.76912052</v>
+        <v>282833.76915032</v>
       </c>
       <c r="P135" t="n">
         <v>251900</v>
@@ -7038,10 +7038,10 @@
         <v>7</v>
       </c>
       <c r="N159" t="n">
-        <v>61666.874092141</v>
+        <v>61666.874114441</v>
       </c>
       <c r="O159" t="n">
-        <v>431668.118644987</v>
+        <v>431668.118801087</v>
       </c>
       <c r="P159" t="n">
         <v>98900</v>
@@ -9699,22 +9699,22 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M220" t="n">
-        <v>1733</v>
+        <v>1727</v>
       </c>
       <c r="N220" t="n">
         <v>1726.32</v>
       </c>
       <c r="O220" t="n">
-        <v>2991712.56</v>
+        <v>2981354.64</v>
       </c>
       <c r="P220" t="n">
         <v>1500</v>
       </c>
       <c r="Q220" t="n">
-        <v>2599500</v>
+        <v>2590500</v>
       </c>
     </row>
     <row r="221">
@@ -9792,10 +9792,10 @@
         <v>116</v>
       </c>
       <c r="N222" t="n">
-        <v>4937.3101635688</v>
+        <v>4937.3101636905</v>
       </c>
       <c r="O222" t="n">
-        <v>572727.9789739808</v>
+        <v>572727.978988098</v>
       </c>
       <c r="P222" t="n">
         <v>7500</v>
@@ -10256,10 +10256,10 @@
         <v>493</v>
       </c>
       <c r="N233" t="n">
-        <v>1098.0595661432</v>
+        <v>1098.0597873486</v>
       </c>
       <c r="O233" t="n">
-        <v>541343.3661085976</v>
+        <v>541343.4751628598</v>
       </c>
       <c r="P233" t="n">
         <v>1500</v>
@@ -12063,10 +12063,10 @@
         <v>202</v>
       </c>
       <c r="N275" t="n">
-        <v>2582.2557353886</v>
+        <v>2582.2557142857</v>
       </c>
       <c r="O275" t="n">
-        <v>521615.6585484972</v>
+        <v>521615.6542857114</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
@@ -12149,22 +12149,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M277" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N277" t="n">
-        <v>5216.8961202577</v>
+        <v>5216.8961124659</v>
       </c>
       <c r="O277" t="n">
-        <v>782534.4180386551</v>
+        <v>772100.6246449532</v>
       </c>
       <c r="P277" t="n">
         <v>8500</v>
       </c>
       <c r="Q277" t="n">
-        <v>1275000</v>
+        <v>1258000</v>
       </c>
     </row>
     <row r="278">
@@ -12323,10 +12323,10 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M281" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N281" t="n">
         <v>0</v>
@@ -12338,7 +12338,7 @@
         <v>1700</v>
       </c>
       <c r="Q281" t="n">
-        <v>11900</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="282">
@@ -12498,10 +12498,10 @@
         <v>689</v>
       </c>
       <c r="N285" t="n">
-        <v>3158.8608260699</v>
+        <v>3158.8608262318</v>
       </c>
       <c r="O285" t="n">
-        <v>2176455.109162161</v>
+        <v>2176455.10927371</v>
       </c>
       <c r="P285" t="n">
         <v>5600</v>
@@ -12590,10 +12590,10 @@
         <v>12</v>
       </c>
       <c r="N287" t="n">
-        <v>3841.6247928994</v>
+        <v>3841.6248214286</v>
       </c>
       <c r="O287" t="n">
-        <v>46099.4975147928</v>
+        <v>46099.4978571432</v>
       </c>
       <c r="P287" t="n">
         <v>6900</v>
@@ -12807,22 +12807,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M292" t="n">
-        <v>908</v>
+        <v>872</v>
       </c>
       <c r="N292" t="n">
         <v>1480</v>
       </c>
       <c r="O292" t="n">
-        <v>1343840</v>
+        <v>1290560</v>
       </c>
       <c r="P292" t="n">
         <v>2600</v>
       </c>
       <c r="Q292" t="n">
-        <v>2360800</v>
+        <v>2267200</v>
       </c>
     </row>
     <row r="293">
@@ -13032,22 +13032,22 @@
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M297" t="n">
-        <v>458</v>
+        <v>392</v>
       </c>
       <c r="N297" t="n">
         <v>1026.13</v>
       </c>
       <c r="O297" t="n">
-        <v>469967.54</v>
+        <v>402242.96</v>
       </c>
       <c r="P297" t="n">
         <v>1900</v>
       </c>
       <c r="Q297" t="n">
-        <v>870200</v>
+        <v>744800</v>
       </c>
     </row>
     <row r="298">
@@ -13673,10 +13673,10 @@
         <v>34</v>
       </c>
       <c r="N311" t="n">
-        <v>4890.9300487805</v>
+        <v>4890.93004884</v>
       </c>
       <c r="O311" t="n">
-        <v>166291.621658537</v>
+        <v>166291.62166056</v>
       </c>
       <c r="P311" t="n">
         <v>8200</v>
@@ -14115,22 +14115,22 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M321" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N321" t="n">
         <v>7041</v>
       </c>
       <c r="O321" t="n">
-        <v>112656</v>
+        <v>105615</v>
       </c>
       <c r="P321" t="n">
         <v>11500</v>
       </c>
       <c r="Q321" t="n">
-        <v>184000</v>
+        <v>172500</v>
       </c>
     </row>
     <row r="322">
@@ -14340,22 +14340,22 @@
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M326" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N326" t="n">
         <v>10716.34</v>
       </c>
       <c r="O326" t="n">
-        <v>385788.24</v>
+        <v>364355.56</v>
       </c>
       <c r="P326" t="n">
         <v>39000</v>
       </c>
       <c r="Q326" t="n">
-        <v>1404000</v>
+        <v>1326000</v>
       </c>
     </row>
     <row r="327">
@@ -14553,22 +14553,22 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M331" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N331" t="n">
-        <v>3594.2540186916</v>
+        <v>3594.254</v>
       </c>
       <c r="O331" t="n">
-        <v>161741.430841122</v>
+        <v>143770.16</v>
       </c>
       <c r="P331" t="n">
         <v>6500</v>
       </c>
       <c r="Q331" t="n">
-        <v>292500</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="332">
@@ -14722,22 +14722,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M335" t="n">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="N335" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.850037037</v>
       </c>
       <c r="O335" t="n">
-        <v>651410.8565472333</v>
+        <v>418069.654777773</v>
       </c>
       <c r="P335" t="n">
         <v>5200</v>
       </c>
       <c r="Q335" t="n">
-        <v>1045200</v>
+        <v>670800</v>
       </c>
     </row>
     <row r="336">
@@ -14945,25 +14945,25 @@
         <v>289</v>
       </c>
       <c r="K340" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M340" t="n">
-        <v>289</v>
+        <v>791</v>
       </c>
       <c r="N340" t="n">
         <v>2090.85</v>
       </c>
       <c r="O340" t="n">
-        <v>604255.65</v>
+        <v>1653862.35</v>
       </c>
       <c r="P340" t="n">
         <v>2900</v>
       </c>
       <c r="Q340" t="n">
-        <v>838100</v>
+        <v>2293900</v>
       </c>
     </row>
     <row r="341">
@@ -15301,22 +15301,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M348" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="N348" t="n">
         <v>3309</v>
       </c>
       <c r="O348" t="n">
-        <v>241557</v>
+        <v>221703</v>
       </c>
       <c r="P348" t="n">
         <v>5900</v>
       </c>
       <c r="Q348" t="n">
-        <v>430700</v>
+        <v>395300</v>
       </c>
     </row>
     <row r="349">
@@ -15485,10 +15485,10 @@
         <v>426</v>
       </c>
       <c r="N352" t="n">
-        <v>3041.660013245</v>
+        <v>3041.6600132802</v>
       </c>
       <c r="O352" t="n">
-        <v>1295747.16564237</v>
+        <v>1295747.165657365</v>
       </c>
       <c r="P352" t="n">
         <v>5500</v>
@@ -15662,10 +15662,10 @@
         <v>2</v>
       </c>
       <c r="N356" t="n">
-        <v>1592.566762142</v>
+        <v>1592.5667254408</v>
       </c>
       <c r="O356" t="n">
-        <v>3185.133524284</v>
+        <v>3185.1334508816</v>
       </c>
       <c r="P356" t="n">
         <v>3900</v>
@@ -16228,22 +16228,22 @@
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M369" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="N369" t="n">
         <v>4648.6</v>
       </c>
       <c r="O369" t="n">
-        <v>1706036.2</v>
+        <v>1692090.4</v>
       </c>
       <c r="P369" t="n">
         <v>8900</v>
       </c>
       <c r="Q369" t="n">
-        <v>3266300</v>
+        <v>3239600</v>
       </c>
     </row>
     <row r="370">
@@ -16618,22 +16618,22 @@
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M378" t="n">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="N378" t="n">
         <v>1647.46</v>
       </c>
       <c r="O378" t="n">
-        <v>527187.2</v>
+        <v>497532.92</v>
       </c>
       <c r="P378" t="n">
         <v>2900</v>
       </c>
       <c r="Q378" t="n">
-        <v>928000</v>
+        <v>875800</v>
       </c>
     </row>
     <row r="379">
@@ -16706,22 +16706,22 @@
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M380" t="n">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="N380" t="n">
         <v>1387.55</v>
       </c>
       <c r="O380" t="n">
-        <v>588321.2</v>
+        <v>546694.7</v>
       </c>
       <c r="P380" t="n">
         <v>2300</v>
       </c>
       <c r="Q380" t="n">
-        <v>975200</v>
+        <v>906200</v>
       </c>
     </row>
     <row r="381">
@@ -17723,22 +17723,22 @@
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M403" t="n">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="N403" t="n">
-        <v>1630.9235901027</v>
+        <v>1630.9236367936</v>
       </c>
       <c r="O403" t="n">
-        <v>914948.1340476148</v>
+        <v>875805.9929581633</v>
       </c>
       <c r="P403" t="n">
         <v>2500</v>
       </c>
       <c r="Q403" t="n">
-        <v>1402500</v>
+        <v>1342500</v>
       </c>
     </row>
     <row r="404">
@@ -17850,22 +17850,22 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M406" t="n">
         <v>152</v>
       </c>
       <c r="N406" t="n">
-        <v>1690.5972035794</v>
+        <v>1690.5971524664</v>
       </c>
       <c r="O406" t="n">
-        <v>256970.7749440688</v>
+        <v>256970.7671748928</v>
       </c>
       <c r="P406" t="n">
         <v>2900</v>
@@ -17896,28 +17896,28 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>1351</v>
+        <v>1387</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M407" t="n">
-        <v>1351</v>
+        <v>1327</v>
       </c>
       <c r="N407" t="n">
-        <v>1550.1936753491</v>
+        <v>1550.1936973199</v>
       </c>
       <c r="O407" t="n">
-        <v>2094311.655396634</v>
+        <v>2057107.036343507</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
       </c>
       <c r="Q407" t="n">
-        <v>3377500</v>
+        <v>3317500</v>
       </c>
     </row>
     <row r="408">
@@ -17954,10 +17954,10 @@
         <v>3</v>
       </c>
       <c r="N408" t="n">
-        <v>1579.3905526316</v>
+        <v>1579.3904266667</v>
       </c>
       <c r="O408" t="n">
-        <v>4738.1716578948</v>
+        <v>4738.171280000101</v>
       </c>
       <c r="P408" t="n">
         <v>2900</v>
@@ -17988,22 +17988,22 @@
         </is>
       </c>
       <c r="J409" t="n">
-        <v>824</v>
+        <v>874</v>
       </c>
       <c r="K409" t="n">
         <v>0</v>
       </c>
       <c r="L409" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M409" t="n">
         <v>824</v>
       </c>
       <c r="N409" t="n">
-        <v>2403.5119996136</v>
+        <v>2403.5120742613</v>
       </c>
       <c r="O409" t="n">
-        <v>1980493.887681606</v>
+        <v>1980493.949191311</v>
       </c>
       <c r="P409" t="n">
         <v>3500</v>
@@ -18767,22 +18767,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M427" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N427" t="n">
         <v>59081.6</v>
       </c>
       <c r="O427" t="n">
-        <v>590816</v>
+        <v>472652.8</v>
       </c>
       <c r="P427" t="n">
         <v>40000</v>
       </c>
       <c r="Q427" t="n">
-        <v>400000</v>
+        <v>320000</v>
       </c>
     </row>
     <row r="428">
@@ -19307,25 +19307,25 @@
         <v>110</v>
       </c>
       <c r="K439" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L439" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M439" t="n">
-        <v>110</v>
+        <v>326</v>
       </c>
       <c r="N439" t="n">
         <v>3253</v>
       </c>
       <c r="O439" t="n">
-        <v>357830</v>
+        <v>1060478</v>
       </c>
       <c r="P439" t="n">
         <v>3900</v>
       </c>
       <c r="Q439" t="n">
-        <v>429000</v>
+        <v>1271400</v>
       </c>
     </row>
     <row r="440">
@@ -19699,25 +19699,25 @@
         <v>45</v>
       </c>
       <c r="K448" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="L448" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M448" t="n">
-        <v>45</v>
+        <v>211</v>
       </c>
       <c r="N448" t="n">
         <v>3253</v>
       </c>
       <c r="O448" t="n">
-        <v>146385</v>
+        <v>686383</v>
       </c>
       <c r="P448" t="n">
         <v>3900</v>
       </c>
       <c r="Q448" t="n">
-        <v>175500</v>
+        <v>822900</v>
       </c>
     </row>
     <row r="449">
@@ -20866,10 +20866,10 @@
         <v>148</v>
       </c>
       <c r="N475" t="n">
-        <v>4196.8725291181</v>
+        <v>4196.8725298197</v>
       </c>
       <c r="O475" t="n">
-        <v>621137.1343094788</v>
+        <v>621137.1344133156</v>
       </c>
       <c r="P475" t="n">
         <v>5900</v>
@@ -21562,22 +21562,22 @@
         <v>0</v>
       </c>
       <c r="L492" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M492" t="n">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="N492" t="n">
         <v>2567</v>
       </c>
       <c r="O492" t="n">
-        <v>634049</v>
+        <v>572441</v>
       </c>
       <c r="P492" t="n">
         <v>4500</v>
       </c>
       <c r="Q492" t="n">
-        <v>1111500</v>
+        <v>1003500</v>
       </c>
     </row>
     <row r="493">
@@ -21931,22 +21931,22 @@
         <v>0</v>
       </c>
       <c r="L501" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M501" t="n">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="N501" t="n">
-        <v>2029.8738129131</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O501" t="n">
-        <v>935771.8277529391</v>
+        <v>887054.8768245011</v>
       </c>
       <c r="P501" t="n">
         <v>3600</v>
       </c>
       <c r="Q501" t="n">
-        <v>1659600</v>
+        <v>1573200</v>
       </c>
     </row>
     <row r="502">
@@ -23546,10 +23546,10 @@
         <v>278</v>
       </c>
       <c r="N539" t="n">
-        <v>4285.1955097614</v>
+        <v>4285.1955337691</v>
       </c>
       <c r="O539" t="n">
-        <v>1191284.351713669</v>
+        <v>1191284.35838781</v>
       </c>
       <c r="P539" t="n">
         <v>6900</v>
@@ -25555,22 +25555,22 @@
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M586" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N586" t="n">
         <v>22730.48</v>
       </c>
       <c r="O586" t="n">
-        <v>363687.68</v>
+        <v>340957.2</v>
       </c>
       <c r="P586" t="n">
         <v>36900</v>
       </c>
       <c r="Q586" t="n">
-        <v>590400</v>
+        <v>553500</v>
       </c>
     </row>
     <row r="587">
@@ -25949,22 +25949,22 @@
         <v>0</v>
       </c>
       <c r="L595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M595" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N595" t="n">
         <v>4100.45</v>
       </c>
       <c r="O595" t="n">
-        <v>65607.2</v>
+        <v>61506.75</v>
       </c>
       <c r="P595" t="n">
         <v>26900</v>
       </c>
       <c r="Q595" t="n">
-        <v>430400</v>
+        <v>403500</v>
       </c>
     </row>
     <row r="596">
@@ -26175,10 +26175,10 @@
         <v>68</v>
       </c>
       <c r="N600" t="n">
-        <v>1561.0003205128</v>
+        <v>1561.0009152542</v>
       </c>
       <c r="O600" t="n">
-        <v>106148.0217948704</v>
+        <v>106148.0622372856</v>
       </c>
       <c r="P600" t="n">
         <v>2900</v>
@@ -28771,10 +28771,10 @@
         <v>248</v>
       </c>
       <c r="N659" t="n">
-        <v>1664.355659204</v>
+        <v>1664.3554968553</v>
       </c>
       <c r="O659" t="n">
-        <v>412760.203482592</v>
+        <v>412760.1632201144</v>
       </c>
       <c r="P659" t="n">
         <v>2900</v>
@@ -29415,22 +29415,22 @@
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M673" t="n">
-        <v>1400</v>
+        <v>1360</v>
       </c>
       <c r="N673" t="n">
-        <v>1778.4726299141</v>
+        <v>1778.4726458554</v>
       </c>
       <c r="O673" t="n">
-        <v>2489861.68187974</v>
+        <v>2418722.798363344</v>
       </c>
       <c r="P673" t="n">
         <v>4900</v>
       </c>
       <c r="Q673" t="n">
-        <v>6860000</v>
+        <v>6664000</v>
       </c>
     </row>
     <row r="674">
@@ -29461,22 +29461,22 @@
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M674" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="N674" t="n">
         <v>1548</v>
       </c>
       <c r="O674" t="n">
-        <v>309600</v>
+        <v>272448</v>
       </c>
       <c r="P674" t="n">
         <v>3900</v>
       </c>
       <c r="Q674" t="n">
-        <v>780000</v>
+        <v>686400</v>
       </c>
     </row>
     <row r="675">
@@ -32231,10 +32231,10 @@
         <v>684</v>
       </c>
       <c r="N734" t="n">
-        <v>2328.1187114504</v>
+        <v>2328.1187098747</v>
       </c>
       <c r="O734" t="n">
-        <v>1592433.198632074</v>
+        <v>1592433.197554295</v>
       </c>
       <c r="P734" t="n">
         <v>4500</v>
@@ -34661,22 +34661,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M787" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="N787" t="n">
         <v>753</v>
       </c>
       <c r="O787" t="n">
-        <v>457824</v>
+        <v>451800</v>
       </c>
       <c r="P787" t="n">
         <v>1600</v>
       </c>
       <c r="Q787" t="n">
-        <v>972800</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="788">
@@ -34897,10 +34897,10 @@
         <v>171</v>
       </c>
       <c r="N792" t="n">
-        <v>17075.989523151</v>
+        <v>17075.989522822</v>
       </c>
       <c r="O792" t="n">
-        <v>2919994.208458821</v>
+        <v>2919994.208402562</v>
       </c>
       <c r="P792" t="n">
         <v>27500</v>
@@ -36456,22 +36456,22 @@
         <v>0</v>
       </c>
       <c r="L826" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M826" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="N826" t="n">
         <v>1803</v>
       </c>
       <c r="O826" t="n">
-        <v>349782</v>
+        <v>320934</v>
       </c>
       <c r="P826" t="n">
         <v>3900</v>
       </c>
       <c r="Q826" t="n">
-        <v>756600</v>
+        <v>694200</v>
       </c>
     </row>
     <row r="827">
@@ -36594,22 +36594,22 @@
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M829" t="n">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="N829" t="n">
-        <v>1516.0387982037</v>
+        <v>1516.0387951453</v>
       </c>
       <c r="O829" t="n">
-        <v>900527.0461329978</v>
+        <v>864142.113232821</v>
       </c>
       <c r="P829" t="n">
         <v>2300</v>
       </c>
       <c r="Q829" t="n">
-        <v>1366200</v>
+        <v>1311000</v>
       </c>
     </row>
     <row r="830">
@@ -36730,22 +36730,22 @@
         <v>0</v>
       </c>
       <c r="L832" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M832" t="n">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="N832" t="n">
-        <v>2458.5131328074</v>
+        <v>2458.5130759032</v>
       </c>
       <c r="O832" t="n">
-        <v>799016.768162405</v>
+        <v>740012.4358468632</v>
       </c>
       <c r="P832" t="n">
         <v>3500</v>
       </c>
       <c r="Q832" t="n">
-        <v>1137500</v>
+        <v>1053500</v>
       </c>
     </row>
     <row r="833">
@@ -36868,22 +36868,22 @@
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M835" t="n">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="N835" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839709361</v>
       </c>
       <c r="O835" t="n">
-        <v>842150.5303081005</v>
+        <v>792245.2929266541</v>
       </c>
       <c r="P835" t="n">
         <v>2900</v>
       </c>
       <c r="Q835" t="n">
-        <v>1174500</v>
+        <v>1104900</v>
       </c>
     </row>
     <row r="836">
@@ -36914,22 +36914,22 @@
         <v>0</v>
       </c>
       <c r="L836" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M836" t="n">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="N836" t="n">
-        <v>1803.0156051587</v>
+        <v>1803.0156237558</v>
       </c>
       <c r="O836" t="n">
-        <v>1087218.409910696</v>
+        <v>1076400.327382213</v>
       </c>
       <c r="P836" t="n">
         <v>2500</v>
       </c>
       <c r="Q836" t="n">
-        <v>1507500</v>
+        <v>1492500</v>
       </c>
     </row>
     <row r="837">
@@ -36960,22 +36960,22 @@
         <v>0</v>
       </c>
       <c r="L837" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M837" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="N837" t="n">
-        <v>3306.5951153324</v>
+        <v>3306.5946745562</v>
       </c>
       <c r="O837" t="n">
-        <v>214928.682496606</v>
+        <v>16532.973372781</v>
       </c>
       <c r="P837" t="n">
         <v>4900</v>
       </c>
       <c r="Q837" t="n">
-        <v>318500</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="838">
@@ -37012,10 +37012,10 @@
         <v>413</v>
       </c>
       <c r="N838" t="n">
-        <v>2122.1638529227</v>
+        <v>2122.1638509903</v>
       </c>
       <c r="O838" t="n">
-        <v>876453.671257075</v>
+        <v>876453.6704589939</v>
       </c>
       <c r="P838" t="n">
         <v>2900</v>
@@ -37058,10 +37058,10 @@
         <v>372</v>
       </c>
       <c r="N839" t="n">
-        <v>2108.7920330806</v>
+        <v>2108.792083045</v>
       </c>
       <c r="O839" t="n">
-        <v>784470.6363059832</v>
+        <v>784470.65489274</v>
       </c>
       <c r="P839" t="n">
         <v>2900</v>
@@ -37098,22 +37098,22 @@
         <v>0</v>
       </c>
       <c r="L840" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M840" t="n">
-        <v>881</v>
+        <v>809</v>
       </c>
       <c r="N840" t="n">
-        <v>2056.0831723454</v>
+        <v>2056.0829891304</v>
       </c>
       <c r="O840" t="n">
-        <v>1811409.274836297</v>
+        <v>1663371.138206494</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
       </c>
       <c r="Q840" t="n">
-        <v>2554900</v>
+        <v>2346100</v>
       </c>
     </row>
     <row r="841">
@@ -37150,10 +37150,10 @@
         <v>207</v>
       </c>
       <c r="N841" t="n">
-        <v>3224.5688003933</v>
+        <v>3224.5688090551</v>
       </c>
       <c r="O841" t="n">
-        <v>667485.7416814131</v>
+        <v>667485.7434744056</v>
       </c>
       <c r="P841" t="n">
         <v>4500</v>
@@ -37190,22 +37190,22 @@
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M842" t="n">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="N842" t="n">
-        <v>1655.9308592201</v>
+        <v>1655.9308045213</v>
       </c>
       <c r="O842" t="n">
-        <v>743512.9557898249</v>
+        <v>723641.7615758081</v>
       </c>
       <c r="P842" t="n">
         <v>2500</v>
       </c>
       <c r="Q842" t="n">
-        <v>1122500</v>
+        <v>1092500</v>
       </c>
     </row>
     <row r="843">
@@ -37611,10 +37611,10 @@
         <v>2</v>
       </c>
       <c r="N851" t="n">
-        <v>1906.1836708861</v>
+        <v>1906.1834782609</v>
       </c>
       <c r="O851" t="n">
-        <v>3812.3673417722</v>
+        <v>3812.3669565218</v>
       </c>
       <c r="P851" t="n">
         <v>2900</v>
@@ -37703,10 +37703,10 @@
         <v>61</v>
       </c>
       <c r="N853" t="n">
-        <v>2546.9839186296</v>
+        <v>2546.9838660907</v>
       </c>
       <c r="O853" t="n">
-        <v>155366.0190364056</v>
+        <v>155366.0158315327</v>
       </c>
       <c r="P853" t="n">
         <v>3900</v>
@@ -37749,10 +37749,10 @@
         <v>269</v>
       </c>
       <c r="N854" t="n">
-        <v>1259.2745472973</v>
+        <v>1259.274561681</v>
       </c>
       <c r="O854" t="n">
-        <v>338744.8532229737</v>
+        <v>338744.857092189</v>
       </c>
       <c r="P854" t="n">
         <v>1900</v>
@@ -39486,22 +39486,22 @@
         <v>0</v>
       </c>
       <c r="L892" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M892" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="N892" t="n">
         <v>1828.64</v>
       </c>
       <c r="O892" t="n">
-        <v>1214216.96</v>
+        <v>1205073.76</v>
       </c>
       <c r="P892" t="n">
         <v>2000</v>
       </c>
       <c r="Q892" t="n">
-        <v>1328000</v>
+        <v>1318000</v>
       </c>
     </row>
     <row r="893">
@@ -40824,22 +40824,22 @@
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M922" t="n">
-        <v>2856</v>
+        <v>2801</v>
       </c>
       <c r="N922" t="n">
-        <v>517.2898138359</v>
+        <v>517.28990087531</v>
       </c>
       <c r="O922" t="n">
-        <v>1477379.70831533</v>
+        <v>1448929.012351743</v>
       </c>
       <c r="P922" t="n">
         <v>900</v>
       </c>
       <c r="Q922" t="n">
-        <v>2570400</v>
+        <v>2520900</v>
       </c>
     </row>
     <row r="923">
@@ -41056,10 +41056,10 @@
         <v>581</v>
       </c>
       <c r="N927" t="n">
-        <v>3110.8415227818</v>
+        <v>3110.8414032101</v>
       </c>
       <c r="O927" t="n">
-        <v>1807398.924736226</v>
+        <v>1807398.855265068</v>
       </c>
       <c r="P927" t="n">
         <v>4500</v>
@@ -41272,22 +41272,22 @@
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M932" t="n">
-        <v>1077</v>
+        <v>1053</v>
       </c>
       <c r="N932" t="n">
-        <v>703.795175</v>
+        <v>703.79516919374</v>
       </c>
       <c r="O932" t="n">
-        <v>757987.4034749999</v>
+        <v>741096.3131610082</v>
       </c>
       <c r="P932" t="n">
         <v>900</v>
       </c>
       <c r="Q932" t="n">
-        <v>969300</v>
+        <v>947700</v>
       </c>
     </row>
     <row r="933">
@@ -41812,22 +41812,22 @@
         <v>0</v>
       </c>
       <c r="L944" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M944" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N944" t="n">
         <v>1300</v>
       </c>
       <c r="O944" t="n">
-        <v>80600</v>
+        <v>79300</v>
       </c>
       <c r="P944" t="n">
         <v>2200</v>
       </c>
       <c r="Q944" t="n">
-        <v>136400</v>
+        <v>134200</v>
       </c>
     </row>
     <row r="945">
@@ -42329,22 +42329,22 @@
         <v>0</v>
       </c>
       <c r="L956" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M956" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="N956" t="n">
-        <v>1595.5123423818</v>
+        <v>1595.5119633274</v>
       </c>
       <c r="O956" t="n">
-        <v>100517.2775700534</v>
+        <v>23932.679449911</v>
       </c>
       <c r="P956" t="n">
         <v>2500</v>
       </c>
       <c r="Q956" t="n">
-        <v>157500</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="957">
@@ -44824,10 +44824,10 @@
         <v>181</v>
       </c>
       <c r="N1009" t="n">
-        <v>7046.9398281418</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O1009" t="n">
-        <v>1275496.108893666</v>
+        <v>1275496.10885352</v>
       </c>
       <c r="P1009" t="n">
         <v>9900</v>
@@ -45581,10 +45581,10 @@
         <v>186</v>
       </c>
       <c r="N1025" t="n">
-        <v>430.6099761621</v>
+        <v>430.60997607656</v>
       </c>
       <c r="O1025" t="n">
-        <v>80093.4555661506</v>
+        <v>80093.45555024015</v>
       </c>
       <c r="P1025" t="n">
         <v>2200</v>
@@ -47337,22 +47337,22 @@
         <v>0</v>
       </c>
       <c r="L1066" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1066" t="n">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="N1066" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1066" t="n">
-        <v>154130.67</v>
+        <v>125892.99</v>
       </c>
       <c r="P1066" t="n">
         <v>1900</v>
       </c>
       <c r="Q1066" t="n">
-        <v>248900</v>
+        <v>203300</v>
       </c>
     </row>
     <row r="1067">
@@ -47378,25 +47378,25 @@
         <v>273</v>
       </c>
       <c r="K1067" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L1067" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1067" t="n">
-        <v>273</v>
+        <v>449</v>
       </c>
       <c r="N1067" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1067" t="n">
-        <v>868658.7000000001</v>
+        <v>1428673.1</v>
       </c>
       <c r="P1067" t="n">
         <v>5100</v>
       </c>
       <c r="Q1067" t="n">
-        <v>1392300</v>
+        <v>2289900</v>
       </c>
     </row>
     <row r="1068">
@@ -48715,10 +48715,10 @@
         <v>89</v>
       </c>
       <c r="N1098" t="n">
-        <v>4985.4053097345</v>
+        <v>4985.4053571429</v>
       </c>
       <c r="O1098" t="n">
-        <v>443701.0725663705</v>
+        <v>443701.0767857181</v>
       </c>
       <c r="P1098" t="n">
         <v>7900</v>
@@ -49619,22 +49619,22 @@
         <v>0</v>
       </c>
       <c r="L1118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1118" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="N1118" t="n">
         <v>1584</v>
       </c>
       <c r="O1118" t="n">
-        <v>294624</v>
+        <v>286704</v>
       </c>
       <c r="P1118" t="n">
         <v>2000</v>
       </c>
       <c r="Q1118" t="n">
-        <v>372000</v>
+        <v>362000</v>
       </c>
     </row>
     <row r="1119">
@@ -49757,22 +49757,22 @@
         <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1121" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N1121" t="n">
         <v>4400</v>
       </c>
       <c r="O1121" t="n">
-        <v>523600</v>
+        <v>510400</v>
       </c>
       <c r="P1121" t="n">
         <v>5900</v>
       </c>
       <c r="Q1121" t="n">
-        <v>702100</v>
+        <v>684400</v>
       </c>
     </row>
     <row r="1122">
@@ -49803,22 +49803,22 @@
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1122" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="N1122" t="n">
         <v>3520</v>
       </c>
       <c r="O1122" t="n">
-        <v>601920</v>
+        <v>559680</v>
       </c>
       <c r="P1122" t="n">
         <v>4500</v>
       </c>
       <c r="Q1122" t="n">
-        <v>769500</v>
+        <v>715500</v>
       </c>
     </row>
     <row r="1123">
@@ -49987,22 +49987,22 @@
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1126" t="n">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="N1126" t="n">
         <v>2288</v>
       </c>
       <c r="O1126" t="n">
-        <v>1285856</v>
+        <v>1276704</v>
       </c>
       <c r="P1126" t="n">
         <v>2900</v>
       </c>
       <c r="Q1126" t="n">
-        <v>1629800</v>
+        <v>1618200</v>
       </c>
     </row>
     <row r="1127">
@@ -50033,22 +50033,22 @@
         <v>0</v>
       </c>
       <c r="L1127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1127" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N1127" t="n">
         <v>4576</v>
       </c>
       <c r="O1127" t="n">
-        <v>791648</v>
+        <v>782496</v>
       </c>
       <c r="P1127" t="n">
         <v>5900</v>
       </c>
       <c r="Q1127" t="n">
-        <v>1020700</v>
+        <v>1008900</v>
       </c>
     </row>
     <row r="1128">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1697,19 +1697,19 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N32" t="n">
         <v>4072</v>
       </c>
       <c r="O32" t="n">
-        <v>415344</v>
+        <v>407200</v>
       </c>
       <c r="P32" t="n">
         <v>7500</v>
       </c>
       <c r="Q32" t="n">
-        <v>765000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="33">
@@ -4095,10 +4095,10 @@
         <v>53</v>
       </c>
       <c r="N91" t="n">
-        <v>3910.6281404959</v>
+        <v>3910.628136646</v>
       </c>
       <c r="O91" t="n">
-        <v>207263.2914462827</v>
+        <v>207263.291242238</v>
       </c>
       <c r="P91" t="n">
         <v>9100</v>
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
         <v>8</v>
@@ -9693,13 +9693,13 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>1733</v>
+        <v>1727</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
         <v>1727</v>
@@ -12051,7 +12051,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12060,19 +12060,19 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N275" t="n">
-        <v>2582.2557142857</v>
+        <v>2582.2556563454</v>
       </c>
       <c r="O275" t="n">
-        <v>521615.6542857114</v>
+        <v>516451.13126908</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
       </c>
       <c r="Q275" t="n">
-        <v>909000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="276">
@@ -12143,28 +12143,28 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="N277" t="n">
-        <v>5216.8961124659</v>
+        <v>5216.8961063218</v>
       </c>
       <c r="O277" t="n">
-        <v>772100.6246449532</v>
+        <v>756449.9354166611</v>
       </c>
       <c r="P277" t="n">
         <v>8500</v>
       </c>
       <c r="Q277" t="n">
-        <v>1258000</v>
+        <v>1232500</v>
       </c>
     </row>
     <row r="278">
@@ -12317,13 +12317,13 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
         <v>2</v>
@@ -12801,13 +12801,13 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>908</v>
+        <v>872</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
         <v>872</v>
@@ -13026,13 +13026,13 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>458</v>
+        <v>392</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
         <v>392</v>
@@ -13118,7 +13118,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>4075</v>
+        <v>4055</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13127,19 +13127,19 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>4075</v>
+        <v>4055</v>
       </c>
       <c r="N299" t="n">
         <v>156.25</v>
       </c>
       <c r="O299" t="n">
-        <v>636718.75</v>
+        <v>633593.75</v>
       </c>
       <c r="P299" t="n">
         <v>250</v>
       </c>
       <c r="Q299" t="n">
-        <v>1018750</v>
+        <v>1013750</v>
       </c>
     </row>
     <row r="300">
@@ -13673,10 +13673,10 @@
         <v>34</v>
       </c>
       <c r="N311" t="n">
-        <v>4890.93004884</v>
+        <v>4890.9300488998</v>
       </c>
       <c r="O311" t="n">
-        <v>166291.62166056</v>
+        <v>166291.6216625932</v>
       </c>
       <c r="P311" t="n">
         <v>8200</v>
@@ -13756,7 +13756,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -13765,19 +13765,19 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="N313" t="n">
         <v>1203.38</v>
       </c>
       <c r="O313" t="n">
-        <v>873653.8800000001</v>
+        <v>866433.6000000001</v>
       </c>
       <c r="P313" t="n">
         <v>1900</v>
       </c>
       <c r="Q313" t="n">
-        <v>1379400</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="314">
@@ -14109,13 +14109,13 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M321" t="n">
         <v>15</v>
@@ -14334,13 +14334,13 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
         <v>34</v>
@@ -14547,13 +14547,13 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M331" t="n">
         <v>40</v>
@@ -14716,22 +14716,22 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M335" t="n">
         <v>129</v>
       </c>
       <c r="N335" t="n">
-        <v>3240.850037037</v>
+        <v>3240.8500371058</v>
       </c>
       <c r="O335" t="n">
-        <v>418069.654777773</v>
+        <v>418069.6547866482</v>
       </c>
       <c r="P335" t="n">
         <v>5200</v>
@@ -14762,7 +14762,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -14771,19 +14771,19 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N336" t="n">
         <v>4891</v>
       </c>
       <c r="O336" t="n">
-        <v>528228</v>
+        <v>523337</v>
       </c>
       <c r="P336" t="n">
         <v>8200</v>
       </c>
       <c r="Q336" t="n">
-        <v>885600</v>
+        <v>877400</v>
       </c>
     </row>
     <row r="337">
@@ -14942,28 +14942,28 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>289</v>
+        <v>767</v>
       </c>
       <c r="K340" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>791</v>
+        <v>767</v>
       </c>
       <c r="N340" t="n">
         <v>2090.85</v>
       </c>
       <c r="O340" t="n">
-        <v>1653862.35</v>
+        <v>1603681.95</v>
       </c>
       <c r="P340" t="n">
         <v>2900</v>
       </c>
       <c r="Q340" t="n">
-        <v>2293900</v>
+        <v>2224300</v>
       </c>
     </row>
     <row r="341">
@@ -15039,10 +15039,10 @@
         <v>321</v>
       </c>
       <c r="N342" t="n">
-        <v>5191.4800278552</v>
+        <v>5191.4800280899</v>
       </c>
       <c r="O342" t="n">
-        <v>1666465.088941519</v>
+        <v>1666465.089016858</v>
       </c>
       <c r="P342" t="n">
         <v>9100</v>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
@@ -15124,19 +15124,19 @@
         <v>0</v>
       </c>
       <c r="M344" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N344" t="n">
         <v>2665.4</v>
       </c>
       <c r="O344" t="n">
-        <v>63969.60000000001</v>
+        <v>55973.4</v>
       </c>
       <c r="P344" t="n">
         <v>20900</v>
       </c>
       <c r="Q344" t="n">
-        <v>501600</v>
+        <v>438900</v>
       </c>
     </row>
     <row r="345">
@@ -15295,13 +15295,13 @@
         </is>
       </c>
       <c r="J348" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M348" t="n">
         <v>67</v>
@@ -15572,10 +15572,10 @@
         <v>204</v>
       </c>
       <c r="N354" t="n">
-        <v>4372.2107902432</v>
+        <v>4372.2107903559</v>
       </c>
       <c r="O354" t="n">
-        <v>891931.0012096128</v>
+        <v>891931.0012326036</v>
       </c>
       <c r="P354" t="n">
         <v>7500</v>
@@ -15604,7 +15604,7 @@
         </is>
       </c>
       <c r="J355" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K355" t="n">
         <v>0</v>
@@ -15613,19 +15613,19 @@
         <v>0</v>
       </c>
       <c r="M355" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N355" t="n">
         <v>6441.03</v>
       </c>
       <c r="O355" t="n">
-        <v>212553.99</v>
+        <v>193230.9</v>
       </c>
       <c r="P355" t="n">
         <v>10500</v>
       </c>
       <c r="Q355" t="n">
-        <v>346500</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="356">
@@ -16222,13 +16222,13 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M369" t="n">
         <v>364</v>
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="J378" t="n">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="K378" t="n">
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M378" t="n">
         <v>302</v>
@@ -16700,13 +16700,13 @@
         </is>
       </c>
       <c r="J380" t="n">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="K380" t="n">
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M380" t="n">
         <v>394</v>
@@ -17717,22 +17717,22 @@
         </is>
       </c>
       <c r="J403" t="n">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="K403" t="n">
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M403" t="n">
         <v>537</v>
       </c>
       <c r="N403" t="n">
-        <v>1630.9236367936</v>
+        <v>1630.9236471425</v>
       </c>
       <c r="O403" t="n">
-        <v>875805.9929581633</v>
+        <v>875805.9985155225</v>
       </c>
       <c r="P403" t="n">
         <v>2500</v>
@@ -17850,22 +17850,22 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M406" t="n">
         <v>152</v>
       </c>
       <c r="N406" t="n">
-        <v>1690.5971524664</v>
+        <v>1690.5969977427</v>
       </c>
       <c r="O406" t="n">
-        <v>256970.7671748928</v>
+        <v>256970.7436568904</v>
       </c>
       <c r="P406" t="n">
         <v>2900</v>
@@ -17896,22 +17896,22 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>1387</v>
+        <v>1327</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M407" t="n">
         <v>1327</v>
       </c>
       <c r="N407" t="n">
-        <v>1550.1936973199</v>
+        <v>1550.1936995315</v>
       </c>
       <c r="O407" t="n">
-        <v>2057107.036343507</v>
+        <v>2057107.0392783</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
@@ -17988,28 +17988,28 @@
         </is>
       </c>
       <c r="J409" t="n">
-        <v>874</v>
+        <v>823</v>
       </c>
       <c r="K409" t="n">
         <v>0</v>
       </c>
       <c r="L409" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M409" t="n">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="N409" t="n">
-        <v>2403.5120742613</v>
+        <v>2403.5121001364</v>
       </c>
       <c r="O409" t="n">
-        <v>1980493.949191311</v>
+        <v>1978090.458412257</v>
       </c>
       <c r="P409" t="n">
         <v>3500</v>
       </c>
       <c r="Q409" t="n">
-        <v>2884000</v>
+        <v>2880500</v>
       </c>
     </row>
     <row r="410">
@@ -18761,13 +18761,13 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M427" t="n">
         <v>8</v>
@@ -19304,13 +19304,13 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>110</v>
+        <v>326</v>
       </c>
       <c r="K439" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M439" t="n">
         <v>326</v>
@@ -19696,13 +19696,13 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>45</v>
+        <v>211</v>
       </c>
       <c r="K448" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="L448" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M448" t="n">
         <v>211</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="J489" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K489" t="n">
         <v>0</v>
@@ -21437,19 +21437,19 @@
         <v>0</v>
       </c>
       <c r="M489" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N489" t="n">
         <v>1958.73</v>
       </c>
       <c r="O489" t="n">
-        <v>17628.57</v>
+        <v>15669.84</v>
       </c>
       <c r="P489" t="n">
         <v>3400</v>
       </c>
       <c r="Q489" t="n">
-        <v>30600</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="490">
@@ -21556,28 +21556,28 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
       </c>
       <c r="L492" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="N492" t="n">
         <v>2567</v>
       </c>
       <c r="O492" t="n">
-        <v>572441</v>
+        <v>541637</v>
       </c>
       <c r="P492" t="n">
         <v>4500</v>
       </c>
       <c r="Q492" t="n">
-        <v>1003500</v>
+        <v>949500</v>
       </c>
     </row>
     <row r="493">
@@ -21802,7 +21802,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -21811,19 +21811,19 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N498" t="n">
         <v>2517.22</v>
       </c>
       <c r="O498" t="n">
-        <v>505961.22</v>
+        <v>500926.78</v>
       </c>
       <c r="P498" t="n">
         <v>4200</v>
       </c>
       <c r="Q498" t="n">
-        <v>844200</v>
+        <v>835800</v>
       </c>
     </row>
     <row r="499">
@@ -21925,13 +21925,13 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
       </c>
       <c r="L501" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M501" t="n">
         <v>437</v>
@@ -22507,7 +22507,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -22516,19 +22516,19 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="N515" t="n">
-        <v>2680.7396988322</v>
+        <v>2680.739695084</v>
       </c>
       <c r="O515" t="n">
-        <v>447683.5297049774</v>
+        <v>394068.735177348</v>
       </c>
       <c r="P515" t="n">
         <v>4900</v>
       </c>
       <c r="Q515" t="n">
-        <v>818300</v>
+        <v>720300</v>
       </c>
     </row>
     <row r="516">
@@ -24358,10 +24358,10 @@
         <v>50</v>
       </c>
       <c r="N558" t="n">
-        <v>11562.038474114</v>
+        <v>11562.038465753</v>
       </c>
       <c r="O558" t="n">
-        <v>578101.9237057001</v>
+        <v>578101.92328765</v>
       </c>
       <c r="P558" t="n">
         <v>18500</v>
@@ -24404,10 +24404,10 @@
         <v>58</v>
       </c>
       <c r="N559" t="n">
-        <v>13513.643059701</v>
+        <v>13513.643082707</v>
       </c>
       <c r="O559" t="n">
-        <v>783791.297462658</v>
+        <v>783791.298797006</v>
       </c>
       <c r="P559" t="n">
         <v>21900</v>
@@ -25549,13 +25549,13 @@
         </is>
       </c>
       <c r="J586" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K586" t="n">
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M586" t="n">
         <v>15</v>
@@ -25779,7 +25779,7 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="M591" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N591" t="n">
         <v>16974.69</v>
       </c>
       <c r="O591" t="n">
-        <v>1324025.82</v>
+        <v>1290076.44</v>
       </c>
       <c r="P591" t="n">
         <v>26900</v>
       </c>
       <c r="Q591" t="n">
-        <v>2098200</v>
+        <v>2044400</v>
       </c>
     </row>
     <row r="592">
@@ -25943,28 +25943,28 @@
         </is>
       </c>
       <c r="J595" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K595" t="n">
         <v>0</v>
       </c>
       <c r="L595" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M595" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N595" t="n">
         <v>4100.45</v>
       </c>
       <c r="O595" t="n">
-        <v>61506.75</v>
+        <v>49205.39999999999</v>
       </c>
       <c r="P595" t="n">
         <v>26900</v>
       </c>
       <c r="Q595" t="n">
-        <v>403500</v>
+        <v>322800</v>
       </c>
     </row>
     <row r="596">
@@ -26175,10 +26175,10 @@
         <v>68</v>
       </c>
       <c r="N600" t="n">
-        <v>1561.0009152542</v>
+        <v>1561.0009337861</v>
       </c>
       <c r="O600" t="n">
-        <v>106148.0622372856</v>
+        <v>106148.0634974548</v>
       </c>
       <c r="P600" t="n">
         <v>2900</v>
@@ -28265,10 +28265,10 @@
         <v>20</v>
       </c>
       <c r="N648" t="n">
-        <v>5218.170554855</v>
+        <v>5218.1705597964</v>
       </c>
       <c r="O648" t="n">
-        <v>104363.4110971</v>
+        <v>104363.411195928</v>
       </c>
       <c r="P648" t="n">
         <v>8500</v>
@@ -28311,10 +28311,10 @@
         <v>133</v>
       </c>
       <c r="N649" t="n">
-        <v>1595.0093634841</v>
+        <v>1595.0093515358</v>
       </c>
       <c r="O649" t="n">
-        <v>212136.2453433853</v>
+        <v>212136.2437542614</v>
       </c>
       <c r="P649" t="n">
         <v>2600</v>
@@ -28391,7 +28391,7 @@
         </is>
       </c>
       <c r="J651" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K651" t="n">
         <v>0</v>
@@ -28400,19 +28400,19 @@
         <v>0</v>
       </c>
       <c r="M651" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N651" t="n">
         <v>5194</v>
       </c>
       <c r="O651" t="n">
-        <v>244118</v>
+        <v>238924</v>
       </c>
       <c r="P651" t="n">
         <v>9000</v>
       </c>
       <c r="Q651" t="n">
-        <v>423000</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="652">
@@ -29133,7 +29133,7 @@
         </is>
       </c>
       <c r="J667" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K667" t="n">
         <v>0</v>
@@ -29142,19 +29142,19 @@
         <v>0</v>
       </c>
       <c r="M667" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N667" t="n">
         <v>55139</v>
       </c>
       <c r="O667" t="n">
-        <v>385973</v>
+        <v>330834</v>
       </c>
       <c r="P667" t="n">
         <v>89900</v>
       </c>
       <c r="Q667" t="n">
-        <v>629300</v>
+        <v>539400</v>
       </c>
     </row>
     <row r="668">
@@ -29179,7 +29179,7 @@
         </is>
       </c>
       <c r="J668" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K668" t="n">
         <v>0</v>
@@ -29188,19 +29188,19 @@
         <v>0</v>
       </c>
       <c r="M668" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N668" t="n">
         <v>63521</v>
       </c>
       <c r="O668" t="n">
-        <v>317605</v>
+        <v>254084</v>
       </c>
       <c r="P668" t="n">
         <v>105900</v>
       </c>
       <c r="Q668" t="n">
-        <v>529500</v>
+        <v>423600</v>
       </c>
     </row>
     <row r="669">
@@ -29409,13 +29409,13 @@
         </is>
       </c>
       <c r="J673" t="n">
-        <v>1400</v>
+        <v>1360</v>
       </c>
       <c r="K673" t="n">
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M673" t="n">
         <v>1360</v>
@@ -29455,13 +29455,13 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M674" t="n">
         <v>176</v>
@@ -30979,7 +30979,7 @@
         </is>
       </c>
       <c r="J707" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K707" t="n">
         <v>0</v>
@@ -30988,19 +30988,19 @@
         <v>0</v>
       </c>
       <c r="M707" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N707" t="n">
         <v>44055</v>
       </c>
       <c r="O707" t="n">
-        <v>1013265</v>
+        <v>969210</v>
       </c>
       <c r="P707" t="n">
         <v>70900</v>
       </c>
       <c r="Q707" t="n">
-        <v>1630700</v>
+        <v>1559800</v>
       </c>
     </row>
     <row r="708">
@@ -31209,7 +31209,7 @@
         </is>
       </c>
       <c r="J712" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K712" t="n">
         <v>0</v>
@@ -31218,19 +31218,19 @@
         <v>0</v>
       </c>
       <c r="M712" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N712" t="n">
         <v>13687</v>
       </c>
       <c r="O712" t="n">
-        <v>1300265</v>
+        <v>1286578</v>
       </c>
       <c r="P712" t="n">
         <v>21900</v>
       </c>
       <c r="Q712" t="n">
-        <v>2080500</v>
+        <v>2058600</v>
       </c>
     </row>
     <row r="713">
@@ -31577,7 +31577,7 @@
         </is>
       </c>
       <c r="J720" t="n">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="K720" t="n">
         <v>0</v>
@@ -31586,19 +31586,19 @@
         <v>0</v>
       </c>
       <c r="M720" t="n">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="N720" t="n">
         <v>8858.16</v>
       </c>
       <c r="O720" t="n">
-        <v>3047207.04</v>
+        <v>3020632.56</v>
       </c>
       <c r="P720" t="n">
         <v>15500</v>
       </c>
       <c r="Q720" t="n">
-        <v>5332000</v>
+        <v>5285500</v>
       </c>
     </row>
     <row r="721">
@@ -32771,7 +32771,7 @@
         </is>
       </c>
       <c r="J746" t="n">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="K746" t="n">
         <v>0</v>
@@ -32780,19 +32780,19 @@
         <v>0</v>
       </c>
       <c r="M746" t="n">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="N746" t="n">
         <v>4544</v>
       </c>
       <c r="O746" t="n">
-        <v>2162944</v>
+        <v>2053888</v>
       </c>
       <c r="P746" t="n">
         <v>7900</v>
       </c>
       <c r="Q746" t="n">
-        <v>3760400</v>
+        <v>3570800</v>
       </c>
     </row>
     <row r="747">
@@ -32863,7 +32863,7 @@
         </is>
       </c>
       <c r="J748" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K748" t="n">
         <v>0</v>
@@ -32872,19 +32872,19 @@
         <v>0</v>
       </c>
       <c r="M748" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N748" t="n">
         <v>13922</v>
       </c>
       <c r="O748" t="n">
-        <v>375894</v>
+        <v>361972</v>
       </c>
       <c r="P748" t="n">
         <v>22900</v>
       </c>
       <c r="Q748" t="n">
-        <v>618300</v>
+        <v>595400</v>
       </c>
     </row>
     <row r="749">
@@ -33093,7 +33093,7 @@
         </is>
       </c>
       <c r="J753" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="K753" t="n">
         <v>0</v>
@@ -33102,19 +33102,19 @@
         <v>0</v>
       </c>
       <c r="M753" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="N753" t="n">
         <v>13210</v>
       </c>
       <c r="O753" t="n">
-        <v>2060760</v>
+        <v>1981500</v>
       </c>
       <c r="P753" t="n">
         <v>23900</v>
       </c>
       <c r="Q753" t="n">
-        <v>3728400</v>
+        <v>3585000</v>
       </c>
     </row>
     <row r="754">
@@ -34284,7 +34284,7 @@
         </is>
       </c>
       <c r="J779" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K779" t="n">
         <v>0</v>
@@ -34293,19 +34293,19 @@
         <v>0</v>
       </c>
       <c r="M779" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N779" t="n">
         <v>7562</v>
       </c>
       <c r="O779" t="n">
-        <v>355414</v>
+        <v>347852</v>
       </c>
       <c r="P779" t="n">
         <v>12900</v>
       </c>
       <c r="Q779" t="n">
-        <v>606300</v>
+        <v>593400</v>
       </c>
     </row>
     <row r="780">
@@ -34655,13 +34655,13 @@
         </is>
       </c>
       <c r="J787" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="K787" t="n">
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M787" t="n">
         <v>600</v>
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="J802" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K802" t="n">
         <v>0</v>
@@ -35352,19 +35352,19 @@
         <v>0</v>
       </c>
       <c r="M802" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N802" t="n">
         <v>10755</v>
       </c>
       <c r="O802" t="n">
-        <v>860400</v>
+        <v>838890</v>
       </c>
       <c r="P802" t="n">
         <v>17900</v>
       </c>
       <c r="Q802" t="n">
-        <v>1432000</v>
+        <v>1396200</v>
       </c>
     </row>
     <row r="803">
@@ -35941,7 +35941,7 @@
         </is>
       </c>
       <c r="J815" t="n">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="K815" t="n">
         <v>0</v>
@@ -35950,19 +35950,19 @@
         <v>0</v>
       </c>
       <c r="M815" t="n">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="N815" t="n">
         <v>1326</v>
       </c>
       <c r="O815" t="n">
-        <v>1458600</v>
+        <v>1454622</v>
       </c>
       <c r="P815" t="n">
         <v>2500</v>
       </c>
       <c r="Q815" t="n">
-        <v>2750000</v>
+        <v>2742500</v>
       </c>
     </row>
     <row r="816">
@@ -35987,7 +35987,7 @@
         </is>
       </c>
       <c r="J816" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K816" t="n">
         <v>0</v>
@@ -35996,19 +35996,19 @@
         <v>0</v>
       </c>
       <c r="M816" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N816" t="n">
         <v>2573</v>
       </c>
       <c r="O816" t="n">
-        <v>357647</v>
+        <v>349928</v>
       </c>
       <c r="P816" t="n">
         <v>4500</v>
       </c>
       <c r="Q816" t="n">
-        <v>625500</v>
+        <v>612000</v>
       </c>
     </row>
     <row r="817">
@@ -36033,7 +36033,7 @@
         </is>
       </c>
       <c r="J817" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K817" t="n">
         <v>0</v>
@@ -36042,19 +36042,19 @@
         <v>0</v>
       </c>
       <c r="M817" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N817" t="n">
         <v>21762</v>
       </c>
       <c r="O817" t="n">
-        <v>282906</v>
+        <v>261144</v>
       </c>
       <c r="P817" t="n">
         <v>35900</v>
       </c>
       <c r="Q817" t="n">
-        <v>466700</v>
+        <v>430800</v>
       </c>
     </row>
     <row r="818">
@@ -36450,13 +36450,13 @@
         </is>
       </c>
       <c r="J826" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="K826" t="n">
         <v>0</v>
       </c>
       <c r="L826" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M826" t="n">
         <v>178</v>
@@ -36542,7 +36542,7 @@
         </is>
       </c>
       <c r="J828" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K828" t="n">
         <v>0</v>
@@ -36551,19 +36551,19 @@
         <v>0</v>
       </c>
       <c r="M828" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N828" t="n">
         <v>38252</v>
       </c>
       <c r="O828" t="n">
-        <v>688536</v>
+        <v>650284</v>
       </c>
       <c r="P828" t="n">
         <v>61900</v>
       </c>
       <c r="Q828" t="n">
-        <v>1114200</v>
+        <v>1052300</v>
       </c>
     </row>
     <row r="829">
@@ -36588,13 +36588,13 @@
         </is>
       </c>
       <c r="J829" t="n">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="K829" t="n">
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M829" t="n">
         <v>570</v>
@@ -36724,28 +36724,28 @@
         </is>
       </c>
       <c r="J832" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="K832" t="n">
         <v>0</v>
       </c>
       <c r="L832" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M832" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N832" t="n">
-        <v>2458.5130759032</v>
+        <v>2458.5130690113</v>
       </c>
       <c r="O832" t="n">
-        <v>740012.4358468632</v>
+        <v>737553.92070339</v>
       </c>
       <c r="P832" t="n">
         <v>3500</v>
       </c>
       <c r="Q832" t="n">
-        <v>1053500</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="833">
@@ -36862,13 +36862,13 @@
         </is>
       </c>
       <c r="J835" t="n">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="K835" t="n">
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M835" t="n">
         <v>381</v>
@@ -36908,13 +36908,13 @@
         </is>
       </c>
       <c r="J836" t="n">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="K836" t="n">
         <v>0</v>
       </c>
       <c r="L836" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M836" t="n">
         <v>597</v>
@@ -36954,13 +36954,13 @@
         </is>
       </c>
       <c r="J837" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="K837" t="n">
         <v>0</v>
       </c>
       <c r="L837" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M837" t="n">
         <v>5</v>
@@ -37058,10 +37058,10 @@
         <v>372</v>
       </c>
       <c r="N839" t="n">
-        <v>2108.792083045</v>
+        <v>2108.7921081831</v>
       </c>
       <c r="O839" t="n">
-        <v>784470.65489274</v>
+        <v>784470.6642441133</v>
       </c>
       <c r="P839" t="n">
         <v>2900</v>
@@ -37092,22 +37092,22 @@
         </is>
       </c>
       <c r="J840" t="n">
-        <v>881</v>
+        <v>809</v>
       </c>
       <c r="K840" t="n">
         <v>0</v>
       </c>
       <c r="L840" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M840" t="n">
         <v>809</v>
       </c>
       <c r="N840" t="n">
-        <v>2056.0829891304</v>
+        <v>2056.0829843644</v>
       </c>
       <c r="O840" t="n">
-        <v>1663371.138206494</v>
+        <v>1663371.1343508</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
@@ -37184,13 +37184,13 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M842" t="n">
         <v>437</v>
@@ -37611,10 +37611,10 @@
         <v>2</v>
       </c>
       <c r="N851" t="n">
-        <v>1906.1834782609</v>
+        <v>1906.1829245283</v>
       </c>
       <c r="O851" t="n">
-        <v>3812.3669565218</v>
+        <v>3812.3658490566</v>
       </c>
       <c r="P851" t="n">
         <v>2900</v>
@@ -37703,10 +37703,10 @@
         <v>61</v>
       </c>
       <c r="N853" t="n">
-        <v>2546.9838660907</v>
+        <v>2546.9837028825</v>
       </c>
       <c r="O853" t="n">
-        <v>155366.0158315327</v>
+        <v>155366.0058758325</v>
       </c>
       <c r="P853" t="n">
         <v>3900</v>
@@ -37829,7 +37829,7 @@
         </is>
       </c>
       <c r="J856" t="n">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K856" t="n">
         <v>0</v>
@@ -37838,19 +37838,19 @@
         <v>0</v>
       </c>
       <c r="M856" t="n">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N856" t="n">
         <v>1801</v>
       </c>
       <c r="O856" t="n">
-        <v>808649</v>
+        <v>805047</v>
       </c>
       <c r="P856" t="n">
         <v>2900</v>
       </c>
       <c r="Q856" t="n">
-        <v>1302100</v>
+        <v>1296300</v>
       </c>
     </row>
     <row r="857">
@@ -38661,7 +38661,7 @@
         </is>
       </c>
       <c r="J874" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K874" t="n">
         <v>0</v>
@@ -38670,19 +38670,19 @@
         <v>0</v>
       </c>
       <c r="M874" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N874" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O874" t="n">
-        <v>2576269.44</v>
+        <v>2558378.68</v>
       </c>
       <c r="P874" t="n">
         <v>14900</v>
       </c>
       <c r="Q874" t="n">
-        <v>4291200</v>
+        <v>4261400</v>
       </c>
     </row>
     <row r="875">
@@ -39346,7 +39346,7 @@
         </is>
       </c>
       <c r="J889" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K889" t="n">
         <v>0</v>
@@ -39355,19 +39355,19 @@
         <v>0</v>
       </c>
       <c r="M889" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N889" t="n">
         <v>2357.74</v>
       </c>
       <c r="O889" t="n">
-        <v>223985.3</v>
+        <v>216912.08</v>
       </c>
       <c r="P889" t="n">
         <v>3000</v>
       </c>
       <c r="Q889" t="n">
-        <v>285000</v>
+        <v>276000</v>
       </c>
     </row>
     <row r="890">
@@ -39480,28 +39480,28 @@
         </is>
       </c>
       <c r="J892" t="n">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="K892" t="n">
         <v>0</v>
       </c>
       <c r="L892" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M892" t="n">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="N892" t="n">
         <v>1828.64</v>
       </c>
       <c r="O892" t="n">
-        <v>1205073.76</v>
+        <v>1194101.92</v>
       </c>
       <c r="P892" t="n">
         <v>2000</v>
       </c>
       <c r="Q892" t="n">
-        <v>1318000</v>
+        <v>1306000</v>
       </c>
     </row>
     <row r="893">
@@ -40737,10 +40737,10 @@
         <v>60</v>
       </c>
       <c r="N920" t="n">
-        <v>4032.3968461538</v>
+        <v>4032.3968380463</v>
       </c>
       <c r="O920" t="n">
-        <v>241943.810769228</v>
+        <v>241943.810282778</v>
       </c>
       <c r="P920" t="n">
         <v>4200</v>
@@ -40818,22 +40818,22 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>2856</v>
+        <v>2801</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M922" t="n">
         <v>2801</v>
       </c>
       <c r="N922" t="n">
-        <v>517.28990087531</v>
+        <v>517.2899423715</v>
       </c>
       <c r="O922" t="n">
-        <v>1448929.012351743</v>
+        <v>1448929.128582572</v>
       </c>
       <c r="P922" t="n">
         <v>900</v>
@@ -41044,7 +41044,7 @@
         </is>
       </c>
       <c r="J927" t="n">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="K927" t="n">
         <v>0</v>
@@ -41053,19 +41053,19 @@
         <v>0</v>
       </c>
       <c r="M927" t="n">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="N927" t="n">
-        <v>3110.8414032101</v>
+        <v>3110.8413822526</v>
       </c>
       <c r="O927" t="n">
-        <v>1807398.855265068</v>
+        <v>1776290.429266235</v>
       </c>
       <c r="P927" t="n">
         <v>4500</v>
       </c>
       <c r="Q927" t="n">
-        <v>2614500</v>
+        <v>2569500</v>
       </c>
     </row>
     <row r="928">
@@ -41266,28 +41266,28 @@
         </is>
       </c>
       <c r="J932" t="n">
-        <v>1077</v>
+        <v>1005</v>
       </c>
       <c r="K932" t="n">
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M932" t="n">
-        <v>1053</v>
+        <v>1005</v>
       </c>
       <c r="N932" t="n">
-        <v>703.79516919374</v>
+        <v>703.79516599434</v>
       </c>
       <c r="O932" t="n">
-        <v>741096.3131610082</v>
+        <v>707314.1418243117</v>
       </c>
       <c r="P932" t="n">
         <v>900</v>
       </c>
       <c r="Q932" t="n">
-        <v>947700</v>
+        <v>904500</v>
       </c>
     </row>
     <row r="933">
@@ -41806,13 +41806,13 @@
         </is>
       </c>
       <c r="J944" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K944" t="n">
         <v>0</v>
       </c>
       <c r="L944" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M944" t="n">
         <v>61</v>
@@ -42323,13 +42323,13 @@
         </is>
       </c>
       <c r="J956" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="K956" t="n">
         <v>0</v>
       </c>
       <c r="L956" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M956" t="n">
         <v>15</v>
@@ -44858,7 +44858,7 @@
         </is>
       </c>
       <c r="J1010" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K1010" t="n">
         <v>0</v>
@@ -44867,19 +44867,19 @@
         <v>0</v>
       </c>
       <c r="M1010" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N1010" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1010" t="n">
-        <v>2287816.18</v>
+        <v>2263477.71</v>
       </c>
       <c r="P1010" t="n">
         <v>27900</v>
       </c>
       <c r="Q1010" t="n">
-        <v>2622600</v>
+        <v>2594700</v>
       </c>
     </row>
     <row r="1011">
@@ -45471,7 +45471,7 @@
         </is>
       </c>
       <c r="J1023" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K1023" t="n">
         <v>0</v>
@@ -45480,19 +45480,19 @@
         <v>0</v>
       </c>
       <c r="M1023" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N1023" t="n">
         <v>2010.71</v>
       </c>
       <c r="O1023" t="n">
-        <v>32171.36</v>
+        <v>10053.55</v>
       </c>
       <c r="P1023" t="n">
         <v>7200</v>
       </c>
       <c r="Q1023" t="n">
-        <v>115200</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="1024">
@@ -45667,7 +45667,7 @@
         </is>
       </c>
       <c r="J1027" t="n">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="K1027" t="n">
         <v>0</v>
@@ -45676,7 +45676,7 @@
         <v>0</v>
       </c>
       <c r="M1027" t="n">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="N1027" t="n">
         <v>0</v>
@@ -45688,7 +45688,7 @@
         <v>6500</v>
       </c>
       <c r="Q1027" t="n">
-        <v>15613000</v>
+        <v>15600000</v>
       </c>
     </row>
     <row r="1028">
@@ -47331,13 +47331,13 @@
         </is>
       </c>
       <c r="J1066" t="n">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="K1066" t="n">
         <v>0</v>
       </c>
       <c r="L1066" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M1066" t="n">
         <v>107</v>
@@ -47375,28 +47375,28 @@
         </is>
       </c>
       <c r="J1067" t="n">
-        <v>273</v>
+        <v>443</v>
       </c>
       <c r="K1067" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L1067" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M1067" t="n">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="N1067" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1067" t="n">
-        <v>1428673.1</v>
+        <v>1409581.7</v>
       </c>
       <c r="P1067" t="n">
         <v>5100</v>
       </c>
       <c r="Q1067" t="n">
-        <v>2289900</v>
+        <v>2259300</v>
       </c>
     </row>
     <row r="1068">
@@ -47513,10 +47513,10 @@
         <v>175</v>
       </c>
       <c r="N1070" t="n">
-        <v>1794.2879692219</v>
+        <v>1794.2879686376</v>
       </c>
       <c r="O1070" t="n">
-        <v>314000.3946138325</v>
+        <v>314000.39451158</v>
       </c>
       <c r="P1070" t="n">
         <v>1600</v>
@@ -47865,10 +47865,10 @@
         <v>40</v>
       </c>
       <c r="N1078" t="n">
-        <v>2523.3377470356</v>
+        <v>2523.3377457627</v>
       </c>
       <c r="O1078" t="n">
-        <v>100933.509881424</v>
+        <v>100933.509830508</v>
       </c>
       <c r="P1078" t="n">
         <v>2800</v>
@@ -48529,7 +48529,7 @@
         </is>
       </c>
       <c r="J1094" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K1094" t="n">
         <v>0</v>
@@ -48538,19 +48538,19 @@
         <v>0</v>
       </c>
       <c r="M1094" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N1094" t="n">
         <v>5077</v>
       </c>
       <c r="O1094" t="n">
-        <v>604163</v>
+        <v>599086</v>
       </c>
       <c r="P1094" t="n">
         <v>8500</v>
       </c>
       <c r="Q1094" t="n">
-        <v>1011500</v>
+        <v>1003000</v>
       </c>
     </row>
     <row r="1095">
@@ -49429,7 +49429,7 @@
         </is>
       </c>
       <c r="J1114" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K1114" t="n">
         <v>0</v>
@@ -49438,19 +49438,19 @@
         <v>0</v>
       </c>
       <c r="M1114" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N1114" t="n">
         <v>7480</v>
       </c>
       <c r="O1114" t="n">
-        <v>104720</v>
+        <v>97240</v>
       </c>
       <c r="P1114" t="n">
         <v>9500</v>
       </c>
       <c r="Q1114" t="n">
-        <v>133000</v>
+        <v>123500</v>
       </c>
     </row>
     <row r="1115">
@@ -49521,7 +49521,7 @@
         </is>
       </c>
       <c r="J1116" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K1116" t="n">
         <v>0</v>
@@ -49530,19 +49530,19 @@
         <v>0</v>
       </c>
       <c r="M1116" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N1116" t="n">
         <v>5280</v>
       </c>
       <c r="O1116" t="n">
-        <v>749760</v>
+        <v>739200</v>
       </c>
       <c r="P1116" t="n">
         <v>6900</v>
       </c>
       <c r="Q1116" t="n">
-        <v>979800</v>
+        <v>966000</v>
       </c>
     </row>
     <row r="1117">
@@ -49613,28 +49613,28 @@
         </is>
       </c>
       <c r="J1118" t="n">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="K1118" t="n">
         <v>0</v>
       </c>
       <c r="L1118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M1118" t="n">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="N1118" t="n">
         <v>1584</v>
       </c>
       <c r="O1118" t="n">
-        <v>286704</v>
+        <v>248688</v>
       </c>
       <c r="P1118" t="n">
         <v>2000</v>
       </c>
       <c r="Q1118" t="n">
-        <v>362000</v>
+        <v>314000</v>
       </c>
     </row>
     <row r="1119">
@@ -49751,28 +49751,28 @@
         </is>
       </c>
       <c r="J1121" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K1121" t="n">
         <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1121" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N1121" t="n">
         <v>4400</v>
       </c>
       <c r="O1121" t="n">
-        <v>510400</v>
+        <v>506000</v>
       </c>
       <c r="P1121" t="n">
         <v>5900</v>
       </c>
       <c r="Q1121" t="n">
-        <v>684400</v>
+        <v>678500</v>
       </c>
     </row>
     <row r="1122">
@@ -49797,28 +49797,28 @@
         </is>
       </c>
       <c r="J1122" t="n">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="K1122" t="n">
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M1122" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N1122" t="n">
         <v>3520</v>
       </c>
       <c r="O1122" t="n">
-        <v>559680</v>
+        <v>552640</v>
       </c>
       <c r="P1122" t="n">
         <v>4500</v>
       </c>
       <c r="Q1122" t="n">
-        <v>715500</v>
+        <v>706500</v>
       </c>
     </row>
     <row r="1123">
@@ -49981,13 +49981,13 @@
         </is>
       </c>
       <c r="J1126" t="n">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="K1126" t="n">
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1126" t="n">
         <v>558</v>
@@ -50027,13 +50027,13 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
       </c>
       <c r="L1127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1127" t="n">
         <v>171</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1301,22 +1301,22 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.307345576</v>
+        <v>1811.3074074074</v>
       </c>
       <c r="O22" t="n">
-        <v>597731.42404008</v>
+        <v>579618.370370368</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
       </c>
       <c r="Q22" t="n">
-        <v>858000</v>
+        <v>832000</v>
       </c>
     </row>
     <row r="23">
@@ -2996,10 +2996,10 @@
         <v>44</v>
       </c>
       <c r="N64" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O64" t="n">
-        <v>172780.8322654216</v>
+        <v>172780.8321991708</v>
       </c>
       <c r="P64" t="n">
         <v>4800</v>
@@ -4985,10 +4985,10 @@
         <v>28</v>
       </c>
       <c r="N111" t="n">
-        <v>15711.965922747</v>
+        <v>15711.965905172</v>
       </c>
       <c r="O111" t="n">
-        <v>439935.045836916</v>
+        <v>439935.045344816</v>
       </c>
       <c r="P111" t="n">
         <v>28500</v>
@@ -10256,10 +10256,10 @@
         <v>493</v>
       </c>
       <c r="N233" t="n">
-        <v>1098.0597873486</v>
+        <v>1098.0598890693</v>
       </c>
       <c r="O233" t="n">
-        <v>541343.4751628598</v>
+        <v>541343.5253111649</v>
       </c>
       <c r="P233" t="n">
         <v>1500</v>
@@ -12498,10 +12498,10 @@
         <v>689</v>
       </c>
       <c r="N285" t="n">
-        <v>3158.8608262318</v>
+        <v>3160.2538267431</v>
       </c>
       <c r="O285" t="n">
-        <v>2176455.10927371</v>
+        <v>2177414.886625996</v>
       </c>
       <c r="P285" t="n">
         <v>5600</v>
@@ -12590,10 +12590,10 @@
         <v>12</v>
       </c>
       <c r="N287" t="n">
-        <v>3841.6248214286</v>
+        <v>3856.9300996016</v>
       </c>
       <c r="O287" t="n">
-        <v>46099.4978571432</v>
+        <v>46283.1611952192</v>
       </c>
       <c r="P287" t="n">
         <v>6900</v>
@@ -12801,13 +12801,13 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>872</v>
+        <v>908</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M292" t="n">
         <v>872</v>
@@ -13026,13 +13026,13 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>392</v>
+        <v>452</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M297" t="n">
         <v>392</v>
@@ -13762,22 +13762,22 @@
         <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M313" t="n">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="N313" t="n">
         <v>1203.38</v>
       </c>
       <c r="O313" t="n">
-        <v>866433.6000000001</v>
+        <v>855603.1800000001</v>
       </c>
       <c r="P313" t="n">
         <v>1900</v>
       </c>
       <c r="Q313" t="n">
-        <v>1368000</v>
+        <v>1350900</v>
       </c>
     </row>
     <row r="314">
@@ -14340,22 +14340,22 @@
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M326" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N326" t="n">
         <v>10716.34</v>
       </c>
       <c r="O326" t="n">
-        <v>364355.56</v>
+        <v>353639.22</v>
       </c>
       <c r="P326" t="n">
         <v>39000</v>
       </c>
       <c r="Q326" t="n">
-        <v>1326000</v>
+        <v>1287000</v>
       </c>
     </row>
     <row r="327">
@@ -14559,10 +14559,10 @@
         <v>40</v>
       </c>
       <c r="N331" t="n">
-        <v>3594.254</v>
+        <v>3594.2539962477</v>
       </c>
       <c r="O331" t="n">
-        <v>143770.16</v>
+        <v>143770.159849908</v>
       </c>
       <c r="P331" t="n">
         <v>6500</v>
@@ -14716,13 +14716,13 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M335" t="n">
         <v>129</v>
@@ -14954,10 +14954,10 @@
         <v>767</v>
       </c>
       <c r="N340" t="n">
-        <v>2090.85</v>
+        <v>2091.1308394896</v>
       </c>
       <c r="O340" t="n">
-        <v>1603681.95</v>
+        <v>1603897.353888523</v>
       </c>
       <c r="P340" t="n">
         <v>2900</v>
@@ -15572,10 +15572,10 @@
         <v>204</v>
       </c>
       <c r="N354" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O354" t="n">
-        <v>891931.0012326036</v>
+        <v>891931.0012441092</v>
       </c>
       <c r="P354" t="n">
         <v>7500</v>
@@ -15662,10 +15662,10 @@
         <v>2</v>
       </c>
       <c r="N356" t="n">
-        <v>1592.5667254408</v>
+        <v>1600.6713740458</v>
       </c>
       <c r="O356" t="n">
-        <v>3185.1334508816</v>
+        <v>3201.3427480916</v>
       </c>
       <c r="P356" t="n">
         <v>3900</v>
@@ -16179,22 +16179,22 @@
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M368" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="N368" t="n">
         <v>6242.93</v>
       </c>
       <c r="O368" t="n">
-        <v>468219.75</v>
+        <v>393304.59</v>
       </c>
       <c r="P368" t="n">
         <v>10400</v>
       </c>
       <c r="Q368" t="n">
-        <v>780000</v>
+        <v>655200</v>
       </c>
     </row>
     <row r="369">
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="J378" t="n">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="K378" t="n">
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M378" t="n">
         <v>302</v>
@@ -16700,13 +16700,13 @@
         </is>
       </c>
       <c r="J380" t="n">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="K380" t="n">
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M380" t="n">
         <v>394</v>
@@ -17112,10 +17112,10 @@
         <v>64</v>
       </c>
       <c r="N389" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="O389" t="n">
-        <v>240742.4</v>
+        <v>241624.2402930432</v>
       </c>
       <c r="P389" t="n">
         <v>6900</v>
@@ -17717,22 +17717,22 @@
         </is>
       </c>
       <c r="J403" t="n">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="K403" t="n">
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M403" t="n">
         <v>537</v>
       </c>
       <c r="N403" t="n">
-        <v>1630.9236471425</v>
+        <v>1630.9236566809</v>
       </c>
       <c r="O403" t="n">
-        <v>875805.9985155225</v>
+        <v>875806.0036376433</v>
       </c>
       <c r="P403" t="n">
         <v>2500</v>
@@ -17862,10 +17862,10 @@
         <v>152</v>
       </c>
       <c r="N406" t="n">
-        <v>1690.5969977427</v>
+        <v>1690.5969630746</v>
       </c>
       <c r="O406" t="n">
-        <v>256970.7436568904</v>
+        <v>256970.7383873392</v>
       </c>
       <c r="P406" t="n">
         <v>2900</v>
@@ -17896,28 +17896,28 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>1327</v>
+        <v>1351</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M407" t="n">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="N407" t="n">
-        <v>1550.1936995315</v>
+        <v>1550.1937050719</v>
       </c>
       <c r="O407" t="n">
-        <v>2057107.0392783</v>
+        <v>2044705.496989836</v>
       </c>
       <c r="P407" t="n">
         <v>2500</v>
       </c>
       <c r="Q407" t="n">
-        <v>3317500</v>
+        <v>3297500</v>
       </c>
     </row>
     <row r="408">
@@ -17954,10 +17954,10 @@
         <v>3</v>
       </c>
       <c r="N408" t="n">
-        <v>1579.3904266667</v>
+        <v>1579.3903753351</v>
       </c>
       <c r="O408" t="n">
-        <v>4738.171280000101</v>
+        <v>4738.1711260053</v>
       </c>
       <c r="P408" t="n">
         <v>2900</v>
@@ -18000,10 +18000,10 @@
         <v>823</v>
       </c>
       <c r="N409" t="n">
-        <v>2403.5121001364</v>
+        <v>2403.5121166602</v>
       </c>
       <c r="O409" t="n">
-        <v>1978090.458412257</v>
+        <v>1978090.472011345</v>
       </c>
       <c r="P409" t="n">
         <v>3500</v>
@@ -19304,13 +19304,13 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>326</v>
+        <v>398</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M439" t="n">
         <v>326</v>
@@ -19696,13 +19696,13 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>211</v>
+        <v>256</v>
       </c>
       <c r="K448" t="n">
         <v>0</v>
       </c>
       <c r="L448" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M448" t="n">
         <v>211</v>
@@ -21556,13 +21556,13 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
       </c>
       <c r="L492" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M492" t="n">
         <v>211</v>
@@ -21925,13 +21925,13 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
       </c>
       <c r="L501" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M501" t="n">
         <v>437</v>
@@ -22519,10 +22519,10 @@
         <v>147</v>
       </c>
       <c r="N515" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O515" t="n">
-        <v>394068.735177348</v>
+        <v>394068.7351494327</v>
       </c>
       <c r="P515" t="n">
         <v>4900</v>
@@ -26175,10 +26175,10 @@
         <v>68</v>
       </c>
       <c r="N600" t="n">
-        <v>1561.0009337861</v>
+        <v>1561.000952381</v>
       </c>
       <c r="O600" t="n">
-        <v>106148.0634974548</v>
+        <v>106148.064761908</v>
       </c>
       <c r="P600" t="n">
         <v>2900</v>
@@ -27897,10 +27897,10 @@
         <v>66</v>
       </c>
       <c r="N640" t="n">
-        <v>3113.8900274725</v>
+        <v>3113.8900276243</v>
       </c>
       <c r="O640" t="n">
-        <v>205516.741813185</v>
+        <v>205516.7418232038</v>
       </c>
       <c r="P640" t="n">
         <v>5000</v>
@@ -28357,10 +28357,10 @@
         <v>75</v>
       </c>
       <c r="N650" t="n">
-        <v>3610.6500258732</v>
+        <v>3610.6500261438</v>
       </c>
       <c r="O650" t="n">
-        <v>270798.75194049</v>
+        <v>270798.751960785</v>
       </c>
       <c r="P650" t="n">
         <v>5800</v>
@@ -29409,13 +29409,13 @@
         </is>
       </c>
       <c r="J673" t="n">
-        <v>1360</v>
+        <v>1384</v>
       </c>
       <c r="K673" t="n">
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M673" t="n">
         <v>1360</v>
@@ -29455,13 +29455,13 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M674" t="n">
         <v>176</v>
@@ -33013,10 +33013,10 @@
         <v>16</v>
       </c>
       <c r="N751" t="n">
-        <v>4907.822092257</v>
+        <v>4956.8186522463</v>
       </c>
       <c r="O751" t="n">
-        <v>78525.153476112</v>
+        <v>79309.0984359408</v>
       </c>
       <c r="P751" t="n">
         <v>8200</v>
@@ -36588,13 +36588,13 @@
         </is>
       </c>
       <c r="J829" t="n">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="K829" t="n">
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M829" t="n">
         <v>570</v>
@@ -36724,13 +36724,13 @@
         </is>
       </c>
       <c r="J832" t="n">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="K832" t="n">
         <v>0</v>
       </c>
       <c r="L832" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M832" t="n">
         <v>300</v>
@@ -36862,13 +36862,13 @@
         </is>
       </c>
       <c r="J835" t="n">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="K835" t="n">
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M835" t="n">
         <v>381</v>
@@ -36920,10 +36920,10 @@
         <v>597</v>
       </c>
       <c r="N836" t="n">
-        <v>1803.0156237558</v>
+        <v>1803.0156368474</v>
       </c>
       <c r="O836" t="n">
-        <v>1076400.327382213</v>
+        <v>1076400.335197898</v>
       </c>
       <c r="P836" t="n">
         <v>2500</v>
@@ -36954,22 +36954,22 @@
         </is>
       </c>
       <c r="J837" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="K837" t="n">
         <v>0</v>
       </c>
       <c r="L837" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M837" t="n">
         <v>5</v>
       </c>
       <c r="N837" t="n">
-        <v>3306.5946745562</v>
+        <v>3306.5946666667</v>
       </c>
       <c r="O837" t="n">
-        <v>16532.973372781</v>
+        <v>16532.9733333335</v>
       </c>
       <c r="P837" t="n">
         <v>4900</v>
@@ -37092,22 +37092,22 @@
         </is>
       </c>
       <c r="J840" t="n">
-        <v>809</v>
+        <v>881</v>
       </c>
       <c r="K840" t="n">
         <v>0</v>
       </c>
       <c r="L840" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M840" t="n">
         <v>809</v>
       </c>
       <c r="N840" t="n">
-        <v>2056.0829843644</v>
+        <v>2056.0829819789</v>
       </c>
       <c r="O840" t="n">
-        <v>1663371.1343508</v>
+        <v>1663371.13242093</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
@@ -37196,10 +37196,10 @@
         <v>437</v>
       </c>
       <c r="N842" t="n">
-        <v>1655.9308045213</v>
+        <v>1655.9307861426</v>
       </c>
       <c r="O842" t="n">
-        <v>723641.7615758081</v>
+        <v>723641.7535443162</v>
       </c>
       <c r="P842" t="n">
         <v>2500</v>
@@ -37611,10 +37611,10 @@
         <v>2</v>
       </c>
       <c r="N851" t="n">
-        <v>1906.1829245283</v>
+        <v>1906.1827536232</v>
       </c>
       <c r="O851" t="n">
-        <v>3812.3658490566</v>
+        <v>3812.3655072464</v>
       </c>
       <c r="P851" t="n">
         <v>2900</v>
@@ -39132,10 +39132,10 @@
         <v>3</v>
       </c>
       <c r="N884" t="n">
-        <v>3629.36</v>
+        <v>3642.7032352941</v>
       </c>
       <c r="O884" t="n">
-        <v>10888.08</v>
+        <v>10928.1097058823</v>
       </c>
       <c r="P884" t="n">
         <v>3900</v>
@@ -40818,22 +40818,22 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>2801</v>
+        <v>2849</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M922" t="n">
         <v>2801</v>
       </c>
       <c r="N922" t="n">
-        <v>517.2899423715</v>
+        <v>517.28997081144</v>
       </c>
       <c r="O922" t="n">
-        <v>1448929.128582572</v>
+        <v>1448929.208242843</v>
       </c>
       <c r="P922" t="n">
         <v>900</v>
@@ -41056,10 +41056,10 @@
         <v>571</v>
       </c>
       <c r="N927" t="n">
-        <v>3110.8413822526</v>
+        <v>3110.8413717354</v>
       </c>
       <c r="O927" t="n">
-        <v>1776290.429266235</v>
+        <v>1776290.423260913</v>
       </c>
       <c r="P927" t="n">
         <v>4500</v>
@@ -41266,22 +41266,22 @@
         </is>
       </c>
       <c r="J932" t="n">
-        <v>1005</v>
+        <v>1029</v>
       </c>
       <c r="K932" t="n">
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M932" t="n">
         <v>1005</v>
       </c>
       <c r="N932" t="n">
-        <v>703.79516599434</v>
+        <v>703.79516401441</v>
       </c>
       <c r="O932" t="n">
-        <v>707314.1418243117</v>
+        <v>707314.1398344821</v>
       </c>
       <c r="P932" t="n">
         <v>900</v>
@@ -41551,10 +41551,10 @@
         <v>3</v>
       </c>
       <c r="N938" t="n">
-        <v>2501.3849767442</v>
+        <v>2501.384953271</v>
       </c>
       <c r="O938" t="n">
-        <v>7504.154930232599</v>
+        <v>7504.154859813</v>
       </c>
       <c r="P938" t="n">
         <v>4100</v>
@@ -42323,13 +42323,13 @@
         </is>
       </c>
       <c r="J956" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="K956" t="n">
         <v>0</v>
       </c>
       <c r="L956" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M956" t="n">
         <v>15</v>
@@ -42860,10 +42860,10 @@
         <v>3</v>
       </c>
       <c r="N967" t="n">
-        <v>2098.4050144928</v>
+        <v>2110.6406122449</v>
       </c>
       <c r="O967" t="n">
-        <v>6295.2150434784</v>
+        <v>6331.921836734699</v>
       </c>
       <c r="P967" t="n">
         <v>9500</v>
@@ -43095,10 +43095,10 @@
         <v>1283</v>
       </c>
       <c r="N972" t="n">
-        <v>3063.6219074262</v>
+        <v>3063.621911315</v>
       </c>
       <c r="O972" t="n">
-        <v>3930626.907227815</v>
+        <v>3930626.912217145</v>
       </c>
       <c r="P972" t="n">
         <v>3500</v>
@@ -47375,13 +47375,13 @@
         </is>
       </c>
       <c r="J1067" t="n">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="K1067" t="n">
         <v>0</v>
       </c>
       <c r="L1067" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1067" t="n">
         <v>443</v>
@@ -49481,22 +49481,22 @@
         <v>0</v>
       </c>
       <c r="L1115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1115" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="N1115" t="n">
         <v>6336</v>
       </c>
       <c r="O1115" t="n">
-        <v>646272</v>
+        <v>620928</v>
       </c>
       <c r="P1115" t="n">
         <v>7500</v>
       </c>
       <c r="Q1115" t="n">
-        <v>765000</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="1116">
@@ -49533,10 +49533,10 @@
         <v>140</v>
       </c>
       <c r="N1116" t="n">
-        <v>5280</v>
+        <v>5305.2631578947</v>
       </c>
       <c r="O1116" t="n">
-        <v>739200</v>
+        <v>742736.842105258</v>
       </c>
       <c r="P1116" t="n">
         <v>6900</v>
@@ -49579,10 +49579,10 @@
         <v>164</v>
       </c>
       <c r="N1117" t="n">
-        <v>5280</v>
+        <v>5301.8181818182</v>
       </c>
       <c r="O1117" t="n">
-        <v>865920</v>
+        <v>869498.1818181848</v>
       </c>
       <c r="P1117" t="n">
         <v>6900</v>
@@ -49987,22 +49987,22 @@
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M1126" t="n">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="N1126" t="n">
         <v>2288</v>
       </c>
       <c r="O1126" t="n">
-        <v>1276704</v>
+        <v>1242384</v>
       </c>
       <c r="P1126" t="n">
         <v>2900</v>
       </c>
       <c r="Q1126" t="n">
-        <v>1618200</v>
+        <v>1574700</v>
       </c>
     </row>
     <row r="1127">
@@ -52902,10 +52902,10 @@
         <v>44</v>
       </c>
       <c r="N1190" t="n">
-        <v>2403.9772262774</v>
+        <v>2403.9772058824</v>
       </c>
       <c r="O1190" t="n">
-        <v>105774.9979562056</v>
+        <v>105774.9970588256</v>
       </c>
       <c r="P1190" t="n">
         <v>3000</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -33013,10 +33013,10 @@
         <v>16</v>
       </c>
       <c r="N751" t="n">
-        <v>4956.8186522463</v>
+        <v>4907.8221131448</v>
       </c>
       <c r="O751" t="n">
-        <v>79309.0984359408</v>
+        <v>78525.1538103168</v>
       </c>
       <c r="P751" t="n">
         <v>8200</v>
@@ -39132,10 +39132,10 @@
         <v>3</v>
       </c>
       <c r="N884" t="n">
-        <v>3642.7032352941</v>
+        <v>3629.36</v>
       </c>
       <c r="O884" t="n">
-        <v>10928.1097058823</v>
+        <v>10888.08</v>
       </c>
       <c r="P884" t="n">
         <v>3900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -691,10 +691,10 @@
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>96741.407702703</v>
+        <v>96741.42375</v>
       </c>
       <c r="O7" t="n">
-        <v>290224.223108109</v>
+        <v>290224.27125</v>
       </c>
       <c r="P7" t="n">
         <v>188900</v>
@@ -1307,10 +1307,10 @@
         <v>303</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.3076124567</v>
+        <v>1811.3076256499</v>
       </c>
       <c r="O22" t="n">
-        <v>548826.2065743802</v>
+        <v>548826.2105719197</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
@@ -3241,10 +3241,10 @@
         <v>74</v>
       </c>
       <c r="N70" t="n">
-        <v>2474.7041355932</v>
+        <v>2474.7040753425</v>
       </c>
       <c r="O70" t="n">
-        <v>183128.1060338968</v>
+        <v>183128.101575345</v>
       </c>
       <c r="P70" t="n">
         <v>4500</v>
@@ -4904,10 +4904,10 @@
         <v>16</v>
       </c>
       <c r="N109" t="n">
-        <v>16486.40875</v>
+        <v>16486.408661417</v>
       </c>
       <c r="O109" t="n">
-        <v>263782.54</v>
+        <v>263782.538582672</v>
       </c>
       <c r="P109" t="n">
         <v>30500</v>
@@ -10210,10 +10210,10 @@
         <v>493</v>
       </c>
       <c r="N232" t="n">
-        <v>1098.0599864057</v>
+        <v>1098.0603685231</v>
       </c>
       <c r="O232" t="n">
-        <v>541343.5732980102</v>
+        <v>541343.7616818883</v>
       </c>
       <c r="P232" t="n">
         <v>1500</v>
@@ -12017,10 +12017,10 @@
         <v>200</v>
       </c>
       <c r="N274" t="n">
-        <v>2582.2556363636</v>
+        <v>2582.2556074972</v>
       </c>
       <c r="O274" t="n">
-        <v>516451.12727272</v>
+        <v>516451.12149944</v>
       </c>
       <c r="P274" t="n">
         <v>4500</v>
@@ -12109,10 +12109,10 @@
         <v>143</v>
       </c>
       <c r="N276" t="n">
-        <v>5216.8960979122</v>
+        <v>5216.8960939752</v>
       </c>
       <c r="O276" t="n">
-        <v>746016.1420014446</v>
+        <v>746016.1414384536</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -13627,10 +13627,10 @@
         <v>33</v>
       </c>
       <c r="N310" t="n">
-        <v>4890.9300489297</v>
+        <v>4890.9300489596</v>
       </c>
       <c r="O310" t="n">
-        <v>161400.6916146801</v>
+        <v>161400.6916156668</v>
       </c>
       <c r="P310" t="n">
         <v>8200</v>
@@ -13716,22 +13716,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M312" t="n">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="N312" t="n">
         <v>1203.38</v>
       </c>
       <c r="O312" t="n">
-        <v>809874.7400000001</v>
+        <v>801451.0800000001</v>
       </c>
       <c r="P312" t="n">
         <v>1900</v>
       </c>
       <c r="Q312" t="n">
-        <v>1278700</v>
+        <v>1265400</v>
       </c>
     </row>
     <row r="313">
@@ -14513,10 +14513,10 @@
         <v>36</v>
       </c>
       <c r="N330" t="n">
-        <v>3594.2539736347</v>
+        <v>3594.2539698492</v>
       </c>
       <c r="O330" t="n">
-        <v>129393.1430508492</v>
+        <v>129393.1429145712</v>
       </c>
       <c r="P330" t="n">
         <v>6500</v>
@@ -14682,10 +14682,10 @@
         <v>129</v>
       </c>
       <c r="N334" t="n">
-        <v>3240.8500374532</v>
+        <v>3240.850037594</v>
       </c>
       <c r="O334" t="n">
-        <v>418069.6548314628</v>
+        <v>418069.6548496259</v>
       </c>
       <c r="P334" t="n">
         <v>5200</v>
@@ -14858,22 +14858,22 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M338" t="n">
-        <v>1646</v>
+        <v>1636</v>
       </c>
       <c r="N338" t="n">
-        <v>616.01871898278</v>
+        <v>616.01871837471</v>
       </c>
       <c r="O338" t="n">
-        <v>1013966.811445656</v>
+        <v>1007806.623261026</v>
       </c>
       <c r="P338" t="n">
         <v>800</v>
       </c>
       <c r="Q338" t="n">
-        <v>1316800</v>
+        <v>1308800</v>
       </c>
     </row>
     <row r="339">
@@ -14902,22 +14902,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="M339" t="n">
-        <v>723</v>
+        <v>415</v>
       </c>
       <c r="N339" t="n">
         <v>2090.85</v>
       </c>
       <c r="O339" t="n">
-        <v>1511684.55</v>
+        <v>867702.75</v>
       </c>
       <c r="P339" t="n">
         <v>2900</v>
       </c>
       <c r="Q339" t="n">
-        <v>2096700</v>
+        <v>1203500</v>
       </c>
     </row>
     <row r="340">
@@ -15439,10 +15439,10 @@
         <v>426</v>
       </c>
       <c r="N351" t="n">
-        <v>3041.6600134228</v>
+        <v>3041.660013459</v>
       </c>
       <c r="O351" t="n">
-        <v>1295747.165718113</v>
+        <v>1295747.165733534</v>
       </c>
       <c r="P351" t="n">
         <v>5500</v>
@@ -15526,10 +15526,10 @@
         <v>204</v>
       </c>
       <c r="N353" t="n">
-        <v>4372.2107907508</v>
+        <v>4372.2107910895</v>
       </c>
       <c r="O353" t="n">
-        <v>891931.0013131632</v>
+        <v>891931.001382258</v>
       </c>
       <c r="P353" t="n">
         <v>7500</v>
@@ -15616,10 +15616,10 @@
         <v>2</v>
       </c>
       <c r="N355" t="n">
-        <v>1592.5665147453</v>
+        <v>1592.566460177</v>
       </c>
       <c r="O355" t="n">
-        <v>3185.1330294906</v>
+        <v>3185.132920354</v>
       </c>
       <c r="P355" t="n">
         <v>3900</v>
@@ -17677,22 +17677,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M402" t="n">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="N402" t="n">
-        <v>1630.923733916</v>
+        <v>1630.9237493905</v>
       </c>
       <c r="O402" t="n">
-        <v>862758.6552415639</v>
+        <v>851342.197181841</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
       </c>
       <c r="Q402" t="n">
-        <v>1322500</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="403">
@@ -17810,22 +17810,22 @@
         <v>0</v>
       </c>
       <c r="L405" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M405" t="n">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="N405" t="n">
-        <v>1690.5964846154</v>
+        <v>1690.5964302236</v>
       </c>
       <c r="O405" t="n">
-        <v>884181.9614538542</v>
+        <v>879110.143716272</v>
       </c>
       <c r="P405" t="n">
         <v>2900</v>
       </c>
       <c r="Q405" t="n">
-        <v>1516700</v>
+        <v>1508000</v>
       </c>
     </row>
     <row r="406">
@@ -17850,28 +17850,28 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>1273</v>
+        <v>2137</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M406" t="n">
-        <v>1273</v>
+        <v>2128</v>
       </c>
       <c r="N406" t="n">
-        <v>1550.1937906027</v>
+        <v>1550.1937917646</v>
       </c>
       <c r="O406" t="n">
-        <v>1973396.695437237</v>
+        <v>3298812.388875069</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
       </c>
       <c r="Q406" t="n">
-        <v>3182500</v>
+        <v>5320000</v>
       </c>
     </row>
     <row r="407">
@@ -17954,10 +17954,10 @@
         <v>1195</v>
       </c>
       <c r="N408" t="n">
-        <v>2403.5124244849</v>
+        <v>2403.5125045299</v>
       </c>
       <c r="O408" t="n">
-        <v>2872197.347259455</v>
+        <v>2872197.442913231</v>
       </c>
       <c r="P408" t="n">
         <v>3500</v>
@@ -18165,22 +18165,22 @@
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M413" t="n">
-        <v>1730</v>
+        <v>1720</v>
       </c>
       <c r="N413" t="n">
         <v>1076.92</v>
       </c>
       <c r="O413" t="n">
-        <v>1863071.6</v>
+        <v>1852302.4</v>
       </c>
       <c r="P413" t="n">
         <v>1400</v>
       </c>
       <c r="Q413" t="n">
-        <v>2422000</v>
+        <v>2408000</v>
       </c>
     </row>
     <row r="414">
@@ -21347,22 +21347,22 @@
         <v>0</v>
       </c>
       <c r="L487" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M487" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N487" t="n">
         <v>1969</v>
       </c>
       <c r="O487" t="n">
-        <v>224466</v>
+        <v>220528</v>
       </c>
       <c r="P487" t="n">
         <v>1500</v>
       </c>
       <c r="Q487" t="n">
-        <v>171000</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="488">
@@ -21891,10 +21891,10 @@
         <v>437</v>
       </c>
       <c r="N500" t="n">
-        <v>2029.8738739669</v>
+        <v>2029.8739473684</v>
       </c>
       <c r="O500" t="n">
-        <v>887054.8829235353</v>
+        <v>887054.9149999908</v>
       </c>
       <c r="P500" t="n">
         <v>3600</v>
@@ -23500,10 +23500,10 @@
         <v>276</v>
       </c>
       <c r="N538" t="n">
-        <v>4285.1956570156</v>
+        <v>4285.195701459</v>
       </c>
       <c r="O538" t="n">
-        <v>1182714.001336306</v>
+        <v>1182714.013602684</v>
       </c>
       <c r="P538" t="n">
         <v>6900</v>
@@ -26129,10 +26129,10 @@
         <v>60</v>
       </c>
       <c r="N599" t="n">
-        <v>1561.0010652921</v>
+        <v>1561.0013915094</v>
       </c>
       <c r="O599" t="n">
-        <v>93660.063917526</v>
+        <v>93660.08349056401</v>
       </c>
       <c r="P599" t="n">
         <v>2900</v>
@@ -27314,22 +27314,22 @@
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M627" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N627" t="n">
         <v>2192</v>
       </c>
       <c r="O627" t="n">
-        <v>72336</v>
+        <v>63568</v>
       </c>
       <c r="P627" t="n">
         <v>3900</v>
       </c>
       <c r="Q627" t="n">
-        <v>128700</v>
+        <v>113100</v>
       </c>
     </row>
     <row r="628">
@@ -27897,10 +27897,10 @@
         <v>66</v>
       </c>
       <c r="N640" t="n">
-        <v>3113.8900276243</v>
+        <v>3113.8900280899</v>
       </c>
       <c r="O640" t="n">
-        <v>205516.7418232038</v>
+        <v>205516.7418539334</v>
       </c>
       <c r="P640" t="n">
         <v>5000</v>
@@ -28081,10 +28081,10 @@
         <v>14</v>
       </c>
       <c r="N644" t="n">
-        <v>4163.1602061856</v>
+        <v>4163.160212766</v>
       </c>
       <c r="O644" t="n">
-        <v>58284.2428865984</v>
+        <v>58284.242978724</v>
       </c>
       <c r="P644" t="n">
         <v>6700</v>
@@ -28771,10 +28771,10 @@
         <v>608</v>
       </c>
       <c r="N659" t="n">
-        <v>1664.3547889182</v>
+        <v>1664.3547486772</v>
       </c>
       <c r="O659" t="n">
-        <v>1011927.711662266</v>
+        <v>1011927.687195738</v>
       </c>
       <c r="P659" t="n">
         <v>2900</v>
@@ -29369,22 +29369,22 @@
         <v>0</v>
       </c>
       <c r="L672" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M672" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N672" t="n">
         <v>3486</v>
       </c>
       <c r="O672" t="n">
-        <v>320712</v>
+        <v>306768</v>
       </c>
       <c r="P672" t="n">
         <v>6900</v>
       </c>
       <c r="Q672" t="n">
-        <v>634800</v>
+        <v>607200</v>
       </c>
     </row>
     <row r="673">
@@ -32231,10 +32231,10 @@
         <v>684</v>
       </c>
       <c r="N734" t="n">
-        <v>2328.1187082951</v>
+        <v>2328.1186987357</v>
       </c>
       <c r="O734" t="n">
-        <v>1592433.196473849</v>
+        <v>1592433.189935219</v>
       </c>
       <c r="P734" t="n">
         <v>4500</v>
@@ -33013,10 +33013,10 @@
         <v>16</v>
       </c>
       <c r="N751" t="n">
-        <v>4907.8221131448</v>
+        <v>4907.8221561969</v>
       </c>
       <c r="O751" t="n">
-        <v>78525.1538103168</v>
+        <v>78525.15449915041</v>
       </c>
       <c r="P751" t="n">
         <v>8200</v>
@@ -34661,22 +34661,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M787" t="n">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="N787" t="n">
         <v>753</v>
       </c>
       <c r="O787" t="n">
-        <v>451800</v>
+        <v>447282</v>
       </c>
       <c r="P787" t="n">
         <v>1600</v>
       </c>
       <c r="Q787" t="n">
-        <v>960000</v>
+        <v>950400</v>
       </c>
     </row>
     <row r="788">
@@ -35585,10 +35585,10 @@
         <v>61</v>
       </c>
       <c r="N807" t="n">
-        <v>4268.7071078431</v>
+        <v>4268.70745</v>
       </c>
       <c r="O807" t="n">
-        <v>260391.1335784291</v>
+        <v>260391.15445</v>
       </c>
       <c r="P807" t="n">
         <v>6900</v>
@@ -36736,10 +36736,10 @@
         <v>296</v>
       </c>
       <c r="N832" t="n">
-        <v>2458.5130528766</v>
+        <v>2458.5130063609</v>
       </c>
       <c r="O832" t="n">
-        <v>727719.8636514735</v>
+        <v>727719.8498828263</v>
       </c>
       <c r="P832" t="n">
         <v>3500</v>
@@ -36828,10 +36828,10 @@
         <v>185</v>
       </c>
       <c r="N834" t="n">
-        <v>1771.0904111406</v>
+        <v>1771.0903664224</v>
       </c>
       <c r="O834" t="n">
-        <v>327651.726061011</v>
+        <v>327651.717788144</v>
       </c>
       <c r="P834" t="n">
         <v>2500</v>
@@ -36920,10 +36920,10 @@
         <v>592</v>
       </c>
       <c r="N836" t="n">
-        <v>1803.0156556557</v>
+        <v>1803.0157013118</v>
       </c>
       <c r="O836" t="n">
-        <v>1067385.268148174</v>
+        <v>1067385.295176586</v>
       </c>
       <c r="P836" t="n">
         <v>2500</v>
@@ -37104,10 +37104,10 @@
         <v>1097</v>
       </c>
       <c r="N840" t="n">
-        <v>2056.0829556314</v>
+        <v>2056.0829120879</v>
       </c>
       <c r="O840" t="n">
-        <v>2255523.002327646</v>
+        <v>2255522.954560426</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
@@ -37611,10 +37611,10 @@
         <v>2</v>
       </c>
       <c r="N851" t="n">
-        <v>1906.1819786096</v>
+        <v>1906.1816666667</v>
       </c>
       <c r="O851" t="n">
-        <v>3812.3639572192</v>
+        <v>3812.3633333334</v>
       </c>
       <c r="P851" t="n">
         <v>2900</v>
@@ -40830,10 +40830,10 @@
         <v>2777</v>
       </c>
       <c r="N922" t="n">
-        <v>517.29010591089</v>
+        <v>517.2904197169401</v>
       </c>
       <c r="O922" t="n">
-        <v>1436514.624114542</v>
+        <v>1436515.495553943</v>
       </c>
       <c r="P922" t="n">
         <v>900</v>
@@ -41050,22 +41050,22 @@
         <v>0</v>
       </c>
       <c r="L927" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M927" t="n">
-        <v>511</v>
+        <v>461</v>
       </c>
       <c r="N927" t="n">
-        <v>3110.8411757364</v>
+        <v>3110.8406506215</v>
       </c>
       <c r="O927" t="n">
-        <v>1589639.8408013</v>
+        <v>1434097.539936512</v>
       </c>
       <c r="P927" t="n">
         <v>4500</v>
       </c>
       <c r="Q927" t="n">
-        <v>2299500</v>
+        <v>2074500</v>
       </c>
     </row>
     <row r="928">
@@ -41272,22 +41272,22 @@
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M932" t="n">
-        <v>1005</v>
+        <v>909</v>
       </c>
       <c r="N932" t="n">
-        <v>703.79514130448</v>
+        <v>703.79512253205</v>
       </c>
       <c r="O932" t="n">
-        <v>707314.1170110024</v>
+        <v>639749.7663816335</v>
       </c>
       <c r="P932" t="n">
         <v>900</v>
       </c>
       <c r="Q932" t="n">
-        <v>904500</v>
+        <v>818100</v>
       </c>
     </row>
     <row r="933">
@@ -43606,22 +43606,22 @@
         <v>0</v>
       </c>
       <c r="L983" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M983" t="n">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="N983" t="n">
         <v>1230.77</v>
       </c>
       <c r="O983" t="n">
-        <v>366769.46</v>
+        <v>354461.76</v>
       </c>
       <c r="P983" t="n">
         <v>1600</v>
       </c>
       <c r="Q983" t="n">
-        <v>476800</v>
+        <v>460800</v>
       </c>
     </row>
     <row r="984">
@@ -46051,22 +46051,22 @@
         <v>0</v>
       </c>
       <c r="L1036" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1036" t="n">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="N1036" t="n">
         <v>1153.85</v>
       </c>
       <c r="O1036" t="n">
-        <v>886156.7999999999</v>
+        <v>874618.2999999999</v>
       </c>
       <c r="P1036" t="n">
         <v>1500</v>
       </c>
       <c r="Q1036" t="n">
-        <v>1152000</v>
+        <v>1137000</v>
       </c>
     </row>
     <row r="1037">
@@ -47428,10 +47428,10 @@
         <v>3</v>
       </c>
       <c r="N1068" t="n">
-        <v>1213.6821359223</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O1068" t="n">
-        <v>3641.0464077669</v>
+        <v>3641.046420233401</v>
       </c>
       <c r="P1068" t="n">
         <v>1500</v>
@@ -47941,22 +47941,22 @@
         <v>0</v>
       </c>
       <c r="L1080" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1080" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="N1080" t="n">
         <v>1076.92</v>
       </c>
       <c r="O1080" t="n">
-        <v>278922.28</v>
+        <v>268153.08</v>
       </c>
       <c r="P1080" t="n">
         <v>1400</v>
       </c>
       <c r="Q1080" t="n">
-        <v>362600</v>
+        <v>348600</v>
       </c>
     </row>
     <row r="1081">
@@ -49435,22 +49435,22 @@
         <v>0</v>
       </c>
       <c r="L1114" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M1114" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N1114" t="n">
         <v>7480</v>
       </c>
       <c r="O1114" t="n">
-        <v>97240</v>
+        <v>14960</v>
       </c>
       <c r="P1114" t="n">
         <v>9500</v>
       </c>
       <c r="Q1114" t="n">
-        <v>123500</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="1115">
@@ -49941,22 +49941,22 @@
         <v>0</v>
       </c>
       <c r="L1125" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M1125" t="n">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="N1125" t="n">
         <v>9240</v>
       </c>
       <c r="O1125" t="n">
-        <v>4601520</v>
+        <v>4416720</v>
       </c>
       <c r="P1125" t="n">
         <v>11500</v>
       </c>
       <c r="Q1125" t="n">
-        <v>5727000</v>
+        <v>5497000</v>
       </c>
     </row>
     <row r="1126">
@@ -51362,22 +51362,22 @@
         <v>0</v>
       </c>
       <c r="L1156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1156" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N1156" t="n">
         <v>576.58</v>
       </c>
       <c r="O1156" t="n">
-        <v>10955.02</v>
+        <v>9801.860000000001</v>
       </c>
       <c r="P1156" t="n">
         <v>5900</v>
       </c>
       <c r="Q1156" t="n">
-        <v>112100</v>
+        <v>100300</v>
       </c>
     </row>
     <row r="1157">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-01</t>
         </is>
       </c>
     </row>
@@ -1307,10 +1307,10 @@
         <v>303</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.3076256499</v>
+        <v>1811.3076655052</v>
       </c>
       <c r="O22" t="n">
-        <v>548826.2105719197</v>
+        <v>548826.2226480755</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
@@ -1424,10 +1424,10 @@
         <v>150</v>
       </c>
       <c r="N25" t="n">
-        <v>3376.7464631809</v>
+        <v>3376.746460274</v>
       </c>
       <c r="O25" t="n">
-        <v>506511.969477135</v>
+        <v>506511.9690411</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1775,19 +1775,19 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N34" t="n">
         <v>37131</v>
       </c>
       <c r="O34" t="n">
-        <v>594096</v>
+        <v>408441</v>
       </c>
       <c r="P34" t="n">
         <v>54600</v>
       </c>
       <c r="Q34" t="n">
-        <v>873600</v>
+        <v>600600</v>
       </c>
     </row>
     <row r="35">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2876,19 +2876,19 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N61" t="n">
-        <v>6272.8548484848</v>
+        <v>6272.8549315068</v>
       </c>
       <c r="O61" t="n">
-        <v>257187.0487878768</v>
+        <v>219549.922602738</v>
       </c>
       <c r="P61" t="n">
         <v>7900</v>
       </c>
       <c r="Q61" t="n">
-        <v>323900</v>
+        <v>276500</v>
       </c>
     </row>
     <row r="62">
@@ -3397,10 +3397,10 @@
         <v>167</v>
       </c>
       <c r="N74" t="n">
-        <v>3716.3301954397</v>
+        <v>3716.3301957586</v>
       </c>
       <c r="O74" t="n">
-        <v>620627.1426384299</v>
+        <v>620627.1426916862</v>
       </c>
       <c r="P74" t="n">
         <v>9500</v>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4686,19 +4686,19 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N104" t="n">
-        <v>30708.828</v>
+        <v>30708.848333333</v>
       </c>
       <c r="O104" t="n">
-        <v>245670.624</v>
+        <v>307088.48333333</v>
       </c>
       <c r="P104" t="n">
         <v>53500</v>
       </c>
       <c r="Q104" t="n">
-        <v>428000</v>
+        <v>535000</v>
       </c>
     </row>
     <row r="105">
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -9958,19 +9958,19 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N226" t="n">
         <v>39171.85</v>
       </c>
       <c r="O226" t="n">
-        <v>391718.5</v>
+        <v>313374.8</v>
       </c>
       <c r="P226" t="n">
         <v>68900</v>
       </c>
       <c r="Q226" t="n">
-        <v>689000</v>
+        <v>551200</v>
       </c>
     </row>
     <row r="227">
@@ -10198,7 +10198,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -10207,19 +10207,19 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="N232" t="n">
-        <v>1098.0603685231</v>
+        <v>1098.0605968058</v>
       </c>
       <c r="O232" t="n">
-        <v>541343.7616818883</v>
+        <v>524872.9652731725</v>
       </c>
       <c r="P232" t="n">
         <v>1500</v>
       </c>
       <c r="Q232" t="n">
-        <v>739500</v>
+        <v>717000</v>
       </c>
     </row>
     <row r="233">
@@ -12017,10 +12017,10 @@
         <v>200</v>
       </c>
       <c r="N274" t="n">
-        <v>2582.2556074972</v>
+        <v>2582.2555674232</v>
       </c>
       <c r="O274" t="n">
-        <v>516451.12149944</v>
+        <v>516451.11348464</v>
       </c>
       <c r="P274" t="n">
         <v>4500</v>
@@ -12109,10 +12109,10 @@
         <v>143</v>
       </c>
       <c r="N276" t="n">
-        <v>5216.8960939752</v>
+        <v>5216.8960872076</v>
       </c>
       <c r="O276" t="n">
-        <v>746016.1414384536</v>
+        <v>746016.1404706868</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="J285" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -12495,19 +12495,19 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="N285" t="n">
         <v>1903</v>
       </c>
       <c r="O285" t="n">
-        <v>226457</v>
+        <v>207427</v>
       </c>
       <c r="P285" t="n">
         <v>3200</v>
       </c>
       <c r="Q285" t="n">
-        <v>380800</v>
+        <v>348800</v>
       </c>
     </row>
     <row r="286">
@@ -12680,10 +12680,10 @@
         <v>64</v>
       </c>
       <c r="N289" t="n">
-        <v>3230.0672177419</v>
+        <v>3230.0671836735</v>
       </c>
       <c r="O289" t="n">
-        <v>206724.3019354816</v>
+        <v>206724.299755104</v>
       </c>
       <c r="P289" t="n">
         <v>6200</v>
@@ -12980,7 +12980,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -12989,19 +12989,19 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="N296" t="n">
         <v>1026.13</v>
       </c>
       <c r="O296" t="n">
-        <v>396086.1800000001</v>
+        <v>402242.96</v>
       </c>
       <c r="P296" t="n">
         <v>1900</v>
       </c>
       <c r="Q296" t="n">
-        <v>733400</v>
+        <v>744800</v>
       </c>
     </row>
     <row r="297">
@@ -13710,28 +13710,28 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="N312" t="n">
         <v>1203.38</v>
       </c>
       <c r="O312" t="n">
-        <v>801451.0800000001</v>
+        <v>793027.42</v>
       </c>
       <c r="P312" t="n">
         <v>1900</v>
       </c>
       <c r="Q312" t="n">
-        <v>1265400</v>
+        <v>1252100</v>
       </c>
     </row>
     <row r="313">
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -14297,19 +14297,19 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N325" t="n">
         <v>10716.34</v>
       </c>
       <c r="O325" t="n">
-        <v>225043.14</v>
+        <v>235759.48</v>
       </c>
       <c r="P325" t="n">
         <v>39000</v>
       </c>
       <c r="Q325" t="n">
-        <v>819000</v>
+        <v>858000</v>
       </c>
     </row>
     <row r="326">
@@ -14513,10 +14513,10 @@
         <v>36</v>
       </c>
       <c r="N330" t="n">
-        <v>3594.2539698492</v>
+        <v>3594.2539622642</v>
       </c>
       <c r="O330" t="n">
-        <v>129393.1429145712</v>
+        <v>129393.1426415112</v>
       </c>
       <c r="P330" t="n">
         <v>6500</v>
@@ -14820,10 +14820,10 @@
         <v>54</v>
       </c>
       <c r="N337" t="n">
-        <v>14822.37884823</v>
+        <v>14822.378847539</v>
       </c>
       <c r="O337" t="n">
-        <v>800408.45780442</v>
+        <v>800408.457767106</v>
       </c>
       <c r="P337" t="n">
         <v>24900</v>
@@ -14852,13 +14852,13 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>1646</v>
+        <v>1636</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
         <v>1636</v>
@@ -14896,28 +14896,28 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>723</v>
+        <v>683</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>415</v>
+        <v>683</v>
       </c>
       <c r="N339" t="n">
         <v>2090.85</v>
       </c>
       <c r="O339" t="n">
-        <v>867702.75</v>
+        <v>1428050.55</v>
       </c>
       <c r="P339" t="n">
         <v>2900</v>
       </c>
       <c r="Q339" t="n">
-        <v>1203500</v>
+        <v>1980700</v>
       </c>
     </row>
     <row r="340">
@@ -15439,10 +15439,10 @@
         <v>426</v>
       </c>
       <c r="N351" t="n">
-        <v>3041.660013459</v>
+        <v>3041.6600135135</v>
       </c>
       <c r="O351" t="n">
-        <v>1295747.165733534</v>
+        <v>1295747.165756751</v>
       </c>
       <c r="P351" t="n">
         <v>5500</v>
@@ -15616,10 +15616,10 @@
         <v>2</v>
       </c>
       <c r="N355" t="n">
-        <v>1592.566460177</v>
+        <v>1592.5664432285</v>
       </c>
       <c r="O355" t="n">
-        <v>3185.132920354</v>
+        <v>3185.132886457</v>
       </c>
       <c r="P355" t="n">
         <v>3900</v>
@@ -16176,7 +16176,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -16185,19 +16185,19 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N368" t="n">
         <v>4648.6</v>
       </c>
       <c r="O368" t="n">
-        <v>1678144.6</v>
+        <v>1692090.4</v>
       </c>
       <c r="P368" t="n">
         <v>8900</v>
       </c>
       <c r="Q368" t="n">
-        <v>3212900</v>
+        <v>3239600</v>
       </c>
     </row>
     <row r="369">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="J379" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="K379" t="n">
         <v>0</v>
@@ -16663,19 +16663,19 @@
         <v>0</v>
       </c>
       <c r="M379" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="N379" t="n">
         <v>1387.55</v>
       </c>
       <c r="O379" t="n">
-        <v>525881.45</v>
+        <v>534206.75</v>
       </c>
       <c r="P379" t="n">
         <v>2300</v>
       </c>
       <c r="Q379" t="n">
-        <v>871700</v>
+        <v>885500</v>
       </c>
     </row>
     <row r="380">
@@ -17190,7 +17190,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -17199,19 +17199,19 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N391" t="n">
         <v>11921.4</v>
       </c>
       <c r="O391" t="n">
-        <v>1549782</v>
+        <v>1537860.6</v>
       </c>
       <c r="P391" t="n">
         <v>19900</v>
       </c>
       <c r="Q391" t="n">
-        <v>2587000</v>
+        <v>2567100</v>
       </c>
     </row>
     <row r="392">
@@ -17671,28 +17671,28 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M402" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="N402" t="n">
-        <v>1630.9237493905</v>
+        <v>1630.9237512195</v>
       </c>
       <c r="O402" t="n">
-        <v>851342.197181841</v>
+        <v>846449.4268829204</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
       </c>
       <c r="Q402" t="n">
-        <v>1305000</v>
+        <v>1297500</v>
       </c>
     </row>
     <row r="403">
@@ -17804,28 +17804,28 @@
         </is>
       </c>
       <c r="J405" t="n">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="K405" t="n">
         <v>0</v>
       </c>
       <c r="L405" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M405" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="N405" t="n">
-        <v>1690.5964302236</v>
+        <v>1690.5961358314</v>
       </c>
       <c r="O405" t="n">
-        <v>879110.143716272</v>
+        <v>875728.7983606652</v>
       </c>
       <c r="P405" t="n">
         <v>2900</v>
       </c>
       <c r="Q405" t="n">
-        <v>1508000</v>
+        <v>1502200</v>
       </c>
     </row>
     <row r="406">
@@ -17850,28 +17850,28 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>2137</v>
+        <v>2120</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>2128</v>
+        <v>2120</v>
       </c>
       <c r="N406" t="n">
-        <v>1550.1937917646</v>
+        <v>1550.193804203</v>
       </c>
       <c r="O406" t="n">
-        <v>3298812.388875069</v>
+        <v>3286410.86491036</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
       </c>
       <c r="Q406" t="n">
-        <v>5320000</v>
+        <v>5300000</v>
       </c>
     </row>
     <row r="407">
@@ -17908,10 +17908,10 @@
         <v>3</v>
       </c>
       <c r="N407" t="n">
-        <v>1579.3897428571</v>
+        <v>1579.3895639535</v>
       </c>
       <c r="O407" t="n">
-        <v>4738.1692285713</v>
+        <v>4738.1686918605</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
@@ -17954,10 +17954,10 @@
         <v>1195</v>
       </c>
       <c r="N408" t="n">
-        <v>2403.5125045299</v>
+        <v>2403.5125525465</v>
       </c>
       <c r="O408" t="n">
-        <v>2872197.442913231</v>
+        <v>2872197.500293068</v>
       </c>
       <c r="P408" t="n">
         <v>3500</v>
@@ -18159,13 +18159,13 @@
         </is>
       </c>
       <c r="J413" t="n">
-        <v>1730</v>
+        <v>1720</v>
       </c>
       <c r="K413" t="n">
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M413" t="n">
         <v>1720</v>
@@ -21341,13 +21341,13 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
       </c>
       <c r="L487" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M487" t="n">
         <v>112</v>
@@ -21510,7 +21510,7 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K491" t="n">
         <v>0</v>
@@ -21519,19 +21519,19 @@
         <v>0</v>
       </c>
       <c r="M491" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N491" t="n">
         <v>2567</v>
       </c>
       <c r="O491" t="n">
-        <v>541637</v>
+        <v>536503</v>
       </c>
       <c r="P491" t="n">
         <v>4500</v>
       </c>
       <c r="Q491" t="n">
-        <v>949500</v>
+        <v>940500</v>
       </c>
     </row>
     <row r="492">
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -23018,19 +23018,19 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N527" t="n">
         <v>30611</v>
       </c>
       <c r="O527" t="n">
-        <v>1775438</v>
+        <v>1744827</v>
       </c>
       <c r="P527" t="n">
         <v>38900</v>
       </c>
       <c r="Q527" t="n">
-        <v>2256200</v>
+        <v>2217300</v>
       </c>
     </row>
     <row r="528">
@@ -23500,10 +23500,10 @@
         <v>276</v>
       </c>
       <c r="N538" t="n">
-        <v>4285.195701459</v>
+        <v>4285.1957207207</v>
       </c>
       <c r="O538" t="n">
-        <v>1182714.013602684</v>
+        <v>1182714.018918913</v>
       </c>
       <c r="P538" t="n">
         <v>6900</v>
@@ -24520,7 +24520,7 @@
         </is>
       </c>
       <c r="J562" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K562" t="n">
         <v>0</v>
@@ -24529,19 +24529,19 @@
         <v>0</v>
       </c>
       <c r="M562" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="N562" t="n">
         <v>1650</v>
       </c>
       <c r="O562" t="n">
-        <v>156750</v>
+        <v>136950</v>
       </c>
       <c r="P562" t="n">
         <v>2900</v>
       </c>
       <c r="Q562" t="n">
-        <v>275500</v>
+        <v>240700</v>
       </c>
     </row>
     <row r="563">
@@ -24976,7 +24976,7 @@
         </is>
       </c>
       <c r="J573" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K573" t="n">
         <v>0</v>
@@ -24985,19 +24985,19 @@
         <v>0</v>
       </c>
       <c r="M573" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N573" t="n">
         <v>39596.9</v>
       </c>
       <c r="O573" t="n">
-        <v>316775.2</v>
+        <v>237581.4</v>
       </c>
       <c r="P573" t="n">
         <v>64900</v>
       </c>
       <c r="Q573" t="n">
-        <v>519200</v>
+        <v>389400</v>
       </c>
     </row>
     <row r="574">
@@ -25503,7 +25503,7 @@
         </is>
       </c>
       <c r="J585" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K585" t="n">
         <v>0</v>
@@ -25512,19 +25512,19 @@
         <v>0</v>
       </c>
       <c r="M585" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N585" t="n">
         <v>22730.48</v>
       </c>
       <c r="O585" t="n">
-        <v>340957.2</v>
+        <v>363687.68</v>
       </c>
       <c r="P585" t="n">
         <v>36900</v>
       </c>
       <c r="Q585" t="n">
-        <v>553500</v>
+        <v>590400</v>
       </c>
     </row>
     <row r="586">
@@ -26129,10 +26129,10 @@
         <v>60</v>
       </c>
       <c r="N599" t="n">
-        <v>1561.0013915094</v>
+        <v>1561.0015412186</v>
       </c>
       <c r="O599" t="n">
-        <v>93660.08349056401</v>
+        <v>93660.092473116</v>
       </c>
       <c r="P599" t="n">
         <v>2900</v>
@@ -27308,13 +27308,13 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M627" t="n">
         <v>29</v>
@@ -28311,10 +28311,10 @@
         <v>133</v>
       </c>
       <c r="N649" t="n">
-        <v>1595.0093425606</v>
+        <v>1595.0093402778</v>
       </c>
       <c r="O649" t="n">
-        <v>212136.2425605598</v>
+        <v>212136.2422569474</v>
       </c>
       <c r="P649" t="n">
         <v>2600</v>
@@ -28771,10 +28771,10 @@
         <v>608</v>
       </c>
       <c r="N659" t="n">
-        <v>1664.3547486772</v>
+        <v>1664.3547082228</v>
       </c>
       <c r="O659" t="n">
-        <v>1011927.687195738</v>
+        <v>1011927.662599462</v>
       </c>
       <c r="P659" t="n">
         <v>2900</v>
@@ -29363,13 +29363,13 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
       </c>
       <c r="L672" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M672" t="n">
         <v>88</v>
@@ -29872,7 +29872,7 @@
         </is>
       </c>
       <c r="J683" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -29881,19 +29881,19 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="N683" t="n">
         <v>4800</v>
       </c>
       <c r="O683" t="n">
-        <v>120000</v>
+        <v>76800</v>
       </c>
       <c r="P683" t="n">
         <v>7900</v>
       </c>
       <c r="Q683" t="n">
-        <v>197500</v>
+        <v>126400</v>
       </c>
     </row>
     <row r="684">
@@ -31209,7 +31209,7 @@
         </is>
       </c>
       <c r="J712" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K712" t="n">
         <v>0</v>
@@ -31218,19 +31218,19 @@
         <v>0</v>
       </c>
       <c r="M712" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="N712" t="n">
         <v>13687</v>
       </c>
       <c r="O712" t="n">
-        <v>1231830</v>
+        <v>1067586</v>
       </c>
       <c r="P712" t="n">
         <v>21900</v>
       </c>
       <c r="Q712" t="n">
-        <v>1971000</v>
+        <v>1708200</v>
       </c>
     </row>
     <row r="713">
@@ -31669,7 +31669,7 @@
         </is>
       </c>
       <c r="J722" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K722" t="n">
         <v>0</v>
@@ -31678,19 +31678,19 @@
         <v>0</v>
       </c>
       <c r="M722" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="N722" t="n">
         <v>10411</v>
       </c>
       <c r="O722" t="n">
-        <v>197809</v>
+        <v>52055</v>
       </c>
       <c r="P722" t="n">
         <v>16900</v>
       </c>
       <c r="Q722" t="n">
-        <v>321100</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="723">
@@ -32219,7 +32219,7 @@
         </is>
       </c>
       <c r="J734" t="n">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K734" t="n">
         <v>0</v>
@@ -32228,19 +32228,19 @@
         <v>0</v>
       </c>
       <c r="M734" t="n">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N734" t="n">
-        <v>2328.1186987357</v>
+        <v>2328.1186979327</v>
       </c>
       <c r="O734" t="n">
-        <v>1592433.189935219</v>
+        <v>1587776.951990101</v>
       </c>
       <c r="P734" t="n">
         <v>4500</v>
       </c>
       <c r="Q734" t="n">
-        <v>3078000</v>
+        <v>3069000</v>
       </c>
     </row>
     <row r="735">
@@ -32909,7 +32909,7 @@
         </is>
       </c>
       <c r="J749" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K749" t="n">
         <v>0</v>
@@ -32918,19 +32918,19 @@
         <v>0</v>
       </c>
       <c r="M749" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N749" t="n">
         <v>3396.38</v>
       </c>
       <c r="O749" t="n">
-        <v>393980.08</v>
+        <v>390583.7</v>
       </c>
       <c r="P749" t="n">
         <v>6500</v>
       </c>
       <c r="Q749" t="n">
-        <v>754000</v>
+        <v>747500</v>
       </c>
     </row>
     <row r="750">
@@ -33289,10 +33289,10 @@
         <v>137</v>
       </c>
       <c r="N757" t="n">
-        <v>3903.736710023</v>
+        <v>3903.7367356322</v>
       </c>
       <c r="O757" t="n">
-        <v>534811.929273151</v>
+        <v>534811.9327816115</v>
       </c>
       <c r="P757" t="n">
         <v>7500</v>
@@ -34655,13 +34655,13 @@
         </is>
       </c>
       <c r="J787" t="n">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="K787" t="n">
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M787" t="n">
         <v>594</v>
@@ -36600,10 +36600,10 @@
         <v>562</v>
       </c>
       <c r="N829" t="n">
-        <v>1516.0387934921</v>
+        <v>1516.0387920714</v>
       </c>
       <c r="O829" t="n">
-        <v>852013.8019425602</v>
+        <v>852013.8011441268</v>
       </c>
       <c r="P829" t="n">
         <v>2300</v>
@@ -36736,10 +36736,10 @@
         <v>296</v>
       </c>
       <c r="N832" t="n">
-        <v>2458.5130063609</v>
+        <v>2458.5129946345</v>
       </c>
       <c r="O832" t="n">
-        <v>727719.8498828263</v>
+        <v>727719.846411812</v>
       </c>
       <c r="P832" t="n">
         <v>3500</v>
@@ -36966,10 +36966,10 @@
         <v>149</v>
       </c>
       <c r="N837" t="n">
-        <v>3306.5946508172</v>
+        <v>3306.5946428571</v>
       </c>
       <c r="O837" t="n">
-        <v>492682.6029717628</v>
+        <v>492682.6017857079</v>
       </c>
       <c r="P837" t="n">
         <v>4900</v>
@@ -37058,10 +37058,10 @@
         <v>588</v>
       </c>
       <c r="N839" t="n">
-        <v>2108.7923742027</v>
+        <v>2108.7924270463</v>
       </c>
       <c r="O839" t="n">
-        <v>1239969.916031188</v>
+        <v>1239969.947103224</v>
       </c>
       <c r="P839" t="n">
         <v>2900</v>
@@ -37138,7 +37138,7 @@
         </is>
       </c>
       <c r="J841" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K841" t="n">
         <v>0</v>
@@ -37147,19 +37147,19 @@
         <v>0</v>
       </c>
       <c r="M841" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N841" t="n">
-        <v>3224.5688526212</v>
+        <v>3224.5688613861</v>
       </c>
       <c r="O841" t="n">
-        <v>664261.1836399672</v>
+        <v>657812.0477227643</v>
       </c>
       <c r="P841" t="n">
         <v>4500</v>
       </c>
       <c r="Q841" t="n">
-        <v>927000</v>
+        <v>918000</v>
       </c>
     </row>
     <row r="842">
@@ -37196,10 +37196,10 @@
         <v>725</v>
       </c>
       <c r="N842" t="n">
-        <v>1655.9307707708</v>
+        <v>1655.9307676903</v>
       </c>
       <c r="O842" t="n">
-        <v>1200549.80880883</v>
+        <v>1200549.806575467</v>
       </c>
       <c r="P842" t="n">
         <v>2500</v>
@@ -37611,10 +37611,10 @@
         <v>2</v>
       </c>
       <c r="N851" t="n">
-        <v>1906.1816666667</v>
+        <v>1906.1816201117</v>
       </c>
       <c r="O851" t="n">
-        <v>3812.3633333334</v>
+        <v>3812.3632402234</v>
       </c>
       <c r="P851" t="n">
         <v>2900</v>
@@ -37885,10 +37885,10 @@
         <v>97</v>
       </c>
       <c r="N857" t="n">
-        <v>692.1522422179</v>
+        <v>692.15225097656</v>
       </c>
       <c r="O857" t="n">
-        <v>67138.7674951363</v>
+        <v>67138.76834472633</v>
       </c>
       <c r="P857" t="n">
         <v>1200</v>
@@ -39480,7 +39480,7 @@
         </is>
       </c>
       <c r="J892" t="n">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="K892" t="n">
         <v>0</v>
@@ -39489,19 +39489,19 @@
         <v>0</v>
       </c>
       <c r="M892" t="n">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="N892" t="n">
         <v>1828.64</v>
       </c>
       <c r="O892" t="n">
-        <v>1183130.08</v>
+        <v>1181301.44</v>
       </c>
       <c r="P892" t="n">
         <v>2000</v>
       </c>
       <c r="Q892" t="n">
-        <v>1294000</v>
+        <v>1292000</v>
       </c>
     </row>
     <row r="893">
@@ -39864,10 +39864,10 @@
         <v>1443</v>
       </c>
       <c r="N900" t="n">
-        <v>711.3366494881</v>
+        <v>711.33664937221</v>
       </c>
       <c r="O900" t="n">
-        <v>1026458.785211328</v>
+        <v>1026458.785044099</v>
       </c>
       <c r="P900" t="n">
         <v>900</v>
@@ -40725,7 +40725,7 @@
         </is>
       </c>
       <c r="J920" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K920" t="n">
         <v>0</v>
@@ -40734,19 +40734,19 @@
         <v>0</v>
       </c>
       <c r="M920" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N920" t="n">
-        <v>4032.3968134715</v>
+        <v>4032.3968051948</v>
       </c>
       <c r="O920" t="n">
-        <v>229846.6183678755</v>
+        <v>225814.2210909088</v>
       </c>
       <c r="P920" t="n">
         <v>4200</v>
       </c>
       <c r="Q920" t="n">
-        <v>239400</v>
+        <v>235200</v>
       </c>
     </row>
     <row r="921">
@@ -40818,7 +40818,7 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>2777</v>
+        <v>2727</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
@@ -40827,19 +40827,19 @@
         <v>0</v>
       </c>
       <c r="M922" t="n">
-        <v>2777</v>
+        <v>2727</v>
       </c>
       <c r="N922" t="n">
-        <v>517.2904197169401</v>
+        <v>517.29054581378</v>
       </c>
       <c r="O922" t="n">
-        <v>1436515.495553943</v>
+        <v>1410651.318434178</v>
       </c>
       <c r="P922" t="n">
         <v>900</v>
       </c>
       <c r="Q922" t="n">
-        <v>2499300</v>
+        <v>2454300</v>
       </c>
     </row>
     <row r="923">
@@ -41044,28 +41044,28 @@
         </is>
       </c>
       <c r="J927" t="n">
-        <v>511</v>
+        <v>466</v>
       </c>
       <c r="K927" t="n">
         <v>0</v>
       </c>
       <c r="L927" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M927" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="N927" t="n">
-        <v>3110.8406506215</v>
+        <v>3110.8406407201</v>
       </c>
       <c r="O927" t="n">
-        <v>1434097.539936512</v>
+        <v>1449651.738575567</v>
       </c>
       <c r="P927" t="n">
         <v>4500</v>
       </c>
       <c r="Q927" t="n">
-        <v>2074500</v>
+        <v>2097000</v>
       </c>
     </row>
     <row r="928">
@@ -41266,28 +41266,28 @@
         </is>
       </c>
       <c r="J932" t="n">
-        <v>1005</v>
+        <v>883</v>
       </c>
       <c r="K932" t="n">
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M932" t="n">
-        <v>909</v>
+        <v>883</v>
       </c>
       <c r="N932" t="n">
-        <v>703.79512253205</v>
+        <v>703.79511760843</v>
       </c>
       <c r="O932" t="n">
-        <v>639749.7663816335</v>
+        <v>621451.0888482437</v>
       </c>
       <c r="P932" t="n">
         <v>900</v>
       </c>
       <c r="Q932" t="n">
-        <v>818100</v>
+        <v>794700</v>
       </c>
     </row>
     <row r="933">
@@ -41551,10 +41551,10 @@
         <v>3</v>
       </c>
       <c r="N938" t="n">
-        <v>2501.3849295775</v>
+        <v>2501.3848325359</v>
       </c>
       <c r="O938" t="n">
-        <v>7504.1547887325</v>
+        <v>7504.1544976077</v>
       </c>
       <c r="P938" t="n">
         <v>4100</v>
@@ -41772,10 +41772,10 @@
         <v>62</v>
       </c>
       <c r="N943" t="n">
-        <v>2583.9607246377</v>
+        <v>2583.9607352941</v>
       </c>
       <c r="O943" t="n">
-        <v>160205.5649275374</v>
+        <v>160205.5655882342</v>
       </c>
       <c r="P943" t="n">
         <v>3000</v>
@@ -42860,10 +42860,10 @@
         <v>3</v>
       </c>
       <c r="N967" t="n">
-        <v>2098.4050733138</v>
+        <v>2098.4050882353</v>
       </c>
       <c r="O967" t="n">
-        <v>6295.2152199414</v>
+        <v>6295.215264705899</v>
       </c>
       <c r="P967" t="n">
         <v>9500</v>
@@ -43600,13 +43600,13 @@
         </is>
       </c>
       <c r="J983" t="n">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="K983" t="n">
         <v>0</v>
       </c>
       <c r="L983" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M983" t="n">
         <v>288</v>
@@ -44445,10 +44445,10 @@
         <v>2</v>
       </c>
       <c r="N1001" t="n">
-        <v>2000.6820300752</v>
+        <v>2000.6838931298</v>
       </c>
       <c r="O1001" t="n">
-        <v>4001.3640601504</v>
+        <v>4001.3677862596</v>
       </c>
       <c r="P1001" t="n">
         <v>2000</v>
@@ -46045,13 +46045,13 @@
         </is>
       </c>
       <c r="J1036" t="n">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="K1036" t="n">
         <v>0</v>
       </c>
       <c r="L1036" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M1036" t="n">
         <v>758</v>
@@ -47331,7 +47331,7 @@
         </is>
       </c>
       <c r="J1066" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="K1066" t="n">
         <v>0</v>
@@ -47340,19 +47340,19 @@
         <v>0</v>
       </c>
       <c r="M1066" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="N1066" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1066" t="n">
-        <v>125892.99</v>
+        <v>102361.59</v>
       </c>
       <c r="P1066" t="n">
         <v>1900</v>
       </c>
       <c r="Q1066" t="n">
-        <v>203300</v>
+        <v>165300</v>
       </c>
     </row>
     <row r="1067">
@@ -47375,7 +47375,7 @@
         </is>
       </c>
       <c r="J1067" t="n">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K1067" t="n">
         <v>0</v>
@@ -47384,19 +47384,19 @@
         <v>0</v>
       </c>
       <c r="M1067" t="n">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="N1067" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1067" t="n">
-        <v>1374580.8</v>
+        <v>1342761.8</v>
       </c>
       <c r="P1067" t="n">
         <v>5100</v>
       </c>
       <c r="Q1067" t="n">
-        <v>2203200</v>
+        <v>2152200</v>
       </c>
     </row>
     <row r="1068">
@@ -47935,13 +47935,13 @@
         </is>
       </c>
       <c r="J1080" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="K1080" t="n">
         <v>0</v>
       </c>
       <c r="L1080" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M1080" t="n">
         <v>249</v>
@@ -48715,10 +48715,10 @@
         <v>83</v>
       </c>
       <c r="N1098" t="n">
-        <v>4985.4055045872</v>
+        <v>4985.4056872038</v>
       </c>
       <c r="O1098" t="n">
-        <v>413788.6568807376</v>
+        <v>413788.6720379154</v>
       </c>
       <c r="P1098" t="n">
         <v>7900</v>
@@ -48766,10 +48766,10 @@
         <v>41</v>
       </c>
       <c r="N1099" t="n">
-        <v>1757.3205603448</v>
+        <v>1757.3205627706</v>
       </c>
       <c r="O1099" t="n">
-        <v>72050.1429741368</v>
+        <v>72050.14307359461</v>
       </c>
       <c r="P1099" t="n">
         <v>2000</v>
@@ -49429,13 +49429,13 @@
         </is>
       </c>
       <c r="J1114" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K1114" t="n">
         <v>0</v>
       </c>
       <c r="L1114" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M1114" t="n">
         <v>2</v>
@@ -49613,7 +49613,7 @@
         </is>
       </c>
       <c r="J1118" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K1118" t="n">
         <v>0</v>
@@ -49622,19 +49622,19 @@
         <v>0</v>
       </c>
       <c r="M1118" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N1118" t="n">
         <v>1584</v>
       </c>
       <c r="O1118" t="n">
-        <v>20592</v>
+        <v>15840</v>
       </c>
       <c r="P1118" t="n">
         <v>2000</v>
       </c>
       <c r="Q1118" t="n">
-        <v>26000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1119">
@@ -49705,7 +49705,7 @@
         </is>
       </c>
       <c r="J1120" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="K1120" t="n">
         <v>0</v>
@@ -49714,19 +49714,19 @@
         <v>0</v>
       </c>
       <c r="M1120" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="N1120" t="n">
         <v>6160</v>
       </c>
       <c r="O1120" t="n">
-        <v>320320</v>
+        <v>246400</v>
       </c>
       <c r="P1120" t="n">
         <v>7900</v>
       </c>
       <c r="Q1120" t="n">
-        <v>410800</v>
+        <v>316000</v>
       </c>
     </row>
     <row r="1121">
@@ -49751,7 +49751,7 @@
         </is>
       </c>
       <c r="J1121" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K1121" t="n">
         <v>0</v>
@@ -49760,19 +49760,19 @@
         <v>0</v>
       </c>
       <c r="M1121" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N1121" t="n">
         <v>4400</v>
       </c>
       <c r="O1121" t="n">
-        <v>506000</v>
+        <v>519200</v>
       </c>
       <c r="P1121" t="n">
         <v>5900</v>
       </c>
       <c r="Q1121" t="n">
-        <v>678500</v>
+        <v>696200</v>
       </c>
     </row>
     <row r="1122">
@@ -49797,7 +49797,7 @@
         </is>
       </c>
       <c r="J1122" t="n">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K1122" t="n">
         <v>0</v>
@@ -49806,19 +49806,19 @@
         <v>0</v>
       </c>
       <c r="M1122" t="n">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="N1122" t="n">
         <v>3520</v>
       </c>
       <c r="O1122" t="n">
-        <v>531520</v>
+        <v>397760</v>
       </c>
       <c r="P1122" t="n">
         <v>4500</v>
       </c>
       <c r="Q1122" t="n">
-        <v>679500</v>
+        <v>508500</v>
       </c>
     </row>
     <row r="1123">
@@ -49935,13 +49935,13 @@
         </is>
       </c>
       <c r="J1125" t="n">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="K1125" t="n">
         <v>0</v>
       </c>
       <c r="L1125" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M1125" t="n">
         <v>478</v>
@@ -49981,7 +49981,7 @@
         </is>
       </c>
       <c r="J1126" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="K1126" t="n">
         <v>0</v>
@@ -49990,19 +49990,19 @@
         <v>0</v>
       </c>
       <c r="M1126" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="N1126" t="n">
         <v>2288</v>
       </c>
       <c r="O1126" t="n">
-        <v>1189760</v>
+        <v>1166880</v>
       </c>
       <c r="P1126" t="n">
         <v>2900</v>
       </c>
       <c r="Q1126" t="n">
-        <v>1508000</v>
+        <v>1479000</v>
       </c>
     </row>
     <row r="1127">
@@ -50027,7 +50027,7 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
@@ -50036,19 +50036,19 @@
         <v>0</v>
       </c>
       <c r="M1127" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N1127" t="n">
         <v>4576</v>
       </c>
       <c r="O1127" t="n">
-        <v>732160</v>
+        <v>741312</v>
       </c>
       <c r="P1127" t="n">
         <v>5900</v>
       </c>
       <c r="Q1127" t="n">
-        <v>944000</v>
+        <v>955800</v>
       </c>
     </row>
     <row r="1128">
@@ -50947,7 +50947,7 @@
         </is>
       </c>
       <c r="J1147" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="K1147" t="n">
         <v>0</v>
@@ -50956,19 +50956,19 @@
         <v>0</v>
       </c>
       <c r="M1147" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="N1147" t="n">
         <v>1900</v>
       </c>
       <c r="O1147" t="n">
-        <v>262200</v>
+        <v>239400</v>
       </c>
       <c r="P1147" t="n">
         <v>2300</v>
       </c>
       <c r="Q1147" t="n">
-        <v>317400</v>
+        <v>289800</v>
       </c>
     </row>
     <row r="1148">
@@ -51356,13 +51356,13 @@
         </is>
       </c>
       <c r="J1156" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K1156" t="n">
         <v>0</v>
       </c>
       <c r="L1156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1156" t="n">
         <v>17</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1266,10 +1266,10 @@
         <v>21</v>
       </c>
       <c r="N21" t="n">
-        <v>14490.384964539</v>
+        <v>14490.384928571</v>
       </c>
       <c r="O21" t="n">
-        <v>304298.084255319</v>
+        <v>304298.083499991</v>
       </c>
       <c r="P21" t="n">
         <v>23600</v>
@@ -4985,10 +4985,10 @@
         <v>27</v>
       </c>
       <c r="N111" t="n">
-        <v>15711.965869565</v>
+        <v>15711.965851528</v>
       </c>
       <c r="O111" t="n">
-        <v>424223.078478255</v>
+        <v>424223.077991256</v>
       </c>
       <c r="P111" t="n">
         <v>28500</v>
@@ -12452,10 +12452,10 @@
         <v>680</v>
       </c>
       <c r="N284" t="n">
-        <v>3158.8608271635</v>
+        <v>3158.8608272041</v>
       </c>
       <c r="O284" t="n">
-        <v>2148025.36247118</v>
+        <v>2148025.362498788</v>
       </c>
       <c r="P284" t="n">
         <v>5600</v>
@@ -14513,10 +14513,10 @@
         <v>36</v>
       </c>
       <c r="N330" t="n">
-        <v>3594.2539622642</v>
+        <v>3594.2539546599</v>
       </c>
       <c r="O330" t="n">
-        <v>129393.1426415112</v>
+        <v>129393.1423677564</v>
       </c>
       <c r="P330" t="n">
         <v>6500</v>
@@ -14682,10 +14682,10 @@
         <v>129</v>
       </c>
       <c r="N334" t="n">
-        <v>3240.850037594</v>
+        <v>3240.8500375235</v>
       </c>
       <c r="O334" t="n">
-        <v>418069.6548496259</v>
+        <v>418069.6548405315</v>
       </c>
       <c r="P334" t="n">
         <v>5200</v>
@@ -18598,10 +18598,10 @@
         <v>164</v>
       </c>
       <c r="N423" t="n">
-        <v>893.67886945501</v>
+        <v>893.67886888156</v>
       </c>
       <c r="O423" t="n">
-        <v>146563.3345906216</v>
+        <v>146563.3344965758</v>
       </c>
       <c r="P423" t="n">
         <v>1200</v>
@@ -24179,10 +24179,10 @@
         <v>12</v>
       </c>
       <c r="N554" t="n">
-        <v>30244.600034762</v>
+        <v>30244.600034742</v>
       </c>
       <c r="O554" t="n">
-        <v>362935.200417144</v>
+        <v>362935.200416904</v>
       </c>
       <c r="P554" t="n">
         <v>48900</v>
@@ -36782,10 +36782,10 @@
         <v>366</v>
       </c>
       <c r="N833" t="n">
-        <v>1907.3929677419</v>
+        <v>1907.3929220779</v>
       </c>
       <c r="O833" t="n">
-        <v>698105.8261935355</v>
+        <v>698105.8094805115</v>
       </c>
       <c r="P833" t="n">
         <v>2500</v>
@@ -36920,10 +36920,10 @@
         <v>592</v>
       </c>
       <c r="N836" t="n">
-        <v>1803.0157013118</v>
+        <v>1803.0157128413</v>
       </c>
       <c r="O836" t="n">
-        <v>1067385.295176586</v>
+        <v>1067385.30200205</v>
       </c>
       <c r="P836" t="n">
         <v>2500</v>
@@ -37058,10 +37058,10 @@
         <v>588</v>
       </c>
       <c r="N839" t="n">
-        <v>2108.7924270463</v>
+        <v>2108.7924803431</v>
       </c>
       <c r="O839" t="n">
-        <v>1239969.947103224</v>
+        <v>1239969.978441743</v>
       </c>
       <c r="P839" t="n">
         <v>2900</v>
@@ -37104,10 +37104,10 @@
         <v>1097</v>
       </c>
       <c r="N840" t="n">
-        <v>2056.0829120879</v>
+        <v>2056.0828974535</v>
       </c>
       <c r="O840" t="n">
-        <v>2255522.954560426</v>
+        <v>2255522.93850649</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
@@ -41278,10 +41278,10 @@
         <v>883</v>
       </c>
       <c r="N932" t="n">
-        <v>703.79511760843</v>
+        <v>703.79511689575</v>
       </c>
       <c r="O932" t="n">
-        <v>621451.0888482437</v>
+        <v>621451.0882189472</v>
       </c>
       <c r="P932" t="n">
         <v>900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -4904,10 +4904,10 @@
         <v>16</v>
       </c>
       <c r="N109" t="n">
-        <v>16486.408661417</v>
+        <v>16486.408571429</v>
       </c>
       <c r="O109" t="n">
-        <v>263782.538582672</v>
+        <v>263782.537142864</v>
       </c>
       <c r="P109" t="n">
         <v>30500</v>
@@ -4985,10 +4985,10 @@
         <v>27</v>
       </c>
       <c r="N111" t="n">
-        <v>15711.965814978</v>
+        <v>15711.96579646</v>
       </c>
       <c r="O111" t="n">
-        <v>424223.077004406</v>
+        <v>424223.07650442</v>
       </c>
       <c r="P111" t="n">
         <v>28500</v>
@@ -5032,10 +5032,10 @@
         <v>11</v>
       </c>
       <c r="N112" t="n">
-        <v>9392.075000000001</v>
+        <v>9392.0750746269</v>
       </c>
       <c r="O112" t="n">
-        <v>103312.825</v>
+        <v>103312.8258208959</v>
       </c>
       <c r="P112" t="n">
         <v>18500</v>
@@ -12017,10 +12017,10 @@
         <v>200</v>
       </c>
       <c r="N274" t="n">
-        <v>2582.2555555556</v>
+        <v>2582.2555535714</v>
       </c>
       <c r="O274" t="n">
-        <v>516451.11111112</v>
+        <v>516451.11071428</v>
       </c>
       <c r="P274" t="n">
         <v>4500</v>
@@ -37242,10 +37242,10 @@
         <v>721</v>
       </c>
       <c r="N843" t="n">
-        <v>1655.9307118872</v>
+        <v>1655.9306993948</v>
       </c>
       <c r="O843" t="n">
-        <v>1193926.043270671</v>
+        <v>1193926.034263651</v>
       </c>
       <c r="P843" t="n">
         <v>2500</v>
@@ -37657,10 +37657,10 @@
         <v>2</v>
       </c>
       <c r="N852" t="n">
-        <v>1906.1813793103</v>
+        <v>1906.1812280702</v>
       </c>
       <c r="O852" t="n">
-        <v>3812.3627586206</v>
+        <v>3812.3624561404</v>
       </c>
       <c r="P852" t="n">
         <v>2900</v>
@@ -37795,10 +37795,10 @@
         <v>249</v>
       </c>
       <c r="N855" t="n">
-        <v>1259.2746360505</v>
+        <v>1259.2746413793</v>
       </c>
       <c r="O855" t="n">
-        <v>313559.3843765745</v>
+        <v>313559.3857034457</v>
       </c>
       <c r="P855" t="n">
         <v>1900</v>
@@ -41102,10 +41102,10 @@
         <v>460</v>
       </c>
       <c r="N928" t="n">
-        <v>3110.8404252438</v>
+        <v>3110.840414859</v>
       </c>
       <c r="O928" t="n">
-        <v>1430986.595612148</v>
+        <v>1430986.59083514</v>
       </c>
       <c r="P928" t="n">
         <v>4500</v>
@@ -42381,10 +42381,10 @@
         <v>15</v>
       </c>
       <c r="N957" t="n">
-        <v>1595.5116515014</v>
+        <v>1595.5116012774</v>
       </c>
       <c r="O957" t="n">
-        <v>23932.674772521</v>
+        <v>23932.674019161</v>
       </c>
       <c r="P957" t="n">
         <v>2500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -12017,10 +12017,10 @@
         <v>200</v>
       </c>
       <c r="N274" t="n">
-        <v>2582.255546613</v>
+        <v>2582.2555436242</v>
       </c>
       <c r="O274" t="n">
-        <v>516451.1093226001</v>
+        <v>516451.10872484</v>
       </c>
       <c r="P274" t="n">
         <v>4500</v>
@@ -17410,22 +17410,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M396" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N396" t="n">
-        <v>8296.6427272727</v>
+        <v>8296.6429032258</v>
       </c>
       <c r="O396" t="n">
-        <v>99559.71272727239</v>
+        <v>82966.42903225801</v>
       </c>
       <c r="P396" t="n">
         <v>15900</v>
       </c>
       <c r="Q396" t="n">
-        <v>190800</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="397">
@@ -17862,10 +17862,10 @@
         <v>2018</v>
       </c>
       <c r="N406" t="n">
-        <v>1550.1938919769</v>
+        <v>1550.1938936103</v>
       </c>
       <c r="O406" t="n">
-        <v>3128291.274009384</v>
+        <v>3128291.277305585</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
@@ -25914,10 +25914,10 @@
         <v>1</v>
       </c>
       <c r="N594" t="n">
-        <v>8332.779621212099</v>
+        <v>8332.779620253201</v>
       </c>
       <c r="O594" t="n">
-        <v>8332.779621212099</v>
+        <v>8332.779620253201</v>
       </c>
       <c r="P594" t="n">
         <v>14900</v>
@@ -34896,22 +34896,22 @@
         <v>0</v>
       </c>
       <c r="L792" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M792" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N792" t="n">
-        <v>17075.989522491</v>
+        <v>17075.989522161</v>
       </c>
       <c r="O792" t="n">
-        <v>2919994.208345961</v>
+        <v>2902918.21876737</v>
       </c>
       <c r="P792" t="n">
         <v>27500</v>
       </c>
       <c r="Q792" t="n">
-        <v>4702500</v>
+        <v>4675000</v>
       </c>
     </row>
     <row r="793">
@@ -40835,10 +40835,10 @@
         <v>2488</v>
       </c>
       <c r="N922" t="n">
-        <v>517.29096206919</v>
+        <v>517.29097263266</v>
       </c>
       <c r="O922" t="n">
-        <v>1287019.913628145</v>
+        <v>1287019.939910058</v>
       </c>
       <c r="P922" t="n">
         <v>900</v>
@@ -47386,22 +47386,22 @@
         <v>0</v>
       </c>
       <c r="L1067" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M1067" t="n">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="N1067" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1067" t="n">
-        <v>1263214.3</v>
+        <v>1205940.1</v>
       </c>
       <c r="P1067" t="n">
         <v>5100</v>
       </c>
       <c r="Q1067" t="n">
-        <v>2024700</v>
+        <v>1932900</v>
       </c>
     </row>
     <row r="1068">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -691,10 +691,10 @@
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>96741.42375</v>
+        <v>96741.43166666701</v>
       </c>
       <c r="O7" t="n">
-        <v>290224.27125</v>
+        <v>290224.295000001</v>
       </c>
       <c r="P7" t="n">
         <v>188900</v>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -771,19 +771,19 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
         <v>27000</v>
       </c>
       <c r="O9" t="n">
-        <v>108000</v>
+        <v>81000</v>
       </c>
       <c r="P9" t="n">
         <v>92000</v>
       </c>
       <c r="Q9" t="n">
-        <v>368000</v>
+        <v>276000</v>
       </c>
     </row>
     <row r="10">
@@ -1385,10 +1385,10 @@
         <v>71</v>
       </c>
       <c r="N24" t="n">
-        <v>1990.0435171103</v>
+        <v>1990.0434548944</v>
       </c>
       <c r="O24" t="n">
-        <v>141293.0897148313</v>
+        <v>141293.0852975024</v>
       </c>
       <c r="P24" t="n">
         <v>4400</v>
@@ -1424,10 +1424,10 @@
         <v>144</v>
       </c>
       <c r="N25" t="n">
-        <v>3376.7464524986</v>
+        <v>3376.7464515243</v>
       </c>
       <c r="O25" t="n">
-        <v>486251.4891597984</v>
+        <v>486251.4890194992</v>
       </c>
       <c r="P25" t="n">
         <v>4500</v>
@@ -2879,10 +2879,10 @@
         <v>35</v>
       </c>
       <c r="N61" t="n">
-        <v>6272.8549315068</v>
+        <v>6272.8549740933</v>
       </c>
       <c r="O61" t="n">
-        <v>219549.922602738</v>
+        <v>219549.9240932655</v>
       </c>
       <c r="P61" t="n">
         <v>7900</v>
@@ -2996,10 +2996,10 @@
         <v>44</v>
       </c>
       <c r="N64" t="n">
-        <v>3926.8370954357</v>
+        <v>3926.8370909091</v>
       </c>
       <c r="O64" t="n">
-        <v>172780.8321991708</v>
+        <v>172780.8320000004</v>
       </c>
       <c r="P64" t="n">
         <v>4800</v>
@@ -3038,10 +3038,10 @@
         <v>13</v>
       </c>
       <c r="N65" t="n">
-        <v>11324.694146341</v>
+        <v>11324.693846154</v>
       </c>
       <c r="O65" t="n">
-        <v>147221.023902433</v>
+        <v>147221.020000002</v>
       </c>
       <c r="P65" t="n">
         <v>19900</v>
@@ -3787,10 +3787,10 @@
         <v>23</v>
       </c>
       <c r="N84" t="n">
-        <v>14857.623257919</v>
+        <v>14857.623272727</v>
       </c>
       <c r="O84" t="n">
-        <v>341725.334932137</v>
+        <v>341725.335272721</v>
       </c>
       <c r="P84" t="n">
         <v>34900</v>
@@ -3920,10 +3920,10 @@
         <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>26465.343333333</v>
+        <v>26465.346</v>
       </c>
       <c r="O87" t="n">
-        <v>26465.343333333</v>
+        <v>26465.346</v>
       </c>
       <c r="P87" t="n">
         <v>42900</v>
@@ -4095,10 +4095,10 @@
         <v>53</v>
       </c>
       <c r="N91" t="n">
-        <v>3910.6280519481</v>
+        <v>3910.6280349345</v>
       </c>
       <c r="O91" t="n">
-        <v>207263.2867532493</v>
+        <v>207263.2858515285</v>
       </c>
       <c r="P91" t="n">
         <v>9100</v>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4686,19 +4686,19 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N104" t="n">
-        <v>30708.848333333</v>
+        <v>30708.828</v>
       </c>
       <c r="O104" t="n">
-        <v>307088.48333333</v>
+        <v>245670.624</v>
       </c>
       <c r="P104" t="n">
         <v>53500</v>
       </c>
       <c r="Q104" t="n">
-        <v>535000</v>
+        <v>428000</v>
       </c>
     </row>
     <row r="105">
@@ -4731,10 +4731,10 @@
         <v>17</v>
       </c>
       <c r="N105" t="n">
-        <v>12837.967540984</v>
+        <v>12837.9714</v>
       </c>
       <c r="O105" t="n">
-        <v>218245.448196728</v>
+        <v>218245.5138</v>
       </c>
       <c r="P105" t="n">
         <v>22900</v>
@@ -4904,10 +4904,10 @@
         <v>16</v>
       </c>
       <c r="N109" t="n">
-        <v>16486.408571429</v>
+        <v>16486.40848</v>
       </c>
       <c r="O109" t="n">
-        <v>263782.537142864</v>
+        <v>263782.53568</v>
       </c>
       <c r="P109" t="n">
         <v>30500</v>
@@ -4985,10 +4985,10 @@
         <v>26</v>
       </c>
       <c r="N111" t="n">
-        <v>15711.965777778</v>
+        <v>15711.96573991</v>
       </c>
       <c r="O111" t="n">
-        <v>408511.110222228</v>
+        <v>408511.10923766</v>
       </c>
       <c r="P111" t="n">
         <v>28500</v>
@@ -5079,10 +5079,10 @@
         <v>10</v>
       </c>
       <c r="N113" t="n">
-        <v>30238.812647059</v>
+        <v>30238.813103448</v>
       </c>
       <c r="O113" t="n">
-        <v>302388.12647059</v>
+        <v>302388.13103448</v>
       </c>
       <c r="P113" t="n">
         <v>51100</v>
@@ -6061,10 +6061,10 @@
         <v>12</v>
       </c>
       <c r="N136" t="n">
-        <v>200072.20075</v>
+        <v>200072.20121739</v>
       </c>
       <c r="O136" t="n">
-        <v>2400866.409</v>
+        <v>2400866.41460868</v>
       </c>
       <c r="P136" t="n">
         <v>312000</v>
@@ -9270,10 +9270,10 @@
         <v>2</v>
       </c>
       <c r="N210" t="n">
-        <v>732.63416666667</v>
+        <v>732.63425531915</v>
       </c>
       <c r="O210" t="n">
-        <v>1465.26833333334</v>
+        <v>1465.2685106383</v>
       </c>
       <c r="P210" t="n">
         <v>6200</v>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9451,19 +9451,19 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N214" t="n">
         <v>1000</v>
       </c>
       <c r="O214" t="n">
-        <v>28000</v>
+        <v>27000</v>
       </c>
       <c r="P214" t="n">
         <v>1200</v>
       </c>
       <c r="Q214" t="n">
-        <v>33600</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="215">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9492,19 +9492,19 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="N215" t="n">
-        <v>1950.214568029</v>
+        <v>1950.2145482866</v>
       </c>
       <c r="O215" t="n">
-        <v>512906.431391627</v>
+        <v>499254.9243613696</v>
       </c>
       <c r="P215" t="n">
         <v>2900</v>
       </c>
       <c r="Q215" t="n">
-        <v>762700</v>
+        <v>742400</v>
       </c>
     </row>
     <row r="216">
@@ -9647,7 +9647,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>1624</v>
+        <v>1613</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -9656,19 +9656,19 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>1624</v>
+        <v>1613</v>
       </c>
       <c r="N219" t="n">
         <v>1726.32</v>
       </c>
       <c r="O219" t="n">
-        <v>2803543.68</v>
+        <v>2784554.16</v>
       </c>
       <c r="P219" t="n">
         <v>1500</v>
       </c>
       <c r="Q219" t="n">
-        <v>2436000</v>
+        <v>2419500</v>
       </c>
     </row>
     <row r="220">
@@ -10198,7 +10198,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -10207,19 +10207,19 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="N232" t="n">
-        <v>1098.0616971665</v>
+        <v>1098.0617613973</v>
       </c>
       <c r="O232" t="n">
-        <v>516088.9976682549</v>
+        <v>509500.6572883472</v>
       </c>
       <c r="P232" t="n">
         <v>1500</v>
       </c>
       <c r="Q232" t="n">
-        <v>705000</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="233">
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="J264" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -11568,19 +11568,19 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="N264" t="n">
         <v>2913</v>
       </c>
       <c r="O264" t="n">
-        <v>448602</v>
+        <v>413646</v>
       </c>
       <c r="P264" t="n">
         <v>4950</v>
       </c>
       <c r="Q264" t="n">
-        <v>762300</v>
+        <v>702900</v>
       </c>
     </row>
     <row r="265">
@@ -11649,7 +11649,7 @@
         </is>
       </c>
       <c r="J266" t="n">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -11658,19 +11658,19 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N266" t="n">
         <v>2804.33</v>
       </c>
       <c r="O266" t="n">
-        <v>1494707.89</v>
+        <v>1491903.56</v>
       </c>
       <c r="P266" t="n">
         <v>4900</v>
       </c>
       <c r="Q266" t="n">
-        <v>2611700</v>
+        <v>2606800</v>
       </c>
     </row>
     <row r="267">
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -11781,19 +11781,19 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N269" t="n">
         <v>2745.81</v>
       </c>
       <c r="O269" t="n">
-        <v>153765.36</v>
+        <v>151019.55</v>
       </c>
       <c r="P269" t="n">
         <v>5600</v>
       </c>
       <c r="Q269" t="n">
-        <v>313600</v>
+        <v>308000</v>
       </c>
     </row>
     <row r="270">
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12014,19 +12014,19 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="N274" t="n">
-        <v>2582.2555436242</v>
+        <v>2582.2555195682</v>
       </c>
       <c r="O274" t="n">
-        <v>516451.10872484</v>
+        <v>506122.0818353671</v>
       </c>
       <c r="P274" t="n">
         <v>4500</v>
       </c>
       <c r="Q274" t="n">
-        <v>900000</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="275">
@@ -12051,7 +12051,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12060,19 +12060,19 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="N275" t="n">
         <v>10600</v>
       </c>
       <c r="O275" t="n">
-        <v>1653600</v>
+        <v>805600</v>
       </c>
       <c r="P275" t="n">
         <v>17200</v>
       </c>
       <c r="Q275" t="n">
-        <v>2683200</v>
+        <v>1307200</v>
       </c>
     </row>
     <row r="276">
@@ -12109,10 +12109,10 @@
         <v>126</v>
       </c>
       <c r="N276" t="n">
-        <v>5216.8960627633</v>
+        <v>5216.8960541642</v>
       </c>
       <c r="O276" t="n">
-        <v>657328.9039081758</v>
+        <v>657328.9028246892</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -12312,7 +12312,7 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -12321,19 +12321,19 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N281" t="n">
         <v>37904.5</v>
       </c>
       <c r="O281" t="n">
-        <v>75809</v>
+        <v>37904.5</v>
       </c>
       <c r="P281" t="n">
         <v>64500</v>
       </c>
       <c r="Q281" t="n">
-        <v>129000</v>
+        <v>64500</v>
       </c>
     </row>
     <row r="282">
@@ -12394,7 +12394,7 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -12403,19 +12403,19 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N283" t="n">
         <v>6713.08</v>
       </c>
       <c r="O283" t="n">
-        <v>537046.4</v>
+        <v>523620.24</v>
       </c>
       <c r="P283" t="n">
         <v>9900</v>
       </c>
       <c r="Q283" t="n">
-        <v>792000</v>
+        <v>772200</v>
       </c>
     </row>
     <row r="284">
@@ -12680,10 +12680,10 @@
         <v>54</v>
       </c>
       <c r="N289" t="n">
-        <v>3230.0670700637</v>
+        <v>3230.0670575693</v>
       </c>
       <c r="O289" t="n">
-        <v>174423.6217834398</v>
+        <v>174423.6211087422</v>
       </c>
       <c r="P289" t="n">
         <v>6200</v>
@@ -12847,7 +12847,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -12856,19 +12856,19 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="N293" t="n">
         <v>1337.34</v>
       </c>
       <c r="O293" t="n">
-        <v>339684.36</v>
+        <v>331660.32</v>
       </c>
       <c r="P293" t="n">
         <v>2500</v>
       </c>
       <c r="Q293" t="n">
-        <v>635000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="294">
@@ -12905,10 +12905,10 @@
         <v>85</v>
       </c>
       <c r="N294" t="n">
-        <v>2694.8231670588</v>
+        <v>2694.8231638418</v>
       </c>
       <c r="O294" t="n">
-        <v>229059.969199998</v>
+        <v>229059.968926553</v>
       </c>
       <c r="P294" t="n">
         <v>4900</v>
@@ -12980,7 +12980,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -12989,19 +12989,19 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="N296" t="n">
         <v>1026.13</v>
       </c>
       <c r="O296" t="n">
-        <v>402242.96</v>
+        <v>363250.02</v>
       </c>
       <c r="P296" t="n">
         <v>1900</v>
       </c>
       <c r="Q296" t="n">
-        <v>744800</v>
+        <v>672600</v>
       </c>
     </row>
     <row r="297">
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>3875</v>
+        <v>3815</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -13081,19 +13081,19 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>3875</v>
+        <v>3815</v>
       </c>
       <c r="N298" t="n">
         <v>156.25</v>
       </c>
       <c r="O298" t="n">
-        <v>605468.75</v>
+        <v>596093.75</v>
       </c>
       <c r="P298" t="n">
         <v>250</v>
       </c>
       <c r="Q298" t="n">
-        <v>968750</v>
+        <v>953750</v>
       </c>
     </row>
     <row r="299">
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -13358,19 +13358,19 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="N304" t="n">
-        <v>3795.7100075815</v>
+        <v>3795.7100075887</v>
       </c>
       <c r="O304" t="n">
-        <v>1089368.772175891</v>
+        <v>1070390.222140013</v>
       </c>
       <c r="P304" t="n">
         <v>6200</v>
       </c>
       <c r="Q304" t="n">
-        <v>1779400</v>
+        <v>1748400</v>
       </c>
     </row>
     <row r="305">
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -13404,19 +13404,19 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N305" t="n">
         <v>3684</v>
       </c>
       <c r="O305" t="n">
-        <v>957840</v>
+        <v>939420</v>
       </c>
       <c r="P305" t="n">
         <v>6200</v>
       </c>
       <c r="Q305" t="n">
-        <v>1612000</v>
+        <v>1581000</v>
       </c>
     </row>
     <row r="306">
@@ -13482,7 +13482,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13491,19 +13491,19 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N307" t="n">
         <v>4357.55</v>
       </c>
       <c r="O307" t="n">
-        <v>915085.5</v>
+        <v>906370.4</v>
       </c>
       <c r="P307" t="n">
         <v>7500</v>
       </c>
       <c r="Q307" t="n">
-        <v>1575000</v>
+        <v>1560000</v>
       </c>
     </row>
     <row r="308">
@@ -13627,10 +13627,10 @@
         <v>33</v>
       </c>
       <c r="N310" t="n">
-        <v>4890.9300489596</v>
+        <v>4890.9300493218</v>
       </c>
       <c r="O310" t="n">
-        <v>161400.6916156668</v>
+        <v>161400.6916276194</v>
       </c>
       <c r="P310" t="n">
         <v>8200</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -13670,19 +13670,19 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N311" t="n">
-        <v>5484.9521212121</v>
+        <v>5484.9528125</v>
       </c>
       <c r="O311" t="n">
-        <v>351036.9357575744</v>
+        <v>334582.1215625</v>
       </c>
       <c r="P311" t="n">
         <v>8500</v>
       </c>
       <c r="Q311" t="n">
-        <v>544000</v>
+        <v>518500</v>
       </c>
     </row>
     <row r="312">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>549</v>
+        <v>485</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -13719,19 +13719,19 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>549</v>
+        <v>485</v>
       </c>
       <c r="N312" t="n">
         <v>1203.38</v>
       </c>
       <c r="O312" t="n">
-        <v>660655.6200000001</v>
+        <v>583639.3</v>
       </c>
       <c r="P312" t="n">
         <v>1900</v>
       </c>
       <c r="Q312" t="n">
-        <v>1043100</v>
+        <v>921500</v>
       </c>
     </row>
     <row r="313">
@@ -13756,7 +13756,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -13765,19 +13765,19 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="N313" t="n">
         <v>3472</v>
       </c>
       <c r="O313" t="n">
-        <v>2340128</v>
+        <v>2298464</v>
       </c>
       <c r="P313" t="n">
         <v>4800</v>
       </c>
       <c r="Q313" t="n">
-        <v>3235200</v>
+        <v>3177600</v>
       </c>
     </row>
     <row r="314">
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -14297,19 +14297,19 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N325" t="n">
         <v>10716.34</v>
       </c>
       <c r="O325" t="n">
-        <v>160745.1</v>
+        <v>64298.04</v>
       </c>
       <c r="P325" t="n">
         <v>39000</v>
       </c>
       <c r="Q325" t="n">
-        <v>585000</v>
+        <v>234000</v>
       </c>
     </row>
     <row r="326">
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -14510,19 +14510,19 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="N330" t="n">
-        <v>3594.2538618926</v>
+        <v>3594.2537131631</v>
       </c>
       <c r="O330" t="n">
-        <v>122204.6313043484</v>
+        <v>370208.1324557993</v>
       </c>
       <c r="P330" t="n">
         <v>6500</v>
       </c>
       <c r="Q330" t="n">
-        <v>221000</v>
+        <v>669500</v>
       </c>
     </row>
     <row r="331">
@@ -14629,7 +14629,7 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -14638,19 +14638,19 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="N333" t="n">
         <v>2953.73</v>
       </c>
       <c r="O333" t="n">
-        <v>558254.97</v>
+        <v>522810.21</v>
       </c>
       <c r="P333" t="n">
         <v>4900</v>
       </c>
       <c r="Q333" t="n">
-        <v>926100</v>
+        <v>867300</v>
       </c>
     </row>
     <row r="334">
@@ -14852,7 +14852,7 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -14861,19 +14861,19 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="N338" t="n">
-        <v>616.01871837471</v>
+        <v>616.01871807046</v>
       </c>
       <c r="O338" t="n">
-        <v>1007806.623261026</v>
+        <v>1004726.52917292</v>
       </c>
       <c r="P338" t="n">
         <v>800</v>
       </c>
       <c r="Q338" t="n">
-        <v>1308800</v>
+        <v>1304800</v>
       </c>
     </row>
     <row r="339">
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>523</v>
+        <v>3</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
@@ -14905,19 +14905,19 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>523</v>
+        <v>3</v>
       </c>
       <c r="N339" t="n">
         <v>2090.85</v>
       </c>
       <c r="O339" t="n">
-        <v>1093514.55</v>
+        <v>6272.549999999999</v>
       </c>
       <c r="P339" t="n">
         <v>2900</v>
       </c>
       <c r="Q339" t="n">
-        <v>1516700</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="340">
@@ -14940,7 +14940,7 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
@@ -14949,19 +14949,19 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="N340" t="n">
-        <v>914.58875378406</v>
+        <v>914.58875315497</v>
       </c>
       <c r="O340" t="n">
-        <v>838677.887219983</v>
+        <v>837763.2978899525</v>
       </c>
       <c r="P340" t="n">
         <v>1200</v>
       </c>
       <c r="Q340" t="n">
-        <v>1100400</v>
+        <v>1099200</v>
       </c>
     </row>
     <row r="341">
@@ -15118,7 +15118,7 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
@@ -15127,19 +15127,19 @@
         <v>0</v>
       </c>
       <c r="M344" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="N344" t="n">
         <v>1381.75</v>
       </c>
       <c r="O344" t="n">
-        <v>117448.75</v>
+        <v>109158.25</v>
       </c>
       <c r="P344" t="n">
         <v>2500</v>
       </c>
       <c r="Q344" t="n">
-        <v>212500</v>
+        <v>197500</v>
       </c>
     </row>
     <row r="345">
@@ -15526,10 +15526,10 @@
         <v>204</v>
       </c>
       <c r="N353" t="n">
-        <v>4372.2107916548</v>
+        <v>4372.2107917679</v>
       </c>
       <c r="O353" t="n">
-        <v>891931.0014975793</v>
+        <v>891931.0015206517</v>
       </c>
       <c r="P353" t="n">
         <v>7500</v>
@@ -15616,10 +15616,10 @@
         <v>2</v>
       </c>
       <c r="N355" t="n">
-        <v>1592.5662962963</v>
+        <v>1592.5662209302</v>
       </c>
       <c r="O355" t="n">
-        <v>3185.1325925926</v>
+        <v>3185.1324418604</v>
       </c>
       <c r="P355" t="n">
         <v>3900</v>
@@ -15732,7 +15732,7 @@
         </is>
       </c>
       <c r="J358" t="n">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K358" t="n">
         <v>0</v>
@@ -15741,19 +15741,19 @@
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="N358" t="n">
         <v>3655.96</v>
       </c>
       <c r="O358" t="n">
-        <v>650760.88</v>
+        <v>632481.08</v>
       </c>
       <c r="P358" t="n">
         <v>5500</v>
       </c>
       <c r="Q358" t="n">
-        <v>979000</v>
+        <v>951500</v>
       </c>
     </row>
     <row r="359">
@@ -16127,7 +16127,7 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
@@ -16136,19 +16136,19 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N367" t="n">
         <v>6242.93</v>
       </c>
       <c r="O367" t="n">
-        <v>343361.15</v>
+        <v>330875.29</v>
       </c>
       <c r="P367" t="n">
         <v>10400</v>
       </c>
       <c r="Q367" t="n">
-        <v>572000</v>
+        <v>551200</v>
       </c>
     </row>
     <row r="368">
@@ -16176,7 +16176,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -16185,19 +16185,19 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="N368" t="n">
         <v>4648.6</v>
       </c>
       <c r="O368" t="n">
-        <v>1566578.2</v>
+        <v>1547983.8</v>
       </c>
       <c r="P368" t="n">
         <v>8900</v>
       </c>
       <c r="Q368" t="n">
-        <v>2999300</v>
+        <v>2963700</v>
       </c>
     </row>
     <row r="369">
@@ -16393,7 +16393,7 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
@@ -16402,19 +16402,19 @@
         <v>0</v>
       </c>
       <c r="M373" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N373" t="n">
-        <v>1532.6290268065</v>
+        <v>1532.6290266647</v>
       </c>
       <c r="O373" t="n">
-        <v>493506.546631693</v>
+        <v>490441.288532704</v>
       </c>
       <c r="P373" t="n">
         <v>1200</v>
       </c>
       <c r="Q373" t="n">
-        <v>386400</v>
+        <v>384000</v>
       </c>
     </row>
     <row r="374">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
@@ -16487,19 +16487,19 @@
         <v>0</v>
       </c>
       <c r="M375" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N375" t="n">
         <v>1343.77</v>
       </c>
       <c r="O375" t="n">
-        <v>221722.05</v>
+        <v>220378.28</v>
       </c>
       <c r="P375" t="n">
         <v>2500</v>
       </c>
       <c r="Q375" t="n">
-        <v>412500</v>
+        <v>410000</v>
       </c>
     </row>
     <row r="376">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="J379" t="n">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="K379" t="n">
         <v>0</v>
@@ -16663,19 +16663,19 @@
         <v>0</v>
       </c>
       <c r="M379" t="n">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="N379" t="n">
         <v>1387.55</v>
       </c>
       <c r="O379" t="n">
-        <v>470379.45</v>
+        <v>462054.15</v>
       </c>
       <c r="P379" t="n">
         <v>2300</v>
       </c>
       <c r="Q379" t="n">
-        <v>779700</v>
+        <v>765900</v>
       </c>
     </row>
     <row r="380">
@@ -17190,7 +17190,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -17199,19 +17199,19 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="N391" t="n">
         <v>11921.4</v>
       </c>
       <c r="O391" t="n">
-        <v>1215982.8</v>
+        <v>429170.4</v>
       </c>
       <c r="P391" t="n">
         <v>19900</v>
       </c>
       <c r="Q391" t="n">
-        <v>2029800</v>
+        <v>716400</v>
       </c>
     </row>
     <row r="392">
@@ -17404,13 +17404,13 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K396" t="n">
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M396" t="n">
         <v>10</v>
@@ -17579,7 +17579,7 @@
         </is>
       </c>
       <c r="J400" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="K400" t="n">
         <v>0</v>
@@ -17588,19 +17588,19 @@
         <v>0</v>
       </c>
       <c r="M400" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="N400" t="n">
         <v>9903</v>
       </c>
       <c r="O400" t="n">
-        <v>693210</v>
+        <v>198060</v>
       </c>
       <c r="P400" t="n">
         <v>15900</v>
       </c>
       <c r="Q400" t="n">
-        <v>1113000</v>
+        <v>318000</v>
       </c>
     </row>
     <row r="401">
@@ -17683,10 +17683,10 @@
         <v>483</v>
       </c>
       <c r="N402" t="n">
-        <v>1630.9238750315</v>
+        <v>1630.9238760081</v>
       </c>
       <c r="O402" t="n">
-        <v>787736.2316402146</v>
+        <v>787736.2321119123</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
@@ -17804,7 +17804,7 @@
         </is>
       </c>
       <c r="J405" t="n">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="K405" t="n">
         <v>0</v>
@@ -17813,19 +17813,19 @@
         <v>0</v>
       </c>
       <c r="M405" t="n">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="N405" t="n">
-        <v>1690.5947980214</v>
+        <v>1690.5946096346</v>
       </c>
       <c r="O405" t="n">
-        <v>791198.3654740152</v>
+        <v>775982.9258222814</v>
       </c>
       <c r="P405" t="n">
         <v>2900</v>
       </c>
       <c r="Q405" t="n">
-        <v>1357200</v>
+        <v>1331100</v>
       </c>
     </row>
     <row r="406">
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>2018</v>
+        <v>1997</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
@@ -17859,19 +17859,19 @@
         <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>2018</v>
+        <v>1997</v>
       </c>
       <c r="N406" t="n">
-        <v>1550.1938936103</v>
+        <v>1550.1939063158</v>
       </c>
       <c r="O406" t="n">
-        <v>3128291.277305585</v>
+        <v>3095737.230912652</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
       </c>
       <c r="Q406" t="n">
-        <v>5045000</v>
+        <v>4992500</v>
       </c>
     </row>
     <row r="407">
@@ -17908,10 +17908,10 @@
         <v>3</v>
       </c>
       <c r="N407" t="n">
-        <v>1579.3891212121</v>
+        <v>1579.3888161994</v>
       </c>
       <c r="O407" t="n">
-        <v>4738.1673636363</v>
+        <v>4738.1664485982</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="J408" t="n">
-        <v>1174</v>
+        <v>1167</v>
       </c>
       <c r="K408" t="n">
         <v>0</v>
@@ -17951,19 +17951,19 @@
         <v>0</v>
       </c>
       <c r="M408" t="n">
-        <v>1174</v>
+        <v>1167</v>
       </c>
       <c r="N408" t="n">
-        <v>2403.5131199831</v>
+        <v>2403.5134379057</v>
       </c>
       <c r="O408" t="n">
-        <v>2821724.402860159</v>
+        <v>2804900.182035952</v>
       </c>
       <c r="P408" t="n">
         <v>3500</v>
       </c>
       <c r="Q408" t="n">
-        <v>4109000</v>
+        <v>4084500</v>
       </c>
     </row>
     <row r="409">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="J413" t="n">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="K413" t="n">
         <v>0</v>
@@ -18168,19 +18168,19 @@
         <v>0</v>
       </c>
       <c r="M413" t="n">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="N413" t="n">
         <v>1076.92</v>
       </c>
       <c r="O413" t="n">
-        <v>1852302.4</v>
+        <v>1850148.56</v>
       </c>
       <c r="P413" t="n">
         <v>1400</v>
       </c>
       <c r="Q413" t="n">
-        <v>2408000</v>
+        <v>2405200</v>
       </c>
     </row>
     <row r="414">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="J414" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K414" t="n">
         <v>0</v>
@@ -18209,19 +18209,19 @@
         <v>0</v>
       </c>
       <c r="M414" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N414" t="n">
-        <v>1232.8069082126</v>
+        <v>1232.80645</v>
       </c>
       <c r="O414" t="n">
-        <v>33285.7865217402</v>
+        <v>32052.9677</v>
       </c>
       <c r="P414" t="n">
         <v>2400</v>
       </c>
       <c r="Q414" t="n">
-        <v>64800</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="415">
@@ -19258,7 +19258,7 @@
         </is>
       </c>
       <c r="J438" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K438" t="n">
         <v>0</v>
@@ -19267,19 +19267,19 @@
         <v>0</v>
       </c>
       <c r="M438" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N438" t="n">
         <v>3253</v>
       </c>
       <c r="O438" t="n">
-        <v>1060478</v>
+        <v>1057225</v>
       </c>
       <c r="P438" t="n">
         <v>3900</v>
       </c>
       <c r="Q438" t="n">
-        <v>1271400</v>
+        <v>1267500</v>
       </c>
     </row>
     <row r="439">
@@ -19565,7 +19565,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -19574,19 +19574,19 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N445" t="n">
         <v>7028</v>
       </c>
       <c r="O445" t="n">
-        <v>660632</v>
+        <v>653604</v>
       </c>
       <c r="P445" t="n">
         <v>15900</v>
       </c>
       <c r="Q445" t="n">
-        <v>1494600</v>
+        <v>1478700</v>
       </c>
     </row>
     <row r="446">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="J473" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
@@ -20773,19 +20773,19 @@
         <v>0</v>
       </c>
       <c r="M473" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N473" t="n">
         <v>42313</v>
       </c>
       <c r="O473" t="n">
-        <v>592382</v>
+        <v>550069</v>
       </c>
       <c r="P473" t="n">
         <v>63900</v>
       </c>
       <c r="Q473" t="n">
-        <v>894600</v>
+        <v>830700</v>
       </c>
     </row>
     <row r="474">
@@ -20808,7 +20808,7 @@
         </is>
       </c>
       <c r="J474" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
@@ -20817,19 +20817,19 @@
         <v>0</v>
       </c>
       <c r="M474" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N474" t="n">
-        <v>4196.872531224</v>
+        <v>4196.8725319267</v>
       </c>
       <c r="O474" t="n">
-        <v>616940.262089928</v>
+        <v>612743.3896612981</v>
       </c>
       <c r="P474" t="n">
         <v>5900</v>
       </c>
       <c r="Q474" t="n">
-        <v>867300</v>
+        <v>861400</v>
       </c>
     </row>
     <row r="475">
@@ -21054,7 +21054,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K480" t="n">
         <v>0</v>
@@ -21063,19 +21063,19 @@
         <v>0</v>
       </c>
       <c r="M480" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N480" t="n">
         <v>2661.82</v>
       </c>
       <c r="O480" t="n">
-        <v>106472.8</v>
+        <v>101149.16</v>
       </c>
       <c r="P480" t="n">
         <v>3200</v>
       </c>
       <c r="Q480" t="n">
-        <v>128000</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="481">
@@ -21218,7 +21218,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -21227,19 +21227,19 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N484" t="n">
         <v>2081</v>
       </c>
       <c r="O484" t="n">
-        <v>185209</v>
+        <v>181047</v>
       </c>
       <c r="P484" t="n">
         <v>3200</v>
       </c>
       <c r="Q484" t="n">
-        <v>284800</v>
+        <v>278400</v>
       </c>
     </row>
     <row r="485">
@@ -21341,7 +21341,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -21350,19 +21350,19 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N487" t="n">
         <v>1969</v>
       </c>
       <c r="O487" t="n">
-        <v>220528</v>
+        <v>216590</v>
       </c>
       <c r="P487" t="n">
         <v>1500</v>
       </c>
       <c r="Q487" t="n">
-        <v>168000</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="488">
@@ -21469,7 +21469,7 @@
         </is>
       </c>
       <c r="J490" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K490" t="n">
         <v>0</v>
@@ -21478,19 +21478,19 @@
         <v>0</v>
       </c>
       <c r="M490" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N490" t="n">
         <v>2567</v>
       </c>
       <c r="O490" t="n">
-        <v>474895</v>
+        <v>472328</v>
       </c>
       <c r="P490" t="n">
         <v>4500</v>
       </c>
       <c r="Q490" t="n">
-        <v>832500</v>
+        <v>828000</v>
       </c>
     </row>
     <row r="491">
@@ -22096,10 +22096,10 @@
         <v>52</v>
       </c>
       <c r="N505" t="n">
-        <v>22485.695561036</v>
+        <v>22485.695555556</v>
       </c>
       <c r="O505" t="n">
-        <v>1169256.169173872</v>
+        <v>1169256.168888912</v>
       </c>
       <c r="P505" t="n">
         <v>36500</v>
@@ -22420,7 +22420,7 @@
         </is>
       </c>
       <c r="J513" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K513" t="n">
         <v>0</v>
@@ -22429,19 +22429,19 @@
         <v>0</v>
       </c>
       <c r="M513" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N513" t="n">
-        <v>2680.7396948941</v>
+        <v>2680.739694704</v>
       </c>
       <c r="O513" t="n">
-        <v>394068.7351494327</v>
+        <v>391387.995426784</v>
       </c>
       <c r="P513" t="n">
         <v>4900</v>
       </c>
       <c r="Q513" t="n">
-        <v>720300</v>
+        <v>715400</v>
       </c>
     </row>
     <row r="514">
@@ -22461,7 +22461,7 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -22470,19 +22470,19 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="N514" t="n">
-        <v>880.32956085919</v>
+        <v>880.32956314156</v>
       </c>
       <c r="O514" t="n">
-        <v>1185803.918477329</v>
+        <v>1184923.59198854</v>
       </c>
       <c r="P514" t="n">
         <v>1200</v>
       </c>
       <c r="Q514" t="n">
-        <v>1616400</v>
+        <v>1615200</v>
       </c>
     </row>
     <row r="515">
@@ -22753,7 +22753,7 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -22762,19 +22762,19 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N521" t="n">
         <v>2465</v>
       </c>
       <c r="O521" t="n">
-        <v>451095</v>
+        <v>448630</v>
       </c>
       <c r="P521" t="n">
         <v>3700</v>
       </c>
       <c r="Q521" t="n">
-        <v>677100</v>
+        <v>673400</v>
       </c>
     </row>
     <row r="522">
@@ -24271,10 +24271,10 @@
         <v>50</v>
       </c>
       <c r="N556" t="n">
-        <v>11562.038465753</v>
+        <v>11562.038444444</v>
       </c>
       <c r="O556" t="n">
-        <v>578101.92328765</v>
+        <v>578101.9222222001</v>
       </c>
       <c r="P556" t="n">
         <v>18500</v>
@@ -24317,10 +24317,10 @@
         <v>57</v>
       </c>
       <c r="N557" t="n">
-        <v>13513.643106061</v>
+        <v>13513.643153846</v>
       </c>
       <c r="O557" t="n">
-        <v>770277.657045477</v>
+        <v>770277.659769222</v>
       </c>
       <c r="P557" t="n">
         <v>21900</v>
@@ -25247,7 +25247,7 @@
         </is>
       </c>
       <c r="J579" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K579" t="n">
         <v>0</v>
@@ -25256,19 +25256,19 @@
         <v>0</v>
       </c>
       <c r="M579" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N579" t="n">
         <v>4793.53</v>
       </c>
       <c r="O579" t="n">
-        <v>1265491.92</v>
+        <v>1255904.86</v>
       </c>
       <c r="P579" t="n">
         <v>7900</v>
       </c>
       <c r="Q579" t="n">
-        <v>2085600</v>
+        <v>2069800</v>
       </c>
     </row>
     <row r="580">
@@ -25462,7 +25462,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
@@ -25471,19 +25471,19 @@
         <v>0</v>
       </c>
       <c r="M584" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N584" t="n">
         <v>22730.48</v>
       </c>
       <c r="O584" t="n">
-        <v>363687.68</v>
+        <v>340957.2</v>
       </c>
       <c r="P584" t="n">
         <v>36900</v>
       </c>
       <c r="Q584" t="n">
-        <v>590400</v>
+        <v>553500</v>
       </c>
     </row>
     <row r="585">
@@ -25658,10 +25658,10 @@
         <v>39</v>
       </c>
       <c r="N588" t="n">
-        <v>27123.76518797</v>
+        <v>27123.765160681</v>
       </c>
       <c r="O588" t="n">
-        <v>1057826.84233083</v>
+        <v>1057826.841266559</v>
       </c>
       <c r="P588" t="n">
         <v>44500</v>
@@ -26076,7 +26076,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -26085,19 +26085,19 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="N598" t="n">
-        <v>1561.0022278481</v>
+        <v>1561.0026027397</v>
       </c>
       <c r="O598" t="n">
-        <v>68684.0980253164</v>
+        <v>40586.0676712322</v>
       </c>
       <c r="P598" t="n">
         <v>2900</v>
       </c>
       <c r="Q598" t="n">
-        <v>127600</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="599">
@@ -26613,10 +26613,10 @@
         <v>30</v>
       </c>
       <c r="N610" t="n">
-        <v>9994.7101470588</v>
+        <v>9994.710151515201</v>
       </c>
       <c r="O610" t="n">
-        <v>299841.304411764</v>
+        <v>299841.304545456</v>
       </c>
       <c r="P610" t="n">
         <v>20800</v>
@@ -28718,7 +28718,7 @@
         </is>
       </c>
       <c r="J658" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K658" t="n">
         <v>0</v>
@@ -28727,19 +28727,19 @@
         <v>0</v>
       </c>
       <c r="M658" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="N658" t="n">
-        <v>1664.352739521</v>
+        <v>1664.3525567322</v>
       </c>
       <c r="O658" t="n">
-        <v>933701.8868712811</v>
+        <v>932037.4317700319</v>
       </c>
       <c r="P658" t="n">
         <v>2900</v>
       </c>
       <c r="Q658" t="n">
-        <v>1626900</v>
+        <v>1624000</v>
       </c>
     </row>
     <row r="659">
@@ -29380,10 +29380,10 @@
         <v>1360</v>
       </c>
       <c r="N672" t="n">
-        <v>1778.4726526892</v>
+        <v>1778.4726559172</v>
       </c>
       <c r="O672" t="n">
-        <v>2418722.807657312</v>
+        <v>2418722.812047392</v>
       </c>
       <c r="P672" t="n">
         <v>4900</v>
@@ -31214,7 +31214,7 @@
         </is>
       </c>
       <c r="J712" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K712" t="n">
         <v>0</v>
@@ -31223,19 +31223,19 @@
         <v>0</v>
       </c>
       <c r="M712" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N712" t="n">
         <v>55898</v>
       </c>
       <c r="O712" t="n">
-        <v>1117960</v>
+        <v>1062062</v>
       </c>
       <c r="P712" t="n">
         <v>89900</v>
       </c>
       <c r="Q712" t="n">
-        <v>1798000</v>
+        <v>1708100</v>
       </c>
     </row>
     <row r="713">
@@ -31444,7 +31444,7 @@
         </is>
       </c>
       <c r="J717" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K717" t="n">
         <v>0</v>
@@ -31453,19 +31453,19 @@
         <v>0</v>
       </c>
       <c r="M717" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N717" t="n">
         <v>3424</v>
       </c>
       <c r="O717" t="n">
-        <v>547840</v>
+        <v>544416</v>
       </c>
       <c r="P717" t="n">
         <v>5900</v>
       </c>
       <c r="Q717" t="n">
-        <v>944000</v>
+        <v>938100</v>
       </c>
     </row>
     <row r="718">
@@ -32868,7 +32868,7 @@
         </is>
       </c>
       <c r="J748" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K748" t="n">
         <v>0</v>
@@ -32877,19 +32877,19 @@
         <v>0</v>
       </c>
       <c r="M748" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N748" t="n">
         <v>13922</v>
       </c>
       <c r="O748" t="n">
-        <v>348050</v>
+        <v>320206</v>
       </c>
       <c r="P748" t="n">
         <v>22900</v>
       </c>
       <c r="Q748" t="n">
-        <v>572500</v>
+        <v>526700</v>
       </c>
     </row>
     <row r="749">
@@ -33018,10 +33018,10 @@
         <v>16</v>
       </c>
       <c r="N751" t="n">
-        <v>4907.8221972318</v>
+        <v>4907.8222048611</v>
       </c>
       <c r="O751" t="n">
-        <v>78525.1551557088</v>
+        <v>78525.15527777759</v>
       </c>
       <c r="P751" t="n">
         <v>8200</v>
@@ -33282,7 +33282,7 @@
         </is>
       </c>
       <c r="J757" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K757" t="n">
         <v>0</v>
@@ -33291,19 +33291,19 @@
         <v>0</v>
       </c>
       <c r="M757" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N757" t="n">
-        <v>3903.7369302326</v>
+        <v>3903.736969697</v>
       </c>
       <c r="O757" t="n">
-        <v>495774.5901395402</v>
+        <v>484063.384242428</v>
       </c>
       <c r="P757" t="n">
         <v>7500</v>
       </c>
       <c r="Q757" t="n">
-        <v>952500</v>
+        <v>930000</v>
       </c>
     </row>
     <row r="758">
@@ -33783,7 +33783,7 @@
         </is>
       </c>
       <c r="J768" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K768" t="n">
         <v>0</v>
@@ -33792,19 +33792,19 @@
         <v>0</v>
       </c>
       <c r="M768" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N768" t="n">
         <v>2629</v>
       </c>
       <c r="O768" t="n">
-        <v>239239</v>
+        <v>236610</v>
       </c>
       <c r="P768" t="n">
         <v>4500</v>
       </c>
       <c r="Q768" t="n">
-        <v>409500</v>
+        <v>405000</v>
       </c>
     </row>
     <row r="769">
@@ -33829,7 +33829,7 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K769" t="n">
         <v>0</v>
@@ -33838,19 +33838,19 @@
         <v>0</v>
       </c>
       <c r="M769" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N769" t="n">
-        <v>5869.1726051282</v>
+        <v>5869.1725975359</v>
       </c>
       <c r="O769" t="n">
-        <v>2828941.195671793</v>
+        <v>2823072.019414768</v>
       </c>
       <c r="P769" t="n">
         <v>9500</v>
       </c>
       <c r="Q769" t="n">
-        <v>4579000</v>
+        <v>4569500</v>
       </c>
     </row>
     <row r="770">
@@ -33921,7 +33921,7 @@
         </is>
       </c>
       <c r="J771" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K771" t="n">
         <v>0</v>
@@ -33930,19 +33930,19 @@
         <v>0</v>
       </c>
       <c r="M771" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N771" t="n">
         <v>4984</v>
       </c>
       <c r="O771" t="n">
-        <v>154504</v>
+        <v>144536</v>
       </c>
       <c r="P771" t="n">
         <v>7900</v>
       </c>
       <c r="Q771" t="n">
-        <v>244900</v>
+        <v>229100</v>
       </c>
     </row>
     <row r="772">
@@ -34013,7 +34013,7 @@
         </is>
       </c>
       <c r="J773" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K773" t="n">
         <v>0</v>
@@ -34022,19 +34022,19 @@
         <v>0</v>
       </c>
       <c r="M773" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N773" t="n">
         <v>6268</v>
       </c>
       <c r="O773" t="n">
-        <v>369812</v>
+        <v>363544</v>
       </c>
       <c r="P773" t="n">
         <v>10900</v>
       </c>
       <c r="Q773" t="n">
-        <v>643100</v>
+        <v>632200</v>
       </c>
     </row>
     <row r="774">
@@ -34381,7 +34381,7 @@
         </is>
       </c>
       <c r="J781" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K781" t="n">
         <v>0</v>
@@ -34390,19 +34390,19 @@
         <v>0</v>
       </c>
       <c r="M781" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N781" t="n">
         <v>13565</v>
       </c>
       <c r="O781" t="n">
-        <v>1342935</v>
+        <v>1329370</v>
       </c>
       <c r="P781" t="n">
         <v>22500</v>
       </c>
       <c r="Q781" t="n">
-        <v>2227500</v>
+        <v>2205000</v>
       </c>
     </row>
     <row r="782">
@@ -34427,7 +34427,7 @@
         </is>
       </c>
       <c r="J782" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K782" t="n">
         <v>0</v>
@@ -34436,19 +34436,19 @@
         <v>0</v>
       </c>
       <c r="M782" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N782" t="n">
         <v>7635</v>
       </c>
       <c r="O782" t="n">
-        <v>534450</v>
+        <v>526815</v>
       </c>
       <c r="P782" t="n">
         <v>13900</v>
       </c>
       <c r="Q782" t="n">
-        <v>973000</v>
+        <v>959100</v>
       </c>
     </row>
     <row r="783">
@@ -34844,7 +34844,7 @@
         </is>
       </c>
       <c r="J791" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K791" t="n">
         <v>0</v>
@@ -34853,19 +34853,19 @@
         <v>0</v>
       </c>
       <c r="M791" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N791" t="n">
         <v>11348</v>
       </c>
       <c r="O791" t="n">
-        <v>283700</v>
+        <v>22696</v>
       </c>
       <c r="P791" t="n">
         <v>19900</v>
       </c>
       <c r="Q791" t="n">
-        <v>497500</v>
+        <v>39800</v>
       </c>
     </row>
     <row r="792">
@@ -34890,13 +34890,13 @@
         </is>
       </c>
       <c r="J792" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K792" t="n">
         <v>0</v>
       </c>
       <c r="L792" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M792" t="n">
         <v>170</v>
@@ -35348,7 +35348,7 @@
         </is>
       </c>
       <c r="J802" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="K802" t="n">
         <v>0</v>
@@ -35357,19 +35357,19 @@
         <v>0</v>
       </c>
       <c r="M802" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="N802" t="n">
         <v>10755</v>
       </c>
       <c r="O802" t="n">
-        <v>699075</v>
+        <v>1021725</v>
       </c>
       <c r="P802" t="n">
         <v>17900</v>
       </c>
       <c r="Q802" t="n">
-        <v>1163500</v>
+        <v>1700500</v>
       </c>
     </row>
     <row r="803">
@@ -35900,7 +35900,7 @@
         </is>
       </c>
       <c r="J814" t="n">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="K814" t="n">
         <v>0</v>
@@ -35909,19 +35909,19 @@
         <v>0</v>
       </c>
       <c r="M814" t="n">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="N814" t="n">
         <v>8700</v>
       </c>
       <c r="O814" t="n">
-        <v>713400</v>
+        <v>269700</v>
       </c>
       <c r="P814" t="n">
         <v>14900</v>
       </c>
       <c r="Q814" t="n">
-        <v>1221800</v>
+        <v>461900</v>
       </c>
     </row>
     <row r="815">
@@ -36605,10 +36605,10 @@
         <v>562</v>
       </c>
       <c r="N829" t="n">
-        <v>1516.0387905286</v>
+        <v>1516.0387891009</v>
       </c>
       <c r="O829" t="n">
-        <v>852013.8002770732</v>
+        <v>852013.7994747058</v>
       </c>
       <c r="P829" t="n">
         <v>2300</v>
@@ -36741,10 +36741,10 @@
         <v>269</v>
       </c>
       <c r="N832" t="n">
-        <v>2458.5129162428</v>
+        <v>2458.5128483396</v>
       </c>
       <c r="O832" t="n">
-        <v>661339.9744693133</v>
+        <v>661339.9562033524</v>
       </c>
       <c r="P832" t="n">
         <v>3500</v>
@@ -36775,7 +36775,7 @@
         </is>
       </c>
       <c r="J833" t="n">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="K833" t="n">
         <v>0</v>
@@ -36784,19 +36784,19 @@
         <v>0</v>
       </c>
       <c r="M833" t="n">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="N833" t="n">
-        <v>1907.3929220779</v>
+        <v>1907.392860262</v>
       </c>
       <c r="O833" t="n">
-        <v>698105.8094805115</v>
+        <v>686661.4296943201</v>
       </c>
       <c r="P833" t="n">
         <v>2500</v>
       </c>
       <c r="Q833" t="n">
-        <v>915000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="834">
@@ -36821,7 +36821,7 @@
         </is>
       </c>
       <c r="J834" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K834" t="n">
         <v>0</v>
@@ -36830,19 +36830,19 @@
         <v>0</v>
       </c>
       <c r="M834" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N834" t="n">
-        <v>1771.0902822581</v>
+        <v>1771.0902626263</v>
       </c>
       <c r="O834" t="n">
-        <v>327651.7022177485</v>
+        <v>322338.4277979866</v>
       </c>
       <c r="P834" t="n">
         <v>2500</v>
       </c>
       <c r="Q834" t="n">
-        <v>462500</v>
+        <v>455000</v>
       </c>
     </row>
     <row r="835">
@@ -36879,10 +36879,10 @@
         <v>380</v>
       </c>
       <c r="N835" t="n">
-        <v>2079.383962775</v>
+        <v>2079.3839381583</v>
       </c>
       <c r="O835" t="n">
-        <v>790165.9058544999</v>
+        <v>790165.896500154</v>
       </c>
       <c r="P835" t="n">
         <v>2900</v>
@@ -36913,7 +36913,7 @@
         </is>
       </c>
       <c r="J836" t="n">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="K836" t="n">
         <v>0</v>
@@ -36922,19 +36922,19 @@
         <v>0</v>
       </c>
       <c r="M836" t="n">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="N836" t="n">
-        <v>1803.015867082</v>
+        <v>1803.0158874609</v>
       </c>
       <c r="O836" t="n">
-        <v>1016900.949034248</v>
+        <v>1007885.881090643</v>
       </c>
       <c r="P836" t="n">
         <v>2500</v>
       </c>
       <c r="Q836" t="n">
-        <v>1410000</v>
+        <v>1397500</v>
       </c>
     </row>
     <row r="837">
@@ -36971,10 +36971,10 @@
         <v>145</v>
       </c>
       <c r="N837" t="n">
-        <v>3306.5946107784</v>
+        <v>3306.5945945946</v>
       </c>
       <c r="O837" t="n">
-        <v>479456.218562868</v>
+        <v>479456.216216217</v>
       </c>
       <c r="P837" t="n">
         <v>4900</v>
@@ -37017,10 +37017,10 @@
         <v>410</v>
       </c>
       <c r="N838" t="n">
-        <v>2122.163732778</v>
+        <v>2122.1637267479</v>
       </c>
       <c r="O838" t="n">
-        <v>870087.1304389799</v>
+        <v>870087.127966639</v>
       </c>
       <c r="P838" t="n">
         <v>2900</v>
@@ -37063,10 +37063,10 @@
         <v>588</v>
       </c>
       <c r="N839" t="n">
-        <v>2108.7926981818</v>
+        <v>2108.7933180778</v>
       </c>
       <c r="O839" t="n">
-        <v>1239970.106530898</v>
+        <v>1239970.471029746</v>
       </c>
       <c r="P839" t="n">
         <v>2900</v>
@@ -37109,10 +37109,10 @@
         <v>1097</v>
       </c>
       <c r="N840" t="n">
-        <v>2056.0828704663</v>
+        <v>2056.0827781666</v>
       </c>
       <c r="O840" t="n">
-        <v>2255522.908901531</v>
+        <v>2255522.80764876</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
@@ -37143,7 +37143,7 @@
         </is>
       </c>
       <c r="J841" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K841" t="n">
         <v>0</v>
@@ -37152,19 +37152,19 @@
         <v>0</v>
       </c>
       <c r="M841" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N841" t="n">
-        <v>3224.5689232303</v>
+        <v>3224.5689410589</v>
       </c>
       <c r="O841" t="n">
-        <v>654587.4914157508</v>
+        <v>644913.7882117799</v>
       </c>
       <c r="P841" t="n">
         <v>4500</v>
       </c>
       <c r="Q841" t="n">
-        <v>913500</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="842">
@@ -37189,7 +37189,7 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
@@ -37198,19 +37198,19 @@
         <v>0</v>
       </c>
       <c r="M842" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="N842" t="n">
-        <v>1655.9305693829</v>
+        <v>1655.9305111492</v>
       </c>
       <c r="O842" t="n">
-        <v>1154183.606859881</v>
+        <v>1150871.705248694</v>
       </c>
       <c r="P842" t="n">
         <v>2500</v>
       </c>
       <c r="Q842" t="n">
-        <v>1742500</v>
+        <v>1737500</v>
       </c>
     </row>
     <row r="843">
@@ -37284,7 +37284,7 @@
         </is>
       </c>
       <c r="J844" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K844" t="n">
         <v>0</v>
@@ -37293,19 +37293,19 @@
         <v>0</v>
       </c>
       <c r="M844" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N844" t="n">
         <v>1019</v>
       </c>
       <c r="O844" t="n">
-        <v>156926</v>
+        <v>155907</v>
       </c>
       <c r="P844" t="n">
         <v>1900</v>
       </c>
       <c r="Q844" t="n">
-        <v>292600</v>
+        <v>290700</v>
       </c>
     </row>
     <row r="845">
@@ -37422,7 +37422,7 @@
         </is>
       </c>
       <c r="J847" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K847" t="n">
         <v>0</v>
@@ -37431,19 +37431,19 @@
         <v>0</v>
       </c>
       <c r="M847" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N847" t="n">
         <v>1662</v>
       </c>
       <c r="O847" t="n">
-        <v>920748</v>
+        <v>919086</v>
       </c>
       <c r="P847" t="n">
         <v>2900</v>
       </c>
       <c r="Q847" t="n">
-        <v>1606600</v>
+        <v>1603700</v>
       </c>
     </row>
     <row r="848">
@@ -37468,7 +37468,7 @@
         </is>
       </c>
       <c r="J848" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K848" t="n">
         <v>0</v>
@@ -37477,19 +37477,19 @@
         <v>0</v>
       </c>
       <c r="M848" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N848" t="n">
         <v>2003</v>
       </c>
       <c r="O848" t="n">
-        <v>330495</v>
+        <v>328492</v>
       </c>
       <c r="P848" t="n">
         <v>3900</v>
       </c>
       <c r="Q848" t="n">
-        <v>643500</v>
+        <v>639600</v>
       </c>
     </row>
     <row r="849">
@@ -37616,10 +37616,10 @@
         <v>2</v>
       </c>
       <c r="N851" t="n">
-        <v>1906.1809638554</v>
+        <v>1906.1809090909</v>
       </c>
       <c r="O851" t="n">
-        <v>3812.3619277108</v>
+        <v>3812.3618181818</v>
       </c>
       <c r="P851" t="n">
         <v>2900</v>
@@ -37708,10 +37708,10 @@
         <v>61</v>
       </c>
       <c r="N853" t="n">
-        <v>2546.9829528536</v>
+        <v>2546.9828463476</v>
       </c>
       <c r="O853" t="n">
-        <v>155365.9601240696</v>
+        <v>155365.9536272036</v>
       </c>
       <c r="P853" t="n">
         <v>3900</v>
@@ -37742,7 +37742,7 @@
         </is>
       </c>
       <c r="J854" t="n">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="K854" t="n">
         <v>0</v>
@@ -37751,19 +37751,19 @@
         <v>0</v>
       </c>
       <c r="M854" t="n">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="N854" t="n">
-        <v>1259.2746531459</v>
+        <v>1259.2746638947</v>
       </c>
       <c r="O854" t="n">
-        <v>306003.7407144537</v>
+        <v>293410.9966874651</v>
       </c>
       <c r="P854" t="n">
         <v>1900</v>
       </c>
       <c r="Q854" t="n">
-        <v>461700</v>
+        <v>442700</v>
       </c>
     </row>
     <row r="855">
@@ -37834,7 +37834,7 @@
         </is>
       </c>
       <c r="J856" t="n">
-        <v>386</v>
+        <v>262</v>
       </c>
       <c r="K856" t="n">
         <v>0</v>
@@ -37843,19 +37843,19 @@
         <v>0</v>
       </c>
       <c r="M856" t="n">
-        <v>386</v>
+        <v>262</v>
       </c>
       <c r="N856" t="n">
         <v>1801</v>
       </c>
       <c r="O856" t="n">
-        <v>695186</v>
+        <v>471862</v>
       </c>
       <c r="P856" t="n">
         <v>2900</v>
       </c>
       <c r="Q856" t="n">
-        <v>1119400</v>
+        <v>759800</v>
       </c>
     </row>
     <row r="857">
@@ -39485,7 +39485,7 @@
         </is>
       </c>
       <c r="J892" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="K892" t="n">
         <v>0</v>
@@ -39494,19 +39494,19 @@
         <v>0</v>
       </c>
       <c r="M892" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="N892" t="n">
         <v>1828.64</v>
       </c>
       <c r="O892" t="n">
-        <v>1181301.44</v>
+        <v>1179472.8</v>
       </c>
       <c r="P892" t="n">
         <v>2000</v>
       </c>
       <c r="Q892" t="n">
-        <v>1292000</v>
+        <v>1290000</v>
       </c>
     </row>
     <row r="893">
@@ -39534,7 +39534,7 @@
         </is>
       </c>
       <c r="J893" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K893" t="n">
         <v>0</v>
@@ -39543,19 +39543,19 @@
         <v>0</v>
       </c>
       <c r="M893" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N893" t="n">
-        <v>2270.3212658228</v>
+        <v>2270.3212987013</v>
       </c>
       <c r="O893" t="n">
-        <v>31784.4977215192</v>
+        <v>27243.8555844156</v>
       </c>
       <c r="P893" t="n">
         <v>3900</v>
       </c>
       <c r="Q893" t="n">
-        <v>54600</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="894">
@@ -39720,7 +39720,7 @@
         </is>
       </c>
       <c r="J897" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K897" t="n">
         <v>0</v>
@@ -39729,19 +39729,19 @@
         <v>0</v>
       </c>
       <c r="M897" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N897" t="n">
         <v>1621.2</v>
       </c>
       <c r="O897" t="n">
-        <v>48636</v>
+        <v>47014.8</v>
       </c>
       <c r="P897" t="n">
         <v>2500</v>
       </c>
       <c r="Q897" t="n">
-        <v>75000</v>
+        <v>72500</v>
       </c>
     </row>
     <row r="898">
@@ -39769,7 +39769,7 @@
         </is>
       </c>
       <c r="J898" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K898" t="n">
         <v>0</v>
@@ -39778,19 +39778,19 @@
         <v>0</v>
       </c>
       <c r="M898" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N898" t="n">
         <v>8702.219999999999</v>
       </c>
       <c r="O898" t="n">
-        <v>687475.38</v>
+        <v>678773.1599999999</v>
       </c>
       <c r="P898" t="n">
         <v>8900</v>
       </c>
       <c r="Q898" t="n">
-        <v>703100</v>
+        <v>694200</v>
       </c>
     </row>
     <row r="899">
@@ -39983,7 +39983,7 @@
         </is>
       </c>
       <c r="J903" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K903" t="n">
         <v>0</v>
@@ -39992,19 +39992,19 @@
         <v>0</v>
       </c>
       <c r="M903" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N903" t="n">
-        <v>2590.4171296296</v>
+        <v>2590.4171028037</v>
       </c>
       <c r="O903" t="n">
-        <v>62170.0111111104</v>
+        <v>59579.5933644851</v>
       </c>
       <c r="P903" t="n">
         <v>2800</v>
       </c>
       <c r="Q903" t="n">
-        <v>67200</v>
+        <v>64400</v>
       </c>
     </row>
     <row r="904">
@@ -40073,7 +40073,7 @@
         </is>
       </c>
       <c r="J905" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K905" t="n">
         <v>0</v>
@@ -40082,19 +40082,19 @@
         <v>0</v>
       </c>
       <c r="M905" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N905" t="n">
         <v>1684.79</v>
       </c>
       <c r="O905" t="n">
-        <v>144891.94</v>
+        <v>141522.36</v>
       </c>
       <c r="P905" t="n">
         <v>2900</v>
       </c>
       <c r="Q905" t="n">
-        <v>249400</v>
+        <v>243600</v>
       </c>
     </row>
     <row r="906">
@@ -40823,7 +40823,7 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>2488</v>
+        <v>2428</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
@@ -40832,19 +40832,19 @@
         <v>0</v>
       </c>
       <c r="M922" t="n">
-        <v>2488</v>
+        <v>2428</v>
       </c>
       <c r="N922" t="n">
-        <v>517.29097263266</v>
+        <v>517.29128286432</v>
       </c>
       <c r="O922" t="n">
-        <v>1287019.939910058</v>
+        <v>1255983.234794569</v>
       </c>
       <c r="P922" t="n">
         <v>900</v>
       </c>
       <c r="Q922" t="n">
-        <v>2239200</v>
+        <v>2185200</v>
       </c>
     </row>
     <row r="923">
@@ -41049,7 +41049,7 @@
         </is>
       </c>
       <c r="J927" t="n">
-        <v>430</v>
+        <v>660</v>
       </c>
       <c r="K927" t="n">
         <v>0</v>
@@ -41058,19 +41058,19 @@
         <v>0</v>
       </c>
       <c r="M927" t="n">
-        <v>430</v>
+        <v>660</v>
       </c>
       <c r="N927" t="n">
-        <v>3110.8403177212</v>
+        <v>3110.8402590245</v>
       </c>
       <c r="O927" t="n">
-        <v>1337661.336620116</v>
+        <v>2053154.57095617</v>
       </c>
       <c r="P927" t="n">
         <v>4500</v>
       </c>
       <c r="Q927" t="n">
-        <v>1935000</v>
+        <v>2970000</v>
       </c>
     </row>
     <row r="928">
@@ -41271,7 +41271,7 @@
         </is>
       </c>
       <c r="J932" t="n">
-        <v>871</v>
+        <v>1599</v>
       </c>
       <c r="K932" t="n">
         <v>0</v>
@@ -41280,19 +41280,19 @@
         <v>0</v>
       </c>
       <c r="M932" t="n">
-        <v>871</v>
+        <v>1599</v>
       </c>
       <c r="N932" t="n">
-        <v>703.79509062003</v>
+        <v>703.79502188713</v>
       </c>
       <c r="O932" t="n">
-        <v>613005.5239300461</v>
+        <v>1125368.239997521</v>
       </c>
       <c r="P932" t="n">
         <v>900</v>
       </c>
       <c r="Q932" t="n">
-        <v>783900</v>
+        <v>1439100</v>
       </c>
     </row>
     <row r="933">
@@ -41364,7 +41364,7 @@
         </is>
       </c>
       <c r="J934" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K934" t="n">
         <v>0</v>
@@ -41373,19 +41373,19 @@
         <v>0</v>
       </c>
       <c r="M934" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N934" t="n">
-        <v>3182.2511173184</v>
+        <v>3182.251119403</v>
       </c>
       <c r="O934" t="n">
-        <v>89103.0312849152</v>
+        <v>85920.780223881</v>
       </c>
       <c r="P934" t="n">
         <v>6900</v>
       </c>
       <c r="Q934" t="n">
-        <v>193200</v>
+        <v>186300</v>
       </c>
     </row>
     <row r="935">
@@ -42068,7 +42068,7 @@
         </is>
       </c>
       <c r="J950" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="K950" t="n">
         <v>0</v>
@@ -42077,19 +42077,19 @@
         <v>0</v>
       </c>
       <c r="M950" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N950" t="n">
-        <v>2077.4946460177</v>
+        <v>2077.4946875</v>
       </c>
       <c r="O950" t="n">
-        <v>529761.1347345135</v>
+        <v>517296.1771875</v>
       </c>
       <c r="P950" t="n">
         <v>2900</v>
       </c>
       <c r="Q950" t="n">
-        <v>739500</v>
+        <v>722100</v>
       </c>
     </row>
     <row r="951">
@@ -42112,7 +42112,7 @@
         </is>
       </c>
       <c r="J951" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K951" t="n">
         <v>0</v>
@@ -42121,19 +42121,19 @@
         <v>0</v>
       </c>
       <c r="M951" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N951" t="n">
-        <v>3629.716029724</v>
+        <v>3629.7160212766</v>
       </c>
       <c r="O951" t="n">
-        <v>65334.888535032</v>
+        <v>61705.1723617022</v>
       </c>
       <c r="P951" t="n">
         <v>4900</v>
       </c>
       <c r="Q951" t="n">
-        <v>88200</v>
+        <v>83300</v>
       </c>
     </row>
     <row r="952">
@@ -42279,7 +42279,7 @@
         </is>
       </c>
       <c r="J955" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K955" t="n">
         <v>0</v>
@@ -42288,19 +42288,19 @@
         <v>0</v>
       </c>
       <c r="M955" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N955" t="n">
-        <v>2575.195625</v>
+        <v>2575.1953333333</v>
       </c>
       <c r="O955" t="n">
-        <v>18026.369375</v>
+        <v>15451.1719999998</v>
       </c>
       <c r="P955" t="n">
         <v>2900</v>
       </c>
       <c r="Q955" t="n">
-        <v>20300</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="956">
@@ -42328,7 +42328,7 @@
         </is>
       </c>
       <c r="J956" t="n">
-        <v>15</v>
+        <v>815</v>
       </c>
       <c r="K956" t="n">
         <v>0</v>
@@ -42337,19 +42337,19 @@
         <v>0</v>
       </c>
       <c r="M956" t="n">
-        <v>15</v>
+        <v>815</v>
       </c>
       <c r="N956" t="n">
-        <v>1595.5116012774</v>
+        <v>1595.5115507777</v>
       </c>
       <c r="O956" t="n">
-        <v>23932.674019161</v>
+        <v>1300341.913883826</v>
       </c>
       <c r="P956" t="n">
         <v>2500</v>
       </c>
       <c r="Q956" t="n">
-        <v>37500</v>
+        <v>2037500</v>
       </c>
     </row>
     <row r="957">
@@ -43646,7 +43646,7 @@
         </is>
       </c>
       <c r="J984" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K984" t="n">
         <v>0</v>
@@ -43655,19 +43655,19 @@
         <v>0</v>
       </c>
       <c r="M984" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N984" t="n">
-        <v>2505.760516129</v>
+        <v>2505.7605194805</v>
       </c>
       <c r="O984" t="n">
-        <v>97724.66012903099</v>
+        <v>95218.899740259</v>
       </c>
       <c r="P984" t="n">
         <v>3000</v>
       </c>
       <c r="Q984" t="n">
-        <v>117000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="985">
@@ -44172,10 +44172,10 @@
         <v>1</v>
       </c>
       <c r="N995" t="n">
-        <v>7314.9902941176</v>
+        <v>7314.9903030303</v>
       </c>
       <c r="O995" t="n">
-        <v>7314.9902941176</v>
+        <v>7314.9903030303</v>
       </c>
       <c r="P995" t="n">
         <v>17500</v>
@@ -45055,10 +45055,10 @@
         <v>14</v>
       </c>
       <c r="N1014" t="n">
-        <v>44113.603841808</v>
+        <v>44113.603953488</v>
       </c>
       <c r="O1014" t="n">
-        <v>617590.453785312</v>
+        <v>617590.455348832</v>
       </c>
       <c r="P1014" t="n">
         <v>71900</v>
@@ -45672,7 +45672,7 @@
         </is>
       </c>
       <c r="J1027" t="n">
-        <v>2400</v>
+        <v>2374</v>
       </c>
       <c r="K1027" t="n">
         <v>0</v>
@@ -45681,7 +45681,7 @@
         <v>0</v>
       </c>
       <c r="M1027" t="n">
-        <v>2400</v>
+        <v>2374</v>
       </c>
       <c r="N1027" t="n">
         <v>0</v>
@@ -45693,7 +45693,7 @@
         <v>6500</v>
       </c>
       <c r="Q1027" t="n">
-        <v>15600000</v>
+        <v>15431000</v>
       </c>
     </row>
     <row r="1028">
@@ -45921,7 +45921,7 @@
         </is>
       </c>
       <c r="J1033" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K1033" t="n">
         <v>0</v>
@@ -45930,19 +45930,19 @@
         <v>0</v>
       </c>
       <c r="M1033" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N1033" t="n">
-        <v>2703.2000014448</v>
+        <v>2703.2000014449</v>
       </c>
       <c r="O1033" t="n">
-        <v>786631.2004204368</v>
+        <v>781224.8004175761</v>
       </c>
       <c r="P1033" t="n">
         <v>4500</v>
       </c>
       <c r="Q1033" t="n">
-        <v>1309500</v>
+        <v>1300500</v>
       </c>
     </row>
     <row r="1034">
@@ -46346,7 +46346,7 @@
         </is>
       </c>
       <c r="J1043" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K1043" t="n">
         <v>0</v>
@@ -46355,19 +46355,19 @@
         <v>0</v>
       </c>
       <c r="M1043" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N1043" t="n">
         <v>3461.54</v>
       </c>
       <c r="O1043" t="n">
-        <v>169615.46</v>
+        <v>166153.92</v>
       </c>
       <c r="P1043" t="n">
         <v>4500</v>
       </c>
       <c r="Q1043" t="n">
-        <v>220500</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="1044">
@@ -46817,7 +46817,7 @@
         </is>
       </c>
       <c r="J1054" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K1054" t="n">
         <v>0</v>
@@ -46826,19 +46826,19 @@
         <v>0</v>
       </c>
       <c r="M1054" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N1054" t="n">
-        <v>2489.1752678107</v>
+        <v>2489.1752653486</v>
       </c>
       <c r="O1054" t="n">
-        <v>114502.0623192922</v>
+        <v>112012.886940687</v>
       </c>
       <c r="P1054" t="n">
         <v>3000</v>
       </c>
       <c r="Q1054" t="n">
-        <v>138000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="1055">
@@ -47251,7 +47251,7 @@
         </is>
       </c>
       <c r="J1064" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K1064" t="n">
         <v>0</v>
@@ -47260,19 +47260,19 @@
         <v>0</v>
       </c>
       <c r="M1064" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N1064" t="n">
         <v>2076.92</v>
       </c>
       <c r="O1064" t="n">
-        <v>22846.12</v>
+        <v>20769.2</v>
       </c>
       <c r="P1064" t="n">
         <v>2700</v>
       </c>
       <c r="Q1064" t="n">
-        <v>29700</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="1065">
@@ -47336,7 +47336,7 @@
         </is>
       </c>
       <c r="J1066" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="K1066" t="n">
         <v>0</v>
@@ -47345,19 +47345,19 @@
         <v>0</v>
       </c>
       <c r="M1066" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="N1066" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1066" t="n">
-        <v>102361.59</v>
+        <v>87066.17999999999</v>
       </c>
       <c r="P1066" t="n">
         <v>1900</v>
       </c>
       <c r="Q1066" t="n">
-        <v>165300</v>
+        <v>140600</v>
       </c>
     </row>
     <row r="1067">
@@ -47380,13 +47380,13 @@
         </is>
       </c>
       <c r="J1067" t="n">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="K1067" t="n">
         <v>0</v>
       </c>
       <c r="L1067" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M1067" t="n">
         <v>379</v>
@@ -47506,7 +47506,7 @@
         </is>
       </c>
       <c r="J1070" t="n">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="K1070" t="n">
         <v>0</v>
@@ -47515,19 +47515,19 @@
         <v>0</v>
       </c>
       <c r="M1070" t="n">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="N1070" t="n">
-        <v>1794.287968053</v>
+        <v>1794.287966297</v>
       </c>
       <c r="O1070" t="n">
-        <v>310411.818473169</v>
+        <v>299646.090371599</v>
       </c>
       <c r="P1070" t="n">
         <v>1600</v>
       </c>
       <c r="Q1070" t="n">
-        <v>276800</v>
+        <v>267200</v>
       </c>
     </row>
     <row r="1071">
@@ -47638,7 +47638,7 @@
         </is>
       </c>
       <c r="J1073" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="K1073" t="n">
         <v>0</v>
@@ -47647,19 +47647,19 @@
         <v>0</v>
       </c>
       <c r="M1073" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="N1073" t="n">
         <v>1727.31</v>
       </c>
       <c r="O1073" t="n">
-        <v>272914.98</v>
+        <v>262551.12</v>
       </c>
       <c r="P1073" t="n">
         <v>2850</v>
       </c>
       <c r="Q1073" t="n">
-        <v>450300</v>
+        <v>433200</v>
       </c>
     </row>
     <row r="1074">
@@ -48575,7 +48575,7 @@
         </is>
       </c>
       <c r="J1095" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K1095" t="n">
         <v>0</v>
@@ -48584,19 +48584,19 @@
         <v>0</v>
       </c>
       <c r="M1095" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N1095" t="n">
         <v>923.08</v>
       </c>
       <c r="O1095" t="n">
-        <v>177231.36</v>
+        <v>176308.28</v>
       </c>
       <c r="P1095" t="n">
         <v>1200</v>
       </c>
       <c r="Q1095" t="n">
-        <v>230400</v>
+        <v>229200</v>
       </c>
     </row>
     <row r="1096">
@@ -48759,7 +48759,7 @@
         </is>
       </c>
       <c r="J1099" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K1099" t="n">
         <v>0</v>
@@ -48768,19 +48768,19 @@
         <v>0</v>
       </c>
       <c r="M1099" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N1099" t="n">
-        <v>1757.3205627706</v>
+        <v>1757.3205652174</v>
       </c>
       <c r="O1099" t="n">
-        <v>72050.14307359461</v>
+        <v>68535.5020434786</v>
       </c>
       <c r="P1099" t="n">
         <v>2000</v>
       </c>
       <c r="Q1099" t="n">
-        <v>82000</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="1100">
@@ -49480,7 +49480,7 @@
         </is>
       </c>
       <c r="J1115" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K1115" t="n">
         <v>0</v>
@@ -49489,19 +49489,19 @@
         <v>0</v>
       </c>
       <c r="M1115" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N1115" t="n">
         <v>6336</v>
       </c>
       <c r="O1115" t="n">
-        <v>361152</v>
+        <v>316800</v>
       </c>
       <c r="P1115" t="n">
         <v>7500</v>
       </c>
       <c r="Q1115" t="n">
-        <v>427500</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="1116">
@@ -49664,7 +49664,7 @@
         </is>
       </c>
       <c r="J1119" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K1119" t="n">
         <v>0</v>
@@ -49673,19 +49673,19 @@
         <v>0</v>
       </c>
       <c r="M1119" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N1119" t="n">
         <v>4400</v>
       </c>
       <c r="O1119" t="n">
-        <v>400400</v>
+        <v>382800</v>
       </c>
       <c r="P1119" t="n">
         <v>5900</v>
       </c>
       <c r="Q1119" t="n">
-        <v>536900</v>
+        <v>513300</v>
       </c>
     </row>
     <row r="1120">
@@ -49848,7 +49848,7 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>453</v>
+        <v>396</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
@@ -49857,19 +49857,19 @@
         <v>0</v>
       </c>
       <c r="M1123" t="n">
-        <v>453</v>
+        <v>396</v>
       </c>
       <c r="N1123" t="n">
         <v>9240</v>
       </c>
       <c r="O1123" t="n">
-        <v>4185720</v>
+        <v>3659040</v>
       </c>
       <c r="P1123" t="n">
         <v>11500</v>
       </c>
       <c r="Q1123" t="n">
-        <v>5209500</v>
+        <v>4554000</v>
       </c>
     </row>
     <row r="1124">
@@ -49894,7 +49894,7 @@
         </is>
       </c>
       <c r="J1124" t="n">
-        <v>486</v>
+        <v>425</v>
       </c>
       <c r="K1124" t="n">
         <v>0</v>
@@ -49903,19 +49903,19 @@
         <v>0</v>
       </c>
       <c r="M1124" t="n">
-        <v>486</v>
+        <v>425</v>
       </c>
       <c r="N1124" t="n">
         <v>2288</v>
       </c>
       <c r="O1124" t="n">
-        <v>1111968</v>
+        <v>972400</v>
       </c>
       <c r="P1124" t="n">
         <v>2900</v>
       </c>
       <c r="Q1124" t="n">
-        <v>1409400</v>
+        <v>1232500</v>
       </c>
     </row>
     <row r="1125">
@@ -49940,7 +49940,7 @@
         </is>
       </c>
       <c r="J1125" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K1125" t="n">
         <v>0</v>
@@ -49949,19 +49949,19 @@
         <v>0</v>
       </c>
       <c r="M1125" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="N1125" t="n">
         <v>4576</v>
       </c>
       <c r="O1125" t="n">
-        <v>608608</v>
+        <v>581152</v>
       </c>
       <c r="P1125" t="n">
         <v>5900</v>
       </c>
       <c r="Q1125" t="n">
-        <v>784700</v>
+        <v>749300</v>
       </c>
     </row>
     <row r="1126">
@@ -49986,7 +49986,7 @@
         </is>
       </c>
       <c r="J1126" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K1126" t="n">
         <v>0</v>
@@ -49995,19 +49995,19 @@
         <v>0</v>
       </c>
       <c r="M1126" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N1126" t="n">
         <v>5280</v>
       </c>
       <c r="O1126" t="n">
-        <v>1605120</v>
+        <v>1599840</v>
       </c>
       <c r="P1126" t="n">
         <v>6900</v>
       </c>
       <c r="Q1126" t="n">
-        <v>2097600</v>
+        <v>2090700</v>
       </c>
     </row>
     <row r="1127">
@@ -50032,7 +50032,7 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
@@ -50041,19 +50041,19 @@
         <v>0</v>
       </c>
       <c r="M1127" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N1127" t="n">
         <v>1800</v>
       </c>
       <c r="O1127" t="n">
-        <v>131400</v>
+        <v>129600</v>
       </c>
       <c r="P1127" t="n">
         <v>2200</v>
       </c>
       <c r="Q1127" t="n">
-        <v>160600</v>
+        <v>158400</v>
       </c>
     </row>
     <row r="1128">
@@ -51504,7 +51504,7 @@
         </is>
       </c>
       <c r="J1159" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K1159" t="n">
         <v>0</v>
@@ -51513,19 +51513,19 @@
         <v>0</v>
       </c>
       <c r="M1159" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N1159" t="n">
-        <v>227.41613363363</v>
+        <v>227.41613824192</v>
       </c>
       <c r="O1159" t="n">
-        <v>18193.2906906904</v>
+        <v>17965.87492111168</v>
       </c>
       <c r="P1159" t="n">
         <v>1200</v>
       </c>
       <c r="Q1159" t="n">
-        <v>96000</v>
+        <v>94800</v>
       </c>
     </row>
     <row r="1160">
@@ -51903,7 +51903,7 @@
         </is>
       </c>
       <c r="J1168" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K1168" t="n">
         <v>0</v>
@@ -51912,19 +51912,19 @@
         <v>0</v>
       </c>
       <c r="M1168" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N1168" t="n">
         <v>2200</v>
       </c>
       <c r="O1168" t="n">
-        <v>26400</v>
+        <v>24200</v>
       </c>
       <c r="P1168" t="n">
         <v>2700</v>
       </c>
       <c r="Q1168" t="n">
-        <v>32400</v>
+        <v>29700</v>
       </c>
     </row>
     <row r="1169">
@@ -51949,7 +51949,7 @@
         </is>
       </c>
       <c r="J1169" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K1169" t="n">
         <v>0</v>
@@ -51958,19 +51958,19 @@
         <v>0</v>
       </c>
       <c r="M1169" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N1169" t="n">
         <v>2200</v>
       </c>
       <c r="O1169" t="n">
-        <v>41800</v>
+        <v>39600</v>
       </c>
       <c r="P1169" t="n">
         <v>2700</v>
       </c>
       <c r="Q1169" t="n">
-        <v>51300</v>
+        <v>48600</v>
       </c>
     </row>
     <row r="1170">
@@ -51995,7 +51995,7 @@
         </is>
       </c>
       <c r="J1170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K1170" t="n">
         <v>0</v>
@@ -52004,19 +52004,19 @@
         <v>0</v>
       </c>
       <c r="M1170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N1170" t="n">
         <v>2200</v>
       </c>
       <c r="O1170" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="P1170" t="n">
         <v>2700</v>
       </c>
       <c r="Q1170" t="n">
-        <v>27000</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="1171">
@@ -52041,7 +52041,7 @@
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
@@ -52050,19 +52050,19 @@
         <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1171" t="n">
         <v>2200</v>
       </c>
       <c r="O1171" t="n">
-        <v>6600</v>
+        <v>4400</v>
       </c>
       <c r="P1171" t="n">
         <v>2700</v>
       </c>
       <c r="Q1171" t="n">
-        <v>8100</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="1172">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -12680,10 +12680,10 @@
         <v>54</v>
       </c>
       <c r="N289" t="n">
-        <v>3230.0670575693</v>
+        <v>3230.0670386266</v>
       </c>
       <c r="O289" t="n">
-        <v>174423.6211087422</v>
+        <v>174423.6200858364</v>
       </c>
       <c r="P289" t="n">
         <v>6200</v>
@@ -13627,10 +13627,10 @@
         <v>33</v>
       </c>
       <c r="N310" t="n">
-        <v>4890.9300493218</v>
+        <v>4890.9300493827</v>
       </c>
       <c r="O310" t="n">
-        <v>161400.6916276194</v>
+        <v>161400.6916296291</v>
       </c>
       <c r="P310" t="n">
         <v>8200</v>
@@ -14908,10 +14908,10 @@
         <v>3</v>
       </c>
       <c r="N339" t="n">
-        <v>2090.85</v>
+        <v>2092.643951094</v>
       </c>
       <c r="O339" t="n">
-        <v>6272.549999999999</v>
+        <v>6277.931853282</v>
       </c>
       <c r="P339" t="n">
         <v>2900</v>
@@ -15526,10 +15526,10 @@
         <v>204</v>
       </c>
       <c r="N353" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O353" t="n">
-        <v>891931.0015206517</v>
+        <v>891931.0015437444</v>
       </c>
       <c r="P353" t="n">
         <v>7500</v>
@@ -15616,10 +15616,10 @@
         <v>2</v>
       </c>
       <c r="N355" t="n">
-        <v>1592.5662209302</v>
+        <v>1617.3578206079</v>
       </c>
       <c r="O355" t="n">
-        <v>3185.1324418604</v>
+        <v>3234.7156412158</v>
       </c>
       <c r="P355" t="n">
         <v>3900</v>
@@ -17683,10 +17683,10 @@
         <v>483</v>
       </c>
       <c r="N402" t="n">
-        <v>1630.9238760081</v>
+        <v>1630.9238867829</v>
       </c>
       <c r="O402" t="n">
-        <v>787736.2321119123</v>
+        <v>787736.2373161407</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
@@ -17862,10 +17862,10 @@
         <v>1997</v>
       </c>
       <c r="N406" t="n">
-        <v>1550.1939063158</v>
+        <v>1550.1939133186</v>
       </c>
       <c r="O406" t="n">
-        <v>3095737.230912652</v>
+        <v>3095737.244897244</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
@@ -17954,10 +17954,10 @@
         <v>1167</v>
       </c>
       <c r="N408" t="n">
-        <v>2403.5134379057</v>
+        <v>2403.513461205</v>
       </c>
       <c r="O408" t="n">
-        <v>2804900.182035952</v>
+        <v>2804900.209226235</v>
       </c>
       <c r="P408" t="n">
         <v>3500</v>
@@ -21727,10 +21727,10 @@
         <v>170</v>
       </c>
       <c r="N496" t="n">
-        <v>2517.22</v>
+        <v>2541.6788178138</v>
       </c>
       <c r="O496" t="n">
-        <v>427927.4</v>
+        <v>432085.399028346</v>
       </c>
       <c r="P496" t="n">
         <v>4200</v>
@@ -28224,10 +28224,10 @@
         <v>20</v>
       </c>
       <c r="N647" t="n">
-        <v>5218.1705692109</v>
+        <v>5218.1705706874</v>
       </c>
       <c r="O647" t="n">
-        <v>104363.411384218</v>
+        <v>104363.411413748</v>
       </c>
       <c r="P647" t="n">
         <v>8500</v>
@@ -28270,10 +28270,10 @@
         <v>133</v>
       </c>
       <c r="N648" t="n">
-        <v>1595.0093202147</v>
+        <v>1595.0093078324</v>
       </c>
       <c r="O648" t="n">
-        <v>212136.2395885551</v>
+        <v>212136.2379417092</v>
       </c>
       <c r="P648" t="n">
         <v>2600</v>
@@ -28730,10 +28730,10 @@
         <v>560</v>
       </c>
       <c r="N658" t="n">
-        <v>1664.3525567322</v>
+        <v>1664.3525037936</v>
       </c>
       <c r="O658" t="n">
-        <v>932037.4317700319</v>
+        <v>932037.402124416</v>
       </c>
       <c r="P658" t="n">
         <v>2900</v>
@@ -36605,10 +36605,10 @@
         <v>562</v>
       </c>
       <c r="N829" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O829" t="n">
-        <v>852013.7994747058</v>
+        <v>853020.7096178638</v>
       </c>
       <c r="P829" t="n">
         <v>2300</v>
@@ -36925,10 +36925,10 @@
         <v>559</v>
       </c>
       <c r="N836" t="n">
-        <v>1803.0158874609</v>
+        <v>1803.0158936022</v>
       </c>
       <c r="O836" t="n">
-        <v>1007885.881090643</v>
+        <v>1007885.88452363</v>
       </c>
       <c r="P836" t="n">
         <v>2500</v>
@@ -40835,10 +40835,10 @@
         <v>2428</v>
       </c>
       <c r="N922" t="n">
-        <v>517.29128286432</v>
+        <v>518.11303680169</v>
       </c>
       <c r="O922" t="n">
-        <v>1255983.234794569</v>
+        <v>1257978.453354503</v>
       </c>
       <c r="P922" t="n">
         <v>900</v>
@@ -41283,10 +41283,10 @@
         <v>1599</v>
       </c>
       <c r="N932" t="n">
-        <v>703.79502188713</v>
+        <v>703.79501848956</v>
       </c>
       <c r="O932" t="n">
-        <v>1125368.239997521</v>
+        <v>1125368.234564806</v>
       </c>
       <c r="P932" t="n">
         <v>900</v>
@@ -49722,10 +49722,10 @@
         <v>80</v>
       </c>
       <c r="N1120" t="n">
-        <v>3520</v>
+        <v>3571.512195122</v>
       </c>
       <c r="O1120" t="n">
-        <v>281600</v>
+        <v>285720.97560976</v>
       </c>
       <c r="P1120" t="n">
         <v>4500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -12097,10 +12097,10 @@
         <v>196</v>
       </c>
       <c r="N276" t="n">
-        <v>2582.2555145238</v>
+        <v>2582.2555084555</v>
       </c>
       <c r="O276" t="n">
-        <v>506122.0808466647</v>
+        <v>506122.079657278</v>
       </c>
       <c r="P276" t="n">
         <v>4500</v>
@@ -12624,10 +12624,10 @@
         <v>12</v>
       </c>
       <c r="N288" t="n">
-        <v>3841.62486</v>
+        <v>3841.6248746239</v>
       </c>
       <c r="O288" t="n">
-        <v>46099.49832</v>
+        <v>46099.4984954868</v>
       </c>
       <c r="P288" t="n">
         <v>6900</v>
@@ -17804,10 +17804,10 @@
         <v>469</v>
       </c>
       <c r="N405" t="n">
-        <v>1630.9239095069</v>
+        <v>1630.9239154786</v>
       </c>
       <c r="O405" t="n">
-        <v>764903.3135587361</v>
+        <v>764903.3163594634</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
@@ -18075,10 +18075,10 @@
         <v>1151</v>
       </c>
       <c r="N411" t="n">
-        <v>2403.5136926808</v>
+        <v>2403.513738111</v>
       </c>
       <c r="O411" t="n">
-        <v>2766444.260275601</v>
+        <v>2766444.312565761</v>
       </c>
       <c r="P411" t="n">
         <v>3500</v>
@@ -29067,10 +29067,10 @@
         <v>549</v>
       </c>
       <c r="N666" t="n">
-        <v>1664.3520684292</v>
+        <v>1664.351984375</v>
       </c>
       <c r="O666" t="n">
-        <v>913729.2855676308</v>
+        <v>913729.239421875</v>
       </c>
       <c r="P666" t="n">
         <v>2900</v>
@@ -41850,10 +41850,10 @@
         <v>1589</v>
       </c>
       <c r="N945" t="n">
-        <v>703.79500857932</v>
+        <v>703.79500789654</v>
       </c>
       <c r="O945" t="n">
-        <v>1118330.26863254</v>
+        <v>1118330.267547602</v>
       </c>
       <c r="P945" t="n">
         <v>900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1013,10 +1013,10 @@
         <v>32</v>
       </c>
       <c r="N15" t="n">
-        <v>27035.809018568</v>
+        <v>27000</v>
       </c>
       <c r="O15" t="n">
-        <v>865145.888594176</v>
+        <v>864000</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
@@ -4180,10 +4180,10 @@
         <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>30074.074074074</v>
+        <v>29000</v>
       </c>
       <c r="O93" t="n">
-        <v>90222.222222222</v>
+        <v>87000</v>
       </c>
       <c r="P93" t="n">
         <v>34800</v>
@@ -11395,10 +11395,10 @@
         <v>62</v>
       </c>
       <c r="N260" t="n">
-        <v>17234.854035088</v>
+        <v>17207.41</v>
       </c>
       <c r="O260" t="n">
-        <v>1068560.950175456</v>
+        <v>1066859.42</v>
       </c>
       <c r="P260" t="n">
         <v>20000</v>
@@ -13126,10 +13126,10 @@
         <v>158</v>
       </c>
       <c r="N299" t="n">
-        <v>8807.6968085106</v>
+        <v>8796</v>
       </c>
       <c r="O299" t="n">
-        <v>1391616.095744675</v>
+        <v>1389768</v>
       </c>
       <c r="P299" t="n">
         <v>14900</v>
@@ -13761,10 +13761,10 @@
         <v>62</v>
       </c>
       <c r="N313" t="n">
-        <v>5946.1052631579</v>
+        <v>5888</v>
       </c>
       <c r="O313" t="n">
-        <v>368658.5263157898</v>
+        <v>365056</v>
       </c>
       <c r="P313" t="n">
         <v>9500</v>
@@ -14982,10 +14982,10 @@
         <v>17</v>
       </c>
       <c r="N341" t="n">
-        <v>2667.0463248919</v>
+        <v>2665.4</v>
       </c>
       <c r="O341" t="n">
-        <v>45339.7875231623</v>
+        <v>45311.8</v>
       </c>
       <c r="P341" t="n">
         <v>20900</v>
@@ -15427,10 +15427,10 @@
         <v>201</v>
       </c>
       <c r="N351" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O351" t="n">
-        <v>878877.2135247519</v>
+        <v>878814.3692591541</v>
       </c>
       <c r="P351" t="n">
         <v>7500</v>
@@ -16347,10 +16347,10 @@
         <v>89</v>
       </c>
       <c r="N372" t="n">
-        <v>17473.953844316</v>
+        <v>17472.91</v>
       </c>
       <c r="O372" t="n">
-        <v>1555181.892144124</v>
+        <v>1555088.99</v>
       </c>
       <c r="P372" t="n">
         <v>2900</v>
@@ -16435,10 +16435,10 @@
         <v>175</v>
       </c>
       <c r="N374" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O374" t="n">
-        <v>267875.348373815</v>
+        <v>267860.25</v>
       </c>
       <c r="P374" t="n">
         <v>2900</v>
@@ -19388,10 +19388,10 @@
         <v>34</v>
       </c>
       <c r="N441" t="n">
-        <v>5101.7647058824</v>
+        <v>4956</v>
       </c>
       <c r="O441" t="n">
-        <v>173460.0000000016</v>
+        <v>168504</v>
       </c>
       <c r="P441" t="n">
         <v>7900</v>
@@ -21428,10 +21428,10 @@
         <v>178</v>
       </c>
       <c r="N489" t="n">
-        <v>2569.7269830028</v>
+        <v>2567</v>
       </c>
       <c r="O489" t="n">
-        <v>457411.4029744984</v>
+        <v>456926</v>
       </c>
       <c r="P489" t="n">
         <v>4500</v>
@@ -26345,10 +26345,10 @@
         <v>126</v>
       </c>
       <c r="N604" t="n">
-        <v>7982.1180305344</v>
+        <v>7969.9501679389</v>
       </c>
       <c r="O604" t="n">
-        <v>1005746.871847334</v>
+        <v>1004213.721160301</v>
       </c>
       <c r="P604" t="n">
         <v>12900</v>
@@ -26514,10 +26514,10 @@
         <v>29</v>
       </c>
       <c r="N608" t="n">
-        <v>10148.474923077</v>
+        <v>9994.710153846199</v>
       </c>
       <c r="O608" t="n">
-        <v>294305.772769233</v>
+        <v>289846.5944615398</v>
       </c>
       <c r="P608" t="n">
         <v>20800</v>
@@ -28629,10 +28629,10 @@
         <v>95</v>
       </c>
       <c r="N656" t="n">
-        <v>14447.670588235</v>
+        <v>14380</v>
       </c>
       <c r="O656" t="n">
-        <v>1372528.705882325</v>
+        <v>1366100</v>
       </c>
       <c r="P656" t="n">
         <v>23000</v>
@@ -32321,10 +32321,10 @@
         <v>10</v>
       </c>
       <c r="N736" t="n">
-        <v>23400.84</v>
+        <v>22942</v>
       </c>
       <c r="O736" t="n">
-        <v>234008.4</v>
+        <v>229420</v>
       </c>
       <c r="P736" t="n">
         <v>36900</v>
@@ -32687,10 +32687,10 @@
         <v>118</v>
       </c>
       <c r="N744" t="n">
-        <v>50584.365236051</v>
+        <v>50153.86</v>
       </c>
       <c r="O744" t="n">
-        <v>5968955.097854018</v>
+        <v>5918155.48</v>
       </c>
       <c r="P744" t="n">
         <v>11500</v>
@@ -33924,10 +33924,10 @@
         <v>72</v>
       </c>
       <c r="N771" t="n">
-        <v>9952.091954023001</v>
+        <v>9839</v>
       </c>
       <c r="O771" t="n">
-        <v>716550.620689656</v>
+        <v>708408</v>
       </c>
       <c r="P771" t="n">
         <v>16900</v>
@@ -35302,10 +35302,10 @@
         <v>132</v>
       </c>
       <c r="N801" t="n">
-        <v>59958.524453694</v>
+        <v>59834</v>
       </c>
       <c r="O801" t="n">
-        <v>7914525.227887608</v>
+        <v>7898088</v>
       </c>
       <c r="P801" t="n">
         <v>7900</v>
@@ -35440,10 +35440,10 @@
         <v>131</v>
       </c>
       <c r="N804" t="n">
-        <v>10270.481108312</v>
+        <v>10219</v>
       </c>
       <c r="O804" t="n">
-        <v>1345433.025188872</v>
+        <v>1338689</v>
       </c>
       <c r="P804" t="n">
         <v>16900</v>
@@ -36225,10 +36225,10 @@
         <v>188</v>
       </c>
       <c r="N821" t="n">
-        <v>3821.6520477816</v>
+        <v>3821</v>
       </c>
       <c r="O821" t="n">
-        <v>718470.5849829408</v>
+        <v>718348</v>
       </c>
       <c r="P821" t="n">
         <v>5900</v>
@@ -36271,10 +36271,10 @@
         <v>11</v>
       </c>
       <c r="N822" t="n">
-        <v>15512.291666667</v>
+        <v>15472</v>
       </c>
       <c r="O822" t="n">
-        <v>170635.208333337</v>
+        <v>170192</v>
       </c>
       <c r="P822" t="n">
         <v>25900</v>
@@ -36455,10 +36455,10 @@
         <v>435</v>
       </c>
       <c r="N826" t="n">
-        <v>5486.9301397206</v>
+        <v>5476</v>
       </c>
       <c r="O826" t="n">
-        <v>2386814.610778461</v>
+        <v>2382060</v>
       </c>
       <c r="P826" t="n">
         <v>8900</v>
@@ -37699,10 +37699,10 @@
         <v>42</v>
       </c>
       <c r="N853" t="n">
-        <v>5372.836713615</v>
+        <v>5347.73</v>
       </c>
       <c r="O853" t="n">
-        <v>225659.14197183</v>
+        <v>224604.66</v>
       </c>
       <c r="P853" t="n">
         <v>9500</v>
@@ -39443,10 +39443,10 @@
         <v>85</v>
       </c>
       <c r="N891" t="n">
-        <v>2407.2030769231</v>
+        <v>2357.74</v>
       </c>
       <c r="O891" t="n">
-        <v>204612.2615384635</v>
+        <v>200407.9</v>
       </c>
       <c r="P891" t="n">
         <v>3000</v>
@@ -44576,10 +44576,10 @@
         <v>9</v>
       </c>
       <c r="N1004" t="n">
-        <v>5235.0773519164</v>
+        <v>5216.9</v>
       </c>
       <c r="O1004" t="n">
-        <v>47115.6961672476</v>
+        <v>46952.1</v>
       </c>
       <c r="P1004" t="n">
         <v>20500</v>
@@ -44909,10 +44909,10 @@
         <v>179</v>
       </c>
       <c r="N1011" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O1011" t="n">
-        <v>1261946.523499465</v>
+        <v>1261402.229104636</v>
       </c>
       <c r="P1011" t="n">
         <v>9900</v>
@@ -47730,10 +47730,10 @@
         <v>145</v>
       </c>
       <c r="N1075" t="n">
-        <v>1728.3970421649</v>
+        <v>1727.31</v>
       </c>
       <c r="O1075" t="n">
-        <v>250617.5711139105</v>
+        <v>250459.95</v>
       </c>
       <c r="P1075" t="n">
         <v>2850</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -2918,10 +2918,10 @@
         <v>8</v>
       </c>
       <c r="N62" t="n">
-        <v>12357.960422535</v>
+        <v>12357.960425532</v>
       </c>
       <c r="O62" t="n">
-        <v>98863.68338028</v>
+        <v>98863.68340425599</v>
       </c>
       <c r="P62" t="n">
         <v>15900</v>
@@ -4813,10 +4813,10 @@
         <v>39</v>
       </c>
       <c r="N107" t="n">
-        <v>10994.361818182</v>
+        <v>10994.362222222</v>
       </c>
       <c r="O107" t="n">
-        <v>428780.110909098</v>
+        <v>428780.126666658</v>
       </c>
       <c r="P107" t="n">
         <v>16900</v>
@@ -4978,10 +4978,10 @@
         <v>26</v>
       </c>
       <c r="N111" t="n">
-        <v>15711.96562212</v>
+        <v>15711.965560748</v>
       </c>
       <c r="O111" t="n">
-        <v>408511.10617512</v>
+        <v>408511.104579448</v>
       </c>
       <c r="P111" t="n">
         <v>28500</v>
@@ -5025,10 +5025,10 @@
         <v>11</v>
       </c>
       <c r="N112" t="n">
-        <v>9392.0750746269</v>
+        <v>9392.075312499999</v>
       </c>
       <c r="O112" t="n">
-        <v>103312.8258208959</v>
+        <v>103312.8284375</v>
       </c>
       <c r="P112" t="n">
         <v>18500</v>
@@ -5477,22 +5477,22 @@
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M123" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N123" t="n">
-        <v>22267.5525</v>
+        <v>22267.552777778</v>
       </c>
       <c r="O123" t="n">
-        <v>111337.7625</v>
+        <v>66802.65833333399</v>
       </c>
       <c r="P123" t="n">
         <v>46300</v>
       </c>
       <c r="Q123" t="n">
-        <v>231500</v>
+        <v>138900</v>
       </c>
     </row>
     <row r="124">
@@ -5865,22 +5865,22 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M132" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N132" t="n">
-        <v>56906.803962264</v>
+        <v>56906.805744681</v>
       </c>
       <c r="O132" t="n">
-        <v>512161.235660376</v>
+        <v>398347.640212767</v>
       </c>
       <c r="P132" t="n">
         <v>95900</v>
       </c>
       <c r="Q132" t="n">
-        <v>863100</v>
+        <v>671300</v>
       </c>
     </row>
     <row r="133">
@@ -5912,22 +5912,22 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N133" t="n">
-        <v>62349.656875</v>
+        <v>62349.656129032</v>
       </c>
       <c r="O133" t="n">
-        <v>374097.94125</v>
+        <v>311748.28064516</v>
       </c>
       <c r="P133" t="n">
         <v>109900</v>
       </c>
       <c r="Q133" t="n">
-        <v>659400</v>
+        <v>549500</v>
       </c>
     </row>
     <row r="134">
@@ -6006,22 +6006,22 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N135" t="n">
-        <v>141416.88459016</v>
+        <v>141416.88460526</v>
       </c>
       <c r="O135" t="n">
-        <v>282833.76918032</v>
+        <v>141416.88460526</v>
       </c>
       <c r="P135" t="n">
         <v>251900</v>
       </c>
       <c r="Q135" t="n">
-        <v>503800</v>
+        <v>251900</v>
       </c>
     </row>
     <row r="136">
@@ -6048,22 +6048,22 @@
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N136" t="n">
-        <v>200072.20183486</v>
+        <v>200072.20194444</v>
       </c>
       <c r="O136" t="n">
-        <v>2400866.42201832</v>
+        <v>2200794.22138884</v>
       </c>
       <c r="P136" t="n">
         <v>312000</v>
       </c>
       <c r="Q136" t="n">
-        <v>3744000</v>
+        <v>3432000</v>
       </c>
     </row>
     <row r="137">
@@ -6090,22 +6090,22 @@
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>174389.79954545</v>
+        <v>174389.80095238</v>
       </c>
       <c r="O137" t="n">
-        <v>174389.79954545</v>
+        <v>0</v>
       </c>
       <c r="P137" t="n">
         <v>368200</v>
       </c>
       <c r="Q137" t="n">
-        <v>368200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -6190,10 +6190,10 @@
         <v>2</v>
       </c>
       <c r="N139" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17844444</v>
       </c>
       <c r="O139" t="n">
-        <v>689198.35702128</v>
+        <v>689198.35688888</v>
       </c>
       <c r="P139" t="n">
         <v>532900</v>
@@ -7031,10 +7031,10 @@
         <v>7</v>
       </c>
       <c r="N159" t="n">
-        <v>61666.874148352</v>
+        <v>61666.87415978</v>
       </c>
       <c r="O159" t="n">
-        <v>431668.119038464</v>
+        <v>431668.11911846</v>
       </c>
       <c r="P159" t="n">
         <v>98900</v>
@@ -10157,10 +10157,10 @@
         <v>440</v>
       </c>
       <c r="N231" t="n">
-        <v>1098.0624184202</v>
+        <v>1098.0625007652</v>
       </c>
       <c r="O231" t="n">
-        <v>483147.464104888</v>
+        <v>483147.500336688</v>
       </c>
       <c r="P231" t="n">
         <v>1500</v>
@@ -12005,10 +12005,10 @@
         <v>193</v>
       </c>
       <c r="N274" t="n">
-        <v>2582.2554768392</v>
+        <v>2582.2554727273</v>
       </c>
       <c r="O274" t="n">
-        <v>498375.3070299656</v>
+        <v>498375.3062363689</v>
       </c>
       <c r="P274" t="n">
         <v>4500</v>
@@ -14414,10 +14414,10 @@
         <v>96</v>
       </c>
       <c r="N328" t="n">
-        <v>3594.253608522</v>
+        <v>3594.2536</v>
       </c>
       <c r="O328" t="n">
-        <v>345048.346418112</v>
+        <v>345048.3456</v>
       </c>
       <c r="P328" t="n">
         <v>6500</v>
@@ -14721,10 +14721,10 @@
         <v>54</v>
       </c>
       <c r="N335" t="n">
-        <v>14822.378837068</v>
+        <v>14822.378836364</v>
       </c>
       <c r="O335" t="n">
-        <v>800408.457201672</v>
+        <v>800408.457163656</v>
       </c>
       <c r="P335" t="n">
         <v>24900</v>
@@ -15517,10 +15517,10 @@
         <v>2</v>
       </c>
       <c r="N353" t="n">
-        <v>1592.5660665658</v>
+        <v>1592.5660516325</v>
       </c>
       <c r="O353" t="n">
-        <v>3185.1321331316</v>
+        <v>3185.132103265</v>
       </c>
       <c r="P353" t="n">
         <v>3900</v>
@@ -17711,22 +17711,22 @@
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M403" t="n">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="N403" t="n">
-        <v>1690.5922846782</v>
+        <v>1690.591979835</v>
       </c>
       <c r="O403" t="n">
-        <v>605232.0379147956</v>
+        <v>584944.82502291</v>
       </c>
       <c r="P403" t="n">
         <v>2900</v>
       </c>
       <c r="Q403" t="n">
-        <v>1038200</v>
+        <v>1003400</v>
       </c>
     </row>
     <row r="404">
@@ -17757,22 +17757,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M404" t="n">
-        <v>1771</v>
+        <v>1759</v>
       </c>
       <c r="N404" t="n">
-        <v>1550.1940319426</v>
+        <v>1550.1940372063</v>
       </c>
       <c r="O404" t="n">
-        <v>2745393.630570345</v>
+        <v>2726791.311445882</v>
       </c>
       <c r="P404" t="n">
         <v>2500</v>
       </c>
       <c r="Q404" t="n">
-        <v>4427500</v>
+        <v>4397500</v>
       </c>
     </row>
     <row r="405">
@@ -17849,22 +17849,22 @@
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M406" t="n">
-        <v>1107</v>
+        <v>1071</v>
       </c>
       <c r="N406" t="n">
-        <v>2403.5140171519</v>
+        <v>2403.5141965714</v>
       </c>
       <c r="O406" t="n">
-        <v>2660690.016987153</v>
+        <v>2574163.704527969</v>
       </c>
       <c r="P406" t="n">
         <v>3500</v>
       </c>
       <c r="Q406" t="n">
-        <v>3874500</v>
+        <v>3748500</v>
       </c>
     </row>
     <row r="407">
@@ -21797,10 +21797,10 @@
         <v>425</v>
       </c>
       <c r="N498" t="n">
-        <v>2029.8739872408</v>
+        <v>2029.8739957379</v>
       </c>
       <c r="O498" t="n">
-        <v>862696.44457734</v>
+        <v>862696.4481886075</v>
       </c>
       <c r="P498" t="n">
         <v>3600</v>
@@ -23406,10 +23406,10 @@
         <v>274</v>
       </c>
       <c r="N536" t="n">
-        <v>4285.1958525346</v>
+        <v>4285.1958592849</v>
       </c>
       <c r="O536" t="n">
-        <v>1174143.66359448</v>
+        <v>1174143.665444063</v>
       </c>
       <c r="P536" t="n">
         <v>6900</v>
@@ -28669,22 +28669,22 @@
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M657" t="n">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="N657" t="n">
-        <v>1664.3497007042</v>
+        <v>1664.3491877256</v>
       </c>
       <c r="O657" t="n">
-        <v>803880.9054401285</v>
+        <v>783908.4674187575</v>
       </c>
       <c r="P657" t="n">
         <v>2900</v>
       </c>
       <c r="Q657" t="n">
-        <v>1400700</v>
+        <v>1365900</v>
       </c>
     </row>
     <row r="658">
@@ -29555,10 +29555,10 @@
         <v>1328</v>
       </c>
       <c r="N676" t="n">
-        <v>1778.4726973583</v>
+        <v>1778.472697775</v>
       </c>
       <c r="O676" t="n">
-        <v>2361811.742091822</v>
+        <v>2361811.7426452</v>
       </c>
       <c r="P676" t="n">
         <v>4900</v>
@@ -33193,10 +33193,10 @@
         <v>16</v>
       </c>
       <c r="N755" t="n">
-        <v>4907.8223782772</v>
+        <v>4907.8223917137</v>
       </c>
       <c r="O755" t="n">
-        <v>78525.1580524352</v>
+        <v>78525.1582674192</v>
       </c>
       <c r="P755" t="n">
         <v>8200</v>
@@ -35031,10 +35031,10 @@
         <v>170</v>
       </c>
       <c r="N795" t="n">
-        <v>17075.98952183</v>
+        <v>17075.989521166</v>
       </c>
       <c r="O795" t="n">
-        <v>2902918.2187111</v>
+        <v>2902918.21859822</v>
       </c>
       <c r="P795" t="n">
         <v>27500</v>
@@ -37238,10 +37238,10 @@
         <v>1082</v>
       </c>
       <c r="N843" t="n">
-        <v>2056.082714437</v>
+        <v>2056.08270929</v>
       </c>
       <c r="O843" t="n">
-        <v>2224681.497020834</v>
+        <v>2224681.49145178</v>
       </c>
       <c r="P843" t="n">
         <v>2900</v>
@@ -37284,10 +37284,10 @@
         <v>198</v>
       </c>
       <c r="N844" t="n">
-        <v>3224.5689724311</v>
+        <v>3224.568981435</v>
       </c>
       <c r="O844" t="n">
-        <v>638464.6565413579</v>
+        <v>638464.65832413</v>
       </c>
       <c r="P844" t="n">
         <v>4500</v>
@@ -40915,10 +40915,10 @@
         <v>2730</v>
       </c>
       <c r="N924" t="n">
-        <v>517.2923857868</v>
+        <v>517.29240467717</v>
       </c>
       <c r="O924" t="n">
-        <v>1412208.213197964</v>
+        <v>1412208.264768674</v>
       </c>
       <c r="P924" t="n">
         <v>900</v>
@@ -41141,10 +41141,10 @@
         <v>617</v>
       </c>
       <c r="N929" t="n">
-        <v>3110.8400113026</v>
+        <v>3110.8399744753</v>
       </c>
       <c r="O929" t="n">
-        <v>1919388.286973704</v>
+        <v>1919388.26425126</v>
       </c>
       <c r="P929" t="n">
         <v>4500</v>
@@ -44530,10 +44530,10 @@
         <v>2</v>
       </c>
       <c r="N1003" t="n">
-        <v>2000.6888095238</v>
+        <v>2000.6919512195</v>
       </c>
       <c r="O1003" t="n">
-        <v>4001.3776190476</v>
+        <v>4001.383902439</v>
       </c>
       <c r="P1003" t="n">
         <v>2000</v>
@@ -49796,22 +49796,22 @@
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1122" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N1122" t="n">
         <v>3520</v>
       </c>
       <c r="O1122" t="n">
-        <v>232320</v>
+        <v>211200</v>
       </c>
       <c r="P1122" t="n">
         <v>4500</v>
       </c>
       <c r="Q1122" t="n">
-        <v>297000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="1123">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -11963,10 +11963,10 @@
         <v>193</v>
       </c>
       <c r="N273" t="n">
-        <v>2582.2554675768</v>
+        <v>2582.2554613807</v>
       </c>
       <c r="O273" t="n">
-        <v>498375.3052423224</v>
+        <v>498375.3040464751</v>
       </c>
       <c r="P273" t="n">
         <v>4500</v>
@@ -13035,10 +13035,10 @@
         <v>138</v>
       </c>
       <c r="N297" t="n">
-        <v>7507.39</v>
+        <v>7518.1997768179</v>
       </c>
       <c r="O297" t="n">
-        <v>1036019.82</v>
+        <v>1037511.56920087</v>
       </c>
       <c r="P297" t="n">
         <v>13500</v>
@@ -13084,10 +13084,10 @@
         <v>158</v>
       </c>
       <c r="N298" t="n">
-        <v>8796</v>
+        <v>8831.230974632799</v>
       </c>
       <c r="O298" t="n">
-        <v>1389768</v>
+        <v>1395334.493991982</v>
       </c>
       <c r="P298" t="n">
         <v>14900</v>
@@ -15074,10 +15074,10 @@
         <v>6</v>
       </c>
       <c r="N343" t="n">
-        <v>15851.61</v>
+        <v>15976.425826772</v>
       </c>
       <c r="O343" t="n">
-        <v>95109.66</v>
+        <v>95858.554960632</v>
       </c>
       <c r="P343" t="n">
         <v>23900</v>
@@ -17721,10 +17721,10 @@
         <v>2120</v>
       </c>
       <c r="N403" t="n">
-        <v>1550.1940686328</v>
+        <v>1550.1940704179</v>
       </c>
       <c r="O403" t="n">
-        <v>3286411.425501536</v>
+        <v>3286411.429285948</v>
       </c>
       <c r="P403" t="n">
         <v>2500</v>
@@ -17813,10 +17813,10 @@
         <v>1068</v>
       </c>
       <c r="N405" t="n">
-        <v>2403.5142945915</v>
+        <v>2403.514304468</v>
       </c>
       <c r="O405" t="n">
-        <v>2566953.266623722</v>
+        <v>2566953.277171824</v>
       </c>
       <c r="P405" t="n">
         <v>3500</v>
@@ -28679,10 +28679,10 @@
         <v>73</v>
       </c>
       <c r="N657" t="n">
-        <v>15502</v>
+        <v>15634.495726496</v>
       </c>
       <c r="O657" t="n">
-        <v>1131646</v>
+        <v>1141318.188034208</v>
       </c>
       <c r="P657" t="n">
         <v>25900</v>
@@ -29513,10 +29513,10 @@
         <v>1328</v>
       </c>
       <c r="N675" t="n">
-        <v>1778.4727006961</v>
+        <v>1778.4727011139</v>
       </c>
       <c r="O675" t="n">
-        <v>2361811.746524421</v>
+        <v>2361811.747079259</v>
       </c>
       <c r="P675" t="n">
         <v>4900</v>
@@ -31497,10 +31497,10 @@
         <v>33</v>
       </c>
       <c r="N718" t="n">
-        <v>28116</v>
+        <v>28613.628318584</v>
       </c>
       <c r="O718" t="n">
-        <v>927828</v>
+        <v>944249.7345132721</v>
       </c>
       <c r="P718" t="n">
         <v>45900</v>
@@ -35447,10 +35447,10 @@
         <v>90</v>
       </c>
       <c r="N804" t="n">
-        <v>10755</v>
+        <v>10792.803163445</v>
       </c>
       <c r="O804" t="n">
-        <v>967950</v>
+        <v>971352.28471005</v>
       </c>
       <c r="P804" t="n">
         <v>17900</v>
@@ -37012,10 +37012,10 @@
         <v>844</v>
       </c>
       <c r="N838" t="n">
-        <v>1803.0159286464</v>
+        <v>1803.0159327966</v>
       </c>
       <c r="O838" t="n">
-        <v>1521745.443777562</v>
+        <v>1521745.44728033</v>
       </c>
       <c r="P838" t="n">
         <v>2500</v>
@@ -37703,10 +37703,10 @@
         <v>2</v>
       </c>
       <c r="N853" t="n">
-        <v>1906.180625</v>
+        <v>1906.1803846154</v>
       </c>
       <c r="O853" t="n">
-        <v>3812.36125</v>
+        <v>3812.3607692308</v>
       </c>
       <c r="P853" t="n">
         <v>2900</v>
@@ -41321,10 +41321,10 @@
         <v>1472</v>
       </c>
       <c r="N933" t="n">
-        <v>703.79497049501</v>
+        <v>703.79496992783</v>
       </c>
       <c r="O933" t="n">
-        <v>1035986.196568655</v>
+        <v>1035986.195733766</v>
       </c>
       <c r="P933" t="n">
         <v>900</v>
@@ -49484,10 +49484,10 @@
         <v>2</v>
       </c>
       <c r="N1115" t="n">
-        <v>7480</v>
+        <v>7524.8351648352</v>
       </c>
       <c r="O1115" t="n">
-        <v>14960</v>
+        <v>15049.6703296704</v>
       </c>
       <c r="P1115" t="n">
         <v>9500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -2879,10 +2879,10 @@
         <v>35</v>
       </c>
       <c r="N61" t="n">
-        <v>6272.8550526316</v>
+        <v>6272.8550704225</v>
       </c>
       <c r="O61" t="n">
-        <v>219549.926842106</v>
+        <v>219549.9274647875</v>
       </c>
       <c r="P61" t="n">
         <v>7900</v>
@@ -3202,10 +3202,10 @@
         <v>2</v>
       </c>
       <c r="N69" t="n">
-        <v>40500</v>
+        <v>27000</v>
       </c>
       <c r="O69" t="n">
-        <v>81000</v>
+        <v>54000</v>
       </c>
       <c r="P69" t="n">
         <v>35000</v>
@@ -4049,10 +4049,10 @@
         <v>88</v>
       </c>
       <c r="N90" t="n">
-        <v>2053.9877300613</v>
+        <v>1800</v>
       </c>
       <c r="O90" t="n">
-        <v>180750.9202453944</v>
+        <v>158400</v>
       </c>
       <c r="P90" t="n">
         <v>2200</v>
@@ -5483,10 +5483,10 @@
         <v>3</v>
       </c>
       <c r="N123" t="n">
-        <v>23504.638888889</v>
+        <v>22267.552777778</v>
       </c>
       <c r="O123" t="n">
-        <v>70513.91666666701</v>
+        <v>66802.65833333399</v>
       </c>
       <c r="P123" t="n">
         <v>46300</v>
@@ -9482,10 +9482,10 @@
         <v>202</v>
       </c>
       <c r="N215" t="n">
-        <v>2834.5536057033</v>
+        <v>2833</v>
       </c>
       <c r="O215" t="n">
-        <v>572579.8283520666</v>
+        <v>572266</v>
       </c>
       <c r="P215" t="n">
         <v>3500</v>
@@ -10115,10 +10115,10 @@
         <v>430</v>
       </c>
       <c r="N230" t="n">
-        <v>1098.0627514701</v>
+        <v>1098.0628221049</v>
       </c>
       <c r="O230" t="n">
-        <v>472166.983132143</v>
+        <v>472167.013505107</v>
       </c>
       <c r="P230" t="n">
         <v>1500</v>
@@ -11312,10 +11312,10 @@
         <v>2</v>
       </c>
       <c r="N258" t="n">
-        <v>13642.54185766</v>
+        <v>13593.35</v>
       </c>
       <c r="O258" t="n">
-        <v>27285.08371532</v>
+        <v>27186.7</v>
       </c>
       <c r="P258" t="n">
         <v>25500</v>
@@ -11607,10 +11607,10 @@
         <v>522</v>
       </c>
       <c r="N265" t="n">
-        <v>2808.3040151157</v>
+        <v>2804.33</v>
       </c>
       <c r="O265" t="n">
-        <v>1465934.695890395</v>
+        <v>1463860.26</v>
       </c>
       <c r="P265" t="n">
         <v>4900</v>
@@ -11963,10 +11963,10 @@
         <v>181</v>
       </c>
       <c r="N273" t="n">
-        <v>2584.0407928094</v>
+        <v>2582.2554090804</v>
       </c>
       <c r="O273" t="n">
-        <v>467711.3834985014</v>
+        <v>467388.2290435524</v>
       </c>
       <c r="P273" t="n">
         <v>4500</v>
@@ -12055,10 +12055,10 @@
         <v>99</v>
       </c>
       <c r="N275" t="n">
-        <v>5216.8960111863</v>
+        <v>5216.8960094242</v>
       </c>
       <c r="O275" t="n">
-        <v>516472.7051074437</v>
+        <v>516472.7049329958</v>
       </c>
       <c r="P275" t="n">
         <v>8500</v>
@@ -12311,10 +12311,10 @@
         <v>77</v>
       </c>
       <c r="N281" t="n">
-        <v>6754.0134146341</v>
+        <v>6713.08</v>
       </c>
       <c r="O281" t="n">
-        <v>520059.0329268257</v>
+        <v>516907.16</v>
       </c>
       <c r="P281" t="n">
         <v>9900</v>
@@ -12357,10 +12357,10 @@
         <v>621</v>
       </c>
       <c r="N282" t="n">
-        <v>3161.3542590035</v>
+        <v>3158.8608322644</v>
       </c>
       <c r="O282" t="n">
-        <v>1963200.994841174</v>
+        <v>1961652.576836192</v>
       </c>
       <c r="P282" t="n">
         <v>5600</v>
@@ -12626,10 +12626,10 @@
         <v>872</v>
       </c>
       <c r="N288" t="n">
-        <v>1482.16796875</v>
+        <v>1480</v>
       </c>
       <c r="O288" t="n">
-        <v>1292450.46875</v>
+        <v>1290560</v>
       </c>
       <c r="P288" t="n">
         <v>2600</v>
@@ -13038,10 +13038,10 @@
         <v>156</v>
       </c>
       <c r="N297" t="n">
-        <v>8807.775100401601</v>
+        <v>8796</v>
       </c>
       <c r="O297" t="n">
-        <v>1374012.91566265</v>
+        <v>1372176</v>
       </c>
       <c r="P297" t="n">
         <v>14900</v>
@@ -13353,10 +13353,10 @@
         <v>191</v>
       </c>
       <c r="N304" t="n">
-        <v>4362.7231895528</v>
+        <v>4357.55</v>
       </c>
       <c r="O304" t="n">
-        <v>833280.1292045849</v>
+        <v>832292.05</v>
       </c>
       <c r="P304" t="n">
         <v>7500</v>
@@ -13480,22 +13480,22 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M307" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N307" t="n">
-        <v>4890.9300496586</v>
+        <v>4890.9300497203</v>
       </c>
       <c r="O307" t="n">
-        <v>141836.9714400994</v>
+        <v>132055.1113424481</v>
       </c>
       <c r="P307" t="n">
         <v>8200</v>
       </c>
       <c r="Q307" t="n">
-        <v>237800</v>
+        <v>221400</v>
       </c>
     </row>
     <row r="308">
@@ -13667,22 +13667,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M311" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N311" t="n">
         <v>5888</v>
       </c>
       <c r="O311" t="n">
-        <v>359168</v>
+        <v>347392</v>
       </c>
       <c r="P311" t="n">
         <v>9500</v>
       </c>
       <c r="Q311" t="n">
-        <v>579500</v>
+        <v>560500</v>
       </c>
     </row>
     <row r="312">
@@ -14026,10 +14026,10 @@
         <v>31</v>
       </c>
       <c r="N319" t="n">
-        <v>8670.9576008273</v>
+        <v>8662</v>
       </c>
       <c r="O319" t="n">
-        <v>268799.6856256463</v>
+        <v>268522</v>
       </c>
       <c r="P319" t="n">
         <v>14200</v>
@@ -14107,22 +14107,22 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M321" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="N321" t="n">
         <v>10716.34</v>
       </c>
       <c r="O321" t="n">
-        <v>267908.5</v>
+        <v>85730.72</v>
       </c>
       <c r="P321" t="n">
         <v>39000</v>
       </c>
       <c r="Q321" t="n">
-        <v>975000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="322">
@@ -14326,10 +14326,10 @@
         <v>96</v>
       </c>
       <c r="N326" t="n">
-        <v>3594.2535785953</v>
+        <v>3594.2535742972</v>
       </c>
       <c r="O326" t="n">
-        <v>345048.3435451488</v>
+        <v>345048.3431325312</v>
       </c>
       <c r="P326" t="n">
         <v>6500</v>
@@ -14535,22 +14535,22 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M331" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N331" t="n">
         <v>4891</v>
       </c>
       <c r="O331" t="n">
-        <v>518446</v>
+        <v>508664</v>
       </c>
       <c r="P331" t="n">
         <v>8200</v>
       </c>
       <c r="Q331" t="n">
-        <v>869200</v>
+        <v>852800</v>
       </c>
     </row>
     <row r="332">
@@ -14633,10 +14633,10 @@
         <v>54</v>
       </c>
       <c r="N333" t="n">
-        <v>14849.377704918</v>
+        <v>14822.378834244</v>
       </c>
       <c r="O333" t="n">
-        <v>801866.396065572</v>
+        <v>800408.457049176</v>
       </c>
       <c r="P333" t="n">
         <v>24900</v>
@@ -14894,10 +14894,10 @@
         <v>16</v>
       </c>
       <c r="N339" t="n">
-        <v>2672.0057001239</v>
+        <v>2665.4</v>
       </c>
       <c r="O339" t="n">
-        <v>42752.0912019824</v>
+        <v>42646.4</v>
       </c>
       <c r="P339" t="n">
         <v>20900</v>
@@ -15252,10 +15252,10 @@
         <v>426</v>
       </c>
       <c r="N347" t="n">
-        <v>3041.6600137268</v>
+        <v>3041.6600137646</v>
       </c>
       <c r="O347" t="n">
-        <v>1295747.165847617</v>
+        <v>1295747.16586372</v>
       </c>
       <c r="P347" t="n">
         <v>5500</v>
@@ -15339,10 +15339,10 @@
         <v>200</v>
       </c>
       <c r="N349" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O349" t="n">
-        <v>874442.15853484</v>
+        <v>874942.91281318</v>
       </c>
       <c r="P349" t="n">
         <v>7500</v>
@@ -16435,10 +16435,10 @@
         <v>58</v>
       </c>
       <c r="N374" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O374" t="n">
-        <v>546511.912903797</v>
+        <v>546029.98</v>
       </c>
       <c r="P374" t="n">
         <v>16900</v>
@@ -17015,10 +17015,10 @@
         <v>82</v>
       </c>
       <c r="N387" t="n">
-        <v>11939.712442396</v>
+        <v>11921.4</v>
       </c>
       <c r="O387" t="n">
-        <v>979056.420276472</v>
+        <v>977554.7999999999</v>
       </c>
       <c r="P387" t="n">
         <v>19900</v>
@@ -17404,10 +17404,10 @@
         <v>63</v>
       </c>
       <c r="N396" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="O396" t="n">
-        <v>625342.1576086944</v>
+        <v>623889</v>
       </c>
       <c r="P396" t="n">
         <v>15900</v>
@@ -17629,10 +17629,10 @@
         <v>304</v>
       </c>
       <c r="N401" t="n">
-        <v>1690.5907183908</v>
+        <v>1830.8887033195</v>
       </c>
       <c r="O401" t="n">
-        <v>513939.5783908032</v>
+        <v>556590.1658091281</v>
       </c>
       <c r="P401" t="n">
         <v>2900</v>
@@ -17669,22 +17669,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M402" t="n">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="N402" t="n">
-        <v>1550.194110545</v>
+        <v>1550.1942738685</v>
       </c>
       <c r="O402" t="n">
-        <v>3191849.673612155</v>
+        <v>3184099.038525899</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
       </c>
       <c r="Q402" t="n">
-        <v>5147500</v>
+        <v>5135000</v>
       </c>
     </row>
     <row r="403">
@@ -17767,10 +17767,10 @@
         <v>1042</v>
       </c>
       <c r="N404" t="n">
-        <v>2403.5145969448</v>
+        <v>2549.7269035153</v>
       </c>
       <c r="O404" t="n">
-        <v>2504462.210016482</v>
+        <v>2656815.433462942</v>
       </c>
       <c r="P404" t="n">
         <v>3500</v>
@@ -18068,10 +18068,10 @@
         <v>2</v>
       </c>
       <c r="N411" t="n">
-        <v>16994.7</v>
+        <v>14778</v>
       </c>
       <c r="O411" t="n">
-        <v>33989.4</v>
+        <v>29556</v>
       </c>
       <c r="P411" t="n">
         <v>24900</v>
@@ -20553,10 +20553,10 @@
         <v>65</v>
       </c>
       <c r="N468" t="n">
-        <v>9396.9148264984</v>
+        <v>9338</v>
       </c>
       <c r="O468" t="n">
-        <v>610799.4637223959</v>
+        <v>606970</v>
       </c>
       <c r="P468" t="n">
         <v>15500</v>
@@ -21253,10 +21253,10 @@
         <v>149</v>
       </c>
       <c r="N485" t="n">
-        <v>8799.4430248307</v>
+        <v>8794.48</v>
       </c>
       <c r="O485" t="n">
-        <v>1311117.010699774</v>
+        <v>1310377.52</v>
       </c>
       <c r="P485" t="n">
         <v>14500</v>
@@ -21586,10 +21586,10 @@
         <v>158</v>
       </c>
       <c r="N493" t="n">
-        <v>2523.5712699748</v>
+        <v>2517.22</v>
       </c>
       <c r="O493" t="n">
-        <v>398724.2606560184</v>
+        <v>397720.76</v>
       </c>
       <c r="P493" t="n">
         <v>4200</v>
@@ -23318,10 +23318,10 @@
         <v>274</v>
       </c>
       <c r="N534" t="n">
-        <v>4285.1958660508</v>
+        <v>4285.1959694477</v>
       </c>
       <c r="O534" t="n">
-        <v>1174143.667297919</v>
+        <v>1174143.69562867</v>
       </c>
       <c r="P534" t="n">
         <v>6900</v>
@@ -24084,10 +24084,10 @@
         <v>26</v>
       </c>
       <c r="N552" t="n">
-        <v>12379.333333333</v>
+        <v>11980</v>
       </c>
       <c r="O552" t="n">
-        <v>321862.666666658</v>
+        <v>311480</v>
       </c>
       <c r="P552" t="n">
         <v>19500</v>
@@ -24130,10 +24130,10 @@
         <v>49</v>
       </c>
       <c r="N553" t="n">
-        <v>11594.607549296</v>
+        <v>11562.038422535</v>
       </c>
       <c r="O553" t="n">
-        <v>568135.769915504</v>
+        <v>566539.882704215</v>
       </c>
       <c r="P553" t="n">
         <v>18500</v>
@@ -24176,10 +24176,10 @@
         <v>55</v>
       </c>
       <c r="N554" t="n">
-        <v>13621.7524</v>
+        <v>13513.64328</v>
       </c>
       <c r="O554" t="n">
-        <v>749196.382</v>
+        <v>743250.3804</v>
       </c>
       <c r="P554" t="n">
         <v>21900</v>
@@ -25558,10 +25558,10 @@
         <v>36</v>
       </c>
       <c r="N586" t="n">
-        <v>27871.270433071</v>
+        <v>27123.76496063</v>
       </c>
       <c r="O586" t="n">
-        <v>1003365.735590556</v>
+        <v>976455.53858268</v>
       </c>
       <c r="P586" t="n">
         <v>44500</v>
@@ -25604,10 +25604,10 @@
         <v>58</v>
       </c>
       <c r="N587" t="n">
-        <v>17070.322056338</v>
+        <v>16974.69</v>
       </c>
       <c r="O587" t="n">
-        <v>990078.6792676039</v>
+        <v>984532.0199999999</v>
       </c>
       <c r="P587" t="n">
         <v>26900</v>
@@ -25768,10 +25768,10 @@
         <v>18</v>
       </c>
       <c r="N591" t="n">
-        <v>4110.4025485437</v>
+        <v>4100.45</v>
       </c>
       <c r="O591" t="n">
-        <v>73987.2458737866</v>
+        <v>73808.09999999999</v>
       </c>
       <c r="P591" t="n">
         <v>26900</v>
@@ -26385,10 +26385,10 @@
         <v>1</v>
       </c>
       <c r="N605" t="n">
-        <v>9681.731751412401</v>
+        <v>9627.34</v>
       </c>
       <c r="O605" t="n">
-        <v>9681.731751412401</v>
+        <v>9627.34</v>
       </c>
       <c r="P605" t="n">
         <v>15900</v>
@@ -28587,10 +28587,10 @@
         <v>440</v>
       </c>
       <c r="N655" t="n">
-        <v>1664.3476116505</v>
+        <v>1664.3474804688</v>
       </c>
       <c r="O655" t="n">
-        <v>732312.9491262201</v>
+        <v>732312.8914062721</v>
       </c>
       <c r="P655" t="n">
         <v>2900</v>
@@ -28823,10 +28823,10 @@
         <v>2</v>
       </c>
       <c r="N660" t="n">
-        <v>11048.707428571</v>
+        <v>10451.48</v>
       </c>
       <c r="O660" t="n">
-        <v>22097.414857142</v>
+        <v>20902.96</v>
       </c>
       <c r="P660" t="n">
         <v>16900</v>
@@ -29099,10 +29099,10 @@
         <v>25</v>
       </c>
       <c r="N666" t="n">
-        <v>15867.472527473</v>
+        <v>15824</v>
       </c>
       <c r="O666" t="n">
-        <v>396686.813186825</v>
+        <v>395600</v>
       </c>
       <c r="P666" t="n">
         <v>26900</v>
@@ -29375,10 +29375,10 @@
         <v>80</v>
       </c>
       <c r="N672" t="n">
-        <v>3494.4765957447</v>
+        <v>3486</v>
       </c>
       <c r="O672" t="n">
-        <v>279558.127659576</v>
+        <v>278880</v>
       </c>
       <c r="P672" t="n">
         <v>6900</v>
@@ -29421,10 +29421,10 @@
         <v>1304</v>
       </c>
       <c r="N673" t="n">
-        <v>1778.4727221703</v>
+        <v>1778.4727234441</v>
       </c>
       <c r="O673" t="n">
-        <v>2319128.429710071</v>
+        <v>2319128.431371106</v>
       </c>
       <c r="P673" t="n">
         <v>4900</v>
@@ -31083,10 +31083,10 @@
         <v>24</v>
       </c>
       <c r="N709" t="n">
-        <v>32376.967005076</v>
+        <v>32295</v>
       </c>
       <c r="O709" t="n">
-        <v>777047.208121824</v>
+        <v>775080</v>
       </c>
       <c r="P709" t="n">
         <v>51900</v>
@@ -31589,10 +31589,10 @@
         <v>316</v>
       </c>
       <c r="N720" t="n">
-        <v>8872.340618996799</v>
+        <v>8858.16</v>
       </c>
       <c r="O720" t="n">
-        <v>2803659.635602988</v>
+        <v>2799178.56</v>
       </c>
       <c r="P720" t="n">
         <v>15500</v>
@@ -31911,10 +31911,10 @@
         <v>46</v>
       </c>
       <c r="N727" t="n">
-        <v>5040.7413333333</v>
+        <v>5014</v>
       </c>
       <c r="O727" t="n">
-        <v>231874.1013333318</v>
+        <v>230644</v>
       </c>
       <c r="P727" t="n">
         <v>8200</v>
@@ -32277,10 +32277,10 @@
         <v>664</v>
       </c>
       <c r="N735" t="n">
-        <v>2336.84913125</v>
+        <v>2328.11868125</v>
       </c>
       <c r="O735" t="n">
-        <v>1551667.82315</v>
+        <v>1545870.80435</v>
       </c>
       <c r="P735" t="n">
         <v>4500</v>
@@ -32415,10 +32415,10 @@
         <v>1</v>
       </c>
       <c r="N738" t="n">
-        <v>9384</v>
+        <v>9686.7096774194</v>
       </c>
       <c r="O738" t="n">
-        <v>9384</v>
+        <v>9686.7096774194</v>
       </c>
       <c r="P738" t="n">
         <v>15900</v>
@@ -32599,10 +32599,10 @@
         <v>32</v>
       </c>
       <c r="N742" t="n">
-        <v>35287.397849462</v>
+        <v>34912</v>
       </c>
       <c r="O742" t="n">
-        <v>1129196.731182784</v>
+        <v>1117184</v>
       </c>
       <c r="P742" t="n">
         <v>56900</v>
@@ -33335,10 +33335,10 @@
         <v>83</v>
       </c>
       <c r="N758" t="n">
-        <v>3922.9680788177</v>
+        <v>3903.7379310345</v>
       </c>
       <c r="O758" t="n">
-        <v>325606.3505418691</v>
+        <v>324010.2482758635</v>
       </c>
       <c r="P758" t="n">
         <v>7500</v>
@@ -34342,10 +34342,10 @@
         <v>37</v>
       </c>
       <c r="N780" t="n">
-        <v>7668.5070422535</v>
+        <v>7562</v>
       </c>
       <c r="O780" t="n">
-        <v>283734.7605633795</v>
+        <v>279794</v>
       </c>
       <c r="P780" t="n">
         <v>12900</v>
@@ -34388,10 +34388,10 @@
         <v>269</v>
       </c>
       <c r="N781" t="n">
-        <v>3901.1562753036</v>
+        <v>3898</v>
       </c>
       <c r="O781" t="n">
-        <v>1049411.038056668</v>
+        <v>1048562</v>
       </c>
       <c r="P781" t="n">
         <v>6900</v>
@@ -34434,10 +34434,10 @@
         <v>98</v>
       </c>
       <c r="N782" t="n">
-        <v>13606.546707504</v>
+        <v>13565</v>
       </c>
       <c r="O782" t="n">
-        <v>1333441.577335392</v>
+        <v>1329370</v>
       </c>
       <c r="P782" t="n">
         <v>22500</v>
@@ -34480,10 +34480,10 @@
         <v>69</v>
       </c>
       <c r="N783" t="n">
-        <v>7647.7960893855</v>
+        <v>7635</v>
       </c>
       <c r="O783" t="n">
-        <v>527697.9301675995</v>
+        <v>526815</v>
       </c>
       <c r="P783" t="n">
         <v>13900</v>
@@ -34526,10 +34526,10 @@
         <v>197</v>
       </c>
       <c r="N784" t="n">
-        <v>5690.8504672897</v>
+        <v>5682</v>
       </c>
       <c r="O784" t="n">
-        <v>1121097.542056071</v>
+        <v>1119354</v>
       </c>
       <c r="P784" t="n">
         <v>9900</v>
@@ -34572,10 +34572,10 @@
         <v>6</v>
       </c>
       <c r="N785" t="n">
-        <v>5465.19</v>
+        <v>5438</v>
       </c>
       <c r="O785" t="n">
-        <v>32791.14</v>
+        <v>32628</v>
       </c>
       <c r="P785" t="n">
         <v>8900</v>
@@ -35631,10 +35631,10 @@
         <v>57</v>
       </c>
       <c r="N808" t="n">
-        <v>5319.824120603</v>
+        <v>5215</v>
       </c>
       <c r="O808" t="n">
-        <v>303229.974874371</v>
+        <v>297255</v>
       </c>
       <c r="P808" t="n">
         <v>8900</v>
@@ -35907,10 +35907,10 @@
         <v>78</v>
       </c>
       <c r="N814" t="n">
-        <v>8721.0653753027</v>
+        <v>8700</v>
       </c>
       <c r="O814" t="n">
-        <v>680243.0992736106</v>
+        <v>678600</v>
       </c>
       <c r="P814" t="n">
         <v>14900</v>
@@ -36045,10 +36045,10 @@
         <v>10</v>
       </c>
       <c r="N817" t="n">
-        <v>21822.282548476</v>
+        <v>21762</v>
       </c>
       <c r="O817" t="n">
-        <v>218222.82548476</v>
+        <v>217620</v>
       </c>
       <c r="P817" t="n">
         <v>35900</v>
@@ -36137,10 +36137,10 @@
         <v>10</v>
       </c>
       <c r="N819" t="n">
-        <v>15512.396866841</v>
+        <v>15472</v>
       </c>
       <c r="O819" t="n">
-        <v>155123.96866841</v>
+        <v>154720</v>
       </c>
       <c r="P819" t="n">
         <v>25900</v>
@@ -36321,10 +36321,10 @@
         <v>433</v>
       </c>
       <c r="N823" t="n">
-        <v>5483.2964690207</v>
+        <v>5476</v>
       </c>
       <c r="O823" t="n">
-        <v>2374267.371085963</v>
+        <v>2371108</v>
       </c>
       <c r="P823" t="n">
         <v>8900</v>
@@ -36554,10 +36554,10 @@
         <v>13</v>
       </c>
       <c r="N828" t="n">
-        <v>38558.016</v>
+        <v>38252</v>
       </c>
       <c r="O828" t="n">
-        <v>501254.208</v>
+        <v>497276</v>
       </c>
       <c r="P828" t="n">
         <v>61900</v>
@@ -38433,10 +38433,10 @@
         <v>1</v>
       </c>
       <c r="N869" t="n">
-        <v>15733.897449664</v>
+        <v>15423.36</v>
       </c>
       <c r="O869" t="n">
-        <v>15733.897449664</v>
+        <v>15423.36</v>
       </c>
       <c r="P869" t="n">
         <v>24900</v>
@@ -41007,10 +41007,10 @@
         <v>605</v>
       </c>
       <c r="N926" t="n">
-        <v>3110.839841954</v>
+        <v>3110.8397979798</v>
       </c>
       <c r="O926" t="n">
-        <v>1882058.10438217</v>
+        <v>1882058.077777779</v>
       </c>
       <c r="P926" t="n">
         <v>4500</v>
@@ -42618,10 +42618,10 @@
         <v>6</v>
       </c>
       <c r="N962" t="n">
-        <v>18621.814408602</v>
+        <v>18423.71</v>
       </c>
       <c r="O962" t="n">
-        <v>111730.886451612</v>
+        <v>110542.26</v>
       </c>
       <c r="P962" t="n">
         <v>10000</v>
@@ -43522,10 +43522,10 @@
         <v>54</v>
       </c>
       <c r="N981" t="n">
-        <v>3098.3874489796</v>
+        <v>3067.0906122449</v>
       </c>
       <c r="O981" t="n">
-        <v>167312.9222448984</v>
+        <v>165622.8930612246</v>
       </c>
       <c r="P981" t="n">
         <v>7200</v>
@@ -44025,10 +44025,10 @@
         <v>1</v>
       </c>
       <c r="N992" t="n">
-        <v>10993.181190476</v>
+        <v>10737.525714286</v>
       </c>
       <c r="O992" t="n">
-        <v>10993.181190476</v>
+        <v>10737.525714286</v>
       </c>
       <c r="P992" t="n">
         <v>18900</v>
@@ -44821,10 +44821,10 @@
         <v>84</v>
       </c>
       <c r="N1009" t="n">
-        <v>24490.111557632</v>
+        <v>24338.47</v>
       </c>
       <c r="O1009" t="n">
-        <v>2057169.370841088</v>
+        <v>2044431.48</v>
       </c>
       <c r="P1009" t="n">
         <v>27900</v>
@@ -49898,10 +49898,10 @@
         <v>108</v>
       </c>
       <c r="N1124" t="n">
-        <v>4598.7284768212</v>
+        <v>4576</v>
       </c>
       <c r="O1124" t="n">
-        <v>496662.6754966896</v>
+        <v>494208</v>
       </c>
       <c r="P1124" t="n">
         <v>5900</v>
@@ -52408,10 +52408,10 @@
         <v>262</v>
       </c>
       <c r="N1179" t="n">
-        <v>4566.0211267606</v>
+        <v>4550</v>
       </c>
       <c r="O1179" t="n">
-        <v>1196297.535211277</v>
+        <v>1192100</v>
       </c>
       <c r="P1179" t="n">
         <v>5500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -11870,10 +11870,10 @@
         <v>181</v>
       </c>
       <c r="N271" t="n">
-        <v>2582.2554027233</v>
+        <v>2582.2553995381</v>
       </c>
       <c r="O271" t="n">
-        <v>467388.2278929173</v>
+        <v>467388.2273163961</v>
       </c>
       <c r="P271" t="n">
         <v>4500</v>
@@ -12446,10 +12446,10 @@
         <v>17</v>
       </c>
       <c r="N284" t="n">
-        <v>3230.0666176471</v>
+        <v>3230.0665925926</v>
       </c>
       <c r="O284" t="n">
-        <v>54911.1325000007</v>
+        <v>54911.1320740742</v>
       </c>
       <c r="P284" t="n">
         <v>6200</v>
@@ -16922,10 +16922,10 @@
         <v>80</v>
       </c>
       <c r="N385" t="n">
-        <v>11921.4</v>
+        <v>11949.297191888</v>
       </c>
       <c r="O385" t="n">
-        <v>953712</v>
+        <v>955943.7753510399</v>
       </c>
       <c r="P385" t="n">
         <v>19900</v>
@@ -17403,10 +17403,10 @@
         <v>368</v>
       </c>
       <c r="N396" t="n">
-        <v>1630.9240698598</v>
+        <v>1630.9240720148</v>
       </c>
       <c r="O396" t="n">
-        <v>600180.0577084065</v>
+        <v>600180.0585014464</v>
       </c>
       <c r="P396" t="n">
         <v>2500</v>
@@ -17582,10 +17582,10 @@
         <v>1955</v>
       </c>
       <c r="N400" t="n">
-        <v>1550.1941645158</v>
+        <v>1550.1941668538</v>
       </c>
       <c r="O400" t="n">
-        <v>3030629.591628389</v>
+        <v>3030629.596199179</v>
       </c>
       <c r="P400" t="n">
         <v>2500</v>
@@ -17674,10 +17674,10 @@
         <v>1041</v>
       </c>
       <c r="N402" t="n">
-        <v>2403.5147075539</v>
+        <v>2403.51472848</v>
       </c>
       <c r="O402" t="n">
-        <v>2502058.81056361</v>
+        <v>2502058.83234768</v>
       </c>
       <c r="P402" t="n">
         <v>3500</v>
@@ -28494,10 +28494,10 @@
         <v>433</v>
       </c>
       <c r="N653" t="n">
-        <v>1664.3470318725</v>
+        <v>1664.3469860279</v>
       </c>
       <c r="O653" t="n">
-        <v>720662.2648007926</v>
+        <v>720662.2449500806</v>
       </c>
       <c r="P653" t="n">
         <v>2900</v>
@@ -29653,10 +29653,10 @@
         <v>1</v>
       </c>
       <c r="N678" t="n">
-        <v>26956</v>
+        <v>28079.166666667</v>
       </c>
       <c r="O678" t="n">
-        <v>26956</v>
+        <v>28079.166666667</v>
       </c>
       <c r="P678" t="n">
         <v>44900</v>
@@ -33242,10 +33242,10 @@
         <v>58</v>
       </c>
       <c r="N756" t="n">
-        <v>3903.7383067896</v>
+        <v>3903.7383529412</v>
       </c>
       <c r="O756" t="n">
-        <v>226416.8217937968</v>
+        <v>226416.8244705896</v>
       </c>
       <c r="P756" t="n">
         <v>7500</v>
@@ -40688,10 +40688,10 @@
         <v>2566</v>
       </c>
       <c r="N919" t="n">
-        <v>517.29287307808</v>
+        <v>517.2929433161599</v>
       </c>
       <c r="O919" t="n">
-        <v>1327373.512318353</v>
+        <v>1327373.692549266</v>
       </c>
       <c r="P919" t="n">
         <v>900</v>
@@ -40914,10 +40914,10 @@
         <v>601</v>
       </c>
       <c r="N924" t="n">
-        <v>3110.8397028838</v>
+        <v>3110.8396848556</v>
       </c>
       <c r="O924" t="n">
-        <v>1869614.661433164</v>
+        <v>1869614.650598216</v>
       </c>
       <c r="P924" t="n">
         <v>4500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -17631,10 +17631,10 @@
         <v>968</v>
       </c>
       <c r="N401" t="n">
-        <v>2403.515543043</v>
+        <v>2403.5155820371</v>
       </c>
       <c r="O401" t="n">
-        <v>2326603.045665624</v>
+        <v>2326603.083411913</v>
       </c>
       <c r="P401" t="n">
         <v>3500</v>
@@ -40691,10 +40691,10 @@
         <v>597</v>
       </c>
       <c r="N919" t="n">
-        <v>3110.8396334311</v>
+        <v>3110.8396273474</v>
       </c>
       <c r="O919" t="n">
-        <v>1857171.261158367</v>
+        <v>1857171.257526398</v>
       </c>
       <c r="P919" t="n">
         <v>4500</v>
@@ -40913,10 +40913,10 @@
         <v>884</v>
       </c>
       <c r="N924" t="n">
-        <v>703.79488487659</v>
+        <v>703.79488357273</v>
       </c>
       <c r="O924" t="n">
-        <v>622154.6782309056</v>
+        <v>622154.6770782933</v>
       </c>
       <c r="P924" t="n">
         <v>900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1013,10 +1013,10 @@
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>27108.144192256</v>
+        <v>27000</v>
       </c>
       <c r="O15" t="n">
-        <v>786136.181575424</v>
+        <v>783000</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
@@ -1346,10 +1346,10 @@
         <v>8</v>
       </c>
       <c r="N23" t="n">
-        <v>27117.391304348</v>
+        <v>27000</v>
       </c>
       <c r="O23" t="n">
-        <v>216939.130434784</v>
+        <v>216000</v>
       </c>
       <c r="P23" t="n">
         <v>30000</v>
@@ -6592,10 +6592,10 @@
         <v>8</v>
       </c>
       <c r="N148" t="n">
-        <v>27229.787234043</v>
+        <v>27000</v>
       </c>
       <c r="O148" t="n">
-        <v>217838.297872344</v>
+        <v>216000</v>
       </c>
       <c r="P148" t="n">
         <v>20000</v>
@@ -12009,10 +12009,10 @@
         <v>82</v>
       </c>
       <c r="N274" t="n">
-        <v>5224.6087374335</v>
+        <v>5216.895993495</v>
       </c>
       <c r="O274" t="n">
-        <v>428417.916469547</v>
+        <v>427785.47146659</v>
       </c>
       <c r="P274" t="n">
         <v>8500</v>
@@ -13399,10 +13399,10 @@
         <v>23</v>
       </c>
       <c r="N305" t="n">
-        <v>4903.3514603175</v>
+        <v>4890.9300507937</v>
       </c>
       <c r="O305" t="n">
-        <v>112777.0835873025</v>
+        <v>112491.3911682551</v>
       </c>
       <c r="P305" t="n">
         <v>8200</v>
@@ -13586,10 +13586,10 @@
         <v>53</v>
       </c>
       <c r="N309" t="n">
-        <v>5928.7474048443</v>
+        <v>5888</v>
       </c>
       <c r="O309" t="n">
-        <v>314223.6124567479</v>
+        <v>312064</v>
       </c>
       <c r="P309" t="n">
         <v>9500</v>
@@ -14500,10 +14500,10 @@
         <v>64</v>
       </c>
       <c r="N330" t="n">
-        <v>8184.2747524752</v>
+        <v>8154</v>
       </c>
       <c r="O330" t="n">
-        <v>523793.5841584128</v>
+        <v>521856</v>
       </c>
       <c r="P330" t="n">
         <v>13500</v>
@@ -14546,10 +14546,10 @@
         <v>50</v>
       </c>
       <c r="N331" t="n">
-        <v>14831.411358927</v>
+        <v>14822.378829982</v>
       </c>
       <c r="O331" t="n">
-        <v>741570.56794635</v>
+        <v>741118.9414991001</v>
       </c>
       <c r="P331" t="n">
         <v>24900</v>
@@ -15031,10 +15031,10 @@
         <v>2</v>
       </c>
       <c r="N342" t="n">
-        <v>15071.76</v>
+        <v>14386.68</v>
       </c>
       <c r="O342" t="n">
-        <v>30143.52</v>
+        <v>28773.36</v>
       </c>
       <c r="P342" t="n">
         <v>21900</v>
@@ -16838,10 +16838,10 @@
         <v>99</v>
       </c>
       <c r="N383" t="n">
-        <v>11959.066350711</v>
+        <v>11921.4</v>
       </c>
       <c r="O383" t="n">
-        <v>1183947.568720389</v>
+        <v>1180218.6</v>
       </c>
       <c r="P383" t="n">
         <v>19900</v>
@@ -19082,10 +19082,10 @@
         <v>14</v>
       </c>
       <c r="N434" t="n">
-        <v>10907.343571429</v>
+        <v>10836.973636364</v>
       </c>
       <c r="O434" t="n">
-        <v>152702.810000006</v>
+        <v>151717.630909096</v>
       </c>
       <c r="P434" t="n">
         <v>19900</v>
@@ -19737,10 +19737,10 @@
         <v>2</v>
       </c>
       <c r="N449" t="n">
-        <v>17970.414</v>
+        <v>16336.74</v>
       </c>
       <c r="O449" t="n">
-        <v>35940.828</v>
+        <v>32673.48</v>
       </c>
       <c r="P449" t="n">
         <v>30900</v>
@@ -20291,10 +20291,10 @@
         <v>57</v>
       </c>
       <c r="N462" t="n">
-        <v>9460.065359477099</v>
+        <v>9338</v>
       </c>
       <c r="O462" t="n">
-        <v>539223.7254901946</v>
+        <v>532266</v>
       </c>
       <c r="P462" t="n">
         <v>15500</v>
@@ -21693,10 +21693,10 @@
         <v>42</v>
       </c>
       <c r="N496" t="n">
-        <v>22541.90975</v>
+        <v>22485.6955</v>
       </c>
       <c r="O496" t="n">
-        <v>946760.2095</v>
+        <v>944399.2110000001</v>
       </c>
       <c r="P496" t="n">
         <v>36500</v>
@@ -21857,10 +21857,10 @@
         <v>8</v>
       </c>
       <c r="N500" t="n">
-        <v>39703.055555556</v>
+        <v>38630</v>
       </c>
       <c r="O500" t="n">
-        <v>317624.444444448</v>
+        <v>309040</v>
       </c>
       <c r="P500" t="n">
         <v>46500</v>
@@ -21947,10 +21947,10 @@
         <v>49</v>
       </c>
       <c r="N502" t="n">
-        <v>24573.894298246</v>
+        <v>24538.02</v>
       </c>
       <c r="O502" t="n">
-        <v>1204120.820614054</v>
+        <v>1202362.98</v>
       </c>
       <c r="P502" t="n">
         <v>52900</v>
@@ -22403,10 +22403,10 @@
         <v>6</v>
       </c>
       <c r="N513" t="n">
-        <v>33243.75</v>
+        <v>26595</v>
       </c>
       <c r="O513" t="n">
-        <v>199462.5</v>
+        <v>159570</v>
       </c>
       <c r="P513" t="n">
         <v>39900</v>
@@ -23822,10 +23822,10 @@
         <v>25</v>
       </c>
       <c r="N546" t="n">
-        <v>12393.103448276</v>
+        <v>11980</v>
       </c>
       <c r="O546" t="n">
-        <v>309827.5862069</v>
+        <v>299500</v>
       </c>
       <c r="P546" t="n">
         <v>19500</v>
@@ -23868,10 +23868,10 @@
         <v>48</v>
       </c>
       <c r="N547" t="n">
-        <v>11594.699548023</v>
+        <v>11562.038418079</v>
       </c>
       <c r="O547" t="n">
-        <v>556545.578305104</v>
+        <v>554977.8440677921</v>
       </c>
       <c r="P547" t="n">
         <v>18500</v>
@@ -23960,10 +23960,10 @@
         <v>62</v>
       </c>
       <c r="N549" t="n">
-        <v>12056.245617021</v>
+        <v>12005.159829787</v>
       </c>
       <c r="O549" t="n">
-        <v>747487.2282553021</v>
+        <v>744319.9094467941</v>
       </c>
       <c r="P549" t="n">
         <v>19500</v>
@@ -24682,10 +24682,10 @@
         <v>5</v>
       </c>
       <c r="N566" t="n">
-        <v>22690.398811881</v>
+        <v>21418.04</v>
       </c>
       <c r="O566" t="n">
-        <v>113451.994059405</v>
+        <v>107090.2</v>
       </c>
       <c r="P566" t="n">
         <v>34900</v>
@@ -25255,10 +25255,10 @@
         <v>29</v>
       </c>
       <c r="N579" t="n">
-        <v>27232.25996</v>
+        <v>27123.76488</v>
       </c>
       <c r="O579" t="n">
-        <v>789735.5388399999</v>
+        <v>786589.18152</v>
       </c>
       <c r="P579" t="n">
         <v>44500</v>
@@ -25772,10 +25772,10 @@
         <v>17</v>
       </c>
       <c r="N591" t="n">
-        <v>6334.8235294118</v>
+        <v>5668</v>
       </c>
       <c r="O591" t="n">
-        <v>107692.0000000006</v>
+        <v>96356</v>
       </c>
       <c r="P591" t="n">
         <v>9900</v>
@@ -25818,10 +25818,10 @@
         <v>31</v>
       </c>
       <c r="N592" t="n">
-        <v>27011.040935673</v>
+        <v>26854</v>
       </c>
       <c r="O592" t="n">
-        <v>837342.269005863</v>
+        <v>832474</v>
       </c>
       <c r="P592" t="n">
         <v>43900</v>
@@ -26123,10 +26123,10 @@
         <v>26</v>
       </c>
       <c r="N599" t="n">
-        <v>10317.12016129</v>
+        <v>9994.710161290301</v>
       </c>
       <c r="O599" t="n">
-        <v>268245.12419354</v>
+        <v>259862.4641935478</v>
       </c>
       <c r="P599" t="n">
         <v>20800</v>
@@ -26456,10 +26456,10 @@
         <v>24</v>
       </c>
       <c r="N607" t="n">
-        <v>13079.564264151</v>
+        <v>12981.59</v>
       </c>
       <c r="O607" t="n">
-        <v>313909.542339624</v>
+        <v>311558.16</v>
       </c>
       <c r="P607" t="n">
         <v>21900</v>
@@ -26502,10 +26502,10 @@
         <v>51</v>
       </c>
       <c r="N608" t="n">
-        <v>13974.031438356</v>
+        <v>13878.97</v>
       </c>
       <c r="O608" t="n">
-        <v>712675.603356156</v>
+        <v>707827.47</v>
       </c>
       <c r="P608" t="n">
         <v>21900</v>
@@ -26707,10 +26707,10 @@
         <v>27</v>
       </c>
       <c r="N613" t="n">
-        <v>23309.866666667</v>
+        <v>21853</v>
       </c>
       <c r="O613" t="n">
-        <v>629366.400000009</v>
+        <v>590031</v>
       </c>
       <c r="P613" t="n">
         <v>37200</v>
@@ -26789,10 +26789,10 @@
         <v>6</v>
       </c>
       <c r="N615" t="n">
-        <v>10448</v>
+        <v>7836</v>
       </c>
       <c r="O615" t="n">
-        <v>62688</v>
+        <v>47016</v>
       </c>
       <c r="P615" t="n">
         <v>13400</v>
@@ -31651,10 +31651,10 @@
         <v>27</v>
       </c>
       <c r="N721" t="n">
-        <v>27408.335664336</v>
+        <v>27218</v>
       </c>
       <c r="O721" t="n">
-        <v>740025.062937072</v>
+        <v>734886</v>
       </c>
       <c r="P721" t="n">
         <v>43900</v>
@@ -31697,10 +31697,10 @@
         <v>1</v>
       </c>
       <c r="N722" t="n">
-        <v>21456.861702128</v>
+        <v>21231</v>
       </c>
       <c r="O722" t="n">
-        <v>21456.861702128</v>
+        <v>21231</v>
       </c>
       <c r="P722" t="n">
         <v>34500</v>
@@ -31743,10 +31743,10 @@
         <v>8</v>
       </c>
       <c r="N723" t="n">
-        <v>23419.958333333</v>
+        <v>22942</v>
       </c>
       <c r="O723" t="n">
-        <v>187359.666666664</v>
+        <v>183536</v>
       </c>
       <c r="P723" t="n">
         <v>36900</v>
@@ -32339,10 +32339,10 @@
         <v>72</v>
       </c>
       <c r="N736" t="n">
-        <v>9198.3277962348</v>
+        <v>9178</v>
       </c>
       <c r="O736" t="n">
-        <v>662279.6013289057</v>
+        <v>660816</v>
       </c>
       <c r="P736" t="n">
         <v>14900</v>
@@ -32385,10 +32385,10 @@
         <v>378</v>
       </c>
       <c r="N737" t="n">
-        <v>4567.8948290973</v>
+        <v>4544</v>
       </c>
       <c r="O737" t="n">
-        <v>1726664.24539878</v>
+        <v>1717632</v>
       </c>
       <c r="P737" t="n">
         <v>7900</v>
@@ -32477,10 +32477,10 @@
         <v>22</v>
       </c>
       <c r="N739" t="n">
-        <v>13948.467680608</v>
+        <v>13922</v>
       </c>
       <c r="O739" t="n">
-        <v>306866.288973376</v>
+        <v>306284</v>
       </c>
       <c r="P739" t="n">
         <v>22900</v>
@@ -32569,10 +32569,10 @@
         <v>21</v>
       </c>
       <c r="N741" t="n">
-        <v>25260.382352941</v>
+        <v>25076</v>
       </c>
       <c r="O741" t="n">
-        <v>530468.029411761</v>
+        <v>526596</v>
       </c>
       <c r="P741" t="n">
         <v>40900</v>
@@ -33346,10 +33346,10 @@
         <v>69</v>
       </c>
       <c r="N758" t="n">
-        <v>10198.963414634</v>
+        <v>9839</v>
       </c>
       <c r="O758" t="n">
-        <v>703728.4756097459</v>
+        <v>678891</v>
       </c>
       <c r="P758" t="n">
         <v>16900</v>
@@ -33668,10 +33668,10 @@
         <v>42</v>
       </c>
       <c r="N765" t="n">
-        <v>14306.769230769</v>
+        <v>14090</v>
       </c>
       <c r="O765" t="n">
-        <v>600884.307692298</v>
+        <v>591780</v>
       </c>
       <c r="P765" t="n">
         <v>22900</v>
@@ -33760,10 +33760,10 @@
         <v>79</v>
       </c>
       <c r="N767" t="n">
-        <v>13121.945155393</v>
+        <v>13098</v>
       </c>
       <c r="O767" t="n">
-        <v>1036633.667276047</v>
+        <v>1034742</v>
       </c>
       <c r="P767" t="n">
         <v>21200</v>
@@ -34453,10 +34453,10 @@
         <v>166</v>
       </c>
       <c r="N782" t="n">
-        <v>17123.621290098</v>
+        <v>17075.989518828</v>
       </c>
       <c r="O782" t="n">
-        <v>2842521.134156268</v>
+        <v>2834614.260125448</v>
       </c>
       <c r="P782" t="n">
         <v>27500</v>
@@ -34499,10 +34499,10 @@
         <v>2</v>
       </c>
       <c r="N783" t="n">
-        <v>145341.6</v>
+        <v>121118</v>
       </c>
       <c r="O783" t="n">
-        <v>290683.2</v>
+        <v>242236</v>
       </c>
       <c r="P783" t="n">
         <v>193900</v>
@@ -34770,10 +34770,10 @@
         <v>4</v>
       </c>
       <c r="N789" t="n">
-        <v>21666.992481203</v>
+        <v>21346</v>
       </c>
       <c r="O789" t="n">
-        <v>86667.969924812</v>
+        <v>85384</v>
       </c>
       <c r="P789" t="n">
         <v>34900</v>
@@ -34957,10 +34957,10 @@
         <v>55</v>
       </c>
       <c r="N793" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O793" t="n">
-        <v>952929.3251533549</v>
+        <v>944240</v>
       </c>
       <c r="P793" t="n">
         <v>27900</v>
@@ -35003,10 +35003,10 @@
         <v>5</v>
       </c>
       <c r="N794" t="n">
-        <v>20944.88372093</v>
+        <v>20014</v>
       </c>
       <c r="O794" t="n">
-        <v>104724.41860465</v>
+        <v>100070</v>
       </c>
       <c r="P794" t="n">
         <v>33900</v>
@@ -35049,10 +35049,10 @@
         <v>90</v>
       </c>
       <c r="N795" t="n">
-        <v>27289.075933076</v>
+        <v>27254</v>
       </c>
       <c r="O795" t="n">
-        <v>2456016.83397684</v>
+        <v>2452860</v>
       </c>
       <c r="P795" t="n">
         <v>43900</v>
@@ -35371,10 +35371,10 @@
         <v>51</v>
       </c>
       <c r="N802" t="n">
-        <v>40316.604863222</v>
+        <v>40073</v>
       </c>
       <c r="O802" t="n">
-        <v>2056146.848024322</v>
+        <v>2043723</v>
       </c>
       <c r="P802" t="n">
         <v>64900</v>
@@ -35463,10 +35463,10 @@
         <v>70</v>
       </c>
       <c r="N804" t="n">
-        <v>8721.297429620599</v>
+        <v>8700</v>
       </c>
       <c r="O804" t="n">
-        <v>610490.820073442</v>
+        <v>609000</v>
       </c>
       <c r="P804" t="n">
         <v>14900</v>
@@ -42416,10 +42416,10 @@
         <v>16</v>
       </c>
       <c r="N957" t="n">
-        <v>10639.697586207</v>
+        <v>10548.76</v>
       </c>
       <c r="O957" t="n">
-        <v>170235.161379312</v>
+        <v>168780.16</v>
       </c>
       <c r="P957" t="n">
         <v>35900</v>
@@ -42893,10 +42893,10 @@
         <v>26</v>
       </c>
       <c r="N967" t="n">
-        <v>7184.3863636364</v>
+        <v>6773.85</v>
       </c>
       <c r="O967" t="n">
-        <v>186794.0454545464</v>
+        <v>176120.1</v>
       </c>
       <c r="P967" t="n">
         <v>9500</v>
@@ -43346,10 +43346,10 @@
         <v>1</v>
       </c>
       <c r="N977" t="n">
-        <v>2830.7108053691</v>
+        <v>2356.29</v>
       </c>
       <c r="O977" t="n">
-        <v>2830.7108053691</v>
+        <v>2356.29</v>
       </c>
       <c r="P977" t="n">
         <v>6500</v>
@@ -44377,10 +44377,10 @@
         <v>79</v>
       </c>
       <c r="N999" t="n">
-        <v>24492.510949367</v>
+        <v>24338.47</v>
       </c>
       <c r="O999" t="n">
-        <v>1934908.364999993</v>
+        <v>1922739.13</v>
       </c>
       <c r="P999" t="n">
         <v>27900</v>
